--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="2151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="2152">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19125843048096</t>
+    <t xml:space="preserve">5.19125890731812</t>
   </si>
   <si>
     <t xml:space="preserve">MB.MI</t>
@@ -47,64 +47,64 @@
     <t xml:space="preserve">5.18521547317505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0552830696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95858907699585</t>
+    <t xml:space="preserve">5.05528211593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95858860015869</t>
   </si>
   <si>
     <t xml:space="preserve">4.83772134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81052684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92535066604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97974014282227</t>
+    <t xml:space="preserve">4.81052541732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92535018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97974061965942</t>
   </si>
   <si>
     <t xml:space="preserve">4.91930770874023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73196172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50533628463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59900760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41468524932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65944194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67455053329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52346611022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59598636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52648735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27870941162109</t>
+    <t xml:space="preserve">4.73196220397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50533485412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59900856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41468477249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65944147109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67455005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52346563339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59598684310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52648687362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27870893478394</t>
   </si>
   <si>
     <t xml:space="preserve">4.4509449005127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31194829940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19410085678101</t>
+    <t xml:space="preserve">4.31194734573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19410181045532</t>
   </si>
   <si>
     <t xml:space="preserve">4.00373554229736</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">4.09136438369751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98862743377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6169593334198</t>
+    <t xml:space="preserve">3.98862719535828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61696004867554</t>
   </si>
   <si>
     <t xml:space="preserve">3.41450667381287</t>
@@ -125,103 +125,103 @@
     <t xml:space="preserve">3.67134976387024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47796225547791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54443907737732</t>
+    <t xml:space="preserve">3.47796177864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5444393157959</t>
   </si>
   <si>
     <t xml:space="preserve">3.64717650413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68041515350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74991393089294</t>
+    <t xml:space="preserve">3.680415391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991345405579</t>
   </si>
   <si>
     <t xml:space="preserve">3.64113283157349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61091661453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75595760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66228485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62300324440002</t>
+    <t xml:space="preserve">3.61091613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75595784187317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66228437423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62300300598145</t>
   </si>
   <si>
     <t xml:space="preserve">3.67437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76804399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78315281867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93725776672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08834266662598</t>
+    <t xml:space="preserve">3.76804447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78315210342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93725824356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08834218978882</t>
   </si>
   <si>
     <t xml:space="preserve">4.1034517288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02488708496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006302833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96143174171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97351861000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03395318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38446807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42979288101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28173112869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29986047744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03697395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07323455810547</t>
+    <t xml:space="preserve">4.0248875617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006374359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96143221855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97351908683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0339527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38446855545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42979335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28173017501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29986095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03697347640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07323503494263</t>
   </si>
   <si>
     <t xml:space="preserve">4.0943865776062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01884412765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8798463344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90402030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82545638084412</t>
+    <t xml:space="preserve">4.01884365081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99164891242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87984609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9040195941925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82545614242554</t>
   </si>
   <si>
     <t xml:space="preserve">3.79221749305725</t>
@@ -230,49 +230,49 @@
     <t xml:space="preserve">3.8314995765686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75897884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79523921012878</t>
+    <t xml:space="preserve">3.75897836685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79523944854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.60487294197083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81336975097656</t>
+    <t xml:space="preserve">3.81336879730225</t>
   </si>
   <si>
     <t xml:space="preserve">3.85567307472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77408719062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97049713134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04301738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97654056549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23036241531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338413238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36936044692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38749074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39655542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33612108230591</t>
+    <t xml:space="preserve">3.77408742904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97049736976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04301786422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97654008865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23036193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2333836555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36935997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38749027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39655494689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33612155914307</t>
   </si>
   <si>
     <t xml:space="preserve">4.21223163604736</t>
@@ -284,139 +284,139 @@
     <t xml:space="preserve">3.88588929176331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85265159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80430436134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078166007996</t>
+    <t xml:space="preserve">3.85265064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80430388450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87078142166138</t>
   </si>
   <si>
     <t xml:space="preserve">3.8979766368866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93423700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9221498966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90704154968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97956275939941</t>
+    <t xml:space="preserve">3.93423676490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92215013504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90704131126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97956252098083</t>
   </si>
   <si>
     <t xml:space="preserve">4.0158224105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21827507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31496953964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30590438842773</t>
+    <t xml:space="preserve">4.21827602386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31496858596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30590534210205</t>
   </si>
   <si>
     <t xml:space="preserve">4.3572735786438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34518671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13366889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10647344589233</t>
+    <t xml:space="preserve">4.34518623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13366842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10647249221802</t>
   </si>
   <si>
     <t xml:space="preserve">4.00071382522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98560547828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610717773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70156717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52026557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38731122016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48098373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46889686584473</t>
+    <t xml:space="preserve">3.98560523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9161069393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70156693458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5202648639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38731169700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48098397254944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46889662742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.60789442062378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80732560157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85869431495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83452153205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2090322971344</t>
+    <t xml:space="preserve">3.80732703208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85869479179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8345205783844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20903182029724</t>
   </si>
   <si>
     <t xml:space="preserve">2.79929113388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96125340461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06399083137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11535978317261</t>
+    <t xml:space="preserve">2.96125364303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0639910697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11536002159119</t>
   </si>
   <si>
     <t xml:space="preserve">3.14557647705078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0132269859314</t>
+    <t xml:space="preserve">3.01322650909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.91653251647949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84763789176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94554018974304</t>
+    <t xml:space="preserve">2.84763813018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9455406665802</t>
   </si>
   <si>
     <t xml:space="preserve">3.19694519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44472408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47191858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57767772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52630853652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58674311637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55350375175476</t>
+    <t xml:space="preserve">3.44472360610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47191834449768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57767820358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5263090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58674240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55350399017334</t>
   </si>
   <si>
     <t xml:space="preserve">3.59580755233765</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">3.61998128890991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53537368774414</t>
+    <t xml:space="preserve">3.53537392616272</t>
   </si>
   <si>
     <t xml:space="preserve">3.65926337242126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61393809318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78617382049561</t>
+    <t xml:space="preserve">3.613938331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78617405891418</t>
   </si>
   <si>
     <t xml:space="preserve">3.71365332603455</t>
@@ -446,58 +446,58 @@
     <t xml:space="preserve">3.40846300125122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42054986953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71969652175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96747589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94028067588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099787712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308522224426</t>
+    <t xml:space="preserve">3.42055034637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71969723701477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96747493743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94028043746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099763870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9130847454071</t>
   </si>
   <si>
     <t xml:space="preserve">3.84962964057922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81639099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69552302360535</t>
+    <t xml:space="preserve">3.8163914680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80128312110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69552326202393</t>
   </si>
   <si>
     <t xml:space="preserve">3.72876191139221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92517185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89495515823364</t>
+    <t xml:space="preserve">3.9251720905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89495491981506</t>
   </si>
   <si>
     <t xml:space="preserve">3.95236706733704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0490608215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14273309707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19107961654663</t>
+    <t xml:space="preserve">4.04905986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14273357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07927751541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19108009338379</t>
   </si>
   <si>
     <t xml:space="preserve">4.15481996536255</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73178386688232</t>
+    <t xml:space="preserve">3.7317841053009</t>
   </si>
   <si>
     <t xml:space="preserve">3.7891960144043</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.77106547355652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77710962295532</t>
+    <t xml:space="preserve">3.77710890769958</t>
   </si>
   <si>
     <t xml:space="preserve">3.49609231948853</t>
@@ -527,70 +527,70 @@
     <t xml:space="preserve">3.54141736030579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47494029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4991135597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49004864692688</t>
+    <t xml:space="preserve">3.47494077682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49911379814148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49004912376404</t>
   </si>
   <si>
     <t xml:space="preserve">3.49307060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68343710899353</t>
+    <t xml:space="preserve">3.68343663215637</t>
   </si>
   <si>
     <t xml:space="preserve">3.7801308631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65321969985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74387049674988</t>
+    <t xml:space="preserve">3.65322041511536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74387001991272</t>
   </si>
   <si>
     <t xml:space="preserve">3.87380266189575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9946711063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10949516296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15784215927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23640584945679</t>
+    <t xml:space="preserve">3.99467086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10949468612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15784168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23640632629395</t>
   </si>
   <si>
     <t xml:space="preserve">4.06114768981934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84358692169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00977897644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14575529098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13971090316772</t>
+    <t xml:space="preserve">3.84358596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00977945327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14575481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13971138000488</t>
   </si>
   <si>
     <t xml:space="preserve">4.25453567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26964473724365</t>
+    <t xml:space="preserve">4.26964426040649</t>
   </si>
   <si>
     <t xml:space="preserve">4.20618867874146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11251640319824</t>
+    <t xml:space="preserve">4.1125168800354</t>
   </si>
   <si>
     <t xml:space="preserve">3.94632387161255</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">3.99360370635986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06294870376587</t>
+    <t xml:space="preserve">4.06294822692871</t>
   </si>
   <si>
     <t xml:space="preserve">4.00306034088135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96208381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9084997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7950267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95577907562256</t>
+    <t xml:space="preserve">3.96208333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90849947929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79502701759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95577955245972</t>
   </si>
   <si>
     <t xml:space="preserve">4.10392427444458</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">4.23946094512939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05979681015015</t>
+    <t xml:space="preserve">4.05979633331299</t>
   </si>
   <si>
     <t xml:space="preserve">4.46325397491455</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">4.67759132385254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80682373046875</t>
+    <t xml:space="preserve">4.80682325363159</t>
   </si>
   <si>
     <t xml:space="preserve">4.67128705978394</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">4.95181703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89508008956909</t>
+    <t xml:space="preserve">4.89507961273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.91714477539062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98964071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95496892929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.939208984375</t>
+    <t xml:space="preserve">4.98964023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95496845245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93920850753784</t>
   </si>
   <si>
     <t xml:space="preserve">5.00224876403809</t>
@@ -677,103 +677,103 @@
     <t xml:space="preserve">4.93605661392212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89823246002197</t>
+    <t xml:space="preserve">4.89823198318481</t>
   </si>
   <si>
     <t xml:space="preserve">4.8887767791748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99279260635376</t>
+    <t xml:space="preserve">4.99279308319092</t>
   </si>
   <si>
     <t xml:space="preserve">5.1377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1693058013916</t>
+    <t xml:space="preserve">5.16930627822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.14408922195435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16300106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92975282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98333644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98018503189087</t>
+    <t xml:space="preserve">5.163001537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92975234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98333692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98018455505371</t>
   </si>
   <si>
     <t xml:space="preserve">4.86356019973755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05898427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04007339477539</t>
+    <t xml:space="preserve">5.05898475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04007291793823</t>
   </si>
   <si>
     <t xml:space="preserve">5.00540113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08420181274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01170444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08735275268555</t>
+    <t xml:space="preserve">5.08420133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01170492172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08735322952271</t>
   </si>
   <si>
     <t xml:space="preserve">5.3710355758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53809118270874</t>
+    <t xml:space="preserve">5.53809070587158</t>
   </si>
   <si>
     <t xml:space="preserve">5.36157894134521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29538631439209</t>
+    <t xml:space="preserve">5.29538583755493</t>
   </si>
   <si>
     <t xml:space="preserve">5.15354585647583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01485681533813</t>
+    <t xml:space="preserve">5.01485729217529</t>
   </si>
   <si>
     <t xml:space="preserve">5.13463354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92344808578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8194317817688</t>
+    <t xml:space="preserve">4.92344856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943130493164</t>
   </si>
   <si>
     <t xml:space="preserve">4.96757698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91084051132202</t>
+    <t xml:space="preserve">4.91084003448486</t>
   </si>
   <si>
     <t xml:space="preserve">5.05583333969116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17561006546021</t>
+    <t xml:space="preserve">5.17560958862305</t>
   </si>
   <si>
     <t xml:space="preserve">5.14724159240723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11887407302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07159376144409</t>
+    <t xml:space="preserve">5.11887311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07159328460693</t>
   </si>
   <si>
     <t xml:space="preserve">5.0243124961853</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">4.97388076782227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82888746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69335174560547</t>
+    <t xml:space="preserve">4.82888793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69335126876831</t>
   </si>
   <si>
     <t xml:space="preserve">4.72802352905273</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">4.76900005340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94866418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9959454536438</t>
+    <t xml:space="preserve">4.94866466522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99594497680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.17245721817017</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">5.21658515930176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22604179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30169010162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24810600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23549842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2512583732605</t>
+    <t xml:space="preserve">5.2260422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30169057846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24810647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23549795150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25125789642334</t>
   </si>
   <si>
     <t xml:space="preserve">5.26071500778198</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">5.33636236190796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27962684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.339515209198</t>
+    <t xml:space="preserve">5.27962636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33951473236084</t>
   </si>
   <si>
     <t xml:space="preserve">5.31745100021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35212230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32690715789795</t>
+    <t xml:space="preserve">5.35212182998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32690620422363</t>
   </si>
   <si>
     <t xml:space="preserve">5.19767379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20713043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20397853851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23865032196045</t>
+    <t xml:space="preserve">5.20712995529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20397806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23864984512329</t>
   </si>
   <si>
     <t xml:space="preserve">5.13148212432861</t>
@@ -869,40 +869,40 @@
     <t xml:space="preserve">5.38364267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46559476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38994646072388</t>
+    <t xml:space="preserve">5.46559429168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38994693756104</t>
   </si>
   <si>
     <t xml:space="preserve">5.35527467727661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56330728530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57906818389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59798002243042</t>
+    <t xml:space="preserve">5.563307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57906770706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59797954559326</t>
   </si>
   <si>
     <t xml:space="preserve">5.70830106735229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78710126876831</t>
+    <t xml:space="preserve">5.78710031509399</t>
   </si>
   <si>
     <t xml:space="preserve">5.75242900848389</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73666858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72090768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79340410232544</t>
+    <t xml:space="preserve">5.7366681098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72090816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7934045791626</t>
   </si>
   <si>
     <t xml:space="preserve">5.76188516616821</t>
@@ -911,22 +911,22 @@
     <t xml:space="preserve">5.78394889831543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62319612503052</t>
+    <t xml:space="preserve">5.62319660186768</t>
   </si>
   <si>
     <t xml:space="preserve">5.64210796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68938779830933</t>
+    <t xml:space="preserve">5.68938875198364</t>
   </si>
   <si>
     <t xml:space="preserve">5.73036479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76818895339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73982048034668</t>
+    <t xml:space="preserve">5.7681884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73982000350952</t>
   </si>
   <si>
     <t xml:space="preserve">5.71460437774658</t>
@@ -935,19 +935,19 @@
     <t xml:space="preserve">5.62949991226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45298671722412</t>
+    <t xml:space="preserve">5.45298624038696</t>
   </si>
   <si>
     <t xml:space="preserve">5.32060194015503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34266757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2544093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27332258224487</t>
+    <t xml:space="preserve">5.3426661491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25441026687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27332162857056</t>
   </si>
   <si>
     <t xml:space="preserve">5.36473083496094</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">5.37418651580811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39309930801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29223442077637</t>
+    <t xml:space="preserve">5.3930983543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29223489761353</t>
   </si>
   <si>
     <t xml:space="preserve">5.21028184890747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35842657089233</t>
+    <t xml:space="preserve">5.35842609405518</t>
   </si>
   <si>
     <t xml:space="preserve">5.34581851959229</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">5.54754781723022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59482860565186</t>
+    <t xml:space="preserve">5.5948281288147</t>
   </si>
   <si>
     <t xml:space="preserve">5.52548360824585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56015539169312</t>
+    <t xml:space="preserve">5.56015634536743</t>
   </si>
   <si>
     <t xml:space="preserve">5.59167575836182</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">5.67678022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49081182479858</t>
+    <t xml:space="preserve">5.49081134796143</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972270965576</t>
@@ -1028,190 +1028,190 @@
     <t xml:space="preserve">5.60743618011475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58221960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55700302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5443959236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67993259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67047643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48450756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53493928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47505140304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38049077987671</t>
+    <t xml:space="preserve">5.58221912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55700254440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54439544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67993307113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67047548294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61058712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48450708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53493976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52863550186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47505187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38049030303955</t>
   </si>
   <si>
     <t xml:space="preserve">5.43407487869263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3300576210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50026845932007</t>
+    <t xml:space="preserve">5.33005809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50026750564575</t>
   </si>
   <si>
     <t xml:space="preserve">5.56646013259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5065712928772</t>
+    <t xml:space="preserve">5.50657081604004</t>
   </si>
   <si>
     <t xml:space="preserve">5.51602792739868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58537197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66732454299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65471601486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69254016876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72406053543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75873279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71145248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79970836639404</t>
+    <t xml:space="preserve">5.58537101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66732358932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65471649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69253969192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72406005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75873231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71145343780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79970932006836</t>
   </si>
   <si>
     <t xml:space="preserve">5.74612474441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77449226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74927663803101</t>
+    <t xml:space="preserve">5.7744927406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74927616119385</t>
   </si>
   <si>
     <t xml:space="preserve">5.77764415740967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78079652786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77134037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8186206817627</t>
+    <t xml:space="preserve">5.78079605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77134084701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81862020492554</t>
   </si>
   <si>
     <t xml:space="preserve">5.91633319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9762225151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93209362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01404523849487</t>
+    <t xml:space="preserve">5.97622203826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93209409713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01404571533203</t>
   </si>
   <si>
     <t xml:space="preserve">6.07708644866943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05187129974365</t>
+    <t xml:space="preserve">6.05187034606934</t>
   </si>
   <si>
     <t xml:space="preserve">6.03295803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10860633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10230207443237</t>
+    <t xml:space="preserve">6.10860538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10230255126953</t>
   </si>
   <si>
     <t xml:space="preserve">6.2315354347229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21577596664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2252311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21892690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20001459121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23178100585938</t>
+    <t xml:space="preserve">6.21577405929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22523021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21892642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2000150680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23178052902222</t>
   </si>
   <si>
     <t xml:space="preserve">6.13353872299194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20885801315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20558261871338</t>
+    <t xml:space="preserve">6.20885753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20558309555054</t>
   </si>
   <si>
     <t xml:space="preserve">6.16956090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09751796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22850656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34966993331909</t>
+    <t xml:space="preserve">6.0975170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22850608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34967041015625</t>
   </si>
   <si>
     <t xml:space="preserve">6.28745126724243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33329725265503</t>
+    <t xml:space="preserve">6.33329629898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.29399967193604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19903373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22195625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28090047836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28417539596558</t>
+    <t xml:space="preserve">6.19903326034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2219557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382394790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28090143203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28417587280273</t>
   </si>
   <si>
     <t xml:space="preserve">6.25470352172852</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">6.1237154006958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15646171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18593454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24160528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26452732086182</t>
+    <t xml:space="preserve">6.15646123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1859335899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24160480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26452779769897</t>
   </si>
   <si>
     <t xml:space="preserve">6.26125335693359</t>
@@ -1241,76 +1241,76 @@
     <t xml:space="preserve">6.19575881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14663743972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27107667922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41843891143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39879131317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40206527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39224100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41188955307007</t>
+    <t xml:space="preserve">6.14663791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27107810974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41843938827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39879083633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40206575393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39224147796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41189002990723</t>
   </si>
   <si>
     <t xml:space="preserve">6.49375772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51995468139648</t>
+    <t xml:space="preserve">6.51995515823364</t>
   </si>
   <si>
     <t xml:space="preserve">6.57562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53305530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52977895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4872088432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43808746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45380687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36604356765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41319894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51406049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45642518997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26780223846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36997318267822</t>
+    <t xml:space="preserve">6.5330548286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5297794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48720836639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43808698654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45380544662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36604404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41319942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47607326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51406097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45642614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26780128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36997270584106</t>
   </si>
   <si>
     <t xml:space="preserve">6.32019805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36473417282104</t>
+    <t xml:space="preserve">6.36473369598389</t>
   </si>
   <si>
     <t xml:space="preserve">6.41581916809082</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">6.47214412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44594717025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46690511703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47869443893433</t>
+    <t xml:space="preserve">6.44594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4669041633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47869300842285</t>
   </si>
   <si>
     <t xml:space="preserve">6.40010070800781</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">6.46166515350342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4747633934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51013088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674646377563</t>
+    <t xml:space="preserve">6.47476434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51013135910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41974973678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674694061279</t>
   </si>
   <si>
     <t xml:space="preserve">6.2101674079895</t>
@@ -1358,22 +1358,22 @@
     <t xml:space="preserve">6.44463777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46559524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45904541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39748096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42498826980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45773649215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40664911270142</t>
+    <t xml:space="preserve">6.46559476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45904588699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39748001098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42498779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45773506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40665006637573</t>
   </si>
   <si>
     <t xml:space="preserve">6.47738456726074</t>
@@ -1385,127 +1385,127 @@
     <t xml:space="preserve">6.25732278823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21671676635742</t>
+    <t xml:space="preserve">6.21671628952026</t>
   </si>
   <si>
     <t xml:space="preserve">6.24684381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25339460372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27828168869019</t>
+    <t xml:space="preserve">6.25339412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27828073501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.35294485092163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34508562088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41713047027588</t>
+    <t xml:space="preserve">6.34508609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41712951660156</t>
   </si>
   <si>
     <t xml:space="preserve">6.39355134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54811763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63457059860229</t>
+    <t xml:space="preserve">6.54811811447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63457012176514</t>
   </si>
   <si>
     <t xml:space="preserve">6.66076803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79503107070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84415245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70661497116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69351625442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67386674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55925226211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69679069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72953605651855</t>
+    <t xml:space="preserve">6.79503154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84415149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70661449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69351482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67386627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55925273895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69678974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72953653335571</t>
   </si>
   <si>
     <t xml:space="preserve">6.5494270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46428537368774</t>
+    <t xml:space="preserve">6.46428442001343</t>
   </si>
   <si>
     <t xml:space="preserve">6.51537036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56907606124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52191972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20754766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01499557495117</t>
+    <t xml:space="preserve">6.56907558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5219202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20754671096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01499462127686</t>
   </si>
   <si>
     <t xml:space="preserve">5.915442943573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95343017578125</t>
+    <t xml:space="preserve">5.95342969894409</t>
   </si>
   <si>
     <t xml:space="preserve">5.81327247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58011293411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24085283279419</t>
+    <t xml:space="preserve">5.58011341094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24085235595703</t>
   </si>
   <si>
     <t xml:space="preserve">5.0312705039978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38624906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28407764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4216160774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32861375808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19238615036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35874176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23823261260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12689208984375</t>
+    <t xml:space="preserve">5.38624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2840781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42161655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32861423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19238662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35874223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23823213577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12689161300659</t>
   </si>
   <si>
     <t xml:space="preserve">5.37708044052124</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">5.3050365447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40327739715576</t>
+    <t xml:space="preserve">5.40327787399292</t>
   </si>
   <si>
     <t xml:space="preserve">5.34826278686523</t>
@@ -1523,28 +1523,28 @@
     <t xml:space="preserve">5.28276872634888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26049995422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4425745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38755893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52378749847412</t>
+    <t xml:space="preserve">5.26050043106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44257497787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38755941390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5237865447998</t>
   </si>
   <si>
     <t xml:space="preserve">5.33254384994507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29848766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21727418899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18321657180786</t>
+    <t xml:space="preserve">5.29848718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21727466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18321752548218</t>
   </si>
   <si>
     <t xml:space="preserve">5.21465444564819</t>
@@ -1553,58 +1553,58 @@
     <t xml:space="preserve">5.18845653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25133037567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32206535339355</t>
+    <t xml:space="preserve">5.25133180618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32206630706787</t>
   </si>
   <si>
     <t xml:space="preserve">5.39148902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30634593963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34040355682373</t>
+    <t xml:space="preserve">5.30634641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34040403366089</t>
   </si>
   <si>
     <t xml:space="preserve">5.26835918426514</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17928791046143</t>
+    <t xml:space="preserve">5.17928743362427</t>
   </si>
   <si>
     <t xml:space="preserve">5.20155572891235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2709789276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28931856155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33778381347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32468461990356</t>
+    <t xml:space="preserve">5.27097988128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2893180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33778285980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32468509674072</t>
   </si>
   <si>
     <t xml:space="preserve">5.3561224937439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51330852508545</t>
+    <t xml:space="preserve">5.51330804824829</t>
   </si>
   <si>
     <t xml:space="preserve">5.57618284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.628577709198</t>
+    <t xml:space="preserve">5.62857818603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.73205900192261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68097352981567</t>
+    <t xml:space="preserve">5.68097305297852</t>
   </si>
   <si>
     <t xml:space="preserve">5.81851148605347</t>
@@ -1613,31 +1613,31 @@
     <t xml:space="preserve">5.74646759033203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68752288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78052425384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68490314483643</t>
+    <t xml:space="preserve">5.68752336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78052473068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68490362167358</t>
   </si>
   <si>
     <t xml:space="preserve">5.75956630706787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75563669204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76742553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70848083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59583139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44912338256836</t>
+    <t xml:space="preserve">5.75563716888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76742601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7084813117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5958309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44912385940552</t>
   </si>
   <si>
     <t xml:space="preserve">5.56439352035522</t>
@@ -1646,76 +1646,76 @@
     <t xml:space="preserve">5.50283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51985740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61023998260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43340492248535</t>
+    <t xml:space="preserve">5.51985788345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61023950576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758958816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43340444564819</t>
   </si>
   <si>
     <t xml:space="preserve">5.43864440917969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42816543579102</t>
+    <t xml:space="preserve">5.42816591262817</t>
   </si>
   <si>
     <t xml:space="preserve">5.39541816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41899728775024</t>
+    <t xml:space="preserve">5.41899681091309</t>
   </si>
   <si>
     <t xml:space="preserve">5.25002145767212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55522441864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73598861694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68621301651001</t>
+    <t xml:space="preserve">5.55522489547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73598957061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68621349334717</t>
   </si>
   <si>
     <t xml:space="preserve">5.93771123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90627384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9364013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89710426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91282272338867</t>
+    <t xml:space="preserve">5.90627336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93640089035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89710474014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91282320022583</t>
   </si>
   <si>
     <t xml:space="preserve">6.01368379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03333234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09620761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00844478607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00713539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96390914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07524967193604</t>
+    <t xml:space="preserve">6.03333330154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09620714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00844430923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00713491439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96390867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07524871826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.06476974487305</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">6.00451564788818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63512802124023</t>
+    <t xml:space="preserve">5.63512754440308</t>
   </si>
   <si>
     <t xml:space="preserve">5.46353244781494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4884204864502</t>
+    <t xml:space="preserve">5.48842000961304</t>
   </si>
   <si>
     <t xml:space="preserve">5.48056125640869</t>
@@ -1742,34 +1742,34 @@
     <t xml:space="preserve">5.13737058639526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18059730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07187700271606</t>
+    <t xml:space="preserve">5.18059682846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07187604904175</t>
   </si>
   <si>
     <t xml:space="preserve">5.02865028381348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0351996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11379337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05484771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00638246536255</t>
+    <t xml:space="preserve">5.03520011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11379289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05484819412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00638198852539</t>
   </si>
   <si>
     <t xml:space="preserve">5.15963888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06663751602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07842683792114</t>
+    <t xml:space="preserve">5.06663703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07842588424683</t>
   </si>
   <si>
     <t xml:space="preserve">4.90683174133301</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">5.09545469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95791673660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09938383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11248397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07711601257324</t>
+    <t xml:space="preserve">4.95791721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09938430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11248254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07711553573608</t>
   </si>
   <si>
     <t xml:space="preserve">5.19500637054443</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">5.13868093490601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15309000015259</t>
+    <t xml:space="preserve">5.15308952331543</t>
   </si>
   <si>
     <t xml:space="preserve">5.14915990829468</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">5.08104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15818929672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690242767334</t>
+    <t xml:space="preserve">5.15818977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0369029045105</t>
   </si>
   <si>
     <t xml:space="preserve">5.08987855911255</t>
@@ -1823,22 +1823,22 @@
     <t xml:space="preserve">5.08011960983276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11776065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34499979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36730480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39100503921509</t>
+    <t xml:space="preserve">5.117760181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34499931335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36730527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39100551605225</t>
   </si>
   <si>
     <t xml:space="preserve">5.44258689880371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44119310379028</t>
+    <t xml:space="preserve">5.44119262695312</t>
   </si>
   <si>
     <t xml:space="preserve">5.47604560852051</t>
@@ -1847,28 +1847,28 @@
     <t xml:space="preserve">5.37706422805786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38821697235107</t>
+    <t xml:space="preserve">5.38821649551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.22650098800659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22231864929199</t>
+    <t xml:space="preserve">5.22231912612915</t>
   </si>
   <si>
     <t xml:space="preserve">5.10242509841919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07733154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24462366104126</t>
+    <t xml:space="preserve">5.07733106613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24462413787842</t>
   </si>
   <si>
     <t xml:space="preserve">5.26553583145142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31293535232544</t>
+    <t xml:space="preserve">5.31293487548828</t>
   </si>
   <si>
     <t xml:space="preserve">5.23068332672119</t>
@@ -1877,52 +1877,52 @@
     <t xml:space="preserve">5.27668857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3728814125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25577688217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12751913070679</t>
+    <t xml:space="preserve">5.37288188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25577640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12751865386963</t>
   </si>
   <si>
     <t xml:space="preserve">5.04944944381714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14146089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09127283096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08709049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38961029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37985229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36312294006348</t>
+    <t xml:space="preserve">5.14145994186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09127235412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08708953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3896107673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37985181808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36312341690063</t>
   </si>
   <si>
     <t xml:space="preserve">5.33524084091187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33802843093872</t>
+    <t xml:space="preserve">5.33802890777588</t>
   </si>
   <si>
     <t xml:space="preserve">5.40494632720947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34639453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33942317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46210479736328</t>
+    <t xml:space="preserve">5.34639406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33942222595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46210384368896</t>
   </si>
   <si>
     <t xml:space="preserve">5.46907520294189</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">5.49138069152832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50671625137329</t>
+    <t xml:space="preserve">5.50671577453613</t>
   </si>
   <si>
     <t xml:space="preserve">5.48859262466431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49277544021606</t>
+    <t xml:space="preserve">5.49277496337891</t>
   </si>
   <si>
     <t xml:space="preserve">5.50253391265869</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">5.55969190597534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48998689651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4481635093689</t>
+    <t xml:space="preserve">5.48998641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44816303253174</t>
   </si>
   <si>
     <t xml:space="preserve">5.45931673049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29481220245361</t>
+    <t xml:space="preserve">5.29481172561646</t>
   </si>
   <si>
     <t xml:space="preserve">5.14424848556519</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">5.11218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28505373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39797592163086</t>
+    <t xml:space="preserve">5.28505325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3979754447937</t>
   </si>
   <si>
     <t xml:space="preserve">5.40355205535889</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">5.5262336730957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62521457672119</t>
+    <t xml:space="preserve">5.62521553039551</t>
   </si>
   <si>
     <t xml:space="preserve">5.59036254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78971862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77717304229736</t>
+    <t xml:space="preserve">5.789719581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80366086959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77717256546021</t>
   </si>
   <si>
     <t xml:space="preserve">5.79808330535889</t>
@@ -2000,31 +2000,31 @@
     <t xml:space="preserve">5.73953151702881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75486660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82735919952393</t>
+    <t xml:space="preserve">5.75486612319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82735967636108</t>
   </si>
   <si>
     <t xml:space="preserve">5.91797685623169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98071193695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14939785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02532291412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07969284057617</t>
+    <t xml:space="preserve">5.98071146011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14939832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02532339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07969331741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.08945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20376825332642</t>
+    <t xml:space="preserve">6.20376777648926</t>
   </si>
   <si>
     <t xml:space="preserve">6.10060501098633</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">6.03786945343018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12430429458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10339307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18982791900635</t>
+    <t xml:space="preserve">6.12430477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10339212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18982744216919</t>
   </si>
   <si>
     <t xml:space="preserve">6.21631574630737</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">6.26510858535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39894342422485</t>
+    <t xml:space="preserve">6.39894390106201</t>
   </si>
   <si>
     <t xml:space="preserve">6.35990810394287</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">6.24001550674438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28602075576782</t>
+    <t xml:space="preserve">6.28602027893066</t>
   </si>
   <si>
     <t xml:space="preserve">6.23583316802979</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">6.22467994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35293769836426</t>
+    <t xml:space="preserve">6.35293817520142</t>
   </si>
   <si>
     <t xml:space="preserve">6.42264318466187</t>
@@ -2078,19 +2078,19 @@
     <t xml:space="preserve">6.45610189437866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5188364982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4254322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44076633453369</t>
+    <t xml:space="preserve">6.51883697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42543172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44076585769653</t>
   </si>
   <si>
     <t xml:space="preserve">6.47840642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52162504196167</t>
+    <t xml:space="preserve">6.52162456512451</t>
   </si>
   <si>
     <t xml:space="preserve">6.46446704864502</t>
@@ -2099,34 +2099,34 @@
     <t xml:space="preserve">6.4853777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.578782081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63175916671753</t>
+    <t xml:space="preserve">6.57878160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63175964355469</t>
   </si>
   <si>
     <t xml:space="preserve">6.6707935333252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69867563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67915916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62199974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54392910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52441263198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56205320358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194675445557</t>
+    <t xml:space="preserve">6.69867610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67915821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62199926376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54392957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52441167831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56205368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194627761841</t>
   </si>
   <si>
     <t xml:space="preserve">6.58714723587036</t>
@@ -2138,22 +2138,22 @@
     <t xml:space="preserve">6.41706705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26789665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34875535964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20237493515015</t>
+    <t xml:space="preserve">6.26789712905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3487548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20237445831299</t>
   </si>
   <si>
     <t xml:space="preserve">6.06435823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22049713134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18146276473999</t>
+    <t xml:space="preserve">6.22049760818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18146228790283</t>
   </si>
   <si>
     <t xml:space="preserve">6.16612768173218</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">5.95980024337769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91937065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84269571304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83433055877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76601982116699</t>
+    <t xml:space="preserve">5.91937112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84269523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83433103561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">5.7325611114502</t>
@@ -2189,37 +2189,37 @@
     <t xml:space="preserve">5.88172960281372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84966564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87894201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96816444396973</t>
+    <t xml:space="preserve">5.84966611862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87894248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96816492080688</t>
   </si>
   <si>
     <t xml:space="preserve">5.9667706489563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93888854980469</t>
+    <t xml:space="preserve">5.93888902664185</t>
   </si>
   <si>
     <t xml:space="preserve">5.97374105453491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94307136535645</t>
+    <t xml:space="preserve">5.94307088851929</t>
   </si>
   <si>
     <t xml:space="preserve">5.94167709350586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07132911682129</t>
+    <t xml:space="preserve">6.07132863998413</t>
   </si>
   <si>
     <t xml:space="preserve">6.16333961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382171630859</t>
+    <t xml:space="preserve">6.14382219314575</t>
   </si>
   <si>
     <t xml:space="preserve">6.19122171401978</t>
@@ -2228,37 +2228,37 @@
     <t xml:space="preserve">6.17031002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29577922821045</t>
+    <t xml:space="preserve">6.29577970504761</t>
   </si>
   <si>
     <t xml:space="preserve">6.33760261535645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31947898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23862075805664</t>
+    <t xml:space="preserve">6.31947946548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2386212348938</t>
   </si>
   <si>
     <t xml:space="preserve">6.30972051620483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47422504425049</t>
+    <t xml:space="preserve">6.47422456741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.60248279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5704174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51186609268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49095439910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55229473114014</t>
+    <t xml:space="preserve">6.57041788101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51186561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49095487594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55229377746582</t>
   </si>
   <si>
     <t xml:space="preserve">6.54114198684692</t>
@@ -2267,55 +2267,55 @@
     <t xml:space="preserve">6.54671859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4979248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56762981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53277730941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950618743896</t>
+    <t xml:space="preserve">6.49792385101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56762933731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53277683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950666427612</t>
   </si>
   <si>
     <t xml:space="preserve">6.41288423538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44355440139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51465320587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48956108093262</t>
+    <t xml:space="preserve">6.44355535507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51465368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4895601272583</t>
   </si>
   <si>
     <t xml:space="preserve">6.50350093841553</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33481502532959</t>
+    <t xml:space="preserve">6.33481550216675</t>
   </si>
   <si>
     <t xml:space="preserve">6.31111478805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32087373733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15915727615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10478734970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03647661209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08666372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92494773864746</t>
+    <t xml:space="preserve">6.32087326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15915679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10478782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03647565841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0866641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9249472618103</t>
   </si>
   <si>
     <t xml:space="preserve">5.91379451751709</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">5.97652959823608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06714677810669</t>
+    <t xml:space="preserve">6.06714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">6.11315155029297</t>
@@ -2342,175 +2342,175 @@
     <t xml:space="preserve">6.04344606399536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872816085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13963890075684</t>
+    <t xml:space="preserve">6.11872720718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13963985443115</t>
   </si>
   <si>
     <t xml:space="preserve">6.1926155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28044414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35712003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296585083008</t>
+    <t xml:space="preserve">6.28044462203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35711908340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296537399292</t>
   </si>
   <si>
     <t xml:space="preserve">6.59829998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68055295944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63036489486694</t>
+    <t xml:space="preserve">6.68055200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63036441802979</t>
   </si>
   <si>
     <t xml:space="preserve">6.66382360458374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72655773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66242790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63454723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76141119003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100879669189</t>
+    <t xml:space="preserve">6.72655820846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66242837905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63454627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7614107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100927352905</t>
   </si>
   <si>
     <t xml:space="preserve">6.89803266525269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90779256820679</t>
+    <t xml:space="preserve">6.90779161453247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94682598114014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04371690750122</t>
+    <t xml:space="preserve">7.04371738433838</t>
   </si>
   <si>
     <t xml:space="preserve">6.95379734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98446702957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95658540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76419973373413</t>
+    <t xml:space="preserve">6.98446750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95658493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76419925689697</t>
   </si>
   <si>
     <t xml:space="preserve">6.8464503288269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83390378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79347562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80462789535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03326034545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19009733200073</t>
+    <t xml:space="preserve">6.8157811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83390331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79347515106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80462837219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03326082229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19009780883789</t>
   </si>
   <si>
     <t xml:space="preserve">7.27025938034058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37481737136841</t>
+    <t xml:space="preserve">7.37481689453125</t>
   </si>
   <si>
     <t xml:space="preserve">7.40269947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38178730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36087656021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.430579662323</t>
+    <t xml:space="preserve">7.38178634643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36087560653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43058013916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.5037727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55953550338745</t>
+    <t xml:space="preserve">7.55953693389893</t>
   </si>
   <si>
     <t xml:space="preserve">7.552565574646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58044672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44103670120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42361068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48286056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6431827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59438896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51422595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27374458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42012691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35390615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51857423782349</t>
+    <t xml:space="preserve">7.58044719696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44103765487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4236102104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48286104202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64318227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59438943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51422691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27374505996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42012596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35390520095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51857471466064</t>
   </si>
   <si>
     <t xml:space="preserve">7.48940467834473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46752691268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52586650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669694900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47481966018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52951335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40189361572266</t>
+    <t xml:space="preserve">7.46752738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52586603164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669599533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47481918334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52951240539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40189456939697</t>
   </si>
   <si>
     <t xml:space="preserve">7.33261585235596</t>
@@ -2519,40 +2519,40 @@
     <t xml:space="preserve">7.29250621795654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35449266433716</t>
+    <t xml:space="preserve">7.35449314117432</t>
   </si>
   <si>
     <t xml:space="preserve">7.32532262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3471999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22687482833862</t>
+    <t xml:space="preserve">7.34720087051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22687435150146</t>
   </si>
   <si>
     <t xml:space="preserve">7.3727240562439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38366270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24437665939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31438493728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28229665756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35813856124878</t>
+    <t xml:space="preserve">7.38366317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24437570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31438446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28229713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35813903808594</t>
   </si>
   <si>
     <t xml:space="preserve">7.28521394729614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21958112716675</t>
+    <t xml:space="preserve">7.21958017349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.15686559677124</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">7.22979068756104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16415929794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18457746505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020980834961</t>
+    <t xml:space="preserve">7.16415882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18457841873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25021076202393</t>
   </si>
   <si>
     <t xml:space="preserve">7.26187801361084</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">7.15832424163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11019325256348</t>
+    <t xml:space="preserve">7.11019468307495</t>
   </si>
   <si>
     <t xml:space="preserve">7.05768775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0781078338623</t>
+    <t xml:space="preserve">7.07810688018799</t>
   </si>
   <si>
     <t xml:space="preserve">6.99643039703369</t>
@@ -2603,58 +2603,58 @@
     <t xml:space="preserve">6.93809127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97309541702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77328014373779</t>
+    <t xml:space="preserve">6.97309446334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77327966690063</t>
   </si>
   <si>
     <t xml:space="preserve">6.98622131347656</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93371534347534</t>
+    <t xml:space="preserve">6.9337158203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.75286102294922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57200765609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71931600570679</t>
+    <t xml:space="preserve">6.5720067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71931552886963</t>
   </si>
   <si>
     <t xml:space="preserve">6.8053674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98038625717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86954116821289</t>
+    <t xml:space="preserve">6.98038721084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86954164505005</t>
   </si>
   <si>
     <t xml:space="preserve">7.00372409820557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04164505004883</t>
+    <t xml:space="preserve">7.04164409637451</t>
   </si>
   <si>
     <t xml:space="preserve">7.0606050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06206464767456</t>
+    <t xml:space="preserve">7.06206321716309</t>
   </si>
   <si>
     <t xml:space="preserve">7.00518178939819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03289270401001</t>
+    <t xml:space="preserve">7.03289318084717</t>
   </si>
   <si>
     <t xml:space="preserve">6.99351358413696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86370754241943</t>
+    <t xml:space="preserve">6.86370658874512</t>
   </si>
   <si>
     <t xml:space="preserve">6.45240926742554</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">6.42178106307983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38677787780762</t>
+    <t xml:space="preserve">6.38677835464478</t>
   </si>
   <si>
     <t xml:space="preserve">6.23363494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97256183624268</t>
+    <t xml:space="preserve">5.97256231307983</t>
   </si>
   <si>
     <t xml:space="preserve">5.76253890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71003293991089</t>
+    <t xml:space="preserve">5.71003246307373</t>
   </si>
   <si>
     <t xml:space="preserve">5.63564920425415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39937210083008</t>
+    <t xml:space="preserve">5.39937162399292</t>
   </si>
   <si>
     <t xml:space="preserve">5.28415012359619</t>
@@ -2690,28 +2690,28 @@
     <t xml:space="preserve">4.52281284332275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21215152740479</t>
+    <t xml:space="preserve">4.21215200424194</t>
   </si>
   <si>
     <t xml:space="preserve">4.33174896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52228045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7760603427887</t>
+    <t xml:space="preserve">3.52228093147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77605986595154</t>
   </si>
   <si>
     <t xml:space="preserve">3.33850979804993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25537538528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06649923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0424337387085</t>
+    <t xml:space="preserve">3.25537514686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06649899482727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04243397712708</t>
   </si>
   <si>
     <t xml:space="preserve">3.10150289535522</t>
@@ -2723,22 +2723,22 @@
     <t xml:space="preserve">3.6185417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90440797805786</t>
+    <t xml:space="preserve">3.90440773963928</t>
   </si>
   <si>
     <t xml:space="preserve">4.01087856292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76439237594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62802195549011</t>
+    <t xml:space="preserve">3.76439213752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62802171707153</t>
   </si>
   <si>
     <t xml:space="preserve">3.66667199134827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64917039871216</t>
+    <t xml:space="preserve">3.64917016029358</t>
   </si>
   <si>
     <t xml:space="preserve">3.77460169792175</t>
@@ -2753,103 +2753,103 @@
     <t xml:space="preserve">4.05171680450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05900907516479</t>
+    <t xml:space="preserve">4.05900955200195</t>
   </si>
   <si>
     <t xml:space="preserve">4.04150676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87232112884521</t>
+    <t xml:space="preserve">3.87232136726379</t>
   </si>
   <si>
     <t xml:space="preserve">3.57989120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64771151542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69292521476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56239008903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51571774482727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73959755897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82419037818909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02254676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85627770423889</t>
+    <t xml:space="preserve">3.64771175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69292497634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56238961219788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51571750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73959732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82419013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545506477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02254629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85627746582031</t>
   </si>
   <si>
     <t xml:space="preserve">3.79939603805542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76585054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75855803489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74834847450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78918671607971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607618331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85336017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68271613121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56311869621277</t>
+    <t xml:space="preserve">3.76585030555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75855731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74834799766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78918647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607594490051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.853360414505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68271589279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56311893463135</t>
   </si>
   <si>
     <t xml:space="preserve">3.80960536003113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74980711936951</t>
+    <t xml:space="preserve">3.74980688095093</t>
   </si>
   <si>
     <t xml:space="preserve">3.69730067253113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168440818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78481149673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921083450317</t>
+    <t xml:space="preserve">3.77168464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78481125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921059608459</t>
   </si>
   <si>
     <t xml:space="preserve">4.16256284713745</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31862211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25590705871582</t>
+    <t xml:space="preserve">4.31862306594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25590753555298</t>
   </si>
   <si>
     <t xml:space="preserve">4.60011339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69929075241089</t>
+    <t xml:space="preserve">4.69929122924805</t>
   </si>
   <si>
     <t xml:space="preserve">4.95452976226807</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">4.95307064056396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18351316452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34540748596191</t>
+    <t xml:space="preserve">5.18351364135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34540700912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.17330408096313</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">4.86410236358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9647388458252</t>
+    <t xml:space="preserve">4.96473836898804</t>
   </si>
   <si>
     <t xml:space="preserve">5.03766345977783</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">5.12079811096191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97348976135254</t>
+    <t xml:space="preserve">4.97348928451538</t>
   </si>
   <si>
     <t xml:space="preserve">4.99682569503784</t>
@@ -2900,28 +2900,28 @@
     <t xml:space="preserve">4.71095943450928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75033855438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55927467346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76200675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65991115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71533489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91952466964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90348196029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92535924911499</t>
+    <t xml:space="preserve">4.75033903121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55927562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76200723648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65991163253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71533536911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91952514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90348148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92535877227783</t>
   </si>
   <si>
     <t xml:space="preserve">4.93119287490845</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">4.92973470687866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05078983306885</t>
+    <t xml:space="preserve">5.05079030990601</t>
   </si>
   <si>
     <t xml:space="preserve">5.13830041885376</t>
@@ -2957,55 +2957,55 @@
     <t xml:space="preserve">5.25498008728027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.316237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22435188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16309452056885</t>
+    <t xml:space="preserve">5.31623697280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22435235977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16309404373169</t>
   </si>
   <si>
     <t xml:space="preserve">5.12663221359253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07850217819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05954122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9224419593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94286108016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73283672332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81305408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94723606109619</t>
+    <t xml:space="preserve">5.07850170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05954074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92244148254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73283624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81305456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94723653793335</t>
   </si>
   <si>
     <t xml:space="preserve">4.91369104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97786569595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27248287200928</t>
+    <t xml:space="preserve">4.97786521911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27248191833496</t>
   </si>
   <si>
     <t xml:space="preserve">5.28706741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29436016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20247364044189</t>
+    <t xml:space="preserve">5.29435968399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20247411727905</t>
   </si>
   <si>
     <t xml:space="preserve">5.1149640083313</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">5.12809133529663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09746217727661</t>
+    <t xml:space="preserve">5.09746170043945</t>
   </si>
   <si>
     <t xml:space="preserve">5.24768781661987</t>
@@ -3038,31 +3038,31 @@
     <t xml:space="preserve">5.31040382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33519792556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32061243057251</t>
+    <t xml:space="preserve">5.33519840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32061290740967</t>
   </si>
   <si>
     <t xml:space="preserve">5.2272686958313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21414184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08141899108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17768001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39207983016968</t>
+    <t xml:space="preserve">5.21414232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08141851425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17767953872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39207935333252</t>
   </si>
   <si>
     <t xml:space="preserve">5.28269195556641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29873514175415</t>
+    <t xml:space="preserve">5.29873466491699</t>
   </si>
   <si>
     <t xml:space="preserve">5.18643093109131</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">4.76054859161377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95161151885986</t>
+    <t xml:space="preserve">4.95161199569702</t>
   </si>
   <si>
     <t xml:space="preserve">4.87576961517334</t>
@@ -3092,19 +3092,19 @@
     <t xml:space="preserve">4.88452100753784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84368276596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92390012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08871173858643</t>
+    <t xml:space="preserve">4.84368371963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92390060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08871126174927</t>
   </si>
   <si>
     <t xml:space="preserve">5.20976686477661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08579397201538</t>
+    <t xml:space="preserve">5.08579444885254</t>
   </si>
   <si>
     <t xml:space="preserve">5.28560924530029</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">5.23310279846191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.203932762146</t>
+    <t xml:space="preserve">5.20393323898315</t>
   </si>
   <si>
     <t xml:space="preserve">5.0114107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02016115188599</t>
+    <t xml:space="preserve">5.02016162872314</t>
   </si>
   <si>
     <t xml:space="preserve">4.82180595397949</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">4.74596309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78971862792969</t>
+    <t xml:space="preserve">4.78971767425537</t>
   </si>
   <si>
     <t xml:space="preserve">4.76638221740723</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">4.64095115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4105076789856</t>
+    <t xml:space="preserve">4.41050815582275</t>
   </si>
   <si>
     <t xml:space="preserve">4.46884775161743</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">4.43967819213867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59427881240845</t>
+    <t xml:space="preserve">4.59427928924561</t>
   </si>
   <si>
     <t xml:space="preserve">4.85680913925171</t>
@@ -3170,22 +3170,22 @@
     <t xml:space="preserve">5.1966404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2053918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51605272293091</t>
+    <t xml:space="preserve">5.20539093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51605176925659</t>
   </si>
   <si>
     <t xml:space="preserve">5.59626913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51459312438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58460092544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4985499382019</t>
+    <t xml:space="preserve">5.51459360122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58460140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49854946136475</t>
   </si>
   <si>
     <t xml:space="preserve">5.72899341583252</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">5.70419883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63710784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45041942596436</t>
+    <t xml:space="preserve">5.63710689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4504189491272</t>
   </si>
   <si>
     <t xml:space="preserve">5.52917909622192</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">5.46500444412231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54230499267578</t>
+    <t xml:space="preserve">5.54230451583862</t>
   </si>
   <si>
     <t xml:space="preserve">5.60210371017456</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">5.49709129333496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4752140045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34978294372559</t>
+    <t xml:space="preserve">5.47521352767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34978246688843</t>
   </si>
   <si>
     <t xml:space="preserve">5.36145114898682</t>
@@ -3236,31 +3236,31 @@
     <t xml:space="preserve">5.53792905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49271678924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.428542137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39062070846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37895345687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52042770385742</t>
+    <t xml:space="preserve">5.49271583557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42854166030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39062118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3789529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52042722702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.52480316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40228843688965</t>
+    <t xml:space="preserve">5.40228891372681</t>
   </si>
   <si>
     <t xml:space="preserve">5.42270803451538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62835645675659</t>
+    <t xml:space="preserve">5.62835597991943</t>
   </si>
   <si>
     <t xml:space="preserve">5.61231327056885</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">5.50438404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46208763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51021862030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46938037872314</t>
+    <t xml:space="preserve">5.46208715438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51021814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46937990188599</t>
   </si>
   <si>
     <t xml:space="preserve">5.44750213623047</t>
@@ -3284,43 +3284,43 @@
     <t xml:space="preserve">5.38186979293823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47083806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40083026885986</t>
+    <t xml:space="preserve">5.47083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40083074569702</t>
   </si>
   <si>
     <t xml:space="preserve">5.40520572662354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44896125793457</t>
+    <t xml:space="preserve">5.44896078109741</t>
   </si>
   <si>
     <t xml:space="preserve">5.35707569122314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39499616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.370201587677</t>
+    <t xml:space="preserve">5.39499568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37020206451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.51167678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73045206069946</t>
+    <t xml:space="preserve">5.7304515838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.89963817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97985553741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17383575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23071765899658</t>
+    <t xml:space="preserve">5.97985506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17383623123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23071813583374</t>
   </si>
   <si>
     <t xml:space="preserve">6.41740608215332</t>
@@ -3329,16 +3329,16 @@
     <t xml:space="preserve">6.5063738822937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48012113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59242630004883</t>
+    <t xml:space="preserve">6.48012161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59242582321167</t>
   </si>
   <si>
     <t xml:space="preserve">6.53700351715088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57929992675781</t>
+    <t xml:space="preserve">6.57930040359497</t>
   </si>
   <si>
     <t xml:space="preserve">6.54429531097412</t>
@@ -3347,70 +3347,70 @@
     <t xml:space="preserve">6.62159585952759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61430311203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58221626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53408670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3955283164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28468227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5019998550415</t>
+    <t xml:space="preserve">6.61430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5822172164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53408622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39552783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28468179702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50199937820435</t>
   </si>
   <si>
     <t xml:space="preserve">6.43490886688232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52679300308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6113862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72514963150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77473926544189</t>
+    <t xml:space="preserve">6.52679347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61138677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7251501083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535871505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77473878860474</t>
   </si>
   <si>
     <t xml:space="preserve">6.85058116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86516523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90162801742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01976728439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09415006637573</t>
+    <t xml:space="preserve">6.86516571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9016284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01976776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09415054321289</t>
   </si>
   <si>
     <t xml:space="preserve">7.09706783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87975072860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84037113189697</t>
+    <t xml:space="preserve">6.87975025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84037160873413</t>
   </si>
   <si>
     <t xml:space="preserve">6.77911376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90016984939575</t>
+    <t xml:space="preserve">6.90016937255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.90600395202637</t>
@@ -3422,10 +3422,10 @@
     <t xml:space="preserve">6.9395489692688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89579486846924</t>
+    <t xml:space="preserve">7.0358099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89579439163208</t>
   </si>
   <si>
     <t xml:space="preserve">6.84912252426147</t>
@@ -3437,46 +3437,46 @@
     <t xml:space="preserve">6.77182197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80682468414307</t>
+    <t xml:space="preserve">6.80682563781738</t>
   </si>
   <si>
     <t xml:space="preserve">6.81849384307861</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80974388122559</t>
+    <t xml:space="preserve">6.80974245071411</t>
   </si>
   <si>
     <t xml:space="preserve">6.78640651702881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85203886032104</t>
+    <t xml:space="preserve">6.8520393371582</t>
   </si>
   <si>
     <t xml:space="preserve">6.84766435623169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70910596847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64201498031616</t>
+    <t xml:space="preserve">6.7091064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64201402664185</t>
   </si>
   <si>
     <t xml:space="preserve">6.65805864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64639043807983</t>
+    <t xml:space="preserve">6.64639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">6.8359956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80828428268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82724475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85641527175903</t>
+    <t xml:space="preserve">6.80828523635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82724571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85641574859619</t>
   </si>
   <si>
     <t xml:space="preserve">6.92788076400757</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">6.78057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90892028808594</t>
+    <t xml:space="preserve">6.90892124176025</t>
   </si>
   <si>
     <t xml:space="preserve">6.94684219360352</t>
@@ -3497,64 +3497,64 @@
     <t xml:space="preserve">7.05477094650269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01393270492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08393955230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13352918624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19770336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0591459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06643867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11748600006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14811611175537</t>
+    <t xml:space="preserve">7.01393222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08394002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13352966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19770383834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05914640426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0664381980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915372848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11748695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14811563491821</t>
   </si>
   <si>
     <t xml:space="preserve">7.21228981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27062845230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344533920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29979991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25604391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2677116394043</t>
+    <t xml:space="preserve">7.2706298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034462928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2997989654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25604343414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26771116256714</t>
   </si>
   <si>
     <t xml:space="preserve">7.20791339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2633376121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25458526611328</t>
+    <t xml:space="preserve">7.26333665847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25458478927612</t>
   </si>
   <si>
     <t xml:space="preserve">7.23270845413208</t>
@@ -3566,94 +3566,94 @@
     <t xml:space="preserve">7.15394878387451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17582750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22249889373779</t>
+    <t xml:space="preserve">7.17582702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22249841690063</t>
   </si>
   <si>
     <t xml:space="preserve">7.28083896636963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27500486373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20062112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18311834335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19332933425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1874942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36178588867188</t>
+    <t xml:space="preserve">7.27500438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20062065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18311977386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19332885742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18749475479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36178541183472</t>
   </si>
   <si>
     <t xml:space="preserve">7.1408224105835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14957332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92350673675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165285110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1889533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20499610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14519929885864</t>
+    <t xml:space="preserve">7.14957284927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92350578308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18895244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20499658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14519786834717</t>
   </si>
   <si>
     <t xml:space="preserve">7.09560871124268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86808252334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9555926322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23416566848755</t>
+    <t xml:space="preserve">6.86808300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95559310913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23416614532471</t>
   </si>
   <si>
     <t xml:space="preserve">7.3107385635376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28667259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28813171386719</t>
+    <t xml:space="preserve">7.28667306900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28813123703003</t>
   </si>
   <si>
     <t xml:space="preserve">7.24145984649658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20937156677246</t>
+    <t xml:space="preserve">7.20937204360962</t>
   </si>
   <si>
     <t xml:space="preserve">7.13207101821899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21083068847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28375577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29615354537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1904125213623</t>
+    <t xml:space="preserve">7.21082973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2837553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29615306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19041109085083</t>
   </si>
   <si>
     <t xml:space="preserve">7.27792167663574</t>
@@ -3662,73 +3662,73 @@
     <t xml:space="preserve">7.27354621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17728519439697</t>
+    <t xml:space="preserve">7.17728471755981</t>
   </si>
   <si>
     <t xml:space="preserve">7.1714506149292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0460205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09852695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13644790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25166940689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27938079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456918716431</t>
+    <t xml:space="preserve">7.04602003097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09852600097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13644742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25166893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27937984466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456871032715</t>
   </si>
   <si>
     <t xml:space="preserve">7.24875164031982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36543226242065</t>
+    <t xml:space="preserve">7.3654317855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.47846555709839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33626222610474</t>
+    <t xml:space="preserve">7.33626270294189</t>
   </si>
   <si>
     <t xml:space="preserve">7.53680610656738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61337614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68630170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58785390853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50398921966553</t>
+    <t xml:space="preserve">7.6133770942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68630218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5878529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50398969650269</t>
   </si>
   <si>
     <t xml:space="preserve">7.45294189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21520662307739</t>
+    <t xml:space="preserve">7.21520614624023</t>
   </si>
   <si>
     <t xml:space="preserve">7.38001728057861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41283226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43106365203857</t>
+    <t xml:space="preserve">7.41283273696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43106412887573</t>
   </si>
   <si>
     <t xml:space="preserve">7.53315925598145</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">7.6060848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55868244171143</t>
+    <t xml:space="preserve">7.55868291854858</t>
   </si>
   <si>
     <t xml:space="preserve">7.52222013473511</t>
@@ -3749,31 +3749,31 @@
     <t xml:space="preserve">7.64254665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67171669006348</t>
+    <t xml:space="preserve">7.67171716690063</t>
   </si>
   <si>
     <t xml:space="preserve">7.77016544342041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76651954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88684606552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8759069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8139214515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81756830215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89778423309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507793426514</t>
+    <t xml:space="preserve">7.76651906967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88684558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87590742111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81392192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81756734848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89778518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507650375366</t>
   </si>
   <si>
     <t xml:space="preserve">7.87955331802368</t>
@@ -3782,109 +3782,106 @@
     <t xml:space="preserve">7.79204320907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74828863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088768005371</t>
+    <t xml:space="preserve">7.74828910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088720321655</t>
   </si>
   <si>
     <t xml:space="preserve">7.90313243865967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72266817092896</t>
+    <t xml:space="preserve">7.72266721725464</t>
   </si>
   <si>
     <t xml:space="preserve">7.72111225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81756782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352554321289</t>
+    <t xml:space="preserve">7.45352458953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.56398296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59976530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
+    <t xml:space="preserve">7.59976434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843347549438</t>
   </si>
   <si>
     <t xml:space="preserve">7.63865756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62776756286621</t>
+    <t xml:space="preserve">7.62776803970337</t>
   </si>
   <si>
     <t xml:space="preserve">7.79034185409546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94591569900513</t>
+    <t xml:space="preserve">7.94591522216797</t>
   </si>
   <si>
     <t xml:space="preserve">7.86034965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82534646987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80978870391846</t>
+    <t xml:space="preserve">7.82534694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80978775024414</t>
   </si>
   <si>
     <t xml:space="preserve">7.71488904953003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76311635971069</t>
+    <t xml:space="preserve">7.76311683654785</t>
   </si>
   <si>
     <t xml:space="preserve">7.76156044006348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84868097305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80589914321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5219783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64954710006714</t>
+    <t xml:space="preserve">7.84868192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80590009689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52197790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6495475769043</t>
   </si>
   <si>
     <t xml:space="preserve">7.68999624252319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8136773109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86423921585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92646789550781</t>
+    <t xml:space="preserve">7.81367778778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86423826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92646884918213</t>
   </si>
   <si>
     <t xml:space="preserve">8.0859317779541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10148811340332</t>
+    <t xml:space="preserve">8.10148906707764</t>
   </si>
   <si>
     <t xml:space="preserve">8.0820426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07815170288086</t>
+    <t xml:space="preserve">8.07815265655518</t>
   </si>
   <si>
     <t xml:space="preserve">8.07037353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13260364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23761558532715</t>
+    <t xml:space="preserve">8.13260269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23761463165283</t>
   </si>
   <si>
     <t xml:space="preserve">8.17538642883301</t>
@@ -3899,25 +3896,25 @@
     <t xml:space="preserve">8.05092716217041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02370166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61532258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66043853759766</t>
+    <t xml:space="preserve">8.02370071411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61532211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66043758392334</t>
   </si>
   <si>
     <t xml:space="preserve">7.77867317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02759075164795</t>
+    <t xml:space="preserve">8.02759170532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.10926723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79812097549438</t>
+    <t xml:space="preserve">7.79812049865723</t>
   </si>
   <si>
     <t xml:space="preserve">8.05870532989502</t>
@@ -3926,19 +3923,19 @@
     <t xml:space="preserve">8.22983741760254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20650196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14427089691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90702104568481</t>
+    <t xml:space="preserve">8.20650100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14427185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90702199935913</t>
   </si>
   <si>
     <t xml:space="preserve">8.07426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88368654251099</t>
+    <t xml:space="preserve">7.88368511199951</t>
   </si>
   <si>
     <t xml:space="preserve">7.9381365776062</t>
@@ -3953,34 +3950,34 @@
     <t xml:space="preserve">7.67755031585693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26994800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29172897338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25439167022705</t>
+    <t xml:space="preserve">7.26994848251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29172849655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25439119338989</t>
   </si>
   <si>
     <t xml:space="preserve">6.68654823303223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73477506637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68499183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12337207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95379686355591</t>
+    <t xml:space="preserve">6.73477554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68499231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12337255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95379638671875</t>
   </si>
   <si>
     <t xml:space="preserve">6.08603429794312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63520812988281</t>
+    <t xml:space="preserve">6.63520860671997</t>
   </si>
   <si>
     <t xml:space="preserve">6.31939458847046</t>
@@ -3992,34 +3989,34 @@
     <t xml:space="preserve">6.61187267303467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66165637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970830917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06925964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22638845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06770324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12993288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02103090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05059051513672</t>
+    <t xml:space="preserve">6.66165685653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06925916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2263879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06770277023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12993240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02103137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0505895614624</t>
   </si>
   <si>
     <t xml:space="preserve">7.22949838638306</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10659646987915</t>
+    <t xml:space="preserve">7.10659551620483</t>
   </si>
   <si>
     <t xml:space="preserve">7.17193794250488</t>
@@ -4028,7 +4025,7 @@
     <t xml:space="preserve">7.30417537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11904287338257</t>
+    <t xml:space="preserve">7.11904239654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.97902584075928</t>
@@ -4037,31 +4034,31 @@
     <t xml:space="preserve">6.89190483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03503227233887</t>
+    <t xml:space="preserve">7.03503274917603</t>
   </si>
   <si>
     <t xml:space="preserve">7.02569770812988</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94946718215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1128191947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19527292251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18438339233398</t>
+    <t xml:space="preserve">6.94946670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11281967163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19527387619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18438291549683</t>
   </si>
   <si>
     <t xml:space="preserve">7.374183177948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44885873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17971563339233</t>
+    <t xml:space="preserve">7.4488582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17971515655518</t>
   </si>
   <si>
     <t xml:space="preserve">7.1641583442688</t>
@@ -4070,34 +4067,34 @@
     <t xml:space="preserve">7.38196086883545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38040494918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686052322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74756002426147</t>
+    <t xml:space="preserve">7.38040542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74755907058716</t>
   </si>
   <si>
     <t xml:space="preserve">7.50486469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48308420181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60598707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54842567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71955585479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088672637939</t>
+    <t xml:space="preserve">7.48308372497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60598754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54842472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71955537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088624954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.71022129058838</t>
@@ -4106,22 +4103,25 @@
     <t xml:space="preserve">7.5235333442688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44574546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38973951339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43485498428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26216983795166</t>
+    <t xml:space="preserve">7.44574594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38973999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43485641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26217079162598</t>
   </si>
   <si>
     <t xml:space="preserve">7.34151172637939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41152095794678</t>
+    <t xml:space="preserve">7.46752786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41152000427246</t>
   </si>
   <si>
     <t xml:space="preserve">7.46908235549927</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">7.32906579971313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42085456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53442239761353</t>
+    <t xml:space="preserve">7.42085409164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442287445068</t>
   </si>
   <si>
     <t xml:space="preserve">7.49864149093628</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">7.50797605514526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01325225830078</t>
+    <t xml:space="preserve">7.01325178146362</t>
   </si>
   <si>
     <t xml:space="preserve">6.90435123443604</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">6.96813583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95102262496948</t>
+    <t xml:space="preserve">6.95102310180664</t>
   </si>
   <si>
     <t xml:space="preserve">6.63054180145264</t>
@@ -4178,22 +4178,22 @@
     <t xml:space="preserve">6.5683126449585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71144008636475</t>
+    <t xml:space="preserve">6.71143960952759</t>
   </si>
   <si>
     <t xml:space="preserve">6.56675672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64765453338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60253763198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42362880706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41896200180054</t>
+    <t xml:space="preserve">6.64765405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60253810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42362928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41896152496338</t>
   </si>
   <si>
     <t xml:space="preserve">6.38784694671631</t>
@@ -4202,37 +4202,37 @@
     <t xml:space="preserve">6.2322735786438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32406187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45785474777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55586624145508</t>
+    <t xml:space="preserve">6.32406234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45785427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55586671829224</t>
   </si>
   <si>
     <t xml:space="preserve">6.4905252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41273880004883</t>
+    <t xml:space="preserve">6.41273975372314</t>
   </si>
   <si>
     <t xml:space="preserve">6.3582878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05958700180054</t>
+    <t xml:space="preserve">6.05958652496338</t>
   </si>
   <si>
     <t xml:space="preserve">6.05491971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20115852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33339643478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26027679443359</t>
+    <t xml:space="preserve">6.20115900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33339595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26027727127075</t>
   </si>
   <si>
     <t xml:space="preserve">6.2213830947876</t>
@@ -4244,34 +4244,34 @@
     <t xml:space="preserve">6.17937850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24005317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35673189163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50297021865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54653263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55119895935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59787082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64921045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7021050453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65232181549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6429877281189</t>
+    <t xml:space="preserve">6.24005222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35673236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50297069549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54653167724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55119848251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59787130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64921092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70210552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65232133865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64298725128174</t>
   </si>
   <si>
     <t xml:space="preserve">6.66010046005249</t>
@@ -4280,25 +4280,25 @@
     <t xml:space="preserve">6.72544145584106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77055835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77833652496338</t>
+    <t xml:space="preserve">6.77055883407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77833604812622</t>
   </si>
   <si>
     <t xml:space="preserve">6.72233057022095</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69588232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44696569442749</t>
+    <t xml:space="preserve">6.69588184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44696474075317</t>
   </si>
   <si>
     <t xml:space="preserve">6.27427816390991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32250642776489</t>
+    <t xml:space="preserve">6.32250595092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.2945032119751</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">6.25872039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1700439453125</t>
+    <t xml:space="preserve">6.17004442214966</t>
   </si>
   <si>
     <t xml:space="preserve">6.15448665618896</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">6.21360445022583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15137529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07825613021851</t>
+    <t xml:space="preserve">6.15137577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07825565338135</t>
   </si>
   <si>
     <t xml:space="preserve">6.31006050109863</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">6.19493627548218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22916269302368</t>
+    <t xml:space="preserve">6.22916221618652</t>
   </si>
   <si>
     <t xml:space="preserve">6.28672409057617</t>
@@ -4340,13 +4340,13 @@
     <t xml:space="preserve">6.44229745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5807580947876</t>
+    <t xml:space="preserve">6.58075857162476</t>
   </si>
   <si>
     <t xml:space="preserve">6.58698129653931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65387773513794</t>
+    <t xml:space="preserve">6.65387725830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.63365316390991</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">6.57764673233032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61031675338745</t>
+    <t xml:space="preserve">6.61031723022461</t>
   </si>
   <si>
     <t xml:space="preserve">6.37540102005005</t>
@@ -4364,28 +4364,28 @@
     <t xml:space="preserve">6.48274660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44074201583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20893716812134</t>
+    <t xml:space="preserve">6.44074153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20893669128418</t>
   </si>
   <si>
     <t xml:space="preserve">6.09381341934204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03314018249512</t>
+    <t xml:space="preserve">6.03313970565796</t>
   </si>
   <si>
     <t xml:space="preserve">5.92112636566162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59009265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48119068145752</t>
+    <t xml:space="preserve">6.26961088180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59009313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48119115829468</t>
   </si>
   <si>
     <t xml:space="preserve">6.23382902145386</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">6.19649124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18248987197876</t>
+    <t xml:space="preserve">6.18249034881592</t>
   </si>
   <si>
     <t xml:space="preserve">6.10003566741943</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">6.2836127281189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45629930496216</t>
+    <t xml:space="preserve">6.45629978179932</t>
   </si>
   <si>
     <t xml:space="preserve">6.52164030075073</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">6.84989976882935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85767936706543</t>
+    <t xml:space="preserve">6.85767889022827</t>
   </si>
   <si>
     <t xml:space="preserve">7.07081460952759</t>
@@ -4427,19 +4427,19 @@
     <t xml:space="preserve">7.10348510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1346001625061</t>
+    <t xml:space="preserve">7.13459968566895</t>
   </si>
   <si>
     <t xml:space="preserve">7.09726142883301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19060564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15326881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31039762496948</t>
+    <t xml:space="preserve">7.19060659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15326929092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31039810180664</t>
   </si>
   <si>
     <t xml:space="preserve">7.49241876602173</t>
@@ -4448,16 +4448,16 @@
     <t xml:space="preserve">7.52820014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57953929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6339898109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74289226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91480112075806</t>
+    <t xml:space="preserve">7.57954072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63399028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74289178848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">7.90892219543457</t>
@@ -4466,19 +4466,19 @@
     <t xml:space="preserve">7.91228055953979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93243598937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87029314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83502244949341</t>
+    <t xml:space="preserve">7.93243646621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87029218673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83502292633057</t>
   </si>
   <si>
     <t xml:space="preserve">7.7728796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73760986328125</t>
+    <t xml:space="preserve">7.73760938644409</t>
   </si>
   <si>
     <t xml:space="preserve">7.69562101364136</t>
@@ -4487,40 +4487,40 @@
     <t xml:space="preserve">7.71409606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73928880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68554496765137</t>
+    <t xml:space="preserve">7.7392897605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68554449081421</t>
   </si>
   <si>
     <t xml:space="preserve">7.63515853881836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65867137908936</t>
+    <t xml:space="preserve">7.6586709022522</t>
   </si>
   <si>
     <t xml:space="preserve">7.7107367515564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69394159317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81990718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79471445083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48064088821411</t>
+    <t xml:space="preserve">7.69394254684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81990814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79471397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48064136505127</t>
   </si>
   <si>
     <t xml:space="preserve">7.50415468215942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52934789657593</t>
+    <t xml:space="preserve">7.52934741973877</t>
   </si>
   <si>
     <t xml:space="preserve">7.66371059417725</t>
@@ -4535,40 +4535,40 @@
     <t xml:space="preserve">7.5864520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53774452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64691495895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54446363449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59484910964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67210817337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79807329177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78463840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77959823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85685729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90052461624146</t>
+    <t xml:space="preserve">7.53774499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64691543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54446315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59484958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67210721969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79807424545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78463745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77959775924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85685682296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90052509307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.02145099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12558174133301</t>
+    <t xml:space="preserve">8.12558269500732</t>
   </si>
   <si>
     <t xml:space="preserve">8.11550426483154</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">8.11046600341797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01977157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92403745651245</t>
+    <t xml:space="preserve">8.01977062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92403841018677</t>
   </si>
   <si>
     <t xml:space="preserve">8.04496479034424</t>
@@ -4592,10 +4592,10 @@
     <t xml:space="preserve">8.08191299438477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13230133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18100643157959</t>
+    <t xml:space="preserve">8.13230037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18100547790527</t>
   </si>
   <si>
     <t xml:space="preserve">8.28513813018799</t>
@@ -4607,16 +4607,16 @@
     <t xml:space="preserve">8.34560108184814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27674007415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37247276306152</t>
+    <t xml:space="preserve">8.27674102783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37247371673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.39430904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4312572479248</t>
+    <t xml:space="preserve">8.43125629425049</t>
   </si>
   <si>
     <t xml:space="preserve">8.51943302154541</t>
@@ -4625,34 +4625,34 @@
     <t xml:space="preserve">8.54042720794678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5698184967041</t>
+    <t xml:space="preserve">8.56981945037842</t>
   </si>
   <si>
     <t xml:space="preserve">8.69998168945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56562042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70838069915771</t>
+    <t xml:space="preserve">8.56561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7083797454834</t>
   </si>
   <si>
     <t xml:space="preserve">8.74197101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60340881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6328010559082</t>
+    <t xml:space="preserve">8.60340976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63280010223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.61180686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50263690948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49423885345459</t>
+    <t xml:space="preserve">8.5026388168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49423980712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.39094829559326</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">8.25490570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42286014556885</t>
+    <t xml:space="preserve">8.42285919189453</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164367675781</t>
@@ -4673,40 +4673,40 @@
     <t xml:space="preserve">8.37415313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36407661437988</t>
+    <t xml:space="preserve">8.36407566070557</t>
   </si>
   <si>
     <t xml:space="preserve">8.45644950866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51103591918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46064853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51523303985596</t>
+    <t xml:space="preserve">8.51103401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46064949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51523399353027</t>
   </si>
   <si>
     <t xml:space="preserve">8.40186595916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16757011413574</t>
+    <t xml:space="preserve">8.16756916046143</t>
   </si>
   <si>
     <t xml:space="preserve">7.80143260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99793720245361</t>
+    <t xml:space="preserve">7.99793672561646</t>
   </si>
   <si>
     <t xml:space="preserve">7.54950189590454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52095031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43193531036377</t>
+    <t xml:space="preserve">7.52095079421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43193578720093</t>
   </si>
   <si>
     <t xml:space="preserve">7.73425054550171</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">7.63180017471313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55286169052124</t>
+    <t xml:space="preserve">7.5528621673584</t>
   </si>
   <si>
     <t xml:space="preserve">7.51591110229492</t>
@@ -4724,43 +4724,43 @@
     <t xml:space="preserve">7.60660552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72417259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78295660018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8115086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80982971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74097013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075704574585</t>
+    <t xml:space="preserve">7.72417306900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78295707702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81150960922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80983018875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74096965789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075609207153</t>
   </si>
   <si>
     <t xml:space="preserve">7.92739677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93915367126465</t>
+    <t xml:space="preserve">7.93915414810181</t>
   </si>
   <si>
     <t xml:space="preserve">8.09367084503174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02648830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21795749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14909648895264</t>
+    <t xml:space="preserve">8.0264892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18772506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21795654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14909553527832</t>
   </si>
   <si>
     <t xml:space="preserve">8.21291732788086</t>
@@ -4778,16 +4778,16 @@
     <t xml:space="preserve">8.17092895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89212703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19444370269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09703063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3808708190918</t>
+    <t xml:space="preserve">7.8921275138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19444274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09702968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087177276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.39766597747803</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">8.34056282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36575508117676</t>
+    <t xml:space="preserve">8.36575603485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.13565921783447</t>
@@ -4808,25 +4808,25 @@
     <t xml:space="preserve">8.18436622619629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2532262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27338123321533</t>
+    <t xml:space="preserve">8.25322723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27338218688965</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895992279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42705821990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54462623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73357200622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7713623046875</t>
+    <t xml:space="preserve">8.42705917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5446252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7335729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77136325836182</t>
   </si>
   <si>
     <t xml:space="preserve">8.67898845672607</t>
@@ -4844,22 +4844,22 @@
     <t xml:space="preserve">8.98970127105713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90572452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98130512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96450901031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17025184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19124603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28781986236572</t>
+    <t xml:space="preserve">8.90572547912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98130416870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96450996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17025089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19124507904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28781890869141</t>
   </si>
   <si>
     <t xml:space="preserve">9.38859176635742</t>
@@ -4868,10 +4868,10 @@
     <t xml:space="preserve">9.49776172637939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4263801574707</t>
+    <t xml:space="preserve">9.39698886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42638111114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.40538597106934</t>
@@ -4880,10 +4880,10 @@
     <t xml:space="preserve">9.30461406707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33400726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14925861358643</t>
+    <t xml:space="preserve">9.33400630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14925765991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.03588962554932</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">9.06947994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20384311676025</t>
+    <t xml:space="preserve">9.20384216308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.34660339355469</t>
@@ -4910,22 +4910,22 @@
     <t xml:space="preserve">9.27942180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24583148956299</t>
+    <t xml:space="preserve">9.24583053588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25002956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25842761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43058013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48936367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48096466064453</t>
+    <t xml:space="preserve">9.25842666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057918548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48096561431885</t>
   </si>
   <si>
     <t xml:space="preserve">9.52295398712158</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">9.63632297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930458068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70770263671875</t>
+    <t xml:space="preserve">9.69930553436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70770168304443</t>
   </si>
   <si>
     <t xml:space="preserve">9.68250942230225</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">10.1779708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0520076751709</t>
+    <t xml:space="preserve">10.0520067214966</t>
   </si>
   <si>
     <t xml:space="preserve">9.9554328918457</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">9.94703578948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93863868713379</t>
+    <t xml:space="preserve">9.93863773345947</t>
   </si>
   <si>
     <t xml:space="preserve">9.98062705993652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73289585113525</t>
+    <t xml:space="preserve">9.73289680480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.83366775512695</t>
@@ -4988,13 +4988,13 @@
     <t xml:space="preserve">9.93024063110352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87565517425537</t>
+    <t xml:space="preserve">9.87565612792969</t>
   </si>
   <si>
     <t xml:space="preserve">9.79167938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7664852142334</t>
+    <t xml:space="preserve">9.76648616790771</t>
   </si>
   <si>
     <t xml:space="preserve">9.82526969909668</t>
@@ -5006,13 +5006,13 @@
     <t xml:space="preserve">9.92604160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91344547271729</t>
+    <t xml:space="preserve">9.9134464263916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1653747558594</t>
+    <t xml:space="preserve">10.1653738021851</t>
   </si>
   <si>
     <t xml:space="preserve">10.1947679519653</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">10.144380569458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2199592590332</t>
+    <t xml:space="preserve">10.2199602127075</t>
   </si>
   <si>
     <t xml:space="preserve">10.0981931686401</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">10.1989660263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1317844390869</t>
+    <t xml:space="preserve">10.1317834854126</t>
   </si>
   <si>
     <t xml:space="preserve">10.2157611846924</t>
@@ -5045,13 +5045,13 @@
     <t xml:space="preserve">10.2241592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2115631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3039360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2535514831543</t>
+    <t xml:space="preserve">10.2115621566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.303936958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.25355052948</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905689239502</t>
@@ -5063,31 +5063,31 @@
     <t xml:space="preserve">10.4173049926758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3333292007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2451524734497</t>
+    <t xml:space="preserve">10.3333282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2451515197754</t>
   </si>
   <si>
     <t xml:space="preserve">10.2913408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3963117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4341011047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676923751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3921117782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3207321166992</t>
+    <t xml:space="preserve">10.3963108062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434100151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5222749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3921136856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3207311630249</t>
   </si>
   <si>
     <t xml:space="preserve">10.2745447158813</t>
@@ -5102,13 +5102,13 @@
     <t xml:space="preserve">10.2283582687378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2367563247681</t>
+    <t xml:space="preserve">10.2367553710938</t>
   </si>
   <si>
     <t xml:space="preserve">10.295539855957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695747375488</t>
+    <t xml:space="preserve">10.1695737838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.1527795791626</t>
@@ -5123,34 +5123,34 @@
     <t xml:space="preserve">9.26682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37179660797119</t>
+    <t xml:space="preserve">9.37179565429688</t>
   </si>
   <si>
     <t xml:space="preserve">9.24163246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96870803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46417045593262</t>
+    <t xml:space="preserve">8.96870708465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46417140960693</t>
   </si>
   <si>
     <t xml:space="preserve">9.53135299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58173656463623</t>
+    <t xml:space="preserve">9.58173751831055</t>
   </si>
   <si>
     <t xml:space="preserve">9.65311813354492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731620788574</t>
+    <t xml:space="preserve">9.65731716156006</t>
   </si>
   <si>
     <t xml:space="preserve">9.66991233825684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63212490081787</t>
+    <t xml:space="preserve">9.63212394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.67831039428711</t>
@@ -5171,7 +5171,7 @@
     <t xml:space="preserve">9.73050308227539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82554531097412</t>
+    <t xml:space="preserve">9.8255443572998</t>
   </si>
   <si>
     <t xml:space="preserve">9.81649398803711</t>
@@ -5183,10 +5183,10 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71240043640137</t>
+    <t xml:space="preserve">9.73955535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71239852905273</t>
   </si>
   <si>
     <t xml:space="preserve">9.75313091278076</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">9.72597694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65808963775635</t>
+    <t xml:space="preserve">9.65809059143066</t>
   </si>
   <si>
     <t xml:space="preserve">9.92511367797852</t>
@@ -5207,22 +5207,22 @@
     <t xml:space="preserve">10.0020523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0744647979736</t>
+    <t xml:space="preserve">10.0744657516479</t>
   </si>
   <si>
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0925674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0337324142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0699396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0654144287109</t>
+    <t xml:space="preserve">10.092568397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0337333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.069938659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0654134750366</t>
   </si>
   <si>
     <t xml:space="preserve">10.1378259658813</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">10.1785583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.151403427124</t>
+    <t xml:space="preserve">10.1514043807983</t>
   </si>
   <si>
     <t xml:space="preserve">10.115198135376</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">10.142352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0608863830566</t>
+    <t xml:space="preserve">10.060887336731</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695070266724</t>
@@ -5255,16 +5255,16 @@
     <t xml:space="preserve">10.2736015319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2147655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102394104004</t>
+    <t xml:space="preserve">10.2147645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102384567261</t>
   </si>
   <si>
     <t xml:space="preserve">10.2011880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4455823898315</t>
+    <t xml:space="preserve">10.4455814361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.7126045227051</t>
@@ -5294,13 +5294,13 @@
     <t xml:space="preserve">10.9751024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1063508987427</t>
+    <t xml:space="preserve">11.106351852417</t>
   </si>
   <si>
     <t xml:space="preserve">11.133505821228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9388952255249</t>
+    <t xml:space="preserve">10.9388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">11.0022563934326</t>
@@ -5309,37 +5309,37 @@
     <t xml:space="preserve">10.8393278121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7669153213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7171316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5315723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4908390045166</t>
+    <t xml:space="preserve">10.7669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7171306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5315732955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4908399581909</t>
   </si>
   <si>
     <t xml:space="preserve">10.4184274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3957967758179</t>
+    <t xml:space="preserve">10.3957977294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858812332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.66282081604</t>
+    <t xml:space="preserve">10.5858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6628217697144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7261819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1787643432617</t>
+    <t xml:space="preserve">11.178765296936</t>
   </si>
   <si>
     <t xml:space="preserve">11.7173357009888</t>
@@ -5354,16 +5354,16 @@
     <t xml:space="preserve">11.4231586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005289077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4141054153442</t>
+    <t xml:space="preserve">11.4005298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4141063690186</t>
   </si>
   <si>
     <t xml:space="preserve">11.3869514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4865188598633</t>
+    <t xml:space="preserve">11.486517906189</t>
   </si>
   <si>
     <t xml:space="preserve">11.6313457489014</t>
@@ -5375,10 +5375,10 @@
     <t xml:space="preserve">11.595139503479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6901817321777</t>
+    <t xml:space="preserve">11.7625932693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6901807785034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8576364517212</t>
@@ -5387,43 +5387,43 @@
     <t xml:space="preserve">12.0160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9979372024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567722320557</t>
+    <t xml:space="preserve">11.9979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567712783813</t>
   </si>
   <si>
     <t xml:space="preserve">12.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2785367965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3328475952148</t>
+    <t xml:space="preserve">12.2785358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3328466415405</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003023147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3781061172485</t>
+    <t xml:space="preserve">12.500301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3781051635742</t>
   </si>
   <si>
     <t xml:space="preserve">12.5093536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3962078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4052591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3102188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554754257202</t>
+    <t xml:space="preserve">12.3962087631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4052600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3102178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554763793945</t>
   </si>
   <si>
     <t xml:space="preserve">12.2875881195068</t>
@@ -5438,31 +5438,31 @@
     <t xml:space="preserve">12.2921142578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2151765823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3237943649292</t>
+    <t xml:space="preserve">12.2151756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3237953186035</t>
   </si>
   <si>
     <t xml:space="preserve">12.3509502410889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1337099075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744432449341</t>
+    <t xml:space="preserve">12.1337108612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744441986084</t>
   </si>
   <si>
     <t xml:space="preserve">12.083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1970720291138</t>
+    <t xml:space="preserve">12.1970729827881</t>
   </si>
   <si>
     <t xml:space="preserve">12.3826313018799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6451292037964</t>
+    <t xml:space="preserve">12.6451282501221</t>
   </si>
   <si>
     <t xml:space="preserve">12.6722831726074</t>
@@ -5477,7 +5477,7 @@
     <t xml:space="preserve">13.2244319915771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.514084815979</t>
+    <t xml:space="preserve">13.5140838623047</t>
   </si>
   <si>
     <t xml:space="preserve">13.7539520263672</t>
@@ -5507,7 +5507,7 @@
     <t xml:space="preserve">13.7336559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6259603500366</t>
+    <t xml:space="preserve">13.6259593963623</t>
   </si>
   <si>
     <t xml:space="preserve">13.5369930267334</t>
@@ -5516,19 +5516,19 @@
     <t xml:space="preserve">13.5791349411011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5978660583496</t>
+    <t xml:space="preserve">13.5978651046753</t>
   </si>
   <si>
     <t xml:space="preserve">13.5042161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4199323654175</t>
+    <t xml:space="preserve">13.4199314117432</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620733261108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4339790344238</t>
+    <t xml:space="preserve">13.4339799880981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2794580459595</t>
@@ -5537,16 +5537,16 @@
     <t xml:space="preserve">13.1343011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4246139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9563684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.666054725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7550230026245</t>
+    <t xml:space="preserve">13.424614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9563674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7550220489502</t>
   </si>
   <si>
     <t xml:space="preserve">12.8205757141113</t>
@@ -5555,16 +5555,16 @@
     <t xml:space="preserve">12.7222452163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9329566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0500183105469</t>
+    <t xml:space="preserve">12.9329557418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0500173568726</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001779556274</t>
+    <t xml:space="preserve">12.9001789093018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7831172943115</t>
@@ -5573,7 +5573,7 @@
     <t xml:space="preserve">13.1951732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0359697341919</t>
+    <t xml:space="preserve">13.0359706878662</t>
   </si>
   <si>
     <t xml:space="preserve">13.1670789718628</t>
@@ -5585,7 +5585,7 @@
     <t xml:space="preserve">13.2045392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2888221740723</t>
+    <t xml:space="preserve">13.2888231277466</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654104232788</t>
@@ -5594,7 +5594,7 @@
     <t xml:space="preserve">13.4386615753174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4714393615723</t>
+    <t xml:space="preserve">13.4714384078979</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777894973755</t>
@@ -5603,10 +5603,10 @@
     <t xml:space="preserve">13.382472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4995336532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4808044433594</t>
+    <t xml:space="preserve">13.499532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4808034896851</t>
   </si>
   <si>
     <t xml:space="preserve">13.5182638168335</t>
@@ -5618,7 +5618,7 @@
     <t xml:space="preserve">13.8038930892944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8413534164429</t>
+    <t xml:space="preserve">13.8413524627686</t>
   </si>
   <si>
     <t xml:space="preserve">13.808575630188</t>
@@ -5633,13 +5633,13 @@
     <t xml:space="preserve">13.4573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1623964309692</t>
+    <t xml:space="preserve">13.1623973846436</t>
   </si>
   <si>
     <t xml:space="preserve">12.8486709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1483497619629</t>
+    <t xml:space="preserve">13.1483488082886</t>
   </si>
   <si>
     <t xml:space="preserve">13.0172395706177</t>
@@ -5651,7 +5651,7 @@
     <t xml:space="preserve">13.1389837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1015243530273</t>
+    <t xml:space="preserve">13.101523399353</t>
   </si>
   <si>
     <t xml:space="preserve">13.1904907226562</t>
@@ -5666,13 +5666,13 @@
     <t xml:space="preserve">13.9350023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.949049949646</t>
+    <t xml:space="preserve">13.9490509033203</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0146045684814</t>
+    <t xml:space="preserve">14.0146036148071</t>
   </si>
   <si>
     <t xml:space="preserve">14.047381401062</t>
@@ -5687,10 +5687,10 @@
     <t xml:space="preserve">14.314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3611068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1410312652588</t>
+    <t xml:space="preserve">14.3611059188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1410303115845</t>
   </si>
   <si>
     <t xml:space="preserve">13.9911918640137</t>
@@ -5699,25 +5699,25 @@
     <t xml:space="preserve">14.1223001480103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9865102767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019023895264</t>
+    <t xml:space="preserve">13.9865093231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019033432007</t>
   </si>
   <si>
     <t xml:space="preserve">13.9818267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752387046814</t>
+    <t xml:space="preserve">13.7523860931396</t>
   </si>
   <si>
     <t xml:space="preserve">13.836669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8881778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0005559921265</t>
+    <t xml:space="preserve">13.8881769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0005569458008</t>
   </si>
   <si>
     <t xml:space="preserve">14.3657884597778</t>
@@ -5726,7 +5726,7 @@
     <t xml:space="preserve">14.403247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.286187171936</t>
+    <t xml:space="preserve">14.2861862182617</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815046310425</t>
@@ -5738,19 +5738,19 @@
     <t xml:space="preserve">14.4453907012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4641199111938</t>
+    <t xml:space="preserve">14.4641208648682</t>
   </si>
   <si>
     <t xml:space="preserve">14.3517408370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1129360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.033332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460359573364</t>
+    <t xml:space="preserve">14.1129350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0333337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460350036621</t>
   </si>
   <si>
     <t xml:space="preserve">14.0567464828491</t>
@@ -5774,7 +5774,7 @@
     <t xml:space="preserve">14.5624523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6561012268066</t>
+    <t xml:space="preserve">14.6561002731323</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982431411743</t>
@@ -5786,13 +5786,13 @@
     <t xml:space="preserve">15.1009349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9136362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5999116897583</t>
+    <t xml:space="preserve">14.9136371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7684812545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5999126434326</t>
   </si>
   <si>
     <t xml:space="preserve">14.4500732421875</t>
@@ -5813,7 +5813,7 @@
     <t xml:space="preserve">14.4219779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3376941680908</t>
+    <t xml:space="preserve">14.3376951217651</t>
   </si>
   <si>
     <t xml:space="preserve">14.3002347946167</t>
@@ -5834,7 +5834,7 @@
     <t xml:space="preserve">13.5229454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8554000854492</t>
+    <t xml:space="preserve">13.8554010391235</t>
   </si>
   <si>
     <t xml:space="preserve">13.9089336395264</t>
@@ -6465,6 +6465,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.3600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3999996185303</t>
   </si>
 </sst>
 </file>
@@ -45847,7 +45850,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45873,7 +45876,7 @@
         <v>9.58199977874756</v>
       </c>
       <c r="G1503" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45899,7 +45902,7 @@
         <v>9.72399997711182</v>
       </c>
       <c r="G1504" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45925,7 +45928,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1505" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45951,7 +45954,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G1506" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45977,7 +45980,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1507" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -46003,7 +46006,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G1508" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -46029,7 +46032,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G1509" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -46055,7 +46058,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G1510" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -46081,7 +46084,7 @@
         <v>10.1049995422363</v>
       </c>
       <c r="G1511" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -46107,7 +46110,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1512" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -46133,7 +46136,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1513" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -46159,7 +46162,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G1514" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -46185,7 +46188,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1515" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -46211,7 +46214,7 @@
         <v>9.97799968719482</v>
       </c>
       <c r="G1516" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -46237,7 +46240,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G1517" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -46263,7 +46266,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G1518" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -46289,7 +46292,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G1519" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -46315,7 +46318,7 @@
         <v>9.83399963378906</v>
       </c>
       <c r="G1520" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -46341,7 +46344,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G1521" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -46367,7 +46370,7 @@
         <v>9.88599967956543</v>
       </c>
       <c r="G1522" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -46419,7 +46422,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1524" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -46445,7 +46448,7 @@
         <v>10.0450000762939</v>
       </c>
       <c r="G1525" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -46471,7 +46474,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G1526" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -46497,7 +46500,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1527" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -46523,7 +46526,7 @@
         <v>10.3950004577637</v>
       </c>
       <c r="G1528" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -46549,7 +46552,7 @@
         <v>10.414999961853</v>
       </c>
       <c r="G1529" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -46575,7 +46578,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G1530" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -46601,7 +46604,7 @@
         <v>10.3850002288818</v>
       </c>
       <c r="G1531" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -46627,7 +46630,7 @@
         <v>10.375</v>
       </c>
       <c r="G1532" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -46653,7 +46656,7 @@
         <v>10.4549999237061</v>
       </c>
       <c r="G1533" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -46679,7 +46682,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1534" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -46705,7 +46708,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G1535" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -46731,7 +46734,7 @@
         <v>10.3850002288818</v>
       </c>
       <c r="G1536" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46757,7 +46760,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1537" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -46783,7 +46786,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G1538" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46809,7 +46812,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1539" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46835,7 +46838,7 @@
         <v>10.3149995803833</v>
       </c>
       <c r="G1540" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -46861,7 +46864,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G1541" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -46887,7 +46890,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -46913,7 +46916,7 @@
         <v>9.72399997711182</v>
       </c>
       <c r="G1543" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -46939,7 +46942,7 @@
         <v>9.84799957275391</v>
       </c>
       <c r="G1544" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46965,7 +46968,7 @@
         <v>10</v>
       </c>
       <c r="G1545" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -46991,7 +46994,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G1546" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -47017,7 +47020,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G1547" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -47043,7 +47046,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1548" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -47069,7 +47072,7 @@
         <v>10.4250001907349</v>
       </c>
       <c r="G1549" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -47095,7 +47098,7 @@
         <v>10.3149995803833</v>
       </c>
       <c r="G1550" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -47121,7 +47124,7 @@
         <v>10.0249996185303</v>
       </c>
       <c r="G1551" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -47147,7 +47150,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1552" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -47173,7 +47176,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1553" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -47199,7 +47202,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1554" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -47225,7 +47228,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1555" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -47251,7 +47254,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G1556" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -47277,7 +47280,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1557" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -47303,7 +47306,7 @@
         <v>10.3950004577637</v>
       </c>
       <c r="G1558" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -47329,7 +47332,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1559" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -47355,7 +47358,7 @@
         <v>10.1350002288818</v>
       </c>
       <c r="G1560" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -47381,7 +47384,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G1561" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -47407,7 +47410,7 @@
         <v>9.99600028991699</v>
       </c>
       <c r="G1562" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -47433,7 +47436,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G1563" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -47459,7 +47462,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G1564" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -47485,7 +47488,7 @@
         <v>9.3459997177124</v>
       </c>
       <c r="G1565" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -47511,7 +47514,7 @@
         <v>9.37399959564209</v>
       </c>
       <c r="G1566" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -47537,7 +47540,7 @@
         <v>9.32600021362305</v>
       </c>
       <c r="G1567" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -47563,7 +47566,7 @@
         <v>8.5959997177124</v>
       </c>
       <c r="G1568" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -47589,7 +47592,7 @@
         <v>8.65799999237061</v>
       </c>
       <c r="G1569" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -47615,7 +47618,7 @@
         <v>8.5939998626709</v>
       </c>
       <c r="G1570" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -47641,7 +47644,7 @@
         <v>7.87200021743774</v>
       </c>
       <c r="G1571" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -47667,7 +47670,7 @@
         <v>7.65399980545044</v>
       </c>
       <c r="G1572" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -47693,7 +47696,7 @@
         <v>7.82399988174438</v>
       </c>
       <c r="G1573" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -47719,7 +47722,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1574" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -47745,7 +47748,7 @@
         <v>8.12399959564209</v>
       </c>
       <c r="G1575" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -47771,7 +47774,7 @@
         <v>8.16399955749512</v>
       </c>
       <c r="G1576" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -47797,7 +47800,7 @@
         <v>8.5</v>
       </c>
       <c r="G1577" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -47823,7 +47826,7 @@
         <v>8.56400012969971</v>
       </c>
       <c r="G1578" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -47849,7 +47852,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1579" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -47875,7 +47878,7 @@
         <v>9.08800029754639</v>
       </c>
       <c r="G1580" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -47901,7 +47904,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1581" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -47927,7 +47930,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G1582" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -47953,7 +47956,7 @@
         <v>9.16600036621094</v>
       </c>
       <c r="G1583" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -47979,7 +47982,7 @@
         <v>9.02600002288818</v>
       </c>
       <c r="G1584" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -48005,7 +48008,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G1585" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -48031,7 +48034,7 @@
         <v>9.06400012969971</v>
       </c>
       <c r="G1586" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -48057,7 +48060,7 @@
         <v>9.08800029754639</v>
       </c>
       <c r="G1587" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -48083,7 +48086,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G1588" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -48109,7 +48112,7 @@
         <v>9.13599967956543</v>
       </c>
       <c r="G1589" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -48135,7 +48138,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1590" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -48161,7 +48164,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1591" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -48187,7 +48190,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1592" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -48213,7 +48216,7 @@
         <v>9.15200042724609</v>
       </c>
       <c r="G1593" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -48239,7 +48242,7 @@
         <v>8.97200012207031</v>
       </c>
       <c r="G1594" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -48265,7 +48268,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1595" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -48291,7 +48294,7 @@
         <v>9.04399967193604</v>
       </c>
       <c r="G1596" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -48317,7 +48320,7 @@
         <v>9.0319995880127</v>
       </c>
       <c r="G1597" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -48343,7 +48346,7 @@
         <v>8.93400001525879</v>
       </c>
       <c r="G1598" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -48369,7 +48372,7 @@
         <v>9.14400005340576</v>
       </c>
       <c r="G1599" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -48395,7 +48398,7 @@
         <v>9.25</v>
       </c>
       <c r="G1600" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -48421,7 +48424,7 @@
         <v>9.23600006103516</v>
       </c>
       <c r="G1601" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -48447,7 +48450,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1602" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -48473,7 +48476,7 @@
         <v>9.57600021362305</v>
       </c>
       <c r="G1603" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -48499,7 +48502,7 @@
         <v>9.3459997177124</v>
       </c>
       <c r="G1604" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -48525,7 +48528,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1605" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -48551,7 +48554,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48577,7 +48580,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1607" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -48603,7 +48606,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1608" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -48629,7 +48632,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G1609" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -48655,7 +48658,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1610" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -48681,7 +48684,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1611" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48707,7 +48710,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48733,7 +48736,7 @@
         <v>10</v>
       </c>
       <c r="G1613" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -48759,7 +48762,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G1614" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48785,7 +48788,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1615" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48811,7 +48814,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G1616" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48837,7 +48840,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1617" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -48863,7 +48866,7 @@
         <v>9.70400047302246</v>
       </c>
       <c r="G1618" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48889,7 +48892,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G1619" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48915,7 +48918,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1620" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -48941,7 +48944,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G1621" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -48967,7 +48970,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G1622" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -48993,7 +48996,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G1623" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -49019,7 +49022,7 @@
         <v>9.5</v>
       </c>
       <c r="G1624" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -49045,7 +49048,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G1625" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -49071,7 +49074,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G1626" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -49097,7 +49100,7 @@
         <v>9.4379997253418</v>
       </c>
       <c r="G1627" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -49123,7 +49126,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1628" t="s">
-        <v>827</v>
+        <v>1368</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -49279,7 +49282,7 @@
         <v>9.5</v>
       </c>
       <c r="G1634" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -51827,7 +51830,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1732" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -52269,7 +52272,7 @@
         <v>9.97799968719482</v>
       </c>
       <c r="G1749" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -52295,7 +52298,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G1750" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -52321,7 +52324,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G1751" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -52347,7 +52350,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1752" t="s">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -71439,7 +71442,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6500347222</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>2150559</v>
@@ -71460,6 +71463,32 @@
         <v>2150</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493865741</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>1773587</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>16.4899997711182</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>16.1450004577637</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>16.4549999237061</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="2152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="2153">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19125890731812</t>
+    <t xml:space="preserve">5.19125843048096</t>
   </si>
   <si>
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18521499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0552830696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95858907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83772087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8105263710022</t>
+    <t xml:space="preserve">5.18521595001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05528259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95858860015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.837721824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81052684783936</t>
   </si>
   <si>
     <t xml:space="preserve">4.92534971237183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97974061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91930723190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73196315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50533580780029</t>
+    <t xml:space="preserve">4.97974109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91930675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73196220397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50533533096313</t>
   </si>
   <si>
     <t xml:space="preserve">4.59900856018066</t>
@@ -80,19 +80,19 @@
     <t xml:space="preserve">4.41468524932861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65944194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67455005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52346611022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59598636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52648782730103</t>
+    <t xml:space="preserve">4.65944147109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67455053329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52346658706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59598684310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52648735046387</t>
   </si>
   <si>
     <t xml:space="preserve">4.27870893478394</t>
@@ -101,97 +101,97 @@
     <t xml:space="preserve">4.45094537734985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31194829940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19410228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00373506546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09136486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98862791061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61696004867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41450691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47796177864075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54443883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64717650413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68041515350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74991369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64113330841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091589927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75595688819885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6622850894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62300324440002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67437171936035</t>
+    <t xml:space="preserve">4.3119478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19410181045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00373554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09136533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98862719535828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61695957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41450643539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67134976387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47796154022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54443979263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64717602729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.680415391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113306999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091637611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75595760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62300276756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67437195777893</t>
   </si>
   <si>
     <t xml:space="preserve">3.76804423332214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78315281867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93725872039795</t>
+    <t xml:space="preserve">3.78315186500549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93725919723511</t>
   </si>
   <si>
     <t xml:space="preserve">4.08834314346313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10345077514648</t>
+    <t xml:space="preserve">4.10345125198364</t>
   </si>
   <si>
     <t xml:space="preserve">4.02488708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91006350517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96143174171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97351837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03395318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38446855545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42979288101196</t>
+    <t xml:space="preserve">3.91006326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96143221855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97351884841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0339527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38446807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42979335784912</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173065185547</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">4.03697395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07323455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09438705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01884460449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99164915084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87984704971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90401983261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82545590400696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79221749305725</t>
+    <t xml:space="preserve">4.07323408126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09438610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01884412765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99164867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8798463344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90402054786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82545566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79221773147583</t>
   </si>
   <si>
     <t xml:space="preserve">3.83149933815002</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">3.75897860527039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79523968696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60487341880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81336903572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85567307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77408790588379</t>
+    <t xml:space="preserve">3.79523921012878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60487294197083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8133692741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85567259788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77408719062805</t>
   </si>
   <si>
     <t xml:space="preserve">3.97049689292908</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">4.04301786422729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97654032707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23036241531372</t>
+    <t xml:space="preserve">3.97654056549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23036193847656</t>
   </si>
   <si>
     <t xml:space="preserve">4.23338413238525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36935949325562</t>
+    <t xml:space="preserve">4.36935997009277</t>
   </si>
   <si>
     <t xml:space="preserve">4.38749027252197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39655494689941</t>
+    <t xml:space="preserve">4.39655542373657</t>
   </si>
   <si>
     <t xml:space="preserve">4.33612108230591</t>
@@ -278,34 +278,34 @@
     <t xml:space="preserve">4.21223211288452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05208253860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88588881492615</t>
+    <t xml:space="preserve">4.05208301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88588953018188</t>
   </si>
   <si>
     <t xml:space="preserve">3.85265111923218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8043041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078142166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89797639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93423700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9221498966217</t>
+    <t xml:space="preserve">3.80430436134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8707811832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89797711372375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93423676490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92215061187744</t>
   </si>
   <si>
     <t xml:space="preserve">3.9070417881012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97956204414368</t>
+    <t xml:space="preserve">3.97956252098083</t>
   </si>
   <si>
     <t xml:space="preserve">4.01582288742065</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">4.21827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31496906280518</t>
+    <t xml:space="preserve">4.31497001647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.30590438842773</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">4.13366842269897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10647296905518</t>
+    <t xml:space="preserve">4.10647344589233</t>
   </si>
   <si>
     <t xml:space="preserve">4.00071334838867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9856059551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610741615295</t>
+    <t xml:space="preserve">3.98560619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9161069393158</t>
   </si>
   <si>
     <t xml:space="preserve">3.70156741142273</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">3.38731169700623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48098397254944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46889710426331</t>
+    <t xml:space="preserve">3.48098421096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46889686584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.6078941822052</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">3.85869455337524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83452033996582</t>
+    <t xml:space="preserve">3.83452105522156</t>
   </si>
   <si>
     <t xml:space="preserve">3.2090322971344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79929089546204</t>
+    <t xml:space="preserve">2.79929065704346</t>
   </si>
   <si>
     <t xml:space="preserve">2.96125364303589</t>
@@ -380,34 +380,34 @@
     <t xml:space="preserve">3.06399130821228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11535978317261</t>
+    <t xml:space="preserve">3.11535930633545</t>
   </si>
   <si>
     <t xml:space="preserve">3.14557647705078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01322650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91653251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84763813018799</t>
+    <t xml:space="preserve">3.0132269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91653275489807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84763836860657</t>
   </si>
   <si>
     <t xml:space="preserve">2.9455406665802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19694519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472336769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47191834449768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57767772674561</t>
+    <t xml:space="preserve">3.19694471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47191905975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57767796516418</t>
   </si>
   <si>
     <t xml:space="preserve">3.5263090133667</t>
@@ -422,82 +422,82 @@
     <t xml:space="preserve">3.59580779075623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58976483345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61998105049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5353741645813</t>
+    <t xml:space="preserve">3.58976435661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61998176574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53537440299988</t>
   </si>
   <si>
     <t xml:space="preserve">3.65926337242126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61393809318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78617334365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71365332603455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40846371650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42054986953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71969747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96747589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94027972221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099787712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308450698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84962964057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81639099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80128312110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69552397727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72876167297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92517113685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8949556350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95236682891846</t>
+    <t xml:space="preserve">3.61393713951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78617429733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71365404129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4084632396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42054963111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71969676017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96747541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94028043746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099859237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308569908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84962940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163914680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6955235004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72876262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92517161369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89495468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95236706733704</t>
   </si>
   <si>
     <t xml:space="preserve">4.0490608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14273309707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07927703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19108104705811</t>
+    <t xml:space="preserve">4.14273357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07927751541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19107961654663</t>
   </si>
   <si>
     <t xml:space="preserve">4.15481996536255</t>
@@ -506,58 +506,58 @@
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73178434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78919625282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68645834922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77106547355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77710890769958</t>
+    <t xml:space="preserve">3.7317841053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7891960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68645811080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77106523513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77710962295532</t>
   </si>
   <si>
     <t xml:space="preserve">3.49609231948853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54141712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47494053840637</t>
+    <t xml:space="preserve">3.54141783714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47494029998779</t>
   </si>
   <si>
     <t xml:space="preserve">3.49911379814148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49004864692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49307012557983</t>
+    <t xml:space="preserve">3.49004936218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49307060241699</t>
   </si>
   <si>
     <t xml:space="preserve">3.68343710899353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78013062477112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65322041511536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7438702583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87380337715149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99467062950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10949468612671</t>
+    <t xml:space="preserve">3.7801308631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65321969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74387121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87380313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99467039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10949420928955</t>
   </si>
   <si>
     <t xml:space="preserve">4.15784120559692</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">4.06114768981934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84358620643616</t>
+    <t xml:space="preserve">3.84358668327332</t>
   </si>
   <si>
     <t xml:space="preserve">4.00977897644043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14575481414795</t>
+    <t xml:space="preserve">4.14575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.13971138000488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25453615188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26964473724365</t>
+    <t xml:space="preserve">4.25453519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26964378356934</t>
   </si>
   <si>
     <t xml:space="preserve">4.20618915557861</t>
@@ -593,40 +593,40 @@
     <t xml:space="preserve">4.11251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94632458686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99360418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06294870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00306034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96208381652832</t>
+    <t xml:space="preserve">3.94632387161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99360394477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06294822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00305986404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96208333969116</t>
   </si>
   <si>
     <t xml:space="preserve">3.90849900245667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79502654075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95577907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10392427444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23315668106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23946094512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05979585647583</t>
+    <t xml:space="preserve">3.79502630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95578002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10392475128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23315715789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23946189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05979681015015</t>
   </si>
   <si>
     <t xml:space="preserve">4.46325397491455</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">4.80682325363159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67128705978394</t>
+    <t xml:space="preserve">4.67128658294678</t>
   </si>
   <si>
     <t xml:space="preserve">4.69650316238403</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.79106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95181608200073</t>
+    <t xml:space="preserve">4.95181703567505</t>
   </si>
   <si>
     <t xml:space="preserve">4.89508008956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91714382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98964023590088</t>
+    <t xml:space="preserve">4.91714525222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98964071273804</t>
   </si>
   <si>
     <t xml:space="preserve">4.95496845245361</t>
@@ -668,49 +668,49 @@
     <t xml:space="preserve">4.93920850753784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00224924087524</t>
+    <t xml:space="preserve">5.00224876403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.99909687042236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93605709075928</t>
+    <t xml:space="preserve">4.93605613708496</t>
   </si>
   <si>
     <t xml:space="preserve">4.89823198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8887767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99279260635376</t>
+    <t xml:space="preserve">4.88877630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99279356002808</t>
   </si>
   <si>
     <t xml:space="preserve">5.13778495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16930627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14408922195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.163001537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92975282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98333692550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98018550872803</t>
+    <t xml:space="preserve">5.1693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1440896987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16300106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92975234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98333740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98018455505371</t>
   </si>
   <si>
     <t xml:space="preserve">4.86356019973755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05898523330688</t>
+    <t xml:space="preserve">5.05898571014404</t>
   </si>
   <si>
     <t xml:space="preserve">5.04007339477539</t>
@@ -719,19 +719,19 @@
     <t xml:space="preserve">5.00540065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08420038223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01170492172241</t>
+    <t xml:space="preserve">5.08420133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01170444488525</t>
   </si>
   <si>
     <t xml:space="preserve">5.08735275268555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37103509902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5380916595459</t>
+    <t xml:space="preserve">5.37103462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53809118270874</t>
   </si>
   <si>
     <t xml:space="preserve">5.36157846450806</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">5.29538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15354585647583</t>
+    <t xml:space="preserve">5.15354537963867</t>
   </si>
   <si>
     <t xml:space="preserve">5.01485681533813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13463401794434</t>
+    <t xml:space="preserve">5.13463354110718</t>
   </si>
   <si>
     <t xml:space="preserve">4.92344856262207</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">4.96757698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91084051132202</t>
+    <t xml:space="preserve">4.91084003448486</t>
   </si>
   <si>
     <t xml:space="preserve">5.05583333969116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17560911178589</t>
+    <t xml:space="preserve">5.17560958862305</t>
   </si>
   <si>
     <t xml:space="preserve">5.14724159240723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11887311935425</t>
+    <t xml:space="preserve">5.11887359619141</t>
   </si>
   <si>
     <t xml:space="preserve">5.07159328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0243124961853</t>
+    <t xml:space="preserve">5.02431344985962</t>
   </si>
   <si>
     <t xml:space="preserve">4.97388029098511</t>
@@ -785,43 +785,43 @@
     <t xml:space="preserve">4.82888793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69335079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72802352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7689995765686</t>
+    <t xml:space="preserve">4.69335174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72802305221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76900005340576</t>
   </si>
   <si>
     <t xml:space="preserve">4.94866466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99594449996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17245769500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21658515930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2260422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30169057846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24810552597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23549842834473</t>
+    <t xml:space="preserve">4.99594497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17245817184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21658563613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22604179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30169010162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24810600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23549795150757</t>
   </si>
   <si>
     <t xml:space="preserve">5.25125789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26071453094482</t>
+    <t xml:space="preserve">5.26071405410767</t>
   </si>
   <si>
     <t xml:space="preserve">5.32375431060791</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">5.33636236190796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27962684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.339515209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31745195388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35212326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32690572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19767379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20713043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20397806167603</t>
+    <t xml:space="preserve">5.27962589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33951473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31745100021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35212278366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32690715789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19767427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20712995529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20397853851318</t>
   </si>
   <si>
     <t xml:space="preserve">5.23865032196045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13148212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104944229126</t>
+    <t xml:space="preserve">5.13148164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0810489654541</t>
   </si>
   <si>
     <t xml:space="preserve">4.8509521484375</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">5.46559476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38994693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35527420043945</t>
+    <t xml:space="preserve">5.38994646072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35527467727661</t>
   </si>
   <si>
     <t xml:space="preserve">5.563307762146</t>
@@ -884,28 +884,28 @@
     <t xml:space="preserve">5.57906818389893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59798002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70830106735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75242900848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7366681098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72090864181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79340410232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76188516616821</t>
+    <t xml:space="preserve">5.59798049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70830059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78709983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75242805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73666858673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72090816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7934045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76188468933105</t>
   </si>
   <si>
     <t xml:space="preserve">5.78394889831543</t>
@@ -920,37 +920,37 @@
     <t xml:space="preserve">5.68938827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73036479949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76818895339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73982048034668</t>
+    <t xml:space="preserve">5.73036432266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76818799972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73982000350952</t>
   </si>
   <si>
     <t xml:space="preserve">5.71460390090942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62950038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45298624038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32060194015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3426661491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27332210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36472988128662</t>
+    <t xml:space="preserve">5.62949991226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45298671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32060241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34266710281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25441026687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27332162857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36473035812378</t>
   </si>
   <si>
     <t xml:space="preserve">5.41516304016113</t>
@@ -959,37 +959,37 @@
     <t xml:space="preserve">5.39625072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44983577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37418699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39309930801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29223394393921</t>
+    <t xml:space="preserve">5.4498348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37418651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29223489761353</t>
   </si>
   <si>
     <t xml:space="preserve">5.21028137207031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35842657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34581899642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48135423660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46874809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44668292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754686355591</t>
+    <t xml:space="preserve">5.35842609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34581804275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48135471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46874761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44668340682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754829406738</t>
   </si>
   <si>
     <t xml:space="preserve">5.5948281288147</t>
@@ -998,130 +998,130 @@
     <t xml:space="preserve">5.52548360824585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56015586853027</t>
+    <t xml:space="preserve">5.56015491485596</t>
   </si>
   <si>
     <t xml:space="preserve">5.59167575836182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66101884841919</t>
+    <t xml:space="preserve">5.66102027893066</t>
   </si>
   <si>
     <t xml:space="preserve">5.7177562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67362833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67678022384644</t>
+    <t xml:space="preserve">5.67362880706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67678117752075</t>
   </si>
   <si>
     <t xml:space="preserve">5.49081134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5097222328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56961107254028</t>
+    <t xml:space="preserve">5.50972270965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56961154937744</t>
   </si>
   <si>
     <t xml:space="preserve">5.60743618011475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58222007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55700254440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5443959236145</t>
+    <t xml:space="preserve">5.58221960067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55700302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54439544677734</t>
   </si>
   <si>
     <t xml:space="preserve">5.67993211746216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67047595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48450756072998</t>
+    <t xml:space="preserve">5.67047691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61058807373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48450708389282</t>
   </si>
   <si>
     <t xml:space="preserve">5.53493928909302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47505140304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43407487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33005857467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50026798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56645965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5065712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51602745056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58537101745605</t>
+    <t xml:space="preserve">5.52863550186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47505187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38048982620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43407535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33005809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50026702880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56645917892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50657176971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51602697372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5853705406189</t>
   </si>
   <si>
     <t xml:space="preserve">5.66732358932495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65471696853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69254064559937</t>
+    <t xml:space="preserve">5.65471649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69254016876221</t>
   </si>
   <si>
     <t xml:space="preserve">5.72406053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75873279571533</t>
+    <t xml:space="preserve">5.75873327255249</t>
   </si>
   <si>
     <t xml:space="preserve">5.71145296096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79970932006836</t>
+    <t xml:space="preserve">5.79970788955688</t>
   </si>
   <si>
     <t xml:space="preserve">5.74612474441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77449226379395</t>
+    <t xml:space="preserve">5.7744927406311</t>
   </si>
   <si>
     <t xml:space="preserve">5.74927616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77764463424683</t>
+    <t xml:space="preserve">5.77764415740967</t>
   </si>
   <si>
     <t xml:space="preserve">5.78079652786255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77133989334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81862020492554</t>
+    <t xml:space="preserve">5.77133941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81862115859985</t>
   </si>
   <si>
     <t xml:space="preserve">5.91633367538452</t>
@@ -1130,118 +1130,118 @@
     <t xml:space="preserve">5.97622203826904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93209362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01404523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07708597183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05187034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03295707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10860538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10230302810669</t>
+    <t xml:space="preserve">5.93209314346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01404571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07708692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05186986923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03295803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10860633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10230159759521</t>
   </si>
   <si>
     <t xml:space="preserve">6.2315354347229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21577453613281</t>
+    <t xml:space="preserve">6.21577501296997</t>
   </si>
   <si>
     <t xml:space="preserve">6.2252311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21892642974854</t>
+    <t xml:space="preserve">6.21892690658569</t>
   </si>
   <si>
     <t xml:space="preserve">6.20001459121704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23178100585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13353872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885801315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20558214187622</t>
+    <t xml:space="preserve">6.23178148269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13353824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885705947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20558261871338</t>
   </si>
   <si>
     <t xml:space="preserve">6.1695613861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0975170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22850561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34966945648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28745079040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33329629898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19903326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2219557762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382394790649</t>
+    <t xml:space="preserve">6.09751749038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22850513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34967041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28745031356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33329725265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29399967193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1990327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22195625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382442474365</t>
   </si>
   <si>
     <t xml:space="preserve">6.28090143203735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28417539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25470352172852</t>
+    <t xml:space="preserve">6.28417587280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25470304489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.24815368652344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1237154006958</t>
+    <t xml:space="preserve">6.12371587753296</t>
   </si>
   <si>
     <t xml:space="preserve">6.15646123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18593406677246</t>
+    <t xml:space="preserve">6.18593454360962</t>
   </si>
   <si>
     <t xml:space="preserve">6.24160432815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26452684402466</t>
+    <t xml:space="preserve">6.26452732086182</t>
   </si>
   <si>
     <t xml:space="preserve">6.26125288009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19575834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14663791656494</t>
+    <t xml:space="preserve">6.19575881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14663743972778</t>
   </si>
   <si>
     <t xml:space="preserve">6.27107715606689</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">6.41843938827515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39879083633423</t>
+    <t xml:space="preserve">6.39879131317139</t>
   </si>
   <si>
     <t xml:space="preserve">6.40206575393677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39224100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41188907623291</t>
+    <t xml:space="preserve">6.39224147796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41188955307007</t>
   </si>
   <si>
     <t xml:space="preserve">6.49375772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51995468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57562589645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5330548286438</t>
+    <t xml:space="preserve">6.5199556350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57562494277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53305339813232</t>
   </si>
   <si>
     <t xml:space="preserve">6.52978038787842</t>
@@ -1283,49 +1283,49 @@
     <t xml:space="preserve">6.43808698654175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45380592346191</t>
+    <t xml:space="preserve">6.45380544662476</t>
   </si>
   <si>
     <t xml:space="preserve">6.36604404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41319942474365</t>
+    <t xml:space="preserve">6.41319847106934</t>
   </si>
   <si>
     <t xml:space="preserve">6.47607326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51406049728394</t>
+    <t xml:space="preserve">6.51406145095825</t>
   </si>
   <si>
     <t xml:space="preserve">6.45642566680908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26780223846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36997270584106</t>
+    <t xml:space="preserve">6.2678017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36997318267822</t>
   </si>
   <si>
     <t xml:space="preserve">6.32019710540771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36473369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41581869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44594717025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46690368652344</t>
+    <t xml:space="preserve">6.36473321914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41581916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4551157951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47214460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44594764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46690511703491</t>
   </si>
   <si>
     <t xml:space="preserve">6.47869396209717</t>
@@ -1334,76 +1334,76 @@
     <t xml:space="preserve">6.40010118484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46166563034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47476387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51013088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674694061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21016836166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31102848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44463777542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46559524536133</t>
+    <t xml:space="preserve">6.46166515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4747633934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51013135910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41974878311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674741744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21016788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31102895736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44463682174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46559572219849</t>
   </si>
   <si>
     <t xml:space="preserve">6.45904588699341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39748048782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42498874664307</t>
+    <t xml:space="preserve">6.3974814414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42498922348022</t>
   </si>
   <si>
     <t xml:space="preserve">6.45773506164551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40664958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37390422821045</t>
+    <t xml:space="preserve">6.40664911270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738409042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37390375137329</t>
   </si>
   <si>
     <t xml:space="preserve">6.25732278823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21671581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24684429168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25339365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27828121185303</t>
+    <t xml:space="preserve">6.21671628952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24684476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25339412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">6.35294485092163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34508609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4171290397644</t>
+    <t xml:space="preserve">6.34508562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41712951660156</t>
   </si>
   <si>
     <t xml:space="preserve">6.39355134963989</t>
@@ -1412,34 +1412,34 @@
     <t xml:space="preserve">6.54811763763428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63457059860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66076803207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79503059387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84415102005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70661401748657</t>
+    <t xml:space="preserve">6.63456964492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66076755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79503107070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84415245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70661354064941</t>
   </si>
   <si>
     <t xml:space="preserve">6.69351530075073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59199857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6738657951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55925226211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69678974151611</t>
+    <t xml:space="preserve">6.59199905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67386722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55925178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69679021835327</t>
   </si>
   <si>
     <t xml:space="preserve">6.72953653335571</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">6.46428537368774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51537179946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56907606124878</t>
+    <t xml:space="preserve">6.51537084579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">6.52191972732544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20754766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01499462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91544246673584</t>
+    <t xml:space="preserve">6.20754814147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01499366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.915442943573</t>
   </si>
   <si>
     <t xml:space="preserve">5.95343017578125</t>
@@ -1475,22 +1475,22 @@
     <t xml:space="preserve">5.81327199935913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58011293411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24085140228271</t>
+    <t xml:space="preserve">5.58011245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24085187911987</t>
   </si>
   <si>
     <t xml:space="preserve">5.0312705039978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28407764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42161655426025</t>
+    <t xml:space="preserve">5.38624906539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28407859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4216160774231</t>
   </si>
   <si>
     <t xml:space="preserve">5.32861423492432</t>
@@ -1502,79 +1502,79 @@
     <t xml:space="preserve">5.35874176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23823165893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12689256668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37708044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30503606796265</t>
+    <t xml:space="preserve">5.23823213577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12689208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37707996368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30503702163696</t>
   </si>
   <si>
     <t xml:space="preserve">5.40327787399292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34826278686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28276777267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26050043106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44257497787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38755893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52378702163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33254384994507</t>
+    <t xml:space="preserve">5.34826326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28276872634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26049995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4425745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38755941390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52378797531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33254432678223</t>
   </si>
   <si>
     <t xml:space="preserve">5.29848718643188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21727418899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18321704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21465396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18845653533936</t>
+    <t xml:space="preserve">5.21727466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18321752548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21465492248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1884560585022</t>
   </si>
   <si>
     <t xml:space="preserve">5.25133085250854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32206583023071</t>
+    <t xml:space="preserve">5.32206535339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.39148902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30634689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34040403366089</t>
+    <t xml:space="preserve">5.30634641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34040355682373</t>
   </si>
   <si>
     <t xml:space="preserve">5.26835918426514</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17928695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20155572891235</t>
+    <t xml:space="preserve">5.17928743362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2015552520752</t>
   </si>
   <si>
     <t xml:space="preserve">5.27097988128662</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">5.33778285980225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32468509674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3561224937439</t>
+    <t xml:space="preserve">5.32468461990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35612201690674</t>
   </si>
   <si>
     <t xml:space="preserve">5.51330804824829</t>
@@ -1601,52 +1601,52 @@
     <t xml:space="preserve">5.62857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73205852508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68097305297852</t>
+    <t xml:space="preserve">5.73205900192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68097352981567</t>
   </si>
   <si>
     <t xml:space="preserve">5.81851148605347</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74646759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68752336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78052473068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68490362167358</t>
+    <t xml:space="preserve">5.74646854400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68752241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78052520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68490314483643</t>
   </si>
   <si>
     <t xml:space="preserve">5.75956630706787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75563716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76742553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70848035812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5958309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44912338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56439352035522</t>
+    <t xml:space="preserve">5.75563669204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76742601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70848083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59583044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44912385940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56439447402954</t>
   </si>
   <si>
     <t xml:space="preserve">5.50282955169678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51985788345337</t>
+    <t xml:space="preserve">5.51985740661621</t>
   </si>
   <si>
     <t xml:space="preserve">5.61023950576782</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">5.49759006500244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43340444564819</t>
+    <t xml:space="preserve">5.43340492248535</t>
   </si>
   <si>
     <t xml:space="preserve">5.43864393234253</t>
@@ -1667,31 +1667,31 @@
     <t xml:space="preserve">5.39541864395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41899681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25002098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55522441864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73598957061768</t>
+    <t xml:space="preserve">5.41899633407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25002145767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55522394180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73598861694336</t>
   </si>
   <si>
     <t xml:space="preserve">5.68621301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93771123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90627384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93640184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89710378646851</t>
+    <t xml:space="preserve">5.93771076202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90627336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89710474014282</t>
   </si>
   <si>
     <t xml:space="preserve">5.91282320022583</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">6.03333330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00844430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00713491439819</t>
+    <t xml:space="preserve">6.09620714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00844526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00713443756104</t>
   </si>
   <si>
     <t xml:space="preserve">5.96390867233276</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">6.00451564788818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63512754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46353244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48842000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48056125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38886880874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13737058639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18059730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07187700271606</t>
+    <t xml:space="preserve">5.63512706756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4635329246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4884204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48056077957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3888692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13737106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18059682846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07187652587891</t>
   </si>
   <si>
     <t xml:space="preserve">5.02865028381348</t>
@@ -1754,58 +1754,58 @@
     <t xml:space="preserve">5.03520011901855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11379337310791</t>
+    <t xml:space="preserve">5.11379289627075</t>
   </si>
   <si>
     <t xml:space="preserve">5.05484819412231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00638246536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15963935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06663703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07842588424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90683174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09545469284058</t>
+    <t xml:space="preserve">5.00638198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15963888168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06663751602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07842636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90683126449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09545516967773</t>
   </si>
   <si>
     <t xml:space="preserve">4.95791673660278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09938383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11248350143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0771164894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19500637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.136061668396</t>
+    <t xml:space="preserve">5.09938430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11248302459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07711601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19500589370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13606119155884</t>
   </si>
   <si>
     <t xml:space="preserve">5.11641311645508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13868141174316</t>
+    <t xml:space="preserve">5.13868093490601</t>
   </si>
   <si>
     <t xml:space="preserve">5.15308904647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14915943145752</t>
+    <t xml:space="preserve">5.14916038513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.08104610443115</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">5.15818929672241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987808227539</t>
+    <t xml:space="preserve">5.03690242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987903594971</t>
   </si>
   <si>
     <t xml:space="preserve">5.08011960983276</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">5.11776065826416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34500026702881</t>
+    <t xml:space="preserve">5.34499979019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.36730527877808</t>
@@ -1835,16 +1835,16 @@
     <t xml:space="preserve">5.39100503921509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44258785247803</t>
+    <t xml:space="preserve">5.44258737564087</t>
   </si>
   <si>
     <t xml:space="preserve">5.44119310379028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47604513168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37706470489502</t>
+    <t xml:space="preserve">5.47604608535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37706422805786</t>
   </si>
   <si>
     <t xml:space="preserve">5.38821697235107</t>
@@ -1859,28 +1859,28 @@
     <t xml:space="preserve">5.10242557525635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07733154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24462413787842</t>
+    <t xml:space="preserve">5.07733106613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24462461471558</t>
   </si>
   <si>
     <t xml:space="preserve">5.26553535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31293535232544</t>
+    <t xml:space="preserve">5.31293487548828</t>
   </si>
   <si>
     <t xml:space="preserve">5.23068284988403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27668905258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3728814125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25577640533447</t>
+    <t xml:space="preserve">5.27668857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37288188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25577735900879</t>
   </si>
   <si>
     <t xml:space="preserve">5.12751913070679</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">5.09127235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08709001541138</t>
+    <t xml:space="preserve">5.08709049224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.3896107673645</t>
@@ -1904,25 +1904,25 @@
     <t xml:space="preserve">5.37985229492188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36312341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33524131774902</t>
+    <t xml:space="preserve">5.36312294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33524036407471</t>
   </si>
   <si>
     <t xml:space="preserve">5.33802890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40494632720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34639406204224</t>
+    <t xml:space="preserve">5.40494680404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34639358520508</t>
   </si>
   <si>
     <t xml:space="preserve">5.33942270278931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46210479736328</t>
+    <t xml:space="preserve">5.46210432052612</t>
   </si>
   <si>
     <t xml:space="preserve">5.46907520294189</t>
@@ -1934,19 +1934,19 @@
     <t xml:space="preserve">5.50671577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48859310150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49277448654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50253438949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55969142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48998641967773</t>
+    <t xml:space="preserve">5.48859262466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49277496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50253391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55969190597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48998689651489</t>
   </si>
   <si>
     <t xml:space="preserve">5.44816303253174</t>
@@ -1955,31 +1955,31 @@
     <t xml:space="preserve">5.45931673049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29481220245361</t>
+    <t xml:space="preserve">5.29481172561646</t>
   </si>
   <si>
     <t xml:space="preserve">5.14424848556519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11218404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39797496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40355253219604</t>
+    <t xml:space="preserve">5.11218452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28505277633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39797592163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40355205535889</t>
   </si>
   <si>
     <t xml:space="preserve">5.49835109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52623319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62521457672119</t>
+    <t xml:space="preserve">5.5262336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62521409988403</t>
   </si>
   <si>
     <t xml:space="preserve">5.59036254882812</t>
@@ -1994,37 +1994,37 @@
     <t xml:space="preserve">5.77717256546021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79808330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73953199386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75486612319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82735967636108</t>
+    <t xml:space="preserve">5.79808378219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73953104019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75486660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82736015319824</t>
   </si>
   <si>
     <t xml:space="preserve">5.91797685623169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98071193695068</t>
+    <t xml:space="preserve">5.98071146011353</t>
   </si>
   <si>
     <t xml:space="preserve">6.14939832687378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02532339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07969331741333</t>
+    <t xml:space="preserve">6.02532243728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07969284057617</t>
   </si>
   <si>
     <t xml:space="preserve">6.08945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20376777648926</t>
+    <t xml:space="preserve">6.20376825332642</t>
   </si>
   <si>
     <t xml:space="preserve">6.10060453414917</t>
@@ -2036,46 +2036,46 @@
     <t xml:space="preserve">6.12430477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10339212417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18982744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21631526947021</t>
+    <t xml:space="preserve">6.10339260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18982791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21631622314453</t>
   </si>
   <si>
     <t xml:space="preserve">6.26510906219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39894342422485</t>
+    <t xml:space="preserve">6.3989429473877</t>
   </si>
   <si>
     <t xml:space="preserve">6.35990762710571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24001550674438</t>
+    <t xml:space="preserve">6.24001502990723</t>
   </si>
   <si>
     <t xml:space="preserve">6.28602075576782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23583269119263</t>
+    <t xml:space="preserve">6.2358341217041</t>
   </si>
   <si>
     <t xml:space="preserve">6.17728137969971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22468042373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35293865203857</t>
+    <t xml:space="preserve">6.22467994689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35293817520142</t>
   </si>
   <si>
     <t xml:space="preserve">6.42264318466187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45610189437866</t>
+    <t xml:space="preserve">6.45610237121582</t>
   </si>
   <si>
     <t xml:space="preserve">6.5188364982605</t>
@@ -2090,61 +2090,61 @@
     <t xml:space="preserve">6.47840690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52162408828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46446752548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48537731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.578782081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63175964355469</t>
+    <t xml:space="preserve">6.52162456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4644660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4853777885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63175916671753</t>
   </si>
   <si>
     <t xml:space="preserve">6.6707935333252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69867563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67915725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62199926376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54392957687378</t>
+    <t xml:space="preserve">6.69867515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67915821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6220006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">6.52441215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56205272674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194627761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5871467590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62478876113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26789665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34875535964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20237398147583</t>
+    <t xml:space="preserve">6.56205368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194770812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58714771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6247878074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41706609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.267897605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34875583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20237445831299</t>
   </si>
   <si>
     <t xml:space="preserve">6.06435823440552</t>
@@ -2156,16 +2156,16 @@
     <t xml:space="preserve">6.18146276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16612815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06575202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99465227127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01556491851807</t>
+    <t xml:space="preserve">6.16612720489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06575155258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99465274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01556348800659</t>
   </si>
   <si>
     <t xml:space="preserve">5.95980024337769</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">5.91937065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8426947593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8343300819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76601982116699</t>
+    <t xml:space="preserve">5.84269523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83433055877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">5.73256063461304</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">5.88173007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84966564178467</t>
+    <t xml:space="preserve">5.84966611862183</t>
   </si>
   <si>
     <t xml:space="preserve">5.87894248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96816492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9667706489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93888902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97374105453491</t>
+    <t xml:space="preserve">5.9681658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96677112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93888854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97374057769775</t>
   </si>
   <si>
     <t xml:space="preserve">5.94307041168213</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">6.16333961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382219314575</t>
+    <t xml:space="preserve">6.14382314682007</t>
   </si>
   <si>
     <t xml:space="preserve">6.19122171401978</t>
@@ -2228,85 +2228,85 @@
     <t xml:space="preserve">6.17031002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29577970504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33760356903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31947946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23862075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30972099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47422504425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60248327255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57041788101196</t>
+    <t xml:space="preserve">6.29577922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33760213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31947898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2386212348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30972051620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47422456741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60248231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5704174041748</t>
   </si>
   <si>
     <t xml:space="preserve">6.51186561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49095487594604</t>
+    <t xml:space="preserve">6.49095439910889</t>
   </si>
   <si>
     <t xml:space="preserve">6.55229425430298</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54114198684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54671859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792385101318</t>
+    <t xml:space="preserve">6.54114246368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54671812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792432785034</t>
   </si>
   <si>
     <t xml:space="preserve">6.56762981414795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53277683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41288423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44355440139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5146541595459</t>
+    <t xml:space="preserve">6.53277778625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41288471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44355487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51465463638306</t>
   </si>
   <si>
     <t xml:space="preserve">6.4895601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50350093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33481550216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31111431121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32087373733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15915679931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10478734970093</t>
+    <t xml:space="preserve">6.50350141525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33481359481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31111478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32087278366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15915775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10478687286377</t>
   </si>
   <si>
     <t xml:space="preserve">6.03647613525391</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">5.9249472618103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91379451751709</t>
+    <t xml:space="preserve">5.91379499435425</t>
   </si>
   <si>
     <t xml:space="preserve">5.94446516036987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8064489364624</t>
+    <t xml:space="preserve">5.80644845962524</t>
   </si>
   <si>
     <t xml:space="preserve">5.93052434921265</t>
@@ -2336,46 +2336,46 @@
     <t xml:space="preserve">6.06714677810669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11315202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04344606399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11872720718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13963985443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1926155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28044462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3571195602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296537399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59830045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68055200576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63036489486694</t>
+    <t xml:space="preserve">6.11315250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04344654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11872816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13964033126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19261598587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28044509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35712003707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59829950332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68055248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6303653717041</t>
   </si>
   <si>
     <t xml:space="preserve">6.66382360458374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72655820846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66242790222168</t>
+    <t xml:space="preserve">6.72655725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.662428855896</t>
   </si>
   <si>
     <t xml:space="preserve">6.63454675674438</t>
@@ -2390,37 +2390,37 @@
     <t xml:space="preserve">6.89803266525269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90779209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94682598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0437159538269</t>
+    <t xml:space="preserve">6.90779113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94682693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04371643066406</t>
   </si>
   <si>
     <t xml:space="preserve">6.95379734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98446702957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95658493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76419925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8464503288269</t>
+    <t xml:space="preserve">6.98446846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95658540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76419830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84645080566406</t>
   </si>
   <si>
     <t xml:space="preserve">6.81578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83390378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79347562789917</t>
+    <t xml:space="preserve">6.83390426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79347515106201</t>
   </si>
   <si>
     <t xml:space="preserve">6.80462789535522</t>
@@ -2429,37 +2429,37 @@
     <t xml:space="preserve">7.03326177597046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19009780883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40269947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38178730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36087512969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43058156967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50377225875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55953598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.552565574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58044767379761</t>
+    <t xml:space="preserve">7.19009733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27025890350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481641769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40269994735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38178777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36087608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43058204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50377178192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55953693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256509780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58044719696045</t>
   </si>
   <si>
     <t xml:space="preserve">7.44103765487671</t>
@@ -2468,91 +2468,91 @@
     <t xml:space="preserve">7.42361068725586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48286104202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6431827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59438896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51422786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27374458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42012548446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35390615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51857566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48940467834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752691268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52586698532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47481870651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52951335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40189456939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33261489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29250574111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35449266433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32532215118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34720087051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22687387466431</t>
+    <t xml:space="preserve">7.48286008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64318227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59438943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51422691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27374362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42012596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35390567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51857471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48940420150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752643585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52586650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47481966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52951383590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40189409255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3326153755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34720039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22687435150146</t>
   </si>
   <si>
     <t xml:space="preserve">7.3727240562439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38366270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24437713623047</t>
+    <t xml:space="preserve">7.38366317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24437522888184</t>
   </si>
   <si>
     <t xml:space="preserve">7.31438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28229713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3581395149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21958112716675</t>
+    <t xml:space="preserve">7.2822961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35813856124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2852144241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21958065032959</t>
   </si>
   <si>
     <t xml:space="preserve">7.15686559677124</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">7.1641583442688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18457841873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25021028518677</t>
+    <t xml:space="preserve">7.18457794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25021076202393</t>
   </si>
   <si>
     <t xml:space="preserve">7.26187753677368</t>
@@ -2579,43 +2579,43 @@
     <t xml:space="preserve">7.17874336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18020153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08539962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15832471847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11019372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05768775939941</t>
+    <t xml:space="preserve">7.1802020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08539915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15832424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11019325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05768823623657</t>
   </si>
   <si>
     <t xml:space="preserve">7.07810688018799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99643039703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93809127807617</t>
+    <t xml:space="preserve">6.99643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93809032440186</t>
   </si>
   <si>
     <t xml:space="preserve">6.97309541702271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77328014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98622179031372</t>
+    <t xml:space="preserve">6.77328062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98622131347656</t>
   </si>
   <si>
     <t xml:space="preserve">6.93371534347534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75286102294922</t>
+    <t xml:space="preserve">6.75286197662354</t>
   </si>
   <si>
     <t xml:space="preserve">6.5720067024231</t>
@@ -2624,61 +2624,61 @@
     <t xml:space="preserve">6.71931552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98038721084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86954116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00372409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04164457321167</t>
+    <t xml:space="preserve">6.80536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98038768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86954212188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00372314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04164409637451</t>
   </si>
   <si>
     <t xml:space="preserve">7.0606050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06206369400024</t>
+    <t xml:space="preserve">7.06206321716309</t>
   </si>
   <si>
     <t xml:space="preserve">7.00518178939819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03289318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99351453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86370658874512</t>
+    <t xml:space="preserve">7.03289270401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99351358413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86370754241943</t>
   </si>
   <si>
     <t xml:space="preserve">6.45240926742554</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42178106307983</t>
+    <t xml:space="preserve">6.42178201675415</t>
   </si>
   <si>
     <t xml:space="preserve">6.38677835464478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23363447189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97256231307983</t>
+    <t xml:space="preserve">6.23363494873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97256278991699</t>
   </si>
   <si>
     <t xml:space="preserve">5.76253890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71003293991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63564920425415</t>
+    <t xml:space="preserve">5.71003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63564968109131</t>
   </si>
   <si>
     <t xml:space="preserve">5.39937210083008</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">4.33174896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52228045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7760603427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33850979804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25537538528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06649923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0424337387085</t>
+    <t xml:space="preserve">3.52228021621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77606058120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33851003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25537514686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06649899482727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04243397712708</t>
   </si>
   <si>
     <t xml:space="preserve">3.10150289535522</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">3.17661571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61854195594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90440773963928</t>
+    <t xml:space="preserve">3.61854147911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90440821647644</t>
   </si>
   <si>
     <t xml:space="preserve">4.0108790397644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76439237594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62802243232727</t>
+    <t xml:space="preserve">3.76439213752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62802195549011</t>
   </si>
   <si>
     <t xml:space="preserve">3.66667222976685</t>
@@ -2741,19 +2741,19 @@
     <t xml:space="preserve">3.64917016029358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77460193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70605158805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97149991989136</t>
+    <t xml:space="preserve">3.77460145950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70605134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9714994430542</t>
   </si>
   <si>
     <t xml:space="preserve">4.05171680450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05900907516479</t>
+    <t xml:space="preserve">4.05900955200195</t>
   </si>
   <si>
     <t xml:space="preserve">4.04150724411011</t>
@@ -2765,28 +2765,28 @@
     <t xml:space="preserve">3.57989144325256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64771151542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69292545318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56238985061646</t>
+    <t xml:space="preserve">3.64771175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69292521476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56238961219788</t>
   </si>
   <si>
     <t xml:space="preserve">3.51571750640869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73959708213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82419061660767</t>
+    <t xml:space="preserve">3.73959732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82419085502625</t>
   </si>
   <si>
     <t xml:space="preserve">3.95545554161072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02254724502563</t>
+    <t xml:space="preserve">4.02254629135132</t>
   </si>
   <si>
     <t xml:space="preserve">3.85627746582031</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">3.76585030555725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75855803489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74834823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78918647766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607642173767</t>
+    <t xml:space="preserve">3.75855779647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74834871292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78918671607971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607594490051</t>
   </si>
   <si>
     <t xml:space="preserve">3.85336065292358</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">3.80960536003113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74980688095093</t>
+    <t xml:space="preserve">3.74980711936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.69730067253113</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">3.77168416976929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78481149673462</t>
+    <t xml:space="preserve">3.78481125831604</t>
   </si>
   <si>
     <t xml:space="preserve">3.99921107292175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16256332397461</t>
+    <t xml:space="preserve">4.16256284713745</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862258911133</t>
@@ -2849,28 +2849,28 @@
     <t xml:space="preserve">4.60011291503906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69929170608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95452976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95307111740112</t>
+    <t xml:space="preserve">4.69929122924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95452928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95307016372681</t>
   </si>
   <si>
     <t xml:space="preserve">5.18351316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34540700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17330455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07995986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86410236358643</t>
+    <t xml:space="preserve">5.34540748596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17330408096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07996034622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86410188674927</t>
   </si>
   <si>
     <t xml:space="preserve">4.96473836898804</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">5.23164415359497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12079763412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97348880767822</t>
+    <t xml:space="preserve">5.12079811096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97348976135254</t>
   </si>
   <si>
     <t xml:space="preserve">4.99682569503784</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">4.71095943450928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75033903121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55927562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76200723648071</t>
+    <t xml:space="preserve">4.75033855438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55927515029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76200675964355</t>
   </si>
   <si>
     <t xml:space="preserve">4.65991163253784</t>
@@ -2930,52 +2930,52 @@
     <t xml:space="preserve">4.88014554977417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79701089859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9297342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05079030990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14559316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16601181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13246583938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2520637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25498008728027</t>
+    <t xml:space="preserve">4.79701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92973518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05078983306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13830041885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14559268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16601133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13246631622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25206327438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25498056411743</t>
   </si>
   <si>
     <t xml:space="preserve">5.316237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22435235977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16309404373169</t>
+    <t xml:space="preserve">5.22435188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16309452056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.12663221359253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07850217819214</t>
+    <t xml:space="preserve">5.07850170135498</t>
   </si>
   <si>
     <t xml:space="preserve">5.05954122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92244148254395</t>
+    <t xml:space="preserve">4.9224419593811</t>
   </si>
   <si>
     <t xml:space="preserve">4.94286108016968</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">4.81305456161499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94723701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91369152069092</t>
+    <t xml:space="preserve">4.94723606109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91369104385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.97786569595337</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">5.28706741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29435968399048</t>
+    <t xml:space="preserve">5.29436016082764</t>
   </si>
   <si>
     <t xml:space="preserve">5.20247411727905</t>
@@ -3014,19 +3014,19 @@
     <t xml:space="preserve">5.24622964859009</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12809133529663</t>
+    <t xml:space="preserve">5.12809085845947</t>
   </si>
   <si>
     <t xml:space="preserve">5.09746170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24768781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27685785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4445858001709</t>
+    <t xml:space="preserve">5.24768829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27685832977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44458532333374</t>
   </si>
   <si>
     <t xml:space="preserve">5.47813129425049</t>
@@ -3041,31 +3041,31 @@
     <t xml:space="preserve">5.33519744873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32061290740967</t>
+    <t xml:space="preserve">5.32061243057251</t>
   </si>
   <si>
     <t xml:space="preserve">5.22726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21414184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08141803741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17767953872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39207935333252</t>
+    <t xml:space="preserve">5.21414232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08141899108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17768001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39207983016968</t>
   </si>
   <si>
     <t xml:space="preserve">5.28269195556641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29873514175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18643093109131</t>
+    <t xml:space="preserve">5.29873466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18643045425415</t>
   </si>
   <si>
     <t xml:space="preserve">5.08725261688232</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">4.87722873687744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76054859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95161199569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87576961517334</t>
+    <t xml:space="preserve">4.76054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95161247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8757700920105</t>
   </si>
   <si>
     <t xml:space="preserve">4.88452100753784</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">4.84368324279785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92390012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08871126174927</t>
+    <t xml:space="preserve">4.92390060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08871030807495</t>
   </si>
   <si>
     <t xml:space="preserve">5.20976686477661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08579444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28560876846313</t>
+    <t xml:space="preserve">5.08579397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28560924530029</t>
   </si>
   <si>
     <t xml:space="preserve">5.23310279846191</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">5.02016162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82180547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84222412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79992771148682</t>
+    <t xml:space="preserve">4.82180595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84222459793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79992818832397</t>
   </si>
   <si>
     <t xml:space="preserve">4.84951686859131</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">4.74012899398804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74596309661865</t>
+    <t xml:space="preserve">4.74596357345581</t>
   </si>
   <si>
     <t xml:space="preserve">4.78971815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76638221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64095115661621</t>
+    <t xml:space="preserve">4.76638174057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64095163345337</t>
   </si>
   <si>
     <t xml:space="preserve">4.41050815582275</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">4.46884822845459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43967819213867</t>
+    <t xml:space="preserve">4.43967866897583</t>
   </si>
   <si>
     <t xml:space="preserve">4.59427881240845</t>
@@ -3167,55 +3167,55 @@
     <t xml:space="preserve">5.3089451789856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1966404914856</t>
+    <t xml:space="preserve">5.19664001464844</t>
   </si>
   <si>
     <t xml:space="preserve">5.20539093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51605176925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5962700843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51459407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58460187911987</t>
+    <t xml:space="preserve">5.51605224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59626960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51459360122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58460140228271</t>
   </si>
   <si>
     <t xml:space="preserve">5.4985499382019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72899341583252</t>
+    <t xml:space="preserve">5.72899293899536</t>
   </si>
   <si>
     <t xml:space="preserve">5.75232934951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70419931411743</t>
+    <t xml:space="preserve">5.70419883728027</t>
   </si>
   <si>
     <t xml:space="preserve">5.63710737228394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45041942596436</t>
+    <t xml:space="preserve">5.45041990280151</t>
   </si>
   <si>
     <t xml:space="preserve">5.52917861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46500492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54230451583862</t>
+    <t xml:space="preserve">5.46500444412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54230546951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.60210418701172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53209543228149</t>
+    <t xml:space="preserve">5.53209590911865</t>
   </si>
   <si>
     <t xml:space="preserve">5.48979902267456</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">5.49709129333496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4752140045166</t>
+    <t xml:space="preserve">5.47521448135376</t>
   </si>
   <si>
     <t xml:space="preserve">5.34978294372559</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">5.36145114898682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53792953491211</t>
+    <t xml:space="preserve">5.53793001174927</t>
   </si>
   <si>
     <t xml:space="preserve">5.49271583557129</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">5.52042770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52480316162109</t>
+    <t xml:space="preserve">5.52480268478394</t>
   </si>
   <si>
     <t xml:space="preserve">5.40228891372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42270803451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62835645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61231327056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50438356399536</t>
+    <t xml:space="preserve">5.42270755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62835741043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61231279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50438451766968</t>
   </si>
   <si>
     <t xml:space="preserve">5.46208715438843</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">5.46937990188599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44750165939331</t>
+    <t xml:space="preserve">5.44750213623047</t>
   </si>
   <si>
     <t xml:space="preserve">5.38187026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47083854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40083026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40520620346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44896125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35707569122314</t>
+    <t xml:space="preserve">5.47083806991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40083074569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40520524978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44896078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35707521438599</t>
   </si>
   <si>
     <t xml:space="preserve">5.39499616622925</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">5.37020206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51167678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73045110702515</t>
+    <t xml:space="preserve">5.51167631149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7304515838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.89963817596436</t>
@@ -3317,31 +3317,31 @@
     <t xml:space="preserve">5.97985506057739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17383575439453</t>
+    <t xml:space="preserve">6.17383623123169</t>
   </si>
   <si>
     <t xml:space="preserve">6.23071765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41740608215332</t>
+    <t xml:space="preserve">6.417405128479</t>
   </si>
   <si>
     <t xml:space="preserve">6.50637435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48012113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59242582321167</t>
+    <t xml:space="preserve">6.48012065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59242630004883</t>
   </si>
   <si>
     <t xml:space="preserve">6.53700304031372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57930040359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54429578781128</t>
+    <t xml:space="preserve">6.57929944992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54429531097412</t>
   </si>
   <si>
     <t xml:space="preserve">6.62159585952759</t>
@@ -3350,34 +3350,34 @@
     <t xml:space="preserve">6.61430358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5822172164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53408575057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39552783966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28468227386475</t>
+    <t xml:space="preserve">6.58221673965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53408527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3955283164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28468179702759</t>
   </si>
   <si>
     <t xml:space="preserve">6.50199937820435</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43490839004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52679347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6113862991333</t>
+    <t xml:space="preserve">6.43490743637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52679300308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61138725280762</t>
   </si>
   <si>
     <t xml:space="preserve">6.7251501083374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73535871505737</t>
+    <t xml:space="preserve">6.73535966873169</t>
   </si>
   <si>
     <t xml:space="preserve">6.77473878860474</t>
@@ -3386,40 +3386,40 @@
     <t xml:space="preserve">6.85058069229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86516523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90162801742554</t>
+    <t xml:space="preserve">6.86516571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90162897109985</t>
   </si>
   <si>
     <t xml:space="preserve">7.01976776123047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09415006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09706830978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87975025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84037160873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77911424636841</t>
+    <t xml:space="preserve">7.09415149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09706878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87974977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84037065505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77911376953125</t>
   </si>
   <si>
     <t xml:space="preserve">6.90016984939575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90600442886353</t>
+    <t xml:space="preserve">6.90600395202637</t>
   </si>
   <si>
     <t xml:space="preserve">6.92058849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9395489692688</t>
+    <t xml:space="preserve">6.93954944610596</t>
   </si>
   <si>
     <t xml:space="preserve">7.03581047058105</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">6.86079072952271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77182245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80682516098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81849384307861</t>
+    <t xml:space="preserve">6.77182197570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80682563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81849431991577</t>
   </si>
   <si>
     <t xml:space="preserve">6.80974292755127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78640604019165</t>
+    <t xml:space="preserve">6.78640651702881</t>
   </si>
   <si>
     <t xml:space="preserve">6.85203886032104</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">6.7091064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.642014503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64639186859131</t>
+    <t xml:space="preserve">6.64201498031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64639043807983</t>
   </si>
   <si>
     <t xml:space="preserve">6.8359956741333</t>
@@ -3473,34 +3473,34 @@
     <t xml:space="preserve">6.80828475952148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82724571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85641574859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92788171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78057241439819</t>
+    <t xml:space="preserve">6.82724523544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85641527175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92788076400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78057336807251</t>
   </si>
   <si>
     <t xml:space="preserve">6.9089207649231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94684171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04018688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.054771900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01393270492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08394002914429</t>
+    <t xml:space="preserve">6.94684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04018640518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01393222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08394050598145</t>
   </si>
   <si>
     <t xml:space="preserve">7.13352966308594</t>
@@ -3509,40 +3509,40 @@
     <t xml:space="preserve">7.19770383834839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05914735794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06643867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102464675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915372848511</t>
+    <t xml:space="preserve">7.05914640426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06643915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915420532227</t>
   </si>
   <si>
     <t xml:space="preserve">7.11748647689819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14811515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21228933334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344581604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29979944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25604486465454</t>
+    <t xml:space="preserve">7.14811420440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27062940597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034462928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29979848861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25604391098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.26771211624146</t>
@@ -3551,106 +3551,106 @@
     <t xml:space="preserve">7.20791339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26333713531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25458526611328</t>
+    <t xml:space="preserve">7.26333665847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25458478927612</t>
   </si>
   <si>
     <t xml:space="preserve">7.23270845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23562526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17582654953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22249937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27500438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20062065124512</t>
+    <t xml:space="preserve">7.23562574386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17582607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22249841690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28083944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27500486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20062112808228</t>
   </si>
   <si>
     <t xml:space="preserve">7.18311929702759</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19332838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18749523162842</t>
+    <t xml:space="preserve">7.19332885742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18749475479126</t>
   </si>
   <si>
     <t xml:space="preserve">7.36178541183472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1408224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92350673675537</t>
+    <t xml:space="preserve">7.14082193374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14957427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92350625991821</t>
   </si>
   <si>
     <t xml:space="preserve">7.11165237426758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18895292282104</t>
+    <t xml:space="preserve">7.1889533996582</t>
   </si>
   <si>
     <t xml:space="preserve">7.20499658584595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14519786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09560775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86808252334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95559310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23416709899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3107385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28667306900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28813171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24146032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13207149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21082973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28375577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2961540222168</t>
+    <t xml:space="preserve">7.14519882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09560871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86808300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9555926322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23416614532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31073760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2866735458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28813123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13207197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21083068847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28375625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29615259170532</t>
   </si>
   <si>
     <t xml:space="preserve">7.19041204452515</t>
@@ -3662,28 +3662,28 @@
     <t xml:space="preserve">7.27354621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17728471755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1714506149292</t>
+    <t xml:space="preserve">7.17728567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17145156860352</t>
   </si>
   <si>
     <t xml:space="preserve">7.04601955413818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09852600097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13644742965698</t>
+    <t xml:space="preserve">7.09852647781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13644695281982</t>
   </si>
   <si>
     <t xml:space="preserve">7.25166845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27938079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456823348999</t>
+    <t xml:space="preserve">7.27938032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456966400146</t>
   </si>
   <si>
     <t xml:space="preserve">7.24875164031982</t>
@@ -3692,130 +3692,130 @@
     <t xml:space="preserve">7.36543226242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47846603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33626270294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53680562973022</t>
+    <t xml:space="preserve">7.47846651077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33626222610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53680515289307</t>
   </si>
   <si>
     <t xml:space="preserve">7.61337661743164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68630218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58785390853882</t>
+    <t xml:space="preserve">7.68630266189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58785247802734</t>
   </si>
   <si>
     <t xml:space="preserve">7.73734903335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50399017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294284820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21520614624023</t>
+    <t xml:space="preserve">7.50398969650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21520662307739</t>
   </si>
   <si>
     <t xml:space="preserve">7.38001728057861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41283226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43106508255005</t>
+    <t xml:space="preserve">7.41283273696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43106365203857</t>
   </si>
   <si>
     <t xml:space="preserve">7.53315925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5805606842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60608530044556</t>
+    <t xml:space="preserve">7.58056116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60608434677124</t>
   </si>
   <si>
     <t xml:space="preserve">7.55868291854858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52222013473511</t>
+    <t xml:space="preserve">7.52222061157227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64254713058472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67171716690063</t>
+    <t xml:space="preserve">7.67171669006348</t>
   </si>
   <si>
     <t xml:space="preserve">7.77016592025757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76651954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88684558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87590742111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81392097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81756830215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89778614044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507745742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955331802368</t>
+    <t xml:space="preserve">7.76652002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88684511184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87590646743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8139214515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81756782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955522537231</t>
   </si>
   <si>
     <t xml:space="preserve">7.79204320907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74828815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088768005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90313148498535</t>
+    <t xml:space="preserve">7.74828863143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90313196182251</t>
   </si>
   <si>
     <t xml:space="preserve">7.7226676940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72111225128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352506637573</t>
+    <t xml:space="preserve">7.72111034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45352554321289</t>
   </si>
   <si>
     <t xml:space="preserve">7.56398296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59976530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843395233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63865756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79034185409546</t>
+    <t xml:space="preserve">7.59976387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6386570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776851654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79034233093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.94591522216797</t>
@@ -3824,67 +3824,67 @@
     <t xml:space="preserve">7.86034917831421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82534694671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80978870391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71488857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311540603638</t>
+    <t xml:space="preserve">7.82534551620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80978918075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71488904953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311588287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.76155996322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84868192672729</t>
+    <t xml:space="preserve">7.84868144989014</t>
   </si>
   <si>
     <t xml:space="preserve">7.80589914321899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5219783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64954710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68999576568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81367683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86423921585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92646884918213</t>
+    <t xml:space="preserve">7.52197790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6495475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68999719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81367778778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86423778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92646741867065</t>
   </si>
   <si>
     <t xml:space="preserve">8.0859317779541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10149002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08204174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07815361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07037353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13260364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23761558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17538642883301</t>
+    <t xml:space="preserve">8.10148906707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07815456390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07037448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13260269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23761463165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17538547515869</t>
   </si>
   <si>
     <t xml:space="preserve">8.09759998321533</t>
@@ -3896,16 +3896,16 @@
     <t xml:space="preserve">8.05092811584473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02370071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61532258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6604380607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77867269515991</t>
+    <t xml:space="preserve">8.02370166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61532068252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66043710708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77867460250854</t>
   </si>
   <si>
     <t xml:space="preserve">8.02759170532227</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">8.10926723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79812145233154</t>
+    <t xml:space="preserve">7.79812049865723</t>
   </si>
   <si>
     <t xml:space="preserve">8.05870628356934</t>
@@ -3923,52 +3923,52 @@
     <t xml:space="preserve">8.22983741760254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20650100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14427280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90702104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88368606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9381365776062</t>
+    <t xml:space="preserve">8.20650196075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14427185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90702199935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07426357269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88368558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93813610076904</t>
   </si>
   <si>
     <t xml:space="preserve">7.77556276321411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67288446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67755031585693</t>
+    <t xml:space="preserve">7.67288494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67755079269409</t>
   </si>
   <si>
     <t xml:space="preserve">7.26994800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29172849655151</t>
+    <t xml:space="preserve">7.29172801971436</t>
   </si>
   <si>
     <t xml:space="preserve">7.25439119338989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68654775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73477554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68499231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12337255477905</t>
+    <t xml:space="preserve">6.68654823303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73477602005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68499279022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12337207794189</t>
   </si>
   <si>
     <t xml:space="preserve">5.95379686355591</t>
@@ -3983,61 +3983,61 @@
     <t xml:space="preserve">6.3193941116333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35050868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61187314987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66165637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06925964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2263879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06770372390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12993192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02103185653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05059003829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22949934005737</t>
+    <t xml:space="preserve">6.35050821304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61187267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66165590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06925821304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22638750076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06770324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12993240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02103137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0505895614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22949886322021</t>
   </si>
   <si>
     <t xml:space="preserve">7.10659599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17193794250488</t>
+    <t xml:space="preserve">7.17193698883057</t>
   </si>
   <si>
     <t xml:space="preserve">7.30417490005493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11904239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97902584075928</t>
+    <t xml:space="preserve">7.11904287338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97902631759644</t>
   </si>
   <si>
     <t xml:space="preserve">6.89190483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03503274917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02569723129272</t>
+    <t xml:space="preserve">7.03503322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02569818496704</t>
   </si>
   <si>
     <t xml:space="preserve">6.94946718215942</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">7.19527387619019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18438291549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37418270111084</t>
+    <t xml:space="preserve">7.18438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37418174743652</t>
   </si>
   <si>
     <t xml:space="preserve">7.44885778427124</t>
@@ -4061,46 +4061,46 @@
     <t xml:space="preserve">7.17971563339233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38196134567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38040542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686147689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74755954742432</t>
+    <t xml:space="preserve">7.38196182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38040637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74755859375</t>
   </si>
   <si>
     <t xml:space="preserve">7.50486421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48308324813843</t>
+    <t xml:space="preserve">7.4830846786499</t>
   </si>
   <si>
     <t xml:space="preserve">7.60598754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54842567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71955633163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71022033691406</t>
+    <t xml:space="preserve">7.54842615127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71955585479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71022176742554</t>
   </si>
   <si>
     <t xml:space="preserve">7.5235333442688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44574594497681</t>
+    <t xml:space="preserve">7.44574689865112</t>
   </si>
   <si>
     <t xml:space="preserve">7.38973999023438</t>
@@ -4109,49 +4109,49 @@
     <t xml:space="preserve">7.43485593795776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26217079162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34151124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752786636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41152000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46908235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43174409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32906579971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4208550453186</t>
+    <t xml:space="preserve">7.26217031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34151268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41152048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46908330917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4317455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32906627655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42085552215576</t>
   </si>
   <si>
     <t xml:space="preserve">7.53442287445068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49864149093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68532943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50797605514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01325178146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90435075759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96813678741455</t>
+    <t xml:space="preserve">7.49864196777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68532991409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50797653198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01325225830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90435123443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96813583374023</t>
   </si>
   <si>
     <t xml:space="preserve">6.9510235786438</t>
@@ -4160,22 +4160,22 @@
     <t xml:space="preserve">6.63054180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59631490707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68188142776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74411010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71921825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5683126449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71143960952759</t>
+    <t xml:space="preserve">6.59631443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68188047409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74410963058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7192177772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56831216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7114405632019</t>
   </si>
   <si>
     <t xml:space="preserve">6.56675672531128</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">6.60253810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42362880706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41896152496338</t>
+    <t xml:space="preserve">6.42362976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41896200180054</t>
   </si>
   <si>
     <t xml:space="preserve">6.38784694671631</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">6.32406187057495</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45785427093506</t>
+    <t xml:space="preserve">6.45785474777222</t>
   </si>
   <si>
     <t xml:space="preserve">6.55586671829224</t>
@@ -4217,73 +4217,73 @@
     <t xml:space="preserve">6.3582878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05958604812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05491971969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20115804672241</t>
+    <t xml:space="preserve">6.05958700180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0549201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20115900039673</t>
   </si>
   <si>
     <t xml:space="preserve">6.33339643478394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26027727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2213830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24783086776733</t>
+    <t xml:space="preserve">6.26027679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22138357162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24783039093018</t>
   </si>
   <si>
     <t xml:space="preserve">6.17937850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24005317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35673236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50297069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54653167724609</t>
+    <t xml:space="preserve">6.24005270004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35673189163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50297164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54653310775757</t>
   </si>
   <si>
     <t xml:space="preserve">6.55119895935059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59787130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64921045303345</t>
+    <t xml:space="preserve">6.59787082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64921092987061</t>
   </si>
   <si>
     <t xml:space="preserve">6.7021050453186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65232181549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64298725128174</t>
+    <t xml:space="preserve">6.65232229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6429877281189</t>
   </si>
   <si>
     <t xml:space="preserve">6.66010046005249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72544193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77055883407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77833652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72233057022095</t>
+    <t xml:space="preserve">6.72544145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77833604812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72232961654663</t>
   </si>
   <si>
     <t xml:space="preserve">6.69588232040405</t>
@@ -4292,19 +4292,19 @@
     <t xml:space="preserve">6.44696474075317</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27427864074707</t>
+    <t xml:space="preserve">6.27427816390991</t>
   </si>
   <si>
     <t xml:space="preserve">6.32250642776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2945032119751</t>
+    <t xml:space="preserve">6.29450273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.25872039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17004442214966</t>
+    <t xml:space="preserve">6.1700439453125</t>
   </si>
   <si>
     <t xml:space="preserve">6.15448665618896</t>
@@ -4331,16 +4331,16 @@
     <t xml:space="preserve">6.22916221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28672456741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44229745864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5807580947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58698081970215</t>
+    <t xml:space="preserve">6.28672361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44229793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58075761795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58698177337646</t>
   </si>
   <si>
     <t xml:space="preserve">6.65387725830078</t>
@@ -4349,43 +4349,43 @@
     <t xml:space="preserve">6.63365268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57764768600464</t>
+    <t xml:space="preserve">6.57764673233032</t>
   </si>
   <si>
     <t xml:space="preserve">6.61031723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37540149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48274660110474</t>
+    <t xml:space="preserve">6.37540102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48274707794189</t>
   </si>
   <si>
     <t xml:space="preserve">6.44074201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20893716812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09381341934204</t>
+    <t xml:space="preserve">6.2089376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09381294250488</t>
   </si>
   <si>
     <t xml:space="preserve">6.0331392288208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92112636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59009313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48119115829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23382949829102</t>
+    <t xml:space="preserve">5.92112684249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26961183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59009265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48119163513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23382902145386</t>
   </si>
   <si>
     <t xml:space="preserve">6.19649171829224</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">6.18248987197876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10003566741943</t>
+    <t xml:space="preserve">6.10003614425659</t>
   </si>
   <si>
     <t xml:space="preserve">6.2836127281189</t>
@@ -4406,16 +4406,16 @@
     <t xml:space="preserve">6.52164030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67877006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85612297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84989976882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85767936706543</t>
+    <t xml:space="preserve">6.67876958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85612344741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8499002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85767889022827</t>
   </si>
   <si>
     <t xml:space="preserve">7.07081460952759</t>
@@ -4424,31 +4424,31 @@
     <t xml:space="preserve">7.10348510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13459920883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09726142883301</t>
+    <t xml:space="preserve">7.1346001625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09726238250732</t>
   </si>
   <si>
     <t xml:space="preserve">7.19060611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15326881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31039810180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49241781234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52820014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57954025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6339898109436</t>
+    <t xml:space="preserve">7.15326833724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31039762496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49241876602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52820110321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57953929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63399076461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.74289131164551</t>
@@ -4457,106 +4457,106 @@
     <t xml:space="preserve">7.9148006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90892219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91228055953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93243551254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87029218673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83502292633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77287912368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73760938644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6956205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71409559249878</t>
+    <t xml:space="preserve">7.90892267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91228151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93243598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87029314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83502340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7728796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73760986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69562101364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7140965461731</t>
   </si>
   <si>
     <t xml:space="preserve">7.73928928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68554449081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63515901565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6586709022522</t>
+    <t xml:space="preserve">7.68554496765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63515758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65867233276367</t>
   </si>
   <si>
     <t xml:space="preserve">7.71073770523071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69394302368164</t>
+    <t xml:space="preserve">7.69394159317017</t>
   </si>
   <si>
     <t xml:space="preserve">7.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79471397399902</t>
+    <t xml:space="preserve">7.79471349716187</t>
   </si>
   <si>
     <t xml:space="preserve">7.51087331771851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48064136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50415515899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52934741973877</t>
+    <t xml:space="preserve">7.48064184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50415468215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52934789657593</t>
   </si>
   <si>
     <t xml:space="preserve">7.6637110710144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56965684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58477163314819</t>
+    <t xml:space="preserve">7.56965732574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58477258682251</t>
   </si>
   <si>
     <t xml:space="preserve">7.5864520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53774499893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64691543579102</t>
+    <t xml:space="preserve">7.53774547576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64691495895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.54446315765381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59484958648682</t>
+    <t xml:space="preserve">7.59485006332397</t>
   </si>
   <si>
     <t xml:space="preserve">7.6721076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79807424545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78463792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77959775924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85685586929321</t>
+    <t xml:space="preserve">7.79807329177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78463649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77959823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85685634613037</t>
   </si>
   <si>
     <t xml:space="preserve">7.90052509307861</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">8.01977062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92403745651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04496479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08191299438477</t>
+    <t xml:space="preserve">7.92403888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04496383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08191394805908</t>
   </si>
   <si>
     <t xml:space="preserve">8.13230037689209</t>
@@ -4601,16 +4601,16 @@
     <t xml:space="preserve">8.31536960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34560108184814</t>
+    <t xml:space="preserve">8.34560012817383</t>
   </si>
   <si>
     <t xml:space="preserve">8.27674007415771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37247371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39430904388428</t>
+    <t xml:space="preserve">8.37247467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39430809020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.4312572479248</t>
@@ -4619,10 +4619,10 @@
     <t xml:space="preserve">8.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54042720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56981945037842</t>
+    <t xml:space="preserve">8.54042625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5698184967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.69998264312744</t>
@@ -4631,7 +4631,7 @@
     <t xml:space="preserve">8.56561946868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7083797454834</t>
+    <t xml:space="preserve">8.70838069915771</t>
   </si>
   <si>
     <t xml:space="preserve">8.74197101593018</t>
@@ -4640,79 +4640,79 @@
     <t xml:space="preserve">8.60340976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63280010223389</t>
+    <t xml:space="preserve">8.6328010559082</t>
   </si>
   <si>
     <t xml:space="preserve">8.61180686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50263786315918</t>
+    <t xml:space="preserve">8.50263690948486</t>
   </si>
   <si>
     <t xml:space="preserve">8.49423980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39094829559326</t>
+    <t xml:space="preserve">8.39094734191895</t>
   </si>
   <si>
     <t xml:space="preserve">8.41026306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25490570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42285919189453</t>
+    <t xml:space="preserve">8.25490665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42285823822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37415409088135</t>
+    <t xml:space="preserve">8.37415313720703</t>
   </si>
   <si>
     <t xml:space="preserve">8.36407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45644855499268</t>
+    <t xml:space="preserve">8.45645046234131</t>
   </si>
   <si>
     <t xml:space="preserve">8.51103496551514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46064949035645</t>
+    <t xml:space="preserve">8.46064853668213</t>
   </si>
   <si>
     <t xml:space="preserve">8.51523399353027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40186595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16757011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80143260955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99793672561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5495023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52095127105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43193578720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73425054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63180017471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5528621673584</t>
+    <t xml:space="preserve">8.40186500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16757106781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80143213272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99793815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54950189590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52095031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43193435668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73425102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63179922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55286169052124</t>
   </si>
   <si>
     <t xml:space="preserve">7.51591157913208</t>
@@ -4721,94 +4721,94 @@
     <t xml:space="preserve">7.60660552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7241735458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78295707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8115086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8098292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74096965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075609207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92739677429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93915510177612</t>
+    <t xml:space="preserve">7.72417402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78295612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81150913238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80982971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74096870422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075656890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92739772796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93915414810181</t>
   </si>
   <si>
     <t xml:space="preserve">8.09366989135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02648830413818</t>
+    <t xml:space="preserve">8.02649021148682</t>
   </si>
   <si>
     <t xml:space="preserve">8.18772411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21795749664307</t>
+    <t xml:space="preserve">8.21795654296875</t>
   </si>
   <si>
     <t xml:space="preserve">8.14909648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21291732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17261028289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19780254364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26834106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17092895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8921275138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19444274902344</t>
+    <t xml:space="preserve">8.21291828155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17260932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19780158996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26834201812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89212703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19444370269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.09703063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3808708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766597747803</t>
+    <t xml:space="preserve">8.38086986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766693115234</t>
   </si>
   <si>
     <t xml:space="preserve">8.34056282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36575508117676</t>
+    <t xml:space="preserve">8.36575603485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.13565921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14741516113281</t>
+    <t xml:space="preserve">8.14741611480713</t>
   </si>
   <si>
     <t xml:space="preserve">8.18436622619629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25322723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27338218688965</t>
+    <t xml:space="preserve">8.2532262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27338123321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895992279053</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">8.67478942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6453971862793</t>
+    <t xml:space="preserve">8.64539813995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.92252063751221</t>
@@ -4841,10 +4841,10 @@
     <t xml:space="preserve">8.98970222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98130321502686</t>
+    <t xml:space="preserve">8.90572452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98130416870117</t>
   </si>
   <si>
     <t xml:space="preserve">8.96450901031494</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">9.17025184631348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19124507904053</t>
+    <t xml:space="preserve">9.19124603271484</t>
   </si>
   <si>
     <t xml:space="preserve">9.28781986236572</t>
@@ -4862,37 +4862,37 @@
     <t xml:space="preserve">9.38859081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49776172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39698886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42638111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40538597106934</t>
+    <t xml:space="preserve">9.49776077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39698791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42638206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40538692474365</t>
   </si>
   <si>
     <t xml:space="preserve">9.30461406707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33400726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14925670623779</t>
+    <t xml:space="preserve">9.33400535583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14925765991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.03588962554932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01909446716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04848480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06947994232178</t>
+    <t xml:space="preserve">9.01909351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04848575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06948089599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.20384216308594</t>
@@ -4901,34 +4901,34 @@
     <t xml:space="preserve">9.34660243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35500144958496</t>
+    <t xml:space="preserve">9.35500049591064</t>
   </si>
   <si>
     <t xml:space="preserve">9.27942180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24583148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25002956390381</t>
+    <t xml:space="preserve">9.24583053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25003051757812</t>
   </si>
   <si>
     <t xml:space="preserve">9.25842761993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43058013916016</t>
+    <t xml:space="preserve">9.43057823181152</t>
   </si>
   <si>
     <t xml:space="preserve">9.48936367034912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48096466064453</t>
+    <t xml:space="preserve">9.48096561431885</t>
   </si>
   <si>
     <t xml:space="preserve">9.52295398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64891815185547</t>
+    <t xml:space="preserve">9.64891910552979</t>
   </si>
   <si>
     <t xml:space="preserve">9.60692977905273</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">9.69930553436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70770168304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68250942230225</t>
+    <t xml:space="preserve">9.70770263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68250846862793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0394096374512</t>
@@ -4955,13 +4955,13 @@
     <t xml:space="preserve">10.1779718399048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0520067214966</t>
+    <t xml:space="preserve">10.0520076751709</t>
   </si>
   <si>
     <t xml:space="preserve">9.9554328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94703578948975</t>
+    <t xml:space="preserve">9.94703674316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.93863868713379</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">9.98062705993652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73289585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83366870880127</t>
+    <t xml:space="preserve">9.73289489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83366680145264</t>
   </si>
   <si>
     <t xml:space="preserve">9.85886001586914</t>
@@ -4985,16 +4985,16 @@
     <t xml:space="preserve">9.93024063110352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87565612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79167938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82526969909668</t>
+    <t xml:space="preserve">9.87565517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7916784286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7664852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.825270652771</t>
   </si>
   <si>
     <t xml:space="preserve">9.97222900390625</t>
@@ -5003,31 +5003,31 @@
     <t xml:space="preserve">9.92604160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9134464263916</t>
+    <t xml:space="preserve">9.91344547271729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1653747558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1947679519653</t>
+    <t xml:space="preserve">10.1653757095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.194766998291</t>
   </si>
   <si>
     <t xml:space="preserve">10.1359834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1401815414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1443796157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2199592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0981931686401</t>
+    <t xml:space="preserve">10.1401824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1443815231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2199602127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0981941223145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1989660263062</t>
@@ -5042,28 +5042,28 @@
     <t xml:space="preserve">10.2241592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2115621566772</t>
+    <t xml:space="preserve">10.2115612030029</t>
   </si>
   <si>
     <t xml:space="preserve">10.303936958313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2535514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1905689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3291311264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173059463501</t>
+    <t xml:space="preserve">10.25355052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1905679702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3291301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173049926758</t>
   </si>
   <si>
     <t xml:space="preserve">10.3333292007446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2451524734497</t>
+    <t xml:space="preserve">10.245153427124</t>
   </si>
   <si>
     <t xml:space="preserve">10.2913408279419</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">10.4676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5222749710083</t>
+    <t xml:space="preserve">10.5222768783569</t>
   </si>
   <si>
     <t xml:space="preserve">10.3921127319336</t>
@@ -5090,22 +5090,22 @@
     <t xml:space="preserve">10.2745447158813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.203164100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1275863647461</t>
+    <t xml:space="preserve">10.2031650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1275854110718</t>
   </si>
   <si>
     <t xml:space="preserve">10.2283582687378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2367553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2955389022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695747375488</t>
+    <t xml:space="preserve">10.2367544174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.295539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695728302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.1527786254883</t>
@@ -5117,31 +5117,31 @@
     <t xml:space="preserve">9.55654430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682472229004</t>
+    <t xml:space="preserve">9.26682376861572</t>
   </si>
   <si>
     <t xml:space="preserve">9.37179565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24163246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96870708465576</t>
+    <t xml:space="preserve">9.24163150787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96870803833008</t>
   </si>
   <si>
     <t xml:space="preserve">9.46417045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53135299682617</t>
+    <t xml:space="preserve">9.53135204315186</t>
   </si>
   <si>
     <t xml:space="preserve">9.58173751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65311717987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731716156006</t>
+    <t xml:space="preserve">9.65311813354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731620788574</t>
   </si>
   <si>
     <t xml:space="preserve">9.66991329193115</t>
@@ -5150,28 +5150,28 @@
     <t xml:space="preserve">9.63212394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67831039428711</t>
+    <t xml:space="preserve">9.67831134796143</t>
   </si>
   <si>
     <t xml:space="preserve">9.69090747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98902416229248</t>
+    <t xml:space="preserve">9.9890251159668</t>
   </si>
   <si>
     <t xml:space="preserve">9.87985515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84817504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73050308227539</t>
+    <t xml:space="preserve">9.84817409515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73050212860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.82554531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81649398803711</t>
+    <t xml:space="preserve">9.81649303436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.81196784973145</t>
@@ -5180,28 +5180,28 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71239852905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78028678894043</t>
+    <t xml:space="preserve">9.73955535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71239948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75313091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78028774261475</t>
   </si>
   <si>
     <t xml:space="preserve">9.72597694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65809059143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92511367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0020513534546</t>
+    <t xml:space="preserve">9.65808963775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9251127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0020523071289</t>
   </si>
   <si>
     <t xml:space="preserve">10.0744647979736</t>
@@ -5210,13 +5210,13 @@
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0925674438477</t>
+    <t xml:space="preserve">10.092568397522</t>
   </si>
   <si>
     <t xml:space="preserve">10.0337324142456</t>
   </si>
   <si>
-    <t xml:space="preserve">10.069938659668</t>
+    <t xml:space="preserve">10.0699396133423</t>
   </si>
   <si>
     <t xml:space="preserve">10.0654134750366</t>
@@ -5225,16 +5225,16 @@
     <t xml:space="preserve">10.1378259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0789918899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1785593032837</t>
+    <t xml:space="preserve">10.0789909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1785583496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1514043807983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1151971817017</t>
+    <t xml:space="preserve">10.115198135376</t>
   </si>
   <si>
     <t xml:space="preserve">10.142352104187</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">10.060887336731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695079803467</t>
+    <t xml:space="preserve">10.1695070266724</t>
   </si>
   <si>
     <t xml:space="preserve">10.2464456558228</t>
@@ -5252,19 +5252,19 @@
     <t xml:space="preserve">10.2736015319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2147645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102384567261</t>
+    <t xml:space="preserve">10.2147655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102394104004</t>
   </si>
   <si>
     <t xml:space="preserve">10.2011880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4455814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7126045227051</t>
+    <t xml:space="preserve">10.4455823898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7126054763794</t>
   </si>
   <si>
     <t xml:space="preserve">10.7895441055298</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">10.9434213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9253187179565</t>
+    <t xml:space="preserve">10.9253177642822</t>
   </si>
   <si>
     <t xml:space="preserve">10.9615240097046</t>
@@ -5294,13 +5294,13 @@
     <t xml:space="preserve">11.1063508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1335067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9388961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0022563934326</t>
+    <t xml:space="preserve">11.133505821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9388952255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0022573471069</t>
   </si>
   <si>
     <t xml:space="preserve">10.8393278121948</t>
@@ -5321,7 +5321,7 @@
     <t xml:space="preserve">10.4184274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3957977294922</t>
+    <t xml:space="preserve">10.3957967758179</t>
   </si>
   <si>
     <t xml:space="preserve">10.5587272644043</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">10.5858812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628217697144</t>
+    <t xml:space="preserve">10.66282081604</t>
   </si>
   <si>
     <t xml:space="preserve">10.7261819839478</t>
@@ -5339,19 +5339,19 @@
     <t xml:space="preserve">11.1787643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7173347473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5906133651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4955701828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4231586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4005298614502</t>
+    <t xml:space="preserve">11.7173357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5906143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4955711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4231576919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4005289077759</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141063690186</t>
@@ -5363,28 +5363,28 @@
     <t xml:space="preserve">11.4865188598633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6313467025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5815620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.595139503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625932693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6901817321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8576364517212</t>
+    <t xml:space="preserve">11.6313457489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.581561088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5951404571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6901807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8576374053955</t>
   </si>
   <si>
     <t xml:space="preserve">12.0160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9979362487793</t>
+    <t xml:space="preserve">11.9979372024536</t>
   </si>
   <si>
     <t xml:space="preserve">12.0567722320557</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">12.2785358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3328475952148</t>
+    <t xml:space="preserve">12.3328466415405</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003023147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3781051635742</t>
+    <t xml:space="preserve">12.5003032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3781061172485</t>
   </si>
   <si>
     <t xml:space="preserve">12.509352684021</t>
@@ -5417,19 +5417,19 @@
     <t xml:space="preserve">12.4052600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3102188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554754257202</t>
+    <t xml:space="preserve">12.3102178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554763793945</t>
   </si>
   <si>
     <t xml:space="preserve">12.2875890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1246604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1699180603027</t>
+    <t xml:space="preserve">12.124659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1699171066284</t>
   </si>
   <si>
     <t xml:space="preserve">12.2921142578125</t>
@@ -5444,10 +5444,10 @@
     <t xml:space="preserve">12.3509502410889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1337108612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744441986084</t>
+    <t xml:space="preserve">12.1337099075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.083927154541</t>
@@ -5465,13 +5465,13 @@
     <t xml:space="preserve">12.6722831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7718505859375</t>
+    <t xml:space="preserve">12.7718496322632</t>
   </si>
   <si>
     <t xml:space="preserve">13.0796060562134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2244310379028</t>
+    <t xml:space="preserve">13.2244319915771</t>
   </si>
   <si>
     <t xml:space="preserve">13.514084815979</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">13.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7403745651245</t>
+    <t xml:space="preserve">13.7403755187988</t>
   </si>
   <si>
     <t xml:space="preserve">13.7992105484009</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">13.7336559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6259593963623</t>
+    <t xml:space="preserve">13.6259603500366</t>
   </si>
   <si>
     <t xml:space="preserve">13.5369930267334</t>
@@ -5513,19 +5513,19 @@
     <t xml:space="preserve">13.5791349411011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5978651046753</t>
+    <t xml:space="preserve">13.5978660583496</t>
   </si>
   <si>
     <t xml:space="preserve">13.5042161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4199314117432</t>
+    <t xml:space="preserve">13.4199323654175</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620733261108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4339799880981</t>
+    <t xml:space="preserve">13.4339790344238</t>
   </si>
   <si>
     <t xml:space="preserve">13.2794580459595</t>
@@ -5534,16 +5534,16 @@
     <t xml:space="preserve">13.1343011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.424614906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9563674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6660556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7550220489502</t>
+    <t xml:space="preserve">13.4246139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9563684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.666054725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7550230026245</t>
   </si>
   <si>
     <t xml:space="preserve">12.8205757141113</t>
@@ -5552,16 +5552,16 @@
     <t xml:space="preserve">12.7222452163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9329557418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0500173568726</t>
+    <t xml:space="preserve">12.9329566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0500183105469</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001789093018</t>
+    <t xml:space="preserve">12.9001779556274</t>
   </si>
   <si>
     <t xml:space="preserve">12.7831172943115</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">13.1951732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0359706878662</t>
+    <t xml:space="preserve">13.0359697341919</t>
   </si>
   <si>
     <t xml:space="preserve">13.1670789718628</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">13.2045392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2888231277466</t>
+    <t xml:space="preserve">13.2888221740723</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654104232788</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">13.4386615753174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4714384078979</t>
+    <t xml:space="preserve">13.4714393615723</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777894973755</t>
@@ -5600,10 +5600,10 @@
     <t xml:space="preserve">13.382472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.499532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4808034896851</t>
+    <t xml:space="preserve">13.4995336532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4808044433594</t>
   </si>
   <si>
     <t xml:space="preserve">13.5182638168335</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">13.8038930892944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8413524627686</t>
+    <t xml:space="preserve">13.8413534164429</t>
   </si>
   <si>
     <t xml:space="preserve">13.808575630188</t>
@@ -5630,13 +5630,13 @@
     <t xml:space="preserve">13.4573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1623973846436</t>
+    <t xml:space="preserve">13.1623964309692</t>
   </si>
   <si>
     <t xml:space="preserve">12.8486709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1483488082886</t>
+    <t xml:space="preserve">13.1483497619629</t>
   </si>
   <si>
     <t xml:space="preserve">13.0172395706177</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">13.1389837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.101523399353</t>
+    <t xml:space="preserve">13.1015243530273</t>
   </si>
   <si>
     <t xml:space="preserve">13.1904907226562</t>
@@ -5663,13 +5663,13 @@
     <t xml:space="preserve">13.9350023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9490509033203</t>
+    <t xml:space="preserve">13.949049949646</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0146036148071</t>
+    <t xml:space="preserve">14.0146045684814</t>
   </si>
   <si>
     <t xml:space="preserve">14.047381401062</t>
@@ -5684,10 +5684,10 @@
     <t xml:space="preserve">14.314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3611059188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1410303115845</t>
+    <t xml:space="preserve">14.3611068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1410312652588</t>
   </si>
   <si>
     <t xml:space="preserve">13.9911918640137</t>
@@ -5696,25 +5696,25 @@
     <t xml:space="preserve">14.1223001480103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9865093231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019033432007</t>
+    <t xml:space="preserve">13.9865102767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019023895264</t>
   </si>
   <si>
     <t xml:space="preserve">13.9818267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7523860931396</t>
+    <t xml:space="preserve">13.752387046814</t>
   </si>
   <si>
     <t xml:space="preserve">13.836669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8881769180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0005569458008</t>
+    <t xml:space="preserve">13.8881778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0005559921265</t>
   </si>
   <si>
     <t xml:space="preserve">14.3657884597778</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">14.403247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2861862182617</t>
+    <t xml:space="preserve">14.286187171936</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815046310425</t>
@@ -5735,19 +5735,19 @@
     <t xml:space="preserve">14.4453907012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4641208648682</t>
+    <t xml:space="preserve">14.4641199111938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3517408370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1129350662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0333337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460350036621</t>
+    <t xml:space="preserve">14.1129360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.033332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460359573364</t>
   </si>
   <si>
     <t xml:space="preserve">14.0567464828491</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">14.5624523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6561002731323</t>
+    <t xml:space="preserve">14.6561012268066</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982431411743</t>
@@ -5783,13 +5783,13 @@
     <t xml:space="preserve">15.1009349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9136371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7684812545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5999126434326</t>
+    <t xml:space="preserve">14.9136362075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7684803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5999116897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.4500732421875</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">14.4219779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3376951217651</t>
+    <t xml:space="preserve">14.3376941680908</t>
   </si>
   <si>
     <t xml:space="preserve">14.3002347946167</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">13.5229454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8554010391235</t>
+    <t xml:space="preserve">13.8554000854492</t>
   </si>
   <si>
     <t xml:space="preserve">13.9089336395264</t>
@@ -6468,6 +6468,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.3899993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499998092651</t>
   </si>
 </sst>
 </file>
@@ -71494,7 +71497,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6518171296</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1853609</v>
@@ -71515,6 +71518,32 @@
         <v>2151</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6518981481</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>1925468</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>16.4699993133545</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>15.9499998092651</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>15.9499998092651</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>2152</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="2158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="2159">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18521499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0552830696106</t>
+    <t xml:space="preserve">5.18521547317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05528259277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.95858860015869</t>
@@ -59,43 +59,43 @@
     <t xml:space="preserve">4.8105263710022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92535066604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97974109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91930675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73196220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50533580780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59900808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41468477249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65944194793701</t>
+    <t xml:space="preserve">4.92535018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97974061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91930723190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73196268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50533533096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59900856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41468524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65944242477417</t>
   </si>
   <si>
     <t xml:space="preserve">4.67455005645752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52346611022949</t>
+    <t xml:space="preserve">4.52346658706665</t>
   </si>
   <si>
     <t xml:space="preserve">4.59598636627197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52648782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27870893478394</t>
+    <t xml:space="preserve">4.52648687362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27870988845825</t>
   </si>
   <si>
     <t xml:space="preserve">4.45094537734985</t>
@@ -104,25 +104,25 @@
     <t xml:space="preserve">4.3119478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19410133361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00373554229736</t>
+    <t xml:space="preserve">4.19410181045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00373601913452</t>
   </si>
   <si>
     <t xml:space="preserve">4.09136486053467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98862791061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61695981025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41450715065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6713502407074</t>
+    <t xml:space="preserve">3.98862767219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61696004867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41450619697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67134952545166</t>
   </si>
   <si>
     <t xml:space="preserve">3.47796201705933</t>
@@ -131,40 +131,40 @@
     <t xml:space="preserve">3.54443860054016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64717602729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68041563034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7499144077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64113306999207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091637611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75595784187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66228485107422</t>
+    <t xml:space="preserve">3.64717674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.680415391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113283157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091661453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75595808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66228580474854</t>
   </si>
   <si>
     <t xml:space="preserve">3.62300276756287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67437195777893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76804399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78315234184265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93725872039795</t>
+    <t xml:space="preserve">3.67437148094177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76804375648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78315258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93725800514221</t>
   </si>
   <si>
     <t xml:space="preserve">4.08834266662598</t>
@@ -179,64 +179,64 @@
     <t xml:space="preserve">3.91006302833557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96143221855164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97351908683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38446807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42979288101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28173065185547</t>
+    <t xml:space="preserve">3.96143174171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97351884841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03395223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38446855545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42979335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28173112869263</t>
   </si>
   <si>
     <t xml:space="preserve">4.29986047744751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03697395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07323503494263</t>
+    <t xml:space="preserve">4.03697443008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07323408126831</t>
   </si>
   <si>
     <t xml:space="preserve">4.0943865776062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01884508132935</t>
+    <t xml:space="preserve">4.01884460449219</t>
   </si>
   <si>
     <t xml:space="preserve">3.99164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87984681129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90402030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82545638084412</t>
+    <t xml:space="preserve">3.87984561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90402007102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82545685768127</t>
   </si>
   <si>
     <t xml:space="preserve">3.79221796989441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83150005340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75897908210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79523968696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6048731803894</t>
+    <t xml:space="preserve">3.83149933815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7589795589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79523944854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60487270355225</t>
   </si>
   <si>
     <t xml:space="preserve">3.81336903572083</t>
@@ -245,82 +245,82 @@
     <t xml:space="preserve">3.85567378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77408790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9704966545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04301786422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97654008865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23036241531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338460922241</t>
+    <t xml:space="preserve">3.77408719062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97049689292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04301691055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97653985023499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23036193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338413238525</t>
   </si>
   <si>
     <t xml:space="preserve">4.36935997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38749074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39655590057373</t>
+    <t xml:space="preserve">4.38748979568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39655447006226</t>
   </si>
   <si>
     <t xml:space="preserve">4.33612108230591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21223163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05208206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88589000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85265111923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80430459976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078142166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8979766368866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93423771858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9221498966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90704202651978</t>
+    <t xml:space="preserve">4.21223258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05208301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88588953018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85265159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8043041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87078166007996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89797616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93423700332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92215085029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90704250335693</t>
   </si>
   <si>
     <t xml:space="preserve">3.97956228256226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0158224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2182765007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31497001647949</t>
+    <t xml:space="preserve">4.01582193374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21827554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31496953964233</t>
   </si>
   <si>
     <t xml:space="preserve">4.30590391159058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3572735786438</t>
+    <t xml:space="preserve">4.35727262496948</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518671035767</t>
@@ -329,112 +329,112 @@
     <t xml:space="preserve">4.13366794586182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10647344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00071430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98560500144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610670089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52026581764221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38731122016907</t>
+    <t xml:space="preserve">4.10647296905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00071382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98560523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91610646247864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70156693458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52026557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38731098175049</t>
   </si>
   <si>
     <t xml:space="preserve">3.48098421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46889662742615</t>
+    <t xml:space="preserve">3.46889686584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.60789442062378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80732607841492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85869479179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8345205783844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20903158187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79929137229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96125340461731</t>
+    <t xml:space="preserve">3.80732583999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85869526863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83452033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20903205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79929113388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96125364303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.0639910697937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11536002159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14557600021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01322627067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91653275489807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84763813018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94554042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19694566726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47191905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57767820358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52630949020386</t>
+    <t xml:space="preserve">3.11535978317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14557671546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01322650909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91653251647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84763789176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9455406665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19694495201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472336769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47191834449768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57767748832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5263090133667</t>
   </si>
   <si>
     <t xml:space="preserve">3.58674263954163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55350422859192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59580779075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58976483345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61998081207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53537464141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65926313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.613938331604</t>
+    <t xml:space="preserve">3.55350470542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5958080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58976435661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61998128890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5353741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65926289558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61393809318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.78617405891418</t>
@@ -443,61 +443,61 @@
     <t xml:space="preserve">3.71365356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4084632396698</t>
+    <t xml:space="preserve">3.40846347808838</t>
   </si>
   <si>
     <t xml:space="preserve">3.42055010795593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71969723701477</t>
+    <t xml:space="preserve">3.71969676017761</t>
   </si>
   <si>
     <t xml:space="preserve">3.96747541427612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9402801990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099835395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84962964057922</t>
+    <t xml:space="preserve">3.94027996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84962940216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.81639099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80128264427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6955235004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72876214981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92517137527466</t>
+    <t xml:space="preserve">3.80128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69552397727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72876262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92517185211182</t>
   </si>
   <si>
     <t xml:space="preserve">3.89495468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95236706733704</t>
+    <t xml:space="preserve">3.95236730575562</t>
   </si>
   <si>
     <t xml:space="preserve">4.0490608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14273357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19107961654663</t>
+    <t xml:space="preserve">4.14273309707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07927894592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19108009338379</t>
   </si>
   <si>
     <t xml:space="preserve">4.15481996536255</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73178315162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78919625282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68645882606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77106618881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77710962295532</t>
+    <t xml:space="preserve">3.7317841053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78919553756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68645834922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7710657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77710914611816</t>
   </si>
   <si>
     <t xml:space="preserve">3.49609208106995</t>
@@ -527,67 +527,67 @@
     <t xml:space="preserve">3.54141783714294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47494029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4991135597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49004888534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49307036399841</t>
+    <t xml:space="preserve">3.47494077682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49911403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49004912376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49307060241699</t>
   </si>
   <si>
     <t xml:space="preserve">3.68343639373779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78013038635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65321946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74387049674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87380313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9946711063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10949468612671</t>
+    <t xml:space="preserve">3.78013062477112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65322017669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74387073516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87380266189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99467015266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10949420928955</t>
   </si>
   <si>
     <t xml:space="preserve">4.15784168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23640537261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84358596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00977945327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14575576782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13971185684204</t>
+    <t xml:space="preserve">4.23640489578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84358620643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00977849960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14575529098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13971042633057</t>
   </si>
   <si>
     <t xml:space="preserve">4.25453615188599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26964473724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20618915557861</t>
+    <t xml:space="preserve">4.26964378356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2061882019043</t>
   </si>
   <si>
     <t xml:space="preserve">4.11251640319824</t>
@@ -596,28 +596,28 @@
     <t xml:space="preserve">3.94632387161255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99360370635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06294822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00306034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96208310127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90849876403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79502701759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95578002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1039252281189</t>
+    <t xml:space="preserve">3.99360394477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06294870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00305986404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96208357810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90849924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79502725601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95578050613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10392427444458</t>
   </si>
   <si>
     <t xml:space="preserve">4.23315715789795</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">4.23946094512939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05979633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46325349807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67759084701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80682325363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67128705978394</t>
+    <t xml:space="preserve">4.05979681015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46325445175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67759132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80682373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67128753662109</t>
   </si>
   <si>
     <t xml:space="preserve">4.69650316238403</t>
@@ -647,34 +647,34 @@
     <t xml:space="preserve">4.74693536758423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79106378555298</t>
+    <t xml:space="preserve">4.79106426239014</t>
   </si>
   <si>
     <t xml:space="preserve">4.95181655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89508008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91714477539062</t>
+    <t xml:space="preserve">4.89507961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91714429855347</t>
   </si>
   <si>
     <t xml:space="preserve">4.98964071273804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95496892929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93920803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00224876403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99909687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93605709075928</t>
+    <t xml:space="preserve">4.95496845245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.939208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00224828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99909734725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93605661392212</t>
   </si>
   <si>
     <t xml:space="preserve">4.89823246002197</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">4.88877630233765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99279308319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1377854347229</t>
+    <t xml:space="preserve">4.99279260635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13778591156006</t>
   </si>
   <si>
     <t xml:space="preserve">5.1693058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1440896987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.163001537323</t>
+    <t xml:space="preserve">5.14408922195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16300106048584</t>
   </si>
   <si>
     <t xml:space="preserve">4.92975282669067</t>
@@ -704,40 +704,40 @@
     <t xml:space="preserve">4.98333740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98018503189087</t>
+    <t xml:space="preserve">4.98018455505371</t>
   </si>
   <si>
     <t xml:space="preserve">4.86356019973755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05898475646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04007291793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00540018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08420133590698</t>
+    <t xml:space="preserve">5.05898523330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04007339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00540113449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08420085906982</t>
   </si>
   <si>
     <t xml:space="preserve">5.01170444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08735322952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103509902954</t>
+    <t xml:space="preserve">5.08735275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37103462219238</t>
   </si>
   <si>
     <t xml:space="preserve">5.5380916595459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36157894134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29538583755493</t>
+    <t xml:space="preserve">5.36157846450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29538631439209</t>
   </si>
   <si>
     <t xml:space="preserve">5.15354585647583</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">5.01485681533813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13463354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92344856262207</t>
+    <t xml:space="preserve">5.13463306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92344808578491</t>
   </si>
   <si>
     <t xml:space="preserve">4.8194317817688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96757698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91084003448486</t>
+    <t xml:space="preserve">4.96757650375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91084051132202</t>
   </si>
   <si>
     <t xml:space="preserve">5.05583333969116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17560958862305</t>
+    <t xml:space="preserve">5.17560911178589</t>
   </si>
   <si>
     <t xml:space="preserve">5.14724159240723</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">5.02431297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97388076782227</t>
+    <t xml:space="preserve">4.97388029098511</t>
   </si>
   <si>
     <t xml:space="preserve">4.82888793945312</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">4.69335126876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72802400588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76900005340576</t>
+    <t xml:space="preserve">4.72802305221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7689995765686</t>
   </si>
   <si>
     <t xml:space="preserve">4.94866418838501</t>
@@ -800,49 +800,49 @@
     <t xml:space="preserve">4.99594497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17245674133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21658611297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22604179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30169010162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24810552597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23549747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2512583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26071405410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32375431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33636283874512</t>
+    <t xml:space="preserve">5.17245769500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21658515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2260422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30168962478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24810600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23549795150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25125789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26071453094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32375383377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3363618850708</t>
   </si>
   <si>
     <t xml:space="preserve">5.27962684631348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33951377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31745100021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35212230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32690668106079</t>
+    <t xml:space="preserve">5.33951473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31745052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35212182998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32690620422363</t>
   </si>
   <si>
     <t xml:space="preserve">5.19767332077026</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">5.20712995529175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20397853851318</t>
+    <t xml:space="preserve">5.20397758483887</t>
   </si>
   <si>
     <t xml:space="preserve">5.23865032196045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13148212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104944229126</t>
+    <t xml:space="preserve">5.13148164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104991912842</t>
   </si>
   <si>
     <t xml:space="preserve">4.85095262527466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38364267349243</t>
+    <t xml:space="preserve">5.38364219665527</t>
   </si>
   <si>
     <t xml:space="preserve">5.46559524536133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38994693756104</t>
+    <t xml:space="preserve">5.38994741439819</t>
   </si>
   <si>
     <t xml:space="preserve">5.35527420043945</t>
@@ -884,82 +884,82 @@
     <t xml:space="preserve">5.57906770706177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59798049926758</t>
+    <t xml:space="preserve">5.59798002243042</t>
   </si>
   <si>
     <t xml:space="preserve">5.70830106735229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75242900848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73666858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72090816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79340410232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76188516616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78394842147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62319564819336</t>
+    <t xml:space="preserve">5.78710031509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75242853164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7366681098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72090864181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7934045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76188564300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78394937515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62319612503052</t>
   </si>
   <si>
     <t xml:space="preserve">5.64210796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68938875198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7303638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76818799972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73982048034668</t>
+    <t xml:space="preserve">5.68938779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73036479949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76818895339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.739821434021</t>
   </si>
   <si>
     <t xml:space="preserve">5.71460437774658</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62949991226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45298624038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32060241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3426661491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25441026687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27332258224487</t>
+    <t xml:space="preserve">5.62950086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45298671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32060289382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34266662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27332210540771</t>
   </si>
   <si>
     <t xml:space="preserve">5.36473083496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41516256332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39625024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44983530044556</t>
+    <t xml:space="preserve">5.41516208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39625072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44983625411987</t>
   </si>
   <si>
     <t xml:space="preserve">5.37418651580811</t>
@@ -974,31 +974,31 @@
     <t xml:space="preserve">5.21028232574463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35842609405518</t>
+    <t xml:space="preserve">5.35842657089233</t>
   </si>
   <si>
     <t xml:space="preserve">5.34581851959229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48135566711426</t>
+    <t xml:space="preserve">5.4813551902771</t>
   </si>
   <si>
     <t xml:space="preserve">5.46874713897705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44668340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754781723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52548313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56015539169312</t>
+    <t xml:space="preserve">5.44668292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5948281288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52548408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56015586853027</t>
   </si>
   <si>
     <t xml:space="preserve">5.59167528152466</t>
@@ -1007,16 +1007,16 @@
     <t xml:space="preserve">5.66101980209351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7177562713623</t>
+    <t xml:space="preserve">5.71775579452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.67362785339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67677974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49081134796143</t>
+    <t xml:space="preserve">5.67678022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49081230163574</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972270965576</t>
@@ -1025,25 +1025,25 @@
     <t xml:space="preserve">5.56961154937744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60743570327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58221960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55700254440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54439544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67993259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67047595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61058807373047</t>
+    <t xml:space="preserve">5.6074366569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58221912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55700302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5443959236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.679931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67047643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61058712005615</t>
   </si>
   <si>
     <t xml:space="preserve">5.48450708389282</t>
@@ -1058,37 +1058,37 @@
     <t xml:space="preserve">5.47505140304565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43407535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33005809783936</t>
+    <t xml:space="preserve">5.38049125671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43407487869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33005857467651</t>
   </si>
   <si>
     <t xml:space="preserve">5.50026750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56645917892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5065712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51602697372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58537197113037</t>
+    <t xml:space="preserve">5.56645965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50657081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51602745056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58537149429321</t>
   </si>
   <si>
     <t xml:space="preserve">5.66732406616211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6547155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69253969192505</t>
+    <t xml:space="preserve">5.65471601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69254016876221</t>
   </si>
   <si>
     <t xml:space="preserve">5.72406005859375</t>
@@ -1106,40 +1106,40 @@
     <t xml:space="preserve">5.74612426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77449226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74927663803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77764415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78079652786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77134084701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81862115859985</t>
+    <t xml:space="preserve">5.7744927406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74927616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77764463424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78079700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77134037017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81862020492554</t>
   </si>
   <si>
     <t xml:space="preserve">5.91633367538452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97622156143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93209314346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01404619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07708692550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05187082290649</t>
+    <t xml:space="preserve">5.97622203826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93209218978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01404571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07708644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05187034606934</t>
   </si>
   <si>
     <t xml:space="preserve">6.03295755386353</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">6.10860586166382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10230207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23153448104858</t>
+    <t xml:space="preserve">6.10230255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23153495788574</t>
   </si>
   <si>
     <t xml:space="preserve">6.21577501296997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22523021697998</t>
+    <t xml:space="preserve">6.22523069381714</t>
   </si>
   <si>
     <t xml:space="preserve">6.21892690658569</t>
@@ -1166,58 +1166,58 @@
     <t xml:space="preserve">6.2000150680542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23178052902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13353776931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885705947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20558309555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1695613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09751796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34967088699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28745174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33329582214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29399919509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19903326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2219557762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28090190887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28417587280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25470304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2481541633606</t>
+    <t xml:space="preserve">6.23178100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13353824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20558214187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16956090927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0975170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22850513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34966945648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28745126724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33329677581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29399871826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1990327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22195625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28090143203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28417539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25470447540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24815368652344</t>
   </si>
   <si>
     <t xml:space="preserve">6.1237154006958</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">6.18593454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24160480499268</t>
+    <t xml:space="preserve">6.24160432815552</t>
   </si>
   <si>
     <t xml:space="preserve">6.26452779769897</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">6.26125240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19575786590576</t>
+    <t xml:space="preserve">6.19575881958008</t>
   </si>
   <si>
     <t xml:space="preserve">6.14663791656494</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">6.27107667922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41843891143799</t>
+    <t xml:space="preserve">6.4184398651123</t>
   </si>
   <si>
     <t xml:space="preserve">6.39879179000854</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">6.40206432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39224100112915</t>
+    <t xml:space="preserve">6.39224052429199</t>
   </si>
   <si>
     <t xml:space="preserve">6.41188955307007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49375820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51995515823364</t>
+    <t xml:space="preserve">6.49375677108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5199556350708</t>
   </si>
   <si>
     <t xml:space="preserve">6.5756254196167</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">6.53305435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5297794342041</t>
+    <t xml:space="preserve">6.52978038787842</t>
   </si>
   <si>
     <t xml:space="preserve">6.48720788955688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43808746337891</t>
+    <t xml:space="preserve">6.43808603286743</t>
   </si>
   <si>
     <t xml:space="preserve">6.45380592346191</t>
@@ -1289,124 +1289,124 @@
     <t xml:space="preserve">6.36604404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41319894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51406145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45642471313477</t>
+    <t xml:space="preserve">6.41319990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47607326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51406049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45642518997192</t>
   </si>
   <si>
     <t xml:space="preserve">6.26780223846436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36997270584106</t>
+    <t xml:space="preserve">6.36997222900391</t>
   </si>
   <si>
     <t xml:space="preserve">6.32019758224487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3647346496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41581869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44594669342041</t>
+    <t xml:space="preserve">6.36473512649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41581916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4551157951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47214365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44594717025757</t>
   </si>
   <si>
     <t xml:space="preserve">6.46690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47869443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40010118484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46166563034058</t>
+    <t xml:space="preserve">6.47869491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40010166168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46166610717773</t>
   </si>
   <si>
     <t xml:space="preserve">6.47476434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51013088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674646377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2101674079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31102800369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44463777542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46559524536133</t>
+    <t xml:space="preserve">6.51013040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41974830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674741744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21016693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31102895736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44463682174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46559429168701</t>
   </si>
   <si>
     <t xml:space="preserve">6.45904588699341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39748096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42498922348022</t>
+    <t xml:space="preserve">6.39748001098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42498874664307</t>
   </si>
   <si>
     <t xml:space="preserve">6.45773553848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40665054321289</t>
+    <t xml:space="preserve">6.40664958953857</t>
   </si>
   <si>
     <t xml:space="preserve">6.47738409042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37390232086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25732278823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21671676635742</t>
+    <t xml:space="preserve">6.37390327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25732326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21671581268311</t>
   </si>
   <si>
     <t xml:space="preserve">6.24684429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25339412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27828073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35294437408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34508562088013</t>
+    <t xml:space="preserve">6.25339365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27828216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35294485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34508466720581</t>
   </si>
   <si>
     <t xml:space="preserve">6.4171290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39355230331421</t>
+    <t xml:space="preserve">6.39355182647705</t>
   </si>
   <si>
     <t xml:space="preserve">6.54811763763428</t>
@@ -1415,22 +1415,22 @@
     <t xml:space="preserve">6.63457012176514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66076755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79503154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84415149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70661354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199857711792</t>
+    <t xml:space="preserve">6.66076850891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79503107070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84415102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70661401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69351673126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199905395508</t>
   </si>
   <si>
     <t xml:space="preserve">6.67386674880981</t>
@@ -1439,52 +1439,52 @@
     <t xml:space="preserve">6.55925178527832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69678974151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72953653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54942750930786</t>
+    <t xml:space="preserve">6.69679021835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72953701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5494270324707</t>
   </si>
   <si>
     <t xml:space="preserve">6.46428489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51537084579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56907510757446</t>
+    <t xml:space="preserve">6.51537036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56907653808594</t>
   </si>
   <si>
     <t xml:space="preserve">6.52191972732544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20754766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01499366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.915442943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95342969894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81327247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58011293411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24085235595703</t>
+    <t xml:space="preserve">6.20754718780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01499462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91544246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95343017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81327199935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58011245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24085187911987</t>
   </si>
   <si>
     <t xml:space="preserve">5.0312705039978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38625001907349</t>
+    <t xml:space="preserve">5.38624954223633</t>
   </si>
   <si>
     <t xml:space="preserve">5.28407764434814</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">5.32861423492432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19238662719727</t>
+    <t xml:space="preserve">5.19238615036011</t>
   </si>
   <si>
     <t xml:space="preserve">5.35874223709106</t>
@@ -1511,52 +1511,52 @@
     <t xml:space="preserve">5.37707996368408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3050365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40327787399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34826326370239</t>
+    <t xml:space="preserve">5.30503606796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40327835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34826278686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.28276824951172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26049947738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44257545471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38755893707275</t>
+    <t xml:space="preserve">5.26049995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4425745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38755989074707</t>
   </si>
   <si>
     <t xml:space="preserve">5.52378749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33254384994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29848718643188</t>
+    <t xml:space="preserve">5.33254432678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29848766326904</t>
   </si>
   <si>
     <t xml:space="preserve">5.21727418899536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18321657180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21465444564819</t>
+    <t xml:space="preserve">5.18321704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21465396881104</t>
   </si>
   <si>
     <t xml:space="preserve">5.1884560585022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25133180618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32206583023071</t>
+    <t xml:space="preserve">5.25133085250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3220648765564</t>
   </si>
   <si>
     <t xml:space="preserve">5.39148855209351</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">5.34040355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26835966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17928743362427</t>
+    <t xml:space="preserve">5.26835870742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17928695678711</t>
   </si>
   <si>
     <t xml:space="preserve">5.2015552520752</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">5.2893180847168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3377833366394</t>
+    <t xml:space="preserve">5.33778381347656</t>
   </si>
   <si>
     <t xml:space="preserve">5.32468461990356</t>
@@ -1595,25 +1595,25 @@
     <t xml:space="preserve">5.51330852508545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57618236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.628577709198</t>
+    <t xml:space="preserve">5.57618284225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62857818603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.73205900192261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68097400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81851148605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74646711349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68752288818359</t>
+    <t xml:space="preserve">5.68097352981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81851100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74646854400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68752336502075</t>
   </si>
   <si>
     <t xml:space="preserve">5.78052473068237</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">5.75956630706787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75563669204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76742553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70848035812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59583044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44912433624268</t>
+    <t xml:space="preserve">5.75563764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76742601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70848083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5958309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44912338256836</t>
   </si>
   <si>
     <t xml:space="preserve">5.56439399719238</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">5.50282955169678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51985788345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61023950576782</t>
+    <t xml:space="preserve">5.51985836029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61023998260498</t>
   </si>
   <si>
     <t xml:space="preserve">5.49758958816528</t>
@@ -1658,19 +1658,19 @@
     <t xml:space="preserve">5.43340444564819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43864440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42816591262817</t>
+    <t xml:space="preserve">5.43864488601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42816543579102</t>
   </si>
   <si>
     <t xml:space="preserve">5.39541864395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41899681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25002145767212</t>
+    <t xml:space="preserve">5.41899585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25002098083496</t>
   </si>
   <si>
     <t xml:space="preserve">5.55522489547729</t>
@@ -1682,64 +1682,64 @@
     <t xml:space="preserve">5.68621301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93771028518677</t>
+    <t xml:space="preserve">5.93771123886108</t>
   </si>
   <si>
     <t xml:space="preserve">5.90627336502075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89710474014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91282320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01368427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03333234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09620761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00844526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00713586807251</t>
+    <t xml:space="preserve">5.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89710426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91282272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03333282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00844478607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00713443756104</t>
   </si>
   <si>
     <t xml:space="preserve">5.96390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07524919509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06476974487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00451517105103</t>
+    <t xml:space="preserve">6.07524871826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06477117538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00451612472534</t>
   </si>
   <si>
     <t xml:space="preserve">5.63512706756592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46353197097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48842000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48056077957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38886880874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13737154006958</t>
+    <t xml:space="preserve">5.46353244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4884204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48056125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3888692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13737106323242</t>
   </si>
   <si>
     <t xml:space="preserve">5.18059730529785</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">5.02865028381348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0351996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11379384994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05484771728516</t>
+    <t xml:space="preserve">5.03520011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11379337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05484867095947</t>
   </si>
   <si>
     <t xml:space="preserve">5.00638246536255</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">5.06663751602173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07842588424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90683174133301</t>
+    <t xml:space="preserve">5.07842636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90683126449585</t>
   </si>
   <si>
     <t xml:space="preserve">5.09545516967773</t>
@@ -1781,46 +1781,46 @@
     <t xml:space="preserve">4.95791673660278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09938430786133</t>
+    <t xml:space="preserve">5.09938335418701</t>
   </si>
   <si>
     <t xml:space="preserve">5.11248350143433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0771164894104</t>
+    <t xml:space="preserve">5.07711601257324</t>
   </si>
   <si>
     <t xml:space="preserve">5.19500637054443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13606119155884</t>
+    <t xml:space="preserve">5.13606071472168</t>
   </si>
   <si>
     <t xml:space="preserve">5.11641263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13868141174316</t>
+    <t xml:space="preserve">5.13868093490601</t>
   </si>
   <si>
     <t xml:space="preserve">5.15308952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14915943145752</t>
+    <t xml:space="preserve">5.14915990829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.08104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15818929672241</t>
+    <t xml:space="preserve">5.15818977355957</t>
   </si>
   <si>
     <t xml:space="preserve">5.03690242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08987855911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08011913299561</t>
+    <t xml:space="preserve">5.08987808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08012008666992</t>
   </si>
   <si>
     <t xml:space="preserve">5.11776065826416</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">5.34499979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36730527877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39100456237793</t>
+    <t xml:space="preserve">5.36730480194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39100551605225</t>
   </si>
   <si>
     <t xml:space="preserve">5.44258689880371</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">5.47604608535767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37706422805786</t>
+    <t xml:space="preserve">5.37706470489502</t>
   </si>
   <si>
     <t xml:space="preserve">5.38821697235107</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">5.22650098800659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22231912612915</t>
+    <t xml:space="preserve">5.22231864929199</t>
   </si>
   <si>
     <t xml:space="preserve">5.10242509841919</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">5.24462413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26553535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31293535232544</t>
+    <t xml:space="preserve">5.26553583145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31293487548828</t>
   </si>
   <si>
     <t xml:space="preserve">5.23068284988403</t>
@@ -1880,16 +1880,16 @@
     <t xml:space="preserve">5.37288188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25577688217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12751865386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04944944381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14146041870117</t>
+    <t xml:space="preserve">5.25577640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12751913070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0494499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14146089553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.09127235412598</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">5.08709049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3896107673645</t>
+    <t xml:space="preserve">5.38961124420166</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985229492188</t>
@@ -1910,22 +1910,22 @@
     <t xml:space="preserve">5.33524036407471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33802938461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40494728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34639406204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33942270278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46210432052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46907520294189</t>
+    <t xml:space="preserve">5.33802890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40494632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34639358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33942317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46210384368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">5.49138021469116</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">5.48859262466431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49277496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50253343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55969142913818</t>
+    <t xml:space="preserve">5.49277544021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50253391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55969190597534</t>
   </si>
   <si>
     <t xml:space="preserve">5.48998689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4481635093689</t>
+    <t xml:space="preserve">5.44816398620605</t>
   </si>
   <si>
     <t xml:space="preserve">5.45931577682495</t>
@@ -1958,25 +1958,25 @@
     <t xml:space="preserve">5.29481220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14424848556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11218404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28505277633667</t>
+    <t xml:space="preserve">5.14424800872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11218452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28505325317383</t>
   </si>
   <si>
     <t xml:space="preserve">5.39797592163086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40355157852173</t>
+    <t xml:space="preserve">5.40355205535889</t>
   </si>
   <si>
     <t xml:space="preserve">5.49835157394409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5262336730957</t>
+    <t xml:space="preserve">5.52623319625854</t>
   </si>
   <si>
     <t xml:space="preserve">5.62521457672119</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">5.59036254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78971862792969</t>
+    <t xml:space="preserve">5.789719581604</t>
   </si>
   <si>
     <t xml:space="preserve">5.80366039276123</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">5.77717256546021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79808378219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73953199386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75486660003662</t>
+    <t xml:space="preserve">5.79808330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73953151702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75486612319946</t>
   </si>
   <si>
     <t xml:space="preserve">5.82735967636108</t>
@@ -2009,112 +2009,112 @@
     <t xml:space="preserve">5.91797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98071098327637</t>
+    <t xml:space="preserve">5.98071193695068</t>
   </si>
   <si>
     <t xml:space="preserve">6.14939785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02532243728638</t>
+    <t xml:space="preserve">6.02532386779785</t>
   </si>
   <si>
     <t xml:space="preserve">6.07969284057617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08945178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20376825332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10060501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03786993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12430429458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10339307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18982791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21631622314453</t>
+    <t xml:space="preserve">6.0894513130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20376777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10060453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03787040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12430477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10339260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18982744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21631526947021</t>
   </si>
   <si>
     <t xml:space="preserve">6.26510858535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39894390106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35990858078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24001455307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28602075576782</t>
+    <t xml:space="preserve">6.3989429473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35990762710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24001502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28602027893066</t>
   </si>
   <si>
     <t xml:space="preserve">6.23583316802979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17728042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22468042373657</t>
+    <t xml:space="preserve">6.17728090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468090057373</t>
   </si>
   <si>
     <t xml:space="preserve">6.35293817520142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42264318466187</t>
+    <t xml:space="preserve">6.42264270782471</t>
   </si>
   <si>
     <t xml:space="preserve">6.45610189437866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51883697509766</t>
+    <t xml:space="preserve">6.5188364982605</t>
   </si>
   <si>
     <t xml:space="preserve">6.42543172836304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44076633453369</t>
+    <t xml:space="preserve">6.44076681137085</t>
   </si>
   <si>
     <t xml:space="preserve">6.47840738296509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5216236114502</t>
+    <t xml:space="preserve">6.52162504196167</t>
   </si>
   <si>
     <t xml:space="preserve">6.46446657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48537731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57878255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63175868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67079401016235</t>
+    <t xml:space="preserve">6.4853777885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.578782081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63175916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6707935333252</t>
   </si>
   <si>
     <t xml:space="preserve">6.69867515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67915916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62200021743774</t>
+    <t xml:space="preserve">6.67915821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62199974060059</t>
   </si>
   <si>
     <t xml:space="preserve">6.54392957687378</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">6.52441263198853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56205415725708</t>
+    <t xml:space="preserve">6.56205272674561</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194675445557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58714723587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62478876113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41706705093384</t>
+    <t xml:space="preserve">6.58714818954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62478828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">6.26789665222168</t>
@@ -2147,91 +2147,91 @@
     <t xml:space="preserve">6.20237398147583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06435823440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22049760818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18146324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16612768173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06575202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99465322494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01556396484375</t>
+    <t xml:space="preserve">6.06435775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22049713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18146276473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16612672805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06575155258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99465274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01556444168091</t>
   </si>
   <si>
     <t xml:space="preserve">5.95980072021484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91937065124512</t>
+    <t xml:space="preserve">5.91937112808228</t>
   </si>
   <si>
     <t xml:space="preserve">5.84269523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83433103561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76601982116699</t>
+    <t xml:space="preserve">5.83433055877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">5.7325611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88173055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84966516494751</t>
+    <t xml:space="preserve">5.88173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84966564178467</t>
   </si>
   <si>
     <t xml:space="preserve">5.87894201278687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96816444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96677112579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93888854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97374057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94307088851929</t>
+    <t xml:space="preserve">5.96816539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9667706489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93888902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97374105453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94307041168213</t>
   </si>
   <si>
     <t xml:space="preserve">5.9416766166687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07132863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16333961486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14382219314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19122219085693</t>
+    <t xml:space="preserve">6.07132911682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16333913803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14382171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19122171401978</t>
   </si>
   <si>
     <t xml:space="preserve">6.17031049728394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29577970504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33760213851929</t>
+    <t xml:space="preserve">6.29577875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3376030921936</t>
   </si>
   <si>
     <t xml:space="preserve">6.31947946548462</t>
@@ -2249,25 +2249,25 @@
     <t xml:space="preserve">6.60248279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5704174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51186513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49095392227173</t>
+    <t xml:space="preserve">6.57041835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51186561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49095487594604</t>
   </si>
   <si>
     <t xml:space="preserve">6.55229473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54114151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54671859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792432785034</t>
+    <t xml:space="preserve">6.54114198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54671812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4979248046875</t>
   </si>
   <si>
     <t xml:space="preserve">6.56762981414795</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">6.53277730941772</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54950666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41288471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44355535507202</t>
+    <t xml:space="preserve">6.54950571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41288423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44355487823486</t>
   </si>
   <si>
     <t xml:space="preserve">6.5146541595459</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">6.4895601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50350046157837</t>
+    <t xml:space="preserve">6.50350141525269</t>
   </si>
   <si>
     <t xml:space="preserve">6.33481502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31111431121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32087278366089</t>
+    <t xml:space="preserve">6.31111478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32087326049805</t>
   </si>
   <si>
     <t xml:space="preserve">6.15915727615356</t>
@@ -2309,31 +2309,31 @@
     <t xml:space="preserve">6.10478734970093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03647565841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08666372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92494773864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91379499435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94446420669556</t>
+    <t xml:space="preserve">6.03647613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08666324615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9249472618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91379547119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94446516036987</t>
   </si>
   <si>
     <t xml:space="preserve">5.80644845962524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9305248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97652959823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06714725494385</t>
+    <t xml:space="preserve">5.93052434921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97653007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06714630126953</t>
   </si>
   <si>
     <t xml:space="preserve">6.11315202713013</t>
@@ -2342,22 +2342,22 @@
     <t xml:space="preserve">6.04344654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.118727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13963890075684</t>
+    <t xml:space="preserve">6.11872816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13963937759399</t>
   </si>
   <si>
     <t xml:space="preserve">6.19261598587036</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28044462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35712003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296537399292</t>
+    <t xml:space="preserve">6.28044366836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3571195602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296585083008</t>
   </si>
   <si>
     <t xml:space="preserve">6.59830045700073</t>
@@ -2366,31 +2366,31 @@
     <t xml:space="preserve">6.68055248260498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63036489486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66382312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7265567779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66242980957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63454675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7614107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100927352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90779161453247</t>
+    <t xml:space="preserve">6.6303653717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66382360458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72655773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66242933273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63454627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76141023635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100879669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803266525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90779209136963</t>
   </si>
   <si>
     <t xml:space="preserve">6.94682598114014</t>
@@ -2399,49 +2399,49 @@
     <t xml:space="preserve">7.04371690750122</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95379686355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98446750640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95658588409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76419925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84645080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83390378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79347562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80462694168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0332612991333</t>
+    <t xml:space="preserve">6.95379781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98446846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95658540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76419878005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84645128250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81578016281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83390331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79347610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80462837219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03326225280762</t>
   </si>
   <si>
     <t xml:space="preserve">7.19009780883789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27025890350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481737136841</t>
+    <t xml:space="preserve">7.27025985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481641769409</t>
   </si>
   <si>
     <t xml:space="preserve">7.40269947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38178730010986</t>
+    <t xml:space="preserve">7.38178777694702</t>
   </si>
   <si>
     <t xml:space="preserve">7.36087703704834</t>
@@ -2456,82 +2456,82 @@
     <t xml:space="preserve">7.55953598022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.552565574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58044672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44103765487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42361116409302</t>
+    <t xml:space="preserve">7.55256605148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58044767379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44103717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42361068725586</t>
   </si>
   <si>
     <t xml:space="preserve">7.48286008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64318323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59438896179199</t>
+    <t xml:space="preserve">7.6431827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59438943862915</t>
   </si>
   <si>
     <t xml:space="preserve">7.51422739028931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27374505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42012596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35390520095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51857423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48940467834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752643585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52586698532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669742584229</t>
+    <t xml:space="preserve">7.27374362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42012548446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35390567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5185751914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48940420150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752691268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5258674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669599533081</t>
   </si>
   <si>
     <t xml:space="preserve">7.47481918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52951288223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40189456939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33261489868164</t>
+    <t xml:space="preserve">7.52951335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40189409255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33261632919312</t>
   </si>
   <si>
     <t xml:space="preserve">7.2925066947937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35449266433716</t>
+    <t xml:space="preserve">7.35449361801147</t>
   </si>
   <si>
     <t xml:space="preserve">7.3253231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3471999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22687387466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37272310256958</t>
+    <t xml:space="preserve">7.34719944000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22687435150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37272357940674</t>
   </si>
   <si>
     <t xml:space="preserve">7.38366222381592</t>
@@ -2549,40 +2549,40 @@
     <t xml:space="preserve">7.3581395149231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28521490097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21958065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1568660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22979164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16415977478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18457794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020980834961</t>
+    <t xml:space="preserve">7.2852144241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21958112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15686702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22979116439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16415882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18457746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25021028518677</t>
   </si>
   <si>
     <t xml:space="preserve">7.261878490448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21812343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18020153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08539915084839</t>
+    <t xml:space="preserve">7.2181224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18020248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08539867401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.15832424163818</t>
@@ -2591,31 +2591,31 @@
     <t xml:space="preserve">7.11019372940063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05768823623657</t>
+    <t xml:space="preserve">7.05768775939941</t>
   </si>
   <si>
     <t xml:space="preserve">7.07810688018799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99643135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93809080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97309589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77328062057495</t>
+    <t xml:space="preserve">6.99643182754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93809127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97309494018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77328014373779</t>
   </si>
   <si>
     <t xml:space="preserve">6.98622131347656</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93371534347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75286149978638</t>
+    <t xml:space="preserve">6.93371486663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75286197662354</t>
   </si>
   <si>
     <t xml:space="preserve">6.57200717926025</t>
@@ -2627,43 +2627,43 @@
     <t xml:space="preserve">6.8053674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98038625717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86954069137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00372314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04164409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06060457229614</t>
+    <t xml:space="preserve">6.98038673400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86954116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00372362136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04164552688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0606050491333</t>
   </si>
   <si>
     <t xml:space="preserve">7.06206369400024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00518226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03289413452148</t>
+    <t xml:space="preserve">7.00518178939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03289318084717</t>
   </si>
   <si>
     <t xml:space="preserve">6.99351453781128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86370706558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4524097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42178106307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38677740097046</t>
+    <t xml:space="preserve">6.86370801925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45241022109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42178153991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38677787780762</t>
   </si>
   <si>
     <t xml:space="preserve">6.23363494873047</t>
@@ -2672,49 +2672,49 @@
     <t xml:space="preserve">5.97256278991699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76253890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71003246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63564968109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39937162399292</t>
+    <t xml:space="preserve">5.76253938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71003341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63564920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39937114715576</t>
   </si>
   <si>
     <t xml:space="preserve">5.28415012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5228123664856</t>
+    <t xml:space="preserve">4.52281284332275</t>
   </si>
   <si>
     <t xml:space="preserve">4.21215200424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33174848556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52228045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77606010437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33850955963135</t>
+    <t xml:space="preserve">4.33174896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5222806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77605986595154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33850932121277</t>
   </si>
   <si>
     <t xml:space="preserve">3.25537490844727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06649899482727</t>
+    <t xml:space="preserve">3.06649947166443</t>
   </si>
   <si>
     <t xml:space="preserve">3.0424337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10150265693665</t>
+    <t xml:space="preserve">3.10150289535522</t>
   </si>
   <si>
     <t xml:space="preserve">3.17661571502686</t>
@@ -2723,31 +2723,31 @@
     <t xml:space="preserve">3.61854195594788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90440821647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0108790397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76439189910889</t>
+    <t xml:space="preserve">3.90440797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01087856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76439237594604</t>
   </si>
   <si>
     <t xml:space="preserve">3.62802219390869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66667222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64917039871216</t>
+    <t xml:space="preserve">3.66667175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64917016029358</t>
   </si>
   <si>
     <t xml:space="preserve">3.77460169792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70605182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97149968147278</t>
+    <t xml:space="preserve">3.70605158805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97149848937988</t>
   </si>
   <si>
     <t xml:space="preserve">4.05171680450439</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">4.05900907516479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04150772094727</t>
+    <t xml:space="preserve">4.04150724411011</t>
   </si>
   <si>
     <t xml:space="preserve">3.87232112884521</t>
@@ -2768,19 +2768,19 @@
     <t xml:space="preserve">3.64771175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69292545318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56238961219788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51571774482727</t>
+    <t xml:space="preserve">3.69292569160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56239008903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51571750640869</t>
   </si>
   <si>
     <t xml:space="preserve">3.73959755897522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82418990135193</t>
+    <t xml:space="preserve">3.82419037818909</t>
   </si>
   <si>
     <t xml:space="preserve">3.95545530319214</t>
@@ -2792,49 +2792,49 @@
     <t xml:space="preserve">3.85627770423889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.799396276474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76585030555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75855779647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74834871292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78918647766113</t>
+    <t xml:space="preserve">3.79939651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76585054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75855755805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74834799766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78918671607971</t>
   </si>
   <si>
     <t xml:space="preserve">3.91607570648193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85336017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68271613121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56311869621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80960583686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74980759620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69730091094971</t>
+    <t xml:space="preserve">3.85336112976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68271636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56311917304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80960536003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74980688095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69730138778687</t>
   </si>
   <si>
     <t xml:space="preserve">3.77168464660645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78481125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921083450317</t>
+    <t xml:space="preserve">3.7848105430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921035766602</t>
   </si>
   <si>
     <t xml:space="preserve">4.16256284713745</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">4.31862258911133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25590705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60011291503906</t>
+    <t xml:space="preserve">4.25590658187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60011386871338</t>
   </si>
   <si>
     <t xml:space="preserve">4.69929122924805</t>
@@ -2855,64 +2855,64 @@
     <t xml:space="preserve">4.95452928543091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95307064056396</t>
+    <t xml:space="preserve">4.95307016372681</t>
   </si>
   <si>
     <t xml:space="preserve">5.18351364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34540748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17330408096313</t>
+    <t xml:space="preserve">5.34540700912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17330455780029</t>
   </si>
   <si>
     <t xml:space="preserve">5.07996034622192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86410236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96473836898804</t>
+    <t xml:space="preserve">4.86410188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9647388458252</t>
   </si>
   <si>
     <t xml:space="preserve">5.03766393661499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16455316543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1397590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23164415359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12079858779907</t>
+    <t xml:space="preserve">5.16455268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13975858688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23164367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12079811096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.97348976135254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.996826171875</t>
+    <t xml:space="preserve">4.99682569503784</t>
   </si>
   <si>
     <t xml:space="preserve">4.71095895767212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75033903121948</t>
+    <t xml:space="preserve">4.75033855438232</t>
   </si>
   <si>
     <t xml:space="preserve">4.55927515029907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76200771331787</t>
+    <t xml:space="preserve">4.76200675964355</t>
   </si>
   <si>
     <t xml:space="preserve">4.65991163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71533536911011</t>
+    <t xml:space="preserve">4.71533489227295</t>
   </si>
   <si>
     <t xml:space="preserve">4.91952466964722</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">4.93119335174561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88014507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79701089859009</t>
+    <t xml:space="preserve">4.88014554977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79701137542725</t>
   </si>
   <si>
     <t xml:space="preserve">4.92973470687866</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">5.13830041885376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.145592212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16601181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13246583938599</t>
+    <t xml:space="preserve">5.14559268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16601133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13246631622314</t>
   </si>
   <si>
     <t xml:space="preserve">5.25206327438354</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">5.25498008728027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.316237449646</t>
+    <t xml:space="preserve">5.31623697280884</t>
   </si>
   <si>
     <t xml:space="preserve">5.22435188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16309452056885</t>
+    <t xml:space="preserve">5.16309499740601</t>
   </si>
   <si>
     <t xml:space="preserve">5.12663269042969</t>
@@ -2975,19 +2975,19 @@
     <t xml:space="preserve">5.05954122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92244243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94286108016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73283624649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81305456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94723653793335</t>
+    <t xml:space="preserve">4.9224419593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73283672332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81305408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94723606109619</t>
   </si>
   <si>
     <t xml:space="preserve">4.91369104385376</t>
@@ -2999,34 +2999,34 @@
     <t xml:space="preserve">5.27248287200928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28706693649292</t>
+    <t xml:space="preserve">5.28706741333008</t>
   </si>
   <si>
     <t xml:space="preserve">5.29436016082764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20247459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1149640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24622917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12809085845947</t>
+    <t xml:space="preserve">5.20247364044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11496353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24622964859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12809133529663</t>
   </si>
   <si>
     <t xml:space="preserve">5.09746217727661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24768733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27685785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4445858001709</t>
+    <t xml:space="preserve">5.24768781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27685737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44458532333374</t>
   </si>
   <si>
     <t xml:space="preserve">5.47813081741333</t>
@@ -3035,37 +3035,37 @@
     <t xml:space="preserve">5.42416667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31040334701538</t>
+    <t xml:space="preserve">5.31040382385254</t>
   </si>
   <si>
     <t xml:space="preserve">5.33519792556763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32061290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2272686958313</t>
+    <t xml:space="preserve">5.32061243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22726917266846</t>
   </si>
   <si>
     <t xml:space="preserve">5.21414232254028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08141851425171</t>
+    <t xml:space="preserve">5.08141803741455</t>
   </si>
   <si>
     <t xml:space="preserve">5.17768001556396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39207935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28269195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29873514175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18643093109131</t>
+    <t xml:space="preserve">5.39207983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28269147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18643045425415</t>
   </si>
   <si>
     <t xml:space="preserve">5.08725261688232</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">4.87722873687744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76054763793945</t>
+    <t xml:space="preserve">4.76054811477661</t>
   </si>
   <si>
     <t xml:space="preserve">4.95161151885986</t>
@@ -3092,37 +3092,37 @@
     <t xml:space="preserve">4.88452100753784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84368324279785</t>
+    <t xml:space="preserve">4.84368276596069</t>
   </si>
   <si>
     <t xml:space="preserve">4.92390012741089</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08871173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20976734161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08579397201538</t>
+    <t xml:space="preserve">5.08871126174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20976686477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08579349517822</t>
   </si>
   <si>
     <t xml:space="preserve">5.28560876846313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23310327529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20393228530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0114107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0201621055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180500030518</t>
+    <t xml:space="preserve">5.23310279846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.203932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01141119003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02016162872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180547714233</t>
   </si>
   <si>
     <t xml:space="preserve">4.84222459793091</t>
@@ -3131,28 +3131,28 @@
     <t xml:space="preserve">4.79992771148682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84951686859131</t>
+    <t xml:space="preserve">4.84951734542847</t>
   </si>
   <si>
     <t xml:space="preserve">4.7401294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74596357345581</t>
+    <t xml:space="preserve">4.74596309661865</t>
   </si>
   <si>
     <t xml:space="preserve">4.78971815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76638269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64095163345337</t>
+    <t xml:space="preserve">4.76638221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64095115661621</t>
   </si>
   <si>
     <t xml:space="preserve">4.41050815582275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46884775161743</t>
+    <t xml:space="preserve">4.46884822845459</t>
   </si>
   <si>
     <t xml:space="preserve">4.43967819213867</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">4.59427928924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85680913925171</t>
+    <t xml:space="preserve">4.85680961608887</t>
   </si>
   <si>
     <t xml:space="preserve">5.3089451789856</t>
@@ -3176,67 +3176,67 @@
     <t xml:space="preserve">5.51605224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59626960754395</t>
+    <t xml:space="preserve">5.5962700843811</t>
   </si>
   <si>
     <t xml:space="preserve">5.51459360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58460187911987</t>
+    <t xml:space="preserve">5.58460140228271</t>
   </si>
   <si>
     <t xml:space="preserve">5.4985499382019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72899389266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75232982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70419883728027</t>
+    <t xml:space="preserve">5.72899341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75232887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70419836044312</t>
   </si>
   <si>
     <t xml:space="preserve">5.63710784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45041990280151</t>
+    <t xml:space="preserve">5.4504189491272</t>
   </si>
   <si>
     <t xml:space="preserve">5.52917814254761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46500444412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54230499267578</t>
+    <t xml:space="preserve">5.46500492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54230546951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.60210371017456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53209495544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48979902267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49709177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4752140045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34978246688843</t>
+    <t xml:space="preserve">5.53209543228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4897985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49709224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47521448135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34978294372559</t>
   </si>
   <si>
     <t xml:space="preserve">5.36145114898682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53792953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49271583557129</t>
+    <t xml:space="preserve">5.53792905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49271631240845</t>
   </si>
   <si>
     <t xml:space="preserve">5.42854166030884</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">5.52042770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52480363845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40228939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42270803451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62835645675659</t>
+    <t xml:space="preserve">5.52480316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40228843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42270755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62835693359375</t>
   </si>
   <si>
     <t xml:space="preserve">5.61231327056885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50438404083252</t>
+    <t xml:space="preserve">5.50438356399536</t>
   </si>
   <si>
     <t xml:space="preserve">5.46208715438843</t>
@@ -3275,22 +3275,22 @@
     <t xml:space="preserve">5.51021862030029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46937990188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44750165939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38186979293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47083806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40083074569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40520620346069</t>
+    <t xml:space="preserve">5.46938037872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44750213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38187026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40083026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40520572662354</t>
   </si>
   <si>
     <t xml:space="preserve">5.44896078109741</t>
@@ -3302,70 +3302,70 @@
     <t xml:space="preserve">5.39499616622925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37020206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51167631149292</t>
+    <t xml:space="preserve">5.370201587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51167678833008</t>
   </si>
   <si>
     <t xml:space="preserve">5.7304515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89963865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97985553741455</t>
+    <t xml:space="preserve">5.8996376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97985506057739</t>
   </si>
   <si>
     <t xml:space="preserve">6.17383575439453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23071718215942</t>
+    <t xml:space="preserve">6.23071765899658</t>
   </si>
   <si>
     <t xml:space="preserve">6.41740608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50637435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48012113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59242582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53700256347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57929992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54429531097412</t>
+    <t xml:space="preserve">6.50637483596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48012161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59242630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53700304031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57929944992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54429578781128</t>
   </si>
   <si>
     <t xml:space="preserve">6.62159585952759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61430358886719</t>
+    <t xml:space="preserve">6.61430311203003</t>
   </si>
   <si>
     <t xml:space="preserve">6.58221626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53408575057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39552879333496</t>
+    <t xml:space="preserve">6.53408622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3955283164978</t>
   </si>
   <si>
     <t xml:space="preserve">6.28468227386475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50199937820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43490743637085</t>
+    <t xml:space="preserve">6.5019998550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43490791320801</t>
   </si>
   <si>
     <t xml:space="preserve">6.52679347991943</t>
@@ -3374,79 +3374,79 @@
     <t xml:space="preserve">6.61138677597046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72514963150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535966873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77473926544189</t>
+    <t xml:space="preserve">6.7251501083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77473878860474</t>
   </si>
   <si>
     <t xml:space="preserve">6.8505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86516618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90162801742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01976776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09415102005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09706735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87975072860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84037065505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77911376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90016984939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90600347518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92058801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93954944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03581047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89579486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84912252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86078977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77182149887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80682563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81849384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80974340438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78640651702881</t>
+    <t xml:space="preserve">6.86516523361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9016284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01976680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09415054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09706830978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87975120544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84037160873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77911281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90016937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90600395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92058897018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93954849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0358099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89579439163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84912204742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86079120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77182197570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80682468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81849431991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80974245071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78640699386597</t>
   </si>
   <si>
     <t xml:space="preserve">6.8520393371582</t>
@@ -3455,25 +3455,25 @@
     <t xml:space="preserve">6.84766387939453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7091064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64201545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805864334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64639091491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83599519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80828428268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82724475860596</t>
+    <t xml:space="preserve">6.70910549163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64201498031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64639043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83599615097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8082857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82724571228027</t>
   </si>
   <si>
     <t xml:space="preserve">6.85641527175903</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">6.92788124084473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78057241439819</t>
+    <t xml:space="preserve">6.78057384490967</t>
   </si>
   <si>
     <t xml:space="preserve">6.9089207649231</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">6.94684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04018592834473</t>
+    <t xml:space="preserve">7.04018640518188</t>
   </si>
   <si>
     <t xml:space="preserve">7.05477094650269</t>
@@ -3500,43 +3500,43 @@
     <t xml:space="preserve">7.0139331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08394002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1335301399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19770479202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05914640426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06643915176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05331325531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102464675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11748743057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1481146812439</t>
+    <t xml:space="preserve">7.0839409828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13352918624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19770431518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06643867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05331230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915515899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11748647689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14811515808105</t>
   </si>
   <si>
     <t xml:space="preserve">7.21228933334351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344581604004</t>
+    <t xml:space="preserve">7.27062845230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30344533920288</t>
   </si>
   <si>
     <t xml:space="preserve">7.2997989654541</t>
@@ -3554,121 +3554,121 @@
     <t xml:space="preserve">7.26333665847778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25458669662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23270845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23562574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394926071167</t>
+    <t xml:space="preserve">7.25458526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23270893096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23562479019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394973754883</t>
   </si>
   <si>
     <t xml:space="preserve">7.17582654953003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22249794006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27500438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20062017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1831202507019</t>
+    <t xml:space="preserve">7.22249889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28083848953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27500486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20062065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18311834335327</t>
   </si>
   <si>
     <t xml:space="preserve">7.19332885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18749523162842</t>
+    <t xml:space="preserve">7.1874942779541</t>
   </si>
   <si>
     <t xml:space="preserve">7.36178541183472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1408224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14957332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92350673675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165189743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1889533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20499658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14519882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09560918807983</t>
+    <t xml:space="preserve">7.14082193374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.149573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92350625991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165237426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18895292282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20499706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14519786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09560823440552</t>
   </si>
   <si>
     <t xml:space="preserve">6.86808300018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9555926322937</t>
+    <t xml:space="preserve">6.95559358596802</t>
   </si>
   <si>
     <t xml:space="preserve">7.23416709899902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31073760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28667211532593</t>
+    <t xml:space="preserve">7.31073713302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28667259216309</t>
   </si>
   <si>
     <t xml:space="preserve">7.28813123703003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13207149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21083164215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2837553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29615259170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19041156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2779221534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27354621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17728471755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17145109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04601955413818</t>
+    <t xml:space="preserve">7.24145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13207197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21083068847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28375577926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29615354537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19041061401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27792167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27354574203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17728567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1714506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0460205078125</t>
   </si>
   <si>
     <t xml:space="preserve">7.09852647781372</t>
@@ -3677,28 +3677,28 @@
     <t xml:space="preserve">7.13644695281982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25166845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27937984466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456966400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24875068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543226242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47846603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33626270294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53680562973022</t>
+    <t xml:space="preserve">7.25166893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27938079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24875116348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47846651077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33626174926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53680610656738</t>
   </si>
   <si>
     <t xml:space="preserve">7.61337614059448</t>
@@ -3707,76 +3707,76 @@
     <t xml:space="preserve">7.68630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5878529548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734998703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50398874282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294237136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21520709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38001728057861</t>
+    <t xml:space="preserve">7.58785200119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50398921966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21520614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38001680374146</t>
   </si>
   <si>
     <t xml:space="preserve">7.41283321380615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43106412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5331597328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58056163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60608434677124</t>
+    <t xml:space="preserve">7.43106460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53315830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58056211471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6060848236084</t>
   </si>
   <si>
     <t xml:space="preserve">7.55868339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52222061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64254713058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67171716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77016448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76652002334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8868465423584</t>
+    <t xml:space="preserve">7.52221965789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64254665374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67171669006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77016544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76651954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88684606552124</t>
   </si>
   <si>
     <t xml:space="preserve">7.8759069442749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81392097473145</t>
+    <t xml:space="preserve">7.8139214515686</t>
   </si>
   <si>
     <t xml:space="preserve">7.81756734848022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8977837562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507745742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955331802368</t>
+    <t xml:space="preserve">7.89778614044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955379486084</t>
   </si>
   <si>
     <t xml:space="preserve">7.79204320907593</t>
@@ -3785,85 +3785,85 @@
     <t xml:space="preserve">7.74828863143921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70088815689087</t>
+    <t xml:space="preserve">7.70088768005371</t>
   </si>
   <si>
     <t xml:space="preserve">7.90313148498535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72266721725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72111082077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5639820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59976482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843252182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63865756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79034280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86034965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82534646987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8097882270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71488857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311540603638</t>
+    <t xml:space="preserve">7.7226676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72111177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45352506637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56398248672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59976530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6386570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79034185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86034917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82534599304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80978870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71488952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311635971069</t>
   </si>
   <si>
     <t xml:space="preserve">7.76156044006348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84868240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80589962005615</t>
+    <t xml:space="preserve">7.84868192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80590009689331</t>
   </si>
   <si>
     <t xml:space="preserve">7.5219783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64954710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68999767303467</t>
+    <t xml:space="preserve">7.6495475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68999719619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.81367778778076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86423921585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92646837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0859317779541</t>
+    <t xml:space="preserve">7.86423826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92646884918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08593273162842</t>
   </si>
   <si>
     <t xml:space="preserve">8.10148906707764</t>
@@ -3872,31 +3872,31 @@
     <t xml:space="preserve">8.08204174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07815170288086</t>
+    <t xml:space="preserve">8.07815265655518</t>
   </si>
   <si>
     <t xml:space="preserve">8.07037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13260269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23761463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17538642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09759902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03536987304688</t>
+    <t xml:space="preserve">8.13260364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23761558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17538738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09759998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03536891937256</t>
   </si>
   <si>
     <t xml:space="preserve">8.05092716217041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02370166778564</t>
+    <t xml:space="preserve">8.02370071411133</t>
   </si>
   <si>
     <t xml:space="preserve">7.61532163619995</t>
@@ -3905,25 +3905,25 @@
     <t xml:space="preserve">7.6604380607605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77867412567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02759265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10926818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79812097549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05870532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22983646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20650196075439</t>
+    <t xml:space="preserve">7.77867364883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02759170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10926723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79811954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05870628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22983741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20650005340576</t>
   </si>
   <si>
     <t xml:space="preserve">8.14427185058594</t>
@@ -3932,52 +3932,52 @@
     <t xml:space="preserve">7.90702199935913</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07426452636719</t>
+    <t xml:space="preserve">8.07426261901855</t>
   </si>
   <si>
     <t xml:space="preserve">7.88368606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93813705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77556276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6728835105896</t>
+    <t xml:space="preserve">7.9381365776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77556324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67288398742676</t>
   </si>
   <si>
     <t xml:space="preserve">7.67755126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26994752883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29172849655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25439167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68654775619507</t>
+    <t xml:space="preserve">7.26994848251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29172945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25439119338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68654823303223</t>
   </si>
   <si>
     <t xml:space="preserve">6.73477602005005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68499183654785</t>
+    <t xml:space="preserve">6.68499231338501</t>
   </si>
   <si>
     <t xml:space="preserve">6.12337207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95379686355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08603477478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63520812988281</t>
+    <t xml:space="preserve">5.95379734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08603429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63520860671997</t>
   </si>
   <si>
     <t xml:space="preserve">6.31939458847046</t>
@@ -3986,43 +3986,43 @@
     <t xml:space="preserve">6.35050868988037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61187267303467</t>
+    <t xml:space="preserve">6.61187219619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.66165637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10970783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06925868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22638845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06770420074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12993240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02103042602539</t>
+    <t xml:space="preserve">7.10970830917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06925916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2263879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06770372390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12993192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02103090286255</t>
   </si>
   <si>
     <t xml:space="preserve">7.05059003829956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22949886322021</t>
+    <t xml:space="preserve">7.22949981689453</t>
   </si>
   <si>
     <t xml:space="preserve">7.10659599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17193651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30417537689209</t>
+    <t xml:space="preserve">7.17193698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30417490005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.11904239654541</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">6.97902679443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89190435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03503227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02569818496704</t>
+    <t xml:space="preserve">6.89190483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03503274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02569770812988</t>
   </si>
   <si>
     <t xml:space="preserve">6.94946718215942</t>
@@ -4046,34 +4046,31 @@
     <t xml:space="preserve">7.11281967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19527292251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18438386917114</t>
+    <t xml:space="preserve">7.19527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18438339233398</t>
   </si>
   <si>
     <t xml:space="preserve">7.374183177948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44885778427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17971515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16415882110596</t>
+    <t xml:space="preserve">7.4488582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17971611022949</t>
   </si>
   <si>
     <t xml:space="preserve">7.38196134567261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38040542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757562637329</t>
+    <t xml:space="preserve">7.38040637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757610321045</t>
   </si>
   <si>
     <t xml:space="preserve">7.74755907058716</t>
@@ -4085,46 +4082,49 @@
     <t xml:space="preserve">7.48308420181274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60598707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54842567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71955537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088720321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71022176742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5235333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44574546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38974046707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43485689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2621693611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34151172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41152048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46908283233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4317455291748</t>
+    <t xml:space="preserve">7.60598659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54842615127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71955633163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71022081375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52353286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44574594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38973999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43485593795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26217126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34151220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41152000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46908235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43174409866333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32906675338745</t>
@@ -4133,31 +4133,31 @@
     <t xml:space="preserve">7.42085456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53442287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49864196777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68532991409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50797700881958</t>
+    <t xml:space="preserve">7.53442335128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49864149093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68533039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50797653198242</t>
   </si>
   <si>
     <t xml:space="preserve">7.01325225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90435123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96813631057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95102214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63054227828979</t>
+    <t xml:space="preserve">6.90435075759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95102262496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63054180145264</t>
   </si>
   <si>
     <t xml:space="preserve">6.59631490707397</t>
@@ -4166,16 +4166,16 @@
     <t xml:space="preserve">6.68188095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74411058425903</t>
+    <t xml:space="preserve">6.74411010742188</t>
   </si>
   <si>
     <t xml:space="preserve">6.71921825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56831169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7114405632019</t>
+    <t xml:space="preserve">6.5683126449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71144008636475</t>
   </si>
   <si>
     <t xml:space="preserve">6.56675672531128</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">6.64765405654907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60253858566284</t>
+    <t xml:space="preserve">6.60253810882568</t>
   </si>
   <si>
     <t xml:space="preserve">6.42362928390503</t>
@@ -4193,16 +4193,16 @@
     <t xml:space="preserve">6.41896152496338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38784646987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23227310180664</t>
+    <t xml:space="preserve">6.38784694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2322735786438</t>
   </si>
   <si>
     <t xml:space="preserve">6.32406187057495</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45785474777222</t>
+    <t xml:space="preserve">6.45785522460938</t>
   </si>
   <si>
     <t xml:space="preserve">6.55586624145508</t>
@@ -4211,25 +4211,25 @@
     <t xml:space="preserve">6.4905252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41273880004883</t>
+    <t xml:space="preserve">6.41273927688599</t>
   </si>
   <si>
     <t xml:space="preserve">6.3582878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05958652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05491971969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20115900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33339643478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26027679443359</t>
+    <t xml:space="preserve">6.05958700180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0549201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20115852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33339595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26027727127075</t>
   </si>
   <si>
     <t xml:space="preserve">6.2213830947876</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">6.24783039093018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17937850952148</t>
+    <t xml:space="preserve">6.17937898635864</t>
   </si>
   <si>
     <t xml:space="preserve">6.24005222320557</t>
@@ -4250,25 +4250,25 @@
     <t xml:space="preserve">6.50297117233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54653167724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55119895935059</t>
+    <t xml:space="preserve">6.54653215408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55119848251343</t>
   </si>
   <si>
     <t xml:space="preserve">6.59787178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64921092987061</t>
+    <t xml:space="preserve">6.64921045303345</t>
   </si>
   <si>
     <t xml:space="preserve">6.70210552215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65232229232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6429877281189</t>
+    <t xml:space="preserve">6.65232181549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64298677444458</t>
   </si>
   <si>
     <t xml:space="preserve">6.66010093688965</t>
@@ -4277,31 +4277,31 @@
     <t xml:space="preserve">6.72544097900391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77055835723877</t>
+    <t xml:space="preserve">6.77055788040161</t>
   </si>
   <si>
     <t xml:space="preserve">6.77833652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72233057022095</t>
+    <t xml:space="preserve">6.72233009338379</t>
   </si>
   <si>
     <t xml:space="preserve">6.69588232040405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44696474075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27427816390991</t>
+    <t xml:space="preserve">6.44696521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27427864074707</t>
   </si>
   <si>
     <t xml:space="preserve">6.32250642776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29450368881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25872087478638</t>
+    <t xml:space="preserve">6.29450273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25872039794922</t>
   </si>
   <si>
     <t xml:space="preserve">6.17004442214966</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">6.21360445022583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15137481689453</t>
+    <t xml:space="preserve">6.15137529373169</t>
   </si>
   <si>
     <t xml:space="preserve">6.07825565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31006002426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21204853057861</t>
+    <t xml:space="preserve">6.31006050109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21204900741577</t>
   </si>
   <si>
     <t xml:space="preserve">6.19493579864502</t>
@@ -4331,10 +4331,10 @@
     <t xml:space="preserve">6.22916221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28672409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44229793548584</t>
+    <t xml:space="preserve">6.28672361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44229698181152</t>
   </si>
   <si>
     <t xml:space="preserve">6.5807580947876</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">6.58698129653931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65387725830078</t>
+    <t xml:space="preserve">6.65387773513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.63365316390991</t>
@@ -4361,37 +4361,37 @@
     <t xml:space="preserve">6.48274660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44074201583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20893716812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09381294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0331392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92112636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26961183547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59009218215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23382902145386</t>
+    <t xml:space="preserve">6.44074153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20893669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09381341934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03313970565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92112731933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26961135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59009265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48119115829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23382949829102</t>
   </si>
   <si>
     <t xml:space="preserve">6.19649124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18249034881592</t>
+    <t xml:space="preserve">6.18248987197876</t>
   </si>
   <si>
     <t xml:space="preserve">6.10003614425659</t>
@@ -4400,10 +4400,10 @@
     <t xml:space="preserve">6.2836127281189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45629835128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52164030075073</t>
+    <t xml:space="preserve">6.45629978179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52163982391357</t>
   </si>
   <si>
     <t xml:space="preserve">6.67876958847046</t>
@@ -4418,43 +4418,43 @@
     <t xml:space="preserve">6.85767889022827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07081460952759</t>
+    <t xml:space="preserve">7.07081413269043</t>
   </si>
   <si>
     <t xml:space="preserve">7.10348463058472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13459968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09726238250732</t>
+    <t xml:space="preserve">7.13459920883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09726190567017</t>
   </si>
   <si>
     <t xml:space="preserve">7.19060611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15326833724976</t>
+    <t xml:space="preserve">7.15326881408691</t>
   </si>
   <si>
     <t xml:space="preserve">7.31039714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49241876602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52820062637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57954025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6339898109436</t>
+    <t xml:space="preserve">7.49241924285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52820014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57953977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63399124145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.74289226531982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91480112075806</t>
+    <t xml:space="preserve">7.9148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">7.90892314910889</t>
@@ -4463,31 +4463,31 @@
     <t xml:space="preserve">7.91228151321411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93243503570557</t>
+    <t xml:space="preserve">7.93243551254272</t>
   </si>
   <si>
     <t xml:space="preserve">7.87029218673706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83502244949341</t>
+    <t xml:space="preserve">7.83502197265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.7728796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73760986328125</t>
+    <t xml:space="preserve">7.73760938644409</t>
   </si>
   <si>
     <t xml:space="preserve">7.69562149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71409702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73928880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68554449081421</t>
+    <t xml:space="preserve">7.7140965461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73928928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68554496765137</t>
   </si>
   <si>
     <t xml:space="preserve">7.6351580619812</t>
@@ -4496,22 +4496,22 @@
     <t xml:space="preserve">7.65867185592651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71073770523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69394254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81990814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79471349716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48064136505127</t>
+    <t xml:space="preserve">7.71073722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69394159317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81990718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79471302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48064088821411</t>
   </si>
   <si>
     <t xml:space="preserve">7.50415468215942</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">7.66371059417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56965589523315</t>
+    <t xml:space="preserve">7.56965684890747</t>
   </si>
   <si>
     <t xml:space="preserve">7.58477210998535</t>
@@ -4532,19 +4532,19 @@
     <t xml:space="preserve">7.58645248413086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53774547576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64691495895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54446411132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59484958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67210817337036</t>
+    <t xml:space="preserve">7.53774499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64691591262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54446363449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5948486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6721076965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.79807329177856</t>
@@ -4553,22 +4553,22 @@
     <t xml:space="preserve">7.78463745117188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7795991897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85685634613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90052461624146</t>
+    <t xml:space="preserve">7.77959823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85685682296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90052509307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.02145099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12558174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11550426483154</t>
+    <t xml:space="preserve">8.12558269500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11550521850586</t>
   </si>
   <si>
     <t xml:space="preserve">8.09535121917725</t>
@@ -4580,19 +4580,19 @@
     <t xml:space="preserve">8.01977157592773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92403745651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04496383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08191299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13230133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18100643157959</t>
+    <t xml:space="preserve">7.92403841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04496479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0819149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13230037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18100547790527</t>
   </si>
   <si>
     <t xml:space="preserve">8.28513813018799</t>
@@ -4604,25 +4604,25 @@
     <t xml:space="preserve">8.34560108184814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2767391204834</t>
+    <t xml:space="preserve">8.27674007415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.37247371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39430713653564</t>
+    <t xml:space="preserve">8.39430809020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.4312572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51943206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54042625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56981945037842</t>
+    <t xml:space="preserve">8.51943302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54042720794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5698184967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.69998168945312</t>
@@ -4637,22 +4637,22 @@
     <t xml:space="preserve">8.74197006225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60340881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63280200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61180782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50263786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49423885345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39094829559326</t>
+    <t xml:space="preserve">8.60340976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6328010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61180686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50263690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49423980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39094734191895</t>
   </si>
   <si>
     <t xml:space="preserve">8.41026306152344</t>
@@ -4676,10 +4676,10 @@
     <t xml:space="preserve">8.45644950866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51103591918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46064853668213</t>
+    <t xml:space="preserve">8.51103496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46064949035645</t>
   </si>
   <si>
     <t xml:space="preserve">8.51523399353027</t>
@@ -4688,43 +4688,43 @@
     <t xml:space="preserve">8.40186500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16757106781006</t>
+    <t xml:space="preserve">8.16757011413574</t>
   </si>
   <si>
     <t xml:space="preserve">7.80143260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99793720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54950189590454</t>
+    <t xml:space="preserve">7.99793863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54950284957886</t>
   </si>
   <si>
     <t xml:space="preserve">7.52095031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43193483352661</t>
+    <t xml:space="preserve">7.43193578720093</t>
   </si>
   <si>
     <t xml:space="preserve">7.73425054550171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63179969787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55286169052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51591062545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60660600662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72417449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78295755386353</t>
+    <t xml:space="preserve">7.63179922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5528621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51591157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60660696029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72417306900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78295707702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.81150960922241</t>
@@ -4733,31 +4733,31 @@
     <t xml:space="preserve">7.80983018875122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74096918106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075609207153</t>
+    <t xml:space="preserve">7.74096870422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075704574585</t>
   </si>
   <si>
     <t xml:space="preserve">7.92739677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93915462493896</t>
+    <t xml:space="preserve">7.93915414810181</t>
   </si>
   <si>
     <t xml:space="preserve">8.09366989135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0264892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772411346436</t>
+    <t xml:space="preserve">8.02648830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18772506713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.21795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14909648895264</t>
+    <t xml:space="preserve">8.149094581604</t>
   </si>
   <si>
     <t xml:space="preserve">8.21291732788086</t>
@@ -4772,28 +4772,28 @@
     <t xml:space="preserve">8.26834201812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17092895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89212608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19444370269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09703063964844</t>
+    <t xml:space="preserve">8.17092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89212656021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19444274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09702968597412</t>
   </si>
   <si>
     <t xml:space="preserve">8.3808708190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39766597747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34056282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36575508117676</t>
+    <t xml:space="preserve">8.39766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34056186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36575603485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.13565921783447</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">8.2532262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27338027954102</t>
+    <t xml:space="preserve">8.27338123321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895992279053</t>
@@ -4823,73 +4823,73 @@
     <t xml:space="preserve">8.7335729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7713623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67898750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67479038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64539813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92252159118652</t>
+    <t xml:space="preserve">8.77136325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67898845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67478942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92252063751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.98970222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90572452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98130416870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96450996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17025184631348</t>
+    <t xml:space="preserve">8.90572547912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98130321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96450901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17025089263916</t>
   </si>
   <si>
     <t xml:space="preserve">9.19124603271484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28781890869141</t>
+    <t xml:space="preserve">9.28781986236572</t>
   </si>
   <si>
     <t xml:space="preserve">9.38859176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49776172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42638111114502</t>
+    <t xml:space="preserve">9.49776268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39698886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4263801574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.40538597106934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30461502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33400726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14925861358643</t>
+    <t xml:space="preserve">9.30461406707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33400630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14925765991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.03588962554932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01909446716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04848575592041</t>
+    <t xml:space="preserve">9.01909351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04848480224609</t>
   </si>
   <si>
     <t xml:space="preserve">9.06947994232178</t>
@@ -4898,40 +4898,40 @@
     <t xml:space="preserve">9.20384216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34660243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35500049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27942085266113</t>
+    <t xml:space="preserve">9.34660339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35500144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27942180633545</t>
   </si>
   <si>
     <t xml:space="preserve">9.24583053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25003051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25842666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48936367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48096466064453</t>
+    <t xml:space="preserve">9.25002956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25842761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43058013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48096561431885</t>
   </si>
   <si>
     <t xml:space="preserve">9.52295398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64891910552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60693073272705</t>
+    <t xml:space="preserve">9.64891815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60692977905273</t>
   </si>
   <si>
     <t xml:space="preserve">9.67411231994629</t>
@@ -4940,13 +4940,13 @@
     <t xml:space="preserve">9.63632297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930553436279</t>
+    <t xml:space="preserve">9.69930458068848</t>
   </si>
   <si>
     <t xml:space="preserve">9.70770263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68250942230225</t>
+    <t xml:space="preserve">9.68250846862793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0394096374512</t>
@@ -4973,34 +4973,34 @@
     <t xml:space="preserve">9.73289585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83366680145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85886001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83786678314209</t>
+    <t xml:space="preserve">9.83366775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85886096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83786582946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.93024063110352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87565612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7916784286499</t>
+    <t xml:space="preserve">9.87565517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79167938232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.76648616790771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82526969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97222805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9260425567627</t>
+    <t xml:space="preserve">9.825270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97222900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92604160308838</t>
   </si>
   <si>
     <t xml:space="preserve">9.91344547271729</t>
@@ -5009,7 +5009,7 @@
     <t xml:space="preserve">10.0268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1653747558594</t>
+    <t xml:space="preserve">10.1653757095337</t>
   </si>
   <si>
     <t xml:space="preserve">10.194766998291</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">10.1359834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1401824951172</t>
+    <t xml:space="preserve">10.1401815414429</t>
   </si>
   <si>
     <t xml:space="preserve">10.144380569458</t>
@@ -5027,61 +5027,61 @@
     <t xml:space="preserve">10.2199602127075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0981931686401</t>
+    <t xml:space="preserve">10.0981941223145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1989660263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1317834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2157621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2241582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2115631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.303936958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2535514831543</t>
+    <t xml:space="preserve">10.1317844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2157611846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2241592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2115621566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3039379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.25355052948</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3291301727295</t>
+    <t xml:space="preserve">10.3291292190552</t>
   </si>
   <si>
     <t xml:space="preserve">10.4173049926758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3333292007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.245153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3963117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4341011047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3921117782593</t>
+    <t xml:space="preserve">10.3333282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2451524734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913408279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3963108062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434100151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676904678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5222768783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3921136856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3207321166992</t>
@@ -5090,31 +5090,31 @@
     <t xml:space="preserve">10.2745447158813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.203164100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1275873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2283573150635</t>
+    <t xml:space="preserve">10.2031650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1275863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2283582687378</t>
   </si>
   <si>
     <t xml:space="preserve">10.2367553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2955389022827</t>
+    <t xml:space="preserve">10.295539855957</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695737838745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1527795791626</t>
+    <t xml:space="preserve">10.1527786254883</t>
   </si>
   <si>
     <t xml:space="preserve">9.94283676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55654525756836</t>
+    <t xml:space="preserve">9.55654430389404</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682472229004</t>
@@ -5123,52 +5123,52 @@
     <t xml:space="preserve">9.37179565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24163246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96870708465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46417045593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53135204315186</t>
+    <t xml:space="preserve">9.24163341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96870803833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46417140960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53135299682617</t>
   </si>
   <si>
     <t xml:space="preserve">9.58173751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65311813354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731620788574</t>
+    <t xml:space="preserve">9.65311717987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731716156006</t>
   </si>
   <si>
     <t xml:space="preserve">9.66991329193115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63212299346924</t>
+    <t xml:space="preserve">9.63212394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.67831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6909065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9890251159668</t>
+    <t xml:space="preserve">9.69090747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98902416229248</t>
   </si>
   <si>
     <t xml:space="preserve">9.87985515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84817504882812</t>
+    <t xml:space="preserve">9.84817409515381</t>
   </si>
   <si>
     <t xml:space="preserve">9.73050308227539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82554531097412</t>
+    <t xml:space="preserve">9.8255443572998</t>
   </si>
   <si>
     <t xml:space="preserve">9.81649398803711</t>
@@ -5180,46 +5180,46 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71239948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78028678894043</t>
+    <t xml:space="preserve">9.73955535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71239852905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75313091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78028774261475</t>
   </si>
   <si>
     <t xml:space="preserve">9.72597694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65808963775635</t>
+    <t xml:space="preserve">9.65809059143066</t>
   </si>
   <si>
     <t xml:space="preserve">9.92511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0020513534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0744647979736</t>
+    <t xml:space="preserve">10.0020523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0744657516479</t>
   </si>
   <si>
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0925674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0337314605713</t>
+    <t xml:space="preserve">10.092568397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0337333679199</t>
   </si>
   <si>
     <t xml:space="preserve">10.069938659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0654144287109</t>
+    <t xml:space="preserve">10.0654134750366</t>
   </si>
   <si>
     <t xml:space="preserve">10.1378259658813</t>
@@ -5231,10 +5231,10 @@
     <t xml:space="preserve">10.1785583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.151403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1151971817017</t>
+    <t xml:space="preserve">10.1514043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.115198135376</t>
   </si>
   <si>
     <t xml:space="preserve">10.142352104187</t>
@@ -5252,13 +5252,13 @@
     <t xml:space="preserve">10.2736015319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2147655487061</t>
+    <t xml:space="preserve">10.2147645950317</t>
   </si>
   <si>
     <t xml:space="preserve">10.2102384567261</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2011890411377</t>
+    <t xml:space="preserve">10.2011880874634</t>
   </si>
   <si>
     <t xml:space="preserve">10.4455814361572</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">10.9434213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9253177642822</t>
+    <t xml:space="preserve">10.9253187179565</t>
   </si>
   <si>
     <t xml:space="preserve">10.9615240097046</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">10.9751024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1063508987427</t>
+    <t xml:space="preserve">11.106351852417</t>
   </si>
   <si>
     <t xml:space="preserve">11.133505821228</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">10.8393278121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7669153213501</t>
+    <t xml:space="preserve">10.7669143676758</t>
   </si>
   <si>
     <t xml:space="preserve">10.7171306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5315723419189</t>
+    <t xml:space="preserve">10.5315732955933</t>
   </si>
   <si>
     <t xml:space="preserve">10.4908399581909</t>
@@ -5327,16 +5327,16 @@
     <t xml:space="preserve">10.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858812332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.66282081604</t>
+    <t xml:space="preserve">10.5858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6628217697144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7261819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1787643432617</t>
+    <t xml:space="preserve">11.178765296936</t>
   </si>
   <si>
     <t xml:space="preserve">11.7173357009888</t>
@@ -5351,7 +5351,7 @@
     <t xml:space="preserve">11.4231586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005289077759</t>
+    <t xml:space="preserve">11.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141063690186</t>
@@ -5360,10 +5360,10 @@
     <t xml:space="preserve">11.3869514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4865188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6313467025757</t>
+    <t xml:space="preserve">11.486517906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6313457489014</t>
   </si>
   <si>
     <t xml:space="preserve">11.5815620422363</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">11.595139503479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6901817321777</t>
+    <t xml:space="preserve">11.7625932693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6901807785034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8576364517212</t>
@@ -5384,43 +5384,43 @@
     <t xml:space="preserve">12.0160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9979372024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567722320557</t>
+    <t xml:space="preserve">11.9979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567712783813</t>
   </si>
   <si>
     <t xml:space="preserve">12.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2785367965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3328475952148</t>
+    <t xml:space="preserve">12.2785358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3328466415405</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003023147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3781061172485</t>
+    <t xml:space="preserve">12.500301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3781051635742</t>
   </si>
   <si>
     <t xml:space="preserve">12.5093536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3962078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4052591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3102188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554754257202</t>
+    <t xml:space="preserve">12.3962087631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4052600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3102178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554763793945</t>
   </si>
   <si>
     <t xml:space="preserve">12.2875881195068</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">12.3826313018799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6451292037964</t>
+    <t xml:space="preserve">12.6451282501221</t>
   </si>
   <si>
     <t xml:space="preserve">12.6722831726074</t>
@@ -5474,7 +5474,7 @@
     <t xml:space="preserve">13.2244319915771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.514084815979</t>
+    <t xml:space="preserve">13.5140838623047</t>
   </si>
   <si>
     <t xml:space="preserve">13.7539520263672</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">13.7336559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6259603500366</t>
+    <t xml:space="preserve">13.6259593963623</t>
   </si>
   <si>
     <t xml:space="preserve">13.5369930267334</t>
@@ -5513,19 +5513,19 @@
     <t xml:space="preserve">13.5791349411011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5978660583496</t>
+    <t xml:space="preserve">13.5978651046753</t>
   </si>
   <si>
     <t xml:space="preserve">13.5042161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4199323654175</t>
+    <t xml:space="preserve">13.4199314117432</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620733261108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4339790344238</t>
+    <t xml:space="preserve">13.4339799880981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2794580459595</t>
@@ -5534,16 +5534,16 @@
     <t xml:space="preserve">13.1343011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4246139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9563684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.666054725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7550230026245</t>
+    <t xml:space="preserve">13.424614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9563674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7550220489502</t>
   </si>
   <si>
     <t xml:space="preserve">12.8205757141113</t>
@@ -5552,16 +5552,16 @@
     <t xml:space="preserve">12.7222452163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9329566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0500183105469</t>
+    <t xml:space="preserve">12.9329557418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0500173568726</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001779556274</t>
+    <t xml:space="preserve">12.9001789093018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7831172943115</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">13.1951732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0359697341919</t>
+    <t xml:space="preserve">13.0359706878662</t>
   </si>
   <si>
     <t xml:space="preserve">13.1670789718628</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">13.2045392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2888221740723</t>
+    <t xml:space="preserve">13.2888231277466</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654104232788</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">13.4386615753174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4714393615723</t>
+    <t xml:space="preserve">13.4714384078979</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777894973755</t>
@@ -5600,10 +5600,10 @@
     <t xml:space="preserve">13.382472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4995336532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4808044433594</t>
+    <t xml:space="preserve">13.499532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4808034896851</t>
   </si>
   <si>
     <t xml:space="preserve">13.5182638168335</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">13.8038930892944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8413534164429</t>
+    <t xml:space="preserve">13.8413524627686</t>
   </si>
   <si>
     <t xml:space="preserve">13.808575630188</t>
@@ -5630,13 +5630,13 @@
     <t xml:space="preserve">13.4573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1623964309692</t>
+    <t xml:space="preserve">13.1623973846436</t>
   </si>
   <si>
     <t xml:space="preserve">12.8486709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1483497619629</t>
+    <t xml:space="preserve">13.1483488082886</t>
   </si>
   <si>
     <t xml:space="preserve">13.0172395706177</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">13.1389837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1015243530273</t>
+    <t xml:space="preserve">13.101523399353</t>
   </si>
   <si>
     <t xml:space="preserve">13.1904907226562</t>
@@ -5663,13 +5663,13 @@
     <t xml:space="preserve">13.9350023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.949049949646</t>
+    <t xml:space="preserve">13.9490509033203</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0146045684814</t>
+    <t xml:space="preserve">14.0146036148071</t>
   </si>
   <si>
     <t xml:space="preserve">14.047381401062</t>
@@ -5684,10 +5684,10 @@
     <t xml:space="preserve">14.314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3611068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1410312652588</t>
+    <t xml:space="preserve">14.3611059188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1410303115845</t>
   </si>
   <si>
     <t xml:space="preserve">13.9911918640137</t>
@@ -5696,25 +5696,25 @@
     <t xml:space="preserve">14.1223001480103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9865102767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019023895264</t>
+    <t xml:space="preserve">13.9865093231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019033432007</t>
   </si>
   <si>
     <t xml:space="preserve">13.9818267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752387046814</t>
+    <t xml:space="preserve">13.7523860931396</t>
   </si>
   <si>
     <t xml:space="preserve">13.836669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8881778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0005559921265</t>
+    <t xml:space="preserve">13.8881769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0005569458008</t>
   </si>
   <si>
     <t xml:space="preserve">14.3657884597778</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">14.403247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.286187171936</t>
+    <t xml:space="preserve">14.2861862182617</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815046310425</t>
@@ -5735,19 +5735,19 @@
     <t xml:space="preserve">14.4453907012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4641199111938</t>
+    <t xml:space="preserve">14.4641208648682</t>
   </si>
   <si>
     <t xml:space="preserve">14.3517408370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1129360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.033332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460359573364</t>
+    <t xml:space="preserve">14.1129350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0333337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460350036621</t>
   </si>
   <si>
     <t xml:space="preserve">14.0567464828491</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">14.5624523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6561012268066</t>
+    <t xml:space="preserve">14.6561002731323</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982431411743</t>
@@ -5783,13 +5783,13 @@
     <t xml:space="preserve">15.1009349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9136362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5999116897583</t>
+    <t xml:space="preserve">14.9136371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7684812545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5999126434326</t>
   </si>
   <si>
     <t xml:space="preserve">14.4500732421875</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">14.4219779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3376941680908</t>
+    <t xml:space="preserve">14.3376951217651</t>
   </si>
   <si>
     <t xml:space="preserve">14.3002347946167</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">13.5229454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8554000854492</t>
+    <t xml:space="preserve">13.8554010391235</t>
   </si>
   <si>
     <t xml:space="preserve">13.9089336395264</t>
@@ -6486,6 +6486,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.2299995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1599998474121</t>
   </si>
 </sst>
 </file>
@@ -48572,7 +48575,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>1349</v>
+        <v>849</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48598,7 +48601,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1607" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -48624,7 +48627,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1608" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -48650,7 +48653,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G1609" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -48702,7 +48705,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1611" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48728,7 +48731,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48780,7 +48783,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G1614" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48806,7 +48809,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1615" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48832,7 +48835,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G1616" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48884,7 +48887,7 @@
         <v>9.70400047302246</v>
       </c>
       <c r="G1618" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48910,7 +48913,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G1619" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48936,7 +48939,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1620" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -48962,7 +48965,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G1621" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -48988,7 +48991,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G1622" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -49014,7 +49017,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G1623" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -49040,7 +49043,7 @@
         <v>9.5</v>
       </c>
       <c r="G1624" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -49066,7 +49069,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G1625" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -49092,7 +49095,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G1626" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -49118,7 +49121,7 @@
         <v>9.4379997253418</v>
       </c>
       <c r="G1627" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -49144,7 +49147,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1628" t="s">
-        <v>827</v>
+        <v>1367</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -49300,7 +49303,7 @@
         <v>9.5</v>
       </c>
       <c r="G1634" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -71668,7 +71671,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6496412037</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>774825</v>
@@ -71689,6 +71692,32 @@
         <v>2157</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6518287037</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>1195841</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>15.9750003814697</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>16.2299995422363</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>16.1599998474121</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2158</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="2159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="2160">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19125843048096</t>
+    <t xml:space="preserve">5.19125890731812</t>
   </si>
   <si>
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18521547317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05528259277344</t>
+    <t xml:space="preserve">5.18521499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0552830696106</t>
   </si>
   <si>
     <t xml:space="preserve">4.95858860015869</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">4.83772134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8105263710022</t>
+    <t xml:space="preserve">4.81052589416504</t>
   </si>
   <si>
     <t xml:space="preserve">4.92535018920898</t>
@@ -68,88 +68,88 @@
     <t xml:space="preserve">4.91930723190308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73196268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50533533096313</t>
+    <t xml:space="preserve">4.73196220397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50533628463745</t>
   </si>
   <si>
     <t xml:space="preserve">4.59900856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41468524932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65944242477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67455005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52346658706665</t>
+    <t xml:space="preserve">4.41468477249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65944194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67455053329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52346563339233</t>
   </si>
   <si>
     <t xml:space="preserve">4.59598636627197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52648687362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27870988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45094537734985</t>
+    <t xml:space="preserve">4.52648782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27870845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45094585418701</t>
   </si>
   <si>
     <t xml:space="preserve">4.3119478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19410181045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00373601913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09136486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98862767219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61696004867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41450619697571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47796201705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54443860054016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64717674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.680415391922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74991321563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64113283157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091661453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75595808029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66228580474854</t>
+    <t xml:space="preserve">4.19410228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00373554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09136438369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98862743377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61695981025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41450643539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67135000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47796177864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64717626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68041563034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113330841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091589927673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75595688819885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66228437423706</t>
   </si>
   <si>
     <t xml:space="preserve">3.62300276756287</t>
@@ -158,52 +158,52 @@
     <t xml:space="preserve">3.67437148094177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76804375648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78315258026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93725800514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08834266662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10345125198364</t>
+    <t xml:space="preserve">3.76804423332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78315281867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93725872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08834314346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10345077514648</t>
   </si>
   <si>
     <t xml:space="preserve">4.0248875617981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91006302833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96143174171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97351884841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03395223617554</t>
+    <t xml:space="preserve">3.91006326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96143221855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97351837158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03395318984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.38446855545044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42979335784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28173112869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29986047744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03697443008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07323408126831</t>
+    <t xml:space="preserve">4.42979288101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28173065185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29986095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03697395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07323455810547</t>
   </si>
   <si>
     <t xml:space="preserve">4.0943865776062</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">4.01884460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87984561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90402007102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82545685768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79221796989441</t>
+    <t xml:space="preserve">3.99164915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87984681129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90401983261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82545590400696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79221749305725</t>
   </si>
   <si>
     <t xml:space="preserve">3.83149933815002</t>
@@ -233,160 +233,160 @@
     <t xml:space="preserve">3.7589795589447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79523944854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60487270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81336903572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85567378997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77408719062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97049689292908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04301691055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97653985023499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23036193847656</t>
+    <t xml:space="preserve">3.79523921012878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6048731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81336951255798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85567307472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77408742904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97049736976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04301786422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97654056549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23036241531372</t>
   </si>
   <si>
     <t xml:space="preserve">4.23338413238525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36935997009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38748979568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39655447006226</t>
+    <t xml:space="preserve">4.36935949325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38749074935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39655542373657</t>
   </si>
   <si>
     <t xml:space="preserve">4.33612108230591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21223258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05208301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88588953018188</t>
+    <t xml:space="preserve">4.21223211288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05208206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88588929176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.85265159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8043041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078166007996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89797616004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93423700332642</t>
+    <t xml:space="preserve">3.80430483818054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87078142166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89797639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93423748016357</t>
   </si>
   <si>
     <t xml:space="preserve">3.92215085029602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90704250335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97956228256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01582193374634</t>
+    <t xml:space="preserve">3.90704226493835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97956204414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01582288742065</t>
   </si>
   <si>
     <t xml:space="preserve">4.21827554702759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31496953964233</t>
+    <t xml:space="preserve">4.31496906280518</t>
   </si>
   <si>
     <t xml:space="preserve">4.30590391159058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35727262496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34518671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13366794586182</t>
+    <t xml:space="preserve">4.35727310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34518623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13366842269897</t>
   </si>
   <si>
     <t xml:space="preserve">4.10647296905518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00071382522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98560523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610646247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70156693458557</t>
+    <t xml:space="preserve">4.00071334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98560547828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91610741615295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70156717300415</t>
   </si>
   <si>
     <t xml:space="preserve">3.52026557922363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38731098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48098421096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46889686584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60789442062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80732583999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85869526863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83452033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20903205871582</t>
+    <t xml:space="preserve">3.3873119354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48098397254944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46889662742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6078941822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80732560157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8586950302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83452081680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2090322971344</t>
   </si>
   <si>
     <t xml:space="preserve">2.79929113388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96125364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0639910697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11535978317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14557671546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01322650909424</t>
+    <t xml:space="preserve">2.96125316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06399083137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11536002159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1455762386322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01322674751282</t>
   </si>
   <si>
     <t xml:space="preserve">2.91653251647949</t>
@@ -395,49 +395,49 @@
     <t xml:space="preserve">2.84763789176941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9455406665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19694495201111</t>
+    <t xml:space="preserve">2.94554042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19694471359253</t>
   </si>
   <si>
     <t xml:space="preserve">3.44472336769104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47191834449768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57767748832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5263090133667</t>
+    <t xml:space="preserve">3.4719181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57767772674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52630925178528</t>
   </si>
   <si>
     <t xml:space="preserve">3.58674263954163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55350470542908</t>
+    <t xml:space="preserve">3.55350422859192</t>
   </si>
   <si>
     <t xml:space="preserve">3.5958080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58976435661316</t>
+    <t xml:space="preserve">3.58976483345032</t>
   </si>
   <si>
     <t xml:space="preserve">3.61998128890991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5353741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65926289558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61393809318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78617405891418</t>
+    <t xml:space="preserve">3.53537392616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65926337242126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.613938331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78617334365845</t>
   </si>
   <si>
     <t xml:space="preserve">3.71365356445312</t>
@@ -446,103 +446,103 @@
     <t xml:space="preserve">3.40846347808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42055010795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71969676017761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96747541427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94027996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099811553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84962940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81639099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69552397727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72876262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92517185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89495468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95236730575562</t>
+    <t xml:space="preserve">3.42054986953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71969723701477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96747589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94027972221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099787712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308450698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84962916374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163914680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80128312110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6955235004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72876191139221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92517113685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89495515823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95236682891846</t>
   </si>
   <si>
     <t xml:space="preserve">4.0490608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14273309707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07927894592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19108009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15481996536255</t>
+    <t xml:space="preserve">4.14273357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07927751541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19108057022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15482044219971</t>
   </si>
   <si>
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7317841053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78919553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68645834922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77710914611816</t>
+    <t xml:space="preserve">3.73178434371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78919625282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68645763397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77106595039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77710890769958</t>
   </si>
   <si>
     <t xml:space="preserve">3.49609208106995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54141783714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47494077682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49911403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49004912376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49307060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68343639373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78013062477112</t>
+    <t xml:space="preserve">3.54141759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47494053840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49911332130432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49004888534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49307036399841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68343687057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78013110160828</t>
   </si>
   <si>
     <t xml:space="preserve">3.65322017669678</t>
@@ -551,70 +551,70 @@
     <t xml:space="preserve">3.74387073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87380266189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99467015266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10949420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15784168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23640489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114721298218</t>
+    <t xml:space="preserve">3.87380290031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99467062950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10949516296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15784120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23640537261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114768981934</t>
   </si>
   <si>
     <t xml:space="preserve">3.84358620643616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00977849960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14575529098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13971042633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25453615188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26964378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11251640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94632387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99360394477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06294870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00305986404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96208357810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90849924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79502725601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95578050613403</t>
+    <t xml:space="preserve">4.00977945327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14575481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13971138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25453567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26964426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20618867874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1125168800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94632458686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99360418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06294822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00306034088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96208333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90849947929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7950267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95577907562256</t>
   </si>
   <si>
     <t xml:space="preserve">4.10392427444458</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">4.23946094512939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05979681015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46325445175171</t>
+    <t xml:space="preserve">4.05979585647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46325397491455</t>
   </si>
   <si>
     <t xml:space="preserve">4.67759132385254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80682373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67128753662109</t>
+    <t xml:space="preserve">4.80682277679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67128801345825</t>
   </si>
   <si>
     <t xml:space="preserve">4.69650316238403</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">4.74693536758423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79106426239014</t>
+    <t xml:space="preserve">4.79106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">4.95181655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89507961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91714429855347</t>
+    <t xml:space="preserve">4.89508008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91714477539062</t>
   </si>
   <si>
     <t xml:space="preserve">4.98964071273804</t>
@@ -665,46 +665,46 @@
     <t xml:space="preserve">4.95496845245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.939208984375</t>
+    <t xml:space="preserve">4.93920850753784</t>
   </si>
   <si>
     <t xml:space="preserve">5.00224828720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99909734725952</t>
+    <t xml:space="preserve">4.99909687042236</t>
   </si>
   <si>
     <t xml:space="preserve">4.93605661392212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89823246002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88877630233765</t>
+    <t xml:space="preserve">4.89823198318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8887767791748</t>
   </si>
   <si>
     <t xml:space="preserve">4.99279260635376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13778591156006</t>
+    <t xml:space="preserve">5.13778495788574</t>
   </si>
   <si>
     <t xml:space="preserve">5.1693058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14408922195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16300106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92975282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98333740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98018455505371</t>
+    <t xml:space="preserve">5.1440896987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.163001537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92975234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98333692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98018550872803</t>
   </si>
   <si>
     <t xml:space="preserve">4.86356019973755</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.05898523330688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04007339477539</t>
+    <t xml:space="preserve">5.04007387161255</t>
   </si>
   <si>
     <t xml:space="preserve">5.00540113449097</t>
@@ -722,166 +722,166 @@
     <t xml:space="preserve">5.08420085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01170444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08735275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103462219238</t>
+    <t xml:space="preserve">5.01170492172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08735227584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3710355758667</t>
   </si>
   <si>
     <t xml:space="preserve">5.5380916595459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36157846450806</t>
+    <t xml:space="preserve">5.36157894134521</t>
   </si>
   <si>
     <t xml:space="preserve">5.29538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15354585647583</t>
+    <t xml:space="preserve">5.15354633331299</t>
   </si>
   <si>
     <t xml:space="preserve">5.01485681533813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13463306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92344808578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8194317817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96757650375366</t>
+    <t xml:space="preserve">5.13463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92344856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96757745742798</t>
   </si>
   <si>
     <t xml:space="preserve">4.91084051132202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05583333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17560911178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14724159240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11887359619141</t>
+    <t xml:space="preserve">5.05583381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17561006546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14724111557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11887311935425</t>
   </si>
   <si>
     <t xml:space="preserve">5.07159328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02431297302246</t>
+    <t xml:space="preserve">5.02431201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.97388029098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82888793945312</t>
+    <t xml:space="preserve">4.82888746261597</t>
   </si>
   <si>
     <t xml:space="preserve">4.69335126876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72802305221558</t>
+    <t xml:space="preserve">4.72802352905273</t>
   </si>
   <si>
     <t xml:space="preserve">4.7689995765686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94866418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99594497680664</t>
+    <t xml:space="preserve">4.94866514205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99594449996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.17245769500732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21658515930176</t>
+    <t xml:space="preserve">5.21658563613892</t>
   </si>
   <si>
     <t xml:space="preserve">5.2260422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30168962478638</t>
+    <t xml:space="preserve">5.30169057846069</t>
   </si>
   <si>
     <t xml:space="preserve">5.24810600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23549795150757</t>
+    <t xml:space="preserve">5.23549842834473</t>
   </si>
   <si>
     <t xml:space="preserve">5.25125789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26071453094482</t>
+    <t xml:space="preserve">5.26071405410767</t>
   </si>
   <si>
     <t xml:space="preserve">5.32375383377075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3363618850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27962684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33951473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31745052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35212182998657</t>
+    <t xml:space="preserve">5.33636283874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27962636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.339515209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31745100021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35212230682373</t>
   </si>
   <si>
     <t xml:space="preserve">5.32690620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19767332077026</t>
+    <t xml:space="preserve">5.19767379760742</t>
   </si>
   <si>
     <t xml:space="preserve">5.20712995529175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20397758483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23865032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13148164749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85095262527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38364219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46559524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38994741439819</t>
+    <t xml:space="preserve">5.20397806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23864984512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13148260116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85095167160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38364267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46559476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38994646072388</t>
   </si>
   <si>
     <t xml:space="preserve">5.35527420043945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56330728530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57906770706177</t>
+    <t xml:space="preserve">5.56330823898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57906818389893</t>
   </si>
   <si>
     <t xml:space="preserve">5.59798002243042</t>
@@ -890,34 +890,34 @@
     <t xml:space="preserve">5.70830106735229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78710031509399</t>
+    <t xml:space="preserve">5.78710079193115</t>
   </si>
   <si>
     <t xml:space="preserve">5.75242853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7366681098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72090864181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7934045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76188564300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78394937515259</t>
+    <t xml:space="preserve">5.73666858673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72090816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79340410232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76188516616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78394889831543</t>
   </si>
   <si>
     <t xml:space="preserve">5.62319612503052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64210796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68938779830933</t>
+    <t xml:space="preserve">5.6421070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68938827514648</t>
   </si>
   <si>
     <t xml:space="preserve">5.73036479949951</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">5.76818895339966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.739821434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71460437774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62950086593628</t>
+    <t xml:space="preserve">5.73982048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71460390090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62950038909912</t>
   </si>
   <si>
     <t xml:space="preserve">5.45298671722412</t>
@@ -944,31 +944,31 @@
     <t xml:space="preserve">5.34266662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25440979003906</t>
+    <t xml:space="preserve">5.25441026687622</t>
   </si>
   <si>
     <t xml:space="preserve">5.27332210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41516208648682</t>
+    <t xml:space="preserve">5.36473035812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41516304016113</t>
   </si>
   <si>
     <t xml:space="preserve">5.39625072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44983625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37418651580811</t>
+    <t xml:space="preserve">5.44983530044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37418603897095</t>
   </si>
   <si>
     <t xml:space="preserve">5.39309883117676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29223442077637</t>
+    <t xml:space="preserve">5.29223394393921</t>
   </si>
   <si>
     <t xml:space="preserve">5.21028232574463</t>
@@ -980,64 +980,64 @@
     <t xml:space="preserve">5.34581851959229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4813551902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46874713897705</t>
+    <t xml:space="preserve">5.48135471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46874761581421</t>
   </si>
   <si>
     <t xml:space="preserve">5.44668292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54754734039307</t>
+    <t xml:space="preserve">5.54754686355591</t>
   </si>
   <si>
     <t xml:space="preserve">5.5948281288147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52548408508301</t>
+    <t xml:space="preserve">5.52548360824585</t>
   </si>
   <si>
     <t xml:space="preserve">5.56015586853027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59167528152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66101980209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71775579452515</t>
+    <t xml:space="preserve">5.59167623519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66101932525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7177562713623</t>
   </si>
   <si>
     <t xml:space="preserve">5.67362785339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67678022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49081230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50972270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56961154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6074366569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58221912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55700302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5443959236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.679931640625</t>
+    <t xml:space="preserve">5.67677974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5097222328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56961107254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60743618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58221960067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55700349807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54439640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67993211746216</t>
   </si>
   <si>
     <t xml:space="preserve">5.67047643661499</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">5.48450708389282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53493928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52863597869873</t>
+    <t xml:space="preserve">5.53493976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52863454818726</t>
   </si>
   <si>
     <t xml:space="preserve">5.47505140304565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38049125671387</t>
+    <t xml:space="preserve">5.38049077987671</t>
   </si>
   <si>
     <t xml:space="preserve">5.43407487869263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33005857467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50026750564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56645965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50657081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51602745056152</t>
+    <t xml:space="preserve">5.33005809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50026845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56646013259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5065712928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51602792739868</t>
   </si>
   <si>
     <t xml:space="preserve">5.58537149429321</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">5.66732406616211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65471601486206</t>
+    <t xml:space="preserve">5.65471649169922</t>
   </si>
   <si>
     <t xml:space="preserve">5.69254016876221</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">5.72406005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75873231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7114520072937</t>
+    <t xml:space="preserve">5.75873279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71145343780518</t>
   </si>
   <si>
     <t xml:space="preserve">5.7997088432312</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">5.74612426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7744927406311</t>
+    <t xml:space="preserve">5.77449226379395</t>
   </si>
   <si>
     <t xml:space="preserve">5.74927616119385</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">5.78079700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77134037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81862020492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91633367538452</t>
+    <t xml:space="preserve">5.77133989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8186206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91633319854736</t>
   </si>
   <si>
     <t xml:space="preserve">5.97622203826904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93209218978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01404571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07708644866943</t>
+    <t xml:space="preserve">5.93209362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01404523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07708549499512</t>
   </si>
   <si>
     <t xml:space="preserve">6.05187034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03295755386353</t>
+    <t xml:space="preserve">6.03295612335205</t>
   </si>
   <si>
     <t xml:space="preserve">6.10860586166382</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">6.23153495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21577501296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22523069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21892690658569</t>
+    <t xml:space="preserve">6.21577453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2252311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21892595291138</t>
   </si>
   <si>
     <t xml:space="preserve">6.2000150680542</t>
@@ -1169,118 +1169,118 @@
     <t xml:space="preserve">6.23178100585938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13353824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885753631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20558214187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16956090927124</t>
+    <t xml:space="preserve">6.1335391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885801315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20558261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16956186294556</t>
   </si>
   <si>
     <t xml:space="preserve">6.0975170135498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22850513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34966945648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28745126724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33329677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29399871826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1990327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22195625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28090143203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28417539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25470447540283</t>
+    <t xml:space="preserve">6.22850561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34966993331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28745079040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33329629898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29400062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19903326034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2219557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382394790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2809009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28417587280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25470352172852</t>
   </si>
   <si>
     <t xml:space="preserve">6.24815368652344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1237154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1564621925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18593454360962</t>
+    <t xml:space="preserve">6.12371587753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15646123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18593406677246</t>
   </si>
   <si>
     <t xml:space="preserve">6.24160432815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26452779769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26125240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19575881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14663791656494</t>
+    <t xml:space="preserve">6.26452684402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26125335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19575834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1466383934021</t>
   </si>
   <si>
     <t xml:space="preserve">6.27107667922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4184398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39879179000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40206432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39224052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41188955307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49375677108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5199556350708</t>
+    <t xml:space="preserve">6.41843938827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39879035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40206575393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39224100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41188907623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49375820159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51995515823364</t>
   </si>
   <si>
     <t xml:space="preserve">6.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53305435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52978038787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48720788955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43808603286743</t>
+    <t xml:space="preserve">6.53305387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52977991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48720836639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43808698654175</t>
   </si>
   <si>
     <t xml:space="preserve">6.45380592346191</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">6.51406049728394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45642518997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26780223846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36997222900391</t>
+    <t xml:space="preserve">6.45642566680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2678017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36997270584106</t>
   </si>
   <si>
     <t xml:space="preserve">6.32019758224487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36473512649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41581916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4551157951355</t>
+    <t xml:space="preserve">6.36473369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41581869125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511627197266</t>
   </si>
   <si>
     <t xml:space="preserve">6.47214365005493</t>
@@ -1325,97 +1325,97 @@
     <t xml:space="preserve">6.44594717025757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46690464019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47869491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40010166168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46166610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47476434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51013040542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674741744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21016693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31102895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44463682174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46559429168701</t>
+    <t xml:space="preserve">6.4669041633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47869443893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40010118484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46166563034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47476387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51013135910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41974925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21016788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31102848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44463729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46559572219849</t>
   </si>
   <si>
     <t xml:space="preserve">6.45904588699341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39748001098633</t>
+    <t xml:space="preserve">6.39748048782349</t>
   </si>
   <si>
     <t xml:space="preserve">6.42498874664307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45773553848267</t>
+    <t xml:space="preserve">6.45773506164551</t>
   </si>
   <si>
     <t xml:space="preserve">6.40664958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47738409042358</t>
+    <t xml:space="preserve">6.47738456726074</t>
   </si>
   <si>
     <t xml:space="preserve">6.37390327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25732326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21671581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24684429168701</t>
+    <t xml:space="preserve">6.25732278823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21671628952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24684476852417</t>
   </si>
   <si>
     <t xml:space="preserve">6.25339365005493</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27828216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35294485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34508466720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4171290397644</t>
+    <t xml:space="preserve">6.27828121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35294437408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34508657455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41712951660156</t>
   </si>
   <si>
     <t xml:space="preserve">6.39355182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54811763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63457012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66076850891113</t>
+    <t xml:space="preserve">6.54811811447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63457107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66076803207397</t>
   </si>
   <si>
     <t xml:space="preserve">6.79503107070923</t>
@@ -1424,43 +1424,43 @@
     <t xml:space="preserve">6.84415102005005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70661401748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69351673126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67386674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55925178527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69679021835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72953701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46428489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51537036895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56907653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52191972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20754718780518</t>
+    <t xml:space="preserve">6.70661354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67386627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55925226211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69678974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72953653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54942750930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46428537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51537179946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56907558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5219202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20754766464233</t>
   </si>
   <si>
     <t xml:space="preserve">6.01499462127686</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">5.91544246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95343017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81327199935913</t>
+    <t xml:space="preserve">5.95342969894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81327247619629</t>
   </si>
   <si>
     <t xml:space="preserve">5.58011245727539</t>
@@ -1496,46 +1496,46 @@
     <t xml:space="preserve">5.32861423492432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19238615036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35874223709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23823213577271</t>
+    <t xml:space="preserve">5.19238567352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35874176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23823165893555</t>
   </si>
   <si>
     <t xml:space="preserve">5.12689208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37707996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30503606796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40327835083008</t>
+    <t xml:space="preserve">5.37708044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3050365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40327787399292</t>
   </si>
   <si>
     <t xml:space="preserve">5.34826278686523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28276824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26049995422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4425745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38755989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52378749847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33254432678223</t>
+    <t xml:space="preserve">5.28276777267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26050043106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44257497787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38755941390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52378702163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33254384994507</t>
   </si>
   <si>
     <t xml:space="preserve">5.29848766326904</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">5.21465396881104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1884560585022</t>
+    <t xml:space="preserve">5.18845653533936</t>
   </si>
   <si>
     <t xml:space="preserve">5.25133085250854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3220648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39148855209351</t>
+    <t xml:space="preserve">5.32206583023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39148902893066</t>
   </si>
   <si>
     <t xml:space="preserve">5.30634641647339</t>
@@ -1568,67 +1568,67 @@
     <t xml:space="preserve">5.34040355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26835870742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17928695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2015552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27097988128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2893180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33778381347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32468461990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35612201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51330852508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57618284225464</t>
+    <t xml:space="preserve">5.26835918426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17928743362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20155572891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27097940444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28931760787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33778285980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32468509674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35612154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51330804824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57618236541748</t>
   </si>
   <si>
     <t xml:space="preserve">5.62857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73205900192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68097352981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81851100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74646854400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68752336502075</t>
+    <t xml:space="preserve">5.73205852508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68097305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81851148605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74646806716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68752384185791</t>
   </si>
   <si>
     <t xml:space="preserve">5.78052473068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68490314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75956630706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75563764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76742601394653</t>
+    <t xml:space="preserve">5.68490362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75956583023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75563716888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76742553710938</t>
   </si>
   <si>
     <t xml:space="preserve">5.70848083496094</t>
@@ -1640,25 +1640,25 @@
     <t xml:space="preserve">5.44912338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56439399719238</t>
+    <t xml:space="preserve">5.56439352035522</t>
   </si>
   <si>
     <t xml:space="preserve">5.50282955169678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51985836029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61023998260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758958816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43340444564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43864488601685</t>
+    <t xml:space="preserve">5.51985788345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61023950576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49759006500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43340396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43864393234253</t>
   </si>
   <si>
     <t xml:space="preserve">5.42816543579102</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">5.39541864395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41899585723877</t>
+    <t xml:space="preserve">5.41899681091309</t>
   </si>
   <si>
     <t xml:space="preserve">5.25002098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55522489547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73598909378052</t>
+    <t xml:space="preserve">5.55522394180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73598957061768</t>
   </si>
   <si>
     <t xml:space="preserve">5.68621301651001</t>
@@ -1685,64 +1685,64 @@
     <t xml:space="preserve">5.93771123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90627336502075</t>
+    <t xml:space="preserve">5.90627384185791</t>
   </si>
   <si>
     <t xml:space="preserve">5.9364013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89710426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91282272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01368474960327</t>
+    <t xml:space="preserve">5.89710378646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91282320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01368427276611</t>
   </si>
   <si>
     <t xml:space="preserve">6.03333282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09620666503906</t>
+    <t xml:space="preserve">6.09620714187622</t>
   </si>
   <si>
     <t xml:space="preserve">6.00844478607178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00713443756104</t>
+    <t xml:space="preserve">6.00713491439819</t>
   </si>
   <si>
     <t xml:space="preserve">5.96390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07524871826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06477117538452</t>
+    <t xml:space="preserve">6.07524919509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06477069854736</t>
   </si>
   <si>
     <t xml:space="preserve">6.00451612472534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63512706756592</t>
+    <t xml:space="preserve">5.63512802124023</t>
   </si>
   <si>
     <t xml:space="preserve">5.46353244781494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4884204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48056125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3888692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13737106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18059730529785</t>
+    <t xml:space="preserve">5.48842000961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48056077957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38886833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13737058639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18059778213501</t>
   </si>
   <si>
     <t xml:space="preserve">5.07187700271606</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">5.03520011901855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11379337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05484867095947</t>
+    <t xml:space="preserve">5.11379289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05484819412231</t>
   </si>
   <si>
     <t xml:space="preserve">5.00638246536255</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">5.15963888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06663751602173</t>
+    <t xml:space="preserve">5.06663703918457</t>
   </si>
   <si>
     <t xml:space="preserve">5.07842636108398</t>
@@ -1775,73 +1775,73 @@
     <t xml:space="preserve">4.90683126449585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09545516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95791673660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09938335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11248350143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07711601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19500637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13606071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11641263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13868093490601</t>
+    <t xml:space="preserve">5.09545469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95791721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09938430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11248302459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0771164894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19500589370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.136061668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11641311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13868141174316</t>
   </si>
   <si>
     <t xml:space="preserve">5.15308952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14915990829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104562759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15818977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690242767334</t>
+    <t xml:space="preserve">5.14915943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104610443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15818929672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03690195083618</t>
   </si>
   <si>
     <t xml:space="preserve">5.08987808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08012008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11776065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34499979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36730480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39100551605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44258689880371</t>
+    <t xml:space="preserve">5.08011960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.117760181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34500026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36730527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39100503921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44258737564087</t>
   </si>
   <si>
     <t xml:space="preserve">5.44119310379028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47604608535767</t>
+    <t xml:space="preserve">5.47604465484619</t>
   </si>
   <si>
     <t xml:space="preserve">5.37706470489502</t>
@@ -1850,46 +1850,46 @@
     <t xml:space="preserve">5.38821697235107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22650098800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22231864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10242509841919</t>
+    <t xml:space="preserve">5.22650051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22231817245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10242605209351</t>
   </si>
   <si>
     <t xml:space="preserve">5.07733154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24462413787842</t>
+    <t xml:space="preserve">5.24462366104126</t>
   </si>
   <si>
     <t xml:space="preserve">5.26553583145142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31293487548828</t>
+    <t xml:space="preserve">5.31293535232544</t>
   </si>
   <si>
     <t xml:space="preserve">5.23068284988403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27668857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37288188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25577640533447</t>
+    <t xml:space="preserve">5.27668905258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3728814125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25577688217163</t>
   </si>
   <si>
     <t xml:space="preserve">5.12751913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0494499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14146089553833</t>
+    <t xml:space="preserve">5.04944944381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14145994186401</t>
   </si>
   <si>
     <t xml:space="preserve">5.09127235412598</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">5.37985229492188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36312294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33524036407471</t>
+    <t xml:space="preserve">5.36312341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33524131774902</t>
   </si>
   <si>
     <t xml:space="preserve">5.33802890777588</t>
@@ -1916,58 +1916,58 @@
     <t xml:space="preserve">5.40494632720947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34639358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33942317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46210384368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49138021469116</t>
+    <t xml:space="preserve">5.34639406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33942270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46210479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46907520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49138069152832</t>
   </si>
   <si>
     <t xml:space="preserve">5.50671577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48859262466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49277544021606</t>
+    <t xml:space="preserve">5.48859310150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49277448654175</t>
   </si>
   <si>
     <t xml:space="preserve">5.50253391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55969190597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48998689651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44816398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45931577682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29481220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14424800872803</t>
+    <t xml:space="preserve">5.55969142913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48998641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4481635093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45931625366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29481172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14424848556519</t>
   </si>
   <si>
     <t xml:space="preserve">5.11218452453613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39797592163086</t>
+    <t xml:space="preserve">5.28505373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3979754447937</t>
   </si>
   <si>
     <t xml:space="preserve">5.40355205535889</t>
@@ -1979,31 +1979,31 @@
     <t xml:space="preserve">5.52623319625854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62521457672119</t>
+    <t xml:space="preserve">5.62521505355835</t>
   </si>
   <si>
     <t xml:space="preserve">5.59036254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.789719581604</t>
+    <t xml:space="preserve">5.78971910476685</t>
   </si>
   <si>
     <t xml:space="preserve">5.80366039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77717256546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79808330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73953151702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75486612319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82735967636108</t>
+    <t xml:space="preserve">5.77717304229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79808378219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73953199386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75486660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82736015319824</t>
   </si>
   <si>
     <t xml:space="preserve">5.91797637939453</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">6.14939785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02532386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07969284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0894513130188</t>
+    <t xml:space="preserve">6.02532339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07969331741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08945178985596</t>
   </si>
   <si>
     <t xml:space="preserve">6.20376777648926</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">6.10060453414917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03787040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12430477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10339260101318</t>
+    <t xml:space="preserve">6.03786945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12430429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10339212417603</t>
   </si>
   <si>
     <t xml:space="preserve">6.18982744216919</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">6.21631526947021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26510858535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3989429473877</t>
+    <t xml:space="preserve">6.26510953903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39894390106201</t>
   </si>
   <si>
     <t xml:space="preserve">6.35990762710571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24001502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28602027893066</t>
+    <t xml:space="preserve">6.24001598358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28602075576782</t>
   </si>
   <si>
     <t xml:space="preserve">6.23583316802979</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">6.17728090286255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22468090057373</t>
+    <t xml:space="preserve">6.22467994689941</t>
   </si>
   <si>
     <t xml:space="preserve">6.35293817520142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42264270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45610189437866</t>
+    <t xml:space="preserve">6.42264318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4561014175415</t>
   </si>
   <si>
     <t xml:space="preserve">6.5188364982605</t>
@@ -2084,22 +2084,22 @@
     <t xml:space="preserve">6.42543172836304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44076681137085</t>
+    <t xml:space="preserve">6.44076585769653</t>
   </si>
   <si>
     <t xml:space="preserve">6.47840738296509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52162504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46446657180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4853777885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.578782081604</t>
+    <t xml:space="preserve">6.52162408828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46446704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48537731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57878160476685</t>
   </si>
   <si>
     <t xml:space="preserve">6.63175916671753</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">6.6707935333252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69867515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67915821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62199974060059</t>
+    <t xml:space="preserve">6.69867610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67915773391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62199926376343</t>
   </si>
   <si>
     <t xml:space="preserve">6.54392957687378</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">6.52441263198853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56205272674561</t>
+    <t xml:space="preserve">6.56205320358276</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194675445557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58714818954468</t>
+    <t xml:space="preserve">6.5871467590332</t>
   </si>
   <si>
     <t xml:space="preserve">6.62478828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41706657409668</t>
+    <t xml:space="preserve">6.41706705093384</t>
   </si>
   <si>
     <t xml:space="preserve">6.26789665222168</t>
@@ -2147,31 +2147,31 @@
     <t xml:space="preserve">6.20237398147583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06435775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22049713134766</t>
+    <t xml:space="preserve">6.06435823440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22049808502197</t>
   </si>
   <si>
     <t xml:space="preserve">6.18146276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16612672805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06575155258179</t>
+    <t xml:space="preserve">6.16612768173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06575202941895</t>
   </si>
   <si>
     <t xml:space="preserve">5.99465274810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01556444168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95980072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91937112808228</t>
+    <t xml:space="preserve">6.01556491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95980024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91937065124512</t>
   </si>
   <si>
     <t xml:space="preserve">5.84269523620605</t>
@@ -2180,10 +2180,10 @@
     <t xml:space="preserve">5.83433055877686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76602029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7325611114502</t>
+    <t xml:space="preserve">5.76601982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73256063461304</t>
   </si>
   <si>
     <t xml:space="preserve">5.88173007965088</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">5.84966564178467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87894201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96816539764404</t>
+    <t xml:space="preserve">5.87894248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96816444396973</t>
   </si>
   <si>
     <t xml:space="preserve">5.9667706489563</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">5.93888902664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97374105453491</t>
+    <t xml:space="preserve">5.97374153137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.94307041168213</t>
@@ -2213,22 +2213,22 @@
     <t xml:space="preserve">5.9416766166687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07132911682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16333913803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14382171630859</t>
+    <t xml:space="preserve">6.07132863998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16334009170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14382219314575</t>
   </si>
   <si>
     <t xml:space="preserve">6.19122171401978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17031049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29577875137329</t>
+    <t xml:space="preserve">6.17031002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29577922821045</t>
   </si>
   <si>
     <t xml:space="preserve">6.3376030921936</t>
@@ -2243,115 +2243,115 @@
     <t xml:space="preserve">6.30972051620483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47422552108765</t>
+    <t xml:space="preserve">6.47422504425049</t>
   </si>
   <si>
     <t xml:space="preserve">6.60248279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57041835784912</t>
+    <t xml:space="preserve">6.5704174041748</t>
   </si>
   <si>
     <t xml:space="preserve">6.51186561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49095487594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55229473114014</t>
+    <t xml:space="preserve">6.49095439910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55229425430298</t>
   </si>
   <si>
     <t xml:space="preserve">6.54114198684692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54671812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4979248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56762981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53277730941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950571060181</t>
+    <t xml:space="preserve">6.54671859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56763029098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53277683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950618743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.41288423538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44355487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5146541595459</t>
+    <t xml:space="preserve">6.44355440139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51465368270874</t>
   </si>
   <si>
     <t xml:space="preserve">6.4895601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50350141525269</t>
+    <t xml:space="preserve">6.50350093841553</t>
   </si>
   <si>
     <t xml:space="preserve">6.33481502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31111478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32087326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15915727615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10478734970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03647613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08666324615479</t>
+    <t xml:space="preserve">6.31111431121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32087373733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15915679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10478782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03647565841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08666372299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.9249472618103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91379547119141</t>
+    <t xml:space="preserve">5.91379451751709</t>
   </si>
   <si>
     <t xml:space="preserve">5.94446516036987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80644845962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93052434921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97653007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06714630126953</t>
+    <t xml:space="preserve">5.80644941329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9305248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97652959823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06714677810669</t>
   </si>
   <si>
     <t xml:space="preserve">6.11315202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04344654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11872816085815</t>
+    <t xml:space="preserve">6.04344606399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.118727684021</t>
   </si>
   <si>
     <t xml:space="preserve">6.13963937759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19261598587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28044366836548</t>
+    <t xml:space="preserve">6.1926155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28044509887695</t>
   </si>
   <si>
     <t xml:space="preserve">6.3571195602417</t>
@@ -2360,103 +2360,103 @@
     <t xml:space="preserve">6.58296585083008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59830045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68055248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6303653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66382360458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72655773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66242933273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63454627990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76141023635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100879669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803266525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90779209136963</t>
+    <t xml:space="preserve">6.59829998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68055200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63036489486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66382312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72655868530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66242790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63454675674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7614107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100975036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803218841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90779161453247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94682598114014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04371690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95379781723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98446846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95658540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76419878005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84645128250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81578016281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83390331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79347610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80462837219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03326225280762</t>
+    <t xml:space="preserve">7.04371643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95379734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98446750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95658493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76419925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8464503288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8157811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83390426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79347515106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80462741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0332612991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.19009780883789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481641769409</t>
+    <t xml:space="preserve">7.27025938034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481594085693</t>
   </si>
   <si>
     <t xml:space="preserve">7.40269947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38178777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36087703704834</t>
+    <t xml:space="preserve">7.38178730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36087560653687</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058109283447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50377225875854</t>
+    <t xml:space="preserve">7.50377130508423</t>
   </si>
   <si>
     <t xml:space="preserve">7.55953598022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256605148315</t>
+    <t xml:space="preserve">7.552565574646</t>
   </si>
   <si>
     <t xml:space="preserve">7.58044767379761</t>
@@ -2465,49 +2465,49 @@
     <t xml:space="preserve">7.44103717803955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42361068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48286008834839</t>
+    <t xml:space="preserve">7.42361116409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48286104202271</t>
   </si>
   <si>
     <t xml:space="preserve">7.6431827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59438943862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51422739028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27374362945557</t>
+    <t xml:space="preserve">7.59438896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51422691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27374505996704</t>
   </si>
   <si>
     <t xml:space="preserve">7.42012548446655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35390567779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5185751914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48940420150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752691268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5258674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669599533081</t>
+    <t xml:space="preserve">7.35390615463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51857566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48940515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752643585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52586698532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669742584229</t>
   </si>
   <si>
     <t xml:space="preserve">7.47481918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52951335906982</t>
+    <t xml:space="preserve">7.52951240539551</t>
   </si>
   <si>
     <t xml:space="preserve">7.40189409255981</t>
@@ -2516,46 +2516,46 @@
     <t xml:space="preserve">7.33261632919312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925066947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35449361801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3253231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34719944000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22687435150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37272357940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38366222381592</t>
+    <t xml:space="preserve">7.29250621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34720039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22687387466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3727240562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38366317749023</t>
   </si>
   <si>
     <t xml:space="preserve">7.24437618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31438398361206</t>
+    <t xml:space="preserve">7.31438493728638</t>
   </si>
   <si>
     <t xml:space="preserve">7.28229761123657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3581395149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2852144241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21958112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15686702728271</t>
+    <t xml:space="preserve">7.35813856124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28521394729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21958160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15686559677124</t>
   </si>
   <si>
     <t xml:space="preserve">7.22979116439819</t>
@@ -2564,28 +2564,28 @@
     <t xml:space="preserve">7.16415882110596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18457746505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25021028518677</t>
+    <t xml:space="preserve">7.18457794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25021076202393</t>
   </si>
   <si>
     <t xml:space="preserve">7.261878490448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2181224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18020248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08539867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15832424163818</t>
+    <t xml:space="preserve">7.21812343597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874383926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1802020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08540010452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15832471847534</t>
   </si>
   <si>
     <t xml:space="preserve">7.11019372940063</t>
@@ -2594,58 +2594,58 @@
     <t xml:space="preserve">7.05768775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07810688018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99643182754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93809127807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97309494018555</t>
+    <t xml:space="preserve">7.07810735702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93809080123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97309446334839</t>
   </si>
   <si>
     <t xml:space="preserve">6.77328014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98622131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93371486663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57200717926025</t>
+    <t xml:space="preserve">6.98622179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93371534347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75286102294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57200765609741</t>
   </si>
   <si>
     <t xml:space="preserve">6.71931552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8053674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98038673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86954116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00372362136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04164552688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0606050491333</t>
+    <t xml:space="preserve">6.80536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98038721084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86954164505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00372409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04164409637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06060552597046</t>
   </si>
   <si>
     <t xml:space="preserve">7.06206369400024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00518178939819</t>
+    <t xml:space="preserve">7.00518131256104</t>
   </si>
   <si>
     <t xml:space="preserve">7.03289318084717</t>
@@ -2654,34 +2654,34 @@
     <t xml:space="preserve">6.99351453781128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86370801925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45241022109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42178153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38677787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23363494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97256278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76253938674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71003341674805</t>
+    <t xml:space="preserve">6.86370706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45240926742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42178106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38677835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23363447189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97256231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76253890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71003293991089</t>
   </si>
   <si>
     <t xml:space="preserve">5.63564920425415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39937114715576</t>
+    <t xml:space="preserve">5.39937162399292</t>
   </si>
   <si>
     <t xml:space="preserve">5.28415012359619</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">4.52281284332275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21215200424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33174896240234</t>
+    <t xml:space="preserve">4.21215152740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33174848556519</t>
   </si>
   <si>
     <t xml:space="preserve">3.5222806930542</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">3.77605986595154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33850932121277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25537490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06649947166443</t>
+    <t xml:space="preserve">3.33850979804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25537514686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06649875640869</t>
   </si>
   <si>
     <t xml:space="preserve">3.0424337387085</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">3.61854195594788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90440797805786</t>
+    <t xml:space="preserve">3.90440821647644</t>
   </si>
   <si>
     <t xml:space="preserve">4.01087856292725</t>
@@ -2732,91 +2732,91 @@
     <t xml:space="preserve">3.76439237594604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62802219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66667175292969</t>
+    <t xml:space="preserve">3.62802195549011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66667199134827</t>
   </si>
   <si>
     <t xml:space="preserve">3.64917016029358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77460169792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70605158805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97149848937988</t>
+    <t xml:space="preserve">3.77460193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70605182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97149991989136</t>
   </si>
   <si>
     <t xml:space="preserve">4.05171680450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05900907516479</t>
+    <t xml:space="preserve">4.05900955200195</t>
   </si>
   <si>
     <t xml:space="preserve">4.04150724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87232112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57989144325256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64771175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69292569160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56239008903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51571750640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73959755897522</t>
+    <t xml:space="preserve">3.87232136726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57989120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64771151542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69292497634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56238985061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51571798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73959732055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.82419037818909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95545530319214</t>
+    <t xml:space="preserve">3.95545554161072</t>
   </si>
   <si>
     <t xml:space="preserve">4.02254676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85627770423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79939651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76585054397583</t>
+    <t xml:space="preserve">3.85627746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76585030555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.75855755805969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74834799766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78918671607971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85336112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68271636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56311917304993</t>
+    <t xml:space="preserve">3.74834871292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78918647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607594490051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85336065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68271613121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56311893463135</t>
   </si>
   <si>
     <t xml:space="preserve">3.80960536003113</t>
@@ -2825,16 +2825,16 @@
     <t xml:space="preserve">3.74980688095093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69730138778687</t>
+    <t xml:space="preserve">3.69730067253113</t>
   </si>
   <si>
     <t xml:space="preserve">3.77168464660645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7848105430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921035766602</t>
+    <t xml:space="preserve">3.78481101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921107292175</t>
   </si>
   <si>
     <t xml:space="preserve">4.16256284713745</t>
@@ -2843,28 +2843,28 @@
     <t xml:space="preserve">4.31862258911133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25590658187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60011386871338</t>
+    <t xml:space="preserve">4.25590753555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60011291503906</t>
   </si>
   <si>
     <t xml:space="preserve">4.69929122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95452928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95307016372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18351364135742</t>
+    <t xml:space="preserve">4.95452976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95307064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18351316452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.34540700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17330455780029</t>
+    <t xml:space="preserve">5.17330408096313</t>
   </si>
   <si>
     <t xml:space="preserve">5.07996034622192</t>
@@ -2873,40 +2873,40 @@
     <t xml:space="preserve">4.86410188674927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9647388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03766393661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16455268859863</t>
+    <t xml:space="preserve">4.96473836898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03766345977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16455364227295</t>
   </si>
   <si>
     <t xml:space="preserve">5.13975858688354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23164367675781</t>
+    <t xml:space="preserve">5.23164415359497</t>
   </si>
   <si>
     <t xml:space="preserve">5.12079811096191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97348976135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99682569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71095895767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75033855438232</t>
+    <t xml:space="preserve">4.97348880767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.996826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71095943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75033903121948</t>
   </si>
   <si>
     <t xml:space="preserve">4.55927515029907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76200675964355</t>
+    <t xml:space="preserve">4.76200723648071</t>
   </si>
   <si>
     <t xml:space="preserve">4.65991163253784</t>
@@ -2915,37 +2915,37 @@
     <t xml:space="preserve">4.71533489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91952466964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90348148345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92535924911499</t>
+    <t xml:space="preserve">4.91952514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90348196029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92535877227783</t>
   </si>
   <si>
     <t xml:space="preserve">4.93119335174561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88014554977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79701137542725</t>
+    <t xml:space="preserve">4.88014507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79701089859009</t>
   </si>
   <si>
     <t xml:space="preserve">4.92973470687866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05079030990601</t>
+    <t xml:space="preserve">5.05078983306885</t>
   </si>
   <si>
     <t xml:space="preserve">5.13830041885376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14559268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16601133346558</t>
+    <t xml:space="preserve">5.14559316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16601181030273</t>
   </si>
   <si>
     <t xml:space="preserve">5.13246631622314</t>
@@ -2954,19 +2954,19 @@
     <t xml:space="preserve">5.25206327438354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25498008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31623697280884</t>
+    <t xml:space="preserve">5.25498056411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.316237449646</t>
   </si>
   <si>
     <t xml:space="preserve">5.22435188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16309499740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12663269042969</t>
+    <t xml:space="preserve">5.16309452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12663221359253</t>
   </si>
   <si>
     <t xml:space="preserve">5.07850170135498</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">5.05954122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9224419593811</t>
+    <t xml:space="preserve">4.92244148254395</t>
   </si>
   <si>
     <t xml:space="preserve">4.94286060333252</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">4.81305408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94723606109619</t>
+    <t xml:space="preserve">4.94723653793335</t>
   </si>
   <si>
     <t xml:space="preserve">4.91369104385376</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">4.97786521911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27248287200928</t>
+    <t xml:space="preserve">5.27248191833496</t>
   </si>
   <si>
     <t xml:space="preserve">5.28706741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29436016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20247364044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11496353149414</t>
+    <t xml:space="preserve">5.29435968399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20247411727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1149640083313</t>
   </si>
   <si>
     <t xml:space="preserve">5.24622964859009</t>
@@ -3026,52 +3026,52 @@
     <t xml:space="preserve">5.27685737609863</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44458532333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47813081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42416667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31040382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33519792556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32061243057251</t>
+    <t xml:space="preserve">5.4445858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47813129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42416620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31040334701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33519744873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32061338424683</t>
   </si>
   <si>
     <t xml:space="preserve">5.22726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21414232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08141803741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17768001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39207983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28269147872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29873561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18643045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08725261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8991060256958</t>
+    <t xml:space="preserve">5.21414184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08141851425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17767906188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39207935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29873466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18643140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08725309371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89910554885864</t>
   </si>
   <si>
     <t xml:space="preserve">4.89327192306519</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">4.87722873687744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76054811477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95161151885986</t>
+    <t xml:space="preserve">4.76054859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95161199569702</t>
   </si>
   <si>
     <t xml:space="preserve">4.8757700920105</t>
@@ -3092,22 +3092,22 @@
     <t xml:space="preserve">4.88452100753784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84368276596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92390012741089</t>
+    <t xml:space="preserve">4.84368324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92390060424805</t>
   </si>
   <si>
     <t xml:space="preserve">5.08871126174927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20976686477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08579349517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28560876846313</t>
+    <t xml:space="preserve">5.20976638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28560924530029</t>
   </si>
   <si>
     <t xml:space="preserve">5.23310279846191</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">5.203932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01141119003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02016162872314</t>
+    <t xml:space="preserve">5.0114107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02016115188599</t>
   </si>
   <si>
     <t xml:space="preserve">4.82180547714233</t>
@@ -3131,55 +3131,55 @@
     <t xml:space="preserve">4.79992771148682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84951734542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7401294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74596309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78971815109253</t>
+    <t xml:space="preserve">4.84951686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74012899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74596357345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78971767425537</t>
   </si>
   <si>
     <t xml:space="preserve">4.76638221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64095115661621</t>
+    <t xml:space="preserve">4.64095163345337</t>
   </si>
   <si>
     <t xml:space="preserve">4.41050815582275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46884822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43967819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59427928924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85680961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3089451789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19664001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20539140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51605224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5962700843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51459360122681</t>
+    <t xml:space="preserve">4.46884775161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43967771530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59427881240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85680866241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30894470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19664096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20539093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51605272293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59626960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51459407806396</t>
   </si>
   <si>
     <t xml:space="preserve">5.58460140228271</t>
@@ -3188,19 +3188,19 @@
     <t xml:space="preserve">5.4985499382019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72899341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75232887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70419836044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63710784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4504189491272</t>
+    <t xml:space="preserve">5.72899293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75232934951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70419883728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63710737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45041942596436</t>
   </si>
   <si>
     <t xml:space="preserve">5.52917814254761</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">5.46500492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54230546951294</t>
+    <t xml:space="preserve">5.54230499267578</t>
   </si>
   <si>
     <t xml:space="preserve">5.60210371017456</t>
@@ -3221,46 +3221,46 @@
     <t xml:space="preserve">5.4897985458374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49709224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47521448135376</t>
+    <t xml:space="preserve">5.49709129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4752140045166</t>
   </si>
   <si>
     <t xml:space="preserve">5.34978294372559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36145114898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53792905807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49271631240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42854166030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39062118530273</t>
+    <t xml:space="preserve">5.36145067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53792953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49271583557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.428542137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39062166213989</t>
   </si>
   <si>
     <t xml:space="preserve">5.3789529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52042770385742</t>
+    <t xml:space="preserve">5.52042722702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.52480316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40228843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42270755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62835693359375</t>
+    <t xml:space="preserve">5.40228891372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42270851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62835597991943</t>
   </si>
   <si>
     <t xml:space="preserve">5.61231327056885</t>
@@ -3269,37 +3269,37 @@
     <t xml:space="preserve">5.50438356399536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46208715438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51021862030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46938037872314</t>
+    <t xml:space="preserve">5.46208667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51021814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46937990188599</t>
   </si>
   <si>
     <t xml:space="preserve">5.44750213623047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38187026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47083854675293</t>
+    <t xml:space="preserve">5.38186979293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47083806991577</t>
   </si>
   <si>
     <t xml:space="preserve">5.40083026885986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40520572662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44896078109741</t>
+    <t xml:space="preserve">5.40520620346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44896173477173</t>
   </si>
   <si>
     <t xml:space="preserve">5.35707569122314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39499616622925</t>
+    <t xml:space="preserve">5.39499568939209</t>
   </si>
   <si>
     <t xml:space="preserve">5.370201587677</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">5.51167678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7304515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8996376991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97985506057739</t>
+    <t xml:space="preserve">5.73045110702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89963865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97985458374023</t>
   </si>
   <si>
     <t xml:space="preserve">6.17383575439453</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">6.41740608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50637483596802</t>
+    <t xml:space="preserve">6.50637435913086</t>
   </si>
   <si>
     <t xml:space="preserve">6.48012161254883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59242630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53700304031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57929944992065</t>
+    <t xml:space="preserve">6.59242582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53700351715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57930040359497</t>
   </si>
   <si>
     <t xml:space="preserve">6.54429578781128</t>
@@ -3347,34 +3347,34 @@
     <t xml:space="preserve">6.62159585952759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61430311203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58221626281738</t>
+    <t xml:space="preserve">6.61430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58221673965454</t>
   </si>
   <si>
     <t xml:space="preserve">6.53408622741699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3955283164978</t>
+    <t xml:space="preserve">6.39552783966064</t>
   </si>
   <si>
     <t xml:space="preserve">6.28468227386475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5019998550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43490791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52679347991943</t>
+    <t xml:space="preserve">6.50199937820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43490839004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52679300308228</t>
   </si>
   <si>
     <t xml:space="preserve">6.61138677597046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7251501083374</t>
+    <t xml:space="preserve">6.72514963150024</t>
   </si>
   <si>
     <t xml:space="preserve">6.73535919189453</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">6.77473878860474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8505802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86516523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9016284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01976680755615</t>
+    <t xml:space="preserve">6.85058116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86516618728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90162897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01976728439331</t>
   </si>
   <si>
     <t xml:space="preserve">7.09415054321289</t>
@@ -3401,76 +3401,76 @@
     <t xml:space="preserve">7.09706830978394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87975120544434</t>
+    <t xml:space="preserve">6.87975072860718</t>
   </si>
   <si>
     <t xml:space="preserve">6.84037160873413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77911281585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90016937255859</t>
+    <t xml:space="preserve">6.77911376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90016984939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.90600395202637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92058897018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93954849243164</t>
+    <t xml:space="preserve">6.92058849334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9395489692688</t>
   </si>
   <si>
     <t xml:space="preserve">7.0358099937439</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89579439163208</t>
+    <t xml:space="preserve">6.89579486846924</t>
   </si>
   <si>
     <t xml:space="preserve">6.84912204742432</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86079120635986</t>
+    <t xml:space="preserve">6.86079025268555</t>
   </si>
   <si>
     <t xml:space="preserve">6.77182197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80682468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81849431991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80974245071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78640699386597</t>
+    <t xml:space="preserve">6.80682516098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81849384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80974292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78640604019165</t>
   </si>
   <si>
     <t xml:space="preserve">6.8520393371582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84766387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70910549163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64201498031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64639043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83599615097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8082857131958</t>
+    <t xml:space="preserve">6.84766435623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7091064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.642014503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64639091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8359956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80828428268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.82724571228027</t>
@@ -3482,28 +3482,28 @@
     <t xml:space="preserve">6.92788124084473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78057384490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9089207649231</t>
+    <t xml:space="preserve">6.78057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90891981124878</t>
   </si>
   <si>
     <t xml:space="preserve">6.94684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04018640518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05477094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0139331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0839409828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13352918624878</t>
+    <t xml:space="preserve">7.04018592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01393270492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08394050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1335301399231</t>
   </si>
   <si>
     <t xml:space="preserve">7.19770431518555</t>
@@ -3515,64 +3515,64 @@
     <t xml:space="preserve">7.06643867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915515899658</t>
+    <t xml:space="preserve">7.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102464675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915468215942</t>
   </si>
   <si>
     <t xml:space="preserve">7.11748647689819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14811515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21228933334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27062845230103</t>
+    <t xml:space="preserve">7.14811611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27062940597534</t>
   </si>
   <si>
     <t xml:space="preserve">7.30344533920288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2997989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25604438781738</t>
+    <t xml:space="preserve">7.29979991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25604391098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.2677116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20791387557983</t>
+    <t xml:space="preserve">7.20791292190552</t>
   </si>
   <si>
     <t xml:space="preserve">7.26333665847778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25458526611328</t>
+    <t xml:space="preserve">7.2545862197876</t>
   </si>
   <si>
     <t xml:space="preserve">7.23270893096924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23562479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17582654953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22249889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28083848953247</t>
+    <t xml:space="preserve">7.23562526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17582702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22249937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28083896636963</t>
   </si>
   <si>
     <t xml:space="preserve">7.27500486373901</t>
@@ -3581,22 +3581,22 @@
     <t xml:space="preserve">7.20062065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18311834335327</t>
+    <t xml:space="preserve">7.18311977386475</t>
   </si>
   <si>
     <t xml:space="preserve">7.19332885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1874942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36178541183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14082193374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.149573802948</t>
+    <t xml:space="preserve">7.18749523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36178588867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1408224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14957332611084</t>
   </si>
   <si>
     <t xml:space="preserve">6.92350625991821</t>
@@ -3605,46 +3605,46 @@
     <t xml:space="preserve">7.11165237426758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18895292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20499706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14519786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09560823440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86808300018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95559358596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23416709899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31073713302612</t>
+    <t xml:space="preserve">7.18895244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20499658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14519882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09560918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86808252334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95559310913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23416662216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31073760986328</t>
   </si>
   <si>
     <t xml:space="preserve">7.28667259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28813123703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24145936965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937252044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13207197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21083068847656</t>
+    <t xml:space="preserve">7.28813171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24145984649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13207101821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21082973480225</t>
   </si>
   <si>
     <t xml:space="preserve">7.28375577926636</t>
@@ -3653,64 +3653,64 @@
     <t xml:space="preserve">7.29615354537964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19041061401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27792167663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27354574203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17728567123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1714506149292</t>
+    <t xml:space="preserve">7.1904125213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2779221534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27354621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17145013809204</t>
   </si>
   <si>
     <t xml:space="preserve">7.0460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09852647781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13644695281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25166893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27938079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456918716431</t>
+    <t xml:space="preserve">7.09852600097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13644742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25166845321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.279381275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456823348999</t>
   </si>
   <si>
     <t xml:space="preserve">7.24875116348267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36543273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47846651077271</t>
+    <t xml:space="preserve">7.36543226242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47846603393555</t>
   </si>
   <si>
     <t xml:space="preserve">7.33626174926758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53680610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61337614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68630170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58785200119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734951019287</t>
+    <t xml:space="preserve">7.53680562973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61337757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68630218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58785390853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734903335571</t>
   </si>
   <si>
     <t xml:space="preserve">7.50398921966553</t>
@@ -3719,109 +3719,109 @@
     <t xml:space="preserve">7.45294189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21520614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38001680374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41283321380615</t>
+    <t xml:space="preserve">7.21520662307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38001728057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41283178329468</t>
   </si>
   <si>
     <t xml:space="preserve">7.43106460571289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53315830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58056211471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6060848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55868339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52221965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64254665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67171669006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77016544342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76651954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88684606552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8759069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8139214515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81756734848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89778614044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955379486084</t>
+    <t xml:space="preserve">7.53315925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5805606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60608530044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55868291854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52222013473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64254713058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67171716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77016592025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76652050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88684558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87590837478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81392192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81756830215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89778518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507745742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955331802368</t>
   </si>
   <si>
     <t xml:space="preserve">7.79204320907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74828863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088768005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90313148498535</t>
+    <t xml:space="preserve">7.74828815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90313243865967</t>
   </si>
   <si>
     <t xml:space="preserve">7.7226676940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72111177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352506637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56398248672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59976530075073</t>
+    <t xml:space="preserve">7.72111225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45352458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56398296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59976434707642</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6386570930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776756286621</t>
+    <t xml:space="preserve">7.63865756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776803970337</t>
   </si>
   <si>
     <t xml:space="preserve">7.79034185409546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94591426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86034917831421</t>
+    <t xml:space="preserve">7.94591617584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86034965515137</t>
   </si>
   <si>
     <t xml:space="preserve">7.82534599304199</t>
@@ -3836,34 +3836,34 @@
     <t xml:space="preserve">7.76311635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76156044006348</t>
+    <t xml:space="preserve">7.76155996322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.84868192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80590009689331</t>
+    <t xml:space="preserve">7.80589914321899</t>
   </si>
   <si>
     <t xml:space="preserve">7.5219783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6495475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68999719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81367778778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86423826217651</t>
+    <t xml:space="preserve">7.64954710006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68999576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81367683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86423921585083</t>
   </si>
   <si>
     <t xml:space="preserve">7.92646884918213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08593273162842</t>
+    <t xml:space="preserve">8.0859317779541</t>
   </si>
   <si>
     <t xml:space="preserve">8.10148906707764</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">8.08204174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07815265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07037448883057</t>
+    <t xml:space="preserve">8.07815361022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07037353515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.13260364532471</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">8.09759998321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03536891937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092716217041</t>
+    <t xml:space="preserve">8.03536987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092811584473</t>
   </si>
   <si>
     <t xml:space="preserve">8.02370071411133</t>
@@ -3914,37 +3914,37 @@
     <t xml:space="preserve">8.10926723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79811954498291</t>
+    <t xml:space="preserve">7.79812049865723</t>
   </si>
   <si>
     <t xml:space="preserve">8.05870628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22983741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20650005340576</t>
+    <t xml:space="preserve">8.22983646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20650100708008</t>
   </si>
   <si>
     <t xml:space="preserve">8.14427185058594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90702199935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07426261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88368606567383</t>
+    <t xml:space="preserve">7.90702104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88368511199951</t>
   </si>
   <si>
     <t xml:space="preserve">7.9381365776062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77556324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67288398742676</t>
+    <t xml:space="preserve">7.77556276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67288494110107</t>
   </si>
   <si>
     <t xml:space="preserve">7.67755126953125</t>
@@ -3953,25 +3953,25 @@
     <t xml:space="preserve">7.26994848251343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29172945022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25439119338989</t>
+    <t xml:space="preserve">7.29172849655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25439167022705</t>
   </si>
   <si>
     <t xml:space="preserve">6.68654823303223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73477602005005</t>
+    <t xml:space="preserve">6.73477554321289</t>
   </si>
   <si>
     <t xml:space="preserve">6.68499231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12337207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95379734039307</t>
+    <t xml:space="preserve">6.12337255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95379686355591</t>
   </si>
   <si>
     <t xml:space="preserve">6.08603429794312</t>
@@ -3980,19 +3980,19 @@
     <t xml:space="preserve">6.63520860671997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31939458847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35050868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61187219619751</t>
+    <t xml:space="preserve">6.3193941116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35050916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61187267303467</t>
   </si>
   <si>
     <t xml:space="preserve">6.66165637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10970830917358</t>
+    <t xml:space="preserve">7.10970783233643</t>
   </si>
   <si>
     <t xml:space="preserve">7.06925916671753</t>
@@ -4001,34 +4001,34 @@
     <t xml:space="preserve">7.2263879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06770372390747</t>
+    <t xml:space="preserve">7.06770324707031</t>
   </si>
   <si>
     <t xml:space="preserve">7.12993192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02103090286255</t>
+    <t xml:space="preserve">7.02103137969971</t>
   </si>
   <si>
     <t xml:space="preserve">7.05059003829956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22949981689453</t>
+    <t xml:space="preserve">7.22949886322021</t>
   </si>
   <si>
     <t xml:space="preserve">7.10659599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17193698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30417490005493</t>
+    <t xml:space="preserve">7.17193794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30417537689209</t>
   </si>
   <si>
     <t xml:space="preserve">7.11904239654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97902679443359</t>
+    <t xml:space="preserve">6.97902584075928</t>
   </si>
   <si>
     <t xml:space="preserve">6.89190483093262</t>
@@ -4049,70 +4049,70 @@
     <t xml:space="preserve">7.19527339935303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18438339233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.374183177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4488582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17971611022949</t>
+    <t xml:space="preserve">7.18438291549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44885778427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17971563339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1641583442688</t>
   </si>
   <si>
     <t xml:space="preserve">7.38196134567261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38040637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74755907058716</t>
+    <t xml:space="preserve">7.38040590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686147689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74755954742432</t>
   </si>
   <si>
     <t xml:space="preserve">7.50486421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48308420181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60598659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54842615127563</t>
+    <t xml:space="preserve">7.48308324813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60598754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54842567443848</t>
   </si>
   <si>
     <t xml:space="preserve">7.71955633163452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70088672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71022081375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52353286743164</t>
+    <t xml:space="preserve">7.71022129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52353429794312</t>
   </si>
   <si>
     <t xml:space="preserve">7.44574594497681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38973999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43485593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26217126846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34151220321655</t>
+    <t xml:space="preserve">7.38973951339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43485546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26217079162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34151172637939</t>
   </si>
   <si>
     <t xml:space="preserve">7.46752738952637</t>
@@ -4127,67 +4127,67 @@
     <t xml:space="preserve">7.43174409866333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32906675338745</t>
+    <t xml:space="preserve">7.32906579971313</t>
   </si>
   <si>
     <t xml:space="preserve">7.42085456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53442335128784</t>
+    <t xml:space="preserve">7.534423828125</t>
   </si>
   <si>
     <t xml:space="preserve">7.49864149093628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68533039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50797653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01325225830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90435075759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96813678741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95102262496948</t>
+    <t xml:space="preserve">7.68532943725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50797605514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01325178146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90435123443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96813631057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95102310180664</t>
   </si>
   <si>
     <t xml:space="preserve">6.63054180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59631490707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68188095092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74411010742188</t>
+    <t xml:space="preserve">6.59631538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68188142776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74410963058472</t>
   </si>
   <si>
     <t xml:space="preserve">6.71921825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5683126449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71144008636475</t>
+    <t xml:space="preserve">6.56831216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71143960952759</t>
   </si>
   <si>
     <t xml:space="preserve">6.56675672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64765405654907</t>
+    <t xml:space="preserve">6.64765453338623</t>
   </si>
   <si>
     <t xml:space="preserve">6.60253810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42362928390503</t>
+    <t xml:space="preserve">6.42362880706787</t>
   </si>
   <si>
     <t xml:space="preserve">6.41896152496338</t>
@@ -4199,91 +4199,91 @@
     <t xml:space="preserve">6.2322735786438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32406187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45785522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55586624145508</t>
+    <t xml:space="preserve">6.32406234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45785474777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55586671829224</t>
   </si>
   <si>
     <t xml:space="preserve">6.4905252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41273927688599</t>
+    <t xml:space="preserve">6.41273880004883</t>
   </si>
   <si>
     <t xml:space="preserve">6.3582878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05958700180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0549201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20115852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33339595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26027727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2213830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24783039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17937898635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24005222320557</t>
+    <t xml:space="preserve">6.05958652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05491971969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20115804672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33339643478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26027679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22138357162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24783086776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17937850952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24005317687988</t>
   </si>
   <si>
     <t xml:space="preserve">6.35673236846924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50297117233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54653215408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55119848251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59787178039551</t>
+    <t xml:space="preserve">6.50297069549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54653167724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55119895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59787130355835</t>
   </si>
   <si>
     <t xml:space="preserve">6.64921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70210552215576</t>
+    <t xml:space="preserve">6.7021050453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.65232181549072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64298677444458</t>
+    <t xml:space="preserve">6.64298725128174</t>
   </si>
   <si>
     <t xml:space="preserve">6.66010093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72544097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77055788040161</t>
+    <t xml:space="preserve">6.72544145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77055883407593</t>
   </si>
   <si>
     <t xml:space="preserve">6.77833652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72233009338379</t>
+    <t xml:space="preserve">6.72233057022095</t>
   </si>
   <si>
     <t xml:space="preserve">6.69588232040405</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">6.32250642776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29450273513794</t>
+    <t xml:space="preserve">6.2945032119751</t>
   </si>
   <si>
     <t xml:space="preserve">6.25872039794922</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">6.15137529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07825565338135</t>
+    <t xml:space="preserve">6.07825613021851</t>
   </si>
   <si>
     <t xml:space="preserve">6.31006050109863</t>
@@ -4325,34 +4325,34 @@
     <t xml:space="preserve">6.21204900741577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19493579864502</t>
+    <t xml:space="preserve">6.19493675231934</t>
   </si>
   <si>
     <t xml:space="preserve">6.22916221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28672361373901</t>
+    <t xml:space="preserve">6.28672409057617</t>
   </si>
   <si>
     <t xml:space="preserve">6.44229698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5807580947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58698129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65387773513794</t>
+    <t xml:space="preserve">6.58075857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65387725830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.63365316390991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57764673233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61031723022461</t>
+    <t xml:space="preserve">6.57764720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61031675338745</t>
   </si>
   <si>
     <t xml:space="preserve">6.37540102005005</t>
@@ -4361,10 +4361,10 @@
     <t xml:space="preserve">6.48274660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44074153900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20893669128418</t>
+    <t xml:space="preserve">6.44074201583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20893716812134</t>
   </si>
   <si>
     <t xml:space="preserve">6.09381341934204</t>
@@ -4373,52 +4373,52 @@
     <t xml:space="preserve">6.03313970565796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92112731933594</t>
+    <t xml:space="preserve">5.92112636566162</t>
   </si>
   <si>
     <t xml:space="preserve">6.26961135864258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59009265899658</t>
+    <t xml:space="preserve">6.59009313583374</t>
   </si>
   <si>
     <t xml:space="preserve">6.48119115829468</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23382949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649124145508</t>
+    <t xml:space="preserve">6.23382902145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649171829224</t>
   </si>
   <si>
     <t xml:space="preserve">6.18248987197876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10003614425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2836127281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45629978179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52163982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67876958847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85612297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8499002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85767889022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07081413269043</t>
+    <t xml:space="preserve">6.10003566741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28361320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45629930496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52164030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67877006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85612344741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84989976882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85767936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07081460952759</t>
   </si>
   <si>
     <t xml:space="preserve">7.10348463058472</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">7.13459920883179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09726190567017</t>
+    <t xml:space="preserve">7.09726142883301</t>
   </si>
   <si>
     <t xml:space="preserve">7.19060611724854</t>
@@ -4436,19 +4436,19 @@
     <t xml:space="preserve">7.15326881408691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31039714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49241924285889</t>
+    <t xml:space="preserve">7.31039810180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49241781234741</t>
   </si>
   <si>
     <t xml:space="preserve">7.52820014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57953977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63399124145508</t>
+    <t xml:space="preserve">7.57954025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6339898109436</t>
   </si>
   <si>
     <t xml:space="preserve">7.74289226531982</t>
@@ -4457,10 +4457,10 @@
     <t xml:space="preserve">7.9148006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90892314910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91228151321411</t>
+    <t xml:space="preserve">7.90892219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91228055953979</t>
   </si>
   <si>
     <t xml:space="preserve">7.93243551254272</t>
@@ -4469,94 +4469,94 @@
     <t xml:space="preserve">7.87029218673706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83502197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7728796005249</t>
+    <t xml:space="preserve">7.83502292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77287912368774</t>
   </si>
   <si>
     <t xml:space="preserve">7.73760938644409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69562149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7140965461731</t>
+    <t xml:space="preserve">7.6956205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71409559249878</t>
   </si>
   <si>
     <t xml:space="preserve">7.73928928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68554496765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6351580619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65867185592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71073722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69394159317017</t>
+    <t xml:space="preserve">7.68554449081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63515901565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6586709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71073770523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69394302368164</t>
   </si>
   <si>
     <t xml:space="preserve">7.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79471302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48064088821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50415468215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52934789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66371059417725</t>
+    <t xml:space="preserve">7.79471397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48064136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50415515899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52934741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6637110710144</t>
   </si>
   <si>
     <t xml:space="preserve">7.56965684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58477210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58645248413086</t>
+    <t xml:space="preserve">7.58477163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5864520072937</t>
   </si>
   <si>
     <t xml:space="preserve">7.53774499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64691591262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54446363449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5948486328125</t>
+    <t xml:space="preserve">7.64691543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54446315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59484958648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.6721076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79807329177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78463745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77959823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85685682296753</t>
+    <t xml:space="preserve">7.79807424545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78463792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77959775924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85685586929321</t>
   </si>
   <si>
     <t xml:space="preserve">7.90052509307861</t>
@@ -4568,31 +4568,31 @@
     <t xml:space="preserve">8.12558269500732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11550521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09535121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11046600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01977157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92403841018677</t>
+    <t xml:space="preserve">8.11550426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09535026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11046695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01977062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92403745651245</t>
   </si>
   <si>
     <t xml:space="preserve">8.04496479034424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0819149017334</t>
+    <t xml:space="preserve">8.08191299438477</t>
   </si>
   <si>
     <t xml:space="preserve">8.13230037689209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18100547790527</t>
+    <t xml:space="preserve">8.18100643157959</t>
   </si>
   <si>
     <t xml:space="preserve">8.28513813018799</t>
@@ -4610,7 +4610,7 @@
     <t xml:space="preserve">8.37247371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39430809020996</t>
+    <t xml:space="preserve">8.39430904388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.4312572479248</t>
@@ -4622,10 +4622,10 @@
     <t xml:space="preserve">8.54042720794678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5698184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69998168945312</t>
+    <t xml:space="preserve">8.56981945037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69998264312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.56561946868896</t>
@@ -4634,25 +4634,25 @@
     <t xml:space="preserve">8.7083797454834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74197006225586</t>
+    <t xml:space="preserve">8.74197101593018</t>
   </si>
   <si>
     <t xml:space="preserve">8.60340976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6328010559082</t>
+    <t xml:space="preserve">8.63280010223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.61180686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50263690948486</t>
+    <t xml:space="preserve">8.50263786315918</t>
   </si>
   <si>
     <t xml:space="preserve">8.49423980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39094734191895</t>
+    <t xml:space="preserve">8.39094829559326</t>
   </si>
   <si>
     <t xml:space="preserve">8.41026306152344</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">8.48164367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37415313720703</t>
+    <t xml:space="preserve">8.37415409088135</t>
   </si>
   <si>
     <t xml:space="preserve">8.36407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45644950866699</t>
+    <t xml:space="preserve">8.45644855499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.51103496551514</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">8.51523399353027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40186500549316</t>
+    <t xml:space="preserve">8.40186595916748</t>
   </si>
   <si>
     <t xml:space="preserve">8.16757011413574</t>
@@ -4694,13 +4694,13 @@
     <t xml:space="preserve">7.80143260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99793863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54950284957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52095031738281</t>
+    <t xml:space="preserve">7.99793672561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5495023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52095127105713</t>
   </si>
   <si>
     <t xml:space="preserve">7.43193578720093</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">7.73425054550171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63179922103882</t>
+    <t xml:space="preserve">7.63180017471313</t>
   </si>
   <si>
     <t xml:space="preserve">7.5528621673584</t>
@@ -4718,31 +4718,31 @@
     <t xml:space="preserve">7.51591157913208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60660696029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72417306900024</t>
+    <t xml:space="preserve">7.60660552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7241735458374</t>
   </si>
   <si>
     <t xml:space="preserve">7.78295707702637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81150960922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80983018875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74096870422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075704574585</t>
+    <t xml:space="preserve">7.8115086555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8098292350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74096965789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075609207153</t>
   </si>
   <si>
     <t xml:space="preserve">7.92739677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93915414810181</t>
+    <t xml:space="preserve">7.93915510177612</t>
   </si>
   <si>
     <t xml:space="preserve">8.09366989135742</t>
@@ -4751,49 +4751,49 @@
     <t xml:space="preserve">8.02648830413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18772506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21795654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.149094581604</t>
+    <t xml:space="preserve">8.18772411346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21795749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14909648895264</t>
   </si>
   <si>
     <t xml:space="preserve">8.21291732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17260932922363</t>
+    <t xml:space="preserve">8.17261028289795</t>
   </si>
   <si>
     <t xml:space="preserve">8.19780254364014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26834201812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17092990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89212656021118</t>
+    <t xml:space="preserve">8.26834106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17092895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8921275138855</t>
   </si>
   <si>
     <t xml:space="preserve">8.19444274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09702968597412</t>
+    <t xml:space="preserve">8.09703063964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.3808708190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34056186676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36575603485107</t>
+    <t xml:space="preserve">8.39766597747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34056282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36575508117676</t>
   </si>
   <si>
     <t xml:space="preserve">8.13565921783447</t>
@@ -4805,10 +4805,10 @@
     <t xml:space="preserve">8.18436622619629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2532262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27338123321533</t>
+    <t xml:space="preserve">8.25322723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27338218688965</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895992279053</t>
@@ -4817,13 +4817,13 @@
     <t xml:space="preserve">8.42705821990967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54462623596191</t>
+    <t xml:space="preserve">8.5446252822876</t>
   </si>
   <si>
     <t xml:space="preserve">8.7335729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77136325836182</t>
+    <t xml:space="preserve">8.7713623046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.67898845672607</t>
@@ -4850,25 +4850,25 @@
     <t xml:space="preserve">8.96450901031494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19124603271484</t>
+    <t xml:space="preserve">9.17025184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19124507904053</t>
   </si>
   <si>
     <t xml:space="preserve">9.28781986236572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38859176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49776268005371</t>
+    <t xml:space="preserve">9.38859081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49776172637939</t>
   </si>
   <si>
     <t xml:space="preserve">9.39698886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4263801574707</t>
+    <t xml:space="preserve">9.42638111114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.40538597106934</t>
@@ -4877,16 +4877,16 @@
     <t xml:space="preserve">9.30461406707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33400630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14925765991211</t>
+    <t xml:space="preserve">9.33400726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14925670623779</t>
   </si>
   <si>
     <t xml:space="preserve">9.03588962554932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01909351348877</t>
+    <t xml:space="preserve">9.01909446716309</t>
   </si>
   <si>
     <t xml:space="preserve">9.04848480224609</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">9.20384216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34660339355469</t>
+    <t xml:space="preserve">9.34660243988037</t>
   </si>
   <si>
     <t xml:space="preserve">9.35500144958496</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">9.27942180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24583053588867</t>
+    <t xml:space="preserve">9.24583148956299</t>
   </si>
   <si>
     <t xml:space="preserve">9.25002956390381</t>
@@ -4919,10 +4919,10 @@
     <t xml:space="preserve">9.43058013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48096561431885</t>
+    <t xml:space="preserve">9.48936367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48096466064453</t>
   </si>
   <si>
     <t xml:space="preserve">9.52295398712158</t>
@@ -4940,28 +4940,28 @@
     <t xml:space="preserve">9.63632297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930458068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70770263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68250846862793</t>
+    <t xml:space="preserve">9.69930553436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70770168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68250942230225</t>
   </si>
   <si>
     <t xml:space="preserve">10.0394096374512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1779708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0520076751709</t>
+    <t xml:space="preserve">10.1779718399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0520067214966</t>
   </si>
   <si>
     <t xml:space="preserve">9.9554328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94703674316406</t>
+    <t xml:space="preserve">9.94703578948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.93863868713379</t>
@@ -4973,19 +4973,19 @@
     <t xml:space="preserve">9.73289585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83366775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85886096954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83786582946777</t>
+    <t xml:space="preserve">9.83366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85886001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83786678314209</t>
   </si>
   <si>
     <t xml:space="preserve">9.93024063110352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87565517425537</t>
+    <t xml:space="preserve">9.87565612792969</t>
   </si>
   <si>
     <t xml:space="preserve">9.79167938232422</t>
@@ -4994,7 +4994,7 @@
     <t xml:space="preserve">9.76648616790771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.825270652771</t>
+    <t xml:space="preserve">9.82526969909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.97222900390625</t>
@@ -5003,16 +5003,16 @@
     <t xml:space="preserve">9.92604160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91344547271729</t>
+    <t xml:space="preserve">9.9134464263916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1653757095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.194766998291</t>
+    <t xml:space="preserve">10.1653747558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1947679519653</t>
   </si>
   <si>
     <t xml:space="preserve">10.1359834671021</t>
@@ -5021,13 +5021,13 @@
     <t xml:space="preserve">10.1401815414429</t>
   </si>
   <si>
-    <t xml:space="preserve">10.144380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2199602127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0981941223145</t>
+    <t xml:space="preserve">10.1443796157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2199592590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0981931686401</t>
   </si>
   <si>
     <t xml:space="preserve">10.1989660263062</t>
@@ -5045,22 +5045,22 @@
     <t xml:space="preserve">10.2115621566772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3039379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.25355052948</t>
+    <t xml:space="preserve">10.303936958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2535514831543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3291292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3333282470703</t>
+    <t xml:space="preserve">10.3291311264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173059463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3333292007446</t>
   </si>
   <si>
     <t xml:space="preserve">10.2451524734497</t>
@@ -5072,16 +5072,16 @@
     <t xml:space="preserve">10.3963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.434100151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5222768783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3921136856079</t>
+    <t xml:space="preserve">10.4341011047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5222749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3921127319336</t>
   </si>
   <si>
     <t xml:space="preserve">10.3207321166992</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">10.2745447158813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2031650543213</t>
+    <t xml:space="preserve">10.203164100647</t>
   </si>
   <si>
     <t xml:space="preserve">10.1275863647461</t>
@@ -5102,10 +5102,10 @@
     <t xml:space="preserve">10.2367553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.295539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695737838745</t>
+    <t xml:space="preserve">10.2955389022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695747375488</t>
   </si>
   <si>
     <t xml:space="preserve">10.1527786254883</t>
@@ -5123,13 +5123,13 @@
     <t xml:space="preserve">9.37179565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24163341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96870803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46417140960693</t>
+    <t xml:space="preserve">9.24163246154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96870708465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46417045593262</t>
   </si>
   <si>
     <t xml:space="preserve">9.53135299682617</t>
@@ -5162,13 +5162,13 @@
     <t xml:space="preserve">9.87985515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84817409515381</t>
+    <t xml:space="preserve">9.84817504882812</t>
   </si>
   <si>
     <t xml:space="preserve">9.73050308227539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8255443572998</t>
+    <t xml:space="preserve">9.82554531097412</t>
   </si>
   <si>
     <t xml:space="preserve">9.81649398803711</t>
@@ -5180,16 +5180,16 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73955535888672</t>
+    <t xml:space="preserve">9.7395544052124</t>
   </si>
   <si>
     <t xml:space="preserve">9.71239852905273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75313091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78028774261475</t>
+    <t xml:space="preserve">9.75313186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78028678894043</t>
   </si>
   <si>
     <t xml:space="preserve">9.72597694396973</t>
@@ -5201,19 +5201,19 @@
     <t xml:space="preserve">9.92511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0020523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0744657516479</t>
+    <t xml:space="preserve">10.0020513534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0744647979736</t>
   </si>
   <si>
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.092568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0337333679199</t>
+    <t xml:space="preserve">10.0925674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0337324142456</t>
   </si>
   <si>
     <t xml:space="preserve">10.069938659668</t>
@@ -5225,16 +5225,16 @@
     <t xml:space="preserve">10.1378259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0789909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1785583496094</t>
+    <t xml:space="preserve">10.0789918899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1785593032837</t>
   </si>
   <si>
     <t xml:space="preserve">10.1514043807983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.115198135376</t>
+    <t xml:space="preserve">10.1151971817017</t>
   </si>
   <si>
     <t xml:space="preserve">10.142352104187</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">10.060887336731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695070266724</t>
+    <t xml:space="preserve">10.1695079803467</t>
   </si>
   <si>
     <t xml:space="preserve">10.2464456558228</t>
@@ -5291,10 +5291,10 @@
     <t xml:space="preserve">10.9751024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.106351852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.133505821228</t>
+    <t xml:space="preserve">11.1063508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1335067749023</t>
   </si>
   <si>
     <t xml:space="preserve">10.9388961791992</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">10.8393278121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7669143676758</t>
+    <t xml:space="preserve">10.7669153213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7171306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5315732955933</t>
+    <t xml:space="preserve">10.5315723419189</t>
   </si>
   <si>
     <t xml:space="preserve">10.4908399581909</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">10.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858821868896</t>
+    <t xml:space="preserve">10.5858812332153</t>
   </si>
   <si>
     <t xml:space="preserve">10.6628217697144</t>
@@ -5336,16 +5336,16 @@
     <t xml:space="preserve">10.7261819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.178765296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7173357009888</t>
+    <t xml:space="preserve">11.1787643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7173347473145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5906133651733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4955711364746</t>
+    <t xml:space="preserve">11.4955701828003</t>
   </si>
   <si>
     <t xml:space="preserve">11.4231586456299</t>
@@ -5360,10 +5360,10 @@
     <t xml:space="preserve">11.3869514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.486517906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6313457489014</t>
+    <t xml:space="preserve">11.4865188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6313467025757</t>
   </si>
   <si>
     <t xml:space="preserve">11.5815620422363</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">11.7625932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6901807785034</t>
+    <t xml:space="preserve">11.6901817321777</t>
   </si>
   <si>
     <t xml:space="preserve">11.8576364517212</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">11.9979362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0567712783813</t>
+    <t xml:space="preserve">12.0567722320557</t>
   </si>
   <si>
     <t xml:space="preserve">12.1291847229004</t>
@@ -5396,40 +5396,40 @@
     <t xml:space="preserve">12.2785358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3328466415405</t>
+    <t xml:space="preserve">12.3328475952148</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500301361084</t>
+    <t xml:space="preserve">12.5003023147583</t>
   </si>
   <si>
     <t xml:space="preserve">12.3781051635742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5093536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3962087631226</t>
+    <t xml:space="preserve">12.509352684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3962078094482</t>
   </si>
   <si>
     <t xml:space="preserve">12.4052600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3102178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2875881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.124659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1699171066284</t>
+    <t xml:space="preserve">12.3102188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554754257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2875890731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1246604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1699180603027</t>
   </si>
   <si>
     <t xml:space="preserve">12.2921142578125</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">12.3826313018799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6451282501221</t>
+    <t xml:space="preserve">12.6451292037964</t>
   </si>
   <si>
     <t xml:space="preserve">12.6722831726074</t>
@@ -5471,16 +5471,16 @@
     <t xml:space="preserve">13.0796060562134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2244319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5140838623047</t>
+    <t xml:space="preserve">13.2244310379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.514084815979</t>
   </si>
   <si>
     <t xml:space="preserve">13.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7403755187988</t>
+    <t xml:space="preserve">13.7403745651245</t>
   </si>
   <si>
     <t xml:space="preserve">13.7992105484009</t>
@@ -6489,6 +6489,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.1599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2350006103516</t>
   </si>
 </sst>
 </file>
@@ -48575,7 +48578,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>849</v>
+        <v>1349</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48601,7 +48604,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1607" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -48627,7 +48630,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1608" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -48653,7 +48656,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G1609" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -48705,7 +48708,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1611" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48731,7 +48734,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48783,7 +48786,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G1614" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48809,7 +48812,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1615" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48835,7 +48838,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G1616" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48887,7 +48890,7 @@
         <v>9.70400047302246</v>
       </c>
       <c r="G1618" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48913,7 +48916,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G1619" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48939,7 +48942,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1620" t="s">
-        <v>1359</v>
+        <v>1257</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -71697,7 +71700,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6518287037</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>1195841</v>
@@ -71718,6 +71721,32 @@
         <v>2158</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494560185</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>1118510</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>16.2649993896484</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>15.9849996566772</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>16.2150001525879</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>16.2350006103516</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="2160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="2161">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">5.18521499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0552830696106</t>
+    <t xml:space="preserve">5.05528259277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.95858860015869</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">4.83772134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81052589416504</t>
+    <t xml:space="preserve">4.8105263710022</t>
   </si>
   <si>
     <t xml:space="preserve">4.92535018920898</t>
@@ -65,133 +65,133 @@
     <t xml:space="preserve">4.97974061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91930723190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73196220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50533628463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59900856018066</t>
+    <t xml:space="preserve">4.91930675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73196268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50533580780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59900808334351</t>
   </si>
   <si>
     <t xml:space="preserve">4.41468477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65944194793701</t>
+    <t xml:space="preserve">4.65944147109985</t>
   </si>
   <si>
     <t xml:space="preserve">4.67455053329468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52346563339233</t>
+    <t xml:space="preserve">4.52346658706665</t>
   </si>
   <si>
     <t xml:space="preserve">4.59598636627197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52648782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27870845794678</t>
+    <t xml:space="preserve">4.52648735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27870893478394</t>
   </si>
   <si>
     <t xml:space="preserve">4.45094585418701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3119478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19410228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00373554229736</t>
+    <t xml:space="preserve">4.31194829940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19410181045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00373601913452</t>
   </si>
   <si>
     <t xml:space="preserve">4.09136438369751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98862743377686</t>
+    <t xml:space="preserve">3.9886269569397</t>
   </si>
   <si>
     <t xml:space="preserve">3.61695981025696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41450643539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67135000228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47796177864075</t>
+    <t xml:space="preserve">3.41450667381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6713502407074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47796201705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.5444393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64717626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68041563034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74991369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64113330841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091589927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75595688819885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66228437423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62300276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67437148094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76804423332214</t>
+    <t xml:space="preserve">3.64717650413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68041491508484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991345405579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113283157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75595760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66228532791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62300324440002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67437171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76804375648499</t>
   </si>
   <si>
     <t xml:space="preserve">3.78315281867981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93725872039795</t>
+    <t xml:space="preserve">3.93725824356079</t>
   </si>
   <si>
     <t xml:space="preserve">4.08834314346313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10345077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0248875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006326675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96143221855164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97351837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03395318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38446855545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42979288101196</t>
+    <t xml:space="preserve">4.10345125198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02488708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006302833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96143174171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97351908683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03395223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38446807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42979383468628</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173065185547</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">4.29986095428467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03697395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07323455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0943865776062</t>
+    <t xml:space="preserve">4.03697443008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07323408126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09438610076904</t>
   </si>
   <si>
     <t xml:space="preserve">4.01884460449219</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">3.90401983261108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82545590400696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79221749305725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83149933815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7589795589447</t>
+    <t xml:space="preserve">3.82545638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79221796989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8314995765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75897860527039</t>
   </si>
   <si>
     <t xml:space="preserve">3.79523921012878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6048731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81336951255798</t>
+    <t xml:space="preserve">3.60487341880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8133692741394</t>
   </si>
   <si>
     <t xml:space="preserve">3.85567307472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77408742904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97049736976624</t>
+    <t xml:space="preserve">3.77408695220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97049760818481</t>
   </si>
   <si>
     <t xml:space="preserve">4.04301786422729</t>
@@ -260,64 +260,64 @@
     <t xml:space="preserve">4.23036241531372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23338413238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36935949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38749074935913</t>
+    <t xml:space="preserve">4.2333836555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36935997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38748979568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.39655542373657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33612108230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21223211288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05208206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88588929176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85265159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80430483818054</t>
+    <t xml:space="preserve">4.33612060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21223163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05208253860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88588953018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85265111923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8043041229248</t>
   </si>
   <si>
     <t xml:space="preserve">3.87078142166138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89797639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93423748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92215085029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90704226493835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97956204414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01582288742065</t>
+    <t xml:space="preserve">3.89797568321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93423700332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9221498966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90704107284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9795618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0158224105835</t>
   </si>
   <si>
     <t xml:space="preserve">4.21827554702759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30590391159058</t>
+    <t xml:space="preserve">4.31496953964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30590534210205</t>
   </si>
   <si>
     <t xml:space="preserve">4.35727310180664</t>
@@ -332,160 +332,160 @@
     <t xml:space="preserve">4.10647296905518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00071334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98560547828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610741615295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70156717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52026557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3873119354248</t>
+    <t xml:space="preserve">4.00071382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98560500144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91610717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70156693458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52026581764221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38731169700623</t>
   </si>
   <si>
     <t xml:space="preserve">3.48098397254944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46889662742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6078941822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80732560157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8586950302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83452081680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2090322971344</t>
+    <t xml:space="preserve">3.46889686584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60789489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80732607841492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85869479179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83452105522156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20903205871582</t>
   </si>
   <si>
     <t xml:space="preserve">2.79929113388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96125316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06399083137512</t>
+    <t xml:space="preserve">2.96125340461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06399130821228</t>
   </si>
   <si>
     <t xml:space="preserve">3.11536002159119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1455762386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01322674751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91653251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84763789176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94554042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19694471359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472336769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4719181060791</t>
+    <t xml:space="preserve">3.14557647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01322650909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91653275489807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84763813018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9455406665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19694519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472289085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47191905975342</t>
   </si>
   <si>
     <t xml:space="preserve">3.57767772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52630925178528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58674263954163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55350422859192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5958080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58976483345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61998128890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53537392616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65926337242126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.613938331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78617334365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71365356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40846347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42054986953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71969723701477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96747589111328</t>
+    <t xml:space="preserve">3.5263090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58674335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55350375175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59580779075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58976435661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61998081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5353741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65926265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61393713951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78617405891418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71365404129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4084632396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42054963111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71969795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96747541427612</t>
   </si>
   <si>
     <t xml:space="preserve">3.94027972221375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90099787712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308450698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84962916374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8163914680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80128312110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6955235004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72876191139221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92517113685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89495515823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95236682891846</t>
+    <t xml:space="preserve">3.90099835395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308522224426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84962964057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81639051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80128264427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69552326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72876214981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92517185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89495468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95236706733704</t>
   </si>
   <si>
     <t xml:space="preserve">4.0490608215332</t>
@@ -494,88 +494,88 @@
     <t xml:space="preserve">4.14273357391357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07927751541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19108057022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15482044219971</t>
+    <t xml:space="preserve">4.07927799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19108009338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15481996536255</t>
   </si>
   <si>
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73178434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78919625282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68645763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77106595039368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77710890769958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49609208106995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54141759872437</t>
+    <t xml:space="preserve">3.73178386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78919649124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68645858764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77106523513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77710938453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49609231948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54141783714294</t>
   </si>
   <si>
     <t xml:space="preserve">3.47494053840637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49911332130432</t>
+    <t xml:space="preserve">3.49911403656006</t>
   </si>
   <si>
     <t xml:space="preserve">3.49004888534546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49307036399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68343687057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78013110160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65322017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74387073516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87380290031433</t>
+    <t xml:space="preserve">3.49307060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68343615531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78013038635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65321969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74387049674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87380266189575</t>
   </si>
   <si>
     <t xml:space="preserve">3.99467062950134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10949516296387</t>
+    <t xml:space="preserve">4.10949468612671</t>
   </si>
   <si>
     <t xml:space="preserve">4.15784120559692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23640537261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84358620643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00977945327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14575481414795</t>
+    <t xml:space="preserve">4.23640584945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114816665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84358644485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00977849960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14575529098511</t>
   </si>
   <si>
     <t xml:space="preserve">4.13971138000488</t>
@@ -590,31 +590,31 @@
     <t xml:space="preserve">4.20618867874146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1125168800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94632458686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99360418319702</t>
+    <t xml:space="preserve">4.11251640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94632387161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99360370635986</t>
   </si>
   <si>
     <t xml:space="preserve">4.06294822692871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00306034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96208333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90849947929382</t>
+    <t xml:space="preserve">4.00305986404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96208381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90849924087524</t>
   </si>
   <si>
     <t xml:space="preserve">3.7950267791748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95577907562256</t>
+    <t xml:space="preserve">3.95578002929688</t>
   </si>
   <si>
     <t xml:space="preserve">4.10392427444458</t>
@@ -632,25 +632,25 @@
     <t xml:space="preserve">4.46325397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67759132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80682277679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67128801345825</t>
+    <t xml:space="preserve">4.67759084701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80682420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67128705978394</t>
   </si>
   <si>
     <t xml:space="preserve">4.69650316238403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74693536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79106378555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95181655883789</t>
+    <t xml:space="preserve">4.74693584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79106330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95181703567505</t>
   </si>
   <si>
     <t xml:space="preserve">4.89508008956909</t>
@@ -665,88 +665,88 @@
     <t xml:space="preserve">4.95496845245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93920850753784</t>
+    <t xml:space="preserve">4.93920803070068</t>
   </si>
   <si>
     <t xml:space="preserve">5.00224828720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99909687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93605661392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89823198318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8887767791748</t>
+    <t xml:space="preserve">4.99909639358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93605709075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89823293685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88877630233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.99279260635376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13778495788574</t>
+    <t xml:space="preserve">5.1377854347229</t>
   </si>
   <si>
     <t xml:space="preserve">5.1693058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1440896987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.163001537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92975234985352</t>
+    <t xml:space="preserve">5.14408874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16300106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92975187301636</t>
   </si>
   <si>
     <t xml:space="preserve">4.98333692550659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98018550872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86356019973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05898523330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04007387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00540113449097</t>
+    <t xml:space="preserve">4.98018503189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86355972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05898475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04007244110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00540018081665</t>
   </si>
   <si>
     <t xml:space="preserve">5.08420085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01170492172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08735227584839</t>
+    <t xml:space="preserve">5.01170444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08735275268555</t>
   </si>
   <si>
     <t xml:space="preserve">5.3710355758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5380916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36157894134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29538631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15354633331299</t>
+    <t xml:space="preserve">5.53809070587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3615779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29538583755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15354585647583</t>
   </si>
   <si>
     <t xml:space="preserve">5.01485681533813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13463401794434</t>
+    <t xml:space="preserve">5.13463306427002</t>
   </si>
   <si>
     <t xml:space="preserve">4.92344856262207</t>
@@ -758,55 +758,55 @@
     <t xml:space="preserve">4.96757745742798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91084051132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05583381652832</t>
+    <t xml:space="preserve">4.91084003448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05583333969116</t>
   </si>
   <si>
     <t xml:space="preserve">5.17561006546021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14724111557007</t>
+    <t xml:space="preserve">5.14724159240723</t>
   </si>
   <si>
     <t xml:space="preserve">5.11887311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07159328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02431201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97388029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82888746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69335126876831</t>
+    <t xml:space="preserve">5.07159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02431297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97388076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82888793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69335174560547</t>
   </si>
   <si>
     <t xml:space="preserve">4.72802352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7689995765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94866514205933</t>
+    <t xml:space="preserve">4.76900005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94866466522217</t>
   </si>
   <si>
     <t xml:space="preserve">4.99594449996948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17245769500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21658563613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2260422706604</t>
+    <t xml:space="preserve">5.17245721817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21658515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22604179382324</t>
   </si>
   <si>
     <t xml:space="preserve">5.30169057846069</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">5.26071405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32375383377075</t>
+    <t xml:space="preserve">5.32375478744507</t>
   </si>
   <si>
     <t xml:space="preserve">5.33636283874512</t>
@@ -833,64 +833,64 @@
     <t xml:space="preserve">5.27962636947632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.339515209198</t>
+    <t xml:space="preserve">5.33951473236084</t>
   </si>
   <si>
     <t xml:space="preserve">5.31745100021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35212230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32690620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19767379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20712995529175</t>
+    <t xml:space="preserve">5.35212278366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32690668106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19767332077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20712947845459</t>
   </si>
   <si>
     <t xml:space="preserve">5.20397806167603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23864984512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13148260116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85095167160034</t>
+    <t xml:space="preserve">5.23865032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13148164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8509521484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.38364267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46559476852417</t>
+    <t xml:space="preserve">5.46559524536133</t>
   </si>
   <si>
     <t xml:space="preserve">5.38994646072388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35527420043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56330823898315</t>
+    <t xml:space="preserve">5.35527467727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56330680847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.57906818389893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59798002243042</t>
+    <t xml:space="preserve">5.5979790687561</t>
   </si>
   <si>
     <t xml:space="preserve">5.70830106735229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78710079193115</t>
+    <t xml:space="preserve">5.78710126876831</t>
   </si>
   <si>
     <t xml:space="preserve">5.75242853164673</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">5.79340410232544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76188516616821</t>
+    <t xml:space="preserve">5.76188468933105</t>
   </si>
   <si>
     <t xml:space="preserve">5.78394889831543</t>
@@ -914,43 +914,43 @@
     <t xml:space="preserve">5.62319612503052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6421070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68938827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73036479949951</t>
+    <t xml:space="preserve">5.64210796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68938875198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73036432266235</t>
   </si>
   <si>
     <t xml:space="preserve">5.76818895339966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73982048034668</t>
+    <t xml:space="preserve">5.73981952667236</t>
   </si>
   <si>
     <t xml:space="preserve">5.71460390090942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62950038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45298671722412</t>
+    <t xml:space="preserve">5.6294994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45298719406128</t>
   </si>
   <si>
     <t xml:space="preserve">5.32060289382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34266662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25441026687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27332210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36473035812378</t>
+    <t xml:space="preserve">5.34266710281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27332162857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36473083496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.41516304016113</t>
@@ -962,85 +962,85 @@
     <t xml:space="preserve">5.44983530044556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37418603897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39309883117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29223394393921</t>
+    <t xml:space="preserve">5.37418651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3930983543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29223489761353</t>
   </si>
   <si>
     <t xml:space="preserve">5.21028232574463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35842657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34581851959229</t>
+    <t xml:space="preserve">5.35842609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34581804275513</t>
   </si>
   <si>
     <t xml:space="preserve">5.48135471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46874761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44668292999268</t>
+    <t xml:space="preserve">5.46874666213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44668340682983</t>
   </si>
   <si>
     <t xml:space="preserve">5.54754686355591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5948281288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52548360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56015586853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59167623519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66101932525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7177562713623</t>
+    <t xml:space="preserve">5.59482717514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52548313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56015539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59167528152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66101980209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71775579452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.67362785339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67677974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49081134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5097222328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56961107254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60743618011475</t>
+    <t xml:space="preserve">5.67678022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49081087112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50972366333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56961154937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60743522644043</t>
   </si>
   <si>
     <t xml:space="preserve">5.58221960067749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55700349807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54439640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67993211746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67047643661499</t>
+    <t xml:space="preserve">5.55700397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54439544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67993259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67047595977783</t>
   </si>
   <si>
     <t xml:space="preserve">5.61058712005615</t>
@@ -1049,61 +1049,61 @@
     <t xml:space="preserve">5.48450708389282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53493976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52863454818726</t>
+    <t xml:space="preserve">5.53493928909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52863550186157</t>
   </si>
   <si>
     <t xml:space="preserve">5.47505140304565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43407487869263</t>
+    <t xml:space="preserve">5.38049030303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43407535552979</t>
   </si>
   <si>
     <t xml:space="preserve">5.33005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50026845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56646013259888</t>
+    <t xml:space="preserve">5.50026750564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56646060943604</t>
   </si>
   <si>
     <t xml:space="preserve">5.5065712928772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51602792739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58537149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66732406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65471649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69254016876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72406005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75873279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71145343780518</t>
+    <t xml:space="preserve">5.51602649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58537197113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66732454299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65471601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69253969192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72406053543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75873231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71145296096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.7997088432312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74612426757812</t>
+    <t xml:space="preserve">5.74612474441528</t>
   </si>
   <si>
     <t xml:space="preserve">5.77449226379395</t>
@@ -1118,70 +1118,70 @@
     <t xml:space="preserve">5.78079700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77133989334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8186206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91633319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97622203826904</t>
+    <t xml:space="preserve">5.77134037017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81862115859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91633415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97622156143188</t>
   </si>
   <si>
     <t xml:space="preserve">5.93209362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01404523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07708549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05187034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03295612335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10860586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10230255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23153495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21577453613281</t>
+    <t xml:space="preserve">6.01404571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07708597183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05187129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03295803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10860538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10230302810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2315354347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2157735824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.2252311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21892595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2000150680542</t>
+    <t xml:space="preserve">6.21892690658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20001459121704</t>
   </si>
   <si>
     <t xml:space="preserve">6.23178100585938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1335391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885801315308</t>
+    <t xml:space="preserve">6.13353824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885705947876</t>
   </si>
   <si>
     <t xml:space="preserve">6.20558261871338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16956186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0975170135498</t>
+    <t xml:space="preserve">6.16956090927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09751796722412</t>
   </si>
   <si>
     <t xml:space="preserve">6.22850561141968</t>
@@ -1190,37 +1190,37 @@
     <t xml:space="preserve">6.34966993331909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28745079040527</t>
+    <t xml:space="preserve">6.28745174407959</t>
   </si>
   <si>
     <t xml:space="preserve">6.33329629898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19903326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2219557762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382394790649</t>
+    <t xml:space="preserve">6.29400014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19903373718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22195625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382442474365</t>
   </si>
   <si>
     <t xml:space="preserve">6.2809009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28417587280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25470352172852</t>
+    <t xml:space="preserve">6.28417634963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25470399856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.24815368652344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12371587753296</t>
+    <t xml:space="preserve">6.12371492385864</t>
   </si>
   <si>
     <t xml:space="preserve">6.15646123886108</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">6.24160432815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26452684402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26125335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19575834274292</t>
+    <t xml:space="preserve">6.26452732086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26125288009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19575786590576</t>
   </si>
   <si>
     <t xml:space="preserve">6.1466383934021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27107667922974</t>
+    <t xml:space="preserve">6.27107763290405</t>
   </si>
   <si>
     <t xml:space="preserve">6.41843938827515</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">6.39879035949707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40206575393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39224100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41188907623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49375820159912</t>
+    <t xml:space="preserve">6.40206480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39224147796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41188955307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4937572479248</t>
   </si>
   <si>
     <t xml:space="preserve">6.51995515823364</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">6.53305387496948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52977991104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48720836639404</t>
+    <t xml:space="preserve">6.5297794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48720741271973</t>
   </si>
   <si>
     <t xml:space="preserve">6.43808698654175</t>
@@ -1286,70 +1286,70 @@
     <t xml:space="preserve">6.45380592346191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36604404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41319990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47607326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51406049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45642566680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2678017616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36997270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32019758224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36473369598389</t>
+    <t xml:space="preserve">6.36604356765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41319894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51406097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4564266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26780223846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36997318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32019662857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36473417282104</t>
   </si>
   <si>
     <t xml:space="preserve">6.41581869125366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45511627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47214365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44594717025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4669041633606</t>
+    <t xml:space="preserve">6.45511674880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47214555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46690464019775</t>
   </si>
   <si>
     <t xml:space="preserve">6.47869443893433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40010118484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46166563034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47476387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51013135910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674646377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21016788482666</t>
+    <t xml:space="preserve">6.40010070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46166467666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47476434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51013088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41974878311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674741744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2101674079895</t>
   </si>
   <si>
     <t xml:space="preserve">6.31102848052979</t>
@@ -1367,40 +1367,40 @@
     <t xml:space="preserve">6.39748048782349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42498874664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45773506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40664958953857</t>
+    <t xml:space="preserve">6.42498922348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45773458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40665054321289</t>
   </si>
   <si>
     <t xml:space="preserve">6.47738456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37390327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25732278823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21671628952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24684476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25339365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27828121185303</t>
+    <t xml:space="preserve">6.37390279769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25732326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21671676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24684381484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25339412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27828168869019</t>
   </si>
   <si>
     <t xml:space="preserve">6.35294437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34508657455444</t>
+    <t xml:space="preserve">6.34508514404297</t>
   </si>
   <si>
     <t xml:space="preserve">6.41712951660156</t>
@@ -1421,61 +1421,61 @@
     <t xml:space="preserve">6.79503107070923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84415102005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70661354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69351530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67386627197266</t>
+    <t xml:space="preserve">6.84415197372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70661306381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69351434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67386722564697</t>
   </si>
   <si>
     <t xml:space="preserve">6.55925226211548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69678974151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72953653335571</t>
+    <t xml:space="preserve">6.69679069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72953605651855</t>
   </si>
   <si>
     <t xml:space="preserve">6.54942750930786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46428537368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51537179946899</t>
+    <t xml:space="preserve">6.46428489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51537084579468</t>
   </si>
   <si>
     <t xml:space="preserve">6.56907558441162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5219202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20754766464233</t>
+    <t xml:space="preserve">6.52191972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20754671096802</t>
   </si>
   <si>
     <t xml:space="preserve">6.01499462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91544246673584</t>
+    <t xml:space="preserve">5.915442943573</t>
   </si>
   <si>
     <t xml:space="preserve">5.95342969894409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81327247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58011245727539</t>
+    <t xml:space="preserve">5.81327295303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58011293411255</t>
   </si>
   <si>
     <t xml:space="preserve">5.24085187911987</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">5.0312705039978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28407764434814</t>
+    <t xml:space="preserve">5.38625001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28407716751099</t>
   </si>
   <si>
     <t xml:space="preserve">5.4216160774231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32861423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19238567352295</t>
+    <t xml:space="preserve">5.32861375808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19238662719727</t>
   </si>
   <si>
     <t xml:space="preserve">5.35874176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23823165893555</t>
+    <t xml:space="preserve">5.23823261260986</t>
   </si>
   <si>
     <t xml:space="preserve">5.12689208984375</t>
@@ -1517,13 +1517,13 @@
     <t xml:space="preserve">5.40327787399292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34826278686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28276777267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26050043106079</t>
+    <t xml:space="preserve">5.34826326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28276824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26049995422363</t>
   </si>
   <si>
     <t xml:space="preserve">5.44257497787476</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">5.38755941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52378702163696</t>
+    <t xml:space="preserve">5.52378749847412</t>
   </si>
   <si>
     <t xml:space="preserve">5.33254384994507</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">5.29848766326904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21727418899536</t>
+    <t xml:space="preserve">5.2172737121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.18321704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21465396881104</t>
+    <t xml:space="preserve">5.21465444564819</t>
   </si>
   <si>
     <t xml:space="preserve">5.18845653533936</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">5.30634641647339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34040355682373</t>
+    <t xml:space="preserve">5.34040307998657</t>
   </si>
   <si>
     <t xml:space="preserve">5.26835918426514</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17928743362427</t>
+    <t xml:space="preserve">5.17928791046143</t>
   </si>
   <si>
     <t xml:space="preserve">5.20155572891235</t>
@@ -1580,46 +1580,46 @@
     <t xml:space="preserve">5.27097940444946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28931760787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33778285980225</t>
+    <t xml:space="preserve">5.28931856155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3377833366394</t>
   </si>
   <si>
     <t xml:space="preserve">5.32468509674072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35612154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51330804824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57618236541748</t>
+    <t xml:space="preserve">5.3561224937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51330900192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57618284225464</t>
   </si>
   <si>
     <t xml:space="preserve">5.62857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73205852508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68097305297852</t>
+    <t xml:space="preserve">5.73205900192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68097352981567</t>
   </si>
   <si>
     <t xml:space="preserve">5.81851148605347</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74646806716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68752384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78052473068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68490362167358</t>
+    <t xml:space="preserve">5.74646854400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68752241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78052425384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68490314483643</t>
   </si>
   <si>
     <t xml:space="preserve">5.75956583023071</t>
@@ -1628,37 +1628,37 @@
     <t xml:space="preserve">5.75563716888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76742553710938</t>
+    <t xml:space="preserve">5.76742649078369</t>
   </si>
   <si>
     <t xml:space="preserve">5.70848083496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5958309173584</t>
+    <t xml:space="preserve">5.59583139419556</t>
   </si>
   <si>
     <t xml:space="preserve">5.44912338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56439352035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50282955169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51985788345337</t>
+    <t xml:space="preserve">5.56439399719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50282907485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51985692977905</t>
   </si>
   <si>
     <t xml:space="preserve">5.61023950576782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49759006500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43340396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43864393234253</t>
+    <t xml:space="preserve">5.49758958816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43340492248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43864488601685</t>
   </si>
   <si>
     <t xml:space="preserve">5.42816543579102</t>
@@ -1670,40 +1670,40 @@
     <t xml:space="preserve">5.41899681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25002098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55522394180298</t>
+    <t xml:space="preserve">5.25002145767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55522489547729</t>
   </si>
   <si>
     <t xml:space="preserve">5.73598957061768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68621301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771123886108</t>
+    <t xml:space="preserve">5.68621349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771171569824</t>
   </si>
   <si>
     <t xml:space="preserve">5.90627384185791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9364013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89710378646851</t>
+    <t xml:space="preserve">5.93640089035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89710474014282</t>
   </si>
   <si>
     <t xml:space="preserve">5.91282320022583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01368427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03333282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09620714187622</t>
+    <t xml:space="preserve">6.01368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03333234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09620761871338</t>
   </si>
   <si>
     <t xml:space="preserve">6.00844478607178</t>
@@ -1712,49 +1712,49 @@
     <t xml:space="preserve">6.00713491439819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07524919509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06477069854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00451612472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63512802124023</t>
+    <t xml:space="preserve">5.96390914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07524967193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06476974487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00451564788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63512754440308</t>
   </si>
   <si>
     <t xml:space="preserve">5.46353244781494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48842000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48056077957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38886833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13737058639526</t>
+    <t xml:space="preserve">5.48842096328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48056125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3888692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13737106323242</t>
   </si>
   <si>
     <t xml:space="preserve">5.18059778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07187700271606</t>
+    <t xml:space="preserve">5.07187652587891</t>
   </si>
   <si>
     <t xml:space="preserve">5.02865028381348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11379289627075</t>
+    <t xml:space="preserve">5.0351996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11379337310791</t>
   </si>
   <si>
     <t xml:space="preserve">5.05484819412231</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">5.00638246536255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15963888168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06663703918457</t>
+    <t xml:space="preserve">5.15963935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06663751602173</t>
   </si>
   <si>
     <t xml:space="preserve">5.07842636108398</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">5.09545469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95791721343994</t>
+    <t xml:space="preserve">4.95791673660278</t>
   </si>
   <si>
     <t xml:space="preserve">5.09938430786133</t>
@@ -1790,22 +1790,22 @@
     <t xml:space="preserve">5.0771164894104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19500589370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.136061668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11641311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13868141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15308952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14915943145752</t>
+    <t xml:space="preserve">5.19500637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13606119155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11641216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13868093490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15308904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14915990829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.08104610443115</t>
@@ -1814,70 +1814,70 @@
     <t xml:space="preserve">5.15818929672241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08011960983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.117760181427</t>
+    <t xml:space="preserve">5.03690242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987855911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08012008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11776113510132</t>
   </si>
   <si>
     <t xml:space="preserve">5.34500026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36730527877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39100503921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44258737564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44119310379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47604465484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37706470489502</t>
+    <t xml:space="preserve">5.36730480194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39100551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44258689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44119262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47604513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37706422805786</t>
   </si>
   <si>
     <t xml:space="preserve">5.38821697235107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22650051116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22231817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10242605209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07733154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24462366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26553583145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31293535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23068284988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27668905258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3728814125061</t>
+    <t xml:space="preserve">5.22650098800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22231864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10242509841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07733106613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24462413787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26553535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31293487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23068332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27668857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37288236618042</t>
   </si>
   <si>
     <t xml:space="preserve">5.25577688217163</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">5.12751913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04944944381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14145994186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09127235412598</t>
+    <t xml:space="preserve">5.04944896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14146089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09127283096313</t>
   </si>
   <si>
     <t xml:space="preserve">5.08709049224854</t>
@@ -1901,43 +1901,43 @@
     <t xml:space="preserve">5.38961124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37985229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36312341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33524131774902</t>
+    <t xml:space="preserve">5.37985277175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36312294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33524084091187</t>
   </si>
   <si>
     <t xml:space="preserve">5.33802890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40494632720947</t>
+    <t xml:space="preserve">5.40494680404663</t>
   </si>
   <si>
     <t xml:space="preserve">5.34639406204224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33942270278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46210479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46907520294189</t>
+    <t xml:space="preserve">5.33942317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46210432052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">5.49138069152832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50671577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48859310150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49277448654175</t>
+    <t xml:space="preserve">5.50671625137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48859262466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49277496337891</t>
   </si>
   <si>
     <t xml:space="preserve">5.50253391265869</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">5.55969142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48998641967773</t>
+    <t xml:space="preserve">5.48998689651489</t>
   </si>
   <si>
     <t xml:space="preserve">5.4481635093689</t>
@@ -1955,19 +1955,19 @@
     <t xml:space="preserve">5.45931625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29481172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14424848556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11218452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28505373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3979754447937</t>
+    <t xml:space="preserve">5.29481220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14424896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11218404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28505325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39797592163086</t>
   </si>
   <si>
     <t xml:space="preserve">5.40355205535889</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">5.52623319625854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62521505355835</t>
+    <t xml:space="preserve">5.62521409988403</t>
   </si>
   <si>
     <t xml:space="preserve">5.59036254882812</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">5.78971910476685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77717304229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79808378219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73953199386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75486660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82736015319824</t>
+    <t xml:space="preserve">5.80365991592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77717256546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79808330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73953151702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75486707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82735967636108</t>
   </si>
   <si>
     <t xml:space="preserve">5.91797637939453</t>
@@ -2015,133 +2015,133 @@
     <t xml:space="preserve">6.14939785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02532339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07969331741333</t>
+    <t xml:space="preserve">6.02532291412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07969284057617</t>
   </si>
   <si>
     <t xml:space="preserve">6.08945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20376777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10060453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03786945343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12430429458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10339212417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18982744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21631526947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26510953903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39894390106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35990762710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24001598358154</t>
+    <t xml:space="preserve">6.20376825332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03787040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1243052482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10339307785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18982791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21631622314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26510906219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39894342422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35990858078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24001502990723</t>
   </si>
   <si>
     <t xml:space="preserve">6.28602075576782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23583316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17728090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22467994689941</t>
+    <t xml:space="preserve">6.23583269119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17728137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468042373657</t>
   </si>
   <si>
     <t xml:space="preserve">6.35293817520142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42264318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4561014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5188364982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42543172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44076585769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47840738296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52162408828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46446704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48537731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57878160476685</t>
+    <t xml:space="preserve">6.42264223098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45610237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51883602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42543125152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44076633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47840642929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52162456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4644660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48537826538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57878255844116</t>
   </si>
   <si>
     <t xml:space="preserve">6.63175916671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6707935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69867610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67915773391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62199926376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54392957687378</t>
+    <t xml:space="preserve">6.67079448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69867515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67915821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62199974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">6.52441263198853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56205320358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194675445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5871467590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62478828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41706705093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26789665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34875583648682</t>
+    <t xml:space="preserve">6.56205368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194723129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58714723587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62478733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.417067527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.267897605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34875440597534</t>
   </si>
   <si>
     <t xml:space="preserve">6.20237398147583</t>
@@ -2150,31 +2150,31 @@
     <t xml:space="preserve">6.06435823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22049808502197</t>
+    <t xml:space="preserve">6.22049713134766</t>
   </si>
   <si>
     <t xml:space="preserve">6.18146276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16612768173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06575202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99465274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01556491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95980024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91937065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84269523620605</t>
+    <t xml:space="preserve">6.16612672805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0657525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99465322494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01556444168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95980072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91937112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84269618988037</t>
   </si>
   <si>
     <t xml:space="preserve">5.83433055877686</t>
@@ -2183,28 +2183,28 @@
     <t xml:space="preserve">5.76601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73256063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84966564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87894248962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96816444396973</t>
+    <t xml:space="preserve">5.7325611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88173055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84966659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87894153594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96816492080688</t>
   </si>
   <si>
     <t xml:space="preserve">5.9667706489563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93888902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97374153137207</t>
+    <t xml:space="preserve">5.93888854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97374105453491</t>
   </si>
   <si>
     <t xml:space="preserve">5.94307041168213</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">6.07132863998413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16334009170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14382219314575</t>
+    <t xml:space="preserve">6.16333961486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14382266998291</t>
   </si>
   <si>
     <t xml:space="preserve">6.19122171401978</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">6.29577922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3376030921936</t>
+    <t xml:space="preserve">6.33760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">6.31947946548462</t>
@@ -2249,52 +2249,52 @@
     <t xml:space="preserve">6.60248279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5704174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51186561584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49095439910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55229425430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54114198684692</t>
+    <t xml:space="preserve">6.57041788101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51186609268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49095487594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55229377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54114246368408</t>
   </si>
   <si>
     <t xml:space="preserve">6.54671859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49792432785034</t>
+    <t xml:space="preserve">6.4979248046875</t>
   </si>
   <si>
     <t xml:space="preserve">6.56763029098511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53277683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41288423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44355440139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51465368270874</t>
+    <t xml:space="preserve">6.53277730941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4128851890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44355487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5146541595459</t>
   </si>
   <si>
     <t xml:space="preserve">6.4895601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50350093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33481502532959</t>
+    <t xml:space="preserve">6.50350189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33481407165527</t>
   </si>
   <si>
     <t xml:space="preserve">6.31111431121826</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">6.32087373733521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15915679931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10478782653809</t>
+    <t xml:space="preserve">6.15915775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10478734970093</t>
   </si>
   <si>
     <t xml:space="preserve">6.03647565841675</t>
@@ -2315,49 +2315,49 @@
     <t xml:space="preserve">6.08666372299194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9249472618103</t>
+    <t xml:space="preserve">5.92494773864746</t>
   </si>
   <si>
     <t xml:space="preserve">5.91379451751709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94446516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80644941329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9305248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97652959823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06714677810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11315202713013</t>
+    <t xml:space="preserve">5.94446468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8064489364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93052434921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97652912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06714725494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11315155029297</t>
   </si>
   <si>
     <t xml:space="preserve">6.04344606399536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.118727684021</t>
+    <t xml:space="preserve">6.11872863769531</t>
   </si>
   <si>
     <t xml:space="preserve">6.13963937759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1926155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28044509887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3571195602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296585083008</t>
+    <t xml:space="preserve">6.19261598587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28044414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35712099075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296537399292</t>
   </si>
   <si>
     <t xml:space="preserve">6.59829998016357</t>
@@ -2366,91 +2366,91 @@
     <t xml:space="preserve">6.68055200576782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63036489486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66382312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72655868530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66242790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63454675674438</t>
+    <t xml:space="preserve">6.63036394119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66382265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72655773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66242933273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63454723358154</t>
   </si>
   <si>
     <t xml:space="preserve">6.7614107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95100975036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803218841553</t>
+    <t xml:space="preserve">6.95100831985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803266525269</t>
   </si>
   <si>
     <t xml:space="preserve">6.90779161453247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94682598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04371643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95379734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98446750640869</t>
+    <t xml:space="preserve">6.94682645797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04371690750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95379686355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98446893692017</t>
   </si>
   <si>
     <t xml:space="preserve">6.95658493041992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76419925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8464503288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8157811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83390426635742</t>
+    <t xml:space="preserve">6.76419973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84645080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83390378952026</t>
   </si>
   <si>
     <t xml:space="preserve">6.79347515106201</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80462741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0332612991333</t>
+    <t xml:space="preserve">6.80462789535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03326082229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.19009780883789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27025938034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481594085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40269947052002</t>
+    <t xml:space="preserve">7.27025842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40269994735718</t>
   </si>
   <si>
     <t xml:space="preserve">7.38178730010986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36087560653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43058109283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50377130508423</t>
+    <t xml:space="preserve">7.36087608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43058204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5037727355957</t>
   </si>
   <si>
     <t xml:space="preserve">7.55953598022461</t>
@@ -2459,109 +2459,109 @@
     <t xml:space="preserve">7.552565574646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58044767379761</t>
+    <t xml:space="preserve">7.58044672012329</t>
   </si>
   <si>
     <t xml:space="preserve">7.44103717803955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42361116409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48286104202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6431827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59438896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51422691345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27374505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42012548446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35390615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51857566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48940515518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752643585205</t>
+    <t xml:space="preserve">7.4236102104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48285961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64318227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59438800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51422786712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27374601364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42012500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35390472412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51857471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48940467834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752595901489</t>
   </si>
   <si>
     <t xml:space="preserve">7.52586698532104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49669742584229</t>
+    <t xml:space="preserve">7.49669694900513</t>
   </si>
   <si>
     <t xml:space="preserve">7.47481918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52951240539551</t>
+    <t xml:space="preserve">7.52951288223267</t>
   </si>
   <si>
     <t xml:space="preserve">7.40189409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33261632919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29250621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35449314117432</t>
+    <t xml:space="preserve">7.33261489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35449266433716</t>
   </si>
   <si>
     <t xml:space="preserve">7.32532262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34720039367676</t>
+    <t xml:space="preserve">7.3471999168396</t>
   </si>
   <si>
     <t xml:space="preserve">7.22687387466431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3727240562439</t>
+    <t xml:space="preserve">7.37272310256958</t>
   </si>
   <si>
     <t xml:space="preserve">7.38366317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24437618255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31438493728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28229761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35813856124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21958160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15686559677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22979116439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16415882110596</t>
+    <t xml:space="preserve">7.24437570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31438398361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28229713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35813903808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28521490097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21958065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15686655044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22979164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1641583442688</t>
   </si>
   <si>
     <t xml:space="preserve">7.18457794189453</t>
@@ -2576,97 +2576,97 @@
     <t xml:space="preserve">7.21812343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17874383926392</t>
+    <t xml:space="preserve">7.17874336242676</t>
   </si>
   <si>
     <t xml:space="preserve">7.1802020072937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08540010452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15832471847534</t>
+    <t xml:space="preserve">7.08539867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15832424163818</t>
   </si>
   <si>
     <t xml:space="preserve">7.11019372940063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05768775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07810735702515</t>
+    <t xml:space="preserve">7.05768871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07810688018799</t>
   </si>
   <si>
     <t xml:space="preserve">6.99643135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93809080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97309446334839</t>
+    <t xml:space="preserve">6.93809127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97309541702271</t>
   </si>
   <si>
     <t xml:space="preserve">6.77328014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98622179031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93371534347534</t>
+    <t xml:space="preserve">6.9862208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9337158203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.75286102294922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57200765609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71931552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80536794662476</t>
+    <t xml:space="preserve">6.5720067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71931457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8053674697876</t>
   </si>
   <si>
     <t xml:space="preserve">6.98038721084595</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86954164505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00372409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04164409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06060552597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06206369400024</t>
+    <t xml:space="preserve">6.86954069137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00372362136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04164457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06060457229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0620641708374</t>
   </si>
   <si>
     <t xml:space="preserve">7.00518131256104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03289318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99351453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86370706558228</t>
+    <t xml:space="preserve">7.03289270401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99351406097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86370754241943</t>
   </si>
   <si>
     <t xml:space="preserve">6.45240926742554</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42178106307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38677835464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23363447189331</t>
+    <t xml:space="preserve">6.42178153991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38677787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23363494873047</t>
   </si>
   <si>
     <t xml:space="preserve">5.97256231307983</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">5.76253890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71003293991089</t>
+    <t xml:space="preserve">5.71003246307373</t>
   </si>
   <si>
     <t xml:space="preserve">5.63564920425415</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">5.39937162399292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28415012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52281284332275</t>
+    <t xml:space="preserve">5.28415060043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5228123664856</t>
   </si>
   <si>
     <t xml:space="preserve">4.21215152740479</t>
@@ -2696,10 +2696,10 @@
     <t xml:space="preserve">4.33174848556519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5222806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77605986595154</t>
+    <t xml:space="preserve">3.52228045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77606010437012</t>
   </si>
   <si>
     <t xml:space="preserve">3.33850979804993</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">3.25537514686584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06649875640869</t>
+    <t xml:space="preserve">3.06649899482727</t>
   </si>
   <si>
     <t xml:space="preserve">3.0424337387085</t>
@@ -2717,37 +2717,37 @@
     <t xml:space="preserve">3.10150289535522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17661571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61854195594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90440821647644</t>
+    <t xml:space="preserve">3.17661595344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61854219436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90440797805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.01087856292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76439237594604</t>
+    <t xml:space="preserve">3.76439189910889</t>
   </si>
   <si>
     <t xml:space="preserve">3.62802195549011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66667199134827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64917016029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77460193634033</t>
+    <t xml:space="preserve">3.66667222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64917063713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77460122108459</t>
   </si>
   <si>
     <t xml:space="preserve">3.70605182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97149991989136</t>
+    <t xml:space="preserve">3.97149920463562</t>
   </si>
   <si>
     <t xml:space="preserve">4.05171680450439</t>
@@ -2762,52 +2762,52 @@
     <t xml:space="preserve">3.87232136726379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57989120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64771151542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69292497634888</t>
+    <t xml:space="preserve">3.57989144325256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64771223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69292521476746</t>
   </si>
   <si>
     <t xml:space="preserve">3.56238985061646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51571798324585</t>
+    <t xml:space="preserve">3.51571774482727</t>
   </si>
   <si>
     <t xml:space="preserve">3.73959732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82419037818909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545554161072</t>
+    <t xml:space="preserve">3.82419061660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545530319214</t>
   </si>
   <si>
     <t xml:space="preserve">4.02254676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85627746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79939603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76585030555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75855755805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74834871292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78918647766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607594490051</t>
+    <t xml:space="preserve">3.85627794265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.799396276474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76585054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75855779647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74834847450256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78918671607971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607618331909</t>
   </si>
   <si>
     <t xml:space="preserve">3.85336065292358</t>
@@ -2816,34 +2816,34 @@
     <t xml:space="preserve">3.68271613121033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56311893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80960536003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74980688095093</t>
+    <t xml:space="preserve">3.56311869621277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80960559844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74980735778809</t>
   </si>
   <si>
     <t xml:space="preserve">3.69730067253113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921107292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256284713745</t>
+    <t xml:space="preserve">3.77168416976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78481078147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921083450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256332397461</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862258911133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25590753555298</t>
+    <t xml:space="preserve">4.25590705871582</t>
   </si>
   <si>
     <t xml:space="preserve">4.60011291503906</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">4.69929122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95452976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95307064056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18351316452026</t>
+    <t xml:space="preserve">4.95452880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95307016372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18351364135742</t>
   </si>
   <si>
     <t xml:space="preserve">5.34540700912476</t>
@@ -2867,43 +2867,43 @@
     <t xml:space="preserve">5.17330408096313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07996034622192</t>
+    <t xml:space="preserve">5.07995986938477</t>
   </si>
   <si>
     <t xml:space="preserve">4.86410188674927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96473836898804</t>
+    <t xml:space="preserve">4.9647388458252</t>
   </si>
   <si>
     <t xml:space="preserve">5.03766345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16455364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13975858688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23164415359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12079811096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97348880767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.996826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71095943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75033903121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55927515029907</t>
+    <t xml:space="preserve">5.16455268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1397590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23164463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12079763412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97348976135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99682569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71095895767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75033855438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55927467346191</t>
   </si>
   <si>
     <t xml:space="preserve">4.76200723648071</t>
@@ -2915,52 +2915,52 @@
     <t xml:space="preserve">4.71533489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91952514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90348196029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92535877227783</t>
+    <t xml:space="preserve">4.91952466964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90348148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92535924911499</t>
   </si>
   <si>
     <t xml:space="preserve">4.93119335174561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88014507293701</t>
+    <t xml:space="preserve">4.88014554977417</t>
   </si>
   <si>
     <t xml:space="preserve">4.79701089859009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92973470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05078983306885</t>
+    <t xml:space="preserve">4.9297342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05079030990601</t>
   </si>
   <si>
     <t xml:space="preserve">5.13830041885376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14559316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16601181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13246631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25206327438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25498056411743</t>
+    <t xml:space="preserve">5.14559268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16601133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13246583938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25206279754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25498008728027</t>
   </si>
   <si>
     <t xml:space="preserve">5.316237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22435188293457</t>
+    <t xml:space="preserve">5.22435140609741</t>
   </si>
   <si>
     <t xml:space="preserve">5.16309452056885</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">5.07850170135498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05954122543335</t>
+    <t xml:space="preserve">5.05954074859619</t>
   </si>
   <si>
     <t xml:space="preserve">4.92244148254395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94286060333252</t>
+    <t xml:space="preserve">4.94286108016968</t>
   </si>
   <si>
     <t xml:space="preserve">4.73283672332764</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">4.81305408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94723653793335</t>
+    <t xml:space="preserve">4.94723701477051</t>
   </si>
   <si>
     <t xml:space="preserve">4.91369104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97786521911621</t>
+    <t xml:space="preserve">4.97786569595337</t>
   </si>
   <si>
     <t xml:space="preserve">5.27248191833496</t>
@@ -3002,28 +3002,28 @@
     <t xml:space="preserve">5.28706741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29435968399048</t>
+    <t xml:space="preserve">5.29436063766479</t>
   </si>
   <si>
     <t xml:space="preserve">5.20247411727905</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1149640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24622964859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12809133529663</t>
+    <t xml:space="preserve">5.11496448516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24622917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12809085845947</t>
   </si>
   <si>
     <t xml:space="preserve">5.09746217727661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24768781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27685737609863</t>
+    <t xml:space="preserve">5.24768829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27685785293579</t>
   </si>
   <si>
     <t xml:space="preserve">5.4445858001709</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">5.47813129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42416620254517</t>
+    <t xml:space="preserve">5.42416667938232</t>
   </si>
   <si>
     <t xml:space="preserve">5.31040334701538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33519744873047</t>
+    <t xml:space="preserve">5.33519840240479</t>
   </si>
   <si>
     <t xml:space="preserve">5.32061338424683</t>
@@ -3047,34 +3047,34 @@
     <t xml:space="preserve">5.22726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21414184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08141851425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17767906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39207935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28269195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29873466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18643140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08725309371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89910554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89327192306519</t>
+    <t xml:space="preserve">5.21414232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08141946792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17768001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39207887649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28269147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18643093109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08725261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8991060256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89327144622803</t>
   </si>
   <si>
     <t xml:space="preserve">4.87722873687744</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">4.8757700920105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88452100753784</t>
+    <t xml:space="preserve">4.884521484375</t>
   </si>
   <si>
     <t xml:space="preserve">4.84368324279785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92390060424805</t>
+    <t xml:space="preserve">4.92390012741089</t>
   </si>
   <si>
     <t xml:space="preserve">5.08871126174927</t>
@@ -3104,25 +3104,25 @@
     <t xml:space="preserve">5.20976638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08579444885254</t>
+    <t xml:space="preserve">5.08579397201538</t>
   </si>
   <si>
     <t xml:space="preserve">5.28560924530029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23310279846191</t>
+    <t xml:space="preserve">5.23310327529907</t>
   </si>
   <si>
     <t xml:space="preserve">5.203932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0114107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02016115188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180547714233</t>
+    <t xml:space="preserve">5.01141023635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0201621055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180643081665</t>
   </si>
   <si>
     <t xml:space="preserve">4.84222459793091</t>
@@ -3134,16 +3134,16 @@
     <t xml:space="preserve">4.84951686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74012899398804</t>
+    <t xml:space="preserve">4.7401294708252</t>
   </si>
   <si>
     <t xml:space="preserve">4.74596357345581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78971767425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76638221740723</t>
+    <t xml:space="preserve">4.78971815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76638269424438</t>
   </si>
   <si>
     <t xml:space="preserve">4.64095163345337</t>
@@ -3152,34 +3152,34 @@
     <t xml:space="preserve">4.41050815582275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46884775161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43967771530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59427881240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85680866241455</t>
+    <t xml:space="preserve">4.46884822845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43967819213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59427928924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85680913925171</t>
   </si>
   <si>
     <t xml:space="preserve">5.30894470214844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19664096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20539093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51605272293091</t>
+    <t xml:space="preserve">5.1966404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20539140701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51605176925659</t>
   </si>
   <si>
     <t xml:space="preserve">5.59626960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51459407806396</t>
+    <t xml:space="preserve">5.51459360122681</t>
   </si>
   <si>
     <t xml:space="preserve">5.58460140228271</t>
@@ -3197,82 +3197,82 @@
     <t xml:space="preserve">5.70419883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63710737228394</t>
+    <t xml:space="preserve">5.63710784912109</t>
   </si>
   <si>
     <t xml:space="preserve">5.45041942596436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52917814254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46500492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54230499267578</t>
+    <t xml:space="preserve">5.52917861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46500444412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54230451583862</t>
   </si>
   <si>
     <t xml:space="preserve">5.60210371017456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53209543228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4897985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49709129333496</t>
+    <t xml:space="preserve">5.53209590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48979902267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49709177017212</t>
   </si>
   <si>
     <t xml:space="preserve">5.4752140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34978294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36145067214966</t>
+    <t xml:space="preserve">5.34978342056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36145114898682</t>
   </si>
   <si>
     <t xml:space="preserve">5.53792953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49271583557129</t>
+    <t xml:space="preserve">5.49271631240845</t>
   </si>
   <si>
     <t xml:space="preserve">5.428542137146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39062166213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3789529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52042722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52480316162109</t>
+    <t xml:space="preserve">5.39062118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37895345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52042770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52480363845825</t>
   </si>
   <si>
     <t xml:space="preserve">5.40228891372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42270851135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62835597991943</t>
+    <t xml:space="preserve">5.42270755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62835693359375</t>
   </si>
   <si>
     <t xml:space="preserve">5.61231327056885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50438356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46208667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51021814346313</t>
+    <t xml:space="preserve">5.50438451766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46208715438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51021766662598</t>
   </si>
   <si>
     <t xml:space="preserve">5.46937990188599</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">5.44750213623047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38186979293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47083806991577</t>
+    <t xml:space="preserve">5.38187026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47083902359009</t>
   </si>
   <si>
     <t xml:space="preserve">5.40083026885986</t>
@@ -3293,70 +3293,70 @@
     <t xml:space="preserve">5.40520620346069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44896173477173</t>
+    <t xml:space="preserve">5.44896078109741</t>
   </si>
   <si>
     <t xml:space="preserve">5.35707569122314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39499568939209</t>
+    <t xml:space="preserve">5.39499616622925</t>
   </si>
   <si>
     <t xml:space="preserve">5.370201587677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51167678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73045110702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89963865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97985458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17383575439453</t>
+    <t xml:space="preserve">5.51167631149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73045206069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8996376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97985506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17383623123169</t>
   </si>
   <si>
     <t xml:space="preserve">6.23071765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41740608215332</t>
+    <t xml:space="preserve">6.41740560531616</t>
   </si>
   <si>
     <t xml:space="preserve">6.50637435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48012161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59242582321167</t>
+    <t xml:space="preserve">6.48012113571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59242725372314</t>
   </si>
   <si>
     <t xml:space="preserve">6.53700351715088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57930040359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54429578781128</t>
+    <t xml:space="preserve">6.57929992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54429531097412</t>
   </si>
   <si>
     <t xml:space="preserve">6.62159585952759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61430358886719</t>
+    <t xml:space="preserve">6.61430311203003</t>
   </si>
   <si>
     <t xml:space="preserve">6.58221673965454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53408622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39552783966064</t>
+    <t xml:space="preserve">6.53408575057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3955283164978</t>
   </si>
   <si>
     <t xml:space="preserve">6.28468227386475</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">6.43490839004517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52679300308228</t>
+    <t xml:space="preserve">6.52679347991943</t>
   </si>
   <si>
     <t xml:space="preserve">6.61138677597046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72514963150024</t>
+    <t xml:space="preserve">6.72514915466309</t>
   </si>
   <si>
     <t xml:space="preserve">6.73535919189453</t>
@@ -3383,28 +3383,28 @@
     <t xml:space="preserve">6.77473878860474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85058116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86516618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90162897109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01976728439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09415054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09706830978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87975072860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84037160873413</t>
+    <t xml:space="preserve">6.8505802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86516571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9016284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01976633071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09415006637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09706735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87975025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84037065505981</t>
   </si>
   <si>
     <t xml:space="preserve">6.77911376953125</t>
@@ -3413,31 +3413,31 @@
     <t xml:space="preserve">6.90016984939575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92058849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9395489692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0358099937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89579486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84912204742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86079025268555</t>
+    <t xml:space="preserve">6.90600442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92058944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93954992294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03581094741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89579439163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84912252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86079072952271</t>
   </si>
   <si>
     <t xml:space="preserve">6.77182197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80682516098022</t>
+    <t xml:space="preserve">6.80682563781738</t>
   </si>
   <si>
     <t xml:space="preserve">6.81849384307861</t>
@@ -3446,52 +3446,52 @@
     <t xml:space="preserve">6.80974292755127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78640604019165</t>
+    <t xml:space="preserve">6.78640651702881</t>
   </si>
   <si>
     <t xml:space="preserve">6.8520393371582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84766435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7091064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.642014503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805864334106</t>
+    <t xml:space="preserve">6.84766387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70910692214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64201402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805816650391</t>
   </si>
   <si>
     <t xml:space="preserve">6.64639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8359956741333</t>
+    <t xml:space="preserve">6.83599519729614</t>
   </si>
   <si>
     <t xml:space="preserve">6.80828428268433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82724571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85641527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92788124084473</t>
+    <t xml:space="preserve">6.82724523544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85641479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92788076400757</t>
   </si>
   <si>
     <t xml:space="preserve">6.78057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90891981124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94684219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04018592834473</t>
+    <t xml:space="preserve">6.9089207649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9468412399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04018640518188</t>
   </si>
   <si>
     <t xml:space="preserve">7.05477142333984</t>
@@ -3500,100 +3500,100 @@
     <t xml:space="preserve">7.01393270492554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08394050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1335301399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19770431518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06643867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0533127784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102464675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915468215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11748647689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14811611175537</t>
+    <t xml:space="preserve">7.08394145965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13352966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19770383834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05914735794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0664381980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05331230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915372848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11748695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14811563491821</t>
   </si>
   <si>
     <t xml:space="preserve">7.21228981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27062940597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344533920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29979991912842</t>
+    <t xml:space="preserve">7.27063083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30344486236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2997989654541</t>
   </si>
   <si>
     <t xml:space="preserve">7.25604391098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2677116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20791292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26333665847778</t>
+    <t xml:space="preserve">7.26771211624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20791339874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26333618164062</t>
   </si>
   <si>
     <t xml:space="preserve">7.2545862197876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23270893096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23562526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17582702636719</t>
+    <t xml:space="preserve">7.23270845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23562479019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17582750320435</t>
   </si>
   <si>
     <t xml:space="preserve">7.22249937057495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27500486373901</t>
+    <t xml:space="preserve">7.28083848953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27500438690186</t>
   </si>
   <si>
     <t xml:space="preserve">7.20062065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18311977386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19332885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18749523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36178588867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1408224105835</t>
+    <t xml:space="preserve">7.18311882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19332933425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18749475479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36178493499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14082288742065</t>
   </si>
   <si>
     <t xml:space="preserve">7.14957332611084</t>
@@ -3605,85 +3605,85 @@
     <t xml:space="preserve">7.11165237426758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18895244598389</t>
+    <t xml:space="preserve">7.1889533996582</t>
   </si>
   <si>
     <t xml:space="preserve">7.20499658584595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14519882202148</t>
+    <t xml:space="preserve">7.14519786834717</t>
   </si>
   <si>
     <t xml:space="preserve">7.09560918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86808252334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95559310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23416662216187</t>
+    <t xml:space="preserve">6.86808347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95559215545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23416709899902</t>
   </si>
   <si>
     <t xml:space="preserve">7.31073760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28667259216309</t>
+    <t xml:space="preserve">7.28667211532593</t>
   </si>
   <si>
     <t xml:space="preserve">7.28813171386719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24145984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13207101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21082973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28375577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29615354537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1904125213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2779221534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27354621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17145013809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0460205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09852600097656</t>
+    <t xml:space="preserve">7.24145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13207197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2108302116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2837553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29615259170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19041156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27792119979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27354669570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17728567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1714506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04601955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09852647781372</t>
   </si>
   <si>
     <t xml:space="preserve">7.13644742965698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25166845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.279381275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456823348999</t>
+    <t xml:space="preserve">7.25166940689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27937984466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456966400146</t>
   </si>
   <si>
     <t xml:space="preserve">7.24875116348267</t>
@@ -3692,448 +3692,448 @@
     <t xml:space="preserve">7.36543226242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47846603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33626174926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53680562973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61337757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68630218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58785390853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734903335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50398921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21520662307739</t>
+    <t xml:space="preserve">7.47846508026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33626127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53680515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61337614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68630170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5878529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50399017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294141769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21520566940308</t>
   </si>
   <si>
     <t xml:space="preserve">7.38001728057861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41283178329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43106460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53315925598145</t>
+    <t xml:space="preserve">7.41283321380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43106269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53316020965576</t>
   </si>
   <si>
     <t xml:space="preserve">7.5805606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60608530044556</t>
+    <t xml:space="preserve">7.60608386993408</t>
   </si>
   <si>
     <t xml:space="preserve">7.55868291854858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52222013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64254713058472</t>
+    <t xml:space="preserve">7.52222061157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6425461769104</t>
   </si>
   <si>
     <t xml:space="preserve">7.67171716690063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77016592025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76652050018311</t>
+    <t xml:space="preserve">7.77016544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76651906967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.88684558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87590837478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81392192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81756830215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89778518676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507745742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955331802368</t>
+    <t xml:space="preserve">7.8759069442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81392097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81756782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.879554271698</t>
   </si>
   <si>
     <t xml:space="preserve">7.79204320907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74828815460205</t>
+    <t xml:space="preserve">7.74828863143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90313339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72111129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45352554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56398296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59976434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63865756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79034185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591474533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86034965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82534551620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80978870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71488904953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76156044006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84868097305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80589914321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52197742462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64954805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68999719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8136773109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86423921585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9264669418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0859317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10148811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07815265655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07037353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13260364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23761558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17538547515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09759998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03537082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02370166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61532163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66043853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77867412567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02759075164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10926723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79812002182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05870532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22983741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20650196075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14427185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90702104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07426357269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88368654251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9381365776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77556276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67288446426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67755031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26994800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29172801971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25439167022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68654823303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73477554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68499231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12337207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95379686355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08603429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63520812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3193941116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35050868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61187267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66165590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970830917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06925868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22638750076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06770324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12993288040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02103090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0505895614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22949838638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10659646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17193698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30417537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11904287338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97902631759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89190483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03503322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02569770812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94946718215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1128191947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19527387619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44885873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17971563339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38196182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38040590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686147689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74755907058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50486469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48308515548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60598707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54842567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71955585479736</t>
   </si>
   <si>
     <t xml:space="preserve">7.70088672637939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90313243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7226676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72111225128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352458953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56398296356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59976434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63865756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79034185409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86034965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82534599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80978870391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71488952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311635971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76155996322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84868192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80589914321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5219783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64954710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68999576568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81367683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86423921585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92646884918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0859317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10148906707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08204174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07815361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07037353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13260364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23761558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17538738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09759998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03536987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02370071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61532163619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6604380607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77867364883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02759170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10926723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79812049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05870628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22983646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20650100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14427185058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90702104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88368511199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9381365776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77556276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67288494110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67755126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26994848251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29172849655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25439167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68654823303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73477554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68499231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12337255477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95379686355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08603429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63520860671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3193941116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35050916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61187267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66165637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06925916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2263879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06770324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12993192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02103137969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05059003829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22949886322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10659599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17193794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30417537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11904239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97902584075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89190483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03503274917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02569770812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94946718215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11281967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19527339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18438291549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44885778427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17971563339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1641583442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38196134567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38040590286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686147689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74755954742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50486421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48308324813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60598754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54842567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71955633163452</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.71022129058838</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52353429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44574594497681</t>
+    <t xml:space="preserve">7.5235333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44574546813965</t>
   </si>
   <si>
     <t xml:space="preserve">7.38973951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43485546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26217079162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34151172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41152000427246</t>
+    <t xml:space="preserve">7.43485593795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26216983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34151268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752691268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41152095794678</t>
   </si>
   <si>
     <t xml:space="preserve">7.46908235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43174409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32906579971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42085456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.534423828125</t>
+    <t xml:space="preserve">7.4317455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32906675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42085552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442239761353</t>
   </si>
   <si>
     <t xml:space="preserve">7.49864149093628</t>
@@ -4145,37 +4145,37 @@
     <t xml:space="preserve">7.50797605514526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01325178146362</t>
+    <t xml:space="preserve">7.01325225830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.90435123443604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96813631057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95102310180664</t>
+    <t xml:space="preserve">6.96813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95102262496948</t>
   </si>
   <si>
     <t xml:space="preserve">6.63054180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59631538391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68188142776489</t>
+    <t xml:space="preserve">6.59631490707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68188047409058</t>
   </si>
   <si>
     <t xml:space="preserve">6.74410963058472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71921825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56831216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71143960952759</t>
+    <t xml:space="preserve">6.7192177772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5683126449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71144008636475</t>
   </si>
   <si>
     <t xml:space="preserve">6.56675672531128</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">6.60253810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42362880706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41896152496338</t>
+    <t xml:space="preserve">6.42362928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41896200180054</t>
   </si>
   <si>
     <t xml:space="preserve">6.38784694671631</t>
@@ -4199,31 +4199,31 @@
     <t xml:space="preserve">6.2322735786438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32406234741211</t>
+    <t xml:space="preserve">6.32406187057495</t>
   </si>
   <si>
     <t xml:space="preserve">6.45785474777222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55586671829224</t>
+    <t xml:space="preserve">6.55586624145508</t>
   </si>
   <si>
     <t xml:space="preserve">6.4905252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41273880004883</t>
+    <t xml:space="preserve">6.41273832321167</t>
   </si>
   <si>
     <t xml:space="preserve">6.3582878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05958652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05491971969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20115804672241</t>
+    <t xml:space="preserve">6.05958700180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0549201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20115900039673</t>
   </si>
   <si>
     <t xml:space="preserve">6.33339643478394</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">6.26027679443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22138357162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24783086776733</t>
+    <t xml:space="preserve">6.2213830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24783039093018</t>
   </si>
   <si>
     <t xml:space="preserve">6.17937850952148</t>
@@ -4250,13 +4250,13 @@
     <t xml:space="preserve">6.50297069549561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54653167724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55119895935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59787130355835</t>
+    <t xml:space="preserve">6.54653310775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55119943618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59787082672119</t>
   </si>
   <si>
     <t xml:space="preserve">6.64921045303345</t>
@@ -4268,22 +4268,22 @@
     <t xml:space="preserve">6.65232181549072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64298725128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66010093688965</t>
+    <t xml:space="preserve">6.64298820495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66009998321533</t>
   </si>
   <si>
     <t xml:space="preserve">6.72544145584106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77055883407593</t>
+    <t xml:space="preserve">6.77055835723877</t>
   </si>
   <si>
     <t xml:space="preserve">6.77833652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72233057022095</t>
+    <t xml:space="preserve">6.72232961654663</t>
   </si>
   <si>
     <t xml:space="preserve">6.69588232040405</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">6.44696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27427864074707</t>
+    <t xml:space="preserve">6.27427816390991</t>
   </si>
   <si>
     <t xml:space="preserve">6.32250642776489</t>
@@ -4325,61 +4325,61 @@
     <t xml:space="preserve">6.21204900741577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19493675231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22916221618652</t>
+    <t xml:space="preserve">6.19493579864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22916269302368</t>
   </si>
   <si>
     <t xml:space="preserve">6.28672409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44229698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58075857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58698081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65387725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63365316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57764720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61031675338745</t>
+    <t xml:space="preserve">6.44229745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58075761795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58698129653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65387773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63365268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57764673233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61031723022461</t>
   </si>
   <si>
     <t xml:space="preserve">6.37540102005005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48274660110474</t>
+    <t xml:space="preserve">6.48274707794189</t>
   </si>
   <si>
     <t xml:space="preserve">6.44074201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20893716812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09381341934204</t>
+    <t xml:space="preserve">6.2089376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09381294250488</t>
   </si>
   <si>
     <t xml:space="preserve">6.03313970565796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92112636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59009313583374</t>
+    <t xml:space="preserve">5.92112684249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26961183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59009265899658</t>
   </si>
   <si>
     <t xml:space="preserve">6.48119115829468</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">6.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19649171829224</t>
+    <t xml:space="preserve">6.19649076461792</t>
   </si>
   <si>
     <t xml:space="preserve">6.18248987197876</t>
@@ -4397,22 +4397,22 @@
     <t xml:space="preserve">6.10003566741943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28361320495605</t>
+    <t xml:space="preserve">6.2836127281189</t>
   </si>
   <si>
     <t xml:space="preserve">6.45629930496216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52164030075073</t>
+    <t xml:space="preserve">6.52164077758789</t>
   </si>
   <si>
     <t xml:space="preserve">6.67877006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85612344741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84989976882935</t>
+    <t xml:space="preserve">6.85612297058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8499002456665</t>
   </si>
   <si>
     <t xml:space="preserve">6.85767936706543</t>
@@ -4421,145 +4421,145 @@
     <t xml:space="preserve">7.07081460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10348463058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13459920883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09726142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19060611724854</t>
+    <t xml:space="preserve">7.10348510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1346001625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09726238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19060564041138</t>
   </si>
   <si>
     <t xml:space="preserve">7.15326881408691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31039810180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49241781234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52820014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57954025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6339898109436</t>
+    <t xml:space="preserve">7.31039762496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49241876602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52820110321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57953929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63399076461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.74289226531982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9148006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90892219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91228055953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93243551254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87029218673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83502292633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77287912368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73760938644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6956205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71409559249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73928928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68554449081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63515901565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6586709022522</t>
+    <t xml:space="preserve">7.91480112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90892314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91228151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93243598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87029314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83502340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7728796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73760986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69562101364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71409606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73928880691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68554496765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63515758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65867233276367</t>
   </si>
   <si>
     <t xml:space="preserve">7.71073770523071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69394302368164</t>
+    <t xml:space="preserve">7.69394159317017</t>
   </si>
   <si>
     <t xml:space="preserve">7.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79471397399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48064136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50415515899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52934741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6637110710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56965684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58477163314819</t>
+    <t xml:space="preserve">7.79471445083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48064184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50415468215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52934789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66371059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56965732574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58477210998535</t>
   </si>
   <si>
     <t xml:space="preserve">7.5864520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53774499893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64691543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54446315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59484958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6721076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79807424545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78463792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77959775924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85685586929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90052509307861</t>
+    <t xml:space="preserve">7.53774547576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64691495895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54446363449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59485006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67210817337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79807329177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78463745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77959823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85685729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90052461624146</t>
   </si>
   <si>
     <t xml:space="preserve">8.02145099639893</t>
@@ -4574,22 +4574,22 @@
     <t xml:space="preserve">8.09535026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11046695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01977062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92403745651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04496479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08191299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13230037689209</t>
+    <t xml:space="preserve">8.11046600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01977157592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92403841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04496383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08191394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13230133056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.18100643157959</t>
@@ -4610,7 +4610,7 @@
     <t xml:space="preserve">8.37247371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39430904388428</t>
+    <t xml:space="preserve">8.39430809020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.4312572479248</t>
@@ -4619,46 +4619,46 @@
     <t xml:space="preserve">8.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54042720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56981945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69998264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56561946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7083797454834</t>
+    <t xml:space="preserve">8.54042625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5698184967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69998168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56562042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70838069915771</t>
   </si>
   <si>
     <t xml:space="preserve">8.74197101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60340976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63280010223389</t>
+    <t xml:space="preserve">8.60340881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6328010559082</t>
   </si>
   <si>
     <t xml:space="preserve">8.61180686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50263786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49423980712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39094829559326</t>
+    <t xml:space="preserve">8.50263690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49423885345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39094734191895</t>
   </si>
   <si>
     <t xml:space="preserve">8.41026306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25490570068359</t>
+    <t xml:space="preserve">8.25490665435791</t>
   </si>
   <si>
     <t xml:space="preserve">8.42285919189453</t>
@@ -4667,55 +4667,55 @@
     <t xml:space="preserve">8.48164367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37415409088135</t>
+    <t xml:space="preserve">8.37415313720703</t>
   </si>
   <si>
     <t xml:space="preserve">8.36407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45644855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51103496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46064949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51523399353027</t>
+    <t xml:space="preserve">8.45645046234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51103591918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46064853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51523303985596</t>
   </si>
   <si>
     <t xml:space="preserve">8.40186595916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16757011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80143260955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99793672561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5495023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52095127105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43193578720093</t>
+    <t xml:space="preserve">8.16757106781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80143165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99793815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54950189590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52095031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43193483352661</t>
   </si>
   <si>
     <t xml:space="preserve">7.73425054550171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63180017471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5528621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51591157913208</t>
+    <t xml:space="preserve">7.63179922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55286169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51591110229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.60660552978516</t>
@@ -4724,76 +4724,76 @@
     <t xml:space="preserve">7.7241735458374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78295707702637</t>
+    <t xml:space="preserve">7.78295660018921</t>
   </si>
   <si>
     <t xml:space="preserve">7.8115086555481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8098292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74096965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075609207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92739677429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93915510177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09366989135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02648830413818</t>
+    <t xml:space="preserve">7.80982971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74096918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075704574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92739772796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93915367126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09367084503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0264892578125</t>
   </si>
   <si>
     <t xml:space="preserve">8.18772411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21795749664307</t>
+    <t xml:space="preserve">8.21795654296875</t>
   </si>
   <si>
     <t xml:space="preserve">8.14909648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21291732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17261028289795</t>
+    <t xml:space="preserve">8.21291828155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17260932922363</t>
   </si>
   <si>
     <t xml:space="preserve">8.19780254364014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26834106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17092895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8921275138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19444274902344</t>
+    <t xml:space="preserve">8.26834201812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89212703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19444370269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.09703063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3808708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766597747803</t>
+    <t xml:space="preserve">8.38086986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766693115234</t>
   </si>
   <si>
     <t xml:space="preserve">8.34056282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36575508117676</t>
+    <t xml:space="preserve">8.36575603485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.13565921783447</t>
@@ -4805,10 +4805,10 @@
     <t xml:space="preserve">8.18436622619629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25322723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27338218688965</t>
+    <t xml:space="preserve">8.25322532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27338123321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895992279053</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">8.42705821990967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5446252822876</t>
+    <t xml:space="preserve">8.54462623596191</t>
   </si>
   <si>
     <t xml:space="preserve">8.7335729598999</t>
@@ -4826,46 +4826,46 @@
     <t xml:space="preserve">8.7713623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67898845672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67478942871094</t>
+    <t xml:space="preserve">8.67898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67479038238525</t>
   </si>
   <si>
     <t xml:space="preserve">8.6453971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92252063751221</t>
+    <t xml:space="preserve">8.92252159118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.98970222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98130321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96450901031494</t>
+    <t xml:space="preserve">8.90572452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98130416870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96450996398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.17025184631348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19124507904053</t>
+    <t xml:space="preserve">9.19124603271484</t>
   </si>
   <si>
     <t xml:space="preserve">9.28781986236572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38859081268311</t>
+    <t xml:space="preserve">9.38859176635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.49776172637939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39698886871338</t>
+    <t xml:space="preserve">9.39698791503906</t>
   </si>
   <si>
     <t xml:space="preserve">9.42638111114502</t>
@@ -4877,16 +4877,16 @@
     <t xml:space="preserve">9.30461406707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33400726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14925670623779</t>
+    <t xml:space="preserve">9.33400630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14925861358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.03588962554932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01909446716309</t>
+    <t xml:space="preserve">9.01909351348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.04848480224609</t>
@@ -4895,13 +4895,13 @@
     <t xml:space="preserve">9.06947994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20384216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34660243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35500144958496</t>
+    <t xml:space="preserve">9.20384311676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34660339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35500049591064</t>
   </si>
   <si>
     <t xml:space="preserve">9.27942180633545</t>
@@ -4910,13 +4910,13 @@
     <t xml:space="preserve">9.24583148956299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25002956390381</t>
+    <t xml:space="preserve">9.25003051757812</t>
   </si>
   <si>
     <t xml:space="preserve">9.25842761993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43058013916016</t>
+    <t xml:space="preserve">9.43057918548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.48936367034912</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">9.52295398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64891815185547</t>
+    <t xml:space="preserve">9.64891910552979</t>
   </si>
   <si>
     <t xml:space="preserve">9.60692977905273</t>
@@ -4940,28 +4940,28 @@
     <t xml:space="preserve">9.63632297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70770168304443</t>
+    <t xml:space="preserve">9.69930458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70770263671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.68250942230225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0394096374512</t>
+    <t xml:space="preserve">10.0394105911255</t>
   </si>
   <si>
     <t xml:space="preserve">10.1779718399048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0520067214966</t>
+    <t xml:space="preserve">10.0520076751709</t>
   </si>
   <si>
     <t xml:space="preserve">9.9554328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94703578948975</t>
+    <t xml:space="preserve">9.94703674316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.93863868713379</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">9.98062705993652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73289585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83366870880127</t>
+    <t xml:space="preserve">9.73289489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83366680145264</t>
   </si>
   <si>
     <t xml:space="preserve">9.85886001586914</t>
@@ -4985,16 +4985,16 @@
     <t xml:space="preserve">9.93024063110352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87565612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79167938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82526969909668</t>
+    <t xml:space="preserve">9.87565517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7916784286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7664852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.825270652771</t>
   </si>
   <si>
     <t xml:space="preserve">9.97222900390625</t>
@@ -5003,16 +5003,16 @@
     <t xml:space="preserve">9.92604160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9134464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0268135070801</t>
+    <t xml:space="preserve">9.91344547271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0268144607544</t>
   </si>
   <si>
     <t xml:space="preserve">10.1653747558594</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1947679519653</t>
+    <t xml:space="preserve">10.194766998291</t>
   </si>
   <si>
     <t xml:space="preserve">10.1359834671021</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">10.1401815414429</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1443796157837</t>
+    <t xml:space="preserve">10.144380569458</t>
   </si>
   <si>
     <t xml:space="preserve">10.2199592590332</t>
@@ -5045,7 +5045,7 @@
     <t xml:space="preserve">10.2115621566772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.303936958313</t>
+    <t xml:space="preserve">10.3039360046387</t>
   </si>
   <si>
     <t xml:space="preserve">10.2535514831543</t>
@@ -5054,16 +5054,16 @@
     <t xml:space="preserve">10.1905689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3291311264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173059463501</t>
+    <t xml:space="preserve">10.3291292190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173049926758</t>
   </si>
   <si>
     <t xml:space="preserve">10.3333292007446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2451524734497</t>
+    <t xml:space="preserve">10.245153427124</t>
   </si>
   <si>
     <t xml:space="preserve">10.2913408279419</t>
@@ -5078,10 +5078,10 @@
     <t xml:space="preserve">10.4676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5222749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3921127319336</t>
+    <t xml:space="preserve">10.5222768783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3921117782593</t>
   </si>
   <si>
     <t xml:space="preserve">10.3207321166992</t>
@@ -5090,10 +5090,10 @@
     <t xml:space="preserve">10.2745447158813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.203164100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1275863647461</t>
+    <t xml:space="preserve">10.2031650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1275854110718</t>
   </si>
   <si>
     <t xml:space="preserve">10.2283582687378</t>
@@ -5102,10 +5102,10 @@
     <t xml:space="preserve">10.2367553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2955389022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695747375488</t>
+    <t xml:space="preserve">10.295539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695737838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.1527786254883</t>
@@ -5123,25 +5123,25 @@
     <t xml:space="preserve">9.37179565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24163246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96870708465576</t>
+    <t xml:space="preserve">9.24163150787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96870803833008</t>
   </si>
   <si>
     <t xml:space="preserve">9.46417045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53135299682617</t>
+    <t xml:space="preserve">9.53135204315186</t>
   </si>
   <si>
     <t xml:space="preserve">9.58173751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65311717987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731716156006</t>
+    <t xml:space="preserve">9.65311813354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731620788574</t>
   </si>
   <si>
     <t xml:space="preserve">9.66991329193115</t>
@@ -5156,13 +5156,13 @@
     <t xml:space="preserve">9.69090747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98902416229248</t>
+    <t xml:space="preserve">9.9890251159668</t>
   </si>
   <si>
     <t xml:space="preserve">9.87985515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84817504882812</t>
+    <t xml:space="preserve">9.84817409515381</t>
   </si>
   <si>
     <t xml:space="preserve">9.73050308227539</t>
@@ -5183,25 +5183,25 @@
     <t xml:space="preserve">9.7395544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71239852905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78028678894043</t>
+    <t xml:space="preserve">9.71240043640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75313091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78028774261475</t>
   </si>
   <si>
     <t xml:space="preserve">9.72597694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65809059143066</t>
+    <t xml:space="preserve">9.65808963775635</t>
   </si>
   <si>
     <t xml:space="preserve">9.92511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0020513534546</t>
+    <t xml:space="preserve">10.0020523071289</t>
   </si>
   <si>
     <t xml:space="preserve">10.0744647979736</t>
@@ -5216,34 +5216,34 @@
     <t xml:space="preserve">10.0337324142456</t>
   </si>
   <si>
-    <t xml:space="preserve">10.069938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0654134750366</t>
+    <t xml:space="preserve">10.0699396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0654144287109</t>
   </si>
   <si>
     <t xml:space="preserve">10.1378259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0789918899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1785593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1514043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1151971817017</t>
+    <t xml:space="preserve">10.0789909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1785583496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.151403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.115198135376</t>
   </si>
   <si>
     <t xml:space="preserve">10.142352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.060887336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695079803467</t>
+    <t xml:space="preserve">10.0608863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695070266724</t>
   </si>
   <si>
     <t xml:space="preserve">10.2464456558228</t>
@@ -5252,16 +5252,16 @@
     <t xml:space="preserve">10.2736015319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2147645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102384567261</t>
+    <t xml:space="preserve">10.2147655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102394104004</t>
   </si>
   <si>
     <t xml:space="preserve">10.2011880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4455814361572</t>
+    <t xml:space="preserve">10.4455823898315</t>
   </si>
   <si>
     <t xml:space="preserve">10.7126045227051</t>
@@ -5294,10 +5294,10 @@
     <t xml:space="preserve">11.1063508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1335067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9388961791992</t>
+    <t xml:space="preserve">11.133505821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9388952255249</t>
   </si>
   <si>
     <t xml:space="preserve">11.0022563934326</t>
@@ -5309,19 +5309,19 @@
     <t xml:space="preserve">10.7669153213501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7171306610107</t>
+    <t xml:space="preserve">10.7171316146851</t>
   </si>
   <si>
     <t xml:space="preserve">10.5315723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4908399581909</t>
+    <t xml:space="preserve">10.4908390045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.4184274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3957977294922</t>
+    <t xml:space="preserve">10.3957967758179</t>
   </si>
   <si>
     <t xml:space="preserve">10.5587272644043</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">10.5858812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628217697144</t>
+    <t xml:space="preserve">10.66282081604</t>
   </si>
   <si>
     <t xml:space="preserve">10.7261819839478</t>
@@ -5339,22 +5339,22 @@
     <t xml:space="preserve">11.1787643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7173347473145</t>
+    <t xml:space="preserve">11.7173357009888</t>
   </si>
   <si>
     <t xml:space="preserve">11.5906133651733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4955701828003</t>
+    <t xml:space="preserve">11.4955711364746</t>
   </si>
   <si>
     <t xml:space="preserve">11.4231586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4141063690186</t>
+    <t xml:space="preserve">11.4005289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4141054153442</t>
   </si>
   <si>
     <t xml:space="preserve">11.3869514465332</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">11.4865188598633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6313467025757</t>
+    <t xml:space="preserve">11.6313457489014</t>
   </si>
   <si>
     <t xml:space="preserve">11.5815620422363</t>
@@ -5372,7 +5372,7 @@
     <t xml:space="preserve">11.595139503479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7625932693481</t>
+    <t xml:space="preserve">11.7625942230225</t>
   </si>
   <si>
     <t xml:space="preserve">11.6901817321777</t>
@@ -5384,7 +5384,7 @@
     <t xml:space="preserve">12.0160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9979362487793</t>
+    <t xml:space="preserve">11.9979372024536</t>
   </si>
   <si>
     <t xml:space="preserve">12.0567722320557</t>
@@ -5393,7 +5393,7 @@
     <t xml:space="preserve">12.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2785358428955</t>
+    <t xml:space="preserve">12.2785367965698</t>
   </si>
   <si>
     <t xml:space="preserve">12.3328475952148</t>
@@ -5405,16 +5405,16 @@
     <t xml:space="preserve">12.5003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3781051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.509352684021</t>
+    <t xml:space="preserve">12.3781061172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093536376953</t>
   </si>
   <si>
     <t xml:space="preserve">12.3962078094482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4052600860596</t>
+    <t xml:space="preserve">12.4052591323853</t>
   </si>
   <si>
     <t xml:space="preserve">12.3102188110352</t>
@@ -5423,37 +5423,37 @@
     <t xml:space="preserve">12.3554754257202</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2875890731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1246604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1699180603027</t>
+    <t xml:space="preserve">12.2875881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.124659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1699171066284</t>
   </si>
   <si>
     <t xml:space="preserve">12.2921142578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2151756286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3237953186035</t>
+    <t xml:space="preserve">12.2151765823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3237943649292</t>
   </si>
   <si>
     <t xml:space="preserve">12.3509502410889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1337108612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744441986084</t>
+    <t xml:space="preserve">12.1337099075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1970729827881</t>
+    <t xml:space="preserve">12.1970720291138</t>
   </si>
   <si>
     <t xml:space="preserve">12.3826313018799</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">13.0796060562134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2244310379028</t>
+    <t xml:space="preserve">13.2244319915771</t>
   </si>
   <si>
     <t xml:space="preserve">13.514084815979</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">13.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7403745651245</t>
+    <t xml:space="preserve">13.7403755187988</t>
   </si>
   <si>
     <t xml:space="preserve">13.7992105484009</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">13.7336559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6259593963623</t>
+    <t xml:space="preserve">13.6259603500366</t>
   </si>
   <si>
     <t xml:space="preserve">13.5369930267334</t>
@@ -5513,19 +5513,19 @@
     <t xml:space="preserve">13.5791349411011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5978651046753</t>
+    <t xml:space="preserve">13.5978660583496</t>
   </si>
   <si>
     <t xml:space="preserve">13.5042161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4199314117432</t>
+    <t xml:space="preserve">13.4199323654175</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620733261108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4339799880981</t>
+    <t xml:space="preserve">13.4339790344238</t>
   </si>
   <si>
     <t xml:space="preserve">13.2794580459595</t>
@@ -5534,16 +5534,16 @@
     <t xml:space="preserve">13.1343011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.424614906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9563674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6660556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7550220489502</t>
+    <t xml:space="preserve">13.4246139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9563684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.666054725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7550230026245</t>
   </si>
   <si>
     <t xml:space="preserve">12.8205757141113</t>
@@ -5552,16 +5552,16 @@
     <t xml:space="preserve">12.7222452163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9329557418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0500173568726</t>
+    <t xml:space="preserve">12.9329566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0500183105469</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001789093018</t>
+    <t xml:space="preserve">12.9001779556274</t>
   </si>
   <si>
     <t xml:space="preserve">12.7831172943115</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">13.1951732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0359706878662</t>
+    <t xml:space="preserve">13.0359697341919</t>
   </si>
   <si>
     <t xml:space="preserve">13.1670789718628</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">13.2045392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2888231277466</t>
+    <t xml:space="preserve">13.2888221740723</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654104232788</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">13.4386615753174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4714384078979</t>
+    <t xml:space="preserve">13.4714393615723</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777894973755</t>
@@ -5600,10 +5600,10 @@
     <t xml:space="preserve">13.382472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.499532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4808034896851</t>
+    <t xml:space="preserve">13.4995336532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4808044433594</t>
   </si>
   <si>
     <t xml:space="preserve">13.5182638168335</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">13.8038930892944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8413524627686</t>
+    <t xml:space="preserve">13.8413534164429</t>
   </si>
   <si>
     <t xml:space="preserve">13.808575630188</t>
@@ -5630,13 +5630,13 @@
     <t xml:space="preserve">13.4573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1623973846436</t>
+    <t xml:space="preserve">13.1623964309692</t>
   </si>
   <si>
     <t xml:space="preserve">12.8486709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1483488082886</t>
+    <t xml:space="preserve">13.1483497619629</t>
   </si>
   <si>
     <t xml:space="preserve">13.0172395706177</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">13.1389837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.101523399353</t>
+    <t xml:space="preserve">13.1015243530273</t>
   </si>
   <si>
     <t xml:space="preserve">13.1904907226562</t>
@@ -5663,13 +5663,13 @@
     <t xml:space="preserve">13.9350023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9490509033203</t>
+    <t xml:space="preserve">13.949049949646</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0146036148071</t>
+    <t xml:space="preserve">14.0146045684814</t>
   </si>
   <si>
     <t xml:space="preserve">14.047381401062</t>
@@ -5684,10 +5684,10 @@
     <t xml:space="preserve">14.314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3611059188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1410303115845</t>
+    <t xml:space="preserve">14.3611068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1410312652588</t>
   </si>
   <si>
     <t xml:space="preserve">13.9911918640137</t>
@@ -5696,25 +5696,25 @@
     <t xml:space="preserve">14.1223001480103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9865093231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019033432007</t>
+    <t xml:space="preserve">13.9865102767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019023895264</t>
   </si>
   <si>
     <t xml:space="preserve">13.9818267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7523860931396</t>
+    <t xml:space="preserve">13.752387046814</t>
   </si>
   <si>
     <t xml:space="preserve">13.836669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8881769180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0005569458008</t>
+    <t xml:space="preserve">13.8881778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0005559921265</t>
   </si>
   <si>
     <t xml:space="preserve">14.3657884597778</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">14.403247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2861862182617</t>
+    <t xml:space="preserve">14.286187171936</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815046310425</t>
@@ -5735,19 +5735,19 @@
     <t xml:space="preserve">14.4453907012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4641208648682</t>
+    <t xml:space="preserve">14.4641199111938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3517408370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1129350662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0333337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460350036621</t>
+    <t xml:space="preserve">14.1129360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.033332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460359573364</t>
   </si>
   <si>
     <t xml:space="preserve">14.0567464828491</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">14.5624523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6561002731323</t>
+    <t xml:space="preserve">14.6561012268066</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982431411743</t>
@@ -5783,13 +5783,13 @@
     <t xml:space="preserve">15.1009349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9136371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7684812545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5999126434326</t>
+    <t xml:space="preserve">14.9136362075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7684803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5999116897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.4500732421875</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">14.4219779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3376951217651</t>
+    <t xml:space="preserve">14.3376941680908</t>
   </si>
   <si>
     <t xml:space="preserve">14.3002347946167</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">13.5229454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8554010391235</t>
+    <t xml:space="preserve">13.8554000854492</t>
   </si>
   <si>
     <t xml:space="preserve">13.9089336395264</t>
@@ -6492,6 +6492,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.2350006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5249996185303</t>
   </si>
 </sst>
 </file>
@@ -48578,7 +48581,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>1349</v>
+        <v>849</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48604,7 +48607,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1607" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -48630,7 +48633,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1608" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -48656,7 +48659,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G1609" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -48708,7 +48711,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1611" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48734,7 +48737,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48786,7 +48789,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G1614" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48812,7 +48815,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1615" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48838,7 +48841,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G1616" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48890,7 +48893,7 @@
         <v>9.70400047302246</v>
       </c>
       <c r="G1618" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48916,7 +48919,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G1619" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48942,7 +48945,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1620" t="s">
-        <v>1257</v>
+        <v>1359</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -71726,7 +71729,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494560185</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>1118510</v>
@@ -71747,6 +71750,32 @@
         <v>2159</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6911921296</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>1382433</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>16.5400009155273</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>16.1650009155273</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>16.3099994659424</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>16.5249996185303</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2160</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="2161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="2162">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19125890731812</t>
+    <t xml:space="preserve">5.19125843048096</t>
   </si>
   <si>
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18521499633789</t>
+    <t xml:space="preserve">5.18521547317505</t>
   </si>
   <si>
     <t xml:space="preserve">5.05528259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95858860015869</t>
+    <t xml:space="preserve">4.95858907699585</t>
   </si>
   <si>
     <t xml:space="preserve">4.83772134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8105263710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92535018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97974061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91930675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73196268081665</t>
+    <t xml:space="preserve">4.81052684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92534971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97974109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91930770874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73196220397949</t>
   </si>
   <si>
     <t xml:space="preserve">4.50533580780029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59900808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41468477249146</t>
+    <t xml:space="preserve">4.59900856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41468524932861</t>
   </si>
   <si>
     <t xml:space="preserve">4.65944147109985</t>
@@ -86,103 +86,103 @@
     <t xml:space="preserve">4.67455053329468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52346658706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59598636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52648735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27870893478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45094585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31194829940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19410181045532</t>
+    <t xml:space="preserve">4.52346611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59598684310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52648782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27870941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45094633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3119478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19410228729248</t>
   </si>
   <si>
     <t xml:space="preserve">4.00373601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09136438369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9886269569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61695981025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41450667381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6713502407074</t>
+    <t xml:space="preserve">4.09136486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98862719535828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61695957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41450643539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67134976387024</t>
   </si>
   <si>
     <t xml:space="preserve">3.47796201705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64717650413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68041491508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74991345405579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64113283157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091613769531</t>
+    <t xml:space="preserve">3.54443883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64717698097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68041515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113306999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091589927673</t>
   </si>
   <si>
     <t xml:space="preserve">3.75595760345459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66228532791138</t>
+    <t xml:space="preserve">3.66228485107422</t>
   </si>
   <si>
     <t xml:space="preserve">3.62300324440002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67437171936035</t>
+    <t xml:space="preserve">3.67437100410461</t>
   </si>
   <si>
     <t xml:space="preserve">3.76804375648499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78315281867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93725824356079</t>
+    <t xml:space="preserve">3.78315234184265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93725872039795</t>
   </si>
   <si>
     <t xml:space="preserve">4.08834314346313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10345125198364</t>
+    <t xml:space="preserve">4.10345220565796</t>
   </si>
   <si>
     <t xml:space="preserve">4.02488708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91006302833557</t>
+    <t xml:space="preserve">3.91006326675415</t>
   </si>
   <si>
     <t xml:space="preserve">3.96143174171448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97351908683777</t>
+    <t xml:space="preserve">3.97351884841919</t>
   </si>
   <si>
     <t xml:space="preserve">4.03395223617554</t>
@@ -191,67 +191,67 @@
     <t xml:space="preserve">4.38446807861328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42979383468628</t>
+    <t xml:space="preserve">4.42979335784912</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173065185547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29986095428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03697443008423</t>
+    <t xml:space="preserve">4.29986047744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03697347640991</t>
   </si>
   <si>
     <t xml:space="preserve">4.07323408126831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09438610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01884460449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99164915084839</t>
+    <t xml:space="preserve">4.0943865776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01884412765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99164867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.87984681129456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90401983261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82545638084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79221796989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8314995765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75897860527039</t>
+    <t xml:space="preserve">3.90402030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82545614242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79221773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83149981498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75897812843323</t>
   </si>
   <si>
     <t xml:space="preserve">3.79523921012878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60487341880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8133692741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85567307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77408695220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97049760818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04301786422729</t>
+    <t xml:space="preserve">3.60487294197083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81336975097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85567355155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77408719062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97049689292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04301738739014</t>
   </si>
   <si>
     <t xml:space="preserve">3.97654056549072</t>
@@ -266,58 +266,58 @@
     <t xml:space="preserve">4.36935997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38748979568481</t>
+    <t xml:space="preserve">4.38749027252197</t>
   </si>
   <si>
     <t xml:space="preserve">4.39655542373657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33612060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21223163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05208253860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88588953018188</t>
+    <t xml:space="preserve">4.33612108230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21223211288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05208301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88589000701904</t>
   </si>
   <si>
     <t xml:space="preserve">3.85265111923218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8043041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078142166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89797568321228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93423700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9221498966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90704107284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9795618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0158224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21827554702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31496953964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30590534210205</t>
+    <t xml:space="preserve">3.80430388450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8707811832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89797711372375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93423676490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92215013504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90704131126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97956299781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01582288742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21827507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30590438842773</t>
   </si>
   <si>
     <t xml:space="preserve">4.35727310180664</t>
@@ -335,37 +335,37 @@
     <t xml:space="preserve">4.00071382522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98560500144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610717773438</t>
+    <t xml:space="preserve">3.98560523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91610741615295</t>
   </si>
   <si>
     <t xml:space="preserve">3.70156693458557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52026581764221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38731169700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48098397254944</t>
+    <t xml:space="preserve">3.52026510238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38731145858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48098349571228</t>
   </si>
   <si>
     <t xml:space="preserve">3.46889686584473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60789489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80732607841492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85869479179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83452105522156</t>
+    <t xml:space="preserve">3.6078941822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80732560157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85869431495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8345205783844</t>
   </si>
   <si>
     <t xml:space="preserve">3.20903205871582</t>
@@ -374,49 +374,49 @@
     <t xml:space="preserve">2.79929113388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96125340461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06399130821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11536002159119</t>
+    <t xml:space="preserve">2.96125292778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06399083137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11535930633545</t>
   </si>
   <si>
     <t xml:space="preserve">3.14557647705078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01322650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91653275489807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84763813018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9455406665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19694519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472289085388</t>
+    <t xml:space="preserve">3.01322627067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91653299331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84763836860657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94554090499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19694495201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472336769104</t>
   </si>
   <si>
     <t xml:space="preserve">3.47191905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57767772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5263090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58674335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55350375175476</t>
+    <t xml:space="preserve">3.57767748832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52630853652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58674263954163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55350422859192</t>
   </si>
   <si>
     <t xml:space="preserve">3.59580779075623</t>
@@ -425,61 +425,61 @@
     <t xml:space="preserve">3.58976435661316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61998081207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5353741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65926265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61393713951111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78617405891418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71365404129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4084632396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42054963111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71969795227051</t>
+    <t xml:space="preserve">3.61998128890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53537440299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65926289558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61393761634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78617382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71365356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40846300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4205493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71969723701477</t>
   </si>
   <si>
     <t xml:space="preserve">3.96747541427612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94027972221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099835395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308522224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84962964057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81639051437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80128264427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69552326202393</t>
+    <t xml:space="preserve">3.94028043746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84962916374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81639099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6955235004425</t>
   </si>
   <si>
     <t xml:space="preserve">3.72876214981079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92517185211182</t>
+    <t xml:space="preserve">3.92517161369324</t>
   </si>
   <si>
     <t xml:space="preserve">3.89495468139648</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">4.0490608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14273357391357</t>
+    <t xml:space="preserve">4.14273309707642</t>
   </si>
   <si>
     <t xml:space="preserve">4.07927799224854</t>
@@ -500,40 +500,40 @@
     <t xml:space="preserve">4.19108009338379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15481996536255</t>
+    <t xml:space="preserve">4.15481948852539</t>
   </si>
   <si>
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73178386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78919649124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68645858764648</t>
+    <t xml:space="preserve">3.7317841053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7891960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68645811080933</t>
   </si>
   <si>
     <t xml:space="preserve">3.77106523513794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77710938453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49609231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54141783714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47494053840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49911403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49004888534546</t>
+    <t xml:space="preserve">3.77710866928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49609184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54141759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47494029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49911379814148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4900484085083</t>
   </si>
   <si>
     <t xml:space="preserve">3.49307060241699</t>
@@ -542,43 +542,43 @@
     <t xml:space="preserve">3.68343615531921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78013038635254</t>
+    <t xml:space="preserve">3.7801308631897</t>
   </si>
   <si>
     <t xml:space="preserve">3.65321969985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74387049674988</t>
+    <t xml:space="preserve">3.74387121200562</t>
   </si>
   <si>
     <t xml:space="preserve">3.87380266189575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99467062950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10949468612671</t>
+    <t xml:space="preserve">3.99466991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10949420928955</t>
   </si>
   <si>
     <t xml:space="preserve">4.15784120559692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23640584945679</t>
+    <t xml:space="preserve">4.23640537261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.06114816665649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84358644485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00977849960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14575529098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13971138000488</t>
+    <t xml:space="preserve">3.84358620643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00977897644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14575481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13971185684204</t>
   </si>
   <si>
     <t xml:space="preserve">4.25453567504883</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">4.26964426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20618867874146</t>
+    <t xml:space="preserve">4.20618915557861</t>
   </si>
   <si>
     <t xml:space="preserve">4.11251640319824</t>
@@ -596,61 +596,61 @@
     <t xml:space="preserve">3.94632387161255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99360370635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06294822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00305986404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96208381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90849924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7950267791748</t>
+    <t xml:space="preserve">3.99360346794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06294870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00306034088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96208333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90849852561951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79502725601196</t>
   </si>
   <si>
     <t xml:space="preserve">3.95578002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10392427444458</t>
+    <t xml:space="preserve">4.10392475128174</t>
   </si>
   <si>
     <t xml:space="preserve">4.23315715789795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23946094512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05979585647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46325397491455</t>
+    <t xml:space="preserve">4.23946142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05979633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46325445175171</t>
   </si>
   <si>
     <t xml:space="preserve">4.67759084701538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80682420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67128705978394</t>
+    <t xml:space="preserve">4.80682373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67128658294678</t>
   </si>
   <si>
     <t xml:space="preserve">4.69650316238403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74693584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79106330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95181703567505</t>
+    <t xml:space="preserve">4.74693489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79106378555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95181655883789</t>
   </si>
   <si>
     <t xml:space="preserve">4.89508008956909</t>
@@ -662,61 +662,61 @@
     <t xml:space="preserve">4.98964071273804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95496845245361</t>
+    <t xml:space="preserve">4.95496797561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.93920803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00224828720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99909639358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93605709075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89823293685913</t>
+    <t xml:space="preserve">5.00224876403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99909687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93605613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89823246002197</t>
   </si>
   <si>
     <t xml:space="preserve">4.88877630233765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99279260635376</t>
+    <t xml:space="preserve">4.99279308319092</t>
   </si>
   <si>
     <t xml:space="preserve">5.1377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14408874511719</t>
+    <t xml:space="preserve">5.16930532455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14408922195435</t>
   </si>
   <si>
     <t xml:space="preserve">5.16300106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92975187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98333692550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98018503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86355972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05898475646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04007244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00540018081665</t>
+    <t xml:space="preserve">4.92975234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98333740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98018455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86356019973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05898523330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04007291793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00540065765381</t>
   </si>
   <si>
     <t xml:space="preserve">5.08420085906982</t>
@@ -731,31 +731,31 @@
     <t xml:space="preserve">5.3710355758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53809070587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3615779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29538583755493</t>
+    <t xml:space="preserve">5.5380916595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36157846450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29538536071777</t>
   </si>
   <si>
     <t xml:space="preserve">5.15354585647583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01485681533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13463306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92344856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96757745742798</t>
+    <t xml:space="preserve">5.01485633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13463354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92344903945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8194317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96757650375366</t>
   </si>
   <si>
     <t xml:space="preserve">4.91084003448486</t>
@@ -770,10 +770,10 @@
     <t xml:space="preserve">5.14724159240723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11887311935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07159280776978</t>
+    <t xml:space="preserve">5.11887359619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07159328460693</t>
   </si>
   <si>
     <t xml:space="preserve">5.02431297302246</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">4.72802352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76900005340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94866466522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99594449996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17245721817017</t>
+    <t xml:space="preserve">4.7689995765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94866514205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99594497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17245817184448</t>
   </si>
   <si>
     <t xml:space="preserve">5.21658515930176</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">5.23549842834473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25125789642334</t>
+    <t xml:space="preserve">5.25125885009766</t>
   </si>
   <si>
     <t xml:space="preserve">5.26071405410767</t>
@@ -827,88 +827,88 @@
     <t xml:space="preserve">5.32375478744507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33636283874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27962636947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33951473236084</t>
+    <t xml:space="preserve">5.33636331558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27962589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.339515209198</t>
   </si>
   <si>
     <t xml:space="preserve">5.31745100021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35212278366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32690668106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19767332077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20712947845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20397806167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23865032196045</t>
+    <t xml:space="preserve">5.35212230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32690620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19767379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20713043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20397853851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23865079879761</t>
   </si>
   <si>
     <t xml:space="preserve">5.13148164749146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104991912842</t>
+    <t xml:space="preserve">5.08104944229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.8509521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38364267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46559524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38994646072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35527467727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56330680847168</t>
+    <t xml:space="preserve">5.38364362716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46559476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38994693756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35527420043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.563307762146</t>
   </si>
   <si>
     <t xml:space="preserve">5.57906818389893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5979790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70830106735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78710126876831</t>
+    <t xml:space="preserve">5.59797954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70830011367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78710079193115</t>
   </si>
   <si>
     <t xml:space="preserve">5.75242853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73666858673096</t>
+    <t xml:space="preserve">5.73666906356812</t>
   </si>
   <si>
     <t xml:space="preserve">5.72090816497803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79340410232544</t>
+    <t xml:space="preserve">5.7934045791626</t>
   </si>
   <si>
     <t xml:space="preserve">5.76188468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78394889831543</t>
+    <t xml:space="preserve">5.78394937515259</t>
   </si>
   <si>
     <t xml:space="preserve">5.62319612503052</t>
@@ -917,40 +917,40 @@
     <t xml:space="preserve">5.64210796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68938875198364</t>
+    <t xml:space="preserve">5.68938827514648</t>
   </si>
   <si>
     <t xml:space="preserve">5.73036432266235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76818895339966</t>
+    <t xml:space="preserve">5.76818799972534</t>
   </si>
   <si>
     <t xml:space="preserve">5.73981952667236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71460390090942</t>
+    <t xml:space="preserve">5.71460342407227</t>
   </si>
   <si>
     <t xml:space="preserve">5.6294994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45298719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32060289382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34266710281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27332162857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36473083496094</t>
+    <t xml:space="preserve">5.45298671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32060146331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34266662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25441026687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27332210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36472988128662</t>
   </si>
   <si>
     <t xml:space="preserve">5.41516304016113</t>
@@ -959,97 +959,97 @@
     <t xml:space="preserve">5.39625072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44983530044556</t>
+    <t xml:space="preserve">5.44983434677124</t>
   </si>
   <si>
     <t xml:space="preserve">5.37418651580811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3930983543396</t>
+    <t xml:space="preserve">5.39309930801392</t>
   </si>
   <si>
     <t xml:space="preserve">5.29223489761353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21028232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35842609405518</t>
+    <t xml:space="preserve">5.21028137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35842704772949</t>
   </si>
   <si>
     <t xml:space="preserve">5.34581804275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48135471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46874666213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44668340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754686355591</t>
+    <t xml:space="preserve">5.4813551902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46874809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44668292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754781723022</t>
   </si>
   <si>
     <t xml:space="preserve">5.59482717514038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52548313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56015539169312</t>
+    <t xml:space="preserve">5.52548360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56015491485596</t>
   </si>
   <si>
     <t xml:space="preserve">5.59167528152466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66101980209351</t>
+    <t xml:space="preserve">5.66101884841919</t>
   </si>
   <si>
     <t xml:space="preserve">5.71775579452515</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67362785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67678022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49081087112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50972366333008</t>
+    <t xml:space="preserve">5.67362880706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67678070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50972270965576</t>
   </si>
   <si>
     <t xml:space="preserve">5.56961154937744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60743522644043</t>
+    <t xml:space="preserve">5.60743570327759</t>
   </si>
   <si>
     <t xml:space="preserve">5.58221960067749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55700397491455</t>
+    <t xml:space="preserve">5.55700349807739</t>
   </si>
   <si>
     <t xml:space="preserve">5.54439544677734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67993259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67047595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61058712005615</t>
+    <t xml:space="preserve">5.67993211746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67047643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61058807373047</t>
   </si>
   <si>
     <t xml:space="preserve">5.48450708389282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53493928909302</t>
+    <t xml:space="preserve">5.53493976593018</t>
   </si>
   <si>
     <t xml:space="preserve">5.52863550186157</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">5.47505140304565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38049030303955</t>
+    <t xml:space="preserve">5.38048982620239</t>
   </si>
   <si>
     <t xml:space="preserve">5.43407535552979</t>
@@ -1067,94 +1067,94 @@
     <t xml:space="preserve">5.33005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50026750564575</t>
+    <t xml:space="preserve">5.50026798248291</t>
   </si>
   <si>
     <t xml:space="preserve">5.56646060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5065712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51602649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58537197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66732454299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65471601486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69253969192505</t>
+    <t xml:space="preserve">5.50657081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51602697372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58537149429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66732406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65471649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69254016876221</t>
   </si>
   <si>
     <t xml:space="preserve">5.72406053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75873231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71145296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7997088432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74612474441528</t>
+    <t xml:space="preserve">5.75873327255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7114520072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79970836639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74612426757812</t>
   </si>
   <si>
     <t xml:space="preserve">5.77449226379395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74927616119385</t>
+    <t xml:space="preserve">5.74927663803101</t>
   </si>
   <si>
     <t xml:space="preserve">5.77764463424683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78079700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77134037017822</t>
+    <t xml:space="preserve">5.78079652786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77133989334106</t>
   </si>
   <si>
     <t xml:space="preserve">5.81862115859985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91633415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97622156143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93209362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01404571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07708597183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05187129974365</t>
+    <t xml:space="preserve">5.91633367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97622108459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93209314346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01404619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07708644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05187082290649</t>
   </si>
   <si>
     <t xml:space="preserve">6.03295803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10860538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10230302810669</t>
+    <t xml:space="preserve">6.10860681533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10230207443237</t>
   </si>
   <si>
     <t xml:space="preserve">6.2315354347229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2157735824585</t>
+    <t xml:space="preserve">6.21577548980713</t>
   </si>
   <si>
     <t xml:space="preserve">6.2252311706543</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">6.20001459121704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23178100585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13353824615479</t>
+    <t xml:space="preserve">6.23178148269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13353872299194</t>
   </si>
   <si>
     <t xml:space="preserve">6.20885705947876</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">6.20558261871338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16956090927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09751796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22850561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34966993331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28745174407959</t>
+    <t xml:space="preserve">6.1695613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09751749038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22850608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34967041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28745126724243</t>
   </si>
   <si>
     <t xml:space="preserve">6.33329629898071</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">6.29400014877319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19903373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22195625305176</t>
+    <t xml:space="preserve">6.19903326034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2219557762146</t>
   </si>
   <si>
     <t xml:space="preserve">6.30382442474365</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">6.2809009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28417634963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25470399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24815368652344</t>
+    <t xml:space="preserve">6.28417587280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25470352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24815511703491</t>
   </si>
   <si>
     <t xml:space="preserve">6.12371492385864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15646123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18593406677246</t>
+    <t xml:space="preserve">6.15646171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18593454360962</t>
   </si>
   <si>
     <t xml:space="preserve">6.24160432815552</t>
@@ -1244,37 +1244,37 @@
     <t xml:space="preserve">6.1466383934021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27107763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41843938827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39879035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40206480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39224147796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41188955307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4937572479248</t>
+    <t xml:space="preserve">6.27107667922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41843843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39879179000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40206527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39224052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41189002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49375677108765</t>
   </si>
   <si>
     <t xml:space="preserve">6.51995515823364</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53305387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5297794342041</t>
+    <t xml:space="preserve">6.57562589645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53305435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52977991104126</t>
   </si>
   <si>
     <t xml:space="preserve">6.48720741271973</t>
@@ -1283,70 +1283,70 @@
     <t xml:space="preserve">6.43808698654175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45380592346191</t>
+    <t xml:space="preserve">6.45380449295044</t>
   </si>
   <si>
     <t xml:space="preserve">6.36604356765747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41319894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47607421875</t>
+    <t xml:space="preserve">6.41319847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47607469558716</t>
   </si>
   <si>
     <t xml:space="preserve">6.51406097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4564266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26780223846436</t>
+    <t xml:space="preserve">6.45642566680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2678017616272</t>
   </si>
   <si>
     <t xml:space="preserve">6.36997318267822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32019662857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36473417282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41581869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47214555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44594669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46690464019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47869443893433</t>
+    <t xml:space="preserve">6.32019758224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3647346496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41581916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47214460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44594717025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46690511703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47869348526001</t>
   </si>
   <si>
     <t xml:space="preserve">6.40010070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46166467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47476434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51013088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974878311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674741744995</t>
+    <t xml:space="preserve">6.46166563034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4747633934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51013135910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41974830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674646377563</t>
   </si>
   <si>
     <t xml:space="preserve">6.2101674079895</t>
@@ -1355,37 +1355,37 @@
     <t xml:space="preserve">6.31102848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44463729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46559572219849</t>
+    <t xml:space="preserve">6.44463682174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46559476852417</t>
   </si>
   <si>
     <t xml:space="preserve">6.45904588699341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39748048782349</t>
+    <t xml:space="preserve">6.39748001098633</t>
   </si>
   <si>
     <t xml:space="preserve">6.42498922348022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45773458480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40665054321289</t>
+    <t xml:space="preserve">6.45773649215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40665006637573</t>
   </si>
   <si>
     <t xml:space="preserve">6.47738456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37390279769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25732326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21671676635742</t>
+    <t xml:space="preserve">6.37390375137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25732278823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21671724319458</t>
   </si>
   <si>
     <t xml:space="preserve">6.24684381484985</t>
@@ -1394,46 +1394,46 @@
     <t xml:space="preserve">6.25339412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27828168869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35294437408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34508514404297</t>
+    <t xml:space="preserve">6.27828216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35294485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34508466720581</t>
   </si>
   <si>
     <t xml:space="preserve">6.41712951660156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39355182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54811811447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63457107543945</t>
+    <t xml:space="preserve">6.39355134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54811859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63457059860229</t>
   </si>
   <si>
     <t xml:space="preserve">6.66076803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79503107070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84415197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70661306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69351434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67386722564697</t>
+    <t xml:space="preserve">6.79503059387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84415149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70661401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67386627197266</t>
   </si>
   <si>
     <t xml:space="preserve">6.55925226211548</t>
@@ -1442,40 +1442,40 @@
     <t xml:space="preserve">6.69679069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72953605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54942750930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46428489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51537084579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56907558441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52191972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20754671096802</t>
+    <t xml:space="preserve">6.7295355796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54942798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46428537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51537036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56907606124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52191925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20754766464233</t>
   </si>
   <si>
     <t xml:space="preserve">6.01499462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.915442943573</t>
+    <t xml:space="preserve">5.91544246673584</t>
   </si>
   <si>
     <t xml:space="preserve">5.95342969894409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81327295303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58011293411255</t>
+    <t xml:space="preserve">5.81327199935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58011341094971</t>
   </si>
   <si>
     <t xml:space="preserve">5.24085187911987</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">5.0312705039978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38625001907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28407716751099</t>
+    <t xml:space="preserve">5.38624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2840781211853</t>
   </si>
   <si>
     <t xml:space="preserve">5.4216160774231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32861375808716</t>
+    <t xml:space="preserve">5.32861423492432</t>
   </si>
   <si>
     <t xml:space="preserve">5.19238662719727</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">5.35874176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23823261260986</t>
+    <t xml:space="preserve">5.23823213577271</t>
   </si>
   <si>
     <t xml:space="preserve">5.12689208984375</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">5.37708044052124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3050365447998</t>
+    <t xml:space="preserve">5.30503702163696</t>
   </si>
   <si>
     <t xml:space="preserve">5.40327787399292</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">5.34826326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28276824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26049995422363</t>
+    <t xml:space="preserve">5.28276872634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26050043106079</t>
   </si>
   <si>
     <t xml:space="preserve">5.44257497787476</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">5.52378749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33254384994507</t>
+    <t xml:space="preserve">5.33254432678223</t>
   </si>
   <si>
     <t xml:space="preserve">5.29848766326904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2172737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18321704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21465444564819</t>
+    <t xml:space="preserve">5.21727514266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18321752548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21465492248535</t>
   </si>
   <si>
     <t xml:space="preserve">5.18845653533936</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">5.25133085250854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32206583023071</t>
+    <t xml:space="preserve">5.32206535339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.39148902893066</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">5.30634641647339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34040307998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26835918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17928791046143</t>
+    <t xml:space="preserve">5.34040355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26835966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17928743362427</t>
   </si>
   <si>
     <t xml:space="preserve">5.20155572891235</t>
@@ -1580,19 +1580,19 @@
     <t xml:space="preserve">5.27097940444946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28931856155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3377833366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32468509674072</t>
+    <t xml:space="preserve">5.28931760787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33778285980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32468461990356</t>
   </si>
   <si>
     <t xml:space="preserve">5.3561224937439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51330900192261</t>
+    <t xml:space="preserve">5.51330852508545</t>
   </si>
   <si>
     <t xml:space="preserve">5.57618284225464</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">5.68097352981567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81851148605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74646854400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68752241134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78052425384521</t>
+    <t xml:space="preserve">5.81851100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74646759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68752288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78052473068237</t>
   </si>
   <si>
     <t xml:space="preserve">5.68490314483643</t>
@@ -1625,34 +1625,34 @@
     <t xml:space="preserve">5.75956583023071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75563716888428</t>
+    <t xml:space="preserve">5.75563764572144</t>
   </si>
   <si>
     <t xml:space="preserve">5.76742649078369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70848083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59583139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44912338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56439399719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50282907485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51985692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61023950576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758958816528</t>
+    <t xml:space="preserve">5.70848035812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5958309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44912385940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56439447402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50282955169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51985740661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61024045944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49759006500244</t>
   </si>
   <si>
     <t xml:space="preserve">5.43340492248535</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">5.43864488601685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42816543579102</t>
+    <t xml:space="preserve">5.42816638946533</t>
   </si>
   <si>
     <t xml:space="preserve">5.39541864395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41899681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25002145767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55522489547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73598957061768</t>
+    <t xml:space="preserve">5.41899585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25002098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55522441864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73598909378052</t>
   </si>
   <si>
     <t xml:space="preserve">5.68621349334717</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">5.93771171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90627384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89710474014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91282320022583</t>
+    <t xml:space="preserve">5.90627336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93640041351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89710521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91282367706299</t>
   </si>
   <si>
     <t xml:space="preserve">6.01368474960327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03333234786987</t>
+    <t xml:space="preserve">6.03333330154419</t>
   </si>
   <si>
     <t xml:space="preserve">6.09620761871338</t>
@@ -1709,106 +1709,106 @@
     <t xml:space="preserve">6.00844478607178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00713491439819</t>
+    <t xml:space="preserve">6.00713586807251</t>
   </si>
   <si>
     <t xml:space="preserve">5.96390914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07524967193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06476974487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00451564788818</t>
+    <t xml:space="preserve">6.07524919509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06477069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00451469421387</t>
   </si>
   <si>
     <t xml:space="preserve">5.63512754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46353244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48842096328735</t>
+    <t xml:space="preserve">5.4635329246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48842000961304</t>
   </si>
   <si>
     <t xml:space="preserve">5.48056125640869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3888692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13737106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18059778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07187652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02865028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0351996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11379337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05484819412231</t>
+    <t xml:space="preserve">5.38886880874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13737058639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18059682846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07187700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02865123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03520011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11379289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05484867095947</t>
   </si>
   <si>
     <t xml:space="preserve">5.00638246536255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15963935852051</t>
+    <t xml:space="preserve">5.15963840484619</t>
   </si>
   <si>
     <t xml:space="preserve">5.06663751602173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07842636108398</t>
+    <t xml:space="preserve">5.07842588424683</t>
   </si>
   <si>
     <t xml:space="preserve">4.90683126449585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09545469284058</t>
+    <t xml:space="preserve">5.09545516967773</t>
   </si>
   <si>
     <t xml:space="preserve">4.95791673660278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09938430786133</t>
+    <t xml:space="preserve">5.09938383102417</t>
   </si>
   <si>
     <t xml:space="preserve">5.11248302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0771164894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19500637054443</t>
+    <t xml:space="preserve">5.07711601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19500589370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.13606119155884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11641216278076</t>
+    <t xml:space="preserve">5.11641263961792</t>
   </si>
   <si>
     <t xml:space="preserve">5.13868093490601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15308904647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14915990829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104610443115</t>
+    <t xml:space="preserve">5.15308952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14916086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104658126831</t>
   </si>
   <si>
     <t xml:space="preserve">5.15818929672241</t>
@@ -1817,31 +1817,31 @@
     <t xml:space="preserve">5.03690242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08987855911255</t>
+    <t xml:space="preserve">5.08987903594971</t>
   </si>
   <si>
     <t xml:space="preserve">5.08012008666992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11776113510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34500026702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36730480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39100551605225</t>
+    <t xml:space="preserve">5.11776065826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34499931335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36730527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39100503921509</t>
   </si>
   <si>
     <t xml:space="preserve">5.44258689880371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44119262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47604513168335</t>
+    <t xml:space="preserve">5.44119310379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47604608535767</t>
   </si>
   <si>
     <t xml:space="preserve">5.37706422805786</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">5.22650098800659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22231864929199</t>
+    <t xml:space="preserve">5.22231817245483</t>
   </si>
   <si>
     <t xml:space="preserve">5.10242509841919</t>
@@ -1871,28 +1871,28 @@
     <t xml:space="preserve">5.31293487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23068332672119</t>
+    <t xml:space="preserve">5.23068284988403</t>
   </si>
   <si>
     <t xml:space="preserve">5.27668857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37288236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25577688217163</t>
+    <t xml:space="preserve">5.37288188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25577640533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.12751913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04944896697998</t>
+    <t xml:space="preserve">5.0494499206543</t>
   </si>
   <si>
     <t xml:space="preserve">5.14146089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09127283096313</t>
+    <t xml:space="preserve">5.09127235412598</t>
   </si>
   <si>
     <t xml:space="preserve">5.08709049224854</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">5.37985277175903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36312294006348</t>
+    <t xml:space="preserve">5.36312246322632</t>
   </si>
   <si>
     <t xml:space="preserve">5.33524084091187</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">5.33802890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40494680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34639406204224</t>
+    <t xml:space="preserve">5.40494632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34639358520508</t>
   </si>
   <si>
     <t xml:space="preserve">5.33942317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46210432052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49138069152832</t>
+    <t xml:space="preserve">5.46210479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46907520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49138021469116</t>
   </si>
   <si>
     <t xml:space="preserve">5.50671625137329</t>
@@ -1943,76 +1943,76 @@
     <t xml:space="preserve">5.50253391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55969142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48998689651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4481635093689</t>
+    <t xml:space="preserve">5.55969190597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48998737335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44816303253174</t>
   </si>
   <si>
     <t xml:space="preserve">5.45931625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29481220245361</t>
+    <t xml:space="preserve">5.2948112487793</t>
   </si>
   <si>
     <t xml:space="preserve">5.14424896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11218404769897</t>
+    <t xml:space="preserve">5.11218452453613</t>
   </si>
   <si>
     <t xml:space="preserve">5.28505325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39797592163086</t>
+    <t xml:space="preserve">5.39797639846802</t>
   </si>
   <si>
     <t xml:space="preserve">5.40355205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49835157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52623319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62521409988403</t>
+    <t xml:space="preserve">5.49835109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52623414993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62521457672119</t>
   </si>
   <si>
     <t xml:space="preserve">5.59036254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78971910476685</t>
+    <t xml:space="preserve">5.789719581604</t>
   </si>
   <si>
     <t xml:space="preserve">5.80365991592407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77717256546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79808330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73953151702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75486707687378</t>
+    <t xml:space="preserve">5.77717304229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7980842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73953104019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75486660003662</t>
   </si>
   <si>
     <t xml:space="preserve">5.82735967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98071193695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14939785003662</t>
+    <t xml:space="preserve">5.91797685623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98071146011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14939832687378</t>
   </si>
   <si>
     <t xml:space="preserve">6.02532291412354</t>
@@ -2021,109 +2021,109 @@
     <t xml:space="preserve">6.07969284057617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08945178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20376825332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10060501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03787040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1243052482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10339307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18982791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21631622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26510906219482</t>
+    <t xml:space="preserve">6.08945226669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20376873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10060453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03786897659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12430477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10339260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18982696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21631574630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26510953903198</t>
   </si>
   <si>
     <t xml:space="preserve">6.39894342422485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35990858078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24001502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28602075576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23583269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17728137969971</t>
+    <t xml:space="preserve">6.35990810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28602027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23583316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17728090286255</t>
   </si>
   <si>
     <t xml:space="preserve">6.22468042373657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35293817520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42264223098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45610237121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51883602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42543125152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44076633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47840642929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52162456512451</t>
+    <t xml:space="preserve">6.35293769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42264270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4561014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5188364982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42543172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44076538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47840690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52162504196167</t>
   </si>
   <si>
     <t xml:space="preserve">6.4644660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48537826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57878255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63175916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67079448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69867515563965</t>
+    <t xml:space="preserve">6.4853777885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63175868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6707935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69867563247681</t>
   </si>
   <si>
     <t xml:space="preserve">6.67915821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62199974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54393005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52441263198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56205368041992</t>
+    <t xml:space="preserve">6.62200021743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5439305305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52441310882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56205320358276</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194723129272</t>
@@ -2132,34 +2132,34 @@
     <t xml:space="preserve">6.58714723587036</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62478733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.417067527771</t>
+    <t xml:space="preserve">6.6247878074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">6.267897605896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34875440597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20237398147583</t>
+    <t xml:space="preserve">6.34875535964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20237445831299</t>
   </si>
   <si>
     <t xml:space="preserve">6.06435823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22049713134766</t>
+    <t xml:space="preserve">6.22049856185913</t>
   </si>
   <si>
     <t xml:space="preserve">6.18146276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16612672805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0657525062561</t>
+    <t xml:space="preserve">6.16612768173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06575202941895</t>
   </si>
   <si>
     <t xml:space="preserve">5.99465322494507</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">5.91937112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84269618988037</t>
+    <t xml:space="preserve">5.84269571304321</t>
   </si>
   <si>
     <t xml:space="preserve">5.83433055877686</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">5.88173055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84966659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87894153594971</t>
+    <t xml:space="preserve">5.84966611862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87894201278687</t>
   </si>
   <si>
     <t xml:space="preserve">5.96816492080688</t>
@@ -2201,49 +2201,49 @@
     <t xml:space="preserve">5.9667706489563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93888854980469</t>
+    <t xml:space="preserve">5.93888902664185</t>
   </si>
   <si>
     <t xml:space="preserve">5.97374105453491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94307041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9416766166687</t>
+    <t xml:space="preserve">5.94307088851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94167709350586</t>
   </si>
   <si>
     <t xml:space="preserve">6.07132863998413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16333961486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14382266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19122171401978</t>
+    <t xml:space="preserve">6.16334009170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14382219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19122219085693</t>
   </si>
   <si>
     <t xml:space="preserve">6.17031002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29577922821045</t>
+    <t xml:space="preserve">6.29577875137329</t>
   </si>
   <si>
     <t xml:space="preserve">6.33760213851929</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31947946548462</t>
+    <t xml:space="preserve">6.31947994232178</t>
   </si>
   <si>
     <t xml:space="preserve">6.2386212348938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30972051620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47422504425049</t>
+    <t xml:space="preserve">6.30972099304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47422552108765</t>
   </si>
   <si>
     <t xml:space="preserve">6.60248279571533</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">6.51186609268188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49095487594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55229377746582</t>
+    <t xml:space="preserve">6.49095439910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55229425430298</t>
   </si>
   <si>
     <t xml:space="preserve">6.54114246368408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54671859741211</t>
+    <t xml:space="preserve">6.54671907424927</t>
   </si>
   <si>
     <t xml:space="preserve">6.4979248046875</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">6.56763029098511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53277730941772</t>
+    <t xml:space="preserve">6.53277683258057</t>
   </si>
   <si>
     <t xml:space="preserve">6.54950666427612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4128851890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44355487823486</t>
+    <t xml:space="preserve">6.41288471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44355440139771</t>
   </si>
   <si>
     <t xml:space="preserve">6.5146541595459</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">6.4895601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50350189208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33481407165527</t>
+    <t xml:space="preserve">6.50350141525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33481359481812</t>
   </si>
   <si>
     <t xml:space="preserve">6.31111431121826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32087373733521</t>
+    <t xml:space="preserve">6.32087326049805</t>
   </si>
   <si>
     <t xml:space="preserve">6.15915775299072</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">6.10478734970093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03647565841675</t>
+    <t xml:space="preserve">6.03647518157959</t>
   </si>
   <si>
     <t xml:space="preserve">6.08666372299194</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">5.91379451751709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94446468353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8064489364624</t>
+    <t xml:space="preserve">5.94446516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80644941329956</t>
   </si>
   <si>
     <t xml:space="preserve">5.93052434921265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97652912139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06714725494385</t>
+    <t xml:space="preserve">5.97653007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06714677810669</t>
   </si>
   <si>
     <t xml:space="preserve">6.11315155029297</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">6.04344606399536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13963937759399</t>
+    <t xml:space="preserve">6.11872816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13963985443115</t>
   </si>
   <si>
     <t xml:space="preserve">6.19261598587036</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">6.28044414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35712099075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296537399292</t>
+    <t xml:space="preserve">6.35712051391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296585083008</t>
   </si>
   <si>
     <t xml:space="preserve">6.59829998016357</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">6.68055200576782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63036394119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66382265090942</t>
+    <t xml:space="preserve">6.63036441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66382312774658</t>
   </si>
   <si>
     <t xml:space="preserve">6.72655773162842</t>
@@ -2384,28 +2384,28 @@
     <t xml:space="preserve">6.7614107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95100831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803266525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90779161453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94682645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04371690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95379686355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98446893692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95658493041992</t>
+    <t xml:space="preserve">6.95100927352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.898033618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90779209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94682693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04371643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95379734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98446750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95658445358276</t>
   </si>
   <si>
     <t xml:space="preserve">6.76419973373413</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">6.81578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83390378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79347515106201</t>
+    <t xml:space="preserve">6.83390474319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7934741973877</t>
   </si>
   <si>
     <t xml:space="preserve">6.80462789535522</t>
@@ -2429,136 +2429,136 @@
     <t xml:space="preserve">7.03326082229614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19009780883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27025842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481737136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40269994735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38178730010986</t>
+    <t xml:space="preserve">7.19009733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27025890350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40269899368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38178682327271</t>
   </si>
   <si>
     <t xml:space="preserve">7.36087608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43058204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5037727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55953598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.552565574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58044672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44103717803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4236102104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48285961151123</t>
+    <t xml:space="preserve">7.43058156967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50377178192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55953693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256605148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58044719696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44103765487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42361068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48286104202271</t>
   </si>
   <si>
     <t xml:space="preserve">7.64318227767944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59438800811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51422786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27374601364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42012500762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35390472412109</t>
+    <t xml:space="preserve">7.59438943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51422691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27374458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42012548446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35390663146973</t>
   </si>
   <si>
     <t xml:space="preserve">7.51857471466064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48940467834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752595901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52586698532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669694900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47481918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52951288223267</t>
+    <t xml:space="preserve">7.48940420150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752643585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52586650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47481966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52951383590698</t>
   </si>
   <si>
     <t xml:space="preserve">7.40189409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33261489868164</t>
+    <t xml:space="preserve">7.3326153755188</t>
   </si>
   <si>
     <t xml:space="preserve">7.29250717163086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35449266433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32532262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3471999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22687387466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37272310256958</t>
+    <t xml:space="preserve">7.35449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34720039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22687435150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3727240562439</t>
   </si>
   <si>
     <t xml:space="preserve">7.38366317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24437570571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31438398361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28229713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35813903808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521490097046</t>
+    <t xml:space="preserve">7.24437522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31438446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2822961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35813856124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2852144241333</t>
   </si>
   <si>
     <t xml:space="preserve">7.21958065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15686655044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22979164123535</t>
+    <t xml:space="preserve">7.15686559677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22979116439819</t>
   </si>
   <si>
     <t xml:space="preserve">7.1641583442688</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">7.25021076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.261878490448</t>
+    <t xml:space="preserve">7.26187753677368</t>
   </si>
   <si>
     <t xml:space="preserve">7.21812343597412</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">7.1802020072937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08539867401123</t>
+    <t xml:space="preserve">7.08539915084839</t>
   </si>
   <si>
     <t xml:space="preserve">7.15832424163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11019372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05768871307373</t>
+    <t xml:space="preserve">7.11019325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05768823623657</t>
   </si>
   <si>
     <t xml:space="preserve">7.07810688018799</t>
@@ -2600,58 +2600,58 @@
     <t xml:space="preserve">6.99643135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93809127807617</t>
+    <t xml:space="preserve">6.93809032440186</t>
   </si>
   <si>
     <t xml:space="preserve">6.97309541702271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77328014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9862208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9337158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75286102294922</t>
+    <t xml:space="preserve">6.77328062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98622131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93371534347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75286197662354</t>
   </si>
   <si>
     <t xml:space="preserve">6.5720067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71931457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8053674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98038721084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86954069137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00372362136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04164457321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06060457229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0620641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00518131256104</t>
+    <t xml:space="preserve">6.71931552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98038768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86954212188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00372314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04164409637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0606050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06206321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00518178939819</t>
   </si>
   <si>
     <t xml:space="preserve">7.03289270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99351406097412</t>
+    <t xml:space="preserve">6.99351358413696</t>
   </si>
   <si>
     <t xml:space="preserve">6.86370754241943</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">6.45240926742554</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42178153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38677787780762</t>
+    <t xml:space="preserve">6.42178201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38677835464478</t>
   </si>
   <si>
     <t xml:space="preserve">6.23363494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97256231307983</t>
+    <t xml:space="preserve">5.97256278991699</t>
   </si>
   <si>
     <t xml:space="preserve">5.76253890991211</t>
@@ -2678,31 +2678,31 @@
     <t xml:space="preserve">5.71003246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63564920425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39937162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28415060043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5228123664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21215152740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33174848556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52228045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77606010437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33850979804993</t>
+    <t xml:space="preserve">5.63564968109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39937210083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28415012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52281284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21215200424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33174896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52228021621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77606058120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33851003646851</t>
   </si>
   <si>
     <t xml:space="preserve">3.25537514686584</t>
@@ -2711,25 +2711,25 @@
     <t xml:space="preserve">3.06649899482727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0424337387085</t>
+    <t xml:space="preserve">3.04243397712708</t>
   </si>
   <si>
     <t xml:space="preserve">3.10150289535522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17661595344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61854219436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90440797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01087856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76439189910889</t>
+    <t xml:space="preserve">3.17661571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61854147911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90440821647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0108790397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76439213752747</t>
   </si>
   <si>
     <t xml:space="preserve">3.62802195549011</t>
@@ -2738,16 +2738,16 @@
     <t xml:space="preserve">3.66667222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64917063713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77460122108459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70605182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97149920463562</t>
+    <t xml:space="preserve">3.64917016029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77460145950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70605134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9714994430542</t>
   </si>
   <si>
     <t xml:space="preserve">4.05171680450439</t>
@@ -2759,55 +2759,55 @@
     <t xml:space="preserve">4.04150724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87232136726379</t>
+    <t xml:space="preserve">3.87232089042664</t>
   </si>
   <si>
     <t xml:space="preserve">3.57989144325256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64771223068237</t>
+    <t xml:space="preserve">3.64771175384521</t>
   </si>
   <si>
     <t xml:space="preserve">3.69292521476746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56238985061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51571774482727</t>
+    <t xml:space="preserve">3.56238961219788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51571750640869</t>
   </si>
   <si>
     <t xml:space="preserve">3.73959732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82419061660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02254676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85627794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.799396276474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76585054397583</t>
+    <t xml:space="preserve">3.82419085502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545554161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02254629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85627746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76585030555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.75855779647827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74834847450256</t>
+    <t xml:space="preserve">3.74834871292114</t>
   </si>
   <si>
     <t xml:space="preserve">3.78918671607971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91607618331909</t>
+    <t xml:space="preserve">3.91607594490051</t>
   </si>
   <si>
     <t xml:space="preserve">3.85336065292358</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">3.68271613121033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56311869621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80960559844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74980735778809</t>
+    <t xml:space="preserve">3.56311893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80960536003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74980711936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.69730067253113</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">3.77168416976929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78481078147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256332397461</t>
+    <t xml:space="preserve">3.78481125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921107292175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256284713745</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862258911133</t>
@@ -2852,43 +2852,43 @@
     <t xml:space="preserve">4.69929122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95452880859375</t>
+    <t xml:space="preserve">4.95452928543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.95307016372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18351364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34540700912476</t>
+    <t xml:space="preserve">5.18351316452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34540748596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.17330408096313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07995986938477</t>
+    <t xml:space="preserve">5.07996034622192</t>
   </si>
   <si>
     <t xml:space="preserve">4.86410188674927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9647388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03766345977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16455268859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1397590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23164463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12079763412476</t>
+    <t xml:space="preserve">4.96473836898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16455316543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13975858688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23164415359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12079811096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.97348976135254</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">4.99682569503784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71095895767212</t>
+    <t xml:space="preserve">4.71095943450928</t>
   </si>
   <si>
     <t xml:space="preserve">4.75033855438232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55927467346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76200723648071</t>
+    <t xml:space="preserve">4.55927515029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76200675964355</t>
   </si>
   <si>
     <t xml:space="preserve">4.65991163253784</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">4.71533489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91952466964722</t>
+    <t xml:space="preserve">4.91952514648438</t>
   </si>
   <si>
     <t xml:space="preserve">4.90348148345947</t>
@@ -2930,13 +2930,13 @@
     <t xml:space="preserve">4.88014554977417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79701089859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9297342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05079030990601</t>
+    <t xml:space="preserve">4.79701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92973518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05078983306885</t>
   </si>
   <si>
     <t xml:space="preserve">5.13830041885376</t>
@@ -2948,19 +2948,19 @@
     <t xml:space="preserve">5.16601133346558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13246583938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25206279754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25498008728027</t>
+    <t xml:space="preserve">5.13246631622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25206327438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25498056411743</t>
   </si>
   <si>
     <t xml:space="preserve">5.316237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22435140609741</t>
+    <t xml:space="preserve">5.22435188293457</t>
   </si>
   <si>
     <t xml:space="preserve">5.16309452056885</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">5.07850170135498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05954074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92244148254395</t>
+    <t xml:space="preserve">5.05954122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9224419593811</t>
   </si>
   <si>
     <t xml:space="preserve">4.94286108016968</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">4.73283672332764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81305408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94723701477051</t>
+    <t xml:space="preserve">4.81305456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94723606109619</t>
   </si>
   <si>
     <t xml:space="preserve">4.91369104385376</t>
@@ -3002,31 +3002,31 @@
     <t xml:space="preserve">5.28706741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29436063766479</t>
+    <t xml:space="preserve">5.29436016082764</t>
   </si>
   <si>
     <t xml:space="preserve">5.20247411727905</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11496448516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24622917175293</t>
+    <t xml:space="preserve">5.1149640083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24622964859009</t>
   </si>
   <si>
     <t xml:space="preserve">5.12809085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09746217727661</t>
+    <t xml:space="preserve">5.09746170043945</t>
   </si>
   <si>
     <t xml:space="preserve">5.24768829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27685785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4445858001709</t>
+    <t xml:space="preserve">5.27685832977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44458532333374</t>
   </si>
   <si>
     <t xml:space="preserve">5.47813129425049</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">5.31040334701538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33519840240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32061338424683</t>
+    <t xml:space="preserve">5.33519744873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32061243057251</t>
   </si>
   <si>
     <t xml:space="preserve">5.22726917266846</t>
@@ -3050,58 +3050,58 @@
     <t xml:space="preserve">5.21414232254028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08141946792603</t>
+    <t xml:space="preserve">5.08141899108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.17768001556396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39207887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28269147872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29873561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18643093109131</t>
+    <t xml:space="preserve">5.39207983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29873466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18643045425415</t>
   </si>
   <si>
     <t xml:space="preserve">5.08725261688232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8991060256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89327144622803</t>
+    <t xml:space="preserve">4.89910554885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89327192306519</t>
   </si>
   <si>
     <t xml:space="preserve">4.87722873687744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76054859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95161199569702</t>
+    <t xml:space="preserve">4.76054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95161247253418</t>
   </si>
   <si>
     <t xml:space="preserve">4.8757700920105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.884521484375</t>
+    <t xml:space="preserve">4.88452100753784</t>
   </si>
   <si>
     <t xml:space="preserve">4.84368324279785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92390012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08871126174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20976638793945</t>
+    <t xml:space="preserve">4.92390060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08871030807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20976686477661</t>
   </si>
   <si>
     <t xml:space="preserve">5.08579397201538</t>
@@ -3110,31 +3110,31 @@
     <t xml:space="preserve">5.28560924530029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23310327529907</t>
+    <t xml:space="preserve">5.23310279846191</t>
   </si>
   <si>
     <t xml:space="preserve">5.203932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01141023635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0201621055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180643081665</t>
+    <t xml:space="preserve">5.0114107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02016162872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180595397949</t>
   </si>
   <si>
     <t xml:space="preserve">4.84222459793091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79992771148682</t>
+    <t xml:space="preserve">4.79992818832397</t>
   </si>
   <si>
     <t xml:space="preserve">4.84951686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7401294708252</t>
+    <t xml:space="preserve">4.74012899398804</t>
   </si>
   <si>
     <t xml:space="preserve">4.74596357345581</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">4.78971815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76638269424438</t>
+    <t xml:space="preserve">4.76638174057007</t>
   </si>
   <si>
     <t xml:space="preserve">4.64095163345337</t>
@@ -3155,25 +3155,25 @@
     <t xml:space="preserve">4.46884822845459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43967819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59427928924561</t>
+    <t xml:space="preserve">4.43967866897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59427881240845</t>
   </si>
   <si>
     <t xml:space="preserve">4.85680913925171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30894470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1966404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20539140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51605176925659</t>
+    <t xml:space="preserve">5.3089451789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19664001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20539093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51605224609375</t>
   </si>
   <si>
     <t xml:space="preserve">5.59626960754395</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">5.70419883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63710784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45041942596436</t>
+    <t xml:space="preserve">5.63710737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45041990280151</t>
   </si>
   <si>
     <t xml:space="preserve">5.52917861938477</t>
@@ -3209,10 +3209,10 @@
     <t xml:space="preserve">5.46500444412231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54230451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60210371017456</t>
+    <t xml:space="preserve">5.54230546951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60210418701172</t>
   </si>
   <si>
     <t xml:space="preserve">5.53209590911865</t>
@@ -3221,22 +3221,22 @@
     <t xml:space="preserve">5.48979902267456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49709177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4752140045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34978342056274</t>
+    <t xml:space="preserve">5.49709129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47521448135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34978294372559</t>
   </si>
   <si>
     <t xml:space="preserve">5.36145114898682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53792953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49271631240845</t>
+    <t xml:space="preserve">5.53793001174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49271583557129</t>
   </si>
   <si>
     <t xml:space="preserve">5.428542137146</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">5.39062118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37895345687866</t>
+    <t xml:space="preserve">5.3789529800415</t>
   </si>
   <si>
     <t xml:space="preserve">5.52042770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52480363845825</t>
+    <t xml:space="preserve">5.52480268478394</t>
   </si>
   <si>
     <t xml:space="preserve">5.40228891372681</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">5.42270755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62835693359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61231327056885</t>
+    <t xml:space="preserve">5.62835741043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61231279373169</t>
   </si>
   <si>
     <t xml:space="preserve">5.50438451766968</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">5.46208715438843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51021766662598</t>
+    <t xml:space="preserve">5.51021814346313</t>
   </si>
   <si>
     <t xml:space="preserve">5.46937990188599</t>
@@ -3284,34 +3284,34 @@
     <t xml:space="preserve">5.38187026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47083902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40083026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40520620346069</t>
+    <t xml:space="preserve">5.47083806991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40083074569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40520524978638</t>
   </si>
   <si>
     <t xml:space="preserve">5.44896078109741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35707569122314</t>
+    <t xml:space="preserve">5.35707521438599</t>
   </si>
   <si>
     <t xml:space="preserve">5.39499616622925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.370201587677</t>
+    <t xml:space="preserve">5.37020206451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.51167631149292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73045206069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8996376991272</t>
+    <t xml:space="preserve">5.7304515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89963817596436</t>
   </si>
   <si>
     <t xml:space="preserve">5.97985506057739</t>
@@ -3323,22 +3323,22 @@
     <t xml:space="preserve">6.23071765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41740560531616</t>
+    <t xml:space="preserve">6.417405128479</t>
   </si>
   <si>
     <t xml:space="preserve">6.50637435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48012113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59242725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53700351715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57929992675781</t>
+    <t xml:space="preserve">6.48012065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59242630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53700304031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57929944992065</t>
   </si>
   <si>
     <t xml:space="preserve">6.54429531097412</t>
@@ -3347,61 +3347,61 @@
     <t xml:space="preserve">6.62159585952759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61430311203003</t>
+    <t xml:space="preserve">6.61430358886719</t>
   </si>
   <si>
     <t xml:space="preserve">6.58221673965454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53408575057983</t>
+    <t xml:space="preserve">6.53408527374268</t>
   </si>
   <si>
     <t xml:space="preserve">6.3955283164978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28468227386475</t>
+    <t xml:space="preserve">6.28468179702759</t>
   </si>
   <si>
     <t xml:space="preserve">6.50199937820435</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43490839004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52679347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61138677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72514915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535919189453</t>
+    <t xml:space="preserve">6.43490743637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52679300308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61138725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7251501083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535966873169</t>
   </si>
   <si>
     <t xml:space="preserve">6.77473878860474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8505802154541</t>
+    <t xml:space="preserve">6.85058069229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.86516571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9016284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01976633071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09415006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09706735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87975025177002</t>
+    <t xml:space="preserve">6.90162897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01976776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09415149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09706878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87974977493286</t>
   </si>
   <si>
     <t xml:space="preserve">6.84037065505981</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">6.90016984939575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90600442886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92058944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93954992294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03581094741821</t>
+    <t xml:space="preserve">6.90600395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92058849334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93954944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03581047058105</t>
   </si>
   <si>
     <t xml:space="preserve">6.89579439163208</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">6.80682563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81849384307861</t>
+    <t xml:space="preserve">6.81849431991577</t>
   </si>
   <si>
     <t xml:space="preserve">6.80974292755127</t>
@@ -3449,46 +3449,46 @@
     <t xml:space="preserve">6.78640651702881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8520393371582</t>
+    <t xml:space="preserve">6.85203886032104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84766387939453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70910692214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64201402664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64639091491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83599519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80828428268433</t>
+    <t xml:space="preserve">6.7091064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64201498031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64639043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8359956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80828475952148</t>
   </si>
   <si>
     <t xml:space="preserve">6.82724523544312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85641479492188</t>
+    <t xml:space="preserve">6.85641527175903</t>
   </si>
   <si>
     <t xml:space="preserve">6.92788076400757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78057241439819</t>
+    <t xml:space="preserve">6.78057336807251</t>
   </si>
   <si>
     <t xml:space="preserve">6.9089207649231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9468412399292</t>
+    <t xml:space="preserve">6.94684219360352</t>
   </si>
   <si>
     <t xml:space="preserve">7.04018640518188</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">7.05477142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01393270492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08394145965576</t>
+    <t xml:space="preserve">7.01393222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08394050598145</t>
   </si>
   <si>
     <t xml:space="preserve">7.13352966308594</t>
@@ -3509,37 +3509,37 @@
     <t xml:space="preserve">7.19770383834839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05914735794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0664381980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915372848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11748695373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14811563491821</t>
+    <t xml:space="preserve">7.05914640426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06643915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11748647689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14811420440674</t>
   </si>
   <si>
     <t xml:space="preserve">7.21228981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27063083648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2997989654541</t>
+    <t xml:space="preserve">7.27062940597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034462928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29979848861694</t>
   </si>
   <si>
     <t xml:space="preserve">7.25604391098022</t>
@@ -3551,52 +3551,52 @@
     <t xml:space="preserve">7.20791339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26333618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2545862197876</t>
+    <t xml:space="preserve">7.26333665847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25458478927612</t>
   </si>
   <si>
     <t xml:space="preserve">7.23270845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23562479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17582750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22249937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28083848953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27500438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20062065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18311882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19332933425903</t>
+    <t xml:space="preserve">7.23562574386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17582607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22249841690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28083944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27500486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20062112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18311929702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19332885742188</t>
   </si>
   <si>
     <t xml:space="preserve">7.18749475479126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36178493499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14082288742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14957332611084</t>
+    <t xml:space="preserve">7.36178541183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14082193374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14957427978516</t>
   </si>
   <si>
     <t xml:space="preserve">6.92350625991821</t>
@@ -3611,61 +3611,61 @@
     <t xml:space="preserve">7.20499658584595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14519786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09560918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86808347702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95559215545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23416709899902</t>
+    <t xml:space="preserve">7.14519882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09560871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86808300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9555926322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23416614532471</t>
   </si>
   <si>
     <t xml:space="preserve">7.31073760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28667211532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28813171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937252044678</t>
+    <t xml:space="preserve">7.2866735458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28813123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937204360962</t>
   </si>
   <si>
     <t xml:space="preserve">7.13207197189331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2108302116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2837553024292</t>
+    <t xml:space="preserve">7.21083068847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28375625610352</t>
   </si>
   <si>
     <t xml:space="preserve">7.29615259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19041156768799</t>
+    <t xml:space="preserve">7.19041204452515</t>
   </si>
   <si>
     <t xml:space="preserve">7.27792119979858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27354669570923</t>
+    <t xml:space="preserve">7.27354621887207</t>
   </si>
   <si>
     <t xml:space="preserve">7.17728567123413</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1714506149292</t>
+    <t xml:space="preserve">7.17145156860352</t>
   </si>
   <si>
     <t xml:space="preserve">7.04601955413818</t>
@@ -3674,70 +3674,70 @@
     <t xml:space="preserve">7.09852647781372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13644742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25166940689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27937984466553</t>
+    <t xml:space="preserve">7.13644695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25166845321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27938032150269</t>
   </si>
   <si>
     <t xml:space="preserve">7.11456966400146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24875116348267</t>
+    <t xml:space="preserve">7.24875164031982</t>
   </si>
   <si>
     <t xml:space="preserve">7.36543226242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47846508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33626127243042</t>
+    <t xml:space="preserve">7.47846651077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33626222610474</t>
   </si>
   <si>
     <t xml:space="preserve">7.53680515289307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61337614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68630170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5878529548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734951019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50399017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294141769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21520566940308</t>
+    <t xml:space="preserve">7.61337661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68630266189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58785247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50398969650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21520662307739</t>
   </si>
   <si>
     <t xml:space="preserve">7.38001728057861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41283321380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43106269836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53316020965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5805606842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60608386993408</t>
+    <t xml:space="preserve">7.41283273696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43106365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53315925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58056116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60608434677124</t>
   </si>
   <si>
     <t xml:space="preserve">7.55868291854858</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">7.52222061157227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6425461769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67171716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77016544342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76651906967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88684558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8759069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81392097473145</t>
+    <t xml:space="preserve">7.64254713058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67171669006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77016592025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76652002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88684511184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87590646743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8139214515686</t>
   </si>
   <si>
     <t xml:space="preserve">7.81756782531738</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">7.90507698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.879554271698</t>
+    <t xml:space="preserve">7.87955522537231</t>
   </si>
   <si>
     <t xml:space="preserve">7.79204320907593</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">7.70088720321655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90313339233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72111129760742</t>
+    <t xml:space="preserve">7.90313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7226676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72111034393311</t>
   </si>
   <si>
     <t xml:space="preserve">7.45352554321289</t>
@@ -3803,85 +3803,85 @@
     <t xml:space="preserve">7.56398296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59976434707642</t>
+    <t xml:space="preserve">7.59976387023926</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63865756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776756286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79034185409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86034965515137</t>
+    <t xml:space="preserve">7.6386570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776851654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79034233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86034917831421</t>
   </si>
   <si>
     <t xml:space="preserve">7.82534551620483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80978870391846</t>
+    <t xml:space="preserve">7.80978918075562</t>
   </si>
   <si>
     <t xml:space="preserve">7.71488904953003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76311540603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76156044006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84868097305298</t>
+    <t xml:space="preserve">7.76311588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76155996322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84868144989014</t>
   </si>
   <si>
     <t xml:space="preserve">7.80589914321899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52197742462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64954805374146</t>
+    <t xml:space="preserve">7.52197790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6495475769043</t>
   </si>
   <si>
     <t xml:space="preserve">7.68999719619751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8136773109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86423921585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9264669418335</t>
+    <t xml:space="preserve">7.81367778778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86423778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92646741867065</t>
   </si>
   <si>
     <t xml:space="preserve">8.0859317779541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10148811340332</t>
+    <t xml:space="preserve">8.10148906707764</t>
   </si>
   <si>
     <t xml:space="preserve">8.0820426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07815265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07037353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13260364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23761558532715</t>
+    <t xml:space="preserve">8.07815456390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07037448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13260269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23761463165283</t>
   </si>
   <si>
     <t xml:space="preserve">8.17538547515869</t>
@@ -3890,34 +3890,34 @@
     <t xml:space="preserve">8.09759998321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03537082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092716217041</t>
+    <t xml:space="preserve">8.03536987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092811584473</t>
   </si>
   <si>
     <t xml:space="preserve">8.02370166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61532163619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66043853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77867412567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02759075164795</t>
+    <t xml:space="preserve">7.61532068252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66043710708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77867460250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02759170532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.10926723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79812002182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05870532989502</t>
+    <t xml:space="preserve">7.79812049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05870628356934</t>
   </si>
   <si>
     <t xml:space="preserve">8.22983741760254</t>
@@ -3929,25 +3929,25 @@
     <t xml:space="preserve">8.14427185058594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90702104568481</t>
+    <t xml:space="preserve">7.90702199935913</t>
   </si>
   <si>
     <t xml:space="preserve">8.07426357269287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88368654251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9381365776062</t>
+    <t xml:space="preserve">7.88368558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93813610076904</t>
   </si>
   <si>
     <t xml:space="preserve">7.77556276321411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67288446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67755031585693</t>
+    <t xml:space="preserve">7.67288494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67755079269409</t>
   </si>
   <si>
     <t xml:space="preserve">7.26994800567627</t>
@@ -3956,16 +3956,16 @@
     <t xml:space="preserve">7.29172801971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25439167022705</t>
+    <t xml:space="preserve">7.25439119338989</t>
   </si>
   <si>
     <t xml:space="preserve">6.68654823303223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73477554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68499231338501</t>
+    <t xml:space="preserve">6.73477602005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68499279022217</t>
   </si>
   <si>
     <t xml:space="preserve">6.12337207794189</t>
@@ -3977,13 +3977,13 @@
     <t xml:space="preserve">6.08603429794312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63520812988281</t>
+    <t xml:space="preserve">6.63520860671997</t>
   </si>
   <si>
     <t xml:space="preserve">6.3193941116333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35050868988037</t>
+    <t xml:space="preserve">6.35050821304321</t>
   </si>
   <si>
     <t xml:space="preserve">6.61187267303467</t>
@@ -3992,10 +3992,10 @@
     <t xml:space="preserve">6.66165590286255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10970830917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06925868988037</t>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06925821304321</t>
   </si>
   <si>
     <t xml:space="preserve">7.22638750076294</t>
@@ -4004,25 +4004,25 @@
     <t xml:space="preserve">7.06770324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12993288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02103090286255</t>
+    <t xml:space="preserve">7.12993240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02103137969971</t>
   </si>
   <si>
     <t xml:space="preserve">7.0505895614624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22949838638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10659646987915</t>
+    <t xml:space="preserve">7.22949886322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10659599304199</t>
   </si>
   <si>
     <t xml:space="preserve">7.17193698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30417537689209</t>
+    <t xml:space="preserve">7.30417490005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.11904287338257</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">7.03503322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02569770812988</t>
+    <t xml:space="preserve">7.02569818496704</t>
   </si>
   <si>
     <t xml:space="preserve">6.94946718215942</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">7.18438339233398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44885873794556</t>
+    <t xml:space="preserve">7.37418174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44885778427124</t>
   </si>
   <si>
     <t xml:space="preserve">7.17971563339233</t>
@@ -4064,85 +4064,85 @@
     <t xml:space="preserve">7.38196182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38040590286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686147689819</t>
+    <t xml:space="preserve">7.38040637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686195373535</t>
   </si>
   <si>
     <t xml:space="preserve">7.88757467269897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74755907058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50486469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48308515548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60598707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54842567443848</t>
+    <t xml:space="preserve">7.74755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50486421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4830846786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60598754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54842615127563</t>
   </si>
   <si>
     <t xml:space="preserve">7.71955585479736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70088672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71022129058838</t>
+    <t xml:space="preserve">7.70088624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71022176742554</t>
   </si>
   <si>
     <t xml:space="preserve">7.5235333442688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44574546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38973951339722</t>
+    <t xml:space="preserve">7.44574689865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38973999023438</t>
   </si>
   <si>
     <t xml:space="preserve">7.43485593795776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26216983795166</t>
+    <t xml:space="preserve">7.26217031478882</t>
   </si>
   <si>
     <t xml:space="preserve">7.34151268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46752691268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41152095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46908235549927</t>
+    <t xml:space="preserve">7.46752738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41152048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46908330917358</t>
   </si>
   <si>
     <t xml:space="preserve">7.4317455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32906675338745</t>
+    <t xml:space="preserve">7.32906627655029</t>
   </si>
   <si>
     <t xml:space="preserve">7.42085552215576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53442239761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49864149093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68532943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50797605514526</t>
+    <t xml:space="preserve">7.53442287445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49864196777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68532991409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50797653198242</t>
   </si>
   <si>
     <t xml:space="preserve">7.01325225830078</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">6.96813583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95102262496948</t>
+    <t xml:space="preserve">6.9510235786438</t>
   </si>
   <si>
     <t xml:space="preserve">6.63054180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59631490707397</t>
+    <t xml:space="preserve">6.59631443023682</t>
   </si>
   <si>
     <t xml:space="preserve">6.68188047409058</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">6.7192177772522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5683126449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71144008636475</t>
+    <t xml:space="preserve">6.56831216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7114405632019</t>
   </si>
   <si>
     <t xml:space="preserve">6.56675672531128</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">6.60253810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42362928390503</t>
+    <t xml:space="preserve">6.42362976074219</t>
   </si>
   <si>
     <t xml:space="preserve">6.41896200180054</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">6.45785474777222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55586624145508</t>
+    <t xml:space="preserve">6.55586671829224</t>
   </si>
   <si>
     <t xml:space="preserve">6.4905252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41273832321167</t>
+    <t xml:space="preserve">6.41273880004883</t>
   </si>
   <si>
     <t xml:space="preserve">6.3582878112793</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">6.26027679443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2213830947876</t>
+    <t xml:space="preserve">6.22138357162476</t>
   </si>
   <si>
     <t xml:space="preserve">6.24783039093018</t>
@@ -4241,37 +4241,37 @@
     <t xml:space="preserve">6.17937850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24005317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35673236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50297069549561</t>
+    <t xml:space="preserve">6.24005270004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35673189163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50297164916992</t>
   </si>
   <si>
     <t xml:space="preserve">6.54653310775757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55119943618774</t>
+    <t xml:space="preserve">6.55119895935059</t>
   </si>
   <si>
     <t xml:space="preserve">6.59787082672119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64921045303345</t>
+    <t xml:space="preserve">6.64921092987061</t>
   </si>
   <si>
     <t xml:space="preserve">6.7021050453186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65232181549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64298820495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66009998321533</t>
+    <t xml:space="preserve">6.65232229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6429877281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66010046005249</t>
   </si>
   <si>
     <t xml:space="preserve">6.72544145584106</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">6.77055835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77833652496338</t>
+    <t xml:space="preserve">6.77833604812622</t>
   </si>
   <si>
     <t xml:space="preserve">6.72232961654663</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">6.69588232040405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44696521759033</t>
+    <t xml:space="preserve">6.44696474075317</t>
   </si>
   <si>
     <t xml:space="preserve">6.27427816390991</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">6.32250642776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2945032119751</t>
+    <t xml:space="preserve">6.29450273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.25872039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17004442214966</t>
+    <t xml:space="preserve">6.1700439453125</t>
   </si>
   <si>
     <t xml:space="preserve">6.15448665618896</t>
@@ -4325,25 +4325,25 @@
     <t xml:space="preserve">6.21204900741577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19493579864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22916269302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28672409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44229745864868</t>
+    <t xml:space="preserve">6.19493627548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22916221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28672361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44229793548584</t>
   </si>
   <si>
     <t xml:space="preserve">6.58075761795044</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58698129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65387773513794</t>
+    <t xml:space="preserve">6.58698177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65387725830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.63365268707275</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">6.09381294250488</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03313970565796</t>
+    <t xml:space="preserve">6.0331392288208</t>
   </si>
   <si>
     <t xml:space="preserve">5.92112684249878</t>
@@ -4382,19 +4382,19 @@
     <t xml:space="preserve">6.59009265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48119115829468</t>
+    <t xml:space="preserve">6.48119163513184</t>
   </si>
   <si>
     <t xml:space="preserve">6.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19649076461792</t>
+    <t xml:space="preserve">6.19649171829224</t>
   </si>
   <si>
     <t xml:space="preserve">6.18248987197876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10003566741943</t>
+    <t xml:space="preserve">6.10003614425659</t>
   </si>
   <si>
     <t xml:space="preserve">6.2836127281189</t>
@@ -4403,19 +4403,19 @@
     <t xml:space="preserve">6.45629930496216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52164077758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67877006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85612297058105</t>
+    <t xml:space="preserve">6.52164030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67876958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85612344741821</t>
   </si>
   <si>
     <t xml:space="preserve">6.8499002456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85767936706543</t>
+    <t xml:space="preserve">6.85767889022827</t>
   </si>
   <si>
     <t xml:space="preserve">7.07081460952759</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">7.09726238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19060564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15326881408691</t>
+    <t xml:space="preserve">7.19060611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15326833724976</t>
   </si>
   <si>
     <t xml:space="preserve">7.31039762496948</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">7.63399076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74289226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91480112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90892314910889</t>
+    <t xml:space="preserve">7.74289131164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9148006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90892267227173</t>
   </si>
   <si>
     <t xml:space="preserve">7.91228151321411</t>
@@ -4481,10 +4481,10 @@
     <t xml:space="preserve">7.69562101364136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71409606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73928880691528</t>
+    <t xml:space="preserve">7.7140965461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73928928375244</t>
   </si>
   <si>
     <t xml:space="preserve">7.68554496765137</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">7.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79471445083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087284088135</t>
+    <t xml:space="preserve">7.79471349716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087331771851</t>
   </si>
   <si>
     <t xml:space="preserve">7.48064184188843</t>
@@ -4520,13 +4520,13 @@
     <t xml:space="preserve">7.52934789657593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66371059417725</t>
+    <t xml:space="preserve">7.6637110710144</t>
   </si>
   <si>
     <t xml:space="preserve">7.56965732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58477210998535</t>
+    <t xml:space="preserve">7.58477258682251</t>
   </si>
   <si>
     <t xml:space="preserve">7.5864520072937</t>
@@ -4538,28 +4538,28 @@
     <t xml:space="preserve">7.64691495895386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54446363449097</t>
+    <t xml:space="preserve">7.54446315765381</t>
   </si>
   <si>
     <t xml:space="preserve">7.59485006332397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67210817337036</t>
+    <t xml:space="preserve">7.6721076965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.79807329177856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78463745117188</t>
+    <t xml:space="preserve">7.78463649749756</t>
   </si>
   <si>
     <t xml:space="preserve">7.77959823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85685729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90052461624146</t>
+    <t xml:space="preserve">7.85685634613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90052509307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.02145099639893</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">8.09535026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11046600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01977157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92403841018677</t>
+    <t xml:space="preserve">8.11046695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01977062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92403888702393</t>
   </si>
   <si>
     <t xml:space="preserve">8.04496383666992</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">8.08191394805908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13230133056641</t>
+    <t xml:space="preserve">8.13230037689209</t>
   </si>
   <si>
     <t xml:space="preserve">8.18100643157959</t>
@@ -4601,13 +4601,13 @@
     <t xml:space="preserve">8.31536960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34560108184814</t>
+    <t xml:space="preserve">8.34560012817383</t>
   </si>
   <si>
     <t xml:space="preserve">8.27674007415771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37247371673584</t>
+    <t xml:space="preserve">8.37247467041016</t>
   </si>
   <si>
     <t xml:space="preserve">8.39430809020996</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">8.5698184967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69998168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56562042236328</t>
+    <t xml:space="preserve">8.69998264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56561946868896</t>
   </si>
   <si>
     <t xml:space="preserve">8.70838069915771</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">8.74197101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60340881347656</t>
+    <t xml:space="preserve">8.60340976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.6328010559082</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">8.50263690948486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49423885345459</t>
+    <t xml:space="preserve">8.49423980712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.39094734191895</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">8.25490665435791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42285919189453</t>
+    <t xml:space="preserve">8.42285823822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164367675781</t>
@@ -4676,22 +4676,22 @@
     <t xml:space="preserve">8.45645046234131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51103591918945</t>
+    <t xml:space="preserve">8.51103496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.46064853668213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51523303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40186595916748</t>
+    <t xml:space="preserve">8.51523399353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40186500549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.16757106781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80143165588379</t>
+    <t xml:space="preserve">7.80143213272095</t>
   </si>
   <si>
     <t xml:space="preserve">7.99793815612793</t>
@@ -4703,10 +4703,10 @@
     <t xml:space="preserve">7.52095031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43193483352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73425054550171</t>
+    <t xml:space="preserve">7.43193435668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73425102233887</t>
   </si>
   <si>
     <t xml:space="preserve">7.63179922103882</t>
@@ -4715,40 +4715,40 @@
     <t xml:space="preserve">7.55286169052124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51591110229492</t>
+    <t xml:space="preserve">7.51591157913208</t>
   </si>
   <si>
     <t xml:space="preserve">7.60660552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7241735458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78295660018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8115086555481</t>
+    <t xml:space="preserve">7.72417402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78295612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81150913238525</t>
   </si>
   <si>
     <t xml:space="preserve">7.80982971191406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74096918106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075704574585</t>
+    <t xml:space="preserve">7.74096870422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075656890869</t>
   </si>
   <si>
     <t xml:space="preserve">7.92739772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93915367126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09367084503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0264892578125</t>
+    <t xml:space="preserve">7.93915414810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09366989135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02649021148682</t>
   </si>
   <si>
     <t xml:space="preserve">8.18772411346436</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">8.17260932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19780254364014</t>
+    <t xml:space="preserve">8.19780158996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.26834201812744</t>
@@ -4799,13 +4799,13 @@
     <t xml:space="preserve">8.13565921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14741516113281</t>
+    <t xml:space="preserve">8.14741611480713</t>
   </si>
   <si>
     <t xml:space="preserve">8.18436622619629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25322532653809</t>
+    <t xml:space="preserve">8.2532262802124</t>
   </si>
   <si>
     <t xml:space="preserve">8.27338123321533</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">8.42705821990967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54462623596191</t>
+    <t xml:space="preserve">8.5446252822876</t>
   </si>
   <si>
     <t xml:space="preserve">8.7335729598999</t>
@@ -4826,16 +4826,16 @@
     <t xml:space="preserve">8.7713623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67898750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67479038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92252159118652</t>
+    <t xml:space="preserve">8.67898845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67478942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64539813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92252063751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.98970222473145</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">8.98130416870117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96450996398926</t>
+    <t xml:space="preserve">8.96450901031494</t>
   </si>
   <si>
     <t xml:space="preserve">9.17025184631348</t>
@@ -4859,28 +4859,28 @@
     <t xml:space="preserve">9.28781986236572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38859176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49776172637939</t>
+    <t xml:space="preserve">9.38859081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49776077270508</t>
   </si>
   <si>
     <t xml:space="preserve">9.39698791503906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42638111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40538597106934</t>
+    <t xml:space="preserve">9.42638206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40538692474365</t>
   </si>
   <si>
     <t xml:space="preserve">9.30461406707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33400630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14925861358643</t>
+    <t xml:space="preserve">9.33400535583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14925765991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.03588962554932</t>
@@ -4889,16 +4889,16 @@
     <t xml:space="preserve">9.01909351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04848480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06947994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20384311676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34660339355469</t>
+    <t xml:space="preserve">9.04848575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06948089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20384216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34660243988037</t>
   </si>
   <si>
     <t xml:space="preserve">9.35500049591064</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">9.27942180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24583148956299</t>
+    <t xml:space="preserve">9.24583053588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25003051757812</t>
@@ -4916,13 +4916,13 @@
     <t xml:space="preserve">9.25842761993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43057918548584</t>
+    <t xml:space="preserve">9.43057823181152</t>
   </si>
   <si>
     <t xml:space="preserve">9.48936367034912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48096466064453</t>
+    <t xml:space="preserve">9.48096561431885</t>
   </si>
   <si>
     <t xml:space="preserve">9.52295398712158</t>
@@ -4940,16 +4940,16 @@
     <t xml:space="preserve">9.63632297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930458068848</t>
+    <t xml:space="preserve">9.69930553436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.70770263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68250942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0394105911255</t>
+    <t xml:space="preserve">9.68250846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0394096374512</t>
   </si>
   <si>
     <t xml:space="preserve">10.1779718399048</t>
@@ -5006,10 +5006,10 @@
     <t xml:space="preserve">9.91344547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0268144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1653747558594</t>
+    <t xml:space="preserve">10.0268135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1653757095337</t>
   </si>
   <si>
     <t xml:space="preserve">10.194766998291</t>
@@ -5018,16 +5018,16 @@
     <t xml:space="preserve">10.1359834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1401815414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.144380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2199592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0981931686401</t>
+    <t xml:space="preserve">10.1401824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1443815231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2199602127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0981941223145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1989660263062</t>
@@ -5042,19 +5042,19 @@
     <t xml:space="preserve">10.2241592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2115621566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3039360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2535514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1905689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3291292190552</t>
+    <t xml:space="preserve">10.2115612030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.303936958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.25355052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1905679702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3291301727295</t>
   </si>
   <si>
     <t xml:space="preserve">10.4173049926758</t>
@@ -5081,7 +5081,7 @@
     <t xml:space="preserve">10.5222768783569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3921117782593</t>
+    <t xml:space="preserve">10.3921127319336</t>
   </si>
   <si>
     <t xml:space="preserve">10.3207321166992</t>
@@ -5099,13 +5099,13 @@
     <t xml:space="preserve">10.2283582687378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2367553710938</t>
+    <t xml:space="preserve">10.2367544174194</t>
   </si>
   <si>
     <t xml:space="preserve">10.295539855957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695737838745</t>
+    <t xml:space="preserve">10.1695728302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.1527786254883</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">9.55654430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682472229004</t>
+    <t xml:space="preserve">9.26682376861572</t>
   </si>
   <si>
     <t xml:space="preserve">9.37179565429688</t>
@@ -5150,7 +5150,7 @@
     <t xml:space="preserve">9.63212394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67831039428711</t>
+    <t xml:space="preserve">9.67831134796143</t>
   </si>
   <si>
     <t xml:space="preserve">9.69090747833252</t>
@@ -5165,13 +5165,13 @@
     <t xml:space="preserve">9.84817409515381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73050308227539</t>
+    <t xml:space="preserve">9.73050212860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.82554531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81649398803711</t>
+    <t xml:space="preserve">9.81649303436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.81196784973145</t>
@@ -5180,10 +5180,10 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71240043640137</t>
+    <t xml:space="preserve">9.73955535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71239948272705</t>
   </si>
   <si>
     <t xml:space="preserve">9.75313091278076</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">9.65808963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92511367797852</t>
+    <t xml:space="preserve">9.9251127243042</t>
   </si>
   <si>
     <t xml:space="preserve">10.0020523071289</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0925674438477</t>
+    <t xml:space="preserve">10.092568397522</t>
   </si>
   <si>
     <t xml:space="preserve">10.0337324142456</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">10.0699396133423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0654144287109</t>
+    <t xml:space="preserve">10.0654134750366</t>
   </si>
   <si>
     <t xml:space="preserve">10.1378259658813</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">10.1785583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.151403427124</t>
+    <t xml:space="preserve">10.1514043807983</t>
   </si>
   <si>
     <t xml:space="preserve">10.115198135376</t>
@@ -5240,7 +5240,7 @@
     <t xml:space="preserve">10.142352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0608863830566</t>
+    <t xml:space="preserve">10.060887336731</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695070266724</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">10.4455823898315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7126045227051</t>
+    <t xml:space="preserve">10.7126054763794</t>
   </si>
   <si>
     <t xml:space="preserve">10.7895441055298</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">10.9434213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9253187179565</t>
+    <t xml:space="preserve">10.9253177642822</t>
   </si>
   <si>
     <t xml:space="preserve">10.9615240097046</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">10.9388952255249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0022563934326</t>
+    <t xml:space="preserve">11.0022573471069</t>
   </si>
   <si>
     <t xml:space="preserve">10.8393278121948</t>
@@ -5309,13 +5309,13 @@
     <t xml:space="preserve">10.7669153213501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7171316146851</t>
+    <t xml:space="preserve">10.7171306610107</t>
   </si>
   <si>
     <t xml:space="preserve">10.5315723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4908390045166</t>
+    <t xml:space="preserve">10.4908399581909</t>
   </si>
   <si>
     <t xml:space="preserve">10.4184274673462</t>
@@ -5342,19 +5342,19 @@
     <t xml:space="preserve">11.7173357009888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5906133651733</t>
+    <t xml:space="preserve">11.5906143188477</t>
   </si>
   <si>
     <t xml:space="preserve">11.4955711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4231586456299</t>
+    <t xml:space="preserve">11.4231576919556</t>
   </si>
   <si>
     <t xml:space="preserve">11.4005289077759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4141054153442</t>
+    <t xml:space="preserve">11.4141063690186</t>
   </si>
   <si>
     <t xml:space="preserve">11.3869514465332</t>
@@ -5366,19 +5366,19 @@
     <t xml:space="preserve">11.6313457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5815620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.595139503479</t>
+    <t xml:space="preserve">11.581561088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5951404571533</t>
   </si>
   <si>
     <t xml:space="preserve">11.7625942230225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6901817321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8576364517212</t>
+    <t xml:space="preserve">11.6901807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8576374053955</t>
   </si>
   <si>
     <t xml:space="preserve">12.0160388946533</t>
@@ -5393,37 +5393,37 @@
     <t xml:space="preserve">12.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2785367965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3328475952148</t>
+    <t xml:space="preserve">12.2785358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3328466415405</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003023147583</t>
+    <t xml:space="preserve">12.5003032684326</t>
   </si>
   <si>
     <t xml:space="preserve">12.3781061172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5093536376953</t>
+    <t xml:space="preserve">12.509352684021</t>
   </si>
   <si>
     <t xml:space="preserve">12.3962078094482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4052591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3102188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554754257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2875881195068</t>
+    <t xml:space="preserve">12.4052600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3102178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2875890731812</t>
   </si>
   <si>
     <t xml:space="preserve">12.124659538269</t>
@@ -5435,10 +5435,10 @@
     <t xml:space="preserve">12.2921142578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2151765823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3237943649292</t>
+    <t xml:space="preserve">12.2151756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3237953186035</t>
   </si>
   <si>
     <t xml:space="preserve">12.3509502410889</t>
@@ -5453,7 +5453,7 @@
     <t xml:space="preserve">12.083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1970720291138</t>
+    <t xml:space="preserve">12.1970729827881</t>
   </si>
   <si>
     <t xml:space="preserve">12.3826313018799</t>
@@ -5465,7 +5465,7 @@
     <t xml:space="preserve">12.6722831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7718505859375</t>
+    <t xml:space="preserve">12.7718496322632</t>
   </si>
   <si>
     <t xml:space="preserve">13.0796060562134</t>
@@ -6495,6 +6495,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.5249996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6700000762939</t>
   </si>
 </sst>
 </file>
@@ -71755,7 +71758,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6911921296</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>1382433</v>
@@ -71776,6 +71779,32 @@
         <v>2160</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6938425926</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>1603143</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>16.7350006103516</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>16.3549995422363</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>16.4449996948242</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>16.6700000762939</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2161</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="2173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="2174">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,37 +44,37 @@
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18521499633789</t>
+    <t xml:space="preserve">5.18521547317505</t>
   </si>
   <si>
     <t xml:space="preserve">5.05528259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95858860015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83772134780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8105263710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92535018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97974061965942</t>
+    <t xml:space="preserve">4.95858955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83772087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81052589416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92534971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97974014282227</t>
   </si>
   <si>
     <t xml:space="preserve">4.91930723190308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73196172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50533628463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59900808334351</t>
+    <t xml:space="preserve">4.73196220397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50533580780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59900760650635</t>
   </si>
   <si>
     <t xml:space="preserve">4.41468524932861</t>
@@ -83,112 +83,112 @@
     <t xml:space="preserve">4.65944194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67455053329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52346611022949</t>
+    <t xml:space="preserve">4.67455005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52346515655518</t>
   </si>
   <si>
     <t xml:space="preserve">4.59598636627197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52648735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27870845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4509449005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31194734573364</t>
+    <t xml:space="preserve">4.52648687362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27870893478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45094537734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31194829940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.19410133361816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00373506546021</t>
+    <t xml:space="preserve">4.00373554229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.09136486053467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98862648010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61696004867554</t>
+    <t xml:space="preserve">3.9886269569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6169605255127</t>
   </si>
   <si>
     <t xml:space="preserve">3.41450667381287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6713502407074</t>
+    <t xml:space="preserve">3.67135000228882</t>
   </si>
   <si>
     <t xml:space="preserve">3.47796201705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54443883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64717698097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.680415391922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74991416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64113259315491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091589927673</t>
+    <t xml:space="preserve">3.5444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64717650413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68041563034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113306999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091661453247</t>
   </si>
   <si>
     <t xml:space="preserve">3.75595760345459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6622850894928</t>
+    <t xml:space="preserve">3.66228437423706</t>
   </si>
   <si>
     <t xml:space="preserve">3.62300300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67437148094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76804423332214</t>
+    <t xml:space="preserve">3.67437171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76804399490356</t>
   </si>
   <si>
     <t xml:space="preserve">3.78315305709839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93725872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08834218978882</t>
+    <t xml:space="preserve">3.93725824356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">4.1034517288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0248875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006350517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96143174171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97351956367493</t>
+    <t xml:space="preserve">4.02488708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96143221855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97351908683777</t>
   </si>
   <si>
     <t xml:space="preserve">4.0339527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38446807861328</t>
+    <t xml:space="preserve">4.38446855545044</t>
   </si>
   <si>
     <t xml:space="preserve">4.42979335784912</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">4.28173112869263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29986000061035</t>
+    <t xml:space="preserve">4.29986095428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.03697443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07323408126831</t>
+    <t xml:space="preserve">4.07323455810547</t>
   </si>
   <si>
     <t xml:space="preserve">4.09438610076904</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">4.01884412765503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99164915084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87984681129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90401983261108</t>
+    <t xml:space="preserve">3.99164843559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87984657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9040195941925</t>
   </si>
   <si>
     <t xml:space="preserve">3.82545638084412</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.79221725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83149909973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75897908210754</t>
+    <t xml:space="preserve">3.8314995765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75897884368896</t>
   </si>
   <si>
     <t xml:space="preserve">3.79523921012878</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">3.60487341880798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81336975097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85567355155945</t>
+    <t xml:space="preserve">3.81336903572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85567307472229</t>
   </si>
   <si>
     <t xml:space="preserve">3.77408719062805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97049713134766</t>
+    <t xml:space="preserve">3.97049736976624</t>
   </si>
   <si>
     <t xml:space="preserve">4.04301738739014</t>
@@ -266,58 +266,58 @@
     <t xml:space="preserve">4.36935949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38748979568481</t>
+    <t xml:space="preserve">4.38749027252197</t>
   </si>
   <si>
     <t xml:space="preserve">4.39655494689941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33612203598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21223163604736</t>
+    <t xml:space="preserve">4.33612108230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21223115921021</t>
   </si>
   <si>
     <t xml:space="preserve">4.05208253860474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88588953018188</t>
+    <t xml:space="preserve">3.88588929176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.85265159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80430459976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078166007996</t>
+    <t xml:space="preserve">3.80430388450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87078142166138</t>
   </si>
   <si>
     <t xml:space="preserve">3.8979766368866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93423700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92214941978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90704202651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97956228256226</t>
+    <t xml:space="preserve">3.93423676490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92215013504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9070417881012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97956204414368</t>
   </si>
   <si>
     <t xml:space="preserve">4.0158224105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21827602386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31496953964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30590486526489</t>
+    <t xml:space="preserve">4.21827554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30590391159058</t>
   </si>
   <si>
     <t xml:space="preserve">4.35727310180664</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">4.34518623352051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13366889953613</t>
+    <t xml:space="preserve">4.13366842269897</t>
   </si>
   <si>
     <t xml:space="preserve">4.10647296905518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00071430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98560547828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610717773438</t>
+    <t xml:space="preserve">4.00071382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98560476303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91610646247864</t>
   </si>
   <si>
     <t xml:space="preserve">3.70156669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52026534080505</t>
+    <t xml:space="preserve">3.52026557922363</t>
   </si>
   <si>
     <t xml:space="preserve">3.38731122016907</t>
@@ -353,85 +353,85 @@
     <t xml:space="preserve">3.48098373413086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46889686584473</t>
+    <t xml:space="preserve">3.46889710426331</t>
   </si>
   <si>
     <t xml:space="preserve">3.60789465904236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80732607841492</t>
+    <t xml:space="preserve">3.80732560157776</t>
   </si>
   <si>
     <t xml:space="preserve">3.85869479179382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83452153205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20903182029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79929113388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96125340461731</t>
+    <t xml:space="preserve">3.83452105522156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20903158187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79929089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96125364303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.06399083137512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11536002159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1455762386322</t>
+    <t xml:space="preserve">3.11535978317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14557671546936</t>
   </si>
   <si>
     <t xml:space="preserve">3.01322674751282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91653251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84763765335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94554042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19694542884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47191858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57767796516418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52630925178528</t>
+    <t xml:space="preserve">2.91653227806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84763836860657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94554090499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19694519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472336769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47191882133484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57767772674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52630949020386</t>
   </si>
   <si>
     <t xml:space="preserve">3.58674263954163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5535044670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59580779075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58976435661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61998105049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5353741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65926313400269</t>
+    <t xml:space="preserve">3.55350422859192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5958080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58976459503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61998128890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53537392616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65926265716553</t>
   </si>
   <si>
     <t xml:space="preserve">3.61393809318542</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">3.78617405891418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71365404129028</t>
+    <t xml:space="preserve">3.71365332603455</t>
   </si>
   <si>
     <t xml:space="preserve">3.4084632396698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42054986953735</t>
+    <t xml:space="preserve">3.42054963111877</t>
   </si>
   <si>
     <t xml:space="preserve">3.71969699859619</t>
@@ -455,34 +455,34 @@
     <t xml:space="preserve">3.96747541427612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9402801990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099787712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84962940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81639122962952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80128216743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69552302360535</t>
+    <t xml:space="preserve">3.94027996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308450698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84962964057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81639075279236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6955235004425</t>
   </si>
   <si>
     <t xml:space="preserve">3.72876214981079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92517185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89495515823364</t>
+    <t xml:space="preserve">3.9251720905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89495491981506</t>
   </si>
   <si>
     <t xml:space="preserve">3.95236659049988</t>
@@ -491,73 +491,73 @@
     <t xml:space="preserve">4.0490608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14273309707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19108009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15482044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0581259727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73178362846375</t>
+    <t xml:space="preserve">4.14273357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07927751541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19107961654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15481996536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05812644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73178339004517</t>
   </si>
   <si>
     <t xml:space="preserve">3.7891960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68645811080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77710962295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49609231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54141736030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47494006156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49911379814148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49004817008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49307107925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68343663215637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78013062477112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6532199382782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74387049674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87380266189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99467062950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10949468612671</t>
+    <t xml:space="preserve">3.68645882606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77106595039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77710938453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49609208106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54141807556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47494029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49911427497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49004888534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49307084083557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68343639373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78013134002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65322017669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74387145042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87380313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99467039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10949516296387</t>
   </si>
   <si>
     <t xml:space="preserve">4.15784168243408</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">4.23640584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06114721298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84358692169189</t>
+    <t xml:space="preserve">4.06114768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84358644485474</t>
   </si>
   <si>
     <t xml:space="preserve">4.00977945327759</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">4.14575529098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13971138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25453567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26964426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20618915557861</t>
+    <t xml:space="preserve">4.13971185684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25453615188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26964330673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20618867874146</t>
   </si>
   <si>
     <t xml:space="preserve">4.11251640319824</t>
@@ -596,37 +596,37 @@
     <t xml:space="preserve">3.94632387161255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99360418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06294870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00305986404419</t>
+    <t xml:space="preserve">3.99360394477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06294822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00305938720703</t>
   </si>
   <si>
     <t xml:space="preserve">3.96208357810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9084997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79502701759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95578002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10392475128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23315715789795</t>
+    <t xml:space="preserve">3.90849924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7950267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95577931404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10392427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23315763473511</t>
   </si>
   <si>
     <t xml:space="preserve">4.23946094512939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05979585647583</t>
+    <t xml:space="preserve">4.05979537963867</t>
   </si>
   <si>
     <t xml:space="preserve">4.46325397491455</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">4.67759132385254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80682373046875</t>
+    <t xml:space="preserve">4.80682420730591</t>
   </si>
   <si>
     <t xml:space="preserve">4.67128705978394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69650316238403</t>
+    <t xml:space="preserve">4.69650363922119</t>
   </si>
   <si>
     <t xml:space="preserve">4.74693584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79106330871582</t>
+    <t xml:space="preserve">4.79106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">4.95181655883789</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.91714477539062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9896411895752</t>
+    <t xml:space="preserve">4.98964071273804</t>
   </si>
   <si>
     <t xml:space="preserve">4.95496892929077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93920850753784</t>
+    <t xml:space="preserve">4.939208984375</t>
   </si>
   <si>
     <t xml:space="preserve">5.00224876403809</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">4.89823246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88877630233765</t>
+    <t xml:space="preserve">4.8887767791748</t>
   </si>
   <si>
     <t xml:space="preserve">4.99279260635376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1377854347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1693058013916</t>
+    <t xml:space="preserve">5.13778495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16930627822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.14408922195435</t>
@@ -698,73 +698,73 @@
     <t xml:space="preserve">5.16300106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92975234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98333644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98018503189087</t>
+    <t xml:space="preserve">4.92975282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98333740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98018455505371</t>
   </si>
   <si>
     <t xml:space="preserve">4.86356019973755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05898523330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04007196426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00540113449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08420085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01170492172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08735322952271</t>
+    <t xml:space="preserve">5.05898475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04007291793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00540018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08420038223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01170444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08735275268555</t>
   </si>
   <si>
     <t xml:space="preserve">5.37103462219238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53809118270874</t>
+    <t xml:space="preserve">5.5380916595459</t>
   </si>
   <si>
     <t xml:space="preserve">5.36157846450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29538536071777</t>
+    <t xml:space="preserve">5.29538631439209</t>
   </si>
   <si>
     <t xml:space="preserve">5.15354537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01485681533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13463354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92344808578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96757650375366</t>
+    <t xml:space="preserve">5.01485633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92344903945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8194317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96757698059082</t>
   </si>
   <si>
     <t xml:space="preserve">4.91084003448486</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05583381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17560958862305</t>
+    <t xml:space="preserve">5.055832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17561006546021</t>
   </si>
   <si>
     <t xml:space="preserve">5.14724159240723</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">5.11887311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02431344985962</t>
+    <t xml:space="preserve">5.07159376144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0243124961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.97388076782227</t>
@@ -785,34 +785,34 @@
     <t xml:space="preserve">4.82888793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69335126876831</t>
+    <t xml:space="preserve">4.69335174560547</t>
   </si>
   <si>
     <t xml:space="preserve">4.72802352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76900005340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94866466522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99594449996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17245721817017</t>
+    <t xml:space="preserve">4.76899909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94866418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99594497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17245817184448</t>
   </si>
   <si>
     <t xml:space="preserve">5.21658515930176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22604131698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30168962478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24810600280762</t>
+    <t xml:space="preserve">5.22604179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30169010162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24810695648193</t>
   </si>
   <si>
     <t xml:space="preserve">5.23549795150757</t>
@@ -821,82 +821,82 @@
     <t xml:space="preserve">5.2512583732605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26071357727051</t>
+    <t xml:space="preserve">5.26071453094482</t>
   </si>
   <si>
     <t xml:space="preserve">5.32375431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33636283874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27962684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33951473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31745100021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35212278366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32690620422363</t>
+    <t xml:space="preserve">5.33636236190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27962636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33951425552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31745052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35212230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32690668106079</t>
   </si>
   <si>
     <t xml:space="preserve">5.19767332077026</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20712947845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20397758483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23864984512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13148212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8509521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38364219665527</t>
+    <t xml:space="preserve">5.20712995529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20397806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23865032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13148164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0810489654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85095262527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38364267349243</t>
   </si>
   <si>
     <t xml:space="preserve">5.46559524536133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38994693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35527467727661</t>
+    <t xml:space="preserve">5.38994598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35527420043945</t>
   </si>
   <si>
     <t xml:space="preserve">5.563307762146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57906770706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59798049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70830059051514</t>
+    <t xml:space="preserve">5.57906723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59797954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70830011367798</t>
   </si>
   <si>
     <t xml:space="preserve">5.78710126876831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75242853164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73666858673096</t>
+    <t xml:space="preserve">5.75242805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7366681098938</t>
   </si>
   <si>
     <t xml:space="preserve">5.72090816497803</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">5.79340410232544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76188516616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78394842147827</t>
+    <t xml:space="preserve">5.76188468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78394889831543</t>
   </si>
   <si>
     <t xml:space="preserve">5.62319612503052</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">5.64210796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68938827514648</t>
+    <t xml:space="preserve">5.68938875198364</t>
   </si>
   <si>
     <t xml:space="preserve">5.73036432266235</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">5.76818799972534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73981952667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71460390090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62949991226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45298624038696</t>
+    <t xml:space="preserve">5.73982000350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62950038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45298719406128</t>
   </si>
   <si>
     <t xml:space="preserve">5.32060241699219</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">5.34266662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27332162857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36473035812378</t>
+    <t xml:space="preserve">5.25441026687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27332210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36473083496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.41516304016113</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">5.37418603897095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3930983543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29223394393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21028184890747</t>
+    <t xml:space="preserve">5.39309930801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29223442077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21028232574463</t>
   </si>
   <si>
     <t xml:space="preserve">5.35842657089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34581899642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4813551902771</t>
+    <t xml:space="preserve">5.34581804275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48135471343994</t>
   </si>
   <si>
     <t xml:space="preserve">5.46874713897705</t>
@@ -989,94 +989,94 @@
     <t xml:space="preserve">5.44668340682983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54754734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59482717514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52548265457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56015491485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5916748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66101932525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7177562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67678022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49081039428711</t>
+    <t xml:space="preserve">5.54754781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5948281288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52548360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56015539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59167671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66101980209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71775531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67677974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49081087112427</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972318649292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56961154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60743570327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58221912384033</t>
+    <t xml:space="preserve">5.56961107254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60743618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58221960067749</t>
   </si>
   <si>
     <t xml:space="preserve">5.55700302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54439544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67993211746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67047595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61058759689331</t>
+    <t xml:space="preserve">5.5443959236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67993259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67047643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61058855056763</t>
   </si>
   <si>
     <t xml:space="preserve">5.48450708389282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53493928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52863645553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47505187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38049125671387</t>
+    <t xml:space="preserve">5.53493976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52863502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47505140304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38049030303955</t>
   </si>
   <si>
     <t xml:space="preserve">5.43407487869263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3300576210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50026750564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56645965576172</t>
+    <t xml:space="preserve">5.33005809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50026702880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56645917892456</t>
   </si>
   <si>
     <t xml:space="preserve">5.5065712928772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51602697372437</t>
+    <t xml:space="preserve">5.51602840423584</t>
   </si>
   <si>
     <t xml:space="preserve">5.58537149429321</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">5.66732454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6547155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69254016876221</t>
+    <t xml:space="preserve">5.65471649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69253969192505</t>
   </si>
   <si>
     <t xml:space="preserve">5.72406005859375</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">5.7114520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7997088432312</t>
+    <t xml:space="preserve">5.79970932006836</t>
   </si>
   <si>
     <t xml:space="preserve">5.74612426757812</t>
@@ -1109,25 +1109,25 @@
     <t xml:space="preserve">5.77449226379395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74927616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77764415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78079652786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77134084701538</t>
+    <t xml:space="preserve">5.74927663803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77764511108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78079700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77134037017822</t>
   </si>
   <si>
     <t xml:space="preserve">5.8186206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91633367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97622156143188</t>
+    <t xml:space="preserve">5.91633415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97622108459473</t>
   </si>
   <si>
     <t xml:space="preserve">5.93209314346313</t>
@@ -1136,34 +1136,34 @@
     <t xml:space="preserve">6.01404571533203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07708597183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05187129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03295803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10860633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10230207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23153495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21577405929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22523069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21892642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20001411437988</t>
+    <t xml:space="preserve">6.07708644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05186986923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03295755386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10860586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10230302810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2315354347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21577453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22523164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21892690658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20001459121704</t>
   </si>
   <si>
     <t xml:space="preserve">6.23178052902222</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">6.20885753631592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20558261871338</t>
+    <t xml:space="preserve">6.20558309555054</t>
   </si>
   <si>
     <t xml:space="preserve">6.16956090927124</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">6.34966993331909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28745174407959</t>
+    <t xml:space="preserve">6.28745126724243</t>
   </si>
   <si>
     <t xml:space="preserve">6.33329629898071</t>
@@ -1199,130 +1199,130 @@
     <t xml:space="preserve">6.29399967193604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19903326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2219557762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382442474365</t>
+    <t xml:space="preserve">6.19903373718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22195625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382394790649</t>
   </si>
   <si>
     <t xml:space="preserve">6.28090143203735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28417587280273</t>
+    <t xml:space="preserve">6.28417634963989</t>
   </si>
   <si>
     <t xml:space="preserve">6.25470352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2481541633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1237154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1564621925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18593549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24160432815552</t>
+    <t xml:space="preserve">6.24815464019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12371397018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15646123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1859335899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24160480499268</t>
   </si>
   <si>
     <t xml:space="preserve">6.26452732086182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26125288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19575881958008</t>
+    <t xml:space="preserve">6.26125335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19575834274292</t>
   </si>
   <si>
     <t xml:space="preserve">6.1466383934021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27107667922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41843938827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39879131317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40206575393677</t>
+    <t xml:space="preserve">6.27107715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4184398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39879083633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40206623077393</t>
   </si>
   <si>
     <t xml:space="preserve">6.39224147796631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41188859939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49375772476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5199556350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57562446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53305387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5297794342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48720836639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43808746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45380640029907</t>
+    <t xml:space="preserve">6.41189002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4937572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51995468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53305435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52977895736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48720788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43808841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45380592346191</t>
   </si>
   <si>
     <t xml:space="preserve">6.36604356765747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41319894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47607374191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51406097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45642566680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26780271530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36997318267822</t>
+    <t xml:space="preserve">6.41319942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51406049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4564266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26780223846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36997365951538</t>
   </si>
   <si>
     <t xml:space="preserve">6.32019758224487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36473321914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41581869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511674880981</t>
+    <t xml:space="preserve">6.36473369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41581916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511531829834</t>
   </si>
   <si>
     <t xml:space="preserve">6.47214412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44594573974609</t>
+    <t xml:space="preserve">6.44594669342041</t>
   </si>
   <si>
     <t xml:space="preserve">6.46690511703491</t>
@@ -1331,43 +1331,43 @@
     <t xml:space="preserve">6.47869443893433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40010070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46166610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47476434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51013088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674741744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2101674079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31102895736694</t>
+    <t xml:space="preserve">6.40010118484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46166515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4747633934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51013040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41974830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674694061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21016788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31102848052979</t>
   </si>
   <si>
     <t xml:space="preserve">6.44463729858398</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46559476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45904588699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39748096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42498874664307</t>
+    <t xml:space="preserve">6.46559524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45904636383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39748048782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42498826980591</t>
   </si>
   <si>
     <t xml:space="preserve">6.45773506164551</t>
@@ -1376,16 +1376,16 @@
     <t xml:space="preserve">6.40665054321289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47738361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37390279769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25732374191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21671676635742</t>
+    <t xml:space="preserve">6.47738456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37390375137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25732326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21671628952026</t>
   </si>
   <si>
     <t xml:space="preserve">6.24684429168701</t>
@@ -1397,79 +1397,79 @@
     <t xml:space="preserve">6.27828121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35294485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34508514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41712856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39355182647705</t>
+    <t xml:space="preserve">6.35294437408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34508466720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41712999343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39355134963989</t>
   </si>
   <si>
     <t xml:space="preserve">6.54811811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63457012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66076803207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79503154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84415245056152</t>
+    <t xml:space="preserve">6.63456964492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66076850891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79503107070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84415197372437</t>
   </si>
   <si>
     <t xml:space="preserve">6.70661354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199905395508</t>
+    <t xml:space="preserve">6.69351434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199857711792</t>
   </si>
   <si>
     <t xml:space="preserve">6.67386627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55925226211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69678974151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72953701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54942750930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46428489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51536989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56907653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52192115783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20754861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0149941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.915442943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95342969894409</t>
+    <t xml:space="preserve">6.55925178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69678926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7295355796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54942798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46428537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51537036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56907558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52191972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20754766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01499366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91544342041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95343017578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.81327247619629</t>
@@ -1478,31 +1478,31 @@
     <t xml:space="preserve">5.58011245727539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24085235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03127002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28407764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42161655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19238662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35874176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23823261260986</t>
+    <t xml:space="preserve">5.24085187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0312705039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38624906539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2840781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4216160774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32861423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19238615036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35874223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23823213577271</t>
   </si>
   <si>
     <t xml:space="preserve">5.12689208984375</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">5.37707996368408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30503702163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40327739715576</t>
+    <t xml:space="preserve">5.3050365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40327787399292</t>
   </si>
   <si>
     <t xml:space="preserve">5.34826326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28276777267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26049995422363</t>
+    <t xml:space="preserve">5.28276824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26050043106079</t>
   </si>
   <si>
     <t xml:space="preserve">5.4425745010376</t>
@@ -1541,52 +1541,52 @@
     <t xml:space="preserve">5.29848718643188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21727418899536</t>
+    <t xml:space="preserve">5.2172737121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.18321657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21465396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1884560585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2513313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32206535339355</t>
+    <t xml:space="preserve">5.21465444564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18845653533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25133085250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3220648765564</t>
   </si>
   <si>
     <t xml:space="preserve">5.39148855209351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30634641647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34040355682373</t>
+    <t xml:space="preserve">5.30634689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34040403366089</t>
   </si>
   <si>
     <t xml:space="preserve">5.26835966110229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17928791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20155477523804</t>
+    <t xml:space="preserve">5.17928743362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2015552520752</t>
   </si>
   <si>
     <t xml:space="preserve">5.27097940444946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2893180847168</t>
+    <t xml:space="preserve">5.28931760787964</t>
   </si>
   <si>
     <t xml:space="preserve">5.3377833366394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32468509674072</t>
+    <t xml:space="preserve">5.32468461990356</t>
   </si>
   <si>
     <t xml:space="preserve">5.35612201690674</t>
@@ -1604,22 +1604,22 @@
     <t xml:space="preserve">5.73205900192261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68097400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81851148605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74646806716919</t>
+    <t xml:space="preserve">5.68097352981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81851196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74646854400635</t>
   </si>
   <si>
     <t xml:space="preserve">5.68752288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78052425384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68490362167358</t>
+    <t xml:space="preserve">5.78052473068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68490314483643</t>
   </si>
   <si>
     <t xml:space="preserve">5.75956583023071</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">5.76742553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70848035812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59583139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44912338256836</t>
+    <t xml:space="preserve">5.70848083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59583044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44912385940552</t>
   </si>
   <si>
     <t xml:space="preserve">5.56439399719238</t>
@@ -1655,55 +1655,55 @@
     <t xml:space="preserve">5.49758958816528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43340444564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43864440917969</t>
+    <t xml:space="preserve">5.43340492248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43864488601685</t>
   </si>
   <si>
     <t xml:space="preserve">5.42816543579102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39541816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41899633407593</t>
+    <t xml:space="preserve">5.39541864395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41899681091309</t>
   </si>
   <si>
     <t xml:space="preserve">5.25002098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55522537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73598909378052</t>
+    <t xml:space="preserve">5.55522489547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73598957061768</t>
   </si>
   <si>
     <t xml:space="preserve">5.68621301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93771076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90627384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9364013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89710521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91282272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01368474960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03333282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09620714187622</t>
+    <t xml:space="preserve">5.93771171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90627288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93640184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89710474014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91282320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01368427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03333234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0962061882019</t>
   </si>
   <si>
     <t xml:space="preserve">6.00844526290894</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">6.00713491439819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07524967193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06476974487305</t>
+    <t xml:space="preserve">5.96390914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07524871826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06477069854736</t>
   </si>
   <si>
     <t xml:space="preserve">6.00451517105103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63512802124023</t>
+    <t xml:space="preserve">5.63512754440308</t>
   </si>
   <si>
     <t xml:space="preserve">5.46353244781494</t>
@@ -1736,55 +1736,55 @@
     <t xml:space="preserve">5.48056125640869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38886833190918</t>
+    <t xml:space="preserve">5.3888692855835</t>
   </si>
   <si>
     <t xml:space="preserve">5.13737106323242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18059730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07187700271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02865028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11379337310791</t>
+    <t xml:space="preserve">5.18059682846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07187604904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02865076065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0351996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11379289627075</t>
   </si>
   <si>
     <t xml:space="preserve">5.05484819412231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00638246536255</t>
+    <t xml:space="preserve">5.00638294219971</t>
   </si>
   <si>
     <t xml:space="preserve">5.15963888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06663751602173</t>
+    <t xml:space="preserve">5.06663703918457</t>
   </si>
   <si>
     <t xml:space="preserve">5.07842683792114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90683126449585</t>
+    <t xml:space="preserve">4.90683174133301</t>
   </si>
   <si>
     <t xml:space="preserve">5.09545469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95791721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09938383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11248302459717</t>
+    <t xml:space="preserve">4.95791673660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09938430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11248350143433</t>
   </si>
   <si>
     <t xml:space="preserve">5.0771164894104</t>
@@ -1796,25 +1796,25 @@
     <t xml:space="preserve">5.13606071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11641263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13868141174316</t>
+    <t xml:space="preserve">5.11641311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13868045806885</t>
   </si>
   <si>
     <t xml:space="preserve">5.15308952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14915990829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104562759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15818977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690242767334</t>
+    <t xml:space="preserve">5.14915943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104658126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15818929672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0369029045105</t>
   </si>
   <si>
     <t xml:space="preserve">5.08987855911255</t>
@@ -1823,16 +1823,16 @@
     <t xml:space="preserve">5.08011960983276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11776065826416</t>
+    <t xml:space="preserve">5.117760181427</t>
   </si>
   <si>
     <t xml:space="preserve">5.34499979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36730480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39100503921509</t>
+    <t xml:space="preserve">5.36730527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39100551605225</t>
   </si>
   <si>
     <t xml:space="preserve">5.44258689880371</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">5.44119310379028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47604513168335</t>
+    <t xml:space="preserve">5.47604560852051</t>
   </si>
   <si>
     <t xml:space="preserve">5.37706470489502</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">5.38821697235107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22650098800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22231864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10242462158203</t>
+    <t xml:space="preserve">5.22650051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22231912612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10242557525635</t>
   </si>
   <si>
     <t xml:space="preserve">5.07733154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24462413787842</t>
+    <t xml:space="preserve">5.24462461471558</t>
   </si>
   <si>
     <t xml:space="preserve">5.26553583145142</t>
@@ -1871,22 +1871,22 @@
     <t xml:space="preserve">5.3129358291626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23068284988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27668809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37288188934326</t>
+    <t xml:space="preserve">5.23068332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27668857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3728814125061</t>
   </si>
   <si>
     <t xml:space="preserve">5.25577688217163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12751865386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04944944381714</t>
+    <t xml:space="preserve">5.12751960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04944896697998</t>
   </si>
   <si>
     <t xml:space="preserve">5.14146041870117</t>
@@ -1895,37 +1895,37 @@
     <t xml:space="preserve">5.09127235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08709049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38961124420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37985277175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36312246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33524131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33802890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40494585037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34639406204224</t>
+    <t xml:space="preserve">5.08709001541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3896107673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37985229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36312294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33524084091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33802938461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40494680404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34639358520508</t>
   </si>
   <si>
     <t xml:space="preserve">5.33942317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46210527420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46907520294189</t>
+    <t xml:space="preserve">5.46210432052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">5.49138069152832</t>
@@ -1934,28 +1934,28 @@
     <t xml:space="preserve">5.50671577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48859214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49277496337891</t>
+    <t xml:space="preserve">5.48859262466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49277544021606</t>
   </si>
   <si>
     <t xml:space="preserve">5.50253343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55969142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48998737335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4481635093689</t>
+    <t xml:space="preserve">5.55969190597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48998641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44816303253174</t>
   </si>
   <si>
     <t xml:space="preserve">5.45931625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29481220245361</t>
+    <t xml:space="preserve">5.29481172561646</t>
   </si>
   <si>
     <t xml:space="preserve">5.14424896240234</t>
@@ -1964,19 +1964,19 @@
     <t xml:space="preserve">5.11218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39797592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40355157852173</t>
+    <t xml:space="preserve">5.28505277633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39797496795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40355205535889</t>
   </si>
   <si>
     <t xml:space="preserve">5.49835109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52623414993286</t>
+    <t xml:space="preserve">5.52623319625854</t>
   </si>
   <si>
     <t xml:space="preserve">5.62521457672119</t>
@@ -1985,46 +1985,46 @@
     <t xml:space="preserve">5.59036207199097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78971910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77717256546021</t>
+    <t xml:space="preserve">5.789719581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80365991592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">5.79808330535889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73953151702881</t>
+    <t xml:space="preserve">5.73953199386597</t>
   </si>
   <si>
     <t xml:space="preserve">5.75486660003662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82735967636108</t>
+    <t xml:space="preserve">5.82736015319824</t>
   </si>
   <si>
     <t xml:space="preserve">5.91797685623169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98071241378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14939737319946</t>
+    <t xml:space="preserve">5.98071146011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14939785003662</t>
   </si>
   <si>
     <t xml:space="preserve">6.02532291412354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07969284057617</t>
+    <t xml:space="preserve">6.07969331741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.08945226669312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20376825332642</t>
+    <t xml:space="preserve">6.20376873016357</t>
   </si>
   <si>
     <t xml:space="preserve">6.10060453414917</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">6.12430477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1033935546875</t>
+    <t xml:space="preserve">6.10339260101318</t>
   </si>
   <si>
     <t xml:space="preserve">6.18982744216919</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">6.21631574630737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26510906219482</t>
+    <t xml:space="preserve">6.26510858535767</t>
   </si>
   <si>
     <t xml:space="preserve">6.39894390106201</t>
@@ -2054,64 +2054,64 @@
     <t xml:space="preserve">6.35990858078003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24001455307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28602027893066</t>
+    <t xml:space="preserve">6.24001550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28601980209351</t>
   </si>
   <si>
     <t xml:space="preserve">6.23583269119263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17728090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22467994689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35293769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42264318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45610094070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5188364982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42543172836304</t>
+    <t xml:space="preserve">6.17728042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35293817520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42264270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45610189437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51883697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4254322052002</t>
   </si>
   <si>
     <t xml:space="preserve">6.44076585769653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47840642929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52162504196167</t>
+    <t xml:space="preserve">6.47840690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52162456512451</t>
   </si>
   <si>
     <t xml:space="preserve">6.4644660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4853777885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.578782081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63175916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6707935333252</t>
+    <t xml:space="preserve">6.48537731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57878255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63175821304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67079401016235</t>
   </si>
   <si>
     <t xml:space="preserve">6.69867563247681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67915868759155</t>
+    <t xml:space="preserve">6.67915821075439</t>
   </si>
   <si>
     <t xml:space="preserve">6.62200021743774</t>
@@ -2120,94 +2120,94 @@
     <t xml:space="preserve">6.54393005371094</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52441310882568</t>
+    <t xml:space="preserve">6.52441263198853</t>
   </si>
   <si>
     <t xml:space="preserve">6.56205320358276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68194723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58714771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62478828430176</t>
+    <t xml:space="preserve">6.68194675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58714818954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6247878074646</t>
   </si>
   <si>
     <t xml:space="preserve">6.41706657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.267897605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34875535964966</t>
+    <t xml:space="preserve">6.26789712905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3487548828125</t>
   </si>
   <si>
     <t xml:space="preserve">6.20237398147583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06435823440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22049808502197</t>
+    <t xml:space="preserve">6.06435775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22049760818481</t>
   </si>
   <si>
     <t xml:space="preserve">6.18146324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16612720489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06575202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99465322494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01556491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95980072021484</t>
+    <t xml:space="preserve">6.16612768173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0657525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99465274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01556444168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95980024337769</t>
   </si>
   <si>
     <t xml:space="preserve">5.91937112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84269618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83433055877686</t>
+    <t xml:space="preserve">5.84269523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8343300819397</t>
   </si>
   <si>
     <t xml:space="preserve">5.76601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7325611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84966564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87894153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96816444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96677112579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93888902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97374105453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94307088851929</t>
+    <t xml:space="preserve">5.73256063461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88172960281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84966611862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87894201278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96816539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9667706489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93888854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97374057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94307136535645</t>
   </si>
   <si>
     <t xml:space="preserve">5.94167709350586</t>
@@ -2216,100 +2216,100 @@
     <t xml:space="preserve">6.07132863998413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16333913803101</t>
+    <t xml:space="preserve">6.16334009170532</t>
   </si>
   <si>
     <t xml:space="preserve">6.14382219314575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19122219085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17030954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29577875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33760213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31947946548462</t>
+    <t xml:space="preserve">6.19122123718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17031002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29577970504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33760166168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31947994232178</t>
   </si>
   <si>
     <t xml:space="preserve">6.2386212348938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30972099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4742259979248</t>
+    <t xml:space="preserve">6.30972051620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47422504425049</t>
   </si>
   <si>
     <t xml:space="preserve">6.60248279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57041788101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51186609268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49095392227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55229377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54114198684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54671907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56763029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53277730941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41288471221924</t>
+    <t xml:space="preserve">6.57041835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51186656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49095487594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55229425430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54114151000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54671859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792385101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56762981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53277826309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41288423538208</t>
   </si>
   <si>
     <t xml:space="preserve">6.44355440139771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51465368270874</t>
+    <t xml:space="preserve">6.5146541595459</t>
   </si>
   <si>
     <t xml:space="preserve">6.48956060409546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50350141525269</t>
+    <t xml:space="preserve">6.50350046157837</t>
   </si>
   <si>
     <t xml:space="preserve">6.33481454849243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31111478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32087373733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15915822982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10478734970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03647518157959</t>
+    <t xml:space="preserve">6.31111431121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32087326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15915775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10478782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03647565841675</t>
   </si>
   <si>
     <t xml:space="preserve">6.0866641998291</t>
@@ -2318,88 +2318,88 @@
     <t xml:space="preserve">5.92494773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91379404067993</t>
+    <t xml:space="preserve">5.91379451751709</t>
   </si>
   <si>
     <t xml:space="preserve">5.94446516036987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80644941329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93052434921265</t>
+    <t xml:space="preserve">5.80644798278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93052387237549</t>
   </si>
   <si>
     <t xml:space="preserve">5.97652959823608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06714725494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11315155029297</t>
+    <t xml:space="preserve">6.06714677810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11315250396729</t>
   </si>
   <si>
     <t xml:space="preserve">6.04344654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13963937759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1926155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28044462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35712051391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296585083008</t>
+    <t xml:space="preserve">6.11872816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13963985443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19261598587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28044509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35712003707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296489715576</t>
   </si>
   <si>
     <t xml:space="preserve">6.59829998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68055200576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63036394119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66382360458374</t>
+    <t xml:space="preserve">6.68055248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63036489486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6638240814209</t>
   </si>
   <si>
     <t xml:space="preserve">6.72655773162842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.662428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63454675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76141166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100879669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90779113769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94682598114014</t>
+    <t xml:space="preserve">6.66242933273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63454723358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76141023635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100927352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803314208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90779256820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94682693481445</t>
   </si>
   <si>
     <t xml:space="preserve">7.04371643066406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95379734039307</t>
+    <t xml:space="preserve">6.95379686355591</t>
   </si>
   <si>
     <t xml:space="preserve">6.98446750640869</t>
@@ -2408,40 +2408,40 @@
     <t xml:space="preserve">6.95658493041992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76420021057129</t>
+    <t xml:space="preserve">6.76419925689697</t>
   </si>
   <si>
     <t xml:space="preserve">6.84645080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8157811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83390426635742</t>
+    <t xml:space="preserve">6.81578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83390378952026</t>
   </si>
   <si>
     <t xml:space="preserve">6.79347467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80462837219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03326082229614</t>
+    <t xml:space="preserve">6.80462789535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03326177597046</t>
   </si>
   <si>
     <t xml:space="preserve">7.19009733200073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27025890350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481641769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4026985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38178730010986</t>
+    <t xml:space="preserve">7.27025938034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40269994735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38178777694702</t>
   </si>
   <si>
     <t xml:space="preserve">7.36087656021118</t>
@@ -2456,22 +2456,22 @@
     <t xml:space="preserve">7.55953598022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58044672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44103717803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4236102104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48285961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6431827545166</t>
+    <t xml:space="preserve">7.55256462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58044767379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44103813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42361068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48286056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64318227767944</t>
   </si>
   <si>
     <t xml:space="preserve">7.59438896179199</t>
@@ -2480,1714 +2480,1714 @@
     <t xml:space="preserve">7.51422786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27374505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42012596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35390615463257</t>
+    <t xml:space="preserve">7.27374458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42012548446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35390520095825</t>
   </si>
   <si>
     <t xml:space="preserve">7.51857471466064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48940467834473</t>
+    <t xml:space="preserve">7.48940563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752595901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52586698532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669599533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47481918334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52951383590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40189409255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33261585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2925066947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3471999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22687387466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3727240562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38366270065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24437570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31438398361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28229761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3581395149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28521490097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21958208084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15686655044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22979068756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16415929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18457746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25021028518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26187705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2181224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1802020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08539962768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15832424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11019420623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05768823623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07810688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93809032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97309541702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77328014373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98622131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93371629714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57200717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71931505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8053674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98038721084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86954116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00372409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04164409637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06060457229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06206369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00518178939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03289365768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99351358413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86370706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45241022109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42178106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38677787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23363447189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97256231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76253843307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63564968109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39937162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28415012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5228123664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21215200424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33174896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5222806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77606010437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33850955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25537514686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06649899482727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04243350028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10150289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17661571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6185417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9044075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01087856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76439189910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62802219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66667199134827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64917063713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77460169792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70605182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97149920463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05171680450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05900955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04150676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87232112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57989144325256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64771151542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69292521476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56238985061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51571750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73959732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82419013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9554557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02254629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85627746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.799396276474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76585054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75855779647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74834799766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78918623924255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607618331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85336065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68271589279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56311893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80960559844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74980688095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69730114936829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168416976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78481125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921083450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256284713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31862211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25590658187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60011339187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69929122924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95452928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95307064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18351364135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34540748596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17330408096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07995986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86410188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96473836898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16455316543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1397590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23164463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12079811096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97348928451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.996826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71095895767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75033855438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55927467346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76200675964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65991163253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71533536911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91952419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90348148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92535924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93119335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88014554977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79701089859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9297342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05078983306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13830041885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14559268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16601181030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13246631622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25206327438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25498056411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.316237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22435140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16309452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12663269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07850217819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05954122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92244148254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94286108016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73283624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81305456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94723701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9136905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97786521911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27248191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28706693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29435968399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20247459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1149640083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24622869491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12809085845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09746265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24768829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27685832977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44458532333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47813129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42416620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31040334701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33519792556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32061338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2272686958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21414232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08141851425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17767953872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39207983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18643093109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08725261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8991060256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89327192306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87722873687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76054811477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95161151885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8757700920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88452100753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84368324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92390060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08871173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20976734161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08579397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28560876846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23310327529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.203932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0114107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02016162872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180547714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84222412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79992771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84951686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74012899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74596309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78971862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76638221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64095115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41050815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46884775161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43967723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85680961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30894470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19664001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20539093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51605176925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59626960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51459360122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58460235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49854946136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72899293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75232887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70419883728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63710737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45041942596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52917861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46500396728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60210371017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53209590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4897985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49709129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4752140045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34978342056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36145114898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53792905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49271631240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42854166030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39062166213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3789529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52042722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52480316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40228891372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42270803451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62835645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61231327056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50438451766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46208763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51021862030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46937990188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44750213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38187074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40083074569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40520620346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44896078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35707569122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39499616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37020206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51167678833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73045110702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89963865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97985553741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17383575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23071718215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41740608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50637435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48012113571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59242630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53700256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57929944992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54429578781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62159585952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61430311203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58221673965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53408622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3955283164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50199937820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43490791320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52679300308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61138725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7251501083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77473878860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85058069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86516523361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90162801742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01976633071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09415054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09706735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87975025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84037113189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77911424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90016984939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90600442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92058897018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93954849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03581047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89579486846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84912300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86079072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77182245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80682516098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81849336624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80974292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78640699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8520393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84766340255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7091064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64201402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64639091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8359956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80828475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82724523544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85641431808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92788124084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78057289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9089207649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94684171676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04018592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01393270492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08394050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13352918624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19770431518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05914640426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06643915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11748695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1481146812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21228933334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27062940597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30344533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29979991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25604438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26771211624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20791387557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26333570480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2545862197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23270893096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23562526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17582750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22249841690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28083896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27500438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20062112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18311929702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19332838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18749475479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36178493499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14082193374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.149573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92350578308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165237426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1889533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20499706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14519882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09560871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86808347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95559310913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23416709899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3107385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28667211532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28813123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13207197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2108302116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2837553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29615211486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19041156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27792167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27354621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17728471755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1714506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04601955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09852695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13644742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25166940689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27938079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24875116348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3654317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47846603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33626222610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53680515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6133770942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68630170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5878529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50398921966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294141769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21520614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38001680374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41283321380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43106460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53315925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5805606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6060848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55868196487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52222061157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64254713058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67171716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77016544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76652002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88684558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87590789794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81392097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81756782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955331802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79204416275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74828863143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90313148498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72266721725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72111129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45352554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5639820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59976530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63865756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776660919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79034280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86034965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82534646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80978965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71488904953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311635971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76156044006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84868192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80589914321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52197742462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64954805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68999624252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81367826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86423826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92646789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0859317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10148811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08204174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07815265655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07037258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13260269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23761558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17538642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09759998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03537082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02370166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61532163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66043758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77867412567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02759075164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10926723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79812002182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05870532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22983741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20650005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14427089691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90702199935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88368606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93813753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77556276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6728835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67755031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26994800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29172897338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25439214706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68654775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73477554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68499183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12337207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95379638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08603429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63520812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31939458847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35050868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61187267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66165637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970830917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06925868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22638845443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06770324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12993240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02103090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0505895614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22949934005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10659599304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17193746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30417490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11904287338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97902679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89190435409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03503274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02569770812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94946765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1128191947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.374183177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44885778427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17971515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38196086883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38040542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686147689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74755907058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50486373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48308420181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60598707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54842519760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71955585479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71022129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52353382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44574642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38974046707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43485593795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26217031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34151268005371</t>
   </si>
   <si>
     <t xml:space="preserve">7.46752691268921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52586603164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669694900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47481918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52951240539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40189361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33261585235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925066947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32532405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3471999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22687339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37272453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38366365432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24437570571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31438398361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28229665756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35813903808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2852144241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21958065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15686655044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22979068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16415882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18457794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25021076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26187801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21812343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1802020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08539867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15832376480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11019372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05768823623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07810735702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99643039703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93809127807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97309494018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77328109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98622131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93371534347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75286149978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5720067024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71931552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8053674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98038721084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86954164505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00372266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04164409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06060457229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06206321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00518226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03289318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99351358413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86370801925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45240926742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42178201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38677787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23363542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97256231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76253843307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71003293991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63564968109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39937210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28415012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5228123664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21215200424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33174896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52228045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77606010437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33850979804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25537490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06649899482727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04243397712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10150289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17661595344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61854147911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90440821647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0108790397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76439166069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62802171707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66667175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64917039871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77460145950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70605182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97149968147278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05171728134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05900955200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04150724411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87232065200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57989144325256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64771175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69292521476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56238961219788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51571702957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73959732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82419085502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02254676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85627746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.799396276474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76585054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75855803489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74834847450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78918647766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607594490051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85336089134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68271589279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56311893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80960583686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74980664253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69730091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168440818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31862211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25590705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60011291503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69929170608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95452928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95307016372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18351316452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34540700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17330408096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07996034622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86410236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96473836898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03766345977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16455316543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13975858688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23164415359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12079811096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97348976135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99682569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71095943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75033903121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55927467346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76200675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.659912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71533489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91952466964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90348100662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92535877227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93119335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88014554977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79701089859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92973470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05079030990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14559268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16601085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13246631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25206327438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25498056411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.316237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22435188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16309499740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12663221359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07850170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05954122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92244243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94286108016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73283672332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81305408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94723653793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9136905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97786521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27248191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28706741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29436016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20247411727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1149640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24622917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12809038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09746217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24768781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27685832977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44458532333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47813129425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42416667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31040287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33519792556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32061290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22726917266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21414232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08141899108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17768001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39207935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28269195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29873514175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18643093109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08725261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89910554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89327192306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87722873687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76054811477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95161199569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87576961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.884521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84368324279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92390060424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08871078491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20976686477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08579397201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28560876846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23310232162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20393228530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0114107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02016162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84222459793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79992771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84951686859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74012899398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74596309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78971862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76638269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64095115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4105076789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46884775161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43967819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85680961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30894470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19664001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20539093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51605224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59626960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51459407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58460140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4985499382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72899293899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75232887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70419883728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63710784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45041942596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52917861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46500492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54230546951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60210371017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53209590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4897985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49709129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47521448135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34978294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36145067214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53792953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49271631240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42854166030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39062118530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3789529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52042722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52480268478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40228843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42270755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62835693359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61231374740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50438451766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46208763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51021766662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46937942504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44750261306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38187026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47083854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40083074569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40520572662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44896125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35707569122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39499616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37020206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51167631149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7304515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89963817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97985553741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17383575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23071718215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41740560531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50637435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48012113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59242630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53700351715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57929992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54429483413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62159585952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58221626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53408575057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3955283164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28468179702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50199937820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43490743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52679347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61138677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72514963150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73536014556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77473878860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85058069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86516523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90162897109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01976776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09415006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09706830978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87975025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84037160873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77911329269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90016984939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92058897018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93954944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03581094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89579391479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84912300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86079072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77182197570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80682563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81849384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80974340438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78640699386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85203838348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84766435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7091064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64201498031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805864334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64639043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83599519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80828475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82724523544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85641527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92788124084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78057336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9089207649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94684219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04018592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05477046966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01393222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08394002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1335301399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19770479202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06643915176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0533127784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11748695373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14811372756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21228933334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27062940597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344533920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2997989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25604343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2677116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20791482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26333665847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25458574295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23270845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23562479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17582654953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22249889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28083848953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27500486373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20062065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18311882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19332885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18749523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36178588867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1408224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92350625991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165285110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18895244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20499658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14519834518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09560871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86808347702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9555926322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23416662216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31073808670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28667259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28813171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24145841598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13207197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21083068847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28375577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29615306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19041156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27792119979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27354669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17728567123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17145156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04602003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09852600097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13644742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25166893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27937936782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24875259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3654317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47846555709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33626270294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53680562973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61337661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68630218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58785343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734903335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50398921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294141769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21520662307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38001775741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41283273696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43106365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53315925598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58056116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60608434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55868434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52222013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64254665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67171764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77016639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76651906967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88684558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87590742111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81392192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81756687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89778518676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507745742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.879554271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79204320907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74828863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088768005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90313148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72111177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352458953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56398248672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59976434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6386570930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79034280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591569900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86034917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82534599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80978918075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71488904953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311540603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76155996322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84868192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80589866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52197790145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6495475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68999671936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81367826461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86423873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92646741867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08593082427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10148906707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08204174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07815265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07037448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13260269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23761558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17538738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09759998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03536987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02370262145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61532211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66043758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77867317199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02758979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10926723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79812049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05870532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22983646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20650100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14427185058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90702104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07426357269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88368606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93813705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77556324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6728835105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67755079269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26994800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29172849655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25439167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68654775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73477554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68499231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12337207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95379686355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08603429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63520812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3193941116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35050916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61187267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66165590286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06925916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2263879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06770324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12993192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02103090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05059003829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22949934005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10659551620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17193698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30417490005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11904287338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97902631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89190483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03503227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02569770812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94946670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11281871795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19527339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18438291549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37418174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4488582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17971611022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38196134567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38040542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686147689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757562637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74755954742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50486421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4830846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60598707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54842519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71955537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71022176742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52353382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44574642181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38973999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43485593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26217031478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34151220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752786636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41152048110962</t>
+    <t xml:space="preserve">7.41152095794678</t>
   </si>
   <si>
     <t xml:space="preserve">7.46908235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43174505233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32906627655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42085456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53442287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49864101409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6853289604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50797605514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01325273513794</t>
+    <t xml:space="preserve">7.43174457550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32906675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42085552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442335128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49864149093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68532943725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50797700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01325225830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.90435075759888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96813631057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9510235786438</t>
+    <t xml:space="preserve">6.96813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95102262496948</t>
   </si>
   <si>
     <t xml:space="preserve">6.63054180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59631443023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68188095092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74410963058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71921825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5683126449585</t>
+    <t xml:space="preserve">6.59631490707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68188047409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74411010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7192177772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56831216812134</t>
   </si>
   <si>
     <t xml:space="preserve">6.71144008636475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56675672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64765453338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60253810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42362928390503</t>
+    <t xml:space="preserve">6.56675624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64765405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60253858566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42362880706787</t>
   </si>
   <si>
     <t xml:space="preserve">6.41896152496338</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">6.2322735786438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32406234741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45785427093506</t>
+    <t xml:space="preserve">6.32406187057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45785474777222</t>
   </si>
   <si>
     <t xml:space="preserve">6.55586671829224</t>
@@ -4211,16 +4211,16 @@
     <t xml:space="preserve">6.4905252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41273880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3582878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05958700180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0549201965332</t>
+    <t xml:space="preserve">6.41273927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35828733444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05958652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05491971969604</t>
   </si>
   <si>
     <t xml:space="preserve">6.20115852355957</t>
@@ -4232,16 +4232,16 @@
     <t xml:space="preserve">6.26027679443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22138404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24783039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17937850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24005222320557</t>
+    <t xml:space="preserve">6.2213830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24783086776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17937803268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24005270004272</t>
   </si>
   <si>
     <t xml:space="preserve">6.35673236846924</t>
@@ -4253,34 +4253,34 @@
     <t xml:space="preserve">6.54653215408325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55119943618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59787130355835</t>
+    <t xml:space="preserve">6.55119895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59787082672119</t>
   </si>
   <si>
     <t xml:space="preserve">6.64921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70210456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65232181549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6429877281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66010046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72544145584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77055835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77833604812622</t>
+    <t xml:space="preserve">6.70210552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65232229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64298820495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66010093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72544097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77055788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77833652496338</t>
   </si>
   <si>
     <t xml:space="preserve">6.72233009338379</t>
@@ -4289,28 +4289,28 @@
     <t xml:space="preserve">6.69588184356689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44696521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27427864074707</t>
+    <t xml:space="preserve">6.44696474075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27427816390991</t>
   </si>
   <si>
     <t xml:space="preserve">6.32250642776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29450273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25872087478638</t>
+    <t xml:space="preserve">6.2945032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25872039794922</t>
   </si>
   <si>
     <t xml:space="preserve">6.17004442214966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15448665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21360445022583</t>
+    <t xml:space="preserve">6.15448713302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21360492706299</t>
   </si>
   <si>
     <t xml:space="preserve">6.15137481689453</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">6.07825565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31006002426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21204900741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19493579864502</t>
+    <t xml:space="preserve">6.31006050109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21204853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19493627548218</t>
   </si>
   <si>
     <t xml:space="preserve">6.22916221618652</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">6.58698129653931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6538782119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63365316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57764720916748</t>
+    <t xml:space="preserve">6.65387725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63365268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57764673233032</t>
   </si>
   <si>
     <t xml:space="preserve">6.61031723022461</t>
@@ -4358,37 +4358,37 @@
     <t xml:space="preserve">6.37540102005005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48274660110474</t>
+    <t xml:space="preserve">6.48274612426758</t>
   </si>
   <si>
     <t xml:space="preserve">6.44074201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2089376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09381341934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03313970565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92112684249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26961135864258</t>
+    <t xml:space="preserve">6.20893716812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09381294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0331392288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92112636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26961183547974</t>
   </si>
   <si>
     <t xml:space="preserve">6.59009265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2338285446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649171829224</t>
+    <t xml:space="preserve">6.48119115829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23382902145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649124145508</t>
   </si>
   <si>
     <t xml:space="preserve">6.18249034881592</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">6.45629930496216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52164077758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6787691116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8561224937439</t>
+    <t xml:space="preserve">6.52164030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67876958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85612344741821</t>
   </si>
   <si>
     <t xml:space="preserve">6.84990072250366</t>
@@ -4418,73 +4418,73 @@
     <t xml:space="preserve">6.85767889022827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07081365585327</t>
+    <t xml:space="preserve">7.07081460952759</t>
   </si>
   <si>
     <t xml:space="preserve">7.10348510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1346001625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09726190567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19060564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15326833724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31039714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49241828918457</t>
+    <t xml:space="preserve">7.13459968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09726238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19060611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15326881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31039810180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49241876602173</t>
   </si>
   <si>
     <t xml:space="preserve">7.52820014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57954025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63399076461792</t>
+    <t xml:space="preserve">7.57953929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6339898109436</t>
   </si>
   <si>
     <t xml:space="preserve">7.74289226531982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91480207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90892267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91228103637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93243646621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87029266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83502340316772</t>
+    <t xml:space="preserve">7.91480112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90892314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91228151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93243551254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87029218673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83502197265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.7728796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73760938644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69562149047852</t>
+    <t xml:space="preserve">7.73761034011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6956205368042</t>
   </si>
   <si>
     <t xml:space="preserve">7.7140965461731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73928928375244</t>
+    <t xml:space="preserve">7.73928833007812</t>
   </si>
   <si>
     <t xml:space="preserve">7.68554496765137</t>
@@ -4493,94 +4493,94 @@
     <t xml:space="preserve">7.6351580619812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65867137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7107367515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69394111633301</t>
+    <t xml:space="preserve">7.65867185592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71073818206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69394254684448</t>
   </si>
   <si>
     <t xml:space="preserve">7.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79471349716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087284088135</t>
+    <t xml:space="preserve">7.79471397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087379455566</t>
   </si>
   <si>
     <t xml:space="preserve">7.48064184188843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50415563583374</t>
+    <t xml:space="preserve">7.50415468215942</t>
   </si>
   <si>
     <t xml:space="preserve">7.52934789657593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6637110710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56965637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58477163314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5864520072937</t>
+    <t xml:space="preserve">7.66371059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56965589523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58477210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58645248413086</t>
   </si>
   <si>
     <t xml:space="preserve">7.53774499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6469144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54446315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59484910964966</t>
+    <t xml:space="preserve">7.64691495895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54446363449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59484958648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.6721076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79807376861572</t>
+    <t xml:space="preserve">7.79807329177856</t>
   </si>
   <si>
     <t xml:space="preserve">7.78463745117188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77959871292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85685729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90052509307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02145195007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12558269500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11550331115723</t>
+    <t xml:space="preserve">7.77959823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85685682296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9005241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02145099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12558174133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11550426483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.09535026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11046600341797</t>
+    <t xml:space="preserve">8.11046695709229</t>
   </si>
   <si>
     <t xml:space="preserve">8.01977157592773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92403793334961</t>
+    <t xml:space="preserve">7.92403841018677</t>
   </si>
   <si>
     <t xml:space="preserve">8.04496479034424</t>
@@ -4592,16 +4592,16 @@
     <t xml:space="preserve">8.13230037689209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18100643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28513813018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31536960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34560012817383</t>
+    <t xml:space="preserve">8.18100547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28513717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31536865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34560108184814</t>
   </si>
   <si>
     <t xml:space="preserve">8.27674007415771</t>
@@ -4613,19 +4613,19 @@
     <t xml:space="preserve">8.39430809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4312572479248</t>
+    <t xml:space="preserve">8.43125820159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54042625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5698184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69998264312744</t>
+    <t xml:space="preserve">8.54042720794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56981945037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69998168945312</t>
   </si>
   <si>
     <t xml:space="preserve">8.56561946868896</t>
@@ -4634,7 +4634,7 @@
     <t xml:space="preserve">8.70838069915771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74197196960449</t>
+    <t xml:space="preserve">8.74197101593018</t>
   </si>
   <si>
     <t xml:space="preserve">8.60340881347656</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">8.61180686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50263690948486</t>
+    <t xml:space="preserve">8.50263786315918</t>
   </si>
   <si>
     <t xml:space="preserve">8.49423980712891</t>
@@ -4658,10 +4658,10 @@
     <t xml:space="preserve">8.41026401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25490665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42285919189453</t>
+    <t xml:space="preserve">8.25490570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42285823822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164367675781</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">8.36407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45645046234131</t>
+    <t xml:space="preserve">8.45644950866699</t>
   </si>
   <si>
     <t xml:space="preserve">8.51103496551514</t>
@@ -4688,10 +4688,10 @@
     <t xml:space="preserve">8.40186500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16757106781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80143213272095</t>
+    <t xml:space="preserve">8.16757011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80143260955811</t>
   </si>
   <si>
     <t xml:space="preserve">7.99793767929077</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">7.52095031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43193531036377</t>
+    <t xml:space="preserve">7.43193578720093</t>
   </si>
   <si>
     <t xml:space="preserve">7.73425149917603</t>
@@ -4712,34 +4712,34 @@
     <t xml:space="preserve">7.63179922103882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55286169052124</t>
+    <t xml:space="preserve">7.5528621673584</t>
   </si>
   <si>
     <t xml:space="preserve">7.51591157913208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60660600662231</t>
+    <t xml:space="preserve">7.60660696029663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72417402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78295660018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81150913238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80982971191406</t>
+    <t xml:space="preserve">7.78295707702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81150960922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80983018875122</t>
   </si>
   <si>
     <t xml:space="preserve">7.74096965789795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93075704574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92739725112915</t>
+    <t xml:space="preserve">7.93075609207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92739677429199</t>
   </si>
   <si>
     <t xml:space="preserve">7.93915414810181</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">8.21291828155518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17260837554932</t>
+    <t xml:space="preserve">8.17261028289795</t>
   </si>
   <si>
     <t xml:space="preserve">8.19780158996582</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">8.17092990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89212703704834</t>
+    <t xml:space="preserve">7.8921275138855</t>
   </si>
   <si>
     <t xml:space="preserve">8.19444274902344</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">8.09702968597412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38086986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766597747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34056186676025</t>
+    <t xml:space="preserve">8.3808708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34056282043457</t>
   </si>
   <si>
     <t xml:space="preserve">8.36575603485107</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">8.13565921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14741611480713</t>
+    <t xml:space="preserve">8.14741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.18436622619629</t>
@@ -4811,7 +4811,7 @@
     <t xml:space="preserve">8.27338123321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34896087646484</t>
+    <t xml:space="preserve">8.34895992279053</t>
   </si>
   <si>
     <t xml:space="preserve">8.42705821990967</t>
@@ -4820,13 +4820,13 @@
     <t xml:space="preserve">8.54462623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7335729598999</t>
+    <t xml:space="preserve">8.73357200622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.77136325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67898845672607</t>
+    <t xml:space="preserve">8.67898750305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.67479038238525</t>
@@ -4835,22 +4835,22 @@
     <t xml:space="preserve">8.6453971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92252159118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98970317840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90572547912598</t>
+    <t xml:space="preserve">8.92252063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98970127105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90572452545166</t>
   </si>
   <si>
     <t xml:space="preserve">8.98130416870117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96450901031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17025279998779</t>
+    <t xml:space="preserve">8.96450996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17025089263916</t>
   </si>
   <si>
     <t xml:space="preserve">9.19124507904053</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">9.39698886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42638111114502</t>
+    <t xml:space="preserve">9.4263801574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.40538597106934</t>
@@ -4880,37 +4880,37 @@
     <t xml:space="preserve">9.33400630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14925861358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03588962554932</t>
+    <t xml:space="preserve">9.14925670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.035888671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.01909351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04848480224609</t>
+    <t xml:space="preserve">9.04848575592041</t>
   </si>
   <si>
     <t xml:space="preserve">9.06947994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20384311676025</t>
+    <t xml:space="preserve">9.20384216308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.34660243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35500049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27942180633545</t>
+    <t xml:space="preserve">9.35500144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27942085266113</t>
   </si>
   <si>
     <t xml:space="preserve">9.24583053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25003051757812</t>
+    <t xml:space="preserve">9.25002956390381</t>
   </si>
   <si>
     <t xml:space="preserve">9.25842666625977</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">9.43057918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4893627166748</t>
+    <t xml:space="preserve">9.48936367034912</t>
   </si>
   <si>
     <t xml:space="preserve">9.48096561431885</t>
@@ -4928,46 +4928,46 @@
     <t xml:space="preserve">9.52295398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64891910552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60693073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67411231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63632202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69930458068848</t>
+    <t xml:space="preserve">9.64891815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60692977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67411136627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63632297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69930553436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.70770263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68250942230225</t>
+    <t xml:space="preserve">9.68250846862793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0394096374512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1779727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0520067214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95543384552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94703578948975</t>
+    <t xml:space="preserve">10.1779718399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0520076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9554328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94703674316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.93863868713379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98062705993652</t>
+    <t xml:space="preserve">9.98062801361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.73289585113525</t>
@@ -4979,16 +4979,16 @@
     <t xml:space="preserve">9.85886096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83786582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93024063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87565612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7916784286499</t>
+    <t xml:space="preserve">9.83786678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9302396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87565517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79167938232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.76648712158203</t>
@@ -4997,19 +4997,19 @@
     <t xml:space="preserve">9.82526969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97222805023193</t>
+    <t xml:space="preserve">9.97222900390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.92604160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9134464263916</t>
+    <t xml:space="preserve">9.91344547271729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1653738021851</t>
+    <t xml:space="preserve">10.1653747558594</t>
   </si>
   <si>
     <t xml:space="preserve">10.194766998291</t>
@@ -5021,28 +5021,28 @@
     <t xml:space="preserve">10.1401824951172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1443815231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2199592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0981931686401</t>
+    <t xml:space="preserve">10.144380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2199602127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0981941223145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1989660263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1317834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2157602310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2241592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2115631103516</t>
+    <t xml:space="preserve">10.1317844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2157611846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.224160194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2115621566772</t>
   </si>
   <si>
     <t xml:space="preserve">10.303936958313</t>
@@ -5051,13 +5051,13 @@
     <t xml:space="preserve">10.25355052948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1905679702759</t>
+    <t xml:space="preserve">10.1905689239502</t>
   </si>
   <si>
     <t xml:space="preserve">10.3291301727295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4173049926758</t>
+    <t xml:space="preserve">10.4173059463501</t>
   </si>
   <si>
     <t xml:space="preserve">10.3333292007446</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">10.2913408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3963108062744</t>
+    <t xml:space="preserve">10.3963117599487</t>
   </si>
   <si>
     <t xml:space="preserve">10.434100151062</t>
@@ -5108,7 +5108,7 @@
     <t xml:space="preserve">10.1695737838745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1527786254883</t>
+    <t xml:space="preserve">10.152777671814</t>
   </si>
   <si>
     <t xml:space="preserve">9.94283676147461</t>
@@ -5120,28 +5120,28 @@
     <t xml:space="preserve">9.26682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37179470062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24163150787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96870803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46417045593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53135204315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58173847198486</t>
+    <t xml:space="preserve">9.37179660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24163341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96870708465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46417140960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53135299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58173751831055</t>
   </si>
   <si>
     <t xml:space="preserve">9.65311717987061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731620788574</t>
+    <t xml:space="preserve">9.65731716156006</t>
   </si>
   <si>
     <t xml:space="preserve">9.66991329193115</t>
@@ -5150,28 +5150,28 @@
     <t xml:space="preserve">9.63212394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67831039428711</t>
+    <t xml:space="preserve">9.67831134796143</t>
   </si>
   <si>
     <t xml:space="preserve">9.69090747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9890251159668</t>
+    <t xml:space="preserve">9.98902416229248</t>
   </si>
   <si>
     <t xml:space="preserve">9.87985515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84817409515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73050212860107</t>
+    <t xml:space="preserve">9.84817504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73050308227539</t>
   </si>
   <si>
     <t xml:space="preserve">9.82554531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81649303436279</t>
+    <t xml:space="preserve">9.81649398803711</t>
   </si>
   <si>
     <t xml:space="preserve">9.81196784973145</t>
@@ -5180,28 +5180,28 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73955535888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71239948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75313091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78028774261475</t>
+    <t xml:space="preserve">9.7395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71239852905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75313186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78028678894043</t>
   </si>
   <si>
     <t xml:space="preserve">9.72597694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65808963775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9251127243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0020523071289</t>
+    <t xml:space="preserve">9.65809059143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0020513534546</t>
   </si>
   <si>
     <t xml:space="preserve">10.0744647979736</t>
@@ -5210,13 +5210,13 @@
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.092568397522</t>
+    <t xml:space="preserve">10.0925674438477</t>
   </si>
   <si>
     <t xml:space="preserve">10.0337324142456</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0699396133423</t>
+    <t xml:space="preserve">10.069938659668</t>
   </si>
   <si>
     <t xml:space="preserve">10.0654134750366</t>
@@ -5225,16 +5225,16 @@
     <t xml:space="preserve">10.1378259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0789909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1785583496094</t>
+    <t xml:space="preserve">10.0789918899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1785593032837</t>
   </si>
   <si>
     <t xml:space="preserve">10.1514043807983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.115198135376</t>
+    <t xml:space="preserve">10.1151971817017</t>
   </si>
   <si>
     <t xml:space="preserve">10.142352104187</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">10.060887336731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695070266724</t>
+    <t xml:space="preserve">10.1695079803467</t>
   </si>
   <si>
     <t xml:space="preserve">10.2464456558228</t>
@@ -5252,19 +5252,19 @@
     <t xml:space="preserve">10.2736015319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2147655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102394104004</t>
+    <t xml:space="preserve">10.2147645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102384567261</t>
   </si>
   <si>
     <t xml:space="preserve">10.2011880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4455823898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7126054763794</t>
+    <t xml:space="preserve">10.4455814361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7126045227051</t>
   </si>
   <si>
     <t xml:space="preserve">10.7895441055298</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">10.9434213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9253177642822</t>
+    <t xml:space="preserve">10.9253187179565</t>
   </si>
   <si>
     <t xml:space="preserve">10.9615240097046</t>
@@ -5294,13 +5294,13 @@
     <t xml:space="preserve">11.1063508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.133505821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9388952255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0022573471069</t>
+    <t xml:space="preserve">11.1335067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9388961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0022563934326</t>
   </si>
   <si>
     <t xml:space="preserve">10.8393278121948</t>
@@ -5321,7 +5321,7 @@
     <t xml:space="preserve">10.4184274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3957967758179</t>
+    <t xml:space="preserve">10.3957977294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5587272644043</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">10.5858812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.66282081604</t>
+    <t xml:space="preserve">10.6628217697144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7261819839478</t>
@@ -5339,19 +5339,19 @@
     <t xml:space="preserve">11.1787643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7173357009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5906143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4955711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4231576919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4005289077759</t>
+    <t xml:space="preserve">11.7173347473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5906133651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4955701828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4231586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141063690186</t>
@@ -5363,28 +5363,28 @@
     <t xml:space="preserve">11.4865188598633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6313457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.581561088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5951404571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6901807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8576374053955</t>
+    <t xml:space="preserve">11.6313467025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5815620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.595139503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625932693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6901817321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8576364517212</t>
   </si>
   <si>
     <t xml:space="preserve">12.0160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9979372024536</t>
+    <t xml:space="preserve">11.9979362487793</t>
   </si>
   <si>
     <t xml:space="preserve">12.0567722320557</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">12.2785358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3328466415405</t>
+    <t xml:space="preserve">12.3328475952148</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3781061172485</t>
+    <t xml:space="preserve">12.5003023147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3781051635742</t>
   </si>
   <si>
     <t xml:space="preserve">12.509352684021</t>
@@ -5417,19 +5417,19 @@
     <t xml:space="preserve">12.4052600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3102178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554763793945</t>
+    <t xml:space="preserve">12.3102188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554754257202</t>
   </si>
   <si>
     <t xml:space="preserve">12.2875890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.124659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1699171066284</t>
+    <t xml:space="preserve">12.1246604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1699180603027</t>
   </si>
   <si>
     <t xml:space="preserve">12.2921142578125</t>
@@ -5444,10 +5444,10 @@
     <t xml:space="preserve">12.3509502410889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1337099075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744432449341</t>
+    <t xml:space="preserve">12.1337108612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744441986084</t>
   </si>
   <si>
     <t xml:space="preserve">12.083927154541</t>
@@ -5465,13 +5465,13 @@
     <t xml:space="preserve">12.6722831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7718496322632</t>
+    <t xml:space="preserve">12.7718505859375</t>
   </si>
   <si>
     <t xml:space="preserve">13.0796060562134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2244319915771</t>
+    <t xml:space="preserve">13.2244310379028</t>
   </si>
   <si>
     <t xml:space="preserve">13.514084815979</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">13.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7403755187988</t>
+    <t xml:space="preserve">13.7403745651245</t>
   </si>
   <si>
     <t xml:space="preserve">13.7992105484009</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">13.7336559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6259603500366</t>
+    <t xml:space="preserve">13.6259593963623</t>
   </si>
   <si>
     <t xml:space="preserve">13.5369930267334</t>
@@ -5513,19 +5513,19 @@
     <t xml:space="preserve">13.5791349411011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5978660583496</t>
+    <t xml:space="preserve">13.5978651046753</t>
   </si>
   <si>
     <t xml:space="preserve">13.5042161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4199323654175</t>
+    <t xml:space="preserve">13.4199314117432</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620733261108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4339790344238</t>
+    <t xml:space="preserve">13.4339799880981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2794580459595</t>
@@ -5534,16 +5534,16 @@
     <t xml:space="preserve">13.1343011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4246139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9563684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.666054725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7550230026245</t>
+    <t xml:space="preserve">13.424614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9563674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7550220489502</t>
   </si>
   <si>
     <t xml:space="preserve">12.8205757141113</t>
@@ -5552,16 +5552,16 @@
     <t xml:space="preserve">12.7222452163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9329566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0500183105469</t>
+    <t xml:space="preserve">12.9329557418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0500173568726</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001779556274</t>
+    <t xml:space="preserve">12.9001789093018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7831172943115</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">13.1951732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0359697341919</t>
+    <t xml:space="preserve">13.0359706878662</t>
   </si>
   <si>
     <t xml:space="preserve">13.1670789718628</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">13.2045392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2888221740723</t>
+    <t xml:space="preserve">13.2888231277466</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654104232788</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">13.4386615753174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4714393615723</t>
+    <t xml:space="preserve">13.4714384078979</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777894973755</t>
@@ -5600,10 +5600,10 @@
     <t xml:space="preserve">13.382472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4995336532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4808044433594</t>
+    <t xml:space="preserve">13.499532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4808034896851</t>
   </si>
   <si>
     <t xml:space="preserve">13.5182638168335</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">13.8038930892944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8413534164429</t>
+    <t xml:space="preserve">13.8413524627686</t>
   </si>
   <si>
     <t xml:space="preserve">13.808575630188</t>
@@ -5630,13 +5630,13 @@
     <t xml:space="preserve">13.4573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1623964309692</t>
+    <t xml:space="preserve">13.1623973846436</t>
   </si>
   <si>
     <t xml:space="preserve">12.8486709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1483497619629</t>
+    <t xml:space="preserve">13.1483488082886</t>
   </si>
   <si>
     <t xml:space="preserve">13.0172395706177</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">13.1389837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1015243530273</t>
+    <t xml:space="preserve">13.101523399353</t>
   </si>
   <si>
     <t xml:space="preserve">13.1904907226562</t>
@@ -5663,13 +5663,13 @@
     <t xml:space="preserve">13.9350023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.949049949646</t>
+    <t xml:space="preserve">13.9490509033203</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0146045684814</t>
+    <t xml:space="preserve">14.0146036148071</t>
   </si>
   <si>
     <t xml:space="preserve">14.047381401062</t>
@@ -5684,10 +5684,10 @@
     <t xml:space="preserve">14.314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3611068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1410312652588</t>
+    <t xml:space="preserve">14.3611059188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1410303115845</t>
   </si>
   <si>
     <t xml:space="preserve">13.9911918640137</t>
@@ -5696,25 +5696,25 @@
     <t xml:space="preserve">14.1223001480103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9865102767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019023895264</t>
+    <t xml:space="preserve">13.9865093231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019033432007</t>
   </si>
   <si>
     <t xml:space="preserve">13.9818267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752387046814</t>
+    <t xml:space="preserve">13.7523860931396</t>
   </si>
   <si>
     <t xml:space="preserve">13.836669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8881778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0005559921265</t>
+    <t xml:space="preserve">13.8881769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0005569458008</t>
   </si>
   <si>
     <t xml:space="preserve">14.3657884597778</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">14.403247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.286187171936</t>
+    <t xml:space="preserve">14.2861862182617</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815046310425</t>
@@ -5735,19 +5735,19 @@
     <t xml:space="preserve">14.4453907012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4641199111938</t>
+    <t xml:space="preserve">14.4641208648682</t>
   </si>
   <si>
     <t xml:space="preserve">14.3517408370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1129360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.033332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460359573364</t>
+    <t xml:space="preserve">14.1129350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0333337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460350036621</t>
   </si>
   <si>
     <t xml:space="preserve">14.0567464828491</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">14.5624523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6561012268066</t>
+    <t xml:space="preserve">14.6561002731323</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982431411743</t>
@@ -5783,13 +5783,13 @@
     <t xml:space="preserve">15.1009349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9136362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5999116897583</t>
+    <t xml:space="preserve">14.9136371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7684812545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5999126434326</t>
   </si>
   <si>
     <t xml:space="preserve">14.4500732421875</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">14.4219779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3376941680908</t>
+    <t xml:space="preserve">14.3376951217651</t>
   </si>
   <si>
     <t xml:space="preserve">14.3002347946167</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">13.5229454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8554000854492</t>
+    <t xml:space="preserve">13.8554010391235</t>
   </si>
   <si>
     <t xml:space="preserve">13.9089336395264</t>
@@ -6531,6 +6531,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.9950008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7000007629395</t>
   </si>
 </sst>
 </file>
@@ -72103,7 +72106,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6942708333</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>2639106</v>
@@ -72124,6 +72127,32 @@
         <v>2172</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6918634259</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>1922037</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>18.1650009155273</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>17.7099990844727</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>18.0799999237061</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="2177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="2178">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19125938415527</t>
+    <t xml:space="preserve">5.19125890731812</t>
   </si>
   <si>
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18521547317505</t>
+    <t xml:space="preserve">5.18521499633789</t>
   </si>
   <si>
     <t xml:space="preserve">5.05528259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95858860015869</t>
+    <t xml:space="preserve">4.95858907699585</t>
   </si>
   <si>
     <t xml:space="preserve">4.837721824646</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">4.97974061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91930723190308</t>
+    <t xml:space="preserve">4.91930770874023</t>
   </si>
   <si>
     <t xml:space="preserve">4.73196220397949</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">4.50533533096313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59900760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41468477249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65944194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67455005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52346563339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59598588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52648735046387</t>
+    <t xml:space="preserve">4.59900808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4146842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65944242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67455053329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52346611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59598636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52648687362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.27870941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4509449005127</t>
+    <t xml:space="preserve">4.45094537734985</t>
   </si>
   <si>
     <t xml:space="preserve">4.3119478225708</t>
@@ -107,91 +107,91 @@
     <t xml:space="preserve">4.19410228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00373601913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09136438369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9886269569397</t>
+    <t xml:space="preserve">4.00373554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09136486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98862767219543</t>
   </si>
   <si>
     <t xml:space="preserve">3.61695981025696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41450691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47796201705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64717650413513</t>
+    <t xml:space="preserve">3.41450715065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6713502407074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47796177864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54443860054016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64717626571655</t>
   </si>
   <si>
     <t xml:space="preserve">3.68041491508484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74991369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6411337852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091661453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75595736503601</t>
+    <t xml:space="preserve">3.74991297721863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113402366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091637611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75595712661743</t>
   </si>
   <si>
     <t xml:space="preserve">3.6622850894928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62300324440002</t>
+    <t xml:space="preserve">3.62300300598145</t>
   </si>
   <si>
     <t xml:space="preserve">3.67437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76804447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78315281867981</t>
+    <t xml:space="preserve">3.76804399490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78315305709839</t>
   </si>
   <si>
     <t xml:space="preserve">3.93725848197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08834314346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10345125198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02488803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006350517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96143245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97351908683777</t>
+    <t xml:space="preserve">4.08834266662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1034517288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02488708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006398200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9614315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97351884841919</t>
   </si>
   <si>
     <t xml:space="preserve">4.0339527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38446807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42979335784912</t>
+    <t xml:space="preserve">4.38446855545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42979288101196</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173112869263</t>
@@ -203,52 +203,52 @@
     <t xml:space="preserve">4.03697443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07323408126831</t>
+    <t xml:space="preserve">4.07323455810547</t>
   </si>
   <si>
     <t xml:space="preserve">4.09438610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01884460449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8798463344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90401983261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82545614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79221796989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83149981498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75897884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79523897171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6048731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81336951255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85567355155945</t>
+    <t xml:space="preserve">4.01884412765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99164915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87984657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90402007102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82545590400696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79221749305725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83149933815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75897860527039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79523944854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60487294197083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81336903572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85567331314087</t>
   </si>
   <si>
     <t xml:space="preserve">3.77408766746521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97049760818481</t>
+    <t xml:space="preserve">3.97049713134766</t>
   </si>
   <si>
     <t xml:space="preserve">4.04301786422729</t>
@@ -263,58 +263,58 @@
     <t xml:space="preserve">4.2333836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36935997009277</t>
+    <t xml:space="preserve">4.36935901641846</t>
   </si>
   <si>
     <t xml:space="preserve">4.38748979568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39655447006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33612108230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21223211288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05208349227905</t>
+    <t xml:space="preserve">4.39655494689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33612155914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21223258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05208253860474</t>
   </si>
   <si>
     <t xml:space="preserve">3.88589000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85265135765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80430436134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078213691711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89797639846802</t>
+    <t xml:space="preserve">3.8526508808136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8043041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87078166007996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8979766368866</t>
   </si>
   <si>
     <t xml:space="preserve">3.93423700332642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92215013504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90704154968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97956275939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0158224105835</t>
+    <t xml:space="preserve">3.92215085029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90704202651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97956228256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01582288742065</t>
   </si>
   <si>
     <t xml:space="preserve">4.21827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31496906280518</t>
+    <t xml:space="preserve">4.31497001647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.30590438842773</t>
@@ -335,49 +335,49 @@
     <t xml:space="preserve">4.00071382522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98560547828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610670089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70156693458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52026581764221</t>
+    <t xml:space="preserve">3.98560523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91610646247864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70156669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52026605606079</t>
   </si>
   <si>
     <t xml:space="preserve">3.38731145858765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48098373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46889662742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60789465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80732583999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85869550704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83452033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20903182029724</t>
+    <t xml:space="preserve">3.48098421096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46889686584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6078941822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8073263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85869431495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83452081680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2090322971344</t>
   </si>
   <si>
     <t xml:space="preserve">2.79929113388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96125316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06399083137512</t>
+    <t xml:space="preserve">2.96125364303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0639910697937</t>
   </si>
   <si>
     <t xml:space="preserve">3.11535930633545</t>
@@ -386,97 +386,97 @@
     <t xml:space="preserve">3.1455762386322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0132269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91653299331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84763789176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94554090499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19694519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4447238445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47191882133484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57767820358276</t>
+    <t xml:space="preserve">3.01322674751282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91653227806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84763813018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94554042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19694495201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472360610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47191858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57767772674561</t>
   </si>
   <si>
     <t xml:space="preserve">3.5263090133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58674287796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5535044670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5958080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58976459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61998105049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5353741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65926313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.613938331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78617453575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71365356445312</t>
+    <t xml:space="preserve">3.58674263954163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55350399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59580779075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58976411819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61998128890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53537368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65926337242126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61393809318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78617405891418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7136538028717</t>
   </si>
   <si>
     <t xml:space="preserve">3.40846347808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42054986953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71969723701477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9674756526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94028067588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099883079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308546066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84962964057922</t>
+    <t xml:space="preserve">3.42054963111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96747541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94028043746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84962940216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.81639099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80128216743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69552373886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72876238822937</t>
+    <t xml:space="preserve">3.80128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6955235004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72876191139221</t>
   </si>
   <si>
     <t xml:space="preserve">3.92517185211182</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">3.8949556350708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95236730575562</t>
+    <t xml:space="preserve">3.95236682891846</t>
   </si>
   <si>
     <t xml:space="preserve">4.0490608215332</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">4.14273309707642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07927799224854</t>
+    <t xml:space="preserve">4.07927751541138</t>
   </si>
   <si>
     <t xml:space="preserve">4.19108009338379</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73178386688232</t>
+    <t xml:space="preserve">3.7317841053009</t>
   </si>
   <si>
     <t xml:space="preserve">3.78919553756714</t>
@@ -515,52 +515,52 @@
     <t xml:space="preserve">3.68645834922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77710914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49609231948853</t>
+    <t xml:space="preserve">3.77106523513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77710866928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4960925579071</t>
   </si>
   <si>
     <t xml:space="preserve">3.54141759872437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47494101524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49911403656006</t>
+    <t xml:space="preserve">3.47494077682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49911427497864</t>
   </si>
   <si>
     <t xml:space="preserve">3.49004936218262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49307084083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68343710899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78013038635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65322017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74387049674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87380337715149</t>
+    <t xml:space="preserve">3.49307107925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68343687057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78013157844543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65321946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74387121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87380266189575</t>
   </si>
   <si>
     <t xml:space="preserve">3.99467062950134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10949468612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15784168243408</t>
+    <t xml:space="preserve">4.10949516296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15784215927124</t>
   </si>
   <si>
     <t xml:space="preserve">4.23640584945679</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">4.06114768981934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84358692169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00977945327759</t>
+    <t xml:space="preserve">3.84358620643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00977849960327</t>
   </si>
   <si>
     <t xml:space="preserve">4.14575529098511</t>
@@ -584,52 +584,52 @@
     <t xml:space="preserve">4.25453567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26964426040649</t>
+    <t xml:space="preserve">4.26964378356934</t>
   </si>
   <si>
     <t xml:space="preserve">4.20618867874146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11251592636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94632411003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99360394477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06294870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00306034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96208381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9084997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79502749443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9557797908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10392427444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23315763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23946094512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05979633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46325397491455</t>
+    <t xml:space="preserve">4.11251640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94632387161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9936044216156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06294918060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00305938720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96208310127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90849924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7950267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95578002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10392475128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23315668106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23945999145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05979585647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46325349807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.67759084701538</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">4.67128705978394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69650363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74693536758423</t>
+    <t xml:space="preserve">4.69650268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74693584442139</t>
   </si>
   <si>
     <t xml:space="preserve">4.79106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95181608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89507961273193</t>
+    <t xml:space="preserve">4.95181655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89508056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.91714429855347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98964023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95496845245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93920850753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00224828720093</t>
+    <t xml:space="preserve">4.98964071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95496892929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.939208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00224876403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.99909687042236</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.93605661392212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89823293685913</t>
+    <t xml:space="preserve">4.89823198318481</t>
   </si>
   <si>
     <t xml:space="preserve">4.8887767791748</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">4.99279260635376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13778495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16930532455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14408922195435</t>
+    <t xml:space="preserve">5.1377854347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1440896987915</t>
   </si>
   <si>
     <t xml:space="preserve">5.16300106048584</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.92975234985352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98333740234375</t>
+    <t xml:space="preserve">4.98333644866943</t>
   </si>
   <si>
     <t xml:space="preserve">4.98018455505371</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">4.86356067657471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05898523330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04007291793823</t>
+    <t xml:space="preserve">5.05898475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04007244110107</t>
   </si>
   <si>
     <t xml:space="preserve">5.00540065765381</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">5.08420085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01170492172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08735275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103462219238</t>
+    <t xml:space="preserve">5.01170539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08735322952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37103509902954</t>
   </si>
   <si>
     <t xml:space="preserve">5.53809070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3615779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29538631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15354537963867</t>
+    <t xml:space="preserve">5.36157846450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29538583755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15354585647583</t>
   </si>
   <si>
     <t xml:space="preserve">5.01485681533813</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">5.13463354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92344903945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96757650375366</t>
+    <t xml:space="preserve">4.92344808578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9675760269165</t>
   </si>
   <si>
     <t xml:space="preserve">4.91084003448486</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05583381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17560958862305</t>
+    <t xml:space="preserve">5.055832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17561006546021</t>
   </si>
   <si>
     <t xml:space="preserve">5.14724159240723</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">5.07159328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0243124961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97387981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82888841629028</t>
+    <t xml:space="preserve">5.02431297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97388029098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82888793945312</t>
   </si>
   <si>
     <t xml:space="preserve">4.69335126876831</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.72802305221558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76900005340576</t>
+    <t xml:space="preserve">4.76899909973145</t>
   </si>
   <si>
     <t xml:space="preserve">4.94866466522217</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">5.21658563613892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2260422706604</t>
+    <t xml:space="preserve">5.22604179382324</t>
   </si>
   <si>
     <t xml:space="preserve">5.30169057846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24810552597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23549795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25125741958618</t>
+    <t xml:space="preserve">5.24810600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23549842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25125789642334</t>
   </si>
   <si>
     <t xml:space="preserve">5.26071453094482</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">5.32375383377075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33636236190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27962589263916</t>
+    <t xml:space="preserve">5.33636283874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27962636947632</t>
   </si>
   <si>
     <t xml:space="preserve">5.33951425552368</t>
@@ -845,64 +845,64 @@
     <t xml:space="preserve">5.32690620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19767379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20712995529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20397806167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23865079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13148212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0810489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85095262527466</t>
+    <t xml:space="preserve">5.19767332077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20712947845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20397758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23865032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13148164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8509521484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.38364219665527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46559524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38994693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35527467727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56330823898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57906770706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59797954559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70830059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78710126876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75242900848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7366681098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72090721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79340362548828</t>
+    <t xml:space="preserve">5.46559476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38994741439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35527420043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.563307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57906818389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59798097610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70830106735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78710031509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75242853164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73666954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72090816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79340410232544</t>
   </si>
   <si>
     <t xml:space="preserve">5.76188516616821</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">5.78394937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62319660186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64210796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68938779830933</t>
+    <t xml:space="preserve">5.62319612503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6421070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68938875198364</t>
   </si>
   <si>
     <t xml:space="preserve">5.73036479949951</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">5.73982048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71460485458374</t>
+    <t xml:space="preserve">5.71460390090942</t>
   </si>
   <si>
     <t xml:space="preserve">5.62949991226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45298719406128</t>
+    <t xml:space="preserve">5.45298671722412</t>
   </si>
   <si>
     <t xml:space="preserve">5.32060194015503</t>
@@ -947,58 +947,58 @@
     <t xml:space="preserve">5.25441026687622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27332210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41516351699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39625120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44983530044556</t>
+    <t xml:space="preserve">5.27332162857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36473035812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41516304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39625072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44983577728271</t>
   </si>
   <si>
     <t xml:space="preserve">5.37418651580811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39309930801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29223394393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21028184890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35842704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34581804275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48135471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46874713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44668340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5948281288147</t>
+    <t xml:space="preserve">5.39309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29223489761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21028232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35842609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34581756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48135566711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46874761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44668292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59482717514038</t>
   </si>
   <si>
     <t xml:space="preserve">5.52548360824585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56015539169312</t>
+    <t xml:space="preserve">5.56015491485596</t>
   </si>
   <si>
     <t xml:space="preserve">5.59167575836182</t>
@@ -1007,181 +1007,181 @@
     <t xml:space="preserve">5.66101980209351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7177562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6736273765564</t>
+    <t xml:space="preserve">5.71775531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362833023071</t>
   </si>
   <si>
     <t xml:space="preserve">5.67678022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49081039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50972366333008</t>
+    <t xml:space="preserve">5.49081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50972318649292</t>
   </si>
   <si>
     <t xml:space="preserve">5.56961154937744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60743618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58221960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55700397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54439544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67993211746216</t>
+    <t xml:space="preserve">5.60743570327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58221864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55700302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54439496994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67993259429932</t>
   </si>
   <si>
     <t xml:space="preserve">5.67047643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48450660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53493976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52863550186157</t>
+    <t xml:space="preserve">5.61058712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48450708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53493881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52863597869873</t>
   </si>
   <si>
     <t xml:space="preserve">5.47505140304565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43407440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33005809783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50026798248291</t>
+    <t xml:space="preserve">5.38049030303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43407487869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33005857467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50026702880859</t>
   </si>
   <si>
     <t xml:space="preserve">5.56645965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5065712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51602745056152</t>
+    <t xml:space="preserve">5.50657081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51602792739868</t>
   </si>
   <si>
     <t xml:space="preserve">5.58537149429321</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66732406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65471649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69254064559937</t>
+    <t xml:space="preserve">5.66732454299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65471601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69253969192505</t>
   </si>
   <si>
     <t xml:space="preserve">5.72406005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75873231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71145296096802</t>
+    <t xml:space="preserve">5.75873279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71145248413086</t>
   </si>
   <si>
     <t xml:space="preserve">5.7997088432312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74612379074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7744927406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74927663803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77764415740967</t>
+    <t xml:space="preserve">5.74612426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77449226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74927711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77764511108398</t>
   </si>
   <si>
     <t xml:space="preserve">5.78079652786255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77134037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81862020492554</t>
+    <t xml:space="preserve">5.77134084701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81862163543701</t>
   </si>
   <si>
     <t xml:space="preserve">5.91633319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97622156143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93209409713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01404619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07708549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05187034606934</t>
+    <t xml:space="preserve">5.97622203826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93209266662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01404523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07708644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05187082290649</t>
   </si>
   <si>
     <t xml:space="preserve">6.03295803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10860633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10230207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2315354347229</t>
+    <t xml:space="preserve">6.10860586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10230255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23153495788574</t>
   </si>
   <si>
     <t xml:space="preserve">6.21577453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22523021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21892595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2000150680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23178052902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1335391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885753631592</t>
+    <t xml:space="preserve">6.2252311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21892690658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20001411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23178100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13353872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885705947876</t>
   </si>
   <si>
     <t xml:space="preserve">6.20558309555054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16956090927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09751749038696</t>
+    <t xml:space="preserve">6.1695613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0975170135498</t>
   </si>
   <si>
     <t xml:space="preserve">6.22850561141968</t>
@@ -1190,109 +1190,109 @@
     <t xml:space="preserve">6.34966993331909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28745079040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33329629898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29399871826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19903421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22195625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382394790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28090143203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28417587280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25470352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2481541633606</t>
+    <t xml:space="preserve">6.28745174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33329725265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29399919509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1990327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22195672988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2809009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28417539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25470399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24815320968628</t>
   </si>
   <si>
     <t xml:space="preserve">6.1237154006958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1564621925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18593454360962</t>
+    <t xml:space="preserve">6.15646171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18593406677246</t>
   </si>
   <si>
     <t xml:space="preserve">6.24160385131836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26452684402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26125240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19575786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14663791656494</t>
+    <t xml:space="preserve">6.26452779769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26125288009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19575881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1466383934021</t>
   </si>
   <si>
     <t xml:space="preserve">6.27107667922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41843843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39879131317139</t>
+    <t xml:space="preserve">6.41843891143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39879083633423</t>
   </si>
   <si>
     <t xml:space="preserve">6.40206480026245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39224147796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41188907623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49375677108765</t>
+    <t xml:space="preserve">6.39224052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41188955307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49375772476196</t>
   </si>
   <si>
     <t xml:space="preserve">6.51995468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57562589645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53305387496948</t>
+    <t xml:space="preserve">6.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53305435180664</t>
   </si>
   <si>
     <t xml:space="preserve">6.5297794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48720693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43808650970459</t>
+    <t xml:space="preserve">6.48720741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43808794021606</t>
   </si>
   <si>
     <t xml:space="preserve">6.45380592346191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36604356765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41319942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47607421875</t>
+    <t xml:space="preserve">6.36604404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41319990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47607374191284</t>
   </si>
   <si>
     <t xml:space="preserve">6.51406097412109</t>
@@ -1301,136 +1301,136 @@
     <t xml:space="preserve">6.45642566680908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26780223846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36997365951538</t>
+    <t xml:space="preserve">6.26780271530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36997318267822</t>
   </si>
   <si>
     <t xml:space="preserve">6.32019662857056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36473512649536</t>
+    <t xml:space="preserve">6.36473417282104</t>
   </si>
   <si>
     <t xml:space="preserve">6.41581916809082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4551157951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47214365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44594717025757</t>
+    <t xml:space="preserve">6.45511531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47214508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44594621658325</t>
   </si>
   <si>
     <t xml:space="preserve">6.4669041633606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47869396209717</t>
+    <t xml:space="preserve">6.47869443893433</t>
   </si>
   <si>
     <t xml:space="preserve">6.40010118484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46166563034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47476482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51012992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32674646377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21016788482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31102800369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44463634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46559524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45904684066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39748048782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42498922348022</t>
+    <t xml:space="preserve">6.46166610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47476434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51013040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41975021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32674694061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21016693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31102848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44463682174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46559619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45904636383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39748096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42498874664307</t>
   </si>
   <si>
     <t xml:space="preserve">6.45773553848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40665006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738409042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37390327453613</t>
+    <t xml:space="preserve">6.40664958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738313674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37390279769897</t>
   </si>
   <si>
     <t xml:space="preserve">6.25732326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21671676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24684381484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25339317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27828216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35294437408447</t>
+    <t xml:space="preserve">6.21671628952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2468433380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25339365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27828121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35294532775879</t>
   </si>
   <si>
     <t xml:space="preserve">6.34508466720581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41712999343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39355134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54811763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63457059860229</t>
+    <t xml:space="preserve">6.41712856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39355182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54811811447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63457012176514</t>
   </si>
   <si>
     <t xml:space="preserve">6.66076755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79503154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84415149688721</t>
+    <t xml:space="preserve">6.79503202438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84415197372437</t>
   </si>
   <si>
     <t xml:space="preserve">6.70661354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199810028076</t>
+    <t xml:space="preserve">6.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199857711792</t>
   </si>
   <si>
     <t xml:space="preserve">6.67386674880981</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">6.72953701019287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54942750930786</t>
+    <t xml:space="preserve">6.54942798614502</t>
   </si>
   <si>
     <t xml:space="preserve">6.46428489685059</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">6.51537036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56907510757446</t>
+    <t xml:space="preserve">6.56907653808594</t>
   </si>
   <si>
     <t xml:space="preserve">6.5219202041626</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">6.20754766464233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01499509811401</t>
+    <t xml:space="preserve">6.01499462127686</t>
   </si>
   <si>
     <t xml:space="preserve">5.915442943573</t>
@@ -1472,61 +1472,61 @@
     <t xml:space="preserve">5.95343017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81327247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58011245727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24085140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03127002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38624954223633</t>
+    <t xml:space="preserve">5.81327199935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58011293411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24085235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03127098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38624906539917</t>
   </si>
   <si>
     <t xml:space="preserve">5.2840781211853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4216160774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32861471176147</t>
+    <t xml:space="preserve">5.42161655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32861423492432</t>
   </si>
   <si>
     <t xml:space="preserve">5.19238615036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35874176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23823165893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12689113616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37707996368408</t>
+    <t xml:space="preserve">5.35874223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23823261260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12689208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37708044052124</t>
   </si>
   <si>
     <t xml:space="preserve">5.3050365447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40327739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34826374053955</t>
+    <t xml:space="preserve">5.40327787399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34826326370239</t>
   </si>
   <si>
     <t xml:space="preserve">5.28276824951172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26049995422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44257545471191</t>
+    <t xml:space="preserve">5.26050043106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44257497787476</t>
   </si>
   <si>
     <t xml:space="preserve">5.38755941390991</t>
@@ -1535,28 +1535,28 @@
     <t xml:space="preserve">5.52378749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33254432678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29848670959473</t>
+    <t xml:space="preserve">5.33254384994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29848718643188</t>
   </si>
   <si>
     <t xml:space="preserve">5.21727418899536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18321704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21465444564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18845701217651</t>
+    <t xml:space="preserve">5.18321657180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21465396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18845653533936</t>
   </si>
   <si>
     <t xml:space="preserve">5.25133085250854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3220648765564</t>
+    <t xml:space="preserve">5.32206535339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.39148902893066</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">5.26835918426514</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17928695678711</t>
+    <t xml:space="preserve">5.17928743362427</t>
   </si>
   <si>
     <t xml:space="preserve">5.2015552520752</t>
@@ -1580,37 +1580,37 @@
     <t xml:space="preserve">5.27097988128662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28931856155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33778285980225</t>
+    <t xml:space="preserve">5.2893180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3377833366394</t>
   </si>
   <si>
     <t xml:space="preserve">5.32468461990356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3561224937439</t>
+    <t xml:space="preserve">5.35612201690674</t>
   </si>
   <si>
     <t xml:space="preserve">5.51330852508545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57618284225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.628577709198</t>
+    <t xml:space="preserve">5.57618236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62857866287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.73205900192261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68097352981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81851196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74646759033203</t>
+    <t xml:space="preserve">5.68097305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81851100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74646806716919</t>
   </si>
   <si>
     <t xml:space="preserve">5.68752241134644</t>
@@ -1622,34 +1622,34 @@
     <t xml:space="preserve">5.68490362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75956678390503</t>
+    <t xml:space="preserve">5.75956583023071</t>
   </si>
   <si>
     <t xml:space="preserve">5.75563716888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76742601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7084813117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59583044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44912385940552</t>
+    <t xml:space="preserve">5.76742553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70848035812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5958309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44912338256836</t>
   </si>
   <si>
     <t xml:space="preserve">5.56439399719238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50282907485962</t>
+    <t xml:space="preserve">5.50282955169678</t>
   </si>
   <si>
     <t xml:space="preserve">5.51985788345337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61023950576782</t>
+    <t xml:space="preserve">5.61023998260498</t>
   </si>
   <si>
     <t xml:space="preserve">5.49758958816528</t>
@@ -1658,58 +1658,58 @@
     <t xml:space="preserve">5.43340444564819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43864440917969</t>
+    <t xml:space="preserve">5.43864488601685</t>
   </si>
   <si>
     <t xml:space="preserve">5.42816543579102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39541864395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41899681091309</t>
+    <t xml:space="preserve">5.39541816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41899633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.25002098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55522441864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73598909378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68621253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90627336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89710474014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91282320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01368427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03333282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09620714187622</t>
+    <t xml:space="preserve">5.55522489547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73598957061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68621301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90627384185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89710521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91282272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03333377838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">6.00844478607178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00713491439819</t>
+    <t xml:space="preserve">6.00713539123535</t>
   </si>
   <si>
     <t xml:space="preserve">5.96390819549561</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">6.07524967193604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06477022171021</t>
+    <t xml:space="preserve">6.06476974487305</t>
   </si>
   <si>
     <t xml:space="preserve">6.00451564788818</t>
@@ -1733,31 +1733,31 @@
     <t xml:space="preserve">5.4884204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48056125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3888692855835</t>
+    <t xml:space="preserve">5.48056077957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38886880874634</t>
   </si>
   <si>
     <t xml:space="preserve">5.13737106323242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18059635162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07187652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02865028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03520059585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11379241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05484771728516</t>
+    <t xml:space="preserve">5.18059682846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07187604904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02865076065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03520011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11379289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05484819412231</t>
   </si>
   <si>
     <t xml:space="preserve">5.00638246536255</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">5.15963888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06663703918457</t>
+    <t xml:space="preserve">5.06663751602173</t>
   </si>
   <si>
     <t xml:space="preserve">5.07842636108398</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">4.95791673660278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09938478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11248397827148</t>
+    <t xml:space="preserve">5.09938430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11248302459717</t>
   </si>
   <si>
     <t xml:space="preserve">5.07711696624756</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">5.19500637054443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.136061668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11641311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13868141174316</t>
+    <t xml:space="preserve">5.13606119155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11641359329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13868093490601</t>
   </si>
   <si>
     <t xml:space="preserve">5.15309000015259</t>
@@ -1808,43 +1808,43 @@
     <t xml:space="preserve">5.14915990829468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104610443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15818929672241</t>
+    <t xml:space="preserve">5.08104562759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15818977355957</t>
   </si>
   <si>
     <t xml:space="preserve">5.03690242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08987855911255</t>
+    <t xml:space="preserve">5.08987808227539</t>
   </si>
   <si>
     <t xml:space="preserve">5.08011960983276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11776065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34499979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36730527877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39100503921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44258737564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44119358062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47604608535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37706470489502</t>
+    <t xml:space="preserve">5.117760181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34500026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36730480194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39100551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44258689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44119262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3770637512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.38821697235107</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">5.22231864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10242605209351</t>
+    <t xml:space="preserve">5.10242509841919</t>
   </si>
   <si>
     <t xml:space="preserve">5.07733201980591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24462461471558</t>
+    <t xml:space="preserve">5.24462413787842</t>
   </si>
   <si>
     <t xml:space="preserve">5.26553583145142</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">5.31293535232544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23068284988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27668905258179</t>
+    <t xml:space="preserve">5.23068332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27668857574463</t>
   </si>
   <si>
     <t xml:space="preserve">5.37288188934326</t>
@@ -1883,22 +1883,22 @@
     <t xml:space="preserve">5.25577640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12751865386963</t>
+    <t xml:space="preserve">5.12751960754395</t>
   </si>
   <si>
     <t xml:space="preserve">5.04944944381714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14145994186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09127283096313</t>
+    <t xml:space="preserve">5.14146089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09127235412598</t>
   </si>
   <si>
     <t xml:space="preserve">5.08709001541138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3896107673645</t>
+    <t xml:space="preserve">5.38961029052734</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985229492188</t>
@@ -1907,31 +1907,31 @@
     <t xml:space="preserve">5.36312294006348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33524084091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33802938461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40494680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34639358520508</t>
+    <t xml:space="preserve">5.33524036407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33802890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40494585037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34639406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.33942317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46210432052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46907567977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.491379737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50671625137329</t>
+    <t xml:space="preserve">5.46210384368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49138021469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50671529769897</t>
   </si>
   <si>
     <t xml:space="preserve">5.48859262466431</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">5.50253343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5596923828125</t>
+    <t xml:space="preserve">5.55969190597534</t>
   </si>
   <si>
     <t xml:space="preserve">5.48998641967773</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">5.45931625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29481267929077</t>
+    <t xml:space="preserve">5.29481220245361</t>
   </si>
   <si>
     <t xml:space="preserve">5.14424896240234</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">5.11218452453613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28505325317383</t>
+    <t xml:space="preserve">5.28505277633667</t>
   </si>
   <si>
     <t xml:space="preserve">5.3979754447937</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">5.59036254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78971862792969</t>
+    <t xml:space="preserve">5.78971910476685</t>
   </si>
   <si>
     <t xml:space="preserve">5.80366039276123</t>
@@ -1994,22 +1994,22 @@
     <t xml:space="preserve">5.77717208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7980842590332</t>
+    <t xml:space="preserve">5.79808330535889</t>
   </si>
   <si>
     <t xml:space="preserve">5.73953151702881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75486660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8273606300354</t>
+    <t xml:space="preserve">5.75486612319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82735967636108</t>
   </si>
   <si>
     <t xml:space="preserve">5.91797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98071146011353</t>
+    <t xml:space="preserve">5.98071193695068</t>
   </si>
   <si>
     <t xml:space="preserve">6.14939785003662</t>
@@ -2018,97 +2018,97 @@
     <t xml:space="preserve">6.02532291412354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07969284057617</t>
+    <t xml:space="preserve">6.07969236373901</t>
   </si>
   <si>
     <t xml:space="preserve">6.08945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20376825332642</t>
+    <t xml:space="preserve">6.20376777648926</t>
   </si>
   <si>
     <t xml:space="preserve">6.10060453414917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03786945343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12430477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10339307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18982791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21631574630737</t>
+    <t xml:space="preserve">6.03787040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12430429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10339260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18982696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21631526947021</t>
   </si>
   <si>
     <t xml:space="preserve">6.26510858535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3989429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35990905761719</t>
+    <t xml:space="preserve">6.39894437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35990762710571</t>
   </si>
   <si>
     <t xml:space="preserve">6.24001502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28602123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23583364486694</t>
+    <t xml:space="preserve">6.28602027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23583316802979</t>
   </si>
   <si>
     <t xml:space="preserve">6.17728137969971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22468042373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35293817520142</t>
+    <t xml:space="preserve">6.22468090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35293769836426</t>
   </si>
   <si>
     <t xml:space="preserve">6.42264270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45610189437866</t>
+    <t xml:space="preserve">6.4561014175415</t>
   </si>
   <si>
     <t xml:space="preserve">6.5188364982605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42543172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44076681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47840690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52162456512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4644660949707</t>
+    <t xml:space="preserve">6.42543125152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44076633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47840738296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52162504196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46446657180786</t>
   </si>
   <si>
     <t xml:space="preserve">6.48537731170654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57878255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63175916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67079401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69867563247681</t>
+    <t xml:space="preserve">6.57878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63175821304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6707935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69867515563965</t>
   </si>
   <si>
     <t xml:space="preserve">6.67915868759155</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">6.6220006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54393005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52441215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56205320358276</t>
+    <t xml:space="preserve">6.54392957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52441310882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56205272674561</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194723129272</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">6.62478828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41706657409668</t>
+    <t xml:space="preserve">6.41706705093384</t>
   </si>
   <si>
     <t xml:space="preserve">6.26789665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3487548828125</t>
+    <t xml:space="preserve">6.34875583648682</t>
   </si>
   <si>
     <t xml:space="preserve">6.20237445831299</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">6.06435775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22049760818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18146324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16612720489502</t>
+    <t xml:space="preserve">6.22049713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18146276473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16612768173218</t>
   </si>
   <si>
     <t xml:space="preserve">6.06575155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99465322494507</t>
+    <t xml:space="preserve">5.99465227127075</t>
   </si>
   <si>
     <t xml:space="preserve">6.01556444168091</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">5.84269523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83433103561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76601982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73256158828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88173055648804</t>
+    <t xml:space="preserve">5.83433055877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76601934432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7325611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88173007965088</t>
   </si>
   <si>
     <t xml:space="preserve">5.84966564178467</t>
@@ -2195,55 +2195,55 @@
     <t xml:space="preserve">5.87894201278687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96816492080688</t>
+    <t xml:space="preserve">5.96816539764404</t>
   </si>
   <si>
     <t xml:space="preserve">5.96677112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93888902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97374057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94307088851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94167709350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07132863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16333961486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14382219314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19122219085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17031049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29577875137329</t>
+    <t xml:space="preserve">5.938889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97374105453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94307041168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9416766166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07132911682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16334009170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14382171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19122123718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17031002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29577922821045</t>
   </si>
   <si>
     <t xml:space="preserve">6.33760261535645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31947898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2386212348938</t>
+    <t xml:space="preserve">6.31947946548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23862075805664</t>
   </si>
   <si>
     <t xml:space="preserve">6.30972051620483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47422552108765</t>
+    <t xml:space="preserve">6.47422504425049</t>
   </si>
   <si>
     <t xml:space="preserve">6.60248231887817</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">6.57041788101196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51186466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49095439910889</t>
+    <t xml:space="preserve">6.51186561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49095487594604</t>
   </si>
   <si>
     <t xml:space="preserve">6.55229473114014</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">6.54114198684692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54671907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792432785034</t>
+    <t xml:space="preserve">6.54671859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792385101318</t>
   </si>
   <si>
     <t xml:space="preserve">6.56762981414795</t>
@@ -2276,25 +2276,25 @@
     <t xml:space="preserve">6.53277683258057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54950666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41288471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44355487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51465368270874</t>
+    <t xml:space="preserve">6.54950714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41288423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44355583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51465320587158</t>
   </si>
   <si>
     <t xml:space="preserve">6.4895601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50350093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33481407165527</t>
+    <t xml:space="preserve">6.50350046157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33481502532959</t>
   </si>
   <si>
     <t xml:space="preserve">6.31111478805542</t>
@@ -2303,28 +2303,28 @@
     <t xml:space="preserve">6.32087326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15915727615356</t>
+    <t xml:space="preserve">6.15915679931641</t>
   </si>
   <si>
     <t xml:space="preserve">6.10478782653809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03647565841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08666372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92494773864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91379499435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94446420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80644798278809</t>
+    <t xml:space="preserve">6.03647518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08666324615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92494678497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91379451751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94446516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8064489364624</t>
   </si>
   <si>
     <t xml:space="preserve">5.93052434921265</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">5.97652959823608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06714677810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11315155029297</t>
+    <t xml:space="preserve">6.06714630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11315202713013</t>
   </si>
   <si>
     <t xml:space="preserve">6.04344654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.118727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13963842391968</t>
+    <t xml:space="preserve">6.11872863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13963937759399</t>
   </si>
   <si>
     <t xml:space="preserve">6.19261598587036</t>
@@ -2354,37 +2354,37 @@
     <t xml:space="preserve">6.28044462203979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35712003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59829950332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68055152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63036489486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66382265090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72655725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.662428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63454723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76140975952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100831985474</t>
+    <t xml:space="preserve">6.35712051391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296632766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59830045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68055295944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6303653717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66382360458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72655773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66242837905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63454627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76141023635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100879669189</t>
   </si>
   <si>
     <t xml:space="preserve">6.89803266525269</t>
@@ -2396,19 +2396,19 @@
     <t xml:space="preserve">6.94682645797729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04371738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95379829406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98446798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95658445358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76419878005981</t>
+    <t xml:space="preserve">7.04371643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95379734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98446846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95658493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76419830322266</t>
   </si>
   <si>
     <t xml:space="preserve">6.84645080566406</t>
@@ -2417,148 +2417,148 @@
     <t xml:space="preserve">6.8157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83390426635742</t>
+    <t xml:space="preserve">6.83390378952026</t>
   </si>
   <si>
     <t xml:space="preserve">6.79347515106201</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80462789535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03326177597046</t>
+    <t xml:space="preserve">6.80462837219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0332612991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.19009780883789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481784820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4026985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38178730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36087608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43058156967163</t>
+    <t xml:space="preserve">7.27025842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481832504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40269947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38178777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36087703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43058109283447</t>
   </si>
   <si>
     <t xml:space="preserve">7.50377225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55953502655029</t>
+    <t xml:space="preserve">7.55953598022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.55256509780884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58044719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44103765487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4236102104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48285961151123</t>
+    <t xml:space="preserve">7.58044672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44103717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42361068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48286008834839</t>
   </si>
   <si>
     <t xml:space="preserve">7.6431827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59438800811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51422595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27374505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42012596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35390520095825</t>
+    <t xml:space="preserve">7.59438896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51422739028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2737455368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42012548446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35390472412109</t>
   </si>
   <si>
     <t xml:space="preserve">7.51857423782349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48940515518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752691268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52586793899536</t>
+    <t xml:space="preserve">7.48940420150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752595901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5258674621582</t>
   </si>
   <si>
     <t xml:space="preserve">7.49669694900513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47481822967529</t>
+    <t xml:space="preserve">7.47482013702393</t>
   </si>
   <si>
     <t xml:space="preserve">7.52951335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40189456939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33261489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29250621795654</t>
+    <t xml:space="preserve">7.40189409255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33261632919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29250717163086</t>
   </si>
   <si>
     <t xml:space="preserve">7.35449266433716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32532262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3471999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22687387466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37272357940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38366317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24437665939331</t>
+    <t xml:space="preserve">7.32532215118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34720039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22687435150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3727240562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38366222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24437618255615</t>
   </si>
   <si>
     <t xml:space="preserve">7.31438398361206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28229761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35813999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21958208084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15686559677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22979068756104</t>
+    <t xml:space="preserve">7.28229713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3581395149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28521347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21958065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15686702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22979164123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.1641583442688</t>
@@ -2576,187 +2576,187 @@
     <t xml:space="preserve">7.21812343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17874336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18020248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08539962768555</t>
+    <t xml:space="preserve">7.1787428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1802020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08539867401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.15832424163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11019325256348</t>
+    <t xml:space="preserve">7.11019468307495</t>
   </si>
   <si>
     <t xml:space="preserve">7.05768775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07810735702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99643135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93809127807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97309494018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77328062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98622179031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93371534347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75286102294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57200622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71931552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98038721084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86954069137573</t>
+    <t xml:space="preserve">7.0781078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99643039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93809032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97309541702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77328014373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98622131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9337158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5720067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71931505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8053674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98038768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86954116821289</t>
   </si>
   <si>
     <t xml:space="preserve">7.00372362136841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04164505004883</t>
+    <t xml:space="preserve">7.04164552688599</t>
   </si>
   <si>
     <t xml:space="preserve">7.0606050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06206369400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00518178939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03289413452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99351453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86370754241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45240926742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42178153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38677740097046</t>
+    <t xml:space="preserve">7.06206321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00518226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03289318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99351406097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86370706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4524097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42178106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38677835464478</t>
   </si>
   <si>
     <t xml:space="preserve">6.23363494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97256231307983</t>
+    <t xml:space="preserve">5.97256278991699</t>
   </si>
   <si>
     <t xml:space="preserve">5.76253890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71003293991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63564920425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39937210083008</t>
+    <t xml:space="preserve">5.71003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63564872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39937162399292</t>
   </si>
   <si>
     <t xml:space="preserve">5.28415012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52281284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21215152740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33174896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52228045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7760603427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33850979804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25537538528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06649923324585</t>
+    <t xml:space="preserve">4.5228123664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21215200424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3317494392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52228093147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77605986595154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33850932121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25537490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06649899482727</t>
   </si>
   <si>
     <t xml:space="preserve">3.0424337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10150265693665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17661595344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61854195594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90440821647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0108790397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76439237594604</t>
+    <t xml:space="preserve">3.10150289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17661547660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61854147911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90440845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01087856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76439189910889</t>
   </si>
   <si>
     <t xml:space="preserve">3.62802219390869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66667222976685</t>
+    <t xml:space="preserve">3.66667175292969</t>
   </si>
   <si>
     <t xml:space="preserve">3.64917039871216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77460169792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70605182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97149968147278</t>
+    <t xml:space="preserve">3.77460217475891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70605158805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97149896621704</t>
   </si>
   <si>
     <t xml:space="preserve">4.05171680450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05900907516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04150724411011</t>
+    <t xml:space="preserve">4.05900859832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04150676727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.87232112884521</t>
@@ -2765,16 +2765,16 @@
     <t xml:space="preserve">3.57989144325256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64771151542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69292569160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56238985061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51571750640869</t>
+    <t xml:space="preserve">3.64771175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69292545318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56239008903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51571702957153</t>
   </si>
   <si>
     <t xml:space="preserve">3.73959708213806</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">3.95545530319214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02254724502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85627770423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79939579963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76585030555725</t>
+    <t xml:space="preserve">4.02254581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85627722740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76585054397583</t>
   </si>
   <si>
     <t xml:space="preserve">3.75855803489685</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">3.78918671607971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91607666015625</t>
+    <t xml:space="preserve">3.91607570648193</t>
   </si>
   <si>
     <t xml:space="preserve">3.85336065292358</t>
@@ -2819,49 +2819,49 @@
     <t xml:space="preserve">3.56311893463135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80960559844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74980711936951</t>
+    <t xml:space="preserve">3.80960536003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74980688095093</t>
   </si>
   <si>
     <t xml:space="preserve">3.69730091094971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168416976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31862211227417</t>
+    <t xml:space="preserve">3.77168393135071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78481149673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31862258911133</t>
   </si>
   <si>
     <t xml:space="preserve">4.25590658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60011291503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69929170608521</t>
+    <t xml:space="preserve">4.60011339187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69929122924805</t>
   </si>
   <si>
     <t xml:space="preserve">4.95452928543091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95307111740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18351316452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34540700912476</t>
+    <t xml:space="preserve">4.95307016372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18351364135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34540748596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.17330455780029</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">5.07996034622192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86410236358643</t>
+    <t xml:space="preserve">4.86410188674927</t>
   </si>
   <si>
     <t xml:space="preserve">4.96473836898804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03766441345215</t>
+    <t xml:space="preserve">5.03766393661499</t>
   </si>
   <si>
     <t xml:space="preserve">5.16455268859863</t>
@@ -2885,37 +2885,37 @@
     <t xml:space="preserve">5.1397590637207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23164415359497</t>
+    <t xml:space="preserve">5.23164367675781</t>
   </si>
   <si>
     <t xml:space="preserve">5.12079811096191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97348976135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.996826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71095943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75033950805664</t>
+    <t xml:space="preserve">4.9734902381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99682569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71095895767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75033855438232</t>
   </si>
   <si>
     <t xml:space="preserve">4.55927515029907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76200771331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.659912109375</t>
+    <t xml:space="preserve">4.76200723648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65991163253784</t>
   </si>
   <si>
     <t xml:space="preserve">4.71533489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91952466964722</t>
+    <t xml:space="preserve">4.91952514648438</t>
   </si>
   <si>
     <t xml:space="preserve">4.90348148345947</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">4.92535972595215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93119382858276</t>
+    <t xml:space="preserve">4.93119287490845</t>
   </si>
   <si>
     <t xml:space="preserve">4.88014554977417</t>
@@ -2933,40 +2933,40 @@
     <t xml:space="preserve">4.79701089859009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92973470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05079078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14559268951416</t>
+    <t xml:space="preserve">4.9297342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05078983306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13830041885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14559316635132</t>
   </si>
   <si>
     <t xml:space="preserve">5.16601181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13246583938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25206279754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25498056411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.316237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22435188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16309452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12663269042969</t>
+    <t xml:space="preserve">5.13246631622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25206327438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25498008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31623697280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22435140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16309499740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12663221359253</t>
   </si>
   <si>
     <t xml:space="preserve">5.07850217819214</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">5.05954122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9224419593811</t>
+    <t xml:space="preserve">4.92244148254395</t>
   </si>
   <si>
     <t xml:space="preserve">4.94286108016968</t>
@@ -2996,64 +2996,64 @@
     <t xml:space="preserve">4.97786521911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27248239517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28706741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29436016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20247459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11496353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24622964859009</t>
+    <t xml:space="preserve">5.27248287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28706693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29435968399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20247364044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1149640083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24622917175293</t>
   </si>
   <si>
     <t xml:space="preserve">5.12809085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09746217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24768781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27685785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4445858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47813081741333</t>
+    <t xml:space="preserve">5.09746170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24768733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27685737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44458532333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47813129425049</t>
   </si>
   <si>
     <t xml:space="preserve">5.42416667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31040334701538</t>
+    <t xml:space="preserve">5.31040382385254</t>
   </si>
   <si>
     <t xml:space="preserve">5.33519792556763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32061290740967</t>
+    <t xml:space="preserve">5.32061243057251</t>
   </si>
   <si>
     <t xml:space="preserve">5.22726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21414279937744</t>
+    <t xml:space="preserve">5.21414232254028</t>
   </si>
   <si>
     <t xml:space="preserve">5.08141851425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17767953872681</t>
+    <t xml:space="preserve">5.17768001556396</t>
   </si>
   <si>
     <t xml:space="preserve">5.39207935333252</t>
@@ -3065,43 +3065,43 @@
     <t xml:space="preserve">5.29873514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18643140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08725214004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89910650253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89327192306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87722873687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76054859161377</t>
+    <t xml:space="preserve">5.18643045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08725261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89910554885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89327144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87722826004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76054811477661</t>
   </si>
   <si>
     <t xml:space="preserve">4.95161199569702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8757700920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88452100753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84368324279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92389965057373</t>
+    <t xml:space="preserve">4.87576961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88452053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84368276596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92390060424805</t>
   </si>
   <si>
     <t xml:space="preserve">5.08871126174927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20976686477661</t>
+    <t xml:space="preserve">5.20976638793945</t>
   </si>
   <si>
     <t xml:space="preserve">5.08579397201538</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">5.28560876846313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23310327529907</t>
+    <t xml:space="preserve">5.23310232162476</t>
   </si>
   <si>
     <t xml:space="preserve">5.203932762146</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">5.0114107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0201621055603</t>
+    <t xml:space="preserve">5.02016162872314</t>
   </si>
   <si>
     <t xml:space="preserve">4.82180500030518</t>
@@ -3128,19 +3128,19 @@
     <t xml:space="preserve">4.84222459793091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79992723464966</t>
+    <t xml:space="preserve">4.79992771148682</t>
   </si>
   <si>
     <t xml:space="preserve">4.84951686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7401294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74596309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78971815109253</t>
+    <t xml:space="preserve">4.74012994766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74596357345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78971862792969</t>
   </si>
   <si>
     <t xml:space="preserve">4.76638221740723</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">4.64095115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41050815582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46884775161743</t>
+    <t xml:space="preserve">4.4105076789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46884822845459</t>
   </si>
   <si>
     <t xml:space="preserve">4.43967819213867</t>
@@ -3161,94 +3161,94 @@
     <t xml:space="preserve">4.59427881240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85680913925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30894565582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19664001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20539140701294</t>
+    <t xml:space="preserve">4.85680961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3089451789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1966404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20539093017578</t>
   </si>
   <si>
     <t xml:space="preserve">5.51605224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5962700843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51459360122681</t>
+    <t xml:space="preserve">5.59626960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51459312438965</t>
   </si>
   <si>
     <t xml:space="preserve">5.58460187911987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49854946136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72899341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75232934951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70419883728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63710784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45041990280151</t>
+    <t xml:space="preserve">5.4985499382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72899389266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75232887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70419836044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63710737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45041942596436</t>
   </si>
   <si>
     <t xml:space="preserve">5.52917861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46500444412231</t>
+    <t xml:space="preserve">5.46500492095947</t>
   </si>
   <si>
     <t xml:space="preserve">5.54230499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60210418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53209543228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48979949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49709129333496</t>
+    <t xml:space="preserve">5.60210371017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53209590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48979902267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49709177017212</t>
   </si>
   <si>
     <t xml:space="preserve">5.4752140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34978294372559</t>
+    <t xml:space="preserve">5.34978246688843</t>
   </si>
   <si>
     <t xml:space="preserve">5.36145114898682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53792905807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49271583557129</t>
+    <t xml:space="preserve">5.53792953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49271631240845</t>
   </si>
   <si>
     <t xml:space="preserve">5.42854166030884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39062070846558</t>
+    <t xml:space="preserve">5.39062118530273</t>
   </si>
   <si>
     <t xml:space="preserve">5.3789529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52042818069458</t>
+    <t xml:space="preserve">5.52042770385742</t>
   </si>
   <si>
     <t xml:space="preserve">5.52480316162109</t>
@@ -3257,43 +3257,43 @@
     <t xml:space="preserve">5.40228891372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42270803451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62835645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61231279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50438404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46208715438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51021766662598</t>
+    <t xml:space="preserve">5.42270755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62835693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61231327056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50438356399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46208763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51021862030029</t>
   </si>
   <si>
     <t xml:space="preserve">5.46937990188599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44750165939331</t>
+    <t xml:space="preserve">5.44750261306763</t>
   </si>
   <si>
     <t xml:space="preserve">5.38187026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47083806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40083026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40520620346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44896078109741</t>
+    <t xml:space="preserve">5.47083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40083074569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40520572662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44896125793457</t>
   </si>
   <si>
     <t xml:space="preserve">5.35707569122314</t>
@@ -3302,52 +3302,52 @@
     <t xml:space="preserve">5.39499664306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37020206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51167631149292</t>
+    <t xml:space="preserve">5.370201587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51167678833008</t>
   </si>
   <si>
     <t xml:space="preserve">5.7304515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89963817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97985601425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17383575439453</t>
+    <t xml:space="preserve">5.8996376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97985553741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17383623123169</t>
   </si>
   <si>
     <t xml:space="preserve">6.23071765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41740560531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50637483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48012065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59242630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53700256347656</t>
+    <t xml:space="preserve">6.41740655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50637531280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48012113571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59242582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53700304031372</t>
   </si>
   <si>
     <t xml:space="preserve">6.57930040359497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54429531097412</t>
+    <t xml:space="preserve">6.54429578781128</t>
   </si>
   <si>
     <t xml:space="preserve">6.62159633636475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61430358886719</t>
+    <t xml:space="preserve">6.61430406570435</t>
   </si>
   <si>
     <t xml:space="preserve">6.58221626281738</t>
@@ -3356,61 +3356,61 @@
     <t xml:space="preserve">6.53408575057983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3955283164978</t>
+    <t xml:space="preserve">6.39552879333496</t>
   </si>
   <si>
     <t xml:space="preserve">6.28468227386475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50199937820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43490791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52679347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6113862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7251501083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535966873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77473926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85058116912842</t>
+    <t xml:space="preserve">6.5019998550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43490839004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52679300308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61138677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72514963150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77473878860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85058069229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.86516523361206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90162801742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01976776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09415006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09706783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87975120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84037113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77911329269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90016984939575</t>
+    <t xml:space="preserve">6.9016284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01976728439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09415054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09706735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87975072860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84037208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77911424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90016937255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.90600442886353</t>
@@ -3425,22 +3425,22 @@
     <t xml:space="preserve">7.03581047058105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89579486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84912300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86078977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77182245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80682516098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81849384307861</t>
+    <t xml:space="preserve">6.89579391479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84912252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86079072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77182197570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80682611465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81849336624146</t>
   </si>
   <si>
     <t xml:space="preserve">6.80974292755127</t>
@@ -3449,85 +3449,85 @@
     <t xml:space="preserve">6.78640604019165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85203838348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84766387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7091064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.642014503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64639091491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83599519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80828380584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82724571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85641527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92788124084473</t>
+    <t xml:space="preserve">6.85203981399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84766340255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70910596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64201498031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64639043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8359956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80828523635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82724475860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85641574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92788219451904</t>
   </si>
   <si>
     <t xml:space="preserve">6.78057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90892124176025</t>
+    <t xml:space="preserve">6.90892028808594</t>
   </si>
   <si>
     <t xml:space="preserve">6.94684171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04018592834473</t>
+    <t xml:space="preserve">7.04018640518188</t>
   </si>
   <si>
     <t xml:space="preserve">7.05477094650269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0139331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08394002914429</t>
+    <t xml:space="preserve">7.01393270492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08394145965576</t>
   </si>
   <si>
     <t xml:space="preserve">7.13352966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19770383834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05914783477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0664381980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915372848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11748743057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1481146812439</t>
+    <t xml:space="preserve">7.19770336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0591459274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06643867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05331325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915468215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11748647689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14811515808105</t>
   </si>
   <si>
     <t xml:space="preserve">7.21228933334351</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">7.27062892913818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30344676971436</t>
+    <t xml:space="preserve">7.30344533920288</t>
   </si>
   <si>
     <t xml:space="preserve">7.29979944229126</t>
@@ -3548,142 +3548,142 @@
     <t xml:space="preserve">7.26771211624146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20791339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26333713531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25458574295044</t>
+    <t xml:space="preserve">7.20791292190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26333665847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25458526611328</t>
   </si>
   <si>
     <t xml:space="preserve">7.23270845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23562526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394973754883</t>
+    <t xml:space="preserve">7.23562479019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394926071167</t>
   </si>
   <si>
     <t xml:space="preserve">7.17582654953003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22249937057495</t>
+    <t xml:space="preserve">7.22249889373779</t>
   </si>
   <si>
     <t xml:space="preserve">7.28083896636963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27500534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20062065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18311977386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19332885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18749475479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36178541183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14082193374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92350673675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165285110474</t>
+    <t xml:space="preserve">7.27500486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20062112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18311929702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19332838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1874942779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36178636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1408224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14957332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92350578308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165189743042</t>
   </si>
   <si>
     <t xml:space="preserve">7.1889533996582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20499658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14519786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09560871124268</t>
+    <t xml:space="preserve">7.20499610900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14519882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09560918807983</t>
   </si>
   <si>
     <t xml:space="preserve">6.86808347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9555926322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23416662216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3107385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28667259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28813171386719</t>
+    <t xml:space="preserve">6.95559310913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23416709899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31073713302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28667163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28813123703003</t>
   </si>
   <si>
     <t xml:space="preserve">7.24145984649658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20937204360962</t>
+    <t xml:space="preserve">7.20937156677246</t>
   </si>
   <si>
     <t xml:space="preserve">7.13207101821899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21083116531372</t>
+    <t xml:space="preserve">7.2108302116394</t>
   </si>
   <si>
     <t xml:space="preserve">7.28375577926636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29615306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19041061401367</t>
+    <t xml:space="preserve">7.29615259170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19041109085083</t>
   </si>
   <si>
     <t xml:space="preserve">7.27792119979858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27354669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17728471755981</t>
+    <t xml:space="preserve">7.27354574203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17728519439697</t>
   </si>
   <si>
     <t xml:space="preserve">7.1714506149292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04601955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09852695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13644742965698</t>
+    <t xml:space="preserve">7.04601907730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09852647781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13644695281982</t>
   </si>
   <si>
     <t xml:space="preserve">7.25166845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27938032150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456918716431</t>
+    <t xml:space="preserve">7.279381275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456871032715</t>
   </si>
   <si>
     <t xml:space="preserve">7.24875116348267</t>
@@ -3695,22 +3695,22 @@
     <t xml:space="preserve">7.47846555709839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33626222610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53680467605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61337614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68630218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58785390853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734903335571</t>
+    <t xml:space="preserve">7.33626270294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53680610656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6133770942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68630170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5878529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734855651855</t>
   </si>
   <si>
     <t xml:space="preserve">7.50398921966553</t>
@@ -3719,73 +3719,73 @@
     <t xml:space="preserve">7.45294189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21520614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3800163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41283226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43106460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53315877914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58056163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6060848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55868291854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52222061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64254713058472</t>
+    <t xml:space="preserve">7.21520709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38001680374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41283321380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43106508255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53315925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58056116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60608386993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55868339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52221965789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64254665374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.67171764373779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77016639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76651906967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8868465423584</t>
+    <t xml:space="preserve">7.77016544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76651954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88684511184692</t>
   </si>
   <si>
     <t xml:space="preserve">7.8759069442749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81392097473145</t>
+    <t xml:space="preserve">7.8139214515686</t>
   </si>
   <si>
     <t xml:space="preserve">7.81756734848022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89778470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507745742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955331802368</t>
+    <t xml:space="preserve">7.89778518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955474853516</t>
   </si>
   <si>
     <t xml:space="preserve">7.79204320907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74828958511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70088720321655</t>
+    <t xml:space="preserve">7.74828863143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088768005371</t>
   </si>
   <si>
     <t xml:space="preserve">7.90313148498535</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">7.72266721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72111177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352602005005</t>
+    <t xml:space="preserve">7.72111225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45352554321289</t>
   </si>
   <si>
     <t xml:space="preserve">7.5639820098877</t>
@@ -3806,52 +3806,52 @@
     <t xml:space="preserve">7.59976530075073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6386570930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79034280776978</t>
+    <t xml:space="preserve">7.61843252182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63865756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776708602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79034185409546</t>
   </si>
   <si>
     <t xml:space="preserve">7.94591522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86035013198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82534646987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80978918075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71488857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311540603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76156044006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84868240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80589962005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5219783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64954710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68999719619751</t>
+    <t xml:space="preserve">7.86034917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82534694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80978870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71488904953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76156091690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84868192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80589914321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52197790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6495475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68999624252319</t>
   </si>
   <si>
     <t xml:space="preserve">7.81367683410645</t>
@@ -3875,34 +3875,34 @@
     <t xml:space="preserve">8.07815265655518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07037353515625</t>
+    <t xml:space="preserve">8.07037448883057</t>
   </si>
   <si>
     <t xml:space="preserve">8.13260364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23761463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17538547515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09759998321533</t>
+    <t xml:space="preserve">8.23761558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17538642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09759902954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.03536987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05092811584473</t>
+    <t xml:space="preserve">8.05092716217041</t>
   </si>
   <si>
     <t xml:space="preserve">8.02370071411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61532163619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6604380607605</t>
+    <t xml:space="preserve">7.61532211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66043710708618</t>
   </si>
   <si>
     <t xml:space="preserve">7.77867412567139</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">8.10926818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79812097549438</t>
+    <t xml:space="preserve">7.79811954498291</t>
   </si>
   <si>
     <t xml:space="preserve">8.05870532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22983741760254</t>
+    <t xml:space="preserve">8.22983837127686</t>
   </si>
   <si>
     <t xml:space="preserve">8.20650005340576</t>
@@ -3929,34 +3929,34 @@
     <t xml:space="preserve">8.14427185058594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90702104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07426357269287</t>
+    <t xml:space="preserve">7.90702199935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07426452636719</t>
   </si>
   <si>
     <t xml:space="preserve">7.88368606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93813610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77556180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67288398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67755079269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26994752883911</t>
+    <t xml:space="preserve">7.93813562393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77556276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6728835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67755031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26994800567627</t>
   </si>
   <si>
     <t xml:space="preserve">7.29172849655151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25439167022705</t>
+    <t xml:space="preserve">7.25439119338989</t>
   </si>
   <si>
     <t xml:space="preserve">6.68654775619507</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">6.73477554321289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68499231338501</t>
+    <t xml:space="preserve">6.68499279022217</t>
   </si>
   <si>
     <t xml:space="preserve">6.12337207794189</t>
@@ -3974,37 +3974,37 @@
     <t xml:space="preserve">5.95379686355591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08603477478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63520812988281</t>
+    <t xml:space="preserve">6.08603429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63520860671997</t>
   </si>
   <si>
     <t xml:space="preserve">6.31939458847046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35050868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61187267303467</t>
+    <t xml:space="preserve">6.35050916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61187219619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.66165637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10970735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06925868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22638845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06770372390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12993240356445</t>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06925916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2263879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06770324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12993192672729</t>
   </si>
   <si>
     <t xml:space="preserve">7.02103090286255</t>
@@ -4013,127 +4013,127 @@
     <t xml:space="preserve">7.05059003829956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22949886322021</t>
+    <t xml:space="preserve">7.22949934005737</t>
   </si>
   <si>
     <t xml:space="preserve">7.10659599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17193698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30417490005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11904239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97902679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89190435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03503274917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02569723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94946670532227</t>
+    <t xml:space="preserve">7.17193746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30417442321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11904287338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97902584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89190483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03503179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02569770812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94946718215942</t>
   </si>
   <si>
     <t xml:space="preserve">7.1128191947937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19527387619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18438386917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37418270111084</t>
+    <t xml:space="preserve">7.19527244567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.374183177948</t>
   </si>
   <si>
     <t xml:space="preserve">7.4488582611084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17971515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16415929794312</t>
+    <t xml:space="preserve">7.17971467971802</t>
   </si>
   <si>
     <t xml:space="preserve">7.38196086883545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38040590286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686147689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757562637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74756002426147</t>
+    <t xml:space="preserve">7.38040542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74755907058716</t>
   </si>
   <si>
     <t xml:space="preserve">7.50486469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48308420181274</t>
+    <t xml:space="preserve">7.48308372497559</t>
   </si>
   <si>
     <t xml:space="preserve">7.60598754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54842519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71955633163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71022081375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52353286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44574594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38973999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43485641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26216983795166</t>
+    <t xml:space="preserve">7.548424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71955537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70088624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71022129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52353429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44574689865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38974094390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43485546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26217079162598</t>
   </si>
   <si>
     <t xml:space="preserve">7.34151220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46752786636353</t>
+    <t xml:space="preserve">7.46752738952637</t>
   </si>
   <si>
     <t xml:space="preserve">7.41152048110962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46908283233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43174505233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32906579971313</t>
+    <t xml:space="preserve">7.46908235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43174457550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32906627655029</t>
   </si>
   <si>
     <t xml:space="preserve">7.4208550453186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53442287445068</t>
+    <t xml:space="preserve">7.534423828125</t>
   </si>
   <si>
     <t xml:space="preserve">7.4986424446106</t>
@@ -4145,16 +4145,16 @@
     <t xml:space="preserve">7.50797605514526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01325178146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90435123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96813631057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95102214813232</t>
+    <t xml:space="preserve">7.01325225830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90435075759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95102310180664</t>
   </si>
   <si>
     <t xml:space="preserve">6.63054180145264</t>
@@ -4163,22 +4163,22 @@
     <t xml:space="preserve">6.59631490707397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68188142776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74411058425903</t>
+    <t xml:space="preserve">6.68188095092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74411010742188</t>
   </si>
   <si>
     <t xml:space="preserve">6.71921825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5683126449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71144008636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56675672531128</t>
+    <t xml:space="preserve">6.56831216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71143913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56675624847412</t>
   </si>
   <si>
     <t xml:space="preserve">6.64765405654907</t>
@@ -4187,19 +4187,19 @@
     <t xml:space="preserve">6.60253858566284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42362928390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41896104812622</t>
+    <t xml:space="preserve">6.42362880706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41896200180054</t>
   </si>
   <si>
     <t xml:space="preserve">6.38784694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23227405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32406187057495</t>
+    <t xml:space="preserve">6.23227310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32406234741211</t>
   </si>
   <si>
     <t xml:space="preserve">6.45785474777222</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">6.55586671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49052572250366</t>
+    <t xml:space="preserve">6.4905252456665</t>
   </si>
   <si>
     <t xml:space="preserve">6.41273927688599</t>
@@ -4217,19 +4217,19 @@
     <t xml:space="preserve">6.3582878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05958700180054</t>
+    <t xml:space="preserve">6.05958652496338</t>
   </si>
   <si>
     <t xml:space="preserve">6.05491971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20115852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33339643478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26027679443359</t>
+    <t xml:space="preserve">6.20115900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33339595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26027727127075</t>
   </si>
   <si>
     <t xml:space="preserve">6.2213830947876</t>
@@ -4238,58 +4238,58 @@
     <t xml:space="preserve">6.24783086776733</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17937850952148</t>
+    <t xml:space="preserve">6.17937803268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.24005270004272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35673189163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50297164916992</t>
+    <t xml:space="preserve">6.35673236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50297069549561</t>
   </si>
   <si>
     <t xml:space="preserve">6.54653167724609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55119943618774</t>
+    <t xml:space="preserve">6.55119848251343</t>
   </si>
   <si>
     <t xml:space="preserve">6.59787178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64921092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70210599899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65232181549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6429877281189</t>
+    <t xml:space="preserve">6.64921045303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7021050453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65232229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64298725128174</t>
   </si>
   <si>
     <t xml:space="preserve">6.66010093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72544097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77055835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77833652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72233057022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69588232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44696474075317</t>
+    <t xml:space="preserve">6.72544145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77055788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77833604812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72233009338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69588184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44696426391602</t>
   </si>
   <si>
     <t xml:space="preserve">6.27427816390991</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">6.2945032119751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25872039794922</t>
+    <t xml:space="preserve">6.25872087478638</t>
   </si>
   <si>
     <t xml:space="preserve">6.17004442214966</t>
@@ -4310,22 +4310,22 @@
     <t xml:space="preserve">6.15448665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21360445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15137529373169</t>
+    <t xml:space="preserve">6.21360492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15137577056885</t>
   </si>
   <si>
     <t xml:space="preserve">6.07825565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31006002426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21204853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19493579864502</t>
+    <t xml:space="preserve">6.31006050109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21204900741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19493627548218</t>
   </si>
   <si>
     <t xml:space="preserve">6.22916221618652</t>
@@ -4334,25 +4334,25 @@
     <t xml:space="preserve">6.28672409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44229793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58075761795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58698129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65387678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63365268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57764673233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61031723022461</t>
+    <t xml:space="preserve">6.44229745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5807580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65387725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63365316390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57764720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61031770706177</t>
   </si>
   <si>
     <t xml:space="preserve">6.37540149688721</t>
@@ -4361,37 +4361,37 @@
     <t xml:space="preserve">6.48274660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44074201583862</t>
+    <t xml:space="preserve">6.44074153900146</t>
   </si>
   <si>
     <t xml:space="preserve">6.20893716812134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09381294250488</t>
+    <t xml:space="preserve">6.09381341934204</t>
   </si>
   <si>
     <t xml:space="preserve">6.0331392288208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92112636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59009265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48119115829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23382949829102</t>
+    <t xml:space="preserve">5.92112684249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26961088180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59009313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48119068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23382902145386</t>
   </si>
   <si>
     <t xml:space="preserve">6.19649124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18248987197876</t>
+    <t xml:space="preserve">6.18249034881592</t>
   </si>
   <si>
     <t xml:space="preserve">6.10003566741943</t>
@@ -4403,22 +4403,22 @@
     <t xml:space="preserve">6.45629930496216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52164030075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67876958847046</t>
+    <t xml:space="preserve">6.52163982391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67877006530762</t>
   </si>
   <si>
     <t xml:space="preserve">6.85612297058105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8499002456665</t>
+    <t xml:space="preserve">6.84989976882935</t>
   </si>
   <si>
     <t xml:space="preserve">6.85767889022827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07081413269043</t>
+    <t xml:space="preserve">7.0708155632019</t>
   </si>
   <si>
     <t xml:space="preserve">7.10348510742188</t>
@@ -4427,67 +4427,67 @@
     <t xml:space="preserve">7.13459968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09726238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19060611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15326881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31039762496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49241781234741</t>
+    <t xml:space="preserve">7.09726142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19060659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15326929092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49241876602173</t>
   </si>
   <si>
     <t xml:space="preserve">7.52820014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57954025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6339898109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74289131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91480016708374</t>
+    <t xml:space="preserve">7.57953977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63399124145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74289178848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91480159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.90892314910889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91228055953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93243503570557</t>
+    <t xml:space="preserve">7.91228151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93243551254272</t>
   </si>
   <si>
     <t xml:space="preserve">7.87029218673706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83502244949341</t>
+    <t xml:space="preserve">7.83502197265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.7728796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73761081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69562101364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71409702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73928880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68554449081421</t>
+    <t xml:space="preserve">7.73760938644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69562149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7140965461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73928928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68554496765137</t>
   </si>
   <si>
     <t xml:space="preserve">7.6351580619812</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">7.65867185592651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71073770523071</t>
+    <t xml:space="preserve">7.71073722839355</t>
   </si>
   <si>
     <t xml:space="preserve">7.69394159317017</t>
@@ -4505,28 +4505,28 @@
     <t xml:space="preserve">7.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79471445083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48064184188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50415420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52934741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66371011734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56965589523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58477163314819</t>
+    <t xml:space="preserve">7.79471302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48064088821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50415468215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52934789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66371059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56965684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58477210998535</t>
   </si>
   <si>
     <t xml:space="preserve">7.58645248413086</t>
@@ -4535,67 +4535,67 @@
     <t xml:space="preserve">7.53774499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64691495895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54446411132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59484958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67210817337036</t>
+    <t xml:space="preserve">7.64691591262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54446363449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5948486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6721076965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.79807329177856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78463649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7795991897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85685634613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90052366256714</t>
+    <t xml:space="preserve">7.78463745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77959823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85685682296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90052509307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.02145099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12558174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11550426483154</t>
+    <t xml:space="preserve">8.12558269500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11550521850586</t>
   </si>
   <si>
     <t xml:space="preserve">8.09535121917725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11046695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01977252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92403745651245</t>
+    <t xml:space="preserve">8.11046600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01977157592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92403841018677</t>
   </si>
   <si>
     <t xml:space="preserve">8.04496479034424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08191299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13230133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18100643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28513717651367</t>
+    <t xml:space="preserve">8.0819149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13230037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18100547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28513813018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.31536960601807</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">8.34560108184814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2767391204834</t>
+    <t xml:space="preserve">8.27674007415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.37247371673584</t>
@@ -4619,7 +4619,7 @@
     <t xml:space="preserve">8.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54042625427246</t>
+    <t xml:space="preserve">8.54042720794678</t>
   </si>
   <si>
     <t xml:space="preserve">8.5698184967041</t>
@@ -4628,28 +4628,28 @@
     <t xml:space="preserve">8.69998168945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56562042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70838069915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74197101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60340785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63280200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61180782318115</t>
+    <t xml:space="preserve">8.56561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7083797454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74197006225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60340976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6328010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61180686950684</t>
   </si>
   <si>
     <t xml:space="preserve">8.50263690948486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49423885345459</t>
+    <t xml:space="preserve">8.49423980712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.39094734191895</t>
@@ -4676,10 +4676,10 @@
     <t xml:space="preserve">8.45644950866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51103591918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46064853668213</t>
+    <t xml:space="preserve">8.51103496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46064949035645</t>
   </si>
   <si>
     <t xml:space="preserve">8.51523399353027</t>
@@ -4694,19 +4694,19 @@
     <t xml:space="preserve">7.80143260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99793815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54950189590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52094984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43193483352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73425149917603</t>
+    <t xml:space="preserve">7.99793863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54950284957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52095031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43193578720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73425054550171</t>
   </si>
   <si>
     <t xml:space="preserve">7.63179922103882</t>
@@ -4715,16 +4715,16 @@
     <t xml:space="preserve">7.5528621673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51591110229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60660648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7241735458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78295755386353</t>
+    <t xml:space="preserve">7.51591157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60660696029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72417306900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78295707702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.81150960922241</t>
@@ -4733,31 +4733,31 @@
     <t xml:space="preserve">7.80983018875122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74096918106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075609207153</t>
+    <t xml:space="preserve">7.74096870422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075704574585</t>
   </si>
   <si>
     <t xml:space="preserve">7.92739677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93915462493896</t>
+    <t xml:space="preserve">7.93915414810181</t>
   </si>
   <si>
     <t xml:space="preserve">8.09366989135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0264892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772411346436</t>
+    <t xml:space="preserve">8.02648830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18772506713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.21795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14909553527832</t>
+    <t xml:space="preserve">8.149094581604</t>
   </si>
   <si>
     <t xml:space="preserve">8.21291732788086</t>
@@ -4766,22 +4766,22 @@
     <t xml:space="preserve">8.17260932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19780158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26834297180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17092895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89212703704834</t>
+    <t xml:space="preserve">8.19780254364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26834201812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89212656021118</t>
   </si>
   <si>
     <t xml:space="preserve">8.19444274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09703063964844</t>
+    <t xml:space="preserve">8.09702968597412</t>
   </si>
   <si>
     <t xml:space="preserve">8.3808708190918</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">8.39766693115234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34056282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36575508117676</t>
+    <t xml:space="preserve">8.34056186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36575603485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.13565921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14741611480713</t>
+    <t xml:space="preserve">8.14741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.18436622619629</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">8.2532262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27338027954102</t>
+    <t xml:space="preserve">8.27338123321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895992279053</t>
@@ -4826,37 +4826,37 @@
     <t xml:space="preserve">8.77136325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67898750305176</t>
+    <t xml:space="preserve">8.67898845672607</t>
   </si>
   <si>
     <t xml:space="preserve">8.67478942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64539813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92252159118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98970127105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90572452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98130416870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96450996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17025184631348</t>
+    <t xml:space="preserve">8.6453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92252063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98970222473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90572547912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98130321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96450901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17025089263916</t>
   </si>
   <si>
     <t xml:space="preserve">9.19124603271484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28781890869141</t>
+    <t xml:space="preserve">9.28781986236572</t>
   </si>
   <si>
     <t xml:space="preserve">9.38859176635742</t>
@@ -4865,16 +4865,16 @@
     <t xml:space="preserve">9.49776268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42638111114502</t>
+    <t xml:space="preserve">9.39698886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4263801574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.40538597106934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30461502075195</t>
+    <t xml:space="preserve">9.30461406707764</t>
   </si>
   <si>
     <t xml:space="preserve">9.33400630950928</t>
@@ -4883,55 +4883,55 @@
     <t xml:space="preserve">9.14925765991211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.035888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01909446716309</t>
+    <t xml:space="preserve">9.03588962554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01909351348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.04848480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06947898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20384311676025</t>
+    <t xml:space="preserve">9.06947994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20384216308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.34660339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35500049591064</t>
+    <t xml:space="preserve">9.35500144958496</t>
   </si>
   <si>
     <t xml:space="preserve">9.27942180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24583148956299</t>
+    <t xml:space="preserve">9.24583053588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25002956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25842666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48936367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48096466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52295303344727</t>
+    <t xml:space="preserve">9.25842761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43058013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48096561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52295398712158</t>
   </si>
   <si>
     <t xml:space="preserve">9.64891815185547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60693073272705</t>
+    <t xml:space="preserve">9.60692977905273</t>
   </si>
   <si>
     <t xml:space="preserve">9.67411231994629</t>
@@ -4940,7 +4940,7 @@
     <t xml:space="preserve">9.63632297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930553436279</t>
+    <t xml:space="preserve">9.69930458068848</t>
   </si>
   <si>
     <t xml:space="preserve">9.70770263671875</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">10.0394096374512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1779718399048</t>
+    <t xml:space="preserve">10.1779708862305</t>
   </si>
   <si>
     <t xml:space="preserve">10.0520076751709</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">9.94703674316406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93863773345947</t>
+    <t xml:space="preserve">9.93863868713379</t>
   </si>
   <si>
     <t xml:space="preserve">9.98062705993652</t>
@@ -4973,13 +4973,13 @@
     <t xml:space="preserve">9.73289585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83366680145264</t>
+    <t xml:space="preserve">9.83366775512695</t>
   </si>
   <si>
     <t xml:space="preserve">9.85886096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83786678314209</t>
+    <t xml:space="preserve">9.83786582946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.93024063110352</t>
@@ -4988,19 +4988,19 @@
     <t xml:space="preserve">9.87565517425537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7916784286499</t>
+    <t xml:space="preserve">9.79167938232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.76648616790771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82526969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97222805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9260425567627</t>
+    <t xml:space="preserve">9.825270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97222900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92604160308838</t>
   </si>
   <si>
     <t xml:space="preserve">9.91344547271729</t>
@@ -5009,7 +5009,7 @@
     <t xml:space="preserve">10.0268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1653747558594</t>
+    <t xml:space="preserve">10.1653757095337</t>
   </si>
   <si>
     <t xml:space="preserve">10.194766998291</t>
@@ -5018,13 +5018,13 @@
     <t xml:space="preserve">10.1359834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1401824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1443815231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2199592590332</t>
+    <t xml:space="preserve">10.1401815414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.144380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2199602127075</t>
   </si>
   <si>
     <t xml:space="preserve">10.0981941223145</t>
@@ -5036,19 +5036,19 @@
     <t xml:space="preserve">10.1317844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2157621383667</t>
+    <t xml:space="preserve">10.2157611846924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2241592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2115631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.303936958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2535514831543</t>
+    <t xml:space="preserve">10.2115621566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3039379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.25355052948</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905689239502</t>
@@ -5057,31 +5057,31 @@
     <t xml:space="preserve">10.3291292190552</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4173059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3333292007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.245153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3963117599487</t>
+    <t xml:space="preserve">10.4173049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3333282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2451524734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913408279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3963108062744</t>
   </si>
   <si>
     <t xml:space="preserve">10.434100151062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4676914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3921127319336</t>
+    <t xml:space="preserve">10.4676904678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5222768783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3921136856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3207321166992</t>
@@ -5096,13 +5096,13 @@
     <t xml:space="preserve">10.1275863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2283573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2367563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2955389022827</t>
+    <t xml:space="preserve">10.2283582687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2367553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.295539855957</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695737838745</t>
@@ -5120,22 +5120,22 @@
     <t xml:space="preserve">9.26682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37179660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24163246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96870708465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46417045593262</t>
+    <t xml:space="preserve">9.37179565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24163341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96870803833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46417140960693</t>
   </si>
   <si>
     <t xml:space="preserve">9.53135299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58173656463623</t>
+    <t xml:space="preserve">9.58173751831055</t>
   </si>
   <si>
     <t xml:space="preserve">9.65311717987061</t>
@@ -5150,25 +5150,25 @@
     <t xml:space="preserve">9.63212394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67831134796143</t>
+    <t xml:space="preserve">9.67831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">9.69090747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9890251159668</t>
+    <t xml:space="preserve">9.98902416229248</t>
   </si>
   <si>
     <t xml:space="preserve">9.87985515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84817504882812</t>
+    <t xml:space="preserve">9.84817409515381</t>
   </si>
   <si>
     <t xml:space="preserve">9.73050308227539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82554531097412</t>
+    <t xml:space="preserve">9.8255443572998</t>
   </si>
   <si>
     <t xml:space="preserve">9.81649398803711</t>
@@ -5180,46 +5180,46 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71239948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78028678894043</t>
+    <t xml:space="preserve">9.73955535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71239852905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75313091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78028774261475</t>
   </si>
   <si>
     <t xml:space="preserve">9.72597694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65808963775635</t>
+    <t xml:space="preserve">9.65809059143066</t>
   </si>
   <si>
     <t xml:space="preserve">9.92511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0020513534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0744647979736</t>
+    <t xml:space="preserve">10.0020523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0744657516479</t>
   </si>
   <si>
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0925674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0337314605713</t>
+    <t xml:space="preserve">10.092568397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0337333679199</t>
   </si>
   <si>
     <t xml:space="preserve">10.069938659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0654144287109</t>
+    <t xml:space="preserve">10.0654134750366</t>
   </si>
   <si>
     <t xml:space="preserve">10.1378259658813</t>
@@ -5231,10 +5231,10 @@
     <t xml:space="preserve">10.1785583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.151403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1151971817017</t>
+    <t xml:space="preserve">10.1514043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.115198135376</t>
   </si>
   <si>
     <t xml:space="preserve">10.142352104187</t>
@@ -5252,13 +5252,13 @@
     <t xml:space="preserve">10.2736015319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2147655487061</t>
+    <t xml:space="preserve">10.2147645950317</t>
   </si>
   <si>
     <t xml:space="preserve">10.2102384567261</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2011890411377</t>
+    <t xml:space="preserve">10.2011880874634</t>
   </si>
   <si>
     <t xml:space="preserve">10.4455814361572</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">10.9434213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9253177642822</t>
+    <t xml:space="preserve">10.9253187179565</t>
   </si>
   <si>
     <t xml:space="preserve">10.9615240097046</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">10.9751024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1063508987427</t>
+    <t xml:space="preserve">11.106351852417</t>
   </si>
   <si>
     <t xml:space="preserve">11.133505821228</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">10.8393278121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7669153213501</t>
+    <t xml:space="preserve">10.7669143676758</t>
   </si>
   <si>
     <t xml:space="preserve">10.7171306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5315723419189</t>
+    <t xml:space="preserve">10.5315732955933</t>
   </si>
   <si>
     <t xml:space="preserve">10.4908399581909</t>
@@ -5327,16 +5327,16 @@
     <t xml:space="preserve">10.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858812332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.66282081604</t>
+    <t xml:space="preserve">10.5858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6628217697144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7261819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1787643432617</t>
+    <t xml:space="preserve">11.178765296936</t>
   </si>
   <si>
     <t xml:space="preserve">11.7173357009888</t>
@@ -5351,7 +5351,7 @@
     <t xml:space="preserve">11.4231586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005289077759</t>
+    <t xml:space="preserve">11.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141063690186</t>
@@ -5360,10 +5360,10 @@
     <t xml:space="preserve">11.3869514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4865188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6313467025757</t>
+    <t xml:space="preserve">11.486517906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6313457489014</t>
   </si>
   <si>
     <t xml:space="preserve">11.5815620422363</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">11.595139503479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6901817321777</t>
+    <t xml:space="preserve">11.7625932693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6901807785034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8576364517212</t>
@@ -5384,43 +5384,43 @@
     <t xml:space="preserve">12.0160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9979372024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567722320557</t>
+    <t xml:space="preserve">11.9979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567712783813</t>
   </si>
   <si>
     <t xml:space="preserve">12.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2785367965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3328475952148</t>
+    <t xml:space="preserve">12.2785358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3328466415405</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003023147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3781061172485</t>
+    <t xml:space="preserve">12.500301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3781051635742</t>
   </si>
   <si>
     <t xml:space="preserve">12.5093536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3962078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4052591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3102188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554754257202</t>
+    <t xml:space="preserve">12.3962087631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4052600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3102178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554763793945</t>
   </si>
   <si>
     <t xml:space="preserve">12.2875881195068</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">12.3826313018799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6451292037964</t>
+    <t xml:space="preserve">12.6451282501221</t>
   </si>
   <si>
     <t xml:space="preserve">12.6722831726074</t>
@@ -5474,7 +5474,7 @@
     <t xml:space="preserve">13.2244319915771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.514084815979</t>
+    <t xml:space="preserve">13.5140838623047</t>
   </si>
   <si>
     <t xml:space="preserve">13.7539520263672</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">13.7336559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6259603500366</t>
+    <t xml:space="preserve">13.6259593963623</t>
   </si>
   <si>
     <t xml:space="preserve">13.5369930267334</t>
@@ -5513,19 +5513,19 @@
     <t xml:space="preserve">13.5791349411011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5978660583496</t>
+    <t xml:space="preserve">13.5978651046753</t>
   </si>
   <si>
     <t xml:space="preserve">13.5042161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4199323654175</t>
+    <t xml:space="preserve">13.4199314117432</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620733261108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4339790344238</t>
+    <t xml:space="preserve">13.4339799880981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2794580459595</t>
@@ -5534,16 +5534,16 @@
     <t xml:space="preserve">13.1343011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4246139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9563684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.666054725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7550230026245</t>
+    <t xml:space="preserve">13.424614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9563674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7550220489502</t>
   </si>
   <si>
     <t xml:space="preserve">12.8205757141113</t>
@@ -5552,16 +5552,16 @@
     <t xml:space="preserve">12.7222452163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9329566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0500183105469</t>
+    <t xml:space="preserve">12.9329557418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0500173568726</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001779556274</t>
+    <t xml:space="preserve">12.9001789093018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7831172943115</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">13.1951732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0359697341919</t>
+    <t xml:space="preserve">13.0359706878662</t>
   </si>
   <si>
     <t xml:space="preserve">13.1670789718628</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">13.2045392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2888221740723</t>
+    <t xml:space="preserve">13.2888231277466</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654104232788</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">13.4386615753174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4714393615723</t>
+    <t xml:space="preserve">13.4714384078979</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777894973755</t>
@@ -5600,10 +5600,10 @@
     <t xml:space="preserve">13.382472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4995336532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4808044433594</t>
+    <t xml:space="preserve">13.499532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4808034896851</t>
   </si>
   <si>
     <t xml:space="preserve">13.5182638168335</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">13.8038930892944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8413534164429</t>
+    <t xml:space="preserve">13.8413524627686</t>
   </si>
   <si>
     <t xml:space="preserve">13.808575630188</t>
@@ -5630,13 +5630,13 @@
     <t xml:space="preserve">13.4573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1623964309692</t>
+    <t xml:space="preserve">13.1623973846436</t>
   </si>
   <si>
     <t xml:space="preserve">12.8486709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1483497619629</t>
+    <t xml:space="preserve">13.1483488082886</t>
   </si>
   <si>
     <t xml:space="preserve">13.0172395706177</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">13.1389837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1015243530273</t>
+    <t xml:space="preserve">13.101523399353</t>
   </si>
   <si>
     <t xml:space="preserve">13.1904907226562</t>
@@ -5663,13 +5663,13 @@
     <t xml:space="preserve">13.9350023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.949049949646</t>
+    <t xml:space="preserve">13.9490509033203</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0146045684814</t>
+    <t xml:space="preserve">14.0146036148071</t>
   </si>
   <si>
     <t xml:space="preserve">14.047381401062</t>
@@ -5684,10 +5684,10 @@
     <t xml:space="preserve">14.314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3611068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1410312652588</t>
+    <t xml:space="preserve">14.3611059188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1410303115845</t>
   </si>
   <si>
     <t xml:space="preserve">13.9911918640137</t>
@@ -5696,25 +5696,25 @@
     <t xml:space="preserve">14.1223001480103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9865102767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019023895264</t>
+    <t xml:space="preserve">13.9865093231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019033432007</t>
   </si>
   <si>
     <t xml:space="preserve">13.9818267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752387046814</t>
+    <t xml:space="preserve">13.7523860931396</t>
   </si>
   <si>
     <t xml:space="preserve">13.836669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8881778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0005559921265</t>
+    <t xml:space="preserve">13.8881769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0005569458008</t>
   </si>
   <si>
     <t xml:space="preserve">14.3657884597778</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">14.403247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.286187171936</t>
+    <t xml:space="preserve">14.2861862182617</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815046310425</t>
@@ -5735,19 +5735,19 @@
     <t xml:space="preserve">14.4453907012939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4641199111938</t>
+    <t xml:space="preserve">14.4641208648682</t>
   </si>
   <si>
     <t xml:space="preserve">14.3517408370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1129360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.033332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460359573364</t>
+    <t xml:space="preserve">14.1129350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0333337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460350036621</t>
   </si>
   <si>
     <t xml:space="preserve">14.0567464828491</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">14.5624523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6561012268066</t>
+    <t xml:space="preserve">14.6561002731323</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982431411743</t>
@@ -5783,13 +5783,13 @@
     <t xml:space="preserve">15.1009349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9136362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5999116897583</t>
+    <t xml:space="preserve">14.9136371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7684812545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5999126434326</t>
   </si>
   <si>
     <t xml:space="preserve">14.4500732421875</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">14.4219779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3376941680908</t>
+    <t xml:space="preserve">14.3376951217651</t>
   </si>
   <si>
     <t xml:space="preserve">14.3002347946167</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">13.5229454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8554000854492</t>
+    <t xml:space="preserve">13.8554010391235</t>
   </si>
   <si>
     <t xml:space="preserve">13.9089336395264</t>
@@ -6543,6 +6543,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.3400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7600002288818</t>
   </si>
 </sst>
 </file>
@@ -48629,7 +48632,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>1349</v>
+        <v>849</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48655,7 +48658,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1607" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -48681,7 +48684,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1608" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -48707,7 +48710,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G1609" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -48759,7 +48762,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1611" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48785,7 +48788,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48837,7 +48840,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G1614" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48863,7 +48866,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1615" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48889,7 +48892,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G1616" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48941,7 +48944,7 @@
         <v>9.70400047302246</v>
       </c>
       <c r="G1618" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48967,7 +48970,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G1619" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48993,7 +48996,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1620" t="s">
-        <v>1257</v>
+        <v>1359</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -72245,7 +72248,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6916898148</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>838185</v>
@@ -72266,6 +72269,32 @@
         <v>2171</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6916898148</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>1470327</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>17.875</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>17.6399993896484</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>17.7800006866455</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>17.7600002288818</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>2177</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="2178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="2179">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19125890731812</t>
+    <t xml:space="preserve">5.19125938415527</t>
   </si>
   <si>
     <t xml:space="preserve">MB.MI</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">4.95858907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.837721824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81052589416504</t>
+    <t xml:space="preserve">4.83772134780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8105263710022</t>
   </si>
   <si>
     <t xml:space="preserve">4.92534971237183</t>
@@ -65,28 +65,28 @@
     <t xml:space="preserve">4.97974061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91930770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73196220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50533533096313</t>
+    <t xml:space="preserve">4.91930675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73196268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50533580780029</t>
   </si>
   <si>
     <t xml:space="preserve">4.59900808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4146842956543</t>
+    <t xml:space="preserve">4.41468524932861</t>
   </si>
   <si>
     <t xml:space="preserve">4.65944242477417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67455053329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52346611022949</t>
+    <t xml:space="preserve">4.67455005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52346563339233</t>
   </si>
   <si>
     <t xml:space="preserve">4.59598636627197</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">4.52648687362671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27870941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45094537734985</t>
+    <t xml:space="preserve">4.27870893478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45094585418701</t>
   </si>
   <si>
     <t xml:space="preserve">4.3119478225708</t>
@@ -107,91 +107,91 @@
     <t xml:space="preserve">4.19410228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00373554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09136486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98862767219543</t>
+    <t xml:space="preserve">4.00373601913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09136438369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98862791061401</t>
   </si>
   <si>
     <t xml:space="preserve">3.61695981025696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41450715065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6713502407074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47796177864075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54443860054016</t>
+    <t xml:space="preserve">3.41450667381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67135000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47796154022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54443883895874</t>
   </si>
   <si>
     <t xml:space="preserve">3.64717626571655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68041491508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74991297721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64113402366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61091637611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75595712661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6622850894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62300300598145</t>
+    <t xml:space="preserve">3.680415391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74991416931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64113330841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61091613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75595784187317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62300276756287</t>
   </si>
   <si>
     <t xml:space="preserve">3.67437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76804399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78315305709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93725848197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08834266662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1034517288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02488708496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006398200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9614315032959</t>
+    <t xml:space="preserve">3.76804423332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78315258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93725824356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08834314346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10345125198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0248875617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96143174171448</t>
   </si>
   <si>
     <t xml:space="preserve">3.97351884841919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38446855545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42979288101196</t>
+    <t xml:space="preserve">4.03395223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38446807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42979335784912</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173112869263</t>
@@ -203,43 +203,43 @@
     <t xml:space="preserve">4.03697443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07323455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09438610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01884412765503</t>
+    <t xml:space="preserve">4.07323408126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0943865776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01884460449219</t>
   </si>
   <si>
     <t xml:space="preserve">3.99164915084839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87984657287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90402007102966</t>
+    <t xml:space="preserve">3.8798463344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90401935577393</t>
   </si>
   <si>
     <t xml:space="preserve">3.82545590400696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79221749305725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83149933815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75897860527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79523944854736</t>
+    <t xml:space="preserve">3.79221725463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8314995765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75897908210754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79523897171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.60487294197083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81336903572083</t>
+    <t xml:space="preserve">3.81336879730225</t>
   </si>
   <si>
     <t xml:space="preserve">3.85567331314087</t>
@@ -248,85 +248,85 @@
     <t xml:space="preserve">3.77408766746521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97049713134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04301786422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97654032707214</t>
+    <t xml:space="preserve">3.97049736976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04301738739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97654056549072</t>
   </si>
   <si>
     <t xml:space="preserve">4.23036241531372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2333836555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36935901641846</t>
+    <t xml:space="preserve">4.23338460922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36935949325562</t>
   </si>
   <si>
     <t xml:space="preserve">4.38748979568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39655494689941</t>
+    <t xml:space="preserve">4.39655542373657</t>
   </si>
   <si>
     <t xml:space="preserve">4.33612155914307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21223258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05208253860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88589000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8526508808136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8043041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87078166007996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8979766368866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93423700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92215085029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90704202651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97956228256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01582288742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21827507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31497001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30590438842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35727262496948</t>
+    <t xml:space="preserve">4.21223211288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05208301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88588976860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85265111923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80430459976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87078142166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89797639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93423748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9221498966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90704226493835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97956252098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01582193374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21827554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30590391159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35727310180664</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13366842269897</t>
+    <t xml:space="preserve">4.13366746902466</t>
   </si>
   <si>
     <t xml:space="preserve">4.10647296905518</t>
@@ -335,70 +335,70 @@
     <t xml:space="preserve">4.00071382522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98560523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91610646247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52026605606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38731145858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48098421096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46889686584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6078941822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8073263168335</t>
+    <t xml:space="preserve">3.98560547828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91610598564148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70156717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52026557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38731098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48098373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46889662742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60789394378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80732560157776</t>
   </si>
   <si>
     <t xml:space="preserve">3.85869431495667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83452081680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2090322971344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79929113388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96125364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0639910697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11535930633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1455762386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01322674751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91653227806091</t>
+    <t xml:space="preserve">3.8345205783844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20903205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79929089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96125316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06399130821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11535978317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14557647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0132269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91653251647949</t>
   </si>
   <si>
     <t xml:space="preserve">2.84763813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94554042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19694495201111</t>
+    <t xml:space="preserve">2.94554090499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19694519042969</t>
   </si>
   <si>
     <t xml:space="preserve">3.44472360610962</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">3.47191858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57767772674561</t>
+    <t xml:space="preserve">3.57767796516418</t>
   </si>
   <si>
     <t xml:space="preserve">3.5263090133667</t>
@@ -419,34 +419,34 @@
     <t xml:space="preserve">3.55350399017334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59580779075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58976411819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61998128890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53537368774414</t>
+    <t xml:space="preserve">3.59580731391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58976483345032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61998105049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5353741645813</t>
   </si>
   <si>
     <t xml:space="preserve">3.65926337242126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61393809318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78617405891418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7136538028717</t>
+    <t xml:space="preserve">3.61393785476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78617382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71365332603455</t>
   </si>
   <si>
     <t xml:space="preserve">3.40846347808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42054963111877</t>
+    <t xml:space="preserve">3.42055010795593</t>
   </si>
   <si>
     <t xml:space="preserve">3.71969699859619</t>
@@ -455,34 +455,34 @@
     <t xml:space="preserve">3.96747541427612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94028043746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90099811553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308498382568</t>
+    <t xml:space="preserve">3.9402801990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90099883079529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308546066284</t>
   </si>
   <si>
     <t xml:space="preserve">3.84962940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81639099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6955235004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72876191139221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92517185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8949556350708</t>
+    <t xml:space="preserve">3.8163914680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80128192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69552326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72876262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9251720905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89495468139648</t>
   </si>
   <si>
     <t xml:space="preserve">3.95236682891846</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">4.0490608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14273309707642</t>
+    <t xml:space="preserve">4.14273357391357</t>
   </si>
   <si>
     <t xml:space="preserve">4.07927751541138</t>
@@ -500,58 +500,58 @@
     <t xml:space="preserve">4.19108009338379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15481996536255</t>
+    <t xml:space="preserve">4.15482044219971</t>
   </si>
   <si>
     <t xml:space="preserve">4.0581259727478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7317841053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78919553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68645834922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77106523513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77710866928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4960925579071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54141759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47494077682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49911427497864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49004936218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49307107925415</t>
+    <t xml:space="preserve">3.73178386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78919529914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68645858764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77106547355652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77710890769958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49609208106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54141736030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47494053840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49911499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49004864692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49307084083557</t>
   </si>
   <si>
     <t xml:space="preserve">3.68343687057495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78013157844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65321946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74387121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87380266189575</t>
+    <t xml:space="preserve">3.78013038635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65321969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74387097358704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87380337715149</t>
   </si>
   <si>
     <t xml:space="preserve">3.99467062950134</t>
@@ -560,61 +560,61 @@
     <t xml:space="preserve">4.10949516296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15784215927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23640584945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84358620643616</t>
+    <t xml:space="preserve">4.15784168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23640537261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84358668327332</t>
   </si>
   <si>
     <t xml:space="preserve">4.00977849960327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14575529098511</t>
+    <t xml:space="preserve">4.14575481414795</t>
   </si>
   <si>
     <t xml:space="preserve">4.13971138000488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25453567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26964378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20618867874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11251640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94632387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9936044216156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06294918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00305938720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96208310127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90849924087524</t>
+    <t xml:space="preserve">4.25453615188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26964426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20618915557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11251592636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94632411003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99360418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06294870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00305986404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96208333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90849900245667</t>
   </si>
   <si>
     <t xml:space="preserve">3.7950267791748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95578002929688</t>
+    <t xml:space="preserve">3.95577955245972</t>
   </si>
   <si>
     <t xml:space="preserve">4.10392475128174</t>
@@ -623,28 +623,28 @@
     <t xml:space="preserve">4.23315668106079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23945999145508</t>
+    <t xml:space="preserve">4.23946142196655</t>
   </si>
   <si>
     <t xml:space="preserve">4.05979585647583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46325349807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67759084701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80682373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67128705978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69650268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74693584442139</t>
+    <t xml:space="preserve">4.46325397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6775918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80682420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67128753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69650363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74693536758423</t>
   </si>
   <si>
     <t xml:space="preserve">4.79106378555298</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">4.95181655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89508056640625</t>
+    <t xml:space="preserve">4.89508008956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.91714429855347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98964071273804</t>
+    <t xml:space="preserve">4.98964023590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.95496892929077</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.939208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00224876403809</t>
+    <t xml:space="preserve">5.00224828720093</t>
   </si>
   <si>
     <t xml:space="preserve">4.99909687042236</t>
@@ -689,55 +689,55 @@
     <t xml:space="preserve">5.1377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1440896987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16300106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92975234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98333644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98018455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86356067657471</t>
+    <t xml:space="preserve">5.16930627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14408922195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16300201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92975282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98333692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98018503189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86355972290039</t>
   </si>
   <si>
     <t xml:space="preserve">5.05898475646973</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04007244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00540065765381</t>
+    <t xml:space="preserve">5.04007339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00540113449097</t>
   </si>
   <si>
     <t xml:space="preserve">5.08420085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01170539855957</t>
+    <t xml:space="preserve">5.01170492172241</t>
   </si>
   <si>
     <t xml:space="preserve">5.08735322952271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37103509902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53809070587158</t>
+    <t xml:space="preserve">5.37103462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5380916595459</t>
   </si>
   <si>
     <t xml:space="preserve">5.36157846450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29538583755493</t>
+    <t xml:space="preserve">5.29538536071777</t>
   </si>
   <si>
     <t xml:space="preserve">5.15354585647583</t>
@@ -746,37 +746,37 @@
     <t xml:space="preserve">5.01485681533813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13463354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92344808578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9675760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91084003448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.055832862854</t>
+    <t xml:space="preserve">5.13463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92344856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943273544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96757650375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91084051132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05583333969116</t>
   </si>
   <si>
     <t xml:space="preserve">5.17561006546021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14724159240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11887359619141</t>
+    <t xml:space="preserve">5.14724111557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11887311935425</t>
   </si>
   <si>
     <t xml:space="preserve">5.07159328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02431297302246</t>
+    <t xml:space="preserve">5.0243124961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.97388029098511</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">4.82888793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69335126876831</t>
+    <t xml:space="preserve">4.69335079193115</t>
   </si>
   <si>
     <t xml:space="preserve">4.72802305221558</t>
@@ -803,49 +803,49 @@
     <t xml:space="preserve">5.17245721817017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21658563613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22604179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30169057846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24810600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23549842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25125789642334</t>
+    <t xml:space="preserve">5.21658515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22604131698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30168962478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24810552597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23549747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2512583732605</t>
   </si>
   <si>
     <t xml:space="preserve">5.26071453094482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32375383377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33636283874512</t>
+    <t xml:space="preserve">5.32375431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33636140823364</t>
   </si>
   <si>
     <t xml:space="preserve">5.27962636947632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33951425552368</t>
+    <t xml:space="preserve">5.339515209198</t>
   </si>
   <si>
     <t xml:space="preserve">5.31745100021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35212182998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32690620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19767332077026</t>
+    <t xml:space="preserve">5.35212278366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32690668106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19767427444458</t>
   </si>
   <si>
     <t xml:space="preserve">5.20712947845459</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">4.8509521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38364219665527</t>
+    <t xml:space="preserve">5.38364315032959</t>
   </si>
   <si>
     <t xml:space="preserve">5.46559476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38994741439819</t>
+    <t xml:space="preserve">5.38994646072388</t>
   </si>
   <si>
     <t xml:space="preserve">5.35527420043945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.563307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57906818389893</t>
+    <t xml:space="preserve">5.56330728530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57906770706177</t>
   </si>
   <si>
     <t xml:space="preserve">5.59798097610474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70830106735229</t>
+    <t xml:space="preserve">5.70830059051514</t>
   </si>
   <si>
     <t xml:space="preserve">5.78710031509399</t>
@@ -896,37 +896,37 @@
     <t xml:space="preserve">5.75242853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73666954040527</t>
+    <t xml:space="preserve">5.73666858673096</t>
   </si>
   <si>
     <t xml:space="preserve">5.72090816497803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79340410232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76188516616821</t>
+    <t xml:space="preserve">5.79340362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7618842124939</t>
   </si>
   <si>
     <t xml:space="preserve">5.78394937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62319612503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6421070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68938875198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73036479949951</t>
+    <t xml:space="preserve">5.62319660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64210796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68938779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73036432266235</t>
   </si>
   <si>
     <t xml:space="preserve">5.7681884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73982048034668</t>
+    <t xml:space="preserve">5.73981952667236</t>
   </si>
   <si>
     <t xml:space="preserve">5.71460390090942</t>
@@ -941,16 +941,16 @@
     <t xml:space="preserve">5.32060194015503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34266662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25441026687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27332162857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36473035812378</t>
+    <t xml:space="preserve">5.34266710281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27332210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36473083496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.41516304016113</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">5.39625072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44983577728271</t>
+    <t xml:space="preserve">5.44983530044556</t>
   </si>
   <si>
     <t xml:space="preserve">5.37418651580811</t>
@@ -971,25 +971,25 @@
     <t xml:space="preserve">5.29223489761353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21028232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35842609405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34581756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48135566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46874761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44668292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754781723022</t>
+    <t xml:space="preserve">5.21028184890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35842752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34581851959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48135471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46874713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44668340682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754734039307</t>
   </si>
   <si>
     <t xml:space="preserve">5.59482717514038</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">5.52548360824585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56015491485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59167575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66101980209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71775531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362833023071</t>
+    <t xml:space="preserve">5.56015539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59167623519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66102027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7177562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362785339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.67678022384644</t>
@@ -1019,19 +1019,19 @@
     <t xml:space="preserve">5.49081134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50972318649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56961154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60743570327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58221864700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55700302124023</t>
+    <t xml:space="preserve">5.5097222328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56961107254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60743618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58221912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55700349807739</t>
   </si>
   <si>
     <t xml:space="preserve">5.54439496994019</t>
@@ -1040,52 +1040,52 @@
     <t xml:space="preserve">5.67993259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67047643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61058712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48450708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53493881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52863597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47505140304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38049030303955</t>
+    <t xml:space="preserve">5.67047595977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61058807373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48450660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53493928909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52863550186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4750509262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38049077987671</t>
   </si>
   <si>
     <t xml:space="preserve">5.43407487869263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33005857467651</t>
+    <t xml:space="preserve">5.3300576210022</t>
   </si>
   <si>
     <t xml:space="preserve">5.50026702880859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56645965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50657081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51602792739868</t>
+    <t xml:space="preserve">5.56646013259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5065712928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51602745056152</t>
   </si>
   <si>
     <t xml:space="preserve">5.58537149429321</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66732454299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65471601486206</t>
+    <t xml:space="preserve">5.66732358932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65471649169922</t>
   </si>
   <si>
     <t xml:space="preserve">5.69253969192505</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">5.75873279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71145248413086</t>
+    <t xml:space="preserve">5.71145296096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.7997088432312</t>
@@ -1106,175 +1106,175 @@
     <t xml:space="preserve">5.74612426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77449226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74927711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77764511108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78079652786255</t>
+    <t xml:space="preserve">5.7744927406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74927663803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77764463424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78079700469971</t>
   </si>
   <si>
     <t xml:space="preserve">5.77134084701538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81862163543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91633319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97622203826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93209266662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01404523849487</t>
+    <t xml:space="preserve">5.8186206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91633367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97622156143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93209409713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01404571533203</t>
   </si>
   <si>
     <t xml:space="preserve">6.07708644866943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05187082290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03295803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10860586166382</t>
+    <t xml:space="preserve">6.05187034606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03295755386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10860633850098</t>
   </si>
   <si>
     <t xml:space="preserve">6.10230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23153495788574</t>
+    <t xml:space="preserve">6.2315354347229</t>
   </si>
   <si>
     <t xml:space="preserve">6.21577453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2252311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21892690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20001411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23178100585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13353872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885705947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20558309555054</t>
+    <t xml:space="preserve">6.22523021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21892642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2000150680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23178052902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1335391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20558261871338</t>
   </si>
   <si>
     <t xml:space="preserve">6.1695613861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0975170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22850561141968</t>
+    <t xml:space="preserve">6.09751749038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22850513458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.34966993331909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28745174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33329725265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29399919509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1990327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22195672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30382442474365</t>
+    <t xml:space="preserve">6.28745079040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33329582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29399871826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19903373718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2219557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30382394790649</t>
   </si>
   <si>
     <t xml:space="preserve">6.2809009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28417539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25470399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24815320968628</t>
+    <t xml:space="preserve">6.28417682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25470304489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24815368652344</t>
   </si>
   <si>
     <t xml:space="preserve">6.1237154006958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15646171569824</t>
+    <t xml:space="preserve">6.15646266937256</t>
   </si>
   <si>
     <t xml:space="preserve">6.18593406677246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24160385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26452779769897</t>
+    <t xml:space="preserve">6.24160432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26452684402466</t>
   </si>
   <si>
     <t xml:space="preserve">6.26125288009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19575881958008</t>
+    <t xml:space="preserve">6.19575834274292</t>
   </si>
   <si>
     <t xml:space="preserve">6.1466383934021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27107667922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41843891143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39879083633423</t>
+    <t xml:space="preserve">6.27107715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41843795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39879179000854</t>
   </si>
   <si>
     <t xml:space="preserve">6.40206480026245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39224052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41188955307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49375772476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51995468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5756254196167</t>
+    <t xml:space="preserve">6.39224195480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41189002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49375677108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51995420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57562637329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.53305435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5297794342041</t>
+    <t xml:space="preserve">6.52977895736694</t>
   </si>
   <si>
     <t xml:space="preserve">6.48720741271973</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">6.36604404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41319990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47607374191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51406097412109</t>
+    <t xml:space="preserve">6.41319942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51406049728394</t>
   </si>
   <si>
     <t xml:space="preserve">6.45642566680908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26780271530151</t>
+    <t xml:space="preserve">6.26780223846436</t>
   </si>
   <si>
     <t xml:space="preserve">6.36997318267822</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">6.32019662857056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36473417282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41581916809082</t>
+    <t xml:space="preserve">6.3647346496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41581869125366</t>
   </si>
   <si>
     <t xml:space="preserve">6.45511531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47214508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44594621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4669041633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47869443893433</t>
+    <t xml:space="preserve">6.47214365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46690511703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47869348526001</t>
   </si>
   <si>
     <t xml:space="preserve">6.40010118484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46166610717773</t>
+    <t xml:space="preserve">6.46166563034058</t>
   </si>
   <si>
     <t xml:space="preserve">6.47476434707642</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">6.51013040542603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41975021362305</t>
+    <t xml:space="preserve">6.41974925994873</t>
   </si>
   <si>
     <t xml:space="preserve">6.32674694061279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21016693115234</t>
+    <t xml:space="preserve">6.21016788482666</t>
   </si>
   <si>
     <t xml:space="preserve">6.31102848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44463682174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46559619903564</t>
+    <t xml:space="preserve">6.44463634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46559524536133</t>
   </si>
   <si>
     <t xml:space="preserve">6.45904636383057</t>
@@ -1367,73 +1367,73 @@
     <t xml:space="preserve">6.39748096466064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42498874664307</t>
+    <t xml:space="preserve">6.42498970031738</t>
   </si>
   <si>
     <t xml:space="preserve">6.45773553848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40664958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738313674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37390279769897</t>
+    <t xml:space="preserve">6.40665054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738361358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37390327453613</t>
   </si>
   <si>
     <t xml:space="preserve">6.25732326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21671628952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2468433380127</t>
+    <t xml:space="preserve">6.21671772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24684429168701</t>
   </si>
   <si>
     <t xml:space="preserve">6.25339365005493</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27828121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35294532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34508466720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41712856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39355182647705</t>
+    <t xml:space="preserve">6.27828073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35294485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34508514404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4171290397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39355134963989</t>
   </si>
   <si>
     <t xml:space="preserve">6.54811811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63457012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66076755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79503202438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84415197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70661354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69351530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59199857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67386674880981</t>
+    <t xml:space="preserve">6.63457107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66076803207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79503011703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84415102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70661401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69351482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59199905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67386627197266</t>
   </si>
   <si>
     <t xml:space="preserve">6.55925226211548</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">6.69679021835327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72953701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54942798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46428489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51537036895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56907653808594</t>
+    <t xml:space="preserve">6.72953653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54942846298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46428537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51537084579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56907510757446</t>
   </si>
   <si>
     <t xml:space="preserve">6.5219202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20754766464233</t>
+    <t xml:space="preserve">6.20754671096802</t>
   </si>
   <si>
     <t xml:space="preserve">6.01499462127686</t>
@@ -1469,46 +1469,46 @@
     <t xml:space="preserve">5.915442943573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95343017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81327199935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58011293411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24085235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03127098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38624906539917</t>
+    <t xml:space="preserve">5.95342969894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81327247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58011245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24085187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0312705039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38624954223633</t>
   </si>
   <si>
     <t xml:space="preserve">5.2840781211853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42161655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32861423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19238615036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35874223709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23823261260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12689208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37708044052124</t>
+    <t xml:space="preserve">5.4216160774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32861375808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19238567352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35874176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23823213577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12689161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3770809173584</t>
   </si>
   <si>
     <t xml:space="preserve">5.3050365447998</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">5.40327787399292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34826326370239</t>
+    <t xml:space="preserve">5.34826231002808</t>
   </si>
   <si>
     <t xml:space="preserve">5.28276824951172</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">5.38755941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52378749847412</t>
+    <t xml:space="preserve">5.52378702163696</t>
   </si>
   <si>
     <t xml:space="preserve">5.33254384994507</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">5.21727418899536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18321657180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21465396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18845653533936</t>
+    <t xml:space="preserve">5.18321704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21465444564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18845701217651</t>
   </si>
   <si>
     <t xml:space="preserve">5.25133085250854</t>
@@ -1568,91 +1568,91 @@
     <t xml:space="preserve">5.34040355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26835918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17928743362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2015552520752</t>
+    <t xml:space="preserve">5.26835870742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17928695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20155572891235</t>
   </si>
   <si>
     <t xml:space="preserve">5.27097988128662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2893180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3377833366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32468461990356</t>
+    <t xml:space="preserve">5.28931760787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33778285980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32468509674072</t>
   </si>
   <si>
     <t xml:space="preserve">5.35612201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51330852508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57618236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62857866287231</t>
+    <t xml:space="preserve">5.51330757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57618284225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62857818603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.73205900192261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68097305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81851100921631</t>
+    <t xml:space="preserve">5.68097352981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81851243972778</t>
   </si>
   <si>
     <t xml:space="preserve">5.74646806716919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68752241134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78052473068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68490362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75956583023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75563716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76742553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70848035812378</t>
+    <t xml:space="preserve">5.68752288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78052520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68490314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75956678390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75563669204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76742649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7084813117981</t>
   </si>
   <si>
     <t xml:space="preserve">5.5958309173584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44912338256836</t>
+    <t xml:space="preserve">5.44912385940552</t>
   </si>
   <si>
     <t xml:space="preserve">5.56439399719238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50282955169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51985788345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61023998260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758958816528</t>
+    <t xml:space="preserve">5.50282907485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51985740661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61023950576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49759006500244</t>
   </si>
   <si>
     <t xml:space="preserve">5.43340444564819</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">5.42816543579102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39541816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41899633407593</t>
+    <t xml:space="preserve">5.39541912078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41899681091309</t>
   </si>
   <si>
     <t xml:space="preserve">5.25002098083496</t>
@@ -1676,88 +1676,88 @@
     <t xml:space="preserve">5.55522489547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73598957061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68621301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90627384185791</t>
+    <t xml:space="preserve">5.73598909378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68621349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771028518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90627288818359</t>
   </si>
   <si>
     <t xml:space="preserve">5.9364013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89710521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91282272338867</t>
+    <t xml:space="preserve">5.89710426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91282320022583</t>
   </si>
   <si>
     <t xml:space="preserve">6.01368474960327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03333377838135</t>
+    <t xml:space="preserve">6.03333282470703</t>
   </si>
   <si>
     <t xml:space="preserve">6.09620666503906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00844478607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00713539123535</t>
+    <t xml:space="preserve">6.00844573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00713443756104</t>
   </si>
   <si>
     <t xml:space="preserve">5.96390819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07524967193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06476974487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00451564788818</t>
+    <t xml:space="preserve">6.07524919509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06477069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00451517105103</t>
   </si>
   <si>
     <t xml:space="preserve">5.63512754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46353244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4884204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48056077957153</t>
+    <t xml:space="preserve">5.46353197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48841953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48056125640869</t>
   </si>
   <si>
     <t xml:space="preserve">5.38886880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13737106323242</t>
+    <t xml:space="preserve">5.13737058639526</t>
   </si>
   <si>
     <t xml:space="preserve">5.18059682846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07187604904175</t>
+    <t xml:space="preserve">5.07187652587891</t>
   </si>
   <si>
     <t xml:space="preserve">5.02865076065063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11379289627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05484819412231</t>
+    <t xml:space="preserve">5.03520059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11379241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05484867095947</t>
   </si>
   <si>
     <t xml:space="preserve">5.00638246536255</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">5.15963888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06663751602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07842636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90683078765869</t>
+    <t xml:space="preserve">5.06663703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07842683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90683126449585</t>
   </si>
   <si>
     <t xml:space="preserve">5.09545469284058</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">5.11248302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07711696624756</t>
+    <t xml:space="preserve">5.07711601257324</t>
   </si>
   <si>
     <t xml:space="preserve">5.19500637054443</t>
@@ -1796,28 +1796,28 @@
     <t xml:space="preserve">5.13606119155884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11641359329224</t>
+    <t xml:space="preserve">5.11641311645508</t>
   </si>
   <si>
     <t xml:space="preserve">5.13868093490601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15309000015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14915990829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08104562759399</t>
+    <t xml:space="preserve">5.15308952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14916038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08104610443115</t>
   </si>
   <si>
     <t xml:space="preserve">5.15818977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690242767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987808227539</t>
+    <t xml:space="preserve">5.0369029045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987855911255</t>
   </si>
   <si>
     <t xml:space="preserve">5.08011960983276</t>
@@ -1826,31 +1826,31 @@
     <t xml:space="preserve">5.117760181427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34500026702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36730480194092</t>
+    <t xml:space="preserve">5.34499979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36730527877808</t>
   </si>
   <si>
     <t xml:space="preserve">5.39100551605225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44258689880371</t>
+    <t xml:space="preserve">5.44258642196655</t>
   </si>
   <si>
     <t xml:space="preserve">5.44119262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47604560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3770637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38821697235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22650098800659</t>
+    <t xml:space="preserve">5.47604513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37706470489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38821649551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22650051116943</t>
   </si>
   <si>
     <t xml:space="preserve">5.22231864929199</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">5.10242509841919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07733201980591</t>
+    <t xml:space="preserve">5.07733154296875</t>
   </si>
   <si>
     <t xml:space="preserve">5.24462413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26553583145142</t>
+    <t xml:space="preserve">5.26553630828857</t>
   </si>
   <si>
     <t xml:space="preserve">5.31293535232544</t>
@@ -1877,61 +1877,61 @@
     <t xml:space="preserve">5.27668857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37288188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25577640533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12751960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04944944381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14146089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09127235412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08709001541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38961029052734</t>
+    <t xml:space="preserve">5.37288236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25577688217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12751865386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0494499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14145994186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09127187728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08708953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38961124420166</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985229492188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36312294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33524036407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33802890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40494585037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34639406204224</t>
+    <t xml:space="preserve">5.36312341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33524084091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33802938461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40494632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34639453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.33942317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46210384368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46907472610474</t>
+    <t xml:space="preserve">5.46210479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46907520294189</t>
   </si>
   <si>
     <t xml:space="preserve">5.49138021469116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50671529769897</t>
+    <t xml:space="preserve">5.50671577453613</t>
   </si>
   <si>
     <t xml:space="preserve">5.48859262466431</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">5.50253343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55969190597534</t>
+    <t xml:space="preserve">5.55969142913818</t>
   </si>
   <si>
     <t xml:space="preserve">5.48998641967773</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">5.4481635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45931625366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29481220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14424896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11218452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28505277633667</t>
+    <t xml:space="preserve">5.45931577682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29481172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14424800872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11218404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28505325317383</t>
   </si>
   <si>
     <t xml:space="preserve">5.3979754447937</t>
@@ -1973,28 +1973,28 @@
     <t xml:space="preserve">5.40355205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49835109710693</t>
+    <t xml:space="preserve">5.49835157394409</t>
   </si>
   <si>
     <t xml:space="preserve">5.52623319625854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62521505355835</t>
+    <t xml:space="preserve">5.62521457672119</t>
   </si>
   <si>
     <t xml:space="preserve">5.59036254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78971910476685</t>
+    <t xml:space="preserve">5.78971862792969</t>
   </si>
   <si>
     <t xml:space="preserve">5.80366039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77717208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79808330535889</t>
+    <t xml:space="preserve">5.77717256546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79808378219604</t>
   </si>
   <si>
     <t xml:space="preserve">5.73953151702881</t>
@@ -2009,49 +2009,49 @@
     <t xml:space="preserve">5.91797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98071193695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14939785003662</t>
+    <t xml:space="preserve">5.98071146011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14939737319946</t>
   </si>
   <si>
     <t xml:space="preserve">6.02532291412354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07969236373901</t>
+    <t xml:space="preserve">6.07969331741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.08945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20376777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10060453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03787040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12430429458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10339260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18982696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21631526947021</t>
+    <t xml:space="preserve">6.20376825332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03786993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12430477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10339212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18982791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21631574630737</t>
   </si>
   <si>
     <t xml:space="preserve">6.26510858535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39894437789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35990762710571</t>
+    <t xml:space="preserve">6.3989429473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35990810394287</t>
   </si>
   <si>
     <t xml:space="preserve">6.24001502990723</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">6.23583316802979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17728137969971</t>
+    <t xml:space="preserve">6.17728090286255</t>
   </si>
   <si>
     <t xml:space="preserve">6.22468090057373</t>
@@ -2072,25 +2072,25 @@
     <t xml:space="preserve">6.35293769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42264270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4561014175415</t>
+    <t xml:space="preserve">6.42264366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45610189437866</t>
   </si>
   <si>
     <t xml:space="preserve">6.5188364982605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42543125152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44076633453369</t>
+    <t xml:space="preserve">6.4254322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44076681137085</t>
   </si>
   <si>
     <t xml:space="preserve">6.47840738296509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52162504196167</t>
+    <t xml:space="preserve">6.52162408828735</t>
   </si>
   <si>
     <t xml:space="preserve">6.46446657180786</t>
@@ -2099,79 +2099,79 @@
     <t xml:space="preserve">6.48537731170654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57878303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63175821304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6707935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69867515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67915868759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6220006942749</t>
+    <t xml:space="preserve">6.57878255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63175868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67079401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69867563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67915821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62200021743774</t>
   </si>
   <si>
     <t xml:space="preserve">6.54392957687378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52441310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56205272674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58714723587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62478828430176</t>
+    <t xml:space="preserve">6.52441215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56205368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58714771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62478876113892</t>
   </si>
   <si>
     <t xml:space="preserve">6.41706705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26789665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34875583648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20237445831299</t>
+    <t xml:space="preserve">6.267897605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34875535964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20237350463867</t>
   </si>
   <si>
     <t xml:space="preserve">6.06435775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22049713134766</t>
+    <t xml:space="preserve">6.22049760818481</t>
   </si>
   <si>
     <t xml:space="preserve">6.18146276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16612768173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06575155258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99465227127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01556444168091</t>
+    <t xml:space="preserve">6.16612672805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06575202941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99465322494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01556396484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.95980072021484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91937065124512</t>
+    <t xml:space="preserve">5.91937112808228</t>
   </si>
   <si>
     <t xml:space="preserve">5.84269523620605</t>
@@ -2180,10 +2180,10 @@
     <t xml:space="preserve">5.83433055877686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76601934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7325611114502</t>
+    <t xml:space="preserve">5.76601982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73256158828735</t>
   </si>
   <si>
     <t xml:space="preserve">5.88173007965088</t>
@@ -2195,73 +2195,73 @@
     <t xml:space="preserve">5.87894201278687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96816539764404</t>
+    <t xml:space="preserve">5.96816492080688</t>
   </si>
   <si>
     <t xml:space="preserve">5.96677112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.938889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97374105453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94307041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9416766166687</t>
+    <t xml:space="preserve">5.93888854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97374153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94307136535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94167709350586</t>
   </si>
   <si>
     <t xml:space="preserve">6.07132911682129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16334009170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14382171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19122123718262</t>
+    <t xml:space="preserve">6.16333961486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14382266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19122219085693</t>
   </si>
   <si>
     <t xml:space="preserve">6.17031002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29577922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33760261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31947946548462</t>
+    <t xml:space="preserve">6.29577970504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3376030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31947898864746</t>
   </si>
   <si>
     <t xml:space="preserve">6.23862075805664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30972051620483</t>
+    <t xml:space="preserve">6.30972003936768</t>
   </si>
   <si>
     <t xml:space="preserve">6.47422504425049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60248231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57041788101196</t>
+    <t xml:space="preserve">6.60248327255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57041835784912</t>
   </si>
   <si>
     <t xml:space="preserve">6.51186561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49095487594604</t>
+    <t xml:space="preserve">6.49095439910889</t>
   </si>
   <si>
     <t xml:space="preserve">6.55229473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54114198684692</t>
+    <t xml:space="preserve">6.54114151000977</t>
   </si>
   <si>
     <t xml:space="preserve">6.54671859741211</t>
@@ -2276,37 +2276,37 @@
     <t xml:space="preserve">6.53277683258057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54950714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41288423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44355583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51465320587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4895601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50350046157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33481502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31111478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32087326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15915679931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10478782653809</t>
+    <t xml:space="preserve">6.54950666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41288471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44355440139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51465368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48956060409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50350141525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33481407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31111431121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32087373733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15915632247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10478687286377</t>
   </si>
   <si>
     <t xml:space="preserve">6.03647518157959</t>
@@ -2315,25 +2315,25 @@
     <t xml:space="preserve">6.08666324615479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92494678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91379451751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94446516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8064489364624</t>
+    <t xml:space="preserve">5.92494773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91379499435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94446468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80644845962524</t>
   </si>
   <si>
     <t xml:space="preserve">5.93052434921265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97652959823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06714630126953</t>
+    <t xml:space="preserve">5.97653007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06714677810669</t>
   </si>
   <si>
     <t xml:space="preserve">6.11315202713013</t>
@@ -2342,40 +2342,40 @@
     <t xml:space="preserve">6.04344654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13963937759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19261598587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28044462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35712051391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58296632766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59830045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68055295944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6303653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66382360458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72655773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66242837905884</t>
+    <t xml:space="preserve">6.11872816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13963890075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19261646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28044414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35712003707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58296537399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59829998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68055200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63036489486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66382312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72655725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66242933273315</t>
   </si>
   <si>
     <t xml:space="preserve">6.63454627990723</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">6.76141023635864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95100879669189</t>
+    <t xml:space="preserve">6.95101022720337</t>
   </si>
   <si>
     <t xml:space="preserve">6.89803266525269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90779161453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94682645797729</t>
+    <t xml:space="preserve">6.90779209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94682598114014</t>
   </si>
   <si>
     <t xml:space="preserve">7.04371643066406</t>
@@ -2402,118 +2402,118 @@
     <t xml:space="preserve">6.95379734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98446846008301</t>
+    <t xml:space="preserve">6.98446798324585</t>
   </si>
   <si>
     <t xml:space="preserve">6.95658493041992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76419830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84645080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8157811164856</t>
+    <t xml:space="preserve">6.76419925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8464503288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81578063964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.83390378952026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79347515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80462837219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0332612991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19009780883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27025842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37481832504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40269947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38178777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36087703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43058109283447</t>
+    <t xml:space="preserve">6.79347610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80462741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03326177597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19009733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27025938034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37481737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40269899368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38178730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36087656021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43058156967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.50377225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55953598022461</t>
+    <t xml:space="preserve">7.55953550338745</t>
   </si>
   <si>
     <t xml:space="preserve">7.55256509780884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58044672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44103717803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42361068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48286008834839</t>
+    <t xml:space="preserve">7.58044767379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44103813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4236102104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48286151885986</t>
   </si>
   <si>
     <t xml:space="preserve">7.6431827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59438896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51422739028931</t>
+    <t xml:space="preserve">7.59438943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51422691345215</t>
   </si>
   <si>
     <t xml:space="preserve">7.2737455368042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42012548446655</t>
+    <t xml:space="preserve">7.42012596130371</t>
   </si>
   <si>
     <t xml:space="preserve">7.35390472412109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51857423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48940420150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46752595901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5258674621582</t>
+    <t xml:space="preserve">7.5185751914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48940563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46752738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52586698532104</t>
   </si>
   <si>
     <t xml:space="preserve">7.49669694900513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47482013702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52951335906982</t>
+    <t xml:space="preserve">7.47481966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52951288223267</t>
   </si>
   <si>
     <t xml:space="preserve">7.40189409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33261632919312</t>
+    <t xml:space="preserve">7.33261442184448</t>
   </si>
   <si>
     <t xml:space="preserve">7.29250717163086</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">7.35449266433716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32532215118408</t>
+    <t xml:space="preserve">7.3253231048584</t>
   </si>
   <si>
     <t xml:space="preserve">7.34720039367676</t>
@@ -2531,103 +2531,103 @@
     <t xml:space="preserve">7.22687435150146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3727240562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38366222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24437618255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31438398361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28229713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3581395149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21958065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15686702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22979164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1641583442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18457746505737</t>
+    <t xml:space="preserve">7.37272453308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38366365432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24437570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3143835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28229761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35813999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28521490097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21958160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1568660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22979068756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16415929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18457698822021</t>
   </si>
   <si>
     <t xml:space="preserve">7.25021028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.261878490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21812343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1802020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08539867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15832424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11019468307495</t>
+    <t xml:space="preserve">7.26187705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21812295913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874240875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18020248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08539915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15832471847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11019372940063</t>
   </si>
   <si>
     <t xml:space="preserve">7.05768775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0781078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99643039703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93809032440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97309541702271</t>
+    <t xml:space="preserve">7.07810688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93809127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97309494018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.77328014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98622131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9337158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75286197662354</t>
+    <t xml:space="preserve">6.98622179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93371486663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75286149978638</t>
   </si>
   <si>
     <t xml:space="preserve">6.5720067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71931505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8053674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98038768768311</t>
+    <t xml:space="preserve">6.71931552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98038673400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.86954116821289</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">7.00372362136841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04164552688599</t>
+    <t xml:space="preserve">7.04164409637451</t>
   </si>
   <si>
     <t xml:space="preserve">7.0606050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06206321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00518226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03289318084717</t>
+    <t xml:space="preserve">7.0620641708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00518131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03289413452148</t>
   </si>
   <si>
     <t xml:space="preserve">6.99351406097412</t>
@@ -2657,28 +2657,28 @@
     <t xml:space="preserve">6.86370706558228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4524097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42178106307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38677835464478</t>
+    <t xml:space="preserve">6.45240879058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42178153991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38677740097046</t>
   </si>
   <si>
     <t xml:space="preserve">6.23363494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97256278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76253890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71003246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63564872741699</t>
+    <t xml:space="preserve">5.97256231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76253843307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71003293991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63564968109131</t>
   </si>
   <si>
     <t xml:space="preserve">5.39937162399292</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">5.28415012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5228123664856</t>
+    <t xml:space="preserve">4.52281284332275</t>
   </si>
   <si>
     <t xml:space="preserve">4.21215200424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3317494392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52228093147278</t>
+    <t xml:space="preserve">4.33174896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5222806930542</t>
   </si>
   <si>
     <t xml:space="preserve">3.77605986595154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33850932121277</t>
+    <t xml:space="preserve">3.33850955963135</t>
   </si>
   <si>
     <t xml:space="preserve">3.25537490844727</t>
@@ -2714,85 +2714,85 @@
     <t xml:space="preserve">3.0424337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10150289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17661547660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61854147911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90440845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01087856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76439189910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62802219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66667175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64917039871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77460217475891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70605158805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97149896621704</t>
+    <t xml:space="preserve">3.10150265693665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17661595344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6185417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90440773963928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01087808609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76439166069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62802195549011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66667199134827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64917016029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77460193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70605206489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9714994430542</t>
   </si>
   <si>
     <t xml:space="preserve">4.05171680450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05900859832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04150676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87232112884521</t>
+    <t xml:space="preserve">4.05900955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04150724411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87232136726379</t>
   </si>
   <si>
     <t xml:space="preserve">3.57989144325256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64771175384521</t>
+    <t xml:space="preserve">3.64771199226379</t>
   </si>
   <si>
     <t xml:space="preserve">3.69292545318604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56239008903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51571702957153</t>
+    <t xml:space="preserve">3.56238985061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51571774482727</t>
   </si>
   <si>
     <t xml:space="preserve">3.73959708213806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82419037818909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02254581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85627722740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79939603805542</t>
+    <t xml:space="preserve">3.82419013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545554161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02254676818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85627746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.799396276474</t>
   </si>
   <si>
     <t xml:space="preserve">3.76585054397583</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">3.74834847450256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78918671607971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85336065292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68271589279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56311893463135</t>
+    <t xml:space="preserve">3.78918695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607594490051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.853360414505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68271636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56311917304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.80960536003113</t>
@@ -2825,49 +2825,49 @@
     <t xml:space="preserve">3.74980688095093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69730091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168393135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78481149673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256332397461</t>
+    <t xml:space="preserve">3.69730138778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78481125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921059608459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256237030029</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862258911133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25590658187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60011339187622</t>
+    <t xml:space="preserve">4.25590705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60011291503906</t>
   </si>
   <si>
     <t xml:space="preserve">4.69929122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95452928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95307016372681</t>
+    <t xml:space="preserve">4.95452976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95307064056396</t>
   </si>
   <si>
     <t xml:space="preserve">5.18351364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34540748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17330455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07996034622192</t>
+    <t xml:space="preserve">5.3454065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17330408096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07996082305908</t>
   </si>
   <si>
     <t xml:space="preserve">4.86410188674927</t>
@@ -2876,43 +2876,43 @@
     <t xml:space="preserve">4.96473836898804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03766393661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16455268859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1397590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23164367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12079811096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9734902381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99682569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71095895767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75033855438232</t>
+    <t xml:space="preserve">5.03766345977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16455316543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13975858688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23164415359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12079858779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97348976135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.996826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71095943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75033903121948</t>
   </si>
   <si>
     <t xml:space="preserve">4.55927515029907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76200723648071</t>
+    <t xml:space="preserve">4.76200675964355</t>
   </si>
   <si>
     <t xml:space="preserve">4.65991163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71533489227295</t>
+    <t xml:space="preserve">4.71533441543579</t>
   </si>
   <si>
     <t xml:space="preserve">4.91952514648438</t>
@@ -2924,37 +2924,37 @@
     <t xml:space="preserve">4.92535972595215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93119287490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88014554977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79701089859009</t>
+    <t xml:space="preserve">4.93119382858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88014602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79701137542725</t>
   </si>
   <si>
     <t xml:space="preserve">4.9297342300415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05078983306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13830041885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14559316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16601181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13246631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25206327438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25498008728027</t>
+    <t xml:space="preserve">5.05079030990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1382999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14559268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16601228713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13246583938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2520637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25498056411743</t>
   </si>
   <si>
     <t xml:space="preserve">5.31623697280884</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">5.22435140609741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16309499740601</t>
+    <t xml:space="preserve">5.16309452056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.12663221359253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07850217819214</t>
+    <t xml:space="preserve">5.07850170135498</t>
   </si>
   <si>
     <t xml:space="preserve">5.05954122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92244148254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94286108016968</t>
+    <t xml:space="preserve">4.92244243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94286060333252</t>
   </si>
   <si>
     <t xml:space="preserve">4.73283672332764</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">4.94723653793335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91369104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97786521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27248287200928</t>
+    <t xml:space="preserve">4.9136905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97786569595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27248239517212</t>
   </si>
   <si>
     <t xml:space="preserve">5.28706693649292</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">5.29435968399048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20247364044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1149640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24622917175293</t>
+    <t xml:space="preserve">5.20247411727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11496448516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24622964859009</t>
   </si>
   <si>
     <t xml:space="preserve">5.12809085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09746170043945</t>
+    <t xml:space="preserve">5.09746217727661</t>
   </si>
   <si>
     <t xml:space="preserve">5.24768733978271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27685737609863</t>
+    <t xml:space="preserve">5.27685785293579</t>
   </si>
   <si>
     <t xml:space="preserve">5.44458532333374</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">5.47813129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42416667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31040382385254</t>
+    <t xml:space="preserve">5.42416620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31040334701538</t>
   </si>
   <si>
     <t xml:space="preserve">5.33519792556763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32061243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22726917266846</t>
+    <t xml:space="preserve">5.32061290740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22726821899414</t>
   </si>
   <si>
     <t xml:space="preserve">5.21414232254028</t>
@@ -3059,118 +3059,118 @@
     <t xml:space="preserve">5.39207935333252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28269147872925</t>
+    <t xml:space="preserve">5.28269195556641</t>
   </si>
   <si>
     <t xml:space="preserve">5.29873514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18643045425415</t>
+    <t xml:space="preserve">5.18643140792847</t>
   </si>
   <si>
     <t xml:space="preserve">5.08725261688232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89910554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89327144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87722826004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76054811477661</t>
+    <t xml:space="preserve">4.89910650253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89327192306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87722873687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76054763793945</t>
   </si>
   <si>
     <t xml:space="preserve">4.95161199569702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87576961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88452053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84368276596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92390060424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08871126174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20976638793945</t>
+    <t xml:space="preserve">4.8757700920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88452100753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84368371963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92390012741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08871173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20976686477661</t>
   </si>
   <si>
     <t xml:space="preserve">5.08579397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28560876846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23310232162476</t>
+    <t xml:space="preserve">5.28560924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23310327529907</t>
   </si>
   <si>
     <t xml:space="preserve">5.203932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0114107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02016162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84222459793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79992771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84951686859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74012994766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74596357345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78971862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76638221740723</t>
+    <t xml:space="preserve">5.01141119003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0201621055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84222412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79992818832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84951639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74012899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74596309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78971815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76638174057007</t>
   </si>
   <si>
     <t xml:space="preserve">4.64095115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4105076789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46884822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43967819213867</t>
+    <t xml:space="preserve">4.41050815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46884727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43967771530151</t>
   </si>
   <si>
     <t xml:space="preserve">4.59427881240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85680961608887</t>
+    <t xml:space="preserve">4.85680913925171</t>
   </si>
   <si>
     <t xml:space="preserve">5.3089451789856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1966404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20539093017578</t>
+    <t xml:space="preserve">5.19664001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20539140701294</t>
   </si>
   <si>
     <t xml:space="preserve">5.51605224609375</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">5.59626960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51459312438965</t>
+    <t xml:space="preserve">5.51459360122681</t>
   </si>
   <si>
     <t xml:space="preserve">5.58460187911987</t>
@@ -3188,16 +3188,16 @@
     <t xml:space="preserve">5.4985499382019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72899389266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75232887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70419836044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63710737228394</t>
+    <t xml:space="preserve">5.72899341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75232934951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70419931411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63710689544678</t>
   </si>
   <si>
     <t xml:space="preserve">5.45041942596436</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">5.46500492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54230499267578</t>
+    <t xml:space="preserve">5.54230451583862</t>
   </si>
   <si>
     <t xml:space="preserve">5.60210371017456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53209590911865</t>
+    <t xml:space="preserve">5.53209543228149</t>
   </si>
   <si>
     <t xml:space="preserve">5.48979902267456</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">5.4752140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34978246688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36145114898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53792953491211</t>
+    <t xml:space="preserve">5.34978294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36145067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53793001174927</t>
   </si>
   <si>
     <t xml:space="preserve">5.49271631240845</t>
@@ -3242,55 +3242,55 @@
     <t xml:space="preserve">5.42854166030884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39062118530273</t>
+    <t xml:space="preserve">5.39062166213989</t>
   </si>
   <si>
     <t xml:space="preserve">5.3789529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52042770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52480316162109</t>
+    <t xml:space="preserve">5.52042818069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52480268478394</t>
   </si>
   <si>
     <t xml:space="preserve">5.40228891372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42270755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62835693359375</t>
+    <t xml:space="preserve">5.42270803451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62835597991943</t>
   </si>
   <si>
     <t xml:space="preserve">5.61231327056885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50438356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46208763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51021862030029</t>
+    <t xml:space="preserve">5.50438404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46208667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51021814346313</t>
   </si>
   <si>
     <t xml:space="preserve">5.46937990188599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44750261306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38187026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47083854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40083074569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40520572662354</t>
+    <t xml:space="preserve">5.44750213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38186931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47083806991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40083026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40520620346069</t>
   </si>
   <si>
     <t xml:space="preserve">5.44896125793457</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">5.39499664306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.370201587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51167678833008</t>
+    <t xml:space="preserve">5.37020206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51167631149292</t>
   </si>
   <si>
     <t xml:space="preserve">5.7304515838623</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">5.97985553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17383623123169</t>
+    <t xml:space="preserve">6.17383575439453</t>
   </si>
   <si>
     <t xml:space="preserve">6.23071765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41740655899048</t>
+    <t xml:space="preserve">6.41740608215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.50637531280518</t>
@@ -3338,37 +3338,37 @@
     <t xml:space="preserve">6.53700304031372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57930040359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54429578781128</t>
+    <t xml:space="preserve">6.57929944992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54429531097412</t>
   </si>
   <si>
     <t xml:space="preserve">6.62159633636475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61430406570435</t>
+    <t xml:space="preserve">6.61430358886719</t>
   </si>
   <si>
     <t xml:space="preserve">6.58221626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53408575057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39552879333496</t>
+    <t xml:space="preserve">6.53408622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3955283164978</t>
   </si>
   <si>
     <t xml:space="preserve">6.28468227386475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5019998550415</t>
+    <t xml:space="preserve">6.50199937820435</t>
   </si>
   <si>
     <t xml:space="preserve">6.43490839004517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52679300308228</t>
+    <t xml:space="preserve">6.52679347991943</t>
   </si>
   <si>
     <t xml:space="preserve">6.61138677597046</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">6.85058069229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86516523361206</t>
+    <t xml:space="preserve">6.86516571044922</t>
   </si>
   <si>
     <t xml:space="preserve">6.9016284942627</t>
@@ -3395,52 +3395,52 @@
     <t xml:space="preserve">7.01976728439331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09415054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09706735610962</t>
+    <t xml:space="preserve">7.09414958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09706878662109</t>
   </si>
   <si>
     <t xml:space="preserve">6.87975072860718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84037208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77911424636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90016937255859</t>
+    <t xml:space="preserve">6.84037160873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77911329269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90016984939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.90600442886353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92058849334717</t>
+    <t xml:space="preserve">6.92058897018433</t>
   </si>
   <si>
     <t xml:space="preserve">6.93954944610596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89579391479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84912252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86079072952271</t>
+    <t xml:space="preserve">7.03580904006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8957953453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84912300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86078977584839</t>
   </si>
   <si>
     <t xml:space="preserve">6.77182197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80682611465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81849336624146</t>
+    <t xml:space="preserve">6.80682563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81849384307861</t>
   </si>
   <si>
     <t xml:space="preserve">6.80974292755127</t>
@@ -3449,19 +3449,19 @@
     <t xml:space="preserve">6.78640604019165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85203981399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84766340255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70910596847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64201498031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65805816650391</t>
+    <t xml:space="preserve">6.85203838348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84766387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7091064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.642014503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65805864334106</t>
   </si>
   <si>
     <t xml:space="preserve">6.64639043807983</t>
@@ -3470,127 +3470,127 @@
     <t xml:space="preserve">6.8359956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80828523635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82724475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85641574859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92788219451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78057241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90892028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94684171676636</t>
+    <t xml:space="preserve">6.80828428268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82724571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85641527175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92788124084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78057289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9089207649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9468412399292</t>
   </si>
   <si>
     <t xml:space="preserve">7.04018640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05477094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01393270492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08394145965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13352966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19770336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0591459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06643867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05331325531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08102369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12915468215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11748647689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14811515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21228933334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344533920288</t>
+    <t xml:space="preserve">7.05477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0139331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08394050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13353061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19770479202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06643915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08102464675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12915420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11748695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1481146812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2706298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30344676971436</t>
   </si>
   <si>
     <t xml:space="preserve">7.29979944229126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25604438781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26771211624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20791292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26333665847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25458526611328</t>
+    <t xml:space="preserve">7.25604391098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26771116256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20791339874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26333713531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25458574295044</t>
   </si>
   <si>
     <t xml:space="preserve">7.23270845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23562479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17582654953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22249889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27500486373901</t>
+    <t xml:space="preserve">7.23562526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17582702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22249937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28083992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27500534057617</t>
   </si>
   <si>
     <t xml:space="preserve">7.20062112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18311929702759</t>
+    <t xml:space="preserve">7.18311977386475</t>
   </si>
   <si>
     <t xml:space="preserve">7.19332838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1874942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36178636550903</t>
+    <t xml:space="preserve">7.18749475479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36178541183472</t>
   </si>
   <si>
     <t xml:space="preserve">7.1408224105835</t>
@@ -3599,61 +3599,61 @@
     <t xml:space="preserve">7.14957332611084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92350578308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165189743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1889533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20499610900879</t>
+    <t xml:space="preserve">6.92350625991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165237426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18895244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20499658584595</t>
   </si>
   <si>
     <t xml:space="preserve">7.14519882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09560918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86808347702026</t>
+    <t xml:space="preserve">7.09560871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86808300018311</t>
   </si>
   <si>
     <t xml:space="preserve">6.95559310913086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23416709899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31073713302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28667163848877</t>
+    <t xml:space="preserve">7.23416757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31073808670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28667259216309</t>
   </si>
   <si>
     <t xml:space="preserve">7.28813123703003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24145984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13207101821899</t>
+    <t xml:space="preserve">7.24145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13207197189331</t>
   </si>
   <si>
     <t xml:space="preserve">7.2108302116394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28375577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29615259170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19041109085083</t>
+    <t xml:space="preserve">7.2837553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29615211486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19041204452515</t>
   </si>
   <si>
     <t xml:space="preserve">7.27792119979858</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">7.27354574203491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17728519439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1714506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04601907730103</t>
+    <t xml:space="preserve">7.17728471755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17145109176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04601955413818</t>
   </si>
   <si>
     <t xml:space="preserve">7.09852647781372</t>
@@ -3677,109 +3677,109 @@
     <t xml:space="preserve">7.13644695281982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25166845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.279381275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11456871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24875116348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3654317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47846555709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33626270294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53680610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6133770942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68630170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5878529548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73734855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50398921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21520709991455</t>
+    <t xml:space="preserve">7.25166893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27938032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24875164031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47846651077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33626174926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53680515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61337757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68630218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58785343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73734903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50398969650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294237136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21520614624023</t>
   </si>
   <si>
     <t xml:space="preserve">7.38001680374146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41283321380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43106508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53315925598145</t>
+    <t xml:space="preserve">7.41283369064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43106412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53316020965576</t>
   </si>
   <si>
     <t xml:space="preserve">7.58056116104126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60608386993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55868339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52221965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64254665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67171764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77016544342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76651954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88684511184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8759069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8139214515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81756734848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89778518676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90507698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955474853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79204320907593</t>
+    <t xml:space="preserve">7.6060848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55868291854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52222061157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6425461769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67171812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77016496658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76652002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8868465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87590742111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81392097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81756830215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89778423309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90507745742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955331802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79204416275024</t>
   </si>
   <si>
     <t xml:space="preserve">7.74828863143921</t>
@@ -3791,52 +3791,52 @@
     <t xml:space="preserve">7.90313148498535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72266721725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72111225128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45352554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5639820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59976530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843252182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63865756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79034185409546</t>
+    <t xml:space="preserve">7.7226676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72111177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45352506637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56398248672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59976482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6386570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79034280776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.94591522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86034917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82534694671631</t>
+    <t xml:space="preserve">7.86034965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82534599304199</t>
   </si>
   <si>
     <t xml:space="preserve">7.80978870391846</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71488904953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76156091690063</t>
+    <t xml:space="preserve">7.71488857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76156044006348</t>
   </si>
   <si>
     <t xml:space="preserve">7.84868192672729</t>
@@ -3845,28 +3845,28 @@
     <t xml:space="preserve">7.80589914321899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52197790145874</t>
+    <t xml:space="preserve">7.52197742462158</t>
   </si>
   <si>
     <t xml:space="preserve">7.6495475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68999624252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81367683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86423921585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92646932601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0859317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10148906707764</t>
+    <t xml:space="preserve">7.68999719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81367778778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86423826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92646884918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08593273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10148811340332</t>
   </si>
   <si>
     <t xml:space="preserve">8.08204174041748</t>
@@ -3878,31 +3878,31 @@
     <t xml:space="preserve">8.07037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13260364532471</t>
+    <t xml:space="preserve">8.13260269165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.23761558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17538642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09759902954102</t>
+    <t xml:space="preserve">8.17538738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09759998321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.03536987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05092716217041</t>
+    <t xml:space="preserve">8.05092620849609</t>
   </si>
   <si>
     <t xml:space="preserve">8.02370071411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61532211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66043710708618</t>
+    <t xml:space="preserve">7.61532163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6604380607605</t>
   </si>
   <si>
     <t xml:space="preserve">7.77867412567139</t>
@@ -3911,16 +3911,16 @@
     <t xml:space="preserve">8.02759170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10926818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79811954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05870532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22983837127686</t>
+    <t xml:space="preserve">8.10926723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79812049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05870628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22983741760254</t>
   </si>
   <si>
     <t xml:space="preserve">8.20650005340576</t>
@@ -3932,31 +3932,31 @@
     <t xml:space="preserve">7.90702199935913</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07426452636719</t>
+    <t xml:space="preserve">8.07426357269287</t>
   </si>
   <si>
     <t xml:space="preserve">7.88368606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93813562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77556276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6728835105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67755031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26994800567627</t>
+    <t xml:space="preserve">7.93813753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77556228637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67288398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67755126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26994752883911</t>
   </si>
   <si>
     <t xml:space="preserve">7.29172849655151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25439119338989</t>
+    <t xml:space="preserve">7.25439167022705</t>
   </si>
   <si>
     <t xml:space="preserve">6.68654775619507</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">6.73477554321289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68499279022217</t>
+    <t xml:space="preserve">6.68499183654785</t>
   </si>
   <si>
     <t xml:space="preserve">6.12337207794189</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">6.31939458847046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35050916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61187219619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66165637969971</t>
+    <t xml:space="preserve">6.35050868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61187267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66165685653687</t>
   </si>
   <si>
     <t xml:space="preserve">7.10970783233643</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">7.2263879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06770324707031</t>
+    <t xml:space="preserve">7.06770372390747</t>
   </si>
   <si>
     <t xml:space="preserve">7.12993192672729</t>
@@ -4010,10 +4010,10 @@
     <t xml:space="preserve">7.02103090286255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05059003829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22949934005737</t>
+    <t xml:space="preserve">7.0505895614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22949886322021</t>
   </si>
   <si>
     <t xml:space="preserve">7.10659599304199</t>
@@ -4022,22 +4022,22 @@
     <t xml:space="preserve">7.17193746566772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30417442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11904287338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97902584075928</t>
+    <t xml:space="preserve">7.30417490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11904239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97902727127075</t>
   </si>
   <si>
     <t xml:space="preserve">6.89190483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03503179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02569770812988</t>
+    <t xml:space="preserve">7.03503274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02569818496704</t>
   </si>
   <si>
     <t xml:space="preserve">6.94946718215942</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">7.1128191947937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19527244567871</t>
+    <t xml:space="preserve">7.19527339935303</t>
   </si>
   <si>
     <t xml:space="preserve">7.18438339233398</t>
@@ -4061,88 +4061,88 @@
     <t xml:space="preserve">7.17971467971802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38196086883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38040542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47686195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88757514953613</t>
+    <t xml:space="preserve">7.16415882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38196134567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38040590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47686100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88757610321045</t>
   </si>
   <si>
     <t xml:space="preserve">7.74755907058716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50486469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48308372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60598754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.548424243927</t>
+    <t xml:space="preserve">7.50486326217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48308420181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60598659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54842519760132</t>
   </si>
   <si>
     <t xml:space="preserve">7.71955537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70088624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71022129058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52353429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44574689865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38974094390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43485546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26217079162598</t>
+    <t xml:space="preserve">7.70088672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71022176742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52353382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44574594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38973999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43485641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26217031478882</t>
   </si>
   <si>
     <t xml:space="preserve">7.34151220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46752738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41152048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46908235549927</t>
+    <t xml:space="preserve">7.41152095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46908330917358</t>
   </si>
   <si>
     <t xml:space="preserve">7.43174457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32906627655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4208550453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.534423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4986424446106</t>
+    <t xml:space="preserve">7.32906675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42085456848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442335128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49864149093628</t>
   </si>
   <si>
     <t xml:space="preserve">7.68532943725586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50797605514526</t>
+    <t xml:space="preserve">7.50797653198242</t>
   </si>
   <si>
     <t xml:space="preserve">7.01325225830078</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">6.96813678741455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95102310180664</t>
+    <t xml:space="preserve">6.95102262496948</t>
   </si>
   <si>
     <t xml:space="preserve">6.63054180145264</t>
@@ -4175,22 +4175,22 @@
     <t xml:space="preserve">6.56831216812134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71143913269043</t>
+    <t xml:space="preserve">6.71144008636475</t>
   </si>
   <si>
     <t xml:space="preserve">6.56675624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64765405654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60253858566284</t>
+    <t xml:space="preserve">6.64765357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60253810882568</t>
   </si>
   <si>
     <t xml:space="preserve">6.42362880706787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41896200180054</t>
+    <t xml:space="preserve">6.41896104812622</t>
   </si>
   <si>
     <t xml:space="preserve">6.38784694671631</t>
@@ -4202,10 +4202,10 @@
     <t xml:space="preserve">6.32406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45785474777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55586671829224</t>
+    <t xml:space="preserve">6.45785522460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55586624145508</t>
   </si>
   <si>
     <t xml:space="preserve">6.4905252456665</t>
@@ -4217,88 +4217,88 @@
     <t xml:space="preserve">6.3582878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05958652496338</t>
+    <t xml:space="preserve">6.05958700180054</t>
   </si>
   <si>
     <t xml:space="preserve">6.05491971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20115900039673</t>
+    <t xml:space="preserve">6.20115852355957</t>
   </si>
   <si>
     <t xml:space="preserve">6.33339595794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26027727127075</t>
+    <t xml:space="preserve">6.26027679443359</t>
   </si>
   <si>
     <t xml:space="preserve">6.2213830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24783086776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17937803268433</t>
+    <t xml:space="preserve">6.24783039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17937850952148</t>
   </si>
   <si>
     <t xml:space="preserve">6.24005270004272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35673236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50297069549561</t>
+    <t xml:space="preserve">6.3567328453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50297117233276</t>
   </si>
   <si>
     <t xml:space="preserve">6.54653167724609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55119848251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59787178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64921045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7021050453186</t>
+    <t xml:space="preserve">6.55119895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59787130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64921092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70210599899292</t>
   </si>
   <si>
     <t xml:space="preserve">6.65232229232788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64298725128174</t>
+    <t xml:space="preserve">6.6429877281189</t>
   </si>
   <si>
     <t xml:space="preserve">6.66010093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72544145584106</t>
+    <t xml:space="preserve">6.72544097900391</t>
   </si>
   <si>
     <t xml:space="preserve">6.77055788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77833604812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72233009338379</t>
+    <t xml:space="preserve">6.77833652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72233057022095</t>
   </si>
   <si>
     <t xml:space="preserve">6.69588184356689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44696426391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27427816390991</t>
+    <t xml:space="preserve">6.44696474075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27427864074707</t>
   </si>
   <si>
     <t xml:space="preserve">6.32250642776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2945032119751</t>
+    <t xml:space="preserve">6.29450273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.25872087478638</t>
@@ -4307,13 +4307,13 @@
     <t xml:space="preserve">6.17004442214966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15448665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21360492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15137577056885</t>
+    <t xml:space="preserve">6.15448713302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21360445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15137529373169</t>
   </si>
   <si>
     <t xml:space="preserve">6.07825565338135</t>
@@ -4340,28 +4340,28 @@
     <t xml:space="preserve">6.5807580947876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58698081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65387725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63365316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57764720916748</t>
+    <t xml:space="preserve">6.58698129653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65387678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63365268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57764673233032</t>
   </si>
   <si>
     <t xml:space="preserve">6.61031770706177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37540149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48274660110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44074153900146</t>
+    <t xml:space="preserve">6.37540102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48274612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44074201583862</t>
   </si>
   <si>
     <t xml:space="preserve">6.20893716812134</t>
@@ -4373,19 +4373,19 @@
     <t xml:space="preserve">6.0331392288208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92112684249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26961088180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59009313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23382902145386</t>
+    <t xml:space="preserve">5.92112636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26961183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59009265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48119115829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23382949829102</t>
   </si>
   <si>
     <t xml:space="preserve">6.19649124145508</t>
@@ -4394,52 +4394,52 @@
     <t xml:space="preserve">6.18249034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10003566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2836127281189</t>
+    <t xml:space="preserve">6.10003614425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28361320495605</t>
   </si>
   <si>
     <t xml:space="preserve">6.45629930496216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52163982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67877006530762</t>
+    <t xml:space="preserve">6.52164030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67876958847046</t>
   </si>
   <si>
     <t xml:space="preserve">6.85612297058105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84989976882935</t>
+    <t xml:space="preserve">6.84990072250366</t>
   </si>
   <si>
     <t xml:space="preserve">6.85767889022827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0708155632019</t>
+    <t xml:space="preserve">7.07081460952759</t>
   </si>
   <si>
     <t xml:space="preserve">7.10348510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13459968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09726142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19060659408569</t>
+    <t xml:space="preserve">7.13459920883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09726238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19060611724854</t>
   </si>
   <si>
     <t xml:space="preserve">7.15326929092407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31039714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49241876602173</t>
+    <t xml:space="preserve">7.31039810180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49241828918457</t>
   </si>
   <si>
     <t xml:space="preserve">7.52820014953613</t>
@@ -4448,13 +4448,13 @@
     <t xml:space="preserve">7.57953977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63399124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74289178848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91480159759521</t>
+    <t xml:space="preserve">7.63399028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74289226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">7.90892314910889</t>
@@ -4475,16 +4475,16 @@
     <t xml:space="preserve">7.7728796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73760938644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69562149047852</t>
+    <t xml:space="preserve">7.73761034011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6956205368042</t>
   </si>
   <si>
     <t xml:space="preserve">7.7140965461731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73928928375244</t>
+    <t xml:space="preserve">7.73928833007812</t>
   </si>
   <si>
     <t xml:space="preserve">7.68554496765137</t>
@@ -4496,22 +4496,22 @@
     <t xml:space="preserve">7.65867185592651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71073722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69394159317017</t>
+    <t xml:space="preserve">7.71073818206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69394254684448</t>
   </si>
   <si>
     <t xml:space="preserve">7.81990718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79471302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51087284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48064088821411</t>
+    <t xml:space="preserve">7.79471397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51087379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48064184188843</t>
   </si>
   <si>
     <t xml:space="preserve">7.50415468215942</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">7.66371059417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56965684890747</t>
+    <t xml:space="preserve">7.56965589523315</t>
   </si>
   <si>
     <t xml:space="preserve">7.58477210998535</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">7.53774499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64691591262817</t>
+    <t xml:space="preserve">7.64691495895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.54446363449097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5948486328125</t>
+    <t xml:space="preserve">7.59484958648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.6721076965332</t>
@@ -4559,22 +4559,22 @@
     <t xml:space="preserve">7.85685682296753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90052509307861</t>
+    <t xml:space="preserve">7.9005241394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.02145099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12558269500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11550521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09535121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11046600341797</t>
+    <t xml:space="preserve">8.12558174133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11550426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09535026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11046695709229</t>
   </si>
   <si>
     <t xml:space="preserve">8.01977157592773</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">8.04496479034424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0819149017334</t>
+    <t xml:space="preserve">8.08191394805908</t>
   </si>
   <si>
     <t xml:space="preserve">8.13230037689209</t>
@@ -4595,10 +4595,10 @@
     <t xml:space="preserve">8.18100547790527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28513813018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31536960601807</t>
+    <t xml:space="preserve">8.28513717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31536865234375</t>
   </si>
   <si>
     <t xml:space="preserve">8.34560108184814</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">8.39430809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4312572479248</t>
+    <t xml:space="preserve">8.43125820159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.51943302154541</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">8.54042720794678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5698184967041</t>
+    <t xml:space="preserve">8.56981945037842</t>
   </si>
   <si>
     <t xml:space="preserve">8.69998168945312</t>
@@ -4631,13 +4631,13 @@
     <t xml:space="preserve">8.56561946868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7083797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74197006225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60340976715088</t>
+    <t xml:space="preserve">8.70838069915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74197101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60340881347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.6328010559082</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">8.61180686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50263690948486</t>
+    <t xml:space="preserve">8.50263786315918</t>
   </si>
   <si>
     <t xml:space="preserve">8.49423980712891</t>
@@ -4655,13 +4655,13 @@
     <t xml:space="preserve">8.39094734191895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41026306152344</t>
+    <t xml:space="preserve">8.41026401519775</t>
   </si>
   <si>
     <t xml:space="preserve">8.25490570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42285919189453</t>
+    <t xml:space="preserve">8.42285823822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164367675781</t>
@@ -4694,10 +4694,10 @@
     <t xml:space="preserve">7.80143260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99793863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54950284957886</t>
+    <t xml:space="preserve">7.99793767929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54950189590454</t>
   </si>
   <si>
     <t xml:space="preserve">7.52095031738281</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">7.43193578720093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73425054550171</t>
+    <t xml:space="preserve">7.73425149917603</t>
   </si>
   <si>
     <t xml:space="preserve">7.63179922103882</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">7.60660696029663</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72417306900024</t>
+    <t xml:space="preserve">7.72417402267456</t>
   </si>
   <si>
     <t xml:space="preserve">7.78295707702637</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">7.80983018875122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74096870422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93075704574585</t>
+    <t xml:space="preserve">7.74096965789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93075609207153</t>
   </si>
   <si>
     <t xml:space="preserve">7.92739677429199</t>
@@ -4748,25 +4748,25 @@
     <t xml:space="preserve">8.09366989135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02648830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772506713867</t>
+    <t xml:space="preserve">8.0264892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18772411346436</t>
   </si>
   <si>
     <t xml:space="preserve">8.21795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.149094581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21291732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17260932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19780254364014</t>
+    <t xml:space="preserve">8.14909553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21291828155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17261028289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19780158996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.26834201812744</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">8.17092990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89212656021118</t>
+    <t xml:space="preserve">7.8921275138855</t>
   </si>
   <si>
     <t xml:space="preserve">8.19444274902344</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">8.39766693115234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34056186676025</t>
+    <t xml:space="preserve">8.34056282043457</t>
   </si>
   <si>
     <t xml:space="preserve">8.36575603485107</t>
@@ -4820,16 +4820,16 @@
     <t xml:space="preserve">8.54462623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7335729598999</t>
+    <t xml:space="preserve">8.73357200622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.77136325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67898845672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67478942871094</t>
+    <t xml:space="preserve">8.67898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67479038238525</t>
   </si>
   <si>
     <t xml:space="preserve">8.6453971862793</t>
@@ -4838,22 +4838,22 @@
     <t xml:space="preserve">8.92252063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98970222473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98130321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96450901031494</t>
+    <t xml:space="preserve">8.98970127105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90572452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98130416870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96450996398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.17025089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19124603271484</t>
+    <t xml:space="preserve">9.19124507904053</t>
   </si>
   <si>
     <t xml:space="preserve">9.28781986236572</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">9.38859176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49776268005371</t>
+    <t xml:space="preserve">9.49776172637939</t>
   </si>
   <si>
     <t xml:space="preserve">9.39698886871338</t>
@@ -4874,22 +4874,22 @@
     <t xml:space="preserve">9.40538597106934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30461406707764</t>
+    <t xml:space="preserve">9.30461502075195</t>
   </si>
   <si>
     <t xml:space="preserve">9.33400630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14925765991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03588962554932</t>
+    <t xml:space="preserve">9.14925670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.035888671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.01909351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04848480224609</t>
+    <t xml:space="preserve">9.04848575592041</t>
   </si>
   <si>
     <t xml:space="preserve">9.06947994232178</t>
@@ -4898,13 +4898,13 @@
     <t xml:space="preserve">9.20384216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34660339355469</t>
+    <t xml:space="preserve">9.34660243988037</t>
   </si>
   <si>
     <t xml:space="preserve">9.35500144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27942180633545</t>
+    <t xml:space="preserve">9.27942085266113</t>
   </si>
   <si>
     <t xml:space="preserve">9.24583053588867</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">9.25002956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25842761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43058013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4893627166748</t>
+    <t xml:space="preserve">9.25842666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057918548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48936367034912</t>
   </si>
   <si>
     <t xml:space="preserve">9.48096561431885</t>
@@ -4934,13 +4934,13 @@
     <t xml:space="preserve">9.60692977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67411231994629</t>
+    <t xml:space="preserve">9.67411136627197</t>
   </si>
   <si>
     <t xml:space="preserve">9.63632297515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930458068848</t>
+    <t xml:space="preserve">9.69930553436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.70770263671875</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">10.0394096374512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1779708862305</t>
+    <t xml:space="preserve">10.1779718399048</t>
   </si>
   <si>
     <t xml:space="preserve">10.0520076751709</t>
@@ -4967,7 +4967,7 @@
     <t xml:space="preserve">9.93863868713379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98062705993652</t>
+    <t xml:space="preserve">9.98062801361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.73289585113525</t>
@@ -4979,10 +4979,10 @@
     <t xml:space="preserve">9.85886096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83786582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93024063110352</t>
+    <t xml:space="preserve">9.83786678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9302396774292</t>
   </si>
   <si>
     <t xml:space="preserve">9.87565517425537</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">9.79167938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.825270652771</t>
+    <t xml:space="preserve">9.76648712158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82526969909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.97222900390625</t>
@@ -5009,7 +5009,7 @@
     <t xml:space="preserve">10.0268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1653757095337</t>
+    <t xml:space="preserve">10.1653747558594</t>
   </si>
   <si>
     <t xml:space="preserve">10.194766998291</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">10.1359834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1401815414429</t>
+    <t xml:space="preserve">10.1401824951172</t>
   </si>
   <si>
     <t xml:space="preserve">10.144380569458</t>
@@ -5039,13 +5039,13 @@
     <t xml:space="preserve">10.2157611846924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2241592407227</t>
+    <t xml:space="preserve">10.224160194397</t>
   </si>
   <si>
     <t xml:space="preserve">10.2115621566772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3039379119873</t>
+    <t xml:space="preserve">10.303936958313</t>
   </si>
   <si>
     <t xml:space="preserve">10.25355052948</t>
@@ -5054,34 +5054,34 @@
     <t xml:space="preserve">10.1905689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3291292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3333282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2451524734497</t>
+    <t xml:space="preserve">10.3291301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173059463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3333292007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.245153427124</t>
   </si>
   <si>
     <t xml:space="preserve">10.2913408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3963108062744</t>
+    <t xml:space="preserve">10.3963117599487</t>
   </si>
   <si>
     <t xml:space="preserve">10.434100151062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4676904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5222768783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3921136856079</t>
+    <t xml:space="preserve">10.4676914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5222759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3921127319336</t>
   </si>
   <si>
     <t xml:space="preserve">10.3207321166992</t>
@@ -5108,7 +5108,7 @@
     <t xml:space="preserve">10.1695737838745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1527786254883</t>
+    <t xml:space="preserve">10.152777671814</t>
   </si>
   <si>
     <t xml:space="preserve">9.94283676147461</t>
@@ -5120,13 +5120,13 @@
     <t xml:space="preserve">9.26682472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37179565429688</t>
+    <t xml:space="preserve">9.37179660797119</t>
   </si>
   <si>
     <t xml:space="preserve">9.24163341522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96870803833008</t>
+    <t xml:space="preserve">8.96870708465576</t>
   </si>
   <si>
     <t xml:space="preserve">9.46417140960693</t>
@@ -5150,7 +5150,7 @@
     <t xml:space="preserve">9.63212394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67831039428711</t>
+    <t xml:space="preserve">9.67831134796143</t>
   </si>
   <si>
     <t xml:space="preserve">9.69090747833252</t>
@@ -5162,13 +5162,13 @@
     <t xml:space="preserve">9.87985515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84817409515381</t>
+    <t xml:space="preserve">9.84817504882812</t>
   </si>
   <si>
     <t xml:space="preserve">9.73050308227539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8255443572998</t>
+    <t xml:space="preserve">9.82554531097412</t>
   </si>
   <si>
     <t xml:space="preserve">9.81649398803711</t>
@@ -5180,16 +5180,16 @@
     <t xml:space="preserve">9.74860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73955535888672</t>
+    <t xml:space="preserve">9.7395544052124</t>
   </si>
   <si>
     <t xml:space="preserve">9.71239852905273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75313091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78028774261475</t>
+    <t xml:space="preserve">9.75313186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78028678894043</t>
   </si>
   <si>
     <t xml:space="preserve">9.72597694396973</t>
@@ -5201,19 +5201,19 @@
     <t xml:space="preserve">9.92511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0020523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0744657516479</t>
+    <t xml:space="preserve">10.0020513534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0744647979736</t>
   </si>
   <si>
     <t xml:space="preserve">10.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.092568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0337333679199</t>
+    <t xml:space="preserve">10.0925674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0337324142456</t>
   </si>
   <si>
     <t xml:space="preserve">10.069938659668</t>
@@ -5225,16 +5225,16 @@
     <t xml:space="preserve">10.1378259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0789909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1785583496094</t>
+    <t xml:space="preserve">10.0789918899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1785593032837</t>
   </si>
   <si>
     <t xml:space="preserve">10.1514043807983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.115198135376</t>
+    <t xml:space="preserve">10.1151971817017</t>
   </si>
   <si>
     <t xml:space="preserve">10.142352104187</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">10.060887336731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695070266724</t>
+    <t xml:space="preserve">10.1695079803467</t>
   </si>
   <si>
     <t xml:space="preserve">10.2464456558228</t>
@@ -5291,10 +5291,10 @@
     <t xml:space="preserve">10.9751024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.106351852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.133505821228</t>
+    <t xml:space="preserve">11.1063508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1335067749023</t>
   </si>
   <si>
     <t xml:space="preserve">10.9388961791992</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">10.8393278121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7669143676758</t>
+    <t xml:space="preserve">10.7669153213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7171306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5315732955933</t>
+    <t xml:space="preserve">10.5315723419189</t>
   </si>
   <si>
     <t xml:space="preserve">10.4908399581909</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">10.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858821868896</t>
+    <t xml:space="preserve">10.5858812332153</t>
   </si>
   <si>
     <t xml:space="preserve">10.6628217697144</t>
@@ -5336,16 +5336,16 @@
     <t xml:space="preserve">10.7261819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.178765296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7173357009888</t>
+    <t xml:space="preserve">11.1787643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7173347473145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5906133651733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4955711364746</t>
+    <t xml:space="preserve">11.4955701828003</t>
   </si>
   <si>
     <t xml:space="preserve">11.4231586456299</t>
@@ -5360,10 +5360,10 @@
     <t xml:space="preserve">11.3869514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.486517906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6313457489014</t>
+    <t xml:space="preserve">11.4865188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6313467025757</t>
   </si>
   <si>
     <t xml:space="preserve">11.5815620422363</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">11.7625932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6901807785034</t>
+    <t xml:space="preserve">11.6901817321777</t>
   </si>
   <si>
     <t xml:space="preserve">11.8576364517212</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">11.9979362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0567712783813</t>
+    <t xml:space="preserve">12.0567722320557</t>
   </si>
   <si>
     <t xml:space="preserve">12.1291847229004</t>
@@ -5396,40 +5396,40 @@
     <t xml:space="preserve">12.2785358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3328466415405</t>
+    <t xml:space="preserve">12.3328475952148</t>
   </si>
   <si>
     <t xml:space="preserve">12.4776725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500301361084</t>
+    <t xml:space="preserve">12.5003023147583</t>
   </si>
   <si>
     <t xml:space="preserve">12.3781051635742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5093536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3962087631226</t>
+    <t xml:space="preserve">12.509352684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3962078094482</t>
   </si>
   <si>
     <t xml:space="preserve">12.4052600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3102178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3554763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2875881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.124659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1699171066284</t>
+    <t xml:space="preserve">12.3102188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3554754257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2875890731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1246604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1699180603027</t>
   </si>
   <si>
     <t xml:space="preserve">12.2921142578125</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">12.3826313018799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6451282501221</t>
+    <t xml:space="preserve">12.6451292037964</t>
   </si>
   <si>
     <t xml:space="preserve">12.6722831726074</t>
@@ -5471,16 +5471,16 @@
     <t xml:space="preserve">13.0796060562134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2244319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5140838623047</t>
+    <t xml:space="preserve">13.2244310379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.514084815979</t>
   </si>
   <si>
     <t xml:space="preserve">13.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7403755187988</t>
+    <t xml:space="preserve">13.7403745651245</t>
   </si>
   <si>
     <t xml:space="preserve">13.7992105484009</t>
@@ -6546,6 +6546,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4249992370605</t>
   </si>
 </sst>
 </file>
@@ -48632,7 +48635,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>849</v>
+        <v>1349</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48658,7 +48661,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1607" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -48684,7 +48687,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1608" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -48710,7 +48713,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G1609" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -48762,7 +48765,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1611" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48788,7 +48791,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48840,7 +48843,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G1614" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48866,7 +48869,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1615" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48892,7 +48895,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G1616" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48944,7 +48947,7 @@
         <v>9.70400047302246</v>
       </c>
       <c r="G1618" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48970,7 +48973,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G1619" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48996,7 +48999,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1620" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -49022,7 +49025,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G1621" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -49048,7 +49051,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G1622" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -49074,7 +49077,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G1623" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -49100,7 +49103,7 @@
         <v>9.5</v>
       </c>
       <c r="G1624" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -49126,7 +49129,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G1625" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -49152,7 +49155,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G1626" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -49178,7 +49181,7 @@
         <v>9.4379997253418</v>
       </c>
       <c r="G1627" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -49204,7 +49207,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1628" t="s">
-        <v>1367</v>
+        <v>827</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -49360,7 +49363,7 @@
         <v>9.5</v>
       </c>
       <c r="G1634" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -72274,7 +72277,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6916898148</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>1470327</v>
@@ -72295,6 +72298,32 @@
         <v>2177</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6911921296</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>1449449</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>17.7399997711182</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>17.2950000762939</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>17.4400005340576</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>17.4249992370605</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>2178</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="2185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="2186">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00964784622192</t>
+    <t xml:space="preserve">5.00964689254761</t>
   </si>
   <si>
     <t xml:space="preserve">4.88411378860474</t>
@@ -56,46 +56,46 @@
     <t xml:space="preserve">4.67391872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64764404296875</t>
+    <t xml:space="preserve">4.64764451980591</t>
   </si>
   <si>
     <t xml:space="preserve">4.75858020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81112909317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75274229049683</t>
+    <t xml:space="preserve">4.81112957000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75274276733398</t>
   </si>
   <si>
     <t xml:space="preserve">4.57174110412598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35278844833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44328880310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2652063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167560577393</t>
+    <t xml:space="preserve">4.35278797149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44328832626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26520586013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167608261108</t>
   </si>
   <si>
     <t xml:space="preserve">4.516273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37030363082886</t>
+    <t xml:space="preserve">4.37030410766602</t>
   </si>
   <si>
     <t xml:space="preserve">4.44036912918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37322330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13383436203003</t>
+    <t xml:space="preserve">4.37322282791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13383483886719</t>
   </si>
   <si>
     <t xml:space="preserve">4.30023860931396</t>
@@ -104,103 +104,103 @@
     <t xml:space="preserve">4.16594886779785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05209159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86817216873169</t>
+    <t xml:space="preserve">4.0520920753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86817145347595</t>
   </si>
   <si>
     <t xml:space="preserve">3.95283341407776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85357475280762</t>
+    <t xml:space="preserve">3.85357546806335</t>
   </si>
   <si>
     <t xml:space="preserve">3.49449157714844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29889369010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5470404624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36020040512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42442655563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52368545532227</t>
+    <t xml:space="preserve">3.29889345169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54704022407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36020064353943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42442631721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52368521690369</t>
   </si>
   <si>
     <t xml:space="preserve">3.55579853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62294435501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51784634590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48865294456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62878346443176</t>
+    <t xml:space="preserve">3.62294411659241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51784682273865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48865270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6287829875946</t>
   </si>
   <si>
     <t xml:space="preserve">3.5382821559906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50033068656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54996013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64046096801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65505743026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80394554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94991374015808</t>
+    <t xml:space="preserve">3.50033044815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54995942115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64046025276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65505766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80394506454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94991445541382</t>
   </si>
   <si>
     <t xml:space="preserve">3.96451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88860678672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77767133712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82730031013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83897829055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8973650932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23601293563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27980279922485</t>
+    <t xml:space="preserve">3.88860750198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77767157554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82730007171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83897709846497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89736533164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23601245880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27980375289917</t>
   </si>
   <si>
     <t xml:space="preserve">4.13675403594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15426969528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90028429031372</t>
+    <t xml:space="preserve">4.15427017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90028500556946</t>
   </si>
   <si>
     <t xml:space="preserve">3.9353175163269</t>
@@ -209,43 +209,43 @@
     <t xml:space="preserve">3.95575308799744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88276886940002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85649394989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74847745895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77183198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6959285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66381502151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7017674446106</t>
+    <t xml:space="preserve">3.88276791572571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85649442672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74847817420959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77183270454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69592833518982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66381549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70176720619202</t>
   </si>
   <si>
     <t xml:space="preserve">3.6317024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66673517227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48281359672546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.684250831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72512197494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6462996006012</t>
+    <t xml:space="preserve">3.66673469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48281455039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68425107002258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72512269020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64629888534546</t>
   </si>
   <si>
     <t xml:space="preserve">3.83605885505676</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">3.90612316131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84189748764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08712434768677</t>
+    <t xml:space="preserve">3.84189772605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08712482452393</t>
   </si>
   <si>
     <t xml:space="preserve">4.0900444984436</t>
@@ -266,109 +266,109 @@
     <t xml:space="preserve">4.22141599655151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23893213272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24769020080566</t>
+    <t xml:space="preserve">4.23893260955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24768972396851</t>
   </si>
   <si>
     <t xml:space="preserve">4.18930244445801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06960821151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91488242149353</t>
+    <t xml:space="preserve">4.06960868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91488194465637</t>
   </si>
   <si>
     <t xml:space="preserve">3.75431609153748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72220349311829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67549300193787</t>
+    <t xml:space="preserve">3.72220230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67549228668213</t>
   </si>
   <si>
     <t xml:space="preserve">3.73971939086914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76599335670471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80102610588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78934860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77475214004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84481644630432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87984991073608</t>
+    <t xml:space="preserve">3.76599311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80102562904358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78934836387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77475166320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8448166847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87984919548035</t>
   </si>
   <si>
     <t xml:space="preserve">4.07544755935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16886758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1601095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20973825454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19806146621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9937047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96743059158325</t>
+    <t xml:space="preserve">4.16886711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16010904312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20973873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19806098937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99370527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96743083000183</t>
   </si>
   <si>
     <t xml:space="preserve">3.86525225639343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85065531730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78351044654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5762345790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40107178688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27261924743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36312031745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35144186019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48573303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67841219902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72804164886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70468688011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10037612915039</t>
+    <t xml:space="preserve">3.85065579414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7835099697113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57623410224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40107131004333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27261900901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36312007904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3514416217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48573327064514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67841267585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72804188728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70468664169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10037565231323</t>
   </si>
   <si>
     <t xml:space="preserve">2.70450878143311</t>
@@ -377,97 +377,97 @@
     <t xml:space="preserve">2.86098766326904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96024584770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00987529754639</t>
+    <t xml:space="preserve">2.96024608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00987577438354</t>
   </si>
   <si>
     <t xml:space="preserve">3.03906917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91120052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8177809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75121903419495</t>
+    <t xml:space="preserve">2.91120076179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81778049468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75121855735779</t>
   </si>
   <si>
     <t xml:space="preserve">2.84580612182617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08869886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32808685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35436129570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45654034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40691018104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46529793739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43318462371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47405576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46821713447571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49741101264954</t>
+    <t xml:space="preserve">3.08869862556458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32808756828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35436201095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45653986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40690994262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46529746055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.433185338974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47405552864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46821761131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49741125106812</t>
   </si>
   <si>
     <t xml:space="preserve">3.41566848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5353627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49157238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6579761505127</t>
+    <t xml:space="preserve">3.53536295890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49157214164734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65797638893127</t>
   </si>
   <si>
     <t xml:space="preserve">3.58791160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29305481910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30473208427429</t>
+    <t xml:space="preserve">3.29305505752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30473184585571</t>
   </si>
   <si>
     <t xml:space="preserve">3.59375023841858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83313989639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80686521530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891255378723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78059053421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68717098236084</t>
+    <t xml:space="preserve">3.83313941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80686545372009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891279220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78059029579163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71928334236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6871702671051</t>
   </si>
   <si>
     <t xml:space="preserve">3.67257380485535</t>
@@ -476,76 +476,76 @@
     <t xml:space="preserve">3.57039546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60250878334045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7922682762146</t>
+    <t xml:space="preserve">3.60250854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79226732254028</t>
   </si>
   <si>
     <t xml:space="preserve">3.76307439804077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81854248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91196227073669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00246286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94115567207336</t>
+    <t xml:space="preserve">3.81854200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91196179389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00246334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94115614891052</t>
   </si>
   <si>
     <t xml:space="preserve">4.04917287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01414108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92072033882141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60542774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66089558601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56163740158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337944984436</t>
+    <t xml:space="preserve">4.01414012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92072057723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60542821884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66089582443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56163763999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64338040351868</t>
   </si>
   <si>
     <t xml:space="preserve">3.64921855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3777163028717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4215075969696</t>
+    <t xml:space="preserve">3.37771677970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42150688171387</t>
   </si>
   <si>
     <t xml:space="preserve">3.35728096961975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38063597679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37187743186951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37479734420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55871796607971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65213799476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52952361106873</t>
+    <t xml:space="preserve">3.3806357383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37187790870667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37479710578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55871772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65213751792908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52952432632446</t>
   </si>
   <si>
     <t xml:space="preserve">3.61710548400879</t>
@@ -554,70 +554,70 @@
     <t xml:space="preserve">3.74263858795166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85941386222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97035026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01705980300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09296321868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92363953590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71344447135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87401103973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00538301467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99954319000244</t>
+    <t xml:space="preserve">3.85941362380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97035002708435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01706027984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09296369552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92364001274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71344518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87401008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00538206100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99954342842102</t>
   </si>
   <si>
     <t xml:space="preserve">4.11047983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12507677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06376981735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97326922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81270384788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85838294029236</t>
+    <t xml:space="preserve">4.12507724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06376934051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97326850891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81270337104797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85838270187378</t>
   </si>
   <si>
     <t xml:space="preserve">3.92537999153137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82792997360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77615928649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66652941703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82183933258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96496820449829</t>
+    <t xml:space="preserve">3.86751937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82793045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616047859192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66652965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8218400478363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96496772766113</t>
   </si>
   <si>
     <t xml:space="preserve">4.08982467651367</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">4.0959153175354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92233443260193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31213045120239</t>
+    <t xml:space="preserve">3.92233419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31213092803955</t>
   </si>
   <si>
     <t xml:space="preserve">4.51921129226685</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">4.51312017440796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53748321533203</t>
+    <t xml:space="preserve">4.53748273849487</t>
   </si>
   <si>
     <t xml:space="preserve">4.58620738983154</t>
@@ -662,58 +662,58 @@
     <t xml:space="preserve">4.82069444656372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78719663619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77196979522705</t>
+    <t xml:space="preserve">4.78719615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77197027206421</t>
   </si>
   <si>
     <t xml:space="preserve">4.83287572860718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82983016967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76892423629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73238134384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72324514389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82373952865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96382236480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99427604675293</t>
+    <t xml:space="preserve">4.82983112335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76892471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73238182067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72324562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82374000549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96382284164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99427652359009</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98818492889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76283407211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81460475921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81155872344971</t>
+    <t xml:space="preserve">4.9881854057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76283359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81460428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81155824661255</t>
   </si>
   <si>
     <t xml:space="preserve">4.69888305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88769149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86941957473755</t>
+    <t xml:space="preserve">4.88769102096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86941814422607</t>
   </si>
   <si>
     <t xml:space="preserve">4.83592128753662</t>
@@ -725,37 +725,37 @@
     <t xml:space="preserve">4.84201192855835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91509866714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18917417526245</t>
+    <t xml:space="preserve">4.91509819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18917608261108</t>
   </si>
   <si>
     <t xml:space="preserve">5.35057497024536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18003940582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97905015945435</t>
+    <t xml:space="preserve">5.1800389289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11608695983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">4.84505701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96077823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75674343109131</t>
+    <t xml:space="preserve">4.96077871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75674390792847</t>
   </si>
   <si>
     <t xml:space="preserve">4.65624904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79937791824341</t>
+    <t xml:space="preserve">4.79937744140625</t>
   </si>
   <si>
     <t xml:space="preserve">4.74456262588501</t>
@@ -764,46 +764,46 @@
     <t xml:space="preserve">4.88464641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00036668777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97295904159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9455509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89987277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85419225692749</t>
+    <t xml:space="preserve">5.00036716461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97295951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94555187225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89987230300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85419321060181</t>
   </si>
   <si>
     <t xml:space="preserve">4.80546808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66538429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53443765640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56793546676636</t>
+    <t xml:space="preserve">4.6653847694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53443717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56793594360352</t>
   </si>
   <si>
     <t xml:space="preserve">4.60752439498901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78110551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82678556442261</t>
+    <t xml:space="preserve">4.78110647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82678604125977</t>
   </si>
   <si>
     <t xml:space="preserve">4.99732208251953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03995561599731</t>
+    <t xml:space="preserve">5.03995513916016</t>
   </si>
   <si>
     <t xml:space="preserve">5.04909086227417</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">5.05822801589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07345342636108</t>
+    <t xml:space="preserve">5.07345390319824</t>
   </si>
   <si>
     <t xml:space="preserve">5.08259057998657</t>
@@ -827,130 +827,130 @@
     <t xml:space="preserve">5.14349555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.155677318573</t>
+    <t xml:space="preserve">5.15567684173584</t>
   </si>
   <si>
     <t xml:space="preserve">5.10086154937744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15872192382812</t>
+    <t xml:space="preserve">5.15872240066528</t>
   </si>
   <si>
     <t xml:space="preserve">5.13740539550781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17090272903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14653968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02168416976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03081941604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02777481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06127262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95773315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90900802612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68670177459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20135545730591</t>
+    <t xml:space="preserve">5.17090320587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14654064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02168321609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03082036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02777433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06127309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95773267745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90900850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68670225143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20135688781738</t>
   </si>
   <si>
     <t xml:space="preserve">5.28053331375122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20744609832764</t>
+    <t xml:space="preserve">5.20744752883911</t>
   </si>
   <si>
     <t xml:space="preserve">5.17394828796387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37493753433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3901629447937</t>
+    <t xml:space="preserve">5.37493658065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39016437530518</t>
   </si>
   <si>
     <t xml:space="preserve">5.40843534469604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51502132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59115266799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55765533447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54242849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5272011756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59724283218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56679105758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58810758590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43279790878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45106887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49674987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53633737564087</t>
+    <t xml:space="preserve">5.51502084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59115362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5576548576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54242897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52720165252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59724426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56679058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5881085395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43279838562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45106935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49674844741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53633832931519</t>
   </si>
   <si>
     <t xml:space="preserve">5.57288122177124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5454740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52111148834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43888902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26835107803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14044952392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16176795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07649946212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09477090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18308448791504</t>
+    <t xml:space="preserve">5.54547357559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52111101150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43888854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26835250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14045000076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16176700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07649898529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09477138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18308401107788</t>
   </si>
   <si>
     <t xml:space="preserve">5.23180866241455</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">5.21353721618652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26530742645264</t>
+    <t xml:space="preserve">5.26530694961548</t>
   </si>
   <si>
     <t xml:space="preserve">5.19221973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21049213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11304330825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03386545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17699337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1648120880127</t>
+    <t xml:space="preserve">5.21049165725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03386497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17699384689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16481256484985</t>
   </si>
   <si>
     <t xml:space="preserve">5.29575967788696</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">5.28357934951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26226139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35971164703369</t>
+    <t xml:space="preserve">5.26226234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35971069335938</t>
   </si>
   <si>
     <t xml:space="preserve">5.40539026260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3383936882019</t>
+    <t xml:space="preserve">5.33839416503906</t>
   </si>
   <si>
     <t xml:space="preserve">5.37189245223999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46934080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52415609359741</t>
+    <t xml:space="preserve">5.40234518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46934127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52415704727173</t>
   </si>
   <si>
     <t xml:space="preserve">5.48152256011963</t>
@@ -1016,175 +1016,175 @@
     <t xml:space="preserve">5.48456811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30489587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.323166847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.381028175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41757202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39320850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36884641647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35666704177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48761320114136</t>
+    <t xml:space="preserve">5.30489635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32316780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38102865219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41757297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39320945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36884689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35666608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48761415481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.47847747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42061614990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29880571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34752893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34143877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28966951370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19831085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25008010864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14958572387695</t>
+    <t xml:space="preserve">5.42061567306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29880523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34752941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34143972396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28966999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19831037521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25008153915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14958620071411</t>
   </si>
   <si>
     <t xml:space="preserve">5.31403207778931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3779821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32012176513672</t>
+    <t xml:space="preserve">5.37798261642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32012224197388</t>
   </si>
   <si>
     <t xml:space="preserve">5.32925796508789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39625406265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4754319190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46325063705444</t>
+    <t xml:space="preserve">5.39625453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47543239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4632511138916</t>
   </si>
   <si>
     <t xml:space="preserve">5.49979448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53024673461914</t>
+    <t xml:space="preserve">5.5302472114563</t>
   </si>
   <si>
     <t xml:space="preserve">5.56374549865723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51806688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60333442687988</t>
+    <t xml:space="preserve">5.51806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60333395004272</t>
   </si>
   <si>
     <t xml:space="preserve">5.55156421661377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57897233963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55460977554321</t>
+    <t xml:space="preserve">5.57897186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55460929870605</t>
   </si>
   <si>
     <t xml:space="preserve">5.58201742172241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58506202697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57592725753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62160539627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71601009368896</t>
+    <t xml:space="preserve">5.5850625038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57592678070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62160634994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71601057052612</t>
   </si>
   <si>
     <t xml:space="preserve">5.77387046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73123598098755</t>
+    <t xml:space="preserve">5.73123693466187</t>
   </si>
   <si>
     <t xml:space="preserve">5.81041383743286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87131929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84695768356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82868528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90177202224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89568281173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0205397605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00531244277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01444864273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00835847854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9900860786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02077627182007</t>
+    <t xml:space="preserve">5.87132024765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84695911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82868576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90177249908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89568376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02053928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00531339645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01444911956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00835752487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99008655548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02077674865723</t>
   </si>
   <si>
     <t xml:space="preserve">5.92586135864258</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99862957000732</t>
+    <t xml:space="preserve">5.99862861633301</t>
   </si>
   <si>
     <t xml:space="preserve">5.99546575546265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96066236495972</t>
+    <t xml:space="preserve">5.96066331863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.89105939865112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01761293411255</t>
+    <t xml:space="preserve">6.01761198043823</t>
   </si>
   <si>
     <t xml:space="preserve">6.13467407226562</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">6.07456207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11885595321655</t>
+    <t xml:space="preserve">6.11885499954224</t>
   </si>
   <si>
     <t xml:space="preserve">6.08088874816895</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">5.98913812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01128387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09038114547729</t>
+    <t xml:space="preserve">6.01128435134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09038066864014</t>
   </si>
   <si>
     <t xml:space="preserve">6.06823348999023</t>
@@ -1214,34 +1214,34 @@
     <t xml:space="preserve">6.07139730453491</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04292249679565</t>
+    <t xml:space="preserve">6.04292297363281</t>
   </si>
   <si>
     <t xml:space="preserve">6.03659534454346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91636991500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94800806045532</t>
+    <t xml:space="preserve">5.9163703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94800758361816</t>
   </si>
   <si>
     <t xml:space="preserve">5.97648239135742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0302677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05241394042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04925155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98597431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93851661682129</t>
+    <t xml:space="preserve">6.03026723861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05241441726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04925060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9859733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93851709365845</t>
   </si>
   <si>
     <t xml:space="preserve">6.0587420463562</t>
@@ -1250,49 +1250,49 @@
     <t xml:space="preserve">6.20111513137817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18213272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18529462814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17580366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19478797912598</t>
+    <t xml:space="preserve">6.18213224411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18529510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17580509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1947865486145</t>
   </si>
   <si>
     <t xml:space="preserve">6.27388334274292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29919385910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35297918319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31184816360474</t>
+    <t xml:space="preserve">6.29919338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35297870635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31184959411621</t>
   </si>
   <si>
     <t xml:space="preserve">6.30868530273438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26755523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22009754180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23528432846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15049409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19605255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25679731369019</t>
+    <t xml:space="preserve">6.26755475997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22009801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23528337478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15049362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19605302810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25679779052734</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349899291992</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">6.05557870864868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15428972244263</t>
+    <t xml:space="preserve">6.15429019927979</t>
   </si>
   <si>
     <t xml:space="preserve">6.10620021820068</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">6.23654985427856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25300216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22769117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24793863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25932884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18339776992798</t>
+    <t xml:space="preserve">6.25300264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22769069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24793910980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25932931900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18339729309082</t>
   </si>
   <si>
     <t xml:space="preserve">6.24287796020508</t>
@@ -1340,37 +1340,37 @@
     <t xml:space="preserve">6.25553226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28970146179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20238065719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11252641677856</t>
+    <t xml:space="preserve">6.28970241546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2023811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11252737045288</t>
   </si>
   <si>
     <t xml:space="preserve">5.9998950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09734058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22642612457275</t>
+    <t xml:space="preserve">6.09734106063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22642517089844</t>
   </si>
   <si>
     <t xml:space="preserve">6.24667358398438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24034547805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18086576461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20744228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23907995223999</t>
+    <t xml:space="preserve">6.24034643173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18086624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20744371414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23908138275146</t>
   </si>
   <si>
     <t xml:space="preserve">6.18972492218018</t>
@@ -1382,58 +1382,58 @@
     <t xml:space="preserve">6.1580867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04545402526855</t>
+    <t xml:space="preserve">6.04545450210571</t>
   </si>
   <si>
     <t xml:space="preserve">6.00622224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0353307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04165744781494</t>
+    <t xml:space="preserve">6.03532981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04165840148926</t>
   </si>
   <si>
     <t xml:space="preserve">6.06570339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1378378868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13024425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19985008239746</t>
+    <t xml:space="preserve">6.13783884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13024473190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19985055923462</t>
   </si>
   <si>
     <t xml:space="preserve">6.17706966400146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32640314102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40992832183838</t>
+    <t xml:space="preserve">6.32640266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40992879867554</t>
   </si>
   <si>
     <t xml:space="preserve">6.43523788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56495523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61241340637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47953224182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46687698364258</t>
+    <t xml:space="preserve">6.56495571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61241292953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47953271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46687602996826</t>
   </si>
   <si>
     <t xml:space="preserve">6.36879873275757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44789409637451</t>
+    <t xml:space="preserve">6.44789361953735</t>
   </si>
   <si>
     <t xml:space="preserve">6.33715963363647</t>
@@ -1442,52 +1442,52 @@
     <t xml:space="preserve">6.47004127502441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50167942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32766771316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24540853500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29476451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34665107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30109119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99736309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81133079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71514940261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75185012817383</t>
+    <t xml:space="preserve">6.50167846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3276686668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29476404190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34665060043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30109214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99736404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81133031845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71514987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75185060501099</t>
   </si>
   <si>
     <t xml:space="preserve">5.61643838882446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39117336273193</t>
+    <t xml:space="preserve">5.39117383956909</t>
   </si>
   <si>
     <t xml:space="preserve">5.06340026855469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.860915184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20387411117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10516262054443</t>
+    <t xml:space="preserve">4.86091470718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20387506484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10516214370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.23804378509521</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">5.0165753364563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17729806900024</t>
+    <t xml:space="preserve">5.1772985458374</t>
   </si>
   <si>
     <t xml:space="preserve">5.06086921691895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95329856872559</t>
+    <t xml:space="preserve">4.95329904556274</t>
   </si>
   <si>
     <t xml:space="preserve">5.19501543045044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12541151046753</t>
+    <t xml:space="preserve">5.12541198730469</t>
   </si>
   <si>
     <t xml:space="preserve">5.22032594680786</t>
@@ -1523,46 +1523,46 @@
     <t xml:space="preserve">5.10389757156372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08238363265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20513963699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33675575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15198707580566</t>
+    <t xml:space="preserve">5.0823826789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25829219818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20514011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675527572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15198755264282</t>
   </si>
   <si>
     <t xml:space="preserve">5.11908388137817</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04062080383301</t>
+    <t xml:space="preserve">5.04062032699585</t>
   </si>
   <si>
     <t xml:space="preserve">5.00771617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03808975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01277923583984</t>
+    <t xml:space="preserve">5.03808927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01277828216553</t>
   </si>
   <si>
     <t xml:space="preserve">5.07352447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14186382293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20893716812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12667655944824</t>
+    <t xml:space="preserve">5.1418628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20893669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1266770362854</t>
   </si>
   <si>
     <t xml:space="preserve">5.15958118438721</t>
@@ -1571,28 +1571,28 @@
     <t xml:space="preserve">5.08997583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00392007827759</t>
+    <t xml:space="preserve">5.00392055511475</t>
   </si>
   <si>
     <t xml:space="preserve">5.0254340171814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09250783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11022424697876</t>
+    <t xml:space="preserve">5.09250736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11022520065308</t>
   </si>
   <si>
     <t xml:space="preserve">5.15704917907715</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1443943977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1747670173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32663106918335</t>
+    <t xml:space="preserve">5.14439392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17476749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32663154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.38737678527832</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">5.43799829483032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53797483444214</t>
+    <t xml:space="preserve">5.5379753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.48861932754517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62150049209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55189561843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49494743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58480024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49241638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56455135345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56075525283813</t>
+    <t xml:space="preserve">5.62150096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55189657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49494647979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58479976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49241590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56455087661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56075477600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.57214403152466</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">5.26461935043335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37598657608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3165078163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33295965194702</t>
+    <t xml:space="preserve">5.37598752975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31650686264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33295917510986</t>
   </si>
   <si>
     <t xml:space="preserve">5.42028045654297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3114447593689</t>
+    <t xml:space="preserve">5.31144523620605</t>
   </si>
   <si>
     <t xml:space="preserve">5.2494330406189</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">5.25449562072754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24437189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21273279190063</t>
+    <t xml:space="preserve">5.24437141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21273326873779</t>
   </si>
   <si>
     <t xml:space="preserve">5.23551273345947</t>
@@ -1673,67 +1673,67 @@
     <t xml:space="preserve">5.07225894927979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36712837219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54177236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49368190765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73666334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70629167556763</t>
+    <t xml:space="preserve">5.36712789535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54177188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49368143081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73666381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70629119873047</t>
   </si>
   <si>
     <t xml:space="preserve">5.73539876937866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69743204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71261882781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81006574630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82904863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88979339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80500221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80373668670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7619743347168</t>
+    <t xml:space="preserve">5.69743156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71261787414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81006479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82904767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88979387283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80500364303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80373764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76197481155396</t>
   </si>
   <si>
     <t xml:space="preserve">5.86954498291016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85942125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80120658874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44432544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27854061126709</t>
+    <t xml:space="preserve">5.85942029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80120611190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44432592391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27854108810425</t>
   </si>
   <si>
     <t xml:space="preserve">5.30258560180664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29499292373657</t>
+    <t xml:space="preserve">5.29499244689941</t>
   </si>
   <si>
     <t xml:space="preserve">5.20640563964844</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">4.96342277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0051851272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.900146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85838413238525</t>
+    <t xml:space="preserve">5.00518560409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90014600753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8583836555481</t>
   </si>
   <si>
     <t xml:space="preserve">4.86471176147461</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">4.94064331054688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88369464874268</t>
+    <t xml:space="preserve">4.88369417190552</t>
   </si>
   <si>
     <t xml:space="preserve">4.83686971664429</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">4.98493719100952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89508390426636</t>
+    <t xml:space="preserve">4.89508438110352</t>
   </si>
   <si>
     <t xml:space="preserve">4.90647411346436</t>
@@ -1778,28 +1778,28 @@
     <t xml:space="preserve">4.92292594909668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7900447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92672204971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.939377784729</t>
+    <t xml:space="preserve">4.79004526138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92672252655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93937730789185</t>
   </si>
   <si>
     <t xml:space="preserve">4.90520858764648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01910638809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96215772628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94317388534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96468877792358</t>
+    <t xml:space="preserve">5.01910591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96215724945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94317436218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96468830108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.97860956192017</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">4.90900468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98353719711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86635589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9175386428833</t>
+    <t xml:space="preserve">4.98353672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86635637283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753768920898</t>
   </si>
   <si>
     <t xml:space="preserve">4.90811014175415</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">5.16402196884155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18557214736938</t>
+    <t xml:space="preserve">5.18557167053223</t>
   </si>
   <si>
     <t xml:space="preserve">5.20846939086914</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">5.25830459594727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25695753097534</t>
+    <t xml:space="preserve">5.25695705413818</t>
   </si>
   <si>
     <t xml:space="preserve">5.29062986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19500017166138</t>
+    <t xml:space="preserve">5.19499969482422</t>
   </si>
   <si>
     <t xml:space="preserve">5.20577526092529</t>
@@ -1856,37 +1856,37 @@
     <t xml:space="preserve">5.04549407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9296612739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9054160118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06704425811768</t>
+    <t xml:space="preserve">4.92966032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90541648864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06704473495483</t>
   </si>
   <si>
     <t xml:space="preserve">5.08724784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13304328918457</t>
+    <t xml:space="preserve">5.13304281234741</t>
   </si>
   <si>
     <t xml:space="preserve">5.05357551574707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09802341461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19095993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07781934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95390462875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87847805023193</t>
+    <t xml:space="preserve">5.09802389144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19095945358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07781982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95390510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87847757339478</t>
   </si>
   <si>
     <t xml:space="preserve">4.96737384796143</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">4.91484451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20712184906006</t>
+    <t xml:space="preserve">5.20712232589722</t>
   </si>
   <si>
     <t xml:space="preserve">5.19769382476807</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">5.18153095245361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15459251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15728664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22193813323975</t>
+    <t xml:space="preserve">5.1545934677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15728712081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2219386100769</t>
   </si>
   <si>
     <t xml:space="preserve">5.16536855697632</t>
@@ -1922,31 +1922,31 @@
     <t xml:space="preserve">5.15863370895386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27716159820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28389596939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30544662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32026243209839</t>
+    <t xml:space="preserve">5.27716112136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28389549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30544567108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32026147842407</t>
   </si>
   <si>
     <t xml:space="preserve">5.30275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30679321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31622123718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37144374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30409860610962</t>
+    <t xml:space="preserve">5.30679273605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31622171401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37144422531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30409955978394</t>
   </si>
   <si>
     <t xml:space="preserve">5.26369190216064</t>
@@ -1961,64 +1961,64 @@
     <t xml:space="preserve">4.97006750106812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93908929824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10610485076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2152042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22059154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31218099594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33911800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43474769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40107679367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59368276596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60715246200562</t>
+    <t xml:space="preserve">4.93908882141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10610437393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21520376205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22059106826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.312180519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33911848068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43474817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4010763168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59368324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6071515083313</t>
   </si>
   <si>
     <t xml:space="preserve">5.58156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60176420211792</t>
+    <t xml:space="preserve">5.60176372528076</t>
   </si>
   <si>
     <t xml:space="preserve">5.54519462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56000995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63004875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71759700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77820920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94118356704712</t>
+    <t xml:space="preserve">5.56001091003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63004970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71759796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77820825576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94118309020996</t>
   </si>
   <si>
     <t xml:space="preserve">5.82130908966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87383890151978</t>
+    <t xml:space="preserve">5.87383794784546</t>
   </si>
   <si>
     <t xml:space="preserve">5.88326644897461</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">5.99371242523193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89404201507568</t>
+    <t xml:space="preserve">5.89404249191284</t>
   </si>
   <si>
     <t xml:space="preserve">5.83343124389648</t>
@@ -2036,22 +2036,22 @@
     <t xml:space="preserve">5.9169397354126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89673519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98024415969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00583505630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05297613143921</t>
+    <t xml:space="preserve">5.89673614501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98024320602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00583553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05297660827637</t>
   </si>
   <si>
     <t xml:space="preserve">6.18227910995483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14456510543823</t>
+    <t xml:space="preserve">6.14456605911255</t>
   </si>
   <si>
     <t xml:space="preserve">6.02873182296753</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">6.07318019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02469205856323</t>
+    <t xml:space="preserve">6.02469158172607</t>
   </si>
   <si>
     <t xml:space="preserve">5.9681224822998</t>
@@ -2069,16 +2069,16 @@
     <t xml:space="preserve">6.01391649246216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13783168792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20517635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2375020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2981128692627</t>
+    <t xml:space="preserve">6.13783121109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20517587661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23750162124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29811239242554</t>
   </si>
   <si>
     <t xml:space="preserve">6.20787048339844</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">6.22268629074097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25905227661133</t>
+    <t xml:space="preserve">6.25905179977417</t>
   </si>
   <si>
     <t xml:space="preserve">6.30080652236938</t>
@@ -2096,49 +2096,49 @@
     <t xml:space="preserve">6.24558401107788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26578664779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35602903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40721082687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44492483139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47186231613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45300483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39778280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32235670089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30349969863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33986711502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45570087432861</t>
+    <t xml:space="preserve">6.26578712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35602951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4072117805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4449257850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47186279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45300579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39778327941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32235717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30350065231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33986616134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45570039749146</t>
   </si>
   <si>
     <t xml:space="preserve">6.36411046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40047645568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19978857040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05566883087158</t>
+    <t xml:space="preserve">6.40047693252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19978952407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05567026138306</t>
   </si>
   <si>
     <t xml:space="preserve">6.13379001617432</t>
@@ -2147,52 +2147,52 @@
     <t xml:space="preserve">5.99236583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85902261734009</t>
+    <t xml:space="preserve">5.85902309417725</t>
   </si>
   <si>
     <t xml:space="preserve">6.00987529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97216272354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95734643936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86036920547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79167795181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81188154220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75800514221191</t>
+    <t xml:space="preserve">5.9721622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95734548568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86036968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7916784286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81188106536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75800561904907</t>
   </si>
   <si>
     <t xml:space="preserve">5.71894454956055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64486503601074</t>
+    <t xml:space="preserve">5.6448655128479</t>
   </si>
   <si>
     <t xml:space="preserve">5.63678359985352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57078552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53845977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68257808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65160036087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6798849105835</t>
+    <t xml:space="preserve">5.5707859992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68257856369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6515998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67988443374634</t>
   </si>
   <si>
     <t xml:space="preserve">5.76608657836914</t>
@@ -2204,25 +2204,25 @@
     <t xml:space="preserve">5.73780202865601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77147340774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74184226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74049520492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86575698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95465278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93579578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98159074783325</t>
+    <t xml:space="preserve">5.77147436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7418417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7404956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86575746536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95465326309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93579626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98159122467041</t>
   </si>
   <si>
     <t xml:space="preserve">5.96138715744019</t>
@@ -2231,40 +2231,40 @@
     <t xml:space="preserve">6.08260822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12301540374756</t>
+    <t xml:space="preserve">6.1230149269104</t>
   </si>
   <si>
     <t xml:space="preserve">6.10550594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02738523483276</t>
+    <t xml:space="preserve">6.02738571166992</t>
   </si>
   <si>
     <t xml:space="preserve">6.09607744216919</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25501155853271</t>
+    <t xml:space="preserve">6.25501251220703</t>
   </si>
   <si>
     <t xml:space="preserve">6.37892723083496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34794807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29137802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27117490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33043766021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31966209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32505035400391</t>
+    <t xml:space="preserve">6.3479471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29137754440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27117395401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33043813705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31966304779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32504987716675</t>
   </si>
   <si>
     <t xml:space="preserve">6.27790927886963</t>
@@ -2279,52 +2279,52 @@
     <t xml:space="preserve">6.32774448394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1957483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22538042068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29407215118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26982831954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28329610824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12032175064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0974235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10685300827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95061159133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89808320999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83208417892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88057327270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72433233261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71355724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74318933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60984563827515</t>
+    <t xml:space="preserve">6.19574880599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22537994384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29407119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2698278427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28329706192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12032127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09742403030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10685253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95061206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8980827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83208465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88057279586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72433280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71355676651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74318885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60984659194946</t>
   </si>
   <si>
     <t xml:space="preserve">5.72972059249878</t>
@@ -2336,154 +2336,154 @@
     <t xml:space="preserve">5.86171722412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90616369247437</t>
+    <t xml:space="preserve">5.90616416931152</t>
   </si>
   <si>
     <t xml:space="preserve">5.83881855010986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91155099868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93175554275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98293781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06779193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14187145233154</t>
+    <t xml:space="preserve">5.91155195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93175506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98293828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0677924156189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14187240600586</t>
   </si>
   <si>
     <t xml:space="preserve">6.36007070541382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37488508224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45435237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40586519241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43819141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49880170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.436842918396</t>
+    <t xml:space="preserve">6.37488555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45435285568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40586423873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43819046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49880123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43684339523315</t>
   </si>
   <si>
     <t xml:space="preserve">6.40990543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53247356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71565246582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66446971893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67389869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71161031723022</t>
+    <t xml:space="preserve">6.53247404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71565198898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66446924209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67389822006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71161222457886</t>
   </si>
   <si>
     <t xml:space="preserve">6.80522060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71834659576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74797821044922</t>
+    <t xml:space="preserve">6.71834516525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74797868728638</t>
   </si>
   <si>
     <t xml:space="preserve">6.72103977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5351676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61463403701782</t>
+    <t xml:space="preserve">6.53516721725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61463451385498</t>
   </si>
   <si>
     <t xml:space="preserve">6.58500289916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6025128364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56345272064209</t>
+    <t xml:space="preserve">6.60251235961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56345224380493</t>
   </si>
   <si>
     <t xml:space="preserve">6.57422733306885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79511880874634</t>
+    <t xml:space="preserve">6.79511833190918</t>
   </si>
   <si>
     <t xml:space="preserve">6.94664525985718</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02409362792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12511014938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15204763412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13184499740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11164140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17898607254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24969863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30357360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29684114456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32377815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18908834457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17225217819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22949552536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38438892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33724641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25979900360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02746057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16888523101807</t>
+    <t xml:space="preserve">7.02409267425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12510967254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15204858779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13184452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11164283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1789870262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24969816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30357456207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29684066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32377767562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18908929824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17225170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22949504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38438940048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33724784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25980043411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02745962142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16888427734375</t>
   </si>
   <si>
     <t xml:space="preserve">7.10490703582764</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">7.26400136947632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23581838607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21468067169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27104520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24286270141602</t>
+    <t xml:space="preserve">7.23581790924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21468162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27104568481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24286365509033</t>
   </si>
   <si>
     <t xml:space="preserve">7.2217264175415</t>
@@ -2510,124 +2510,124 @@
     <t xml:space="preserve">7.27456855773926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15127086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08433771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04558658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10547494888306</t>
+    <t xml:space="preserve">7.15127038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08433723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04558801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10547399520874</t>
   </si>
   <si>
     <t xml:space="preserve">7.07729196548462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09842872619629</t>
+    <t xml:space="preserve">7.09842824935913</t>
   </si>
   <si>
     <t xml:space="preserve">6.98217678070068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12308883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13365650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99908685684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06672382354736</t>
+    <t xml:space="preserve">7.12308788299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13365697860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99908638000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06672334671021</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357232093811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10899686813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03854179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97513055801392</t>
+    <t xml:space="preserve">7.10899639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03854131698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97513103485107</t>
   </si>
   <si>
     <t xml:space="preserve">6.91453981399536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98499441146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92158460617065</t>
+    <t xml:space="preserve">6.98499488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92158365249634</t>
   </si>
   <si>
     <t xml:space="preserve">6.94131231307983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00472211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01599502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97372245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93567562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93708372116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84549236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91594886779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86944818496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81871843338013</t>
+    <t xml:space="preserve">7.00472259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01599597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97372198104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93567657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93708419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84549188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91594791412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86944723129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8187198638916</t>
   </si>
   <si>
     <t xml:space="preserve">6.83844661712646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75953578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70317125320435</t>
+    <t xml:space="preserve">6.7595362663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7031717300415</t>
   </si>
   <si>
     <t xml:space="preserve">6.73699045181274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54394054412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74967241287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69894456863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52421426773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34948348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49180364608765</t>
+    <t xml:space="preserve">6.54394197463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74967193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69894361495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52421379089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34948253631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49180316925049</t>
   </si>
   <si>
     <t xml:space="preserve">6.57494163513184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74403619766235</t>
+    <t xml:space="preserve">6.7440357208252</t>
   </si>
   <si>
     <t xml:space="preserve">6.6369423866272</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">6.76658248901367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80321931838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82153654098511</t>
+    <t xml:space="preserve">6.80321836471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82153749465942</t>
   </si>
   <si>
     <t xml:space="preserve">6.82294702529907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.767991065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79476404190063</t>
+    <t xml:space="preserve">6.76799058914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79476356506348</t>
   </si>
   <si>
     <t xml:space="preserve">6.75671768188477</t>
@@ -2663,22 +2663,22 @@
     <t xml:space="preserve">6.20434379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17052555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0225682258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77033519744873</t>
+    <t xml:space="preserve">6.17052507400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02256774902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77033472061157</t>
   </si>
   <si>
     <t xml:space="preserve">5.56742334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51669454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4448299407959</t>
+    <t xml:space="preserve">5.51669406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44482946395874</t>
   </si>
   <si>
     <t xml:space="preserve">5.21655225753784</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">5.10523223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36967325210571</t>
+    <t xml:space="preserve">4.36967277526855</t>
   </si>
   <si>
     <t xml:space="preserve">4.06953096389771</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">3.4030179977417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64820528030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2254695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514994621277</t>
+    <t xml:space="preserve">3.6482048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22546982765198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14515018463135</t>
   </si>
   <si>
     <t xml:space="preserve">2.96266937255859</t>
@@ -2714,31 +2714,31 @@
     <t xml:space="preserve">2.93941903114319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99648809432983</t>
+    <t xml:space="preserve">2.99648785591125</t>
   </si>
   <si>
     <t xml:space="preserve">3.06905770301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49602007865906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77220726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87507343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63693261146545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5051794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54252123832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52561140060425</t>
+    <t xml:space="preserve">3.49602031707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77220749855042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87507295608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6369321346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50517964363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54252076148987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52561187744141</t>
   </si>
   <si>
     <t xml:space="preserve">3.64679551124573</t>
@@ -2750,31 +2750,31 @@
     <t xml:space="preserve">3.83702683448792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91452836990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92157435417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90466451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74120664596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45867848396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52420234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56788539886475</t>
+    <t xml:space="preserve">3.91452789306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92157387733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90466403961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74120688438416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45867872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52420210838318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56788563728333</t>
   </si>
   <si>
     <t xml:space="preserve">3.44176959991455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39667797088623</t>
+    <t xml:space="preserve">3.39667749404907</t>
   </si>
   <si>
     <t xml:space="preserve">3.61297702789307</t>
@@ -2783,85 +2783,85 @@
     <t xml:space="preserve">3.69470596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82152605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88634562492371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72570633888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67075061798096</t>
+    <t xml:space="preserve">3.82152581214905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88634514808655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7257068157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67075085639954</t>
   </si>
   <si>
     <t xml:space="preserve">3.63834095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63129544258118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62143135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66088652610779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348016738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72288799285889</t>
+    <t xml:space="preserve">3.6312952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62143182754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66088676452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7834804058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72288846969604</t>
   </si>
   <si>
     <t xml:space="preserve">3.55802154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4424741268158</t>
+    <t xml:space="preserve">3.44247388839722</t>
   </si>
   <si>
     <t xml:space="preserve">3.68061447143555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62284111976624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57211208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64397740364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65665984153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86379981040955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0216212272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17239665985107</t>
+    <t xml:space="preserve">3.62284088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57211256027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64397788047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65665936470032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8638002872467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02162170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17239713668823</t>
   </si>
   <si>
     <t xml:space="preserve">4.1118049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4443564414978</t>
+    <t xml:space="preserve">4.44435596466064</t>
   </si>
   <si>
     <t xml:space="preserve">4.5401759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78677225112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78536224365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00800323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16441488265991</t>
+    <t xml:space="preserve">4.78677177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78536176681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00800275802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16441535949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.99813938140869</t>
@@ -2870,70 +2870,70 @@
     <t xml:space="preserve">4.90795612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69940662384033</t>
+    <t xml:space="preserve">4.69940614700317</t>
   </si>
   <si>
     <t xml:space="preserve">4.79663562774658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86709213256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98968458175659</t>
+    <t xml:space="preserve">4.8670916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98968410491943</t>
   </si>
   <si>
     <t xml:space="preserve">4.96572971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05450344085693</t>
+    <t xml:space="preserve">5.05450391769409</t>
   </si>
   <si>
     <t xml:space="preserve">4.94741106033325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80509090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82763624191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55144929885864</t>
+    <t xml:space="preserve">4.80509042739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55144882202148</t>
   </si>
   <si>
     <t xml:space="preserve">4.58949518203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40490102767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60076808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50213003158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55567693710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75295305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73745250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75858974456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76422643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71490669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63458681106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76281690597534</t>
+    <t xml:space="preserve">4.40490055084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60076904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50213050842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55567646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75295352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7374529838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75858926773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76422548294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71490716934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63458728790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7628173828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.87977361679077</t>
@@ -2942,37 +2942,37 @@
     <t xml:space="preserve">4.96432018280029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97136688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99109363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95868349075317</t>
+    <t xml:space="preserve">4.97136640548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99109411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95868396759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.07423162460327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07704973220825</t>
+    <t xml:space="preserve">5.07705020904541</t>
   </si>
   <si>
     <t xml:space="preserve">5.13623285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04745864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98827600479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95304822921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90654706954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88822841644287</t>
+    <t xml:space="preserve">5.04745817184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9882755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95304775238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9065465927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88822889328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.75577116012573</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">4.77549839019775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57258558273315</t>
+    <t xml:space="preserve">4.57258605957031</t>
   </si>
   <si>
     <t xml:space="preserve">4.65008735656738</t>
@@ -2990,16 +2990,16 @@
     <t xml:space="preserve">4.77972602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74731731414795</t>
+    <t xml:space="preserve">4.74731683731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.80931758880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09395933151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10805082321167</t>
+    <t xml:space="preserve">5.09395885467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10805130004883</t>
   </si>
   <si>
     <t xml:space="preserve">5.11509609222412</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">5.02632188796997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94177484512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06859540939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95445680618286</t>
+    <t xml:space="preserve">4.94177436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06859493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9544563293457</t>
   </si>
   <si>
     <t xml:space="preserve">4.92486524581909</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">5.24050760269165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13059663772583</t>
+    <t xml:space="preserve">5.13059616088867</t>
   </si>
   <si>
     <t xml:space="preserve">5.15455102920532</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">5.03759479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90936470031738</t>
+    <t xml:space="preserve">4.90936517715454</t>
   </si>
   <si>
     <t xml:space="preserve">5.00236701965332</t>
@@ -3062,19 +3062,19 @@
     <t xml:space="preserve">5.10382270812988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11932277679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01082134246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91500091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73322534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72758865356445</t>
+    <t xml:space="preserve">5.11932325363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01082181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91500186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73322486877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72758913040161</t>
   </si>
   <si>
     <t xml:space="preserve">4.71208906173706</t>
@@ -3083,106 +3083,106 @@
     <t xml:space="preserve">4.59935903549194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78395318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71067905426025</t>
+    <t xml:space="preserve">4.7839527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71067953109741</t>
   </si>
   <si>
     <t xml:space="preserve">4.71913385391235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67967891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75718021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91641044616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03336715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91359233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10664176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05591297149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0277304649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8417272567749</t>
+    <t xml:space="preserve">4.67967844009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75718069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91641092300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03336763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91359186172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10664224624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05591344833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02773094177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84172773361206</t>
   </si>
   <si>
     <t xml:space="preserve">4.85018157958984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65854167938232</t>
+    <t xml:space="preserve">4.65854215621948</t>
   </si>
   <si>
     <t xml:space="preserve">4.6782693862915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63740539550781</t>
+    <t xml:space="preserve">4.63740491867065</t>
   </si>
   <si>
     <t xml:space="preserve">4.68531513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57963132858276</t>
+    <t xml:space="preserve">4.57963180541992</t>
   </si>
   <si>
     <t xml:space="preserve">4.58526802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62754201889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6049952507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48381042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117134094238</t>
+    <t xml:space="preserve">4.62754106521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60499572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48381185531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117086410522</t>
   </si>
   <si>
     <t xml:space="preserve">4.31753587722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28935384750366</t>
+    <t xml:space="preserve">4.2893533706665</t>
   </si>
   <si>
     <t xml:space="preserve">4.43871974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69236087799072</t>
+    <t xml:space="preserve">4.69236135482788</t>
   </si>
   <si>
     <t xml:space="preserve">5.12918710708618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02068519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02913999557495</t>
+    <t xml:space="preserve">5.02068567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02913951873779</t>
   </si>
   <si>
     <t xml:space="preserve">5.32928228378296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40678358078003</t>
+    <t xml:space="preserve">5.40678310394287</t>
   </si>
   <si>
     <t xml:space="preserve">5.32787275314331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39551019668579</t>
+    <t xml:space="preserve">5.39551067352295</t>
   </si>
   <si>
     <t xml:space="preserve">5.31237268447876</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">5.53501272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55755949020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51105833053589</t>
+    <t xml:space="preserve">5.5575590133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51105785369873</t>
   </si>
   <si>
     <t xml:space="preserve">5.44623851776123</t>
@@ -3203,37 +3203,37 @@
     <t xml:space="preserve">5.26587200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34196424484253</t>
+    <t xml:space="preserve">5.34196376800537</t>
   </si>
   <si>
     <t xml:space="preserve">5.27996301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3546462059021</t>
+    <t xml:space="preserve">5.35464572906494</t>
   </si>
   <si>
     <t xml:space="preserve">5.41242027282715</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34478187561035</t>
+    <t xml:space="preserve">5.34478235244751</t>
   </si>
   <si>
     <t xml:space="preserve">5.30391788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31096363067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2898268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16864252090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17991590499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35041809082031</t>
+    <t xml:space="preserve">5.31096410751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28982639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1686429977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17991542816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35041856765747</t>
   </si>
   <si>
     <t xml:space="preserve">5.30673599243164</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">5.19682502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33350944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33773708343506</t>
+    <t xml:space="preserve">5.33350992202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3377366065979</t>
   </si>
   <si>
     <t xml:space="preserve">5.21937084197998</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">5.239098072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43778371810913</t>
+    <t xml:space="preserve">5.43778419494629</t>
   </si>
   <si>
     <t xml:space="preserve">5.42228412628174</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">5.31800937652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27714443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.323646068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28419017791748</t>
+    <t xml:space="preserve">5.27714490890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32364559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28418970108032</t>
   </si>
   <si>
     <t xml:space="preserve">5.26305341720581</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">5.1996431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28559923171997</t>
+    <t xml:space="preserve">5.28559970855713</t>
   </si>
   <si>
     <t xml:space="preserve">5.21796178817749</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">5.22218942642212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2644624710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17568826675415</t>
+    <t xml:space="preserve">5.26446294784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17568778991699</t>
   </si>
   <si>
     <t xml:space="preserve">5.21232509613037</t>
@@ -3314,31 +3314,31 @@
     <t xml:space="preserve">5.69987964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7773814201355</t>
+    <t xml:space="preserve">5.77738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">5.96479368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0197491645813</t>
+    <t xml:space="preserve">6.01974964141846</t>
   </si>
   <si>
     <t xml:space="preserve">6.20011615753174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28607225418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26070880889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36921072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31566429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35652828216553</t>
+    <t xml:space="preserve">6.28607273101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26070833206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36921167373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31566476821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35652923583984</t>
   </si>
   <si>
     <t xml:space="preserve">6.32270956039429</t>
@@ -3353,37 +3353,37 @@
     <t xml:space="preserve">6.35934686660767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31284618377686</t>
+    <t xml:space="preserve">6.3128457069397</t>
   </si>
   <si>
     <t xml:space="preserve">6.17897987365723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07188653945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2818455696106</t>
+    <t xml:space="preserve">6.07188701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28184604644775</t>
   </si>
   <si>
     <t xml:space="preserve">6.2170262336731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30579996109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38752889633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49744033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50730323791504</t>
+    <t xml:space="preserve">6.30580043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38752937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49743986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50730419158936</t>
   </si>
   <si>
     <t xml:space="preserve">6.54535055160522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61862468719482</t>
+    <t xml:space="preserve">6.61862421035767</t>
   </si>
   <si>
     <t xml:space="preserve">6.63271522521973</t>
@@ -3395,37 +3395,37 @@
     <t xml:space="preserve">6.78208208084106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85394668579102</t>
+    <t xml:space="preserve">6.85394716262817</t>
   </si>
   <si>
     <t xml:space="preserve">6.85676527023315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64680576324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60875988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5495777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66653347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6721715927124</t>
+    <t xml:space="preserve">6.64680624008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60876035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54957723617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66653442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67217111587524</t>
   </si>
   <si>
     <t xml:space="preserve">6.6862621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70457983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79758167266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66230821609497</t>
+    <t xml:space="preserve">6.70458126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79758214950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66230773925781</t>
   </si>
   <si>
     <t xml:space="preserve">6.61721467971802</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">6.62848854064941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54253196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57635021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58762454986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57916975021362</t>
+    <t xml:space="preserve">6.54253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57635116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58762407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57917022705078</t>
   </si>
   <si>
     <t xml:space="preserve">6.55662298202515</t>
@@ -3452,82 +3452,82 @@
     <t xml:space="preserve">6.62003374099731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.615807056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48193979263306</t>
+    <t xml:space="preserve">6.61580657958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48194074630737</t>
   </si>
   <si>
     <t xml:space="preserve">6.4171199798584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43262147903442</t>
+    <t xml:space="preserve">6.43262100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.42134809494019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60453367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57776021957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59607934951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62426137924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6933069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55098676681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67498922348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71162605285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8018102645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8159008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77644634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84408187866211</t>
+    <t xml:space="preserve">6.60453319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57776069641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59607839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6242618560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69330739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55098581314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67498874664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71162557601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80181074142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81590032577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77644538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84408378601074</t>
   </si>
   <si>
     <t xml:space="preserve">6.89199256896973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9539942741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82012844085693</t>
+    <t xml:space="preserve">6.95399332046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82012891769409</t>
   </si>
   <si>
     <t xml:space="preserve">6.82717275619507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81449174880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8412652015686</t>
+    <t xml:space="preserve">6.81449127197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84126424789429</t>
   </si>
   <si>
     <t xml:space="preserve">6.88776540756226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87649250030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90608501434326</t>
+    <t xml:space="preserve">6.87649345397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9060845375061</t>
   </si>
   <si>
     <t xml:space="preserve">6.96808576583862</t>
@@ -3536,58 +3536,58 @@
     <t xml:space="preserve">7.02445030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05615568161011</t>
+    <t xml:space="preserve">7.05615520477295</t>
   </si>
   <si>
     <t xml:space="preserve">7.05263233184814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0103588104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02163076400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96385860443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00895023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98781394958496</t>
+    <t xml:space="preserve">7.01035928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0216326713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96385812759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0174036026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00894975662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98781299591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.99063158035278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91171979904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93285799026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97794914245605</t>
+    <t xml:space="preserve">6.91172170639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93285751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9779486656189</t>
   </si>
   <si>
     <t xml:space="preserve">7.03431415557861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02867746353149</t>
+    <t xml:space="preserve">7.02867650985718</t>
   </si>
   <si>
     <t xml:space="preserve">6.95681190490723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93990421295166</t>
+    <t xml:space="preserve">6.93990325927734</t>
   </si>
   <si>
     <t xml:space="preserve">6.94976806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94413089752197</t>
+    <t xml:space="preserve">6.94413042068481</t>
   </si>
   <si>
     <t xml:space="preserve">7.11252021789551</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">6.89903879165649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90749406814575</t>
+    <t xml:space="preserve">6.90749359130859</t>
   </si>
   <si>
     <t xml:space="preserve">6.68908071517944</t>
@@ -3611,61 +3611,61 @@
     <t xml:space="preserve">6.96103954315186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90326738357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85535526275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63553380966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72008180618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98922300338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06320142745972</t>
+    <t xml:space="preserve">6.90326690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85535621643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63553428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72008085250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98922252655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0632004737854</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995037078857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04135894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9962682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96526765823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89058351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9666748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03713274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0491099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94694852828979</t>
+    <t xml:space="preserve">7.04135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626731872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96526718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89058446884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96667575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03713178634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04910945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94694900512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.03149557113647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02726793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93426704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92862987518311</t>
+    <t xml:space="preserve">7.027268409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93426656723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92863035202026</t>
   </si>
   <si>
     <t xml:space="preserve">6.80744552612305</t>
@@ -3674,76 +3674,76 @@
     <t xml:space="preserve">6.85817527770996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89481210708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00613164901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03290462493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87367343902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00331258773804</t>
+    <t xml:space="preserve">6.89481258392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00613212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03290510177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87367486953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00331354141235</t>
   </si>
   <si>
     <t xml:space="preserve">7.11604309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22524881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08786058425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28161382675171</t>
+    <t xml:space="preserve">7.22524929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08786106109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28161334991455</t>
   </si>
   <si>
     <t xml:space="preserve">7.35559320449829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42604780197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33093404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47536706924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2499098777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20059013366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9709038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13013458251953</t>
+    <t xml:space="preserve">7.42604923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33093309402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47536849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24990940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20058917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97090435028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13013410568237</t>
   </si>
   <si>
     <t xml:space="preserve">7.1618390083313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17945337295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27809143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32388782501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.348548412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30275106430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26752281188965</t>
+    <t xml:space="preserve">7.17945289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27809190750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32388877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34854698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30275011062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26752233505249</t>
   </si>
   <si>
     <t xml:space="preserve">7.38377475738525</t>
@@ -3752,13 +3752,13 @@
     <t xml:space="preserve">7.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50707197189331</t>
+    <t xml:space="preserve">7.50707244873047</t>
   </si>
   <si>
     <t xml:space="preserve">7.50355005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61980199813843</t>
+    <t xml:space="preserve">7.61980152130127</t>
   </si>
   <si>
     <t xml:space="preserve">7.60923433303833</t>
@@ -3767,337 +3767,337 @@
     <t xml:space="preserve">7.54934597015381</t>
   </si>
   <si>
+    <t xml:space="preserve">7.55286931991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63037061691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63741636276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61275672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5282096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48593664169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44014167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63553762435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46118259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45967864990234</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.55287027359009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63037061691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63741588592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61275625228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52821063995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48593711853027</t>
+    <t xml:space="preserve">7.20115327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30787086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34244108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36047792434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38001728057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36949586868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52656602859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67687177658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59420251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56038475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54535388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45366811752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5002613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49875926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293008804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54159545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26728820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39053916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4296178817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54911184310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59795999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65808248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81214666366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82717704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80838966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80463171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79711627960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85723781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95869445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89857292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82342004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76329755783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77832794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75202369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35747051239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40106010437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51529312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75578260421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83469247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53408098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78584337234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95117950439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92863368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86851215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63929510116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80087471008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61674880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66935586929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51228666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41308546066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0237922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04483509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00876188278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46014547348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50674057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45864248275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91603803634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75220537185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87996530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41054439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10542345046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13548421859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38799858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43609619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86897802352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82989740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82839584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8885178565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78330373764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81186151504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98471212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86597108840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92910051345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05686044692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87799644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74272108078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6585488319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79683113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78781270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87198352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95164632797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9411244392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1244969367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19664430618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93661403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13201284408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13050985336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22370004653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62050676345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48523139953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25075435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22971296310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34845304489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29284048080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.458176612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.44013977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63553762435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46118259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4596791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55286979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20115232467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30787134170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34244155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36047697067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38001728057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36949586868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52656602859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67687177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59420299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56038475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54535388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45366811752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50026226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49875974655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58292961120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54159641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26728868484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39053869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42961835861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54911136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59796142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65808343887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81214666366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82717704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80839061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80463171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79711580276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85723876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95869541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89857292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82341909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76329755783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77832794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75202417373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35747241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40106010437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51529216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75578165054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83469343185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53408145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78584337234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95117950439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92863368988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86851215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63929510116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80087471008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61674928665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66935586929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51228761672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41759395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02379274368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04483556747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00876235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46014499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5067400932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45864248275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91603851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75220489501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87996482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41054391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10542345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38799905776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43609666824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86897754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82989835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98170757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82839584350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88851737976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78330326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81186199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98471260070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86597061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92910051345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05686092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87799596786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74272012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65854930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79683113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78781223297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71416282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87198400497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9516453742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94112348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12449741363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19664478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93661499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13201284408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13050889968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22369909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62050580978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48523187637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25075340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22971105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34845352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29284048080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.458176612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44013929367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44915819168091</t>
+    <t xml:space="preserve">7.44915723800659</t>
   </si>
   <si>
     <t xml:space="preserve">7.26879072189331</t>
@@ -4106,46 +4106,46 @@
     <t xml:space="preserve">7.19363832473755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13952732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18311595916748</t>
+    <t xml:space="preserve">7.13952779769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18311643600464</t>
   </si>
   <si>
     <t xml:space="preserve">7.01627779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.092933177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21468114852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16057014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21618509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18011045455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08090877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16958904266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2793116569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24474287033081</t>
+    <t xml:space="preserve">7.09293413162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21468210220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16057062149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21618461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18011093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08090925216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16958951950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27931261062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24474191665649</t>
   </si>
   <si>
     <t xml:space="preserve">7.42510938644409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25376081466675</t>
+    <t xml:space="preserve">7.25376129150391</t>
   </si>
   <si>
     <t xml:space="preserve">6.77578783035278</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">6.67057418823242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73219919204712</t>
+    <t xml:space="preserve">6.73219966888428</t>
   </si>
   <si>
     <t xml:space="preserve">6.71566534042358</t>
@@ -4163,19 +4163,19 @@
     <t xml:space="preserve">6.40603590011597</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3729681968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45563650131226</t>
+    <t xml:space="preserve">6.37296772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4556360244751</t>
   </si>
   <si>
     <t xml:space="preserve">6.51575803756714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49170970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34591341018677</t>
+    <t xml:space="preserve">6.49170923233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34591388702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.4841947555542</t>
@@ -4184,10 +4184,10 @@
     <t xml:space="preserve">6.34441041946411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42256927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37898063659668</t>
+    <t xml:space="preserve">6.4225697517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37898111343384</t>
   </si>
   <si>
     <t xml:space="preserve">6.20612907409668</t>
@@ -4199,121 +4199,121 @@
     <t xml:space="preserve">6.17155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02125215530396</t>
+    <t xml:space="preserve">6.02125263214111</t>
   </si>
   <si>
     <t xml:space="preserve">6.1099328994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23919677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33388948440552</t>
+    <t xml:space="preserve">6.23919582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33388900756836</t>
   </si>
   <si>
     <t xml:space="preserve">6.27076053619385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19560766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14300012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85441303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84990358352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99119091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11895179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04830837249756</t>
+    <t xml:space="preserve">6.19560718536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14300060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8544135093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84990406036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99119186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0483078956604</t>
   </si>
   <si>
     <t xml:space="preserve">6.01073122024536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03628301620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97014856338501</t>
+    <t xml:space="preserve">6.03628253936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97014904022217</t>
   </si>
   <si>
     <t xml:space="preserve">6.02876853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1414966583252</t>
+    <t xml:space="preserve">6.14149713516235</t>
   </si>
   <si>
     <t xml:space="preserve">6.2827844619751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32486963272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32937955856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37447166442871</t>
+    <t xml:space="preserve">6.32487106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32938003540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37447118759155</t>
   </si>
   <si>
     <t xml:space="preserve">6.42407274246216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4751763343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42707777023315</t>
+    <t xml:space="preserve">6.47517585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42707872390747</t>
   </si>
   <si>
     <t xml:space="preserve">6.41806030273438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43459415435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49772310256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54131174087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54882621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49471664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46916437149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.228675365448</t>
+    <t xml:space="preserve">6.43459367752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49772262573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54131126403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54882574081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49471569061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46916341781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22867488861084</t>
   </si>
   <si>
     <t xml:space="preserve">6.06183576583862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10843086242676</t>
+    <t xml:space="preserve">6.1084303855896</t>
   </si>
   <si>
     <t xml:space="preserve">6.08137512207031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04680395126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96113014221191</t>
+    <t xml:space="preserve">6.04680442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96113061904907</t>
   </si>
   <si>
     <t xml:space="preserve">5.94609928131104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00321626663208</t>
+    <t xml:space="preserve">6.00321578979492</t>
   </si>
   <si>
     <t xml:space="preserve">5.94309377670288</t>
@@ -4325,7 +4325,7 @@
     <t xml:space="preserve">6.09640550613403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00171279907227</t>
+    <t xml:space="preserve">6.00171327590942</t>
   </si>
   <si>
     <t xml:space="preserve">5.98517942428589</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">6.01824712753296</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07385969161987</t>
+    <t xml:space="preserve">6.07385921478271</t>
   </si>
   <si>
     <t xml:space="preserve">6.22416543960571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35793781280518</t>
+    <t xml:space="preserve">6.35793733596802</t>
   </si>
   <si>
     <t xml:space="preserve">6.36395072937012</t>
@@ -4349,13 +4349,13 @@
     <t xml:space="preserve">6.42858123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40904188156128</t>
+    <t xml:space="preserve">6.40904140472412</t>
   </si>
   <si>
     <t xml:space="preserve">6.35493135452271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38649559020996</t>
+    <t xml:space="preserve">6.38649606704712</t>
   </si>
   <si>
     <t xml:space="preserve">6.15953397750854</t>
@@ -4376,10 +4376,10 @@
     <t xml:space="preserve">5.82886075973511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72064065933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0573263168335</t>
+    <t xml:space="preserve">5.72064113616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05732679367065</t>
   </si>
   <si>
     <t xml:space="preserve">6.36695623397827</t>
@@ -4391,10 +4391,10 @@
     <t xml:space="preserve">6.02275562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9866828918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97315502166748</t>
+    <t xml:space="preserve">5.98668241500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97315454483032</t>
   </si>
   <si>
     <t xml:space="preserve">5.89349269866943</t>
@@ -4412,31 +4412,31 @@
     <t xml:space="preserve">6.4526309967041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62397909164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6179666519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62548208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83140087127686</t>
+    <t xml:space="preserve">6.62397956848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61796712875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6254825592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83140134811401</t>
   </si>
   <si>
     <t xml:space="preserve">6.86296510696411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89302635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85695219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94713687896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9110631942749</t>
+    <t xml:space="preserve">6.89302682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85695314407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94713640213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91106271743774</t>
   </si>
   <si>
     <t xml:space="preserve">7.0628719329834</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">7.23872995376587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27329969406128</t>
+    <t xml:space="preserve">7.27330112457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.32290124893188</t>
@@ -4454,25 +4454,25 @@
     <t xml:space="preserve">7.3755087852478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48072242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64681053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64113092422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64437627792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66384792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60380983352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56973361968994</t>
+    <t xml:space="preserve">7.48072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64681005477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64113187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64437675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66384840011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60381031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5697340965271</t>
   </si>
   <si>
     <t xml:space="preserve">7.50969505310059</t>
@@ -4481,22 +4481,22 @@
     <t xml:space="preserve">7.47561883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43505239486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4529013633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47724199295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42531681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37663650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39935350418091</t>
+    <t xml:space="preserve">7.43505191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45290184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47724151611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42531728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37663602828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39935445785522</t>
   </si>
   <si>
     <t xml:space="preserve">7.44965696334839</t>
@@ -4508,13 +4508,13 @@
     <t xml:space="preserve">7.55513000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53079032897949</t>
+    <t xml:space="preserve">7.53078985214233</t>
   </si>
   <si>
     <t xml:space="preserve">7.25655937194824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22735166549683</t>
+    <t xml:space="preserve">7.22735214233398</t>
   </si>
   <si>
     <t xml:space="preserve">7.25006866455078</t>
@@ -4523,43 +4523,43 @@
     <t xml:space="preserve">7.2744083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40422296524048</t>
+    <t xml:space="preserve">7.40422248840332</t>
   </si>
   <si>
     <t xml:space="preserve">7.31335353851318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32795667648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32957983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28252124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38799524307251</t>
+    <t xml:space="preserve">7.32795715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28252220153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38799571990967</t>
   </si>
   <si>
     <t xml:space="preserve">7.28901243209839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33769273757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41233444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53403520584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5210542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51618576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59082841873169</t>
+    <t xml:space="preserve">7.3376932144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41233491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53403568267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52105474472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51618528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59082889556885</t>
   </si>
   <si>
     <t xml:space="preserve">7.63301801681519</t>
@@ -4574,16 +4574,16 @@
     <t xml:space="preserve">7.84071826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82124757766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83585214614868</t>
+    <t xml:space="preserve">7.82124662399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83585119247437</t>
   </si>
   <si>
     <t xml:space="preserve">7.74822664260864</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65573453903198</t>
+    <t xml:space="preserve">7.65573644638062</t>
   </si>
   <si>
     <t xml:space="preserve">7.77256679534912</t>
@@ -4592,19 +4592,19 @@
     <t xml:space="preserve">7.808265209198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85694694519043</t>
+    <t xml:space="preserve">7.85694599151611</t>
   </si>
   <si>
     <t xml:space="preserve">7.90400218963623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00460910797119</t>
+    <t xml:space="preserve">8.00460815429688</t>
   </si>
   <si>
     <t xml:space="preserve">8.03381729125977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06302547454834</t>
+    <t xml:space="preserve">8.06302356719971</t>
   </si>
   <si>
     <t xml:space="preserve">7.99649524688721</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">8.08898639678955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11008262634277</t>
+    <t xml:space="preserve">8.11008167266846</t>
   </si>
   <si>
     <t xml:space="preserve">8.14577960968018</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">8.23097038269043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25125312805176</t>
+    <t xml:space="preserve">8.25125217437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.27964973449707</t>
@@ -4634,16 +4634,16 @@
     <t xml:space="preserve">8.27559280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41351890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44597244262695</t>
+    <t xml:space="preserve">8.41351985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44597339630127</t>
   </si>
   <si>
     <t xml:space="preserve">8.31210327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34049892425537</t>
+    <t xml:space="preserve">8.34049987792969</t>
   </si>
   <si>
     <t xml:space="preserve">8.32021617889404</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">8.21474266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20662975311279</t>
+    <t xml:space="preserve">8.20663070678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.10683631896973</t>
@@ -4661,22 +4661,22 @@
     <t xml:space="preserve">8.12549686431885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9753999710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13766765594482</t>
+    <t xml:space="preserve">7.97540092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13766670227051</t>
   </si>
   <si>
     <t xml:space="preserve">8.19446086883545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09061050415039</t>
+    <t xml:space="preserve">8.09060955047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.08087348937988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1701192855835</t>
+    <t xml:space="preserve">8.17012023925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.22285652160645</t>
@@ -4685,37 +4685,37 @@
     <t xml:space="preserve">8.1741771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22691249847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11738395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89102077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53728151321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72713279724121</t>
+    <t xml:space="preserve">8.22691345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11738300323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89102172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53728103637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72713232040405</t>
   </si>
   <si>
     <t xml:space="preserve">7.29388046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26629543304443</t>
+    <t xml:space="preserve">7.26629590988159</t>
   </si>
   <si>
     <t xml:space="preserve">7.18029451370239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47237396240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37339210510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29712629318237</t>
+    <t xml:space="preserve">7.47237348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37339162826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29712581634521</t>
   </si>
   <si>
     <t xml:space="preserve">7.26142740249634</t>
@@ -4724,13 +4724,13 @@
     <t xml:space="preserve">7.34905052185059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46263790130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51943063735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54701566696167</t>
+    <t xml:space="preserve">7.46263837814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51943016052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54701614379883</t>
   </si>
   <si>
     <t xml:space="preserve">7.54539394378662</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">7.66222667694092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65898036956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67034006118774</t>
+    <t xml:space="preserve">7.65898132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67033958435059</t>
   </si>
   <si>
     <t xml:space="preserve">7.81962442398071</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">7.75471687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91049432754517</t>
+    <t xml:space="preserve">7.91049337387085</t>
   </si>
   <si>
     <t xml:space="preserve">7.93970251083374</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">7.87317276000977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93483257293701</t>
+    <t xml:space="preserve">7.93483352661133</t>
   </si>
   <si>
     <t xml:space="preserve">7.89588975906372</t>
@@ -4772,10 +4772,10 @@
     <t xml:space="preserve">7.9202299118042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98837995529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89426565170288</t>
+    <t xml:space="preserve">7.98838090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89426755905151</t>
   </si>
   <si>
     <t xml:space="preserve">7.62490463256836</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">7.91698455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82287073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09710025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11332607269287</t>
+    <t xml:space="preserve">7.82286977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09709930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1133279800415</t>
   </si>
   <si>
     <t xml:space="preserve">8.05815601348877</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">8.08249664306641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86019039154053</t>
+    <t xml:space="preserve">7.86019134521484</t>
   </si>
   <si>
     <t xml:space="preserve">7.87154960632324</t>
@@ -4808,13 +4808,13 @@
     <t xml:space="preserve">7.90724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97377729415894</t>
+    <t xml:space="preserve">7.97377634048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.99324989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06626892089844</t>
+    <t xml:space="preserve">8.06626987457275</t>
   </si>
   <si>
     <t xml:space="preserve">8.14172267913818</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">8.43785953521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47436904907227</t>
+    <t xml:space="preserve">8.47437000274658</t>
   </si>
   <si>
     <t xml:space="preserve">8.38512325286865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38106632232666</t>
+    <t xml:space="preserve">8.38106727600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.35267066955566</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">8.67720222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66097640991211</t>
+    <t xml:space="preserve">8.66097736358643</t>
   </si>
   <si>
     <t xml:space="preserve">8.8597526550293</t>
@@ -4859,16 +4859,16 @@
     <t xml:space="preserve">8.88003635406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97333908081055</t>
+    <t xml:space="preserve">8.97334003448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.07069873809814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17617321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07881259918213</t>
+    <t xml:space="preserve">9.17617225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07881164550781</t>
   </si>
   <si>
     <t xml:space="preserve">9.10720920562744</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">8.9895658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01796245574951</t>
+    <t xml:space="preserve">9.0179615020752</t>
   </si>
   <si>
     <t xml:space="preserve">8.83946895599365</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">8.74210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76239395141602</t>
+    <t xml:space="preserve">8.7623929977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.89220523834229</t>
@@ -4913,31 +4913,31 @@
     <t xml:space="preserve">8.93277263641357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93682956695557</t>
+    <t xml:space="preserve">8.93683052062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.94494247436523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11126613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16805839538574</t>
+    <t xml:space="preserve">9.11126518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16805934906006</t>
   </si>
   <si>
     <t xml:space="preserve">9.15994548797607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20051288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32221126556396</t>
+    <t xml:space="preserve">9.20051193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32221221923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.28164577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34655380249023</t>
+    <t xml:space="preserve">9.34655284881592</t>
   </si>
   <si>
     <t xml:space="preserve">9.31004333496094</t>
@@ -4955,25 +4955,25 @@
     <t xml:space="preserve">9.69948196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83335208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71165180206299</t>
+    <t xml:space="preserve">9.83335304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7116527557373</t>
   </si>
   <si>
     <t xml:space="preserve">9.61834907531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6102352142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60212326049805</t>
+    <t xml:space="preserve">9.61023616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60212230682373</t>
   </si>
   <si>
     <t xml:space="preserve">9.6426887512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40334701538086</t>
+    <t xml:space="preserve">9.40334606170654</t>
   </si>
   <si>
     <t xml:space="preserve">9.50070571899414</t>
@@ -4985,7 +4985,7 @@
     <t xml:space="preserve">9.50476264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59400939941406</t>
+    <t xml:space="preserve">9.59400844573975</t>
   </si>
   <si>
     <t xml:space="preserve">9.54127216339111</t>
@@ -4994,10 +4994,10 @@
     <t xml:space="preserve">9.46013927459717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43579864501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49259185791016</t>
+    <t xml:space="preserve">9.43579959869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49259281158447</t>
   </si>
   <si>
     <t xml:space="preserve">9.63457584381104</t>
@@ -5009,7 +5009,7 @@
     <t xml:space="preserve">9.57778263092041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68731117248535</t>
+    <t xml:space="preserve">9.68731212615967</t>
   </si>
   <si>
     <t xml:space="preserve">9.82118129730225</t>
@@ -5021,10 +5021,10 @@
     <t xml:space="preserve">9.79278564453125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79684162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80089855194092</t>
+    <t xml:space="preserve">9.79684257507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8008975982666</t>
   </si>
   <si>
     <t xml:space="preserve">9.87391757965088</t>
@@ -5036,16 +5036,16 @@
     <t xml:space="preserve">9.85363578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78872871398926</t>
+    <t xml:space="preserve">9.78872776031494</t>
   </si>
   <si>
     <t xml:space="preserve">9.86986255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87797451019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86580657958984</t>
+    <t xml:space="preserve">9.87797546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86580562591553</t>
   </si>
   <si>
     <t xml:space="preserve">9.95505237579346</t>
@@ -5063,10 +5063,10 @@
     <t xml:space="preserve">10.0645818710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98344802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89825820922852</t>
+    <t xml:space="preserve">9.98344898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89825916290283</t>
   </si>
   <si>
     <t xml:space="preserve">9.94288158416748</t>
@@ -5075,13 +5075,13 @@
     <t xml:space="preserve">10.0442981719971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0808086395264</t>
+    <t xml:space="preserve">10.0808095932007</t>
   </si>
   <si>
     <t xml:space="preserve">10.1132621765137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.165997505188</t>
+    <t xml:space="preserve">10.1659984588623</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402421951294</t>
@@ -5105,10 +5105,10 @@
     <t xml:space="preserve">9.89014434814453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94693851470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82523918151855</t>
+    <t xml:space="preserve">9.94693946838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82523822784424</t>
   </si>
   <si>
     <t xml:space="preserve">9.8090124130249</t>
@@ -5120,16 +5120,16 @@
     <t xml:space="preserve">9.23296546936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05447292327881</t>
+    <t xml:space="preserve">8.9530553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05447196960449</t>
   </si>
   <si>
     <t xml:space="preserve">8.92871570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66503238677979</t>
+    <t xml:space="preserve">8.6650333404541</t>
   </si>
   <si>
     <t xml:space="preserve">9.14371967315674</t>
@@ -5144,13 +5144,13 @@
     <t xml:space="preserve">9.32626914978027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33032512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34249591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30598640441895</t>
+    <t xml:space="preserve">9.33032608032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34249687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30598545074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.35060882568359</t>
@@ -5159,31 +5159,31 @@
     <t xml:space="preserve">9.36277961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65080261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54532909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51472187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40103530883789</t>
+    <t xml:space="preserve">9.650803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54533004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51472091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40103435516357</t>
   </si>
   <si>
     <t xml:space="preserve">9.49285793304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48411273956299</t>
+    <t xml:space="preserve">9.4841136932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.47974014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41852569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40978050231934</t>
+    <t xml:space="preserve">9.41852474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40977954864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.38354396820068</t>
@@ -5192,22 +5192,22 @@
     <t xml:space="preserve">9.42289638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44913291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39666175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33107376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58905506134033</t>
+    <t xml:space="preserve">9.44913387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39666080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33107280731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58905601501465</t>
   </si>
   <si>
     <t xml:space="preserve">9.6633882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73334980010986</t>
+    <t xml:space="preserve">9.73335075378418</t>
   </si>
   <si>
     <t xml:space="preserve">9.70274257659912</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">9.72897720336914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7246036529541</t>
+    <t xml:space="preserve">9.72460460662842</t>
   </si>
   <si>
     <t xml:space="preserve">9.79456615447998</t>
@@ -5231,13 +5231,13 @@
     <t xml:space="preserve">9.73772239685059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83391857147217</t>
+    <t xml:space="preserve">9.83391952514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.80768299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77270317077637</t>
+    <t xml:space="preserve">9.77270412445068</t>
   </si>
   <si>
     <t xml:space="preserve">9.7989387512207</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">9.7202320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82517242431641</t>
+    <t xml:space="preserve">9.82517337799072</t>
   </si>
   <si>
     <t xml:space="preserve">9.89950752258301</t>
@@ -5261,10 +5261,10 @@
     <t xml:space="preserve">9.86452674865723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85578155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0918998718262</t>
+    <t xml:space="preserve">9.8557825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0919008255005</t>
   </si>
   <si>
     <t xml:space="preserve">10.3498830795288</t>
@@ -5276,16 +5276,16 @@
     <t xml:space="preserve">10.5072956085205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4766874313354</t>
+    <t xml:space="preserve">10.4766864776611</t>
   </si>
   <si>
     <t xml:space="preserve">10.4417066574097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.572883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5553932189941</t>
+    <t xml:space="preserve">10.5728845596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5553941726685</t>
   </si>
   <si>
     <t xml:space="preserve">10.5903739929199</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">10.7565326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5685119628906</t>
+    <t xml:space="preserve">10.5685110092163</t>
   </si>
   <si>
     <t xml:space="preserve">10.6297273635864</t>
@@ -5312,13 +5312,13 @@
     <t xml:space="preserve">10.4023542404175</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3542566299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1749792098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1356267929077</t>
+    <t xml:space="preserve">10.3542556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1356258392334</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656652450562</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">10.0438022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2012147903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2274513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3017835617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.363000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8002576828003</t>
+    <t xml:space="preserve">10.2012157440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2274503707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3017845153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3629999160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8002586364746</t>
   </si>
   <si>
     <t xml:space="preserve">11.3205947875977</t>
@@ -5348,10 +5348,10 @@
     <t xml:space="preserve">11.1981630325317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1063375473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.036376953125</t>
+    <t xml:space="preserve">11.1063385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0363779067993</t>
   </si>
   <si>
     <t xml:space="preserve">11.0145149230957</t>
@@ -5363,13 +5363,13 @@
     <t xml:space="preserve">11.0013961791992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0975933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2375164031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1894178390503</t>
+    <t xml:space="preserve">11.0975923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2375154495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.189416885376</t>
   </si>
   <si>
     <t xml:space="preserve">11.2025346755981</t>
@@ -5381,10 +5381,10 @@
     <t xml:space="preserve">11.2943592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4561443328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091842651367</t>
+    <t xml:space="preserve">11.4561452865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091833114624</t>
   </si>
   <si>
     <t xml:space="preserve">11.5916948318481</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">11.9152641296387</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0551872253418</t>
+    <t xml:space="preserve">12.0551862716675</t>
   </si>
   <si>
     <t xml:space="preserve">12.0770502090454</t>
@@ -5411,16 +5411,16 @@
     <t xml:space="preserve">11.9589900970459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0857944488525</t>
+    <t xml:space="preserve">12.0857934951782</t>
   </si>
   <si>
     <t xml:space="preserve">11.9764804840088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9852247238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8934030532837</t>
+    <t xml:space="preserve">11.9852256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8934020996094</t>
   </si>
   <si>
     <t xml:space="preserve">11.9371271133423</t>
@@ -5450,43 +5450,43 @@
     <t xml:space="preserve">11.7228708267212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7622241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6747732162476</t>
+    <t xml:space="preserve">11.762225151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6747722625732</t>
   </si>
   <si>
     <t xml:space="preserve">11.7840881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9633636474609</t>
+    <t xml:space="preserve">11.9633626937866</t>
   </si>
   <si>
     <t xml:space="preserve">12.2169723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2432060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3394031524658</t>
+    <t xml:space="preserve">12.2432069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3394041061401</t>
   </si>
   <si>
     <t xml:space="preserve">12.6367387771606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7766618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0565061569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2882528305054</t>
+    <t xml:space="preserve">12.7766609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0565071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2882518768311</t>
   </si>
   <si>
     <t xml:space="preserve">13.2751350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3319787979126</t>
+    <t xml:space="preserve">13.3319778442383</t>
   </si>
   <si>
     <t xml:space="preserve">13.422456741333</t>
@@ -5504,10 +5504,10 @@
     <t xml:space="preserve">13.2369766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2686433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1645927429199</t>
+    <t xml:space="preserve">13.2686424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1645936965942</t>
   </si>
   <si>
     <t xml:space="preserve">13.0786390304565</t>
@@ -5519,7 +5519,7 @@
     <t xml:space="preserve">13.1374502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469722747803</t>
+    <t xml:space="preserve">13.046971321106</t>
   </si>
   <si>
     <t xml:space="preserve">12.9655408859253</t>
@@ -5528,28 +5528,28 @@
     <t xml:space="preserve">13.0062561035156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9791126251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8298234939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.689582824707</t>
+    <t xml:space="preserve">12.9791135787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8298244476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6895818710327</t>
   </si>
   <si>
     <t xml:space="preserve">12.9700651168823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5176725387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2371912002563</t>
+    <t xml:space="preserve">12.5176734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.237190246582</t>
   </si>
   <si>
     <t xml:space="preserve">12.323145866394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3864803314209</t>
+    <t xml:space="preserve">12.3864793777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.2914772033691</t>
@@ -5591,16 +5591,16 @@
     <t xml:space="preserve">12.8162517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9836378097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0153036117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9248266220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.929349899292</t>
+    <t xml:space="preserve">12.9836368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.015305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.924825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9293489456177</t>
   </si>
   <si>
     <t xml:space="preserve">13.0424480438232</t>
@@ -5609,7 +5609,7 @@
     <t xml:space="preserve">13.0243520736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605440139771</t>
+    <t xml:space="preserve">13.0605449676514</t>
   </si>
   <si>
     <t xml:space="preserve">12.9745893478394</t>
@@ -5633,7 +5633,7 @@
     <t xml:space="preserve">13.0017328262329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7167263031006</t>
+    <t xml:space="preserve">12.7167253494263</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136228561401</t>
@@ -5642,25 +5642,25 @@
     <t xml:space="preserve">12.7031545639038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5764846801758</t>
+    <t xml:space="preserve">12.5764837265015</t>
   </si>
   <si>
     <t xml:space="preserve">12.5810079574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6941061019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6579141616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7438688278198</t>
+    <t xml:space="preserve">12.6941051483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6579151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7438697814941</t>
   </si>
   <si>
     <t xml:space="preserve">13.2912626266479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3500747680664</t>
+    <t xml:space="preserve">13.3500738143921</t>
   </si>
   <si>
     <t xml:space="preserve">13.4631719589233</t>
@@ -5669,10 +5669,10 @@
     <t xml:space="preserve">13.4767436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5898418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5400791168213</t>
+    <t xml:space="preserve">13.5898427963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.540078163147</t>
   </si>
   <si>
     <t xml:space="preserve">13.5717458724976</t>
@@ -5681,127 +5681,127 @@
     <t xml:space="preserve">13.5038871765137</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6938915252686</t>
+    <t xml:space="preserve">13.6938924789429</t>
   </si>
   <si>
     <t xml:space="preserve">13.8296089172363</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8748474121094</t>
+    <t xml:space="preserve">13.8748483657837</t>
   </si>
   <si>
     <t xml:space="preserve">13.6622247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5174579620361</t>
+    <t xml:space="preserve">13.5174589157104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6441278457642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5129346847534</t>
+    <t xml:space="preserve">13.5129356384277</t>
   </si>
   <si>
     <t xml:space="preserve">13.7210350036621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5084104537964</t>
+    <t xml:space="preserve">13.5084114074707</t>
   </si>
   <si>
     <t xml:space="preserve">13.2867393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3681697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4179334640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5265054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8793725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9155645370483</t>
+    <t xml:space="preserve">13.3681688308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.417932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5265064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8793716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.915563583374</t>
   </si>
   <si>
     <t xml:space="preserve">13.8024663925171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7979421615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7165107727051</t>
+    <t xml:space="preserve">13.7979412078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7165117263794</t>
   </si>
   <si>
     <t xml:space="preserve">13.9562788009644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9743738174438</t>
+    <t xml:space="preserve">13.9743747711182</t>
   </si>
   <si>
     <t xml:space="preserve">13.8657999038696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6350803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5581741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3772172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5807943344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6803207397461</t>
+    <t xml:space="preserve">13.6350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5581731796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.37721824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5807933807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6803197860718</t>
   </si>
   <si>
     <t xml:space="preserve">13.7074632644653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.793417930603</t>
+    <t xml:space="preserve">13.7934169769287</t>
   </si>
   <si>
     <t xml:space="preserve">13.8341331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9517545700073</t>
+    <t xml:space="preserve">13.9517555236816</t>
   </si>
   <si>
     <t xml:space="preserve">14.0693769454956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.159854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2005701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3543825149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5896263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4086713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2684288024902</t>
+    <t xml:space="preserve">14.1598539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.200569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3543834686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5896272659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.408670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2684297561646</t>
   </si>
   <si>
     <t xml:space="preserve">14.1055679321289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9608030319214</t>
+    <t xml:space="preserve">13.9608020782471</t>
   </si>
   <si>
     <t xml:space="preserve">13.8838958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7436532974243</t>
+    <t xml:space="preserve">13.7436542510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.7255582809448</t>
@@ -5816,10 +5816,10 @@
     <t xml:space="preserve">13.8522291183472</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8160381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8567514419556</t>
+    <t xml:space="preserve">13.8160371780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8567523956299</t>
   </si>
   <si>
     <t xml:space="preserve">14.0965204238892</t>
@@ -5828,7 +5828,7 @@
     <t xml:space="preserve">12.9474458694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0514965057373</t>
+    <t xml:space="preserve">13.051495552063</t>
   </si>
   <si>
     <t xml:space="preserve">13.0650672912598</t>
@@ -5855,13 +5855,13 @@
     <t xml:space="preserve">13.1652765274048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0289211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0994510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1370649337769</t>
+    <t xml:space="preserve">13.0289220809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0994501113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1370658874512</t>
   </si>
   <si>
     <t xml:space="preserve">12.9819040298462</t>
@@ -5909,7 +5909,7 @@
     <t xml:space="preserve">12.9395866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0054121017456</t>
+    <t xml:space="preserve">13.0054130554199</t>
   </si>
   <si>
     <t xml:space="preserve">13.1746807098389</t>
@@ -5927,7 +5927,7 @@
     <t xml:space="preserve">13.5179176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6119565963745</t>
+    <t xml:space="preserve">13.6119556427002</t>
   </si>
   <si>
     <t xml:space="preserve">13.5978498458862</t>
@@ -5942,7 +5942,7 @@
     <t xml:space="preserve">13.6025524139404</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8141355514526</t>
+    <t xml:space="preserve">13.814136505127</t>
   </si>
   <si>
     <t xml:space="preserve">14.1902875900269</t>
@@ -5954,7 +5954,7 @@
     <t xml:space="preserve">14.3783626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4724016189575</t>
+    <t xml:space="preserve">14.4724006652832</t>
   </si>
   <si>
     <t xml:space="preserve">14.4253816604614</t>
@@ -5966,13 +5966,13 @@
     <t xml:space="preserve">15.4880065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5162191390991</t>
+    <t xml:space="preserve">15.5162200927734</t>
   </si>
   <si>
     <t xml:space="preserve">14.839147567749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.904974937439</t>
+    <t xml:space="preserve">14.9049739837646</t>
   </si>
   <si>
     <t xml:space="preserve">15.0037136077881</t>
@@ -5987,22 +5987,22 @@
     <t xml:space="preserve">14.8250417709351</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9190788269043</t>
+    <t xml:space="preserve">14.9190797805786</t>
   </si>
   <si>
     <t xml:space="preserve">15.393970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4644985198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5632371902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9770021438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.906476020813</t>
+    <t xml:space="preserve">15.4644966125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5632362365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9770040512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9064750671387</t>
   </si>
   <si>
     <t xml:space="preserve">15.7889289855957</t>
@@ -6011,7 +6011,7 @@
     <t xml:space="preserve">15.7560138702393</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6713819503784</t>
+    <t xml:space="preserve">15.6713829040527</t>
   </si>
   <si>
     <t xml:space="preserve">15.8500518798828</t>
@@ -6020,31 +6020,31 @@
     <t xml:space="preserve">15.6431694030762</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5209197998047</t>
+    <t xml:space="preserve">15.520920753479</t>
   </si>
   <si>
     <t xml:space="preserve">15.5115175247192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5820446014404</t>
+    <t xml:space="preserve">15.5820455551147</t>
   </si>
   <si>
     <t xml:space="preserve">15.8218431472778</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0663375854492</t>
+    <t xml:space="preserve">16.0663394927979</t>
   </si>
   <si>
     <t xml:space="preserve">16.0757427215576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.127462387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2403106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8030347824097</t>
+    <t xml:space="preserve">16.1274642944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2403087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8030338287354</t>
   </si>
   <si>
     <t xml:space="preserve">16.2591171264648</t>
@@ -6059,7 +6059,7 @@
     <t xml:space="preserve">16.061637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6807832717896</t>
+    <t xml:space="preserve">15.6807842254639</t>
   </si>
   <si>
     <t xml:space="preserve">16.0710411071777</t>
@@ -6074,7 +6074,7 @@
     <t xml:space="preserve">16.4707012176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818639755249</t>
+    <t xml:space="preserve">16.8186416625977</t>
   </si>
   <si>
     <t xml:space="preserve">16.9973125457764</t>
@@ -6083,7 +6083,7 @@
     <t xml:space="preserve">16.9079761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7904300689697</t>
+    <t xml:space="preserve">16.7904281616211</t>
   </si>
   <si>
     <t xml:space="preserve">16.8374481201172</t>
@@ -6107,10 +6107,10 @@
     <t xml:space="preserve">16.4424896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9692983627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2640151977539</t>
+    <t xml:space="preserve">13.9692993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2640161514282</t>
   </si>
   <si>
     <t xml:space="preserve">13.7153968811035</t>
@@ -6119,7 +6119,7 @@
     <t xml:space="preserve">13.6542730331421</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3031320571899</t>
+    <t xml:space="preserve">14.3031330108643</t>
   </si>
   <si>
     <t xml:space="preserve">14.8062343597412</t>
@@ -6128,7 +6128,7 @@
     <t xml:space="preserve">14.7263021469116</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7404079437256</t>
+    <t xml:space="preserve">14.7404088973999</t>
   </si>
   <si>
     <t xml:space="preserve">15.1635780334473</t>
@@ -6137,7 +6137,7 @@
     <t xml:space="preserve">16.5412292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4095764160156</t>
+    <t xml:space="preserve">16.4095783233643</t>
   </si>
   <si>
     <t xml:space="preserve">17.2747249603271</t>
@@ -6567,6 +6567,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.7250003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7399997711182</t>
   </si>
 </sst>
 </file>
@@ -72451,7 +72454,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6911226852</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>1572278</v>
@@ -72472,6 +72475,32 @@
         <v>2184</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6911342593</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>2084863</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>16.9799995422363</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>16.4400005340576</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>16.625</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>16.7399997711182</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>2185</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MB.MI.xlsx
+++ b/data/MB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="2187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="2188">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,58 +44,58 @@
     <t xml:space="preserve">MB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00964689254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88411378860474</t>
+    <t xml:space="preserve">5.00964784622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88411331176758</t>
   </si>
   <si>
     <t xml:space="preserve">4.79069423675537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67391920089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64764499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75858020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81113004684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75274229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57174062728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35278749465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44328832626343</t>
+    <t xml:space="preserve">4.67391872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64764404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75858068466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81112909317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75274276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57174110412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35278797149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44328880310059</t>
   </si>
   <si>
     <t xml:space="preserve">4.2652063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50167560577393</t>
+    <t xml:space="preserve">4.50167608261108</t>
   </si>
   <si>
     <t xml:space="preserve">4.516273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37030410766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37322378158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13383531570435</t>
+    <t xml:space="preserve">4.37030363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44036912918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37322282791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13383483886719</t>
   </si>
   <si>
     <t xml:space="preserve">4.30023908615112</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">4.16594791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05209159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86817169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95283341407776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85357451438904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49449181556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29889392852783</t>
+    <t xml:space="preserve">4.05209302902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86817121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95283365249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8535749912262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4944920539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29889345169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.54704022407532</t>
@@ -128,67 +128,67 @@
     <t xml:space="preserve">3.36020064353943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4244270324707</t>
+    <t xml:space="preserve">3.42442655563354</t>
   </si>
   <si>
     <t xml:space="preserve">3.52368521690369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55579876899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62294387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51784658432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4886531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62878346443176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53828239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50033020973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54995965957642</t>
+    <t xml:space="preserve">3.55579853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62294340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51784682273865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48865270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62878370285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53828191757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50033044815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54996013641357</t>
   </si>
   <si>
     <t xml:space="preserve">3.640460729599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65505790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80394625663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94991421699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96451091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88860702514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77767109870911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82730007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83897805213928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89736533164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23601293563843</t>
+    <t xml:space="preserve">3.65505766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80394577980042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94991397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96451187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88860678672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77767086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82730031013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83897757530212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8973650932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23601245880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.27980375289917</t>
@@ -200,67 +200,67 @@
     <t xml:space="preserve">4.1542706489563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9002845287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93531680107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95575308799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88276863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85649418830872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74847674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77183198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69592833518982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66381549835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70176720619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6317024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66673493385315</t>
+    <t xml:space="preserve">3.90028476715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93531656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95575261116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8827691078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85649442672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74847769737244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77183270454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6959285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66381597518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70176696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63170218467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66673517227173</t>
   </si>
   <si>
     <t xml:space="preserve">3.48281455039978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68425059318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72512245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64629864692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83605909347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90612363815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84189772605896</t>
+    <t xml:space="preserve">3.68425107002258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72512269020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64629912376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8360583782196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90612387657166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84189701080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.08712482452393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09004354476929</t>
+    <t xml:space="preserve">4.0900444984436</t>
   </si>
   <si>
     <t xml:space="preserve">4.22141599655151</t>
@@ -281,109 +281,109 @@
     <t xml:space="preserve">3.91488146781921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75431632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72220325469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67549347877502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73971962928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76599335670471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8010265827179</t>
+    <t xml:space="preserve">3.7543158531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72220301628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67549276351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7397198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76599359512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80102610588074</t>
   </si>
   <si>
     <t xml:space="preserve">3.78934812545776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77475214004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84481620788574</t>
+    <t xml:space="preserve">3.77475190162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84481716156006</t>
   </si>
   <si>
     <t xml:space="preserve">3.8798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07544708251953</t>
+    <t xml:space="preserve">4.07544755935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.16886758804321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16010904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20973825454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19806098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99370503425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96743059158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86525249481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8506555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78351020812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5762345790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40107178688049</t>
+    <t xml:space="preserve">4.16010856628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20973873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1980619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99370455741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96743106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86525225639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85065579414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78350973129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57623410224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40107154846191</t>
   </si>
   <si>
     <t xml:space="preserve">3.27261924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36312007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35144257545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48573327064514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67841291427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72804188728333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70468688011169</t>
+    <t xml:space="preserve">3.36311984062195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3514416217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48573350906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67841196060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72804164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70468640327454</t>
   </si>
   <si>
     <t xml:space="preserve">3.10037636756897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70450878143311</t>
+    <t xml:space="preserve">2.70450925827026</t>
   </si>
   <si>
     <t xml:space="preserve">2.86098718643188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96024608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00987529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03906869888306</t>
+    <t xml:space="preserve">2.96024584770203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00987577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03906893730164</t>
   </si>
   <si>
     <t xml:space="preserve">2.91120076179504</t>
@@ -395,34 +395,34 @@
     <t xml:space="preserve">2.75121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84580659866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.088698387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3280873298645</t>
+    <t xml:space="preserve">2.84580683708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08869886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32808709144592</t>
   </si>
   <si>
     <t xml:space="preserve">3.35436153411865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45653963088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40691041946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46529746055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43318486213684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47405576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46821689605713</t>
+    <t xml:space="preserve">3.45653986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40691089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46529793739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43318438529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47405552864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46821784973145</t>
   </si>
   <si>
     <t xml:space="preserve">3.49741101264954</t>
@@ -431,88 +431,88 @@
     <t xml:space="preserve">3.41566848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5353627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4915714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65797686576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58791160583496</t>
+    <t xml:space="preserve">3.53536248207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49157309532166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65797662734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58791184425354</t>
   </si>
   <si>
     <t xml:space="preserve">3.29305458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30473232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59375071525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83313965797424</t>
+    <t xml:space="preserve">3.30473184585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59375047683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83313941955566</t>
   </si>
   <si>
     <t xml:space="preserve">3.80686473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76891326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78059053421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71928334236145</t>
+    <t xml:space="preserve">3.76891279220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78059005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71928381919861</t>
   </si>
   <si>
     <t xml:space="preserve">3.68717074394226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67257285118103</t>
+    <t xml:space="preserve">3.67257356643677</t>
   </si>
   <si>
     <t xml:space="preserve">3.57039523124695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6025083065033</t>
+    <t xml:space="preserve">3.60250926017761</t>
   </si>
   <si>
     <t xml:space="preserve">3.79226779937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76307463645935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81854224205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91196227073669</t>
+    <t xml:space="preserve">3.76307368278503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81854248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91196203231812</t>
   </si>
   <si>
     <t xml:space="preserve">4.00246286392212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94115591049194</t>
+    <t xml:space="preserve">3.9411563873291</t>
   </si>
   <si>
     <t xml:space="preserve">4.04917287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01414060592651</t>
+    <t xml:space="preserve">4.01414012908936</t>
   </si>
   <si>
     <t xml:space="preserve">3.92072010040283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60542845726013</t>
+    <t xml:space="preserve">3.60542821884155</t>
   </si>
   <si>
     <t xml:space="preserve">3.66089630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56163692474365</t>
+    <t xml:space="preserve">3.56163740158081</t>
   </si>
   <si>
     <t xml:space="preserve">3.64337944984436</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.64921832084656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37771654129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4215075969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35728073120117</t>
+    <t xml:space="preserve">3.37771677970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42150735855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35728144645691</t>
   </si>
   <si>
     <t xml:space="preserve">3.38063597679138</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">3.37187814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37479734420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55871772766113</t>
+    <t xml:space="preserve">3.37479710578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55871748924255</t>
   </si>
   <si>
     <t xml:space="preserve">3.65213775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5295238494873</t>
+    <t xml:space="preserve">3.52952456474304</t>
   </si>
   <si>
     <t xml:space="preserve">3.61710548400879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74263834953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85941386222839</t>
+    <t xml:space="preserve">3.74263858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85941362380981</t>
   </si>
   <si>
     <t xml:space="preserve">3.97035002708435</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">4.09296369552612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92363977432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71344494819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87401032447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0053825378418</t>
+    <t xml:space="preserve">3.92363929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71344566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87401056289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00538206100464</t>
   </si>
   <si>
     <t xml:space="preserve">3.99954319000244</t>
@@ -587,67 +587,67 @@
     <t xml:space="preserve">4.12507677078247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06376934051514</t>
+    <t xml:space="preserve">4.06377029418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.97326922416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81270384788513</t>
+    <t xml:space="preserve">3.81270289421082</t>
   </si>
   <si>
     <t xml:space="preserve">3.8583824634552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92537999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82792973518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77615976333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66652989387512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82183909416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96496844291687</t>
+    <t xml:space="preserve">3.92537975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86751866340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82792997360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616000175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66652894020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82183957099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96496796607971</t>
   </si>
   <si>
     <t xml:space="preserve">4.08982467651367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09591579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92233395576477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31213140487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.519211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64406824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51312017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53748273849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58620738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62884092330933</t>
+    <t xml:space="preserve">4.09591484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92233347892761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31213092803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51921081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64406776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5131196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53748226165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58620691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62884044647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.78415155410767</t>
@@ -659,46 +659,46 @@
     <t xml:space="preserve">4.75065279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82069444656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78719568252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77197027206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83287620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82983016967773</t>
+    <t xml:space="preserve">4.82069492340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78719663619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77196931838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83287572860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82983112335205</t>
   </si>
   <si>
     <t xml:space="preserve">4.76892423629761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73238134384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72324514389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82373952865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96382284164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99427556991577</t>
+    <t xml:space="preserve">4.73238182067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7232460975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82374000549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96382331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99427604675293</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98818492889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76283359527588</t>
+    <t xml:space="preserve">4.9881854057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76283407211304</t>
   </si>
   <si>
     <t xml:space="preserve">4.81460428237915</t>
@@ -710,61 +710,61 @@
     <t xml:space="preserve">4.69888257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88769102096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86941957473755</t>
+    <t xml:space="preserve">4.88769054412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86941909790039</t>
   </si>
   <si>
     <t xml:space="preserve">4.83592128753662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91205310821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84201145172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91509819030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18917465209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35057497024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18003845214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97904968261719</t>
+    <t xml:space="preserve">4.91205358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84201097488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91509914398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18917512893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35057544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1800389289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11608743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97905015945435</t>
   </si>
   <si>
     <t xml:space="preserve">4.84505701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96077871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75674343109131</t>
+    <t xml:space="preserve">4.960777759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75674295425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.65624904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79937696456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74456262588501</t>
+    <t xml:space="preserve">4.79937791824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74456214904785</t>
   </si>
   <si>
     <t xml:space="preserve">4.88464593887329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00036668777466</t>
+    <t xml:space="preserve">5.00036764144897</t>
   </si>
   <si>
     <t xml:space="preserve">4.97295951843262</t>
@@ -773,55 +773,55 @@
     <t xml:space="preserve">4.94555187225342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89987230300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85419273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80546760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66538429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53443717956543</t>
+    <t xml:space="preserve">4.89987182617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85419225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80546808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66538524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53443765640259</t>
   </si>
   <si>
     <t xml:space="preserve">4.56793546676636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60752391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78110551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82678508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99732112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03995561599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04909229278564</t>
+    <t xml:space="preserve">4.60752439498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82678556442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99732160568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03995513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04909133911133</t>
   </si>
   <si>
     <t xml:space="preserve">5.1221776008606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0704083442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05822706222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07345390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08258962631226</t>
+    <t xml:space="preserve">5.07040882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0582275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0734543800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08259010314941</t>
   </si>
   <si>
     <t xml:space="preserve">5.14349508285522</t>
@@ -836,46 +836,46 @@
     <t xml:space="preserve">5.15872192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13740539550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17090272903442</t>
+    <t xml:space="preserve">5.13740491867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17090320587158</t>
   </si>
   <si>
     <t xml:space="preserve">5.14654016494751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02168416976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0308198928833</t>
+    <t xml:space="preserve">5.02168369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03081941604614</t>
   </si>
   <si>
     <t xml:space="preserve">5.02777433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06127262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95773267745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90900850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68670177459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20135688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28053331375122</t>
+    <t xml:space="preserve">5.06127309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95773315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90900802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68670225143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20135593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28053379058838</t>
   </si>
   <si>
     <t xml:space="preserve">5.20744657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17394876480103</t>
+    <t xml:space="preserve">5.17394733428955</t>
   </si>
   <si>
     <t xml:space="preserve">5.37493753433228</t>
@@ -884,49 +884,49 @@
     <t xml:space="preserve">5.39016437530518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40843629837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51502084732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59115314483643</t>
+    <t xml:space="preserve">5.4084358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51502180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59115362167358</t>
   </si>
   <si>
     <t xml:space="preserve">5.5576548576355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54242897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52720165252686</t>
+    <t xml:space="preserve">5.54242849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52720212936401</t>
   </si>
   <si>
     <t xml:space="preserve">5.59724378585815</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56679105758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58810758590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43279790878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45106935501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49674844741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53633785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57288122177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54547309875488</t>
+    <t xml:space="preserve">5.56679058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58810806274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43279838562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45106983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49674892425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53633832931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57288074493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54547357559204</t>
   </si>
   <si>
     <t xml:space="preserve">5.52111101150513</t>
@@ -935,85 +935,85 @@
     <t xml:space="preserve">5.43888902664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26835203170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14045000076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16176700592041</t>
+    <t xml:space="preserve">5.26835250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1404504776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16176795959473</t>
   </si>
   <si>
     <t xml:space="preserve">5.07649898529053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09477043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18308401107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23180866241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21353721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26530742645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19222021102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21049165725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11304330825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03386497497559</t>
+    <t xml:space="preserve">5.0947699546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18308448791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23180913925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21353816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26530694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19221973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21049213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03386545181274</t>
   </si>
   <si>
     <t xml:space="preserve">5.17699337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1648120880127</t>
+    <t xml:space="preserve">5.16481161117554</t>
   </si>
   <si>
     <t xml:space="preserve">5.29575967788696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28357839584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26226234436035</t>
+    <t xml:space="preserve">5.28357887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26226186752319</t>
   </si>
   <si>
     <t xml:space="preserve">5.35971117019653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40539073944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33839416503906</t>
+    <t xml:space="preserve">5.4053897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33839464187622</t>
   </si>
   <si>
     <t xml:space="preserve">5.37189245223999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40234565734863</t>
+    <t xml:space="preserve">5.40234470367432</t>
   </si>
   <si>
     <t xml:space="preserve">5.46934175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52415657043457</t>
+    <t xml:space="preserve">5.52415704727173</t>
   </si>
   <si>
     <t xml:space="preserve">5.48152256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48456811904907</t>
+    <t xml:space="preserve">5.48456764221191</t>
   </si>
   <si>
     <t xml:space="preserve">5.30489587783813</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">5.32316780090332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38102865219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41757154464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3932089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36884593963623</t>
+    <t xml:space="preserve">5.381028175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41757202148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39320945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36884641647339</t>
   </si>
   <si>
     <t xml:space="preserve">5.35666608810425</t>
@@ -1040,28 +1040,28 @@
     <t xml:space="preserve">5.48761320114136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4784779548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4206166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29880571365356</t>
+    <t xml:space="preserve">5.47847747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42061710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29880475997925</t>
   </si>
   <si>
     <t xml:space="preserve">5.34752941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34143972396851</t>
+    <t xml:space="preserve">5.34143924713135</t>
   </si>
   <si>
     <t xml:space="preserve">5.28966951370239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19831085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25008106231689</t>
+    <t xml:space="preserve">5.19831037521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25008058547974</t>
   </si>
   <si>
     <t xml:space="preserve">5.14958572387695</t>
@@ -1070,82 +1070,82 @@
     <t xml:space="preserve">5.31403207778931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37798357009888</t>
+    <t xml:space="preserve">5.37798261642456</t>
   </si>
   <si>
     <t xml:space="preserve">5.32012224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32925844192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39625358581543</t>
+    <t xml:space="preserve">5.32925796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39625406265259</t>
   </si>
   <si>
     <t xml:space="preserve">5.4754319190979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46325159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4997935295105</t>
+    <t xml:space="preserve">5.4632511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49979448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.53024768829346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56374502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60333347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55156421661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57897186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55460977554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5820164680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5850625038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57592582702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62160587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71601009368896</t>
+    <t xml:space="preserve">5.56374549865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51806592941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60333442687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55156373977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57897233963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55461025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58201742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58506345748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57592678070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62160539627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71601057052612</t>
   </si>
   <si>
     <t xml:space="preserve">5.77387046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73123645782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81041288375854</t>
+    <t xml:space="preserve">5.73123598098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81041479110718</t>
   </si>
   <si>
     <t xml:space="preserve">5.87131977081299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84695816040039</t>
+    <t xml:space="preserve">5.84695768356323</t>
   </si>
   <si>
     <t xml:space="preserve">5.82868480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90177249908447</t>
+    <t xml:space="preserve">5.90177202224731</t>
   </si>
   <si>
     <t xml:space="preserve">5.89568185806274</t>
@@ -1154,55 +1154,55 @@
     <t xml:space="preserve">6.02053928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00531148910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01444911956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00835800170898</t>
+    <t xml:space="preserve">6.00531196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01444816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00835847854614</t>
   </si>
   <si>
     <t xml:space="preserve">5.99008655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02077722549438</t>
+    <t xml:space="preserve">6.02077627182007</t>
   </si>
   <si>
     <t xml:space="preserve">5.92586135864258</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99862861633301</t>
+    <t xml:space="preserve">5.99862909317017</t>
   </si>
   <si>
     <t xml:space="preserve">5.99546575546265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96066427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89105892181396</t>
+    <t xml:space="preserve">5.96066331863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89105939865112</t>
   </si>
   <si>
     <t xml:space="preserve">6.01761293411255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13467407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07456207275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11885452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08088874816895</t>
+    <t xml:space="preserve">6.13467454910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07456159591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11885547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08088827133179</t>
   </si>
   <si>
     <t xml:space="preserve">5.98913812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01128435134888</t>
+    <t xml:space="preserve">6.01128530502319</t>
   </si>
   <si>
     <t xml:space="preserve">6.09038066864014</t>
@@ -1211,43 +1211,43 @@
     <t xml:space="preserve">6.06823348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07139730453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04292345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03659582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9163703918457</t>
+    <t xml:space="preserve">6.07139778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04292297363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03659534454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91636943817139</t>
   </si>
   <si>
     <t xml:space="preserve">5.94800758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97648286819458</t>
+    <t xml:space="preserve">5.97648191452026</t>
   </si>
   <si>
     <t xml:space="preserve">6.0302677154541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05241441726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04925107955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98597431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93851661682129</t>
+    <t xml:space="preserve">6.05241394042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04925060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98597383499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
     <t xml:space="preserve">6.05874156951904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20111417770386</t>
+    <t xml:space="preserve">6.20111513137817</t>
   </si>
   <si>
     <t xml:space="preserve">6.18213224411011</t>
@@ -1256,133 +1256,133 @@
     <t xml:space="preserve">6.18529558181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17580461502075</t>
+    <t xml:space="preserve">6.17580413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.19478702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2738823890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35297918319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31184959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30868577957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26755475997925</t>
+    <t xml:space="preserve">6.27388286590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29919290542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35297870635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31184911727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30868482589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26755571365356</t>
   </si>
   <si>
     <t xml:space="preserve">6.22009754180908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23528337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15049409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19605207443237</t>
+    <t xml:space="preserve">6.23528385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15049362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19605255126953</t>
   </si>
   <si>
     <t xml:space="preserve">6.2567982673645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29349899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23781633377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05557823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15428972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10619974136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14922761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19858264923096</t>
+    <t xml:space="preserve">6.29349851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23781585693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05557727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15428924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10619926452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14922857284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19858312606812</t>
   </si>
   <si>
     <t xml:space="preserve">6.23654985427856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25300264358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22769069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2479395866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25933027267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18339729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24287796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25553274154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28970193862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20237922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11252737045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99989461898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09734058380127</t>
+    <t xml:space="preserve">6.25300168991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22769117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24794006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25932931900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18339776992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24287748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25553226470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28970146179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20238065719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11252689361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9998950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09734106063843</t>
   </si>
   <si>
     <t xml:space="preserve">6.22642517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24667358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24034738540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18086624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20744228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23908138275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18972539901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25806522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15808773040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04545497894287</t>
+    <t xml:space="preserve">6.24667310714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24034595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18086433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20744276046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23908042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18972444534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25806379318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15808725357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04545402526855</t>
   </si>
   <si>
     <t xml:space="preserve">6.00622224807739</t>
@@ -1391,85 +1391,85 @@
     <t xml:space="preserve">6.03532981872559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04165840148926</t>
+    <t xml:space="preserve">6.0416579246521</t>
   </si>
   <si>
     <t xml:space="preserve">6.06570291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13783836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13024377822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1998496055603</t>
+    <t xml:space="preserve">6.13783884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.130244731